--- a/EXCEL/2 - RFC PROGRESS.xlsx
+++ b/EXCEL/2 - RFC PROGRESS.xlsx
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G4" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H4" s="24" t="inlineStr">
@@ -1732,12 +1732,12 @@
       </c>
       <c r="G5" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H5" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I5" s="54" t="inlineStr">
@@ -1862,12 +1862,12 @@
       </c>
       <c r="G6" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H6" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I6" s="54" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="G7" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H7" s="24" t="inlineStr"/>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G8" s="27" t="inlineStr">
@@ -2126,9 +2126,9 @@
           <t>PS5 - Milestone F</t>
         </is>
       </c>
-      <c r="I8" s="69" t="inlineStr">
-        <is>
-          <t>68%</t>
+      <c r="I8" s="54" t="inlineStr">
+        <is>
+          <t>93%</t>
         </is>
       </c>
       <c r="J8" s="55" t="n">
@@ -2167,14 +2167,14 @@
         <v>28</v>
       </c>
       <c r="AI8" s="23" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AJ8" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AK8" s="26" t="inlineStr">
-        <is>
-          <t>68%</t>
+        <v>2</v>
+      </c>
+      <c r="AK8" s="29" t="inlineStr">
+        <is>
+          <t>93%</t>
         </is>
       </c>
       <c r="AL8" s="23" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="G9" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H9" s="24" t="inlineStr"/>
@@ -2376,7 +2376,7 @@
       <c r="H10" s="24" t="inlineStr"/>
       <c r="I10" s="69" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="J10" s="55" t="inlineStr">
@@ -2417,14 +2417,14 @@
         <v>132</v>
       </c>
       <c r="AI10" s="23" t="n">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="AJ10" s="23" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AK10" s="26" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="AL10" s="23" t="inlineStr">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="G13" s="27" t="inlineStr">
         <is>
-          <t>DONE(FULL)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H13" s="24" t="inlineStr">
         <is>
-          <t>DONE (PARTIAL)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I13" s="54" t="inlineStr">
@@ -2878,7 +2878,7 @@
       <c r="H14" s="24" t="inlineStr"/>
       <c r="I14" s="70" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="J14" s="55" t="n">
@@ -2917,14 +2917,14 @@
         <v>85</v>
       </c>
       <c r="AI14" s="23" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="AJ14" s="23" t="n">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="AK14" s="25" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="AL14" s="23" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="H17" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I17" s="54" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="J17" s="55" t="n">
@@ -3283,14 +3283,14 @@
         <v>151</v>
       </c>
       <c r="AI17" s="23" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AJ17" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AK17" s="29" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="AL17" s="23" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="H19" s="24" t="inlineStr">
         <is>
-          <t>DONE(Partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I19" s="54" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="H20" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I20" s="54" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="J20" s="55" t="n">
@@ -3665,14 +3665,14 @@
         <v>62</v>
       </c>
       <c r="AI20" s="23" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AJ20" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK20" s="29" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="AL20" s="23" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G21" s="27" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="H21" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I21" s="54" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="H23" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I23" s="54" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="H24" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I24" s="54" t="inlineStr">
@@ -4243,7 +4243,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F25" s="23" t="inlineStr"/>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="G25" s="27" t="inlineStr">
         <is>
           <t>-</t>
@@ -4372,9 +4376,9 @@
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr"/>
-      <c r="I26" s="69" t="inlineStr">
-        <is>
-          <t>63%</t>
+      <c r="I26" s="54" t="inlineStr">
+        <is>
+          <t>91%</t>
         </is>
       </c>
       <c r="J26" s="55" t="n">
@@ -4413,14 +4417,14 @@
         <v>35</v>
       </c>
       <c r="AI26" s="23" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AJ26" s="23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK26" s="26" t="inlineStr">
-        <is>
-          <t>63%</t>
+        <v>3</v>
+      </c>
+      <c r="AK26" s="29" t="inlineStr">
+        <is>
+          <t>91%</t>
         </is>
       </c>
       <c r="AL26" s="23" t="inlineStr">
@@ -4499,7 +4503,7 @@
       </c>
       <c r="H27" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I27" s="54" t="inlineStr">
@@ -5379,7 +5383,7 @@
       </c>
       <c r="H34" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I34" s="54" t="inlineStr">
@@ -6537,7 +6541,7 @@
       </c>
       <c r="H45" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I45" s="54" t="inlineStr">
@@ -6665,7 +6669,7 @@
       </c>
       <c r="H46" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I46" s="54" t="inlineStr">
@@ -6879,7 +6883,7 @@
       </c>
       <c r="H48" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I48" s="54" t="inlineStr">
@@ -8966,7 +8970,7 @@
       <c r="H66" s="24" t="inlineStr"/>
       <c r="I66" s="70" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="J66" s="55" t="n">
@@ -8994,25 +8998,25 @@
         <v>73</v>
       </c>
       <c r="R66" s="62" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="S66" s="72" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="AH66" s="27" t="n">
         <v>74</v>
       </c>
       <c r="AI66" s="23" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="AJ66" s="23" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="AK66" s="25" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="AL66" s="23" t="inlineStr">
@@ -10726,7 +10730,7 @@
       <c r="F82" s="23" t="inlineStr"/>
       <c r="G82" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H82" s="24" t="inlineStr"/>
@@ -10930,7 +10934,7 @@
       <c r="H84" s="24" t="inlineStr"/>
       <c r="I84" s="69" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="J84" s="55" t="n">
@@ -10969,14 +10973,14 @@
         <v>147</v>
       </c>
       <c r="AI84" s="23" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="AJ84" s="23" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="AK84" s="26" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="AL84" s="23" t="inlineStr">
@@ -11091,10 +11095,10 @@
         <v>223</v>
       </c>
       <c r="AI85" s="23" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AJ85" s="23" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK85" s="26" t="inlineStr">
         <is>
@@ -11174,7 +11178,7 @@
       <c r="H86" s="24" t="inlineStr"/>
       <c r="I86" s="69" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="J86" s="55" t="n">
@@ -11213,14 +11217,14 @@
         <v>220</v>
       </c>
       <c r="AI86" s="23" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AJ86" s="23" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AK86" s="26" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="AL86" s="23" t="inlineStr">
@@ -11335,10 +11339,10 @@
         <v>220</v>
       </c>
       <c r="AI87" s="23" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AJ87" s="23" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AK87" s="26" t="inlineStr">
         <is>
@@ -11418,7 +11422,7 @@
       <c r="H88" s="24" t="inlineStr"/>
       <c r="I88" s="69" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="J88" s="55" t="n">
@@ -11457,14 +11461,14 @@
         <v>48</v>
       </c>
       <c r="AI88" s="23" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AJ88" s="23" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AK88" s="26" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="AL88" s="23" t="inlineStr">
@@ -11662,7 +11666,7 @@
       <c r="H90" s="24" t="inlineStr"/>
       <c r="I90" s="69" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="J90" s="55" t="n">
@@ -11701,14 +11705,14 @@
         <v>123</v>
       </c>
       <c r="AI90" s="23" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AJ90" s="23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK90" s="26" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="AL90" s="23" t="inlineStr">
@@ -11784,7 +11788,7 @@
       <c r="H91" s="24" t="inlineStr"/>
       <c r="I91" s="69" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="J91" s="55" t="n">
@@ -11823,14 +11827,14 @@
         <v>14</v>
       </c>
       <c r="AI91" s="23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ91" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK91" s="26" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="AL91" s="23" t="inlineStr">
@@ -11904,14 +11908,10 @@
       </c>
       <c r="G92" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
-        </is>
-      </c>
-      <c r="H92" s="24" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="H92" s="24" t="inlineStr"/>
       <c r="I92" s="54" t="inlineStr">
         <is>
           <t>100%</t>
@@ -12036,7 +12036,7 @@
       <c r="H93" s="24" t="inlineStr"/>
       <c r="I93" s="69" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="J93" s="55" t="n">
@@ -12075,14 +12075,14 @@
         <v>104</v>
       </c>
       <c r="AI93" s="23" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AJ93" s="23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK93" s="26" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="AL93" s="23" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="G94" s="27" t="inlineStr">
         <is>
-          <t>DONE(FULL)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H94" s="24" t="inlineStr">
         <is>
-          <t>DONE (PARTIAL)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I94" s="54" t="inlineStr">
@@ -12254,7 +12254,7 @@
       <c r="AT94" s="67" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="53" t="inlineStr">
+      <c r="A95" s="68" t="inlineStr">
         <is>
           <t>PS5-28-05 - HP Relief Header</t>
         </is>
@@ -12286,17 +12286,17 @@
       </c>
       <c r="G95" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H95" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I95" s="54" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J95" s="55" t="n">
@@ -12335,14 +12335,14 @@
         <v>11</v>
       </c>
       <c r="AI95" s="23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ95" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK95" s="29" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="AL95" s="23" t="inlineStr">
@@ -12422,7 +12422,7 @@
       <c r="H96" s="24" t="inlineStr"/>
       <c r="I96" s="69" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="J96" s="55" t="n">
@@ -12461,14 +12461,14 @@
         <v>64</v>
       </c>
       <c r="AI96" s="23" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AJ96" s="23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AK96" s="26" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="AL96" s="23" t="inlineStr">
@@ -12544,7 +12544,7 @@
       <c r="H97" s="24" t="inlineStr"/>
       <c r="I97" s="54" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="J97" s="55" t="n">
@@ -12583,14 +12583,14 @@
         <v>278</v>
       </c>
       <c r="AI97" s="23" t="n">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="AJ97" s="23" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AK97" s="29" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="AL97" s="23" t="inlineStr">
@@ -13642,7 +13642,7 @@
       <c r="H106" s="24" t="inlineStr"/>
       <c r="I106" s="69" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="J106" s="55" t="n">
@@ -13681,14 +13681,14 @@
         <v>11</v>
       </c>
       <c r="AI106" s="23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ106" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK106" s="26" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="AL106" s="23" t="inlineStr">
@@ -13764,7 +13764,7 @@
       <c r="H107" s="24" t="inlineStr"/>
       <c r="I107" s="69" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="J107" s="55" t="n">
@@ -13803,14 +13803,14 @@
         <v>83</v>
       </c>
       <c r="AI107" s="23" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ107" s="23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK107" s="26" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="AL107" s="23" t="inlineStr">
@@ -14218,7 +14218,7 @@
       <c r="AT110" s="67" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="53" t="inlineStr">
+      <c r="A111" s="74" t="inlineStr">
         <is>
           <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
@@ -14248,14 +14248,14 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="G111" s="27" t="inlineStr">
-        <is>
-          <t>DONE(partial)</t>
+      <c r="G111" s="69" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="H111" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I111" s="69" t="inlineStr">
@@ -14279,7 +14279,7 @@
         <v>1</v>
       </c>
       <c r="O111" s="60" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P111" s="61" t="n">
         <v>0</v>
@@ -14296,10 +14296,10 @@
         </is>
       </c>
       <c r="AH111" s="27" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI111" s="23" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AJ111" s="23" t="n">
         <v>5</v>
@@ -14382,7 +14382,7 @@
       <c r="H112" s="24" t="inlineStr"/>
       <c r="I112" s="69" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="J112" s="55" t="n">
@@ -14421,14 +14421,14 @@
         <v>29</v>
       </c>
       <c r="AI112" s="23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ112" s="23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK112" s="26" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="AL112" s="23" t="inlineStr">
@@ -14504,7 +14504,7 @@
       <c r="H113" s="24" t="inlineStr"/>
       <c r="I113" s="69" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="J113" s="55" t="n">
@@ -14543,14 +14543,14 @@
         <v>17</v>
       </c>
       <c r="AI113" s="23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ113" s="23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK113" s="26" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="AL113" s="23" t="inlineStr">
@@ -14746,9 +14746,9 @@
         </is>
       </c>
       <c r="H115" s="24" t="inlineStr"/>
-      <c r="I115" s="69" t="inlineStr">
-        <is>
-          <t>83%</t>
+      <c r="I115" s="54" t="inlineStr">
+        <is>
+          <t>97%</t>
         </is>
       </c>
       <c r="J115" s="55" t="n">
@@ -14787,14 +14787,14 @@
         <v>58</v>
       </c>
       <c r="AI115" s="23" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="AJ115" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK115" s="26" t="inlineStr">
-        <is>
-          <t>83%</t>
+        <v>2</v>
+      </c>
+      <c r="AK115" s="29" t="inlineStr">
+        <is>
+          <t>97%</t>
         </is>
       </c>
       <c r="AL115" s="23" t="inlineStr">
@@ -14874,7 +14874,7 @@
       <c r="H116" s="24" t="inlineStr"/>
       <c r="I116" s="69" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="J116" s="55" t="n">
@@ -14913,14 +14913,14 @@
         <v>39</v>
       </c>
       <c r="AI116" s="23" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AJ116" s="23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK116" s="26" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="AL116" s="23" t="inlineStr">
@@ -14994,12 +14994,12 @@
       </c>
       <c r="G117" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H117" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I117" s="54" t="inlineStr">
@@ -15259,7 +15259,7 @@
       </c>
       <c r="H119" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I119" s="69" t="inlineStr">
@@ -15384,12 +15384,12 @@
       </c>
       <c r="G120" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H120" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I120" s="54" t="inlineStr">
@@ -15519,7 +15519,7 @@
       </c>
       <c r="H121" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I121" s="54" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="H122" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I122" s="69" t="inlineStr">
@@ -15758,12 +15758,12 @@
       </c>
       <c r="G123" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H123" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I123" s="54" t="inlineStr">
@@ -15895,7 +15895,7 @@
       </c>
       <c r="H124" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I124" s="54" t="inlineStr">
@@ -16017,7 +16017,7 @@
       </c>
       <c r="H125" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I125" s="69" t="inlineStr">
@@ -16134,12 +16134,12 @@
       </c>
       <c r="G126" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H126" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I126" s="54" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="H127" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I127" s="54" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="H128" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I128" s="69" t="inlineStr">
@@ -16508,17 +16508,17 @@
       </c>
       <c r="G129" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H129" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I129" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="J129" s="55" t="n">
@@ -16557,14 +16557,14 @@
         <v>169</v>
       </c>
       <c r="AI129" s="23" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AJ129" s="23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AK129" s="29" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="AL129" s="23" t="inlineStr">
@@ -16643,7 +16643,7 @@
       </c>
       <c r="H130" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I130" s="54" t="inlineStr">
@@ -16763,7 +16763,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H131" s="24" t="inlineStr"/>
+      <c r="H131" s="24" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
       <c r="I131" s="69" t="inlineStr">
         <is>
           <t>88%</t>
@@ -16884,7 +16888,7 @@
       <c r="H132" s="24" t="inlineStr"/>
       <c r="I132" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="J132" s="55" t="n">
@@ -16923,14 +16927,14 @@
         <v>199</v>
       </c>
       <c r="AI132" s="23" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AJ132" s="23" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AK132" s="29" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="AL132" s="23" t="inlineStr">
@@ -17236,9 +17240,9 @@
         </is>
       </c>
       <c r="H135" s="24" t="inlineStr"/>
-      <c r="I135" s="69" t="inlineStr">
-        <is>
-          <t>68%</t>
+      <c r="I135" s="54" t="inlineStr">
+        <is>
+          <t>96%</t>
         </is>
       </c>
       <c r="J135" s="55" t="n">
@@ -17277,14 +17281,14 @@
         <v>170</v>
       </c>
       <c r="AI135" s="23" t="n">
-        <v>116</v>
+        <v>163</v>
       </c>
       <c r="AJ135" s="23" t="n">
-        <v>54</v>
-      </c>
-      <c r="AK135" s="26" t="inlineStr">
-        <is>
-          <t>68%</t>
+        <v>7</v>
+      </c>
+      <c r="AK135" s="29" t="inlineStr">
+        <is>
+          <t>96%</t>
         </is>
       </c>
       <c r="AL135" s="23" t="inlineStr">
@@ -17362,9 +17366,9 @@
         </is>
       </c>
       <c r="H136" s="24" t="inlineStr"/>
-      <c r="I136" s="70" t="inlineStr">
-        <is>
-          <t>40%</t>
+      <c r="I136" s="69" t="inlineStr">
+        <is>
+          <t>60%</t>
         </is>
       </c>
       <c r="J136" s="55" t="n">
@@ -17403,14 +17407,14 @@
         <v>50</v>
       </c>
       <c r="AI136" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ136" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="AJ136" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK136" s="25" t="inlineStr">
-        <is>
-          <t>40%</t>
+      <c r="AK136" s="26" t="inlineStr">
+        <is>
+          <t>60%</t>
         </is>
       </c>
       <c r="AL136" s="23" t="inlineStr">
@@ -17599,7 +17603,7 @@
       </c>
       <c r="H138" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I138" s="69" t="inlineStr">
@@ -17726,7 +17730,7 @@
       </c>
       <c r="G139" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H139" s="24" t="inlineStr"/>
@@ -17852,12 +17856,12 @@
       </c>
       <c r="G140" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H140" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I140" s="54" t="inlineStr">
@@ -17982,12 +17986,12 @@
       </c>
       <c r="G141" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H141" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I141" s="54" t="inlineStr">
@@ -18112,12 +18116,12 @@
       </c>
       <c r="G142" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H142" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I142" s="54" t="inlineStr">
@@ -18242,12 +18246,12 @@
       </c>
       <c r="G143" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H143" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I143" s="54" t="inlineStr">
@@ -18377,7 +18381,7 @@
       </c>
       <c r="H144" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I144" s="54" t="inlineStr">
@@ -18502,12 +18506,12 @@
       </c>
       <c r="G145" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H145" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I145" s="54" t="inlineStr">
@@ -18632,12 +18636,12 @@
       </c>
       <c r="G146" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H146" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I146" s="54" t="inlineStr">
@@ -18762,12 +18766,12 @@
       </c>
       <c r="G147" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H147" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I147" s="54" t="inlineStr">
@@ -18892,12 +18896,12 @@
       </c>
       <c r="G148" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H148" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I148" s="54" t="inlineStr">
@@ -19022,12 +19026,12 @@
       </c>
       <c r="G149" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H149" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I149" s="54" t="inlineStr">
@@ -19152,12 +19156,12 @@
       </c>
       <c r="G150" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H150" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I150" s="54" t="inlineStr">
@@ -19283,7 +19287,7 @@
       </c>
       <c r="H151" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I151" s="54" t="inlineStr">
@@ -19404,12 +19408,12 @@
       <c r="F152" s="23" t="inlineStr"/>
       <c r="G152" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H152" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I152" s="54" t="inlineStr">
@@ -19534,12 +19538,12 @@
       </c>
       <c r="G153" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H153" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I153" s="54" t="inlineStr">
@@ -19664,12 +19668,12 @@
       </c>
       <c r="G154" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H154" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I154" s="54" t="inlineStr">
@@ -19794,12 +19798,12 @@
       </c>
       <c r="G155" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H155" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I155" s="54" t="inlineStr">
@@ -19924,12 +19928,12 @@
       </c>
       <c r="G156" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H156" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I156" s="54" t="inlineStr">
@@ -20060,7 +20064,7 @@
       <c r="H157" s="24" t="inlineStr"/>
       <c r="I157" s="69" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="J157" s="55" t="n">
@@ -20099,14 +20103,14 @@
         <v>34</v>
       </c>
       <c r="AI157" s="23" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AJ157" s="23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AK157" s="26" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="AL157" s="23" t="inlineStr">
@@ -20181,7 +20185,7 @@
       </c>
       <c r="H158" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I158" s="54" t="inlineStr">
@@ -20302,12 +20306,12 @@
       <c r="F159" s="23" t="inlineStr"/>
       <c r="G159" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H159" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I159" s="54" t="inlineStr">
@@ -20432,12 +20436,12 @@
       </c>
       <c r="G160" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H160" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I160" s="54" t="inlineStr">
@@ -20562,12 +20566,12 @@
       </c>
       <c r="G161" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H161" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I161" s="54" t="inlineStr">
@@ -20687,7 +20691,7 @@
       </c>
       <c r="F162" s="23" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G162" s="27" t="inlineStr">
@@ -20818,12 +20822,12 @@
       </c>
       <c r="G163" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H163" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I163" s="54" t="inlineStr">
@@ -21070,12 +21074,12 @@
       </c>
       <c r="G165" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H165" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I165" s="54" t="inlineStr">
@@ -21196,12 +21200,12 @@
       </c>
       <c r="G166" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H166" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I166" s="54" t="inlineStr">
@@ -21318,12 +21322,12 @@
       </c>
       <c r="G167" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H167" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I167" s="54" t="inlineStr">
@@ -21440,12 +21444,12 @@
       </c>
       <c r="G168" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H168" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I168" s="69" t="inlineStr">
@@ -21792,7 +21796,7 @@
       <c r="H171" s="24" t="inlineStr"/>
       <c r="I171" s="69" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="J171" s="55" t="n">
@@ -21831,14 +21835,14 @@
         <v>35</v>
       </c>
       <c r="AI171" s="23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ171" s="23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK171" s="26" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="AL171" s="23" t="inlineStr">
@@ -21904,12 +21908,12 @@
       </c>
       <c r="G172" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H172" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I172" s="54" t="inlineStr">
@@ -22031,7 +22035,7 @@
       </c>
       <c r="H173" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I173" s="54" t="inlineStr">
@@ -22116,7 +22120,7 @@
       <c r="AT173" s="67" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="53" t="inlineStr">
+      <c r="A174" s="68" t="inlineStr">
         <is>
           <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
@@ -22148,17 +22152,17 @@
       </c>
       <c r="G174" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H174" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I174" s="54" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J174" s="55" t="n">
@@ -22197,14 +22201,14 @@
         <v>67</v>
       </c>
       <c r="AI174" s="23" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AJ174" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK174" s="29" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="AL174" s="23" t="inlineStr">
@@ -22275,7 +22279,7 @@
       </c>
       <c r="H175" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I175" s="54" t="inlineStr">
@@ -22360,7 +22364,7 @@
       <c r="AT175" s="67" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="53" t="inlineStr">
+      <c r="A176" s="68" t="inlineStr">
         <is>
           <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
@@ -22392,17 +22396,17 @@
       </c>
       <c r="G176" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H176" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I176" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J176" s="55" t="n">
@@ -22441,14 +22445,14 @@
         <v>67</v>
       </c>
       <c r="AI176" s="23" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AJ176" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK176" s="29" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="AL176" s="23" t="inlineStr">
@@ -22519,7 +22523,7 @@
       </c>
       <c r="H177" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I177" s="54" t="inlineStr">
@@ -22636,12 +22640,12 @@
       </c>
       <c r="G178" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H178" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I178" s="54" t="inlineStr">
@@ -22763,7 +22767,7 @@
       </c>
       <c r="H179" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I179" s="54" t="inlineStr">
@@ -22882,7 +22886,7 @@
       <c r="H180" s="24" t="inlineStr"/>
       <c r="I180" s="54" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="J180" s="55" t="n">
@@ -22921,14 +22925,14 @@
         <v>67</v>
       </c>
       <c r="AI180" s="23" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AJ180" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK180" s="29" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="AL180" s="23" t="inlineStr">
@@ -23122,7 +23126,7 @@
       <c r="H182" s="24" t="inlineStr"/>
       <c r="I182" s="54" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="J182" s="55" t="n">
@@ -23161,14 +23165,14 @@
         <v>67</v>
       </c>
       <c r="AI182" s="23" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AJ182" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK182" s="29" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="AL182" s="23" t="inlineStr">
@@ -23360,9 +23364,9 @@
         </is>
       </c>
       <c r="H184" s="24" t="inlineStr"/>
-      <c r="I184" s="70" t="inlineStr">
-        <is>
-          <t>46%</t>
+      <c r="I184" s="69" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="J184" s="55" t="n">
@@ -23401,14 +23405,14 @@
         <v>67</v>
       </c>
       <c r="AI184" s="23" t="n">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="AJ184" s="23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK184" s="25" t="inlineStr">
-        <is>
-          <t>46%</t>
+        <v>8</v>
+      </c>
+      <c r="AK184" s="26" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="AL184" s="23" t="inlineStr">
@@ -23486,9 +23490,9 @@
         </is>
       </c>
       <c r="H185" s="24" t="inlineStr"/>
-      <c r="I185" s="70" t="inlineStr">
-        <is>
-          <t>41%</t>
+      <c r="I185" s="69" t="inlineStr">
+        <is>
+          <t>71%</t>
         </is>
       </c>
       <c r="J185" s="55" t="n">
@@ -23527,14 +23531,14 @@
         <v>34</v>
       </c>
       <c r="AI185" s="23" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AJ185" s="23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK185" s="25" t="inlineStr">
-        <is>
-          <t>41%</t>
+        <v>10</v>
+      </c>
+      <c r="AK185" s="26" t="inlineStr">
+        <is>
+          <t>71%</t>
         </is>
       </c>
       <c r="AL185" s="23" t="inlineStr">
@@ -23600,12 +23604,12 @@
       </c>
       <c r="G186" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H186" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I186" s="54" t="inlineStr">
@@ -23730,12 +23734,12 @@
       </c>
       <c r="G187" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H187" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I187" s="54" t="inlineStr">
@@ -23860,12 +23864,12 @@
       </c>
       <c r="G188" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H188" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I188" s="54" t="inlineStr">
@@ -23990,12 +23994,12 @@
       </c>
       <c r="G189" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H189" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I189" s="54" t="inlineStr">
@@ -24115,7 +24119,7 @@
       </c>
       <c r="F190" s="23" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G190" s="27" t="inlineStr">
@@ -24125,7 +24129,7 @@
       </c>
       <c r="H190" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I190" s="54" t="inlineStr">
@@ -24250,12 +24254,12 @@
       </c>
       <c r="G191" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H191" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I191" s="54" t="inlineStr">
@@ -24502,12 +24506,12 @@
       </c>
       <c r="G193" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H193" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I193" s="54" t="inlineStr">
@@ -24636,7 +24640,7 @@
       <c r="H194" s="24" t="inlineStr"/>
       <c r="I194" s="69" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="J194" s="55" t="n">
@@ -24675,14 +24679,14 @@
         <v>34</v>
       </c>
       <c r="AI194" s="23" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AJ194" s="23" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AK194" s="26" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="AL194" s="23" t="inlineStr">
@@ -24758,7 +24762,7 @@
       <c r="H195" s="24" t="inlineStr"/>
       <c r="I195" s="69" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="J195" s="55" t="n">
@@ -24797,14 +24801,14 @@
         <v>34</v>
       </c>
       <c r="AI195" s="23" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AJ195" s="23" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AK195" s="26" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="AL195" s="23" t="inlineStr">
@@ -25009,7 +25013,7 @@
       </c>
       <c r="H197" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I197" s="54" t="inlineStr">
@@ -25228,7 +25232,7 @@
       <c r="AT198" s="67" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="53" t="inlineStr">
+      <c r="A199" s="68" t="inlineStr">
         <is>
           <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
@@ -25260,17 +25264,17 @@
       </c>
       <c r="G199" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H199" s="24" t="inlineStr">
         <is>
-          <t>DONE(Partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I199" s="54" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J199" s="55" t="n">
@@ -25309,14 +25313,14 @@
         <v>67</v>
       </c>
       <c r="AI199" s="23" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AJ199" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK199" s="29" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="AL199" s="23" t="inlineStr">
@@ -25643,7 +25647,7 @@
       </c>
       <c r="H202" s="24" t="inlineStr">
         <is>
-          <t>DONE(FULL)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I202" s="54" t="inlineStr">
@@ -25773,7 +25777,7 @@
       </c>
       <c r="H203" s="24" t="inlineStr">
         <is>
-          <t>DONE(FULL)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I203" s="54" t="inlineStr">
@@ -26597,7 +26601,7 @@
       </c>
       <c r="H210" s="24" t="inlineStr">
         <is>
-          <t>DONE(FULL)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I210" s="54" t="inlineStr">
@@ -26849,7 +26853,7 @@
       </c>
       <c r="H212" s="24" t="inlineStr">
         <is>
-          <t>DONE (PARTIAL)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I212" s="70" t="inlineStr">
@@ -27357,12 +27361,12 @@
       </c>
       <c r="H216" s="24" t="inlineStr">
         <is>
-          <t>DONE (PARTIAL)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I216" s="70" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="J216" s="55" t="n">
@@ -27401,14 +27405,14 @@
         <v>39</v>
       </c>
       <c r="AI216" s="23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ216" s="23" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AK216" s="25" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="AL216" s="23" t="inlineStr">
@@ -28635,7 +28639,7 @@
       </c>
       <c r="H227" s="24" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I227" s="70" t="inlineStr">
@@ -28887,7 +28891,7 @@
       </c>
       <c r="H229" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I229" s="69" t="inlineStr">
@@ -29464,7 +29468,7 @@
       <c r="H234" s="24" t="inlineStr"/>
       <c r="I234" s="70" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="J234" s="55" t="n">
@@ -29503,14 +29507,14 @@
         <v>94</v>
       </c>
       <c r="AI234" s="23" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AJ234" s="23" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AK234" s="25" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="AL234" s="23" t="inlineStr">
@@ -29586,7 +29590,7 @@
       <c r="H235" s="24" t="inlineStr"/>
       <c r="I235" s="69" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="J235" s="55" t="n">
@@ -29625,14 +29629,14 @@
         <v>17</v>
       </c>
       <c r="AI235" s="23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ235" s="23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK235" s="26" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="AL235" s="23" t="inlineStr">
@@ -29792,7 +29796,7 @@
       <c r="H237" s="24" t="inlineStr"/>
       <c r="I237" s="69" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="J237" s="55" t="n">
@@ -29811,7 +29815,7 @@
         <v>2</v>
       </c>
       <c r="O237" s="60" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P237" s="61" t="n">
         <v>0</v>
@@ -29828,17 +29832,17 @@
         </is>
       </c>
       <c r="AH237" s="27" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AI237" s="23" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AJ237" s="23" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK237" s="26" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="AL237" s="23" t="inlineStr">
@@ -29916,7 +29920,7 @@
       <c r="H238" s="24" t="inlineStr"/>
       <c r="I238" s="69" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="J238" s="55" t="n">
@@ -29955,14 +29959,14 @@
         <v>64</v>
       </c>
       <c r="AI238" s="23" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AJ238" s="23" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AK238" s="26" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="AL238" s="23" t="inlineStr">
@@ -30042,7 +30046,7 @@
       <c r="H239" s="24" t="inlineStr"/>
       <c r="I239" s="69" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="J239" s="55" t="n">
@@ -30081,14 +30085,14 @@
         <v>62</v>
       </c>
       <c r="AI239" s="23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ239" s="23" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AK239" s="26" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="AL239" s="23" t="inlineStr">
@@ -30310,12 +30314,12 @@
       </c>
       <c r="G241" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H241" s="24" t="inlineStr">
         <is>
-          <t>DONE(Partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I241" s="54" t="inlineStr">
@@ -30447,7 +30451,7 @@
       </c>
       <c r="H242" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I242" s="54" t="inlineStr">
@@ -30585,7 +30589,7 @@
         <v>1</v>
       </c>
       <c r="O243" s="60" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P243" s="61" t="n">
         <v>0</v>
@@ -30602,13 +30606,13 @@
         </is>
       </c>
       <c r="AH243" s="27" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AI243" s="23" t="n">
         <v>66</v>
       </c>
       <c r="AJ243" s="23" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK243" s="26" t="inlineStr">
         <is>
@@ -30932,7 +30936,7 @@
       <c r="H246" s="24" t="inlineStr"/>
       <c r="I246" s="69" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="J246" s="55" t="n">
@@ -30951,7 +30955,7 @@
         <v>1</v>
       </c>
       <c r="O246" s="60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P246" s="61" t="n">
         <v>0</v>
@@ -30968,17 +30972,17 @@
         </is>
       </c>
       <c r="AH246" s="27" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AI246" s="23" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AJ246" s="23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK246" s="26" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="AL246" s="23" t="inlineStr">
@@ -31058,7 +31062,7 @@
       <c r="H247" s="24" t="inlineStr"/>
       <c r="I247" s="69" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="J247" s="55" t="n">
@@ -31097,14 +31101,14 @@
         <v>33</v>
       </c>
       <c r="AI247" s="23" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="AJ247" s="23" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AK247" s="26" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="AL247" s="23" t="inlineStr">
@@ -31178,17 +31182,17 @@
       </c>
       <c r="G248" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H248" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
-        </is>
-      </c>
-      <c r="I248" s="69" t="inlineStr">
-        <is>
-          <t>81%</t>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="I248" s="54" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="J248" s="55" t="n">
@@ -31227,14 +31231,14 @@
         <v>31</v>
       </c>
       <c r="AI248" s="23" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AJ248" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AK248" s="26" t="inlineStr">
-        <is>
-          <t>81%</t>
+        <v>3</v>
+      </c>
+      <c r="AK248" s="29" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="AL248" s="23" t="inlineStr">
@@ -31308,17 +31312,17 @@
       </c>
       <c r="G249" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H249" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I249" s="69" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="J249" s="55" t="n">
@@ -31357,14 +31361,14 @@
         <v>53</v>
       </c>
       <c r="AI249" s="23" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AJ249" s="23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK249" s="26" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="AL249" s="23" t="inlineStr">
@@ -31570,12 +31574,12 @@
       </c>
       <c r="G251" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H251" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I251" s="69" t="inlineStr">
@@ -31700,12 +31704,12 @@
       </c>
       <c r="G252" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H252" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I252" s="54" t="inlineStr">
@@ -31837,7 +31841,7 @@
       </c>
       <c r="H253" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I253" s="54" t="inlineStr">
@@ -31967,7 +31971,7 @@
       </c>
       <c r="H254" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I254" s="69" t="inlineStr">
@@ -32092,12 +32096,12 @@
       </c>
       <c r="G255" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H255" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I255" s="69" t="inlineStr">
@@ -32227,7 +32231,7 @@
       </c>
       <c r="H256" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I256" s="69" t="inlineStr">
@@ -32352,12 +32356,12 @@
       </c>
       <c r="G257" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H257" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I257" s="54" t="inlineStr">
@@ -32484,7 +32488,7 @@
       <c r="H258" s="24" t="inlineStr"/>
       <c r="I258" s="69" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="J258" s="55" t="n">
@@ -32523,14 +32527,14 @@
         <v>16</v>
       </c>
       <c r="AI258" s="23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ258" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK258" s="26" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="AL258" s="23" t="inlineStr">
@@ -32606,7 +32610,7 @@
       <c r="H259" s="24" t="inlineStr"/>
       <c r="I259" s="70" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="J259" s="55" t="n">
@@ -32645,14 +32649,14 @@
         <v>30</v>
       </c>
       <c r="AI259" s="23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ259" s="23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK259" s="25" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="AL259" s="23" t="inlineStr">
@@ -32850,7 +32854,7 @@
       <c r="H261" s="24" t="inlineStr"/>
       <c r="I261" s="69" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="J261" s="55" t="n">
@@ -32889,14 +32893,14 @@
         <v>25</v>
       </c>
       <c r="AI261" s="23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ261" s="23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK261" s="26" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="AL261" s="23" t="inlineStr">
@@ -32938,7 +32942,7 @@
       <c r="AT261" s="67" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="53" t="inlineStr">
+      <c r="A262" s="74" t="inlineStr">
         <is>
           <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
@@ -32964,14 +32968,14 @@
         </is>
       </c>
       <c r="F262" s="23" t="inlineStr"/>
-      <c r="G262" s="27" t="inlineStr">
-        <is>
-          <t>DONE(partial)</t>
+      <c r="G262" s="69" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="H262" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I262" s="69" t="inlineStr">
@@ -33098,7 +33102,7 @@
       <c r="H263" s="24" t="inlineStr"/>
       <c r="I263" s="70" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="J263" s="55" t="n">
@@ -33137,14 +33141,14 @@
         <v>69</v>
       </c>
       <c r="AI263" s="23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AJ263" s="23" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="AK263" s="25" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="AL263" s="23" t="inlineStr">
@@ -33220,7 +33224,7 @@
       <c r="H264" s="24" t="inlineStr"/>
       <c r="I264" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="J264" s="55" t="n">
@@ -33259,14 +33263,14 @@
         <v>71</v>
       </c>
       <c r="AI264" s="23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ264" s="23" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AK264" s="25" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="AL264" s="23" t="inlineStr">
@@ -33342,7 +33346,7 @@
       <c r="H265" s="24" t="inlineStr"/>
       <c r="I265" s="70" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="J265" s="55" t="n">
@@ -33381,14 +33385,14 @@
         <v>69</v>
       </c>
       <c r="AI265" s="23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AJ265" s="23" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="AK265" s="25" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="AL265" s="23" t="inlineStr">
@@ -33464,7 +33468,7 @@
       <c r="H266" s="24" t="inlineStr"/>
       <c r="I266" s="70" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="J266" s="55" t="n">
@@ -33503,14 +33507,14 @@
         <v>65</v>
       </c>
       <c r="AI266" s="23" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AJ266" s="23" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AK266" s="25" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="AL266" s="23" t="inlineStr">
@@ -33586,7 +33590,7 @@
       <c r="H267" s="24" t="inlineStr"/>
       <c r="I267" s="70" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="J267" s="55" t="n">
@@ -33625,14 +33629,14 @@
         <v>67</v>
       </c>
       <c r="AI267" s="23" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AJ267" s="23" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="AK267" s="25" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="AL267" s="23" t="inlineStr">
@@ -33708,7 +33712,7 @@
       <c r="H268" s="24" t="inlineStr"/>
       <c r="I268" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="J268" s="55" t="n">
@@ -33747,14 +33751,14 @@
         <v>75</v>
       </c>
       <c r="AI268" s="23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ268" s="23" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AK268" s="25" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="AL268" s="23" t="inlineStr">
@@ -33830,7 +33834,7 @@
       <c r="H269" s="24" t="inlineStr"/>
       <c r="I269" s="70" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="J269" s="55" t="n">
@@ -33869,14 +33873,14 @@
         <v>75</v>
       </c>
       <c r="AI269" s="23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AJ269" s="23" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AK269" s="25" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="AL269" s="23" t="inlineStr">
@@ -33952,7 +33956,7 @@
       <c r="H270" s="24" t="inlineStr"/>
       <c r="I270" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="J270" s="55" t="n">
@@ -33991,14 +33995,14 @@
         <v>75</v>
       </c>
       <c r="AI270" s="23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AJ270" s="23" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AK270" s="25" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="AL270" s="23" t="inlineStr">
@@ -34074,7 +34078,7 @@
       <c r="H271" s="24" t="inlineStr"/>
       <c r="I271" s="70" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="J271" s="55" t="n">
@@ -34113,14 +34117,14 @@
         <v>75</v>
       </c>
       <c r="AI271" s="23" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AJ271" s="23" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="AK271" s="25" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="AL271" s="23" t="inlineStr">
@@ -34196,7 +34200,7 @@
       <c r="H272" s="24" t="inlineStr"/>
       <c r="I272" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="J272" s="55" t="n">
@@ -34235,14 +34239,14 @@
         <v>71</v>
       </c>
       <c r="AI272" s="23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AJ272" s="23" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="AK272" s="25" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="AL272" s="23" t="inlineStr">
@@ -34318,7 +34322,7 @@
       <c r="H273" s="24" t="inlineStr"/>
       <c r="I273" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="J273" s="55" t="n">
@@ -34357,14 +34361,14 @@
         <v>71</v>
       </c>
       <c r="AI273" s="23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AJ273" s="23" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="AK273" s="25" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="AL273" s="23" t="inlineStr">
@@ -34440,7 +34444,7 @@
       <c r="H274" s="24" t="inlineStr"/>
       <c r="I274" s="70" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="J274" s="55" t="n">
@@ -34479,14 +34483,14 @@
         <v>81</v>
       </c>
       <c r="AI274" s="23" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="AJ274" s="23" t="n">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="AK274" s="25" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="AL274" s="23" t="inlineStr">
@@ -35414,12 +35418,12 @@
       </c>
       <c r="G282" s="27" t="inlineStr">
         <is>
-          <t>DONE(FULL)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H282" s="24" t="inlineStr">
         <is>
-          <t>DONE(FULL)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I282" s="54" t="inlineStr">
@@ -35546,11 +35550,11 @@
       <c r="H283" s="24" t="inlineStr"/>
       <c r="I283" s="70" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J283" s="55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K283" s="56" t="n">
         <v>2</v>
@@ -35582,17 +35586,17 @@
         </is>
       </c>
       <c r="AH283" s="27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI283" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ283" s="23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AK283" s="25" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="AL283" s="23" t="inlineStr">
@@ -35788,7 +35792,7 @@
       </c>
       <c r="G285" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H285" s="24" t="inlineStr"/>
@@ -35914,7 +35918,7 @@
       </c>
       <c r="G286" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H286" s="24" t="inlineStr"/>
@@ -36045,7 +36049,7 @@
       </c>
       <c r="H287" s="24" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I287" s="54" t="inlineStr">

--- a/EXCEL/2 - RFC PROGRESS.xlsx
+++ b/EXCEL/2 - RFC PROGRESS.xlsx
@@ -172,7 +172,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill/>
     </fill>
@@ -303,12 +303,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFfff8e1"/>
         <bgColor rgb="FFfff8e1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
-        <bgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -504,7 +498,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -518,6 +512,9 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -527,10 +524,10 @@
     <xf numFmtId="0" fontId="19" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -542,19 +539,16 @@
     <xf numFmtId="0" fontId="2" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -564,10 +558,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -579,21 +573,21 @@
     <xf numFmtId="0" fontId="10" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -683,13 +677,10 @@
     <xf numFmtId="0" fontId="11" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -707,10 +698,7 @@
     <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -722,13 +710,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -737,37 +719,37 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1209,51 +1191,51 @@
           <t>PS5 COMPLETION PLATFORM  |  2 · RFC PROGRESS</t>
         </is>
       </c>
-      <c r="B1" s="100" t="n"/>
-      <c r="C1" s="100" t="n"/>
-      <c r="D1" s="100" t="n"/>
-      <c r="E1" s="100" t="n"/>
-      <c r="F1" s="100" t="n"/>
-      <c r="G1" s="100" t="n"/>
-      <c r="H1" s="100" t="n"/>
-      <c r="I1" s="100" t="n"/>
-      <c r="J1" s="100" t="n"/>
-      <c r="K1" s="100" t="n"/>
-      <c r="L1" s="100" t="n"/>
-      <c r="M1" s="100" t="n"/>
-      <c r="N1" s="100" t="n"/>
-      <c r="O1" s="100" t="n"/>
-      <c r="P1" s="100" t="n"/>
-      <c r="Q1" s="100" t="n"/>
-      <c r="R1" s="100" t="n"/>
-      <c r="S1" s="100" t="n"/>
-      <c r="T1" s="100" t="n"/>
-      <c r="U1" s="100" t="n"/>
-      <c r="V1" s="100" t="n"/>
-      <c r="W1" s="100" t="n"/>
-      <c r="X1" s="100" t="n"/>
-      <c r="Y1" s="100" t="n"/>
-      <c r="Z1" s="100" t="n"/>
-      <c r="AA1" s="100" t="n"/>
-      <c r="AB1" s="100" t="n"/>
-      <c r="AC1" s="100" t="n"/>
-      <c r="AD1" s="100" t="n"/>
-      <c r="AE1" s="100" t="n"/>
-      <c r="AF1" s="100" t="n"/>
-      <c r="AG1" s="100" t="n"/>
-      <c r="AH1" s="100" t="n"/>
-      <c r="AI1" s="100" t="n"/>
-      <c r="AJ1" s="100" t="n"/>
-      <c r="AK1" s="100" t="n"/>
-      <c r="AL1" s="100" t="n"/>
-      <c r="AM1" s="100" t="n"/>
-      <c r="AN1" s="100" t="n"/>
-      <c r="AO1" s="100" t="n"/>
-      <c r="AP1" s="100" t="n"/>
-      <c r="AQ1" s="100" t="n"/>
-      <c r="AR1" s="100" t="n"/>
-      <c r="AS1" s="100" t="n"/>
-      <c r="AT1" s="101" t="n"/>
+      <c r="B1" s="96" t="n"/>
+      <c r="C1" s="96" t="n"/>
+      <c r="D1" s="96" t="n"/>
+      <c r="E1" s="96" t="n"/>
+      <c r="F1" s="96" t="n"/>
+      <c r="G1" s="96" t="n"/>
+      <c r="H1" s="96" t="n"/>
+      <c r="I1" s="96" t="n"/>
+      <c r="J1" s="96" t="n"/>
+      <c r="K1" s="96" t="n"/>
+      <c r="L1" s="96" t="n"/>
+      <c r="M1" s="96" t="n"/>
+      <c r="N1" s="96" t="n"/>
+      <c r="O1" s="96" t="n"/>
+      <c r="P1" s="96" t="n"/>
+      <c r="Q1" s="96" t="n"/>
+      <c r="R1" s="96" t="n"/>
+      <c r="S1" s="96" t="n"/>
+      <c r="T1" s="96" t="n"/>
+      <c r="U1" s="96" t="n"/>
+      <c r="V1" s="96" t="n"/>
+      <c r="W1" s="96" t="n"/>
+      <c r="X1" s="96" t="n"/>
+      <c r="Y1" s="96" t="n"/>
+      <c r="Z1" s="96" t="n"/>
+      <c r="AA1" s="96" t="n"/>
+      <c r="AB1" s="96" t="n"/>
+      <c r="AC1" s="96" t="n"/>
+      <c r="AD1" s="96" t="n"/>
+      <c r="AE1" s="96" t="n"/>
+      <c r="AF1" s="96" t="n"/>
+      <c r="AG1" s="96" t="n"/>
+      <c r="AH1" s="96" t="n"/>
+      <c r="AI1" s="96" t="n"/>
+      <c r="AJ1" s="96" t="n"/>
+      <c r="AK1" s="96" t="n"/>
+      <c r="AL1" s="96" t="n"/>
+      <c r="AM1" s="96" t="n"/>
+      <c r="AN1" s="96" t="n"/>
+      <c r="AO1" s="96" t="n"/>
+      <c r="AP1" s="96" t="n"/>
+      <c r="AQ1" s="96" t="n"/>
+      <c r="AR1" s="96" t="n"/>
+      <c r="AS1" s="96" t="n"/>
+      <c r="AT1" s="97" t="n"/>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
@@ -1585,7 +1567,7 @@
       </c>
       <c r="D4" s="23" t="inlineStr">
         <is>
-          <t>08-Sep-26</t>
+          <t>E,I,M,P</t>
         </is>
       </c>
       <c r="E4" s="23" t="inlineStr">
@@ -1605,7 +1587,7 @@
       </c>
       <c r="H4" s="24" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I4" s="54" t="inlineStr">
@@ -1628,10 +1610,8 @@
       <c r="N4" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="O4" s="60" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="O4" s="60" t="n">
+        <v>28</v>
       </c>
       <c r="P4" s="61" t="n">
         <v>0</v>
@@ -1681,11 +1661,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP4" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP4" s="65" t="inlineStr"/>
       <c r="AQ4" s="65" t="inlineStr">
         <is>
           <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
@@ -1696,8 +1672,8 @@
           <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
         </is>
       </c>
-      <c r="AS4" s="66" t="n"/>
-      <c r="AT4" s="67" t="inlineStr"/>
+      <c r="AS4" s="23" t="n"/>
+      <c r="AT4" s="66" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="53" t="inlineStr">
@@ -1811,14 +1787,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP5" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP5" s="65" t="inlineStr"/>
       <c r="AQ5" s="65" t="inlineStr">
         <is>
-          <t>EACOP(MR.BENHER TBC)-EXPECTED 19-08-2026</t>
+          <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
         </is>
       </c>
       <c r="AR5" s="23" t="inlineStr">
@@ -1827,7 +1799,7 @@
         </is>
       </c>
       <c r="AS5" s="23" t="n"/>
-      <c r="AT5" s="67" t="inlineStr"/>
+      <c r="AT5" s="66" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="53" t="inlineStr">
@@ -1941,11 +1913,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP6" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP6" s="65" t="inlineStr"/>
       <c r="AQ6" s="65" t="inlineStr">
         <is>
           <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
@@ -1957,10 +1925,10 @@
         </is>
       </c>
       <c r="AS6" s="23" t="n"/>
-      <c r="AT6" s="67" t="inlineStr"/>
+      <c r="AT6" s="66" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="68" t="inlineStr">
+      <c r="A7" s="67" t="inlineStr">
         <is>
           <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
         </is>
@@ -2067,11 +2035,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP7" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP7" s="65" t="inlineStr"/>
       <c r="AQ7" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -2083,7 +2047,7 @@
         </is>
       </c>
       <c r="AS7" s="23" t="n"/>
-      <c r="AT7" s="67" t="inlineStr"/>
+      <c r="AT7" s="66" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="53" t="inlineStr">
@@ -2121,11 +2085,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H8" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone F</t>
-        </is>
-      </c>
+      <c r="H8" s="24" t="inlineStr"/>
       <c r="I8" s="54" t="inlineStr">
         <is>
           <t>93%</t>
@@ -2197,11 +2157,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP8" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP8" s="65" t="inlineStr"/>
       <c r="AQ8" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -2213,10 +2169,10 @@
         </is>
       </c>
       <c r="AS8" s="23" t="n"/>
-      <c r="AT8" s="67" t="inlineStr"/>
+      <c r="AT8" s="66" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="68" t="inlineStr">
+      <c r="A9" s="67" t="inlineStr">
         <is>
           <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
@@ -2323,11 +2279,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP9" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP9" s="65" t="inlineStr"/>
       <c r="AQ9" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -2339,7 +2291,7 @@
         </is>
       </c>
       <c r="AS9" s="23" t="n"/>
-      <c r="AT9" s="67" t="inlineStr"/>
+      <c r="AT9" s="66" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="53" t="inlineStr">
@@ -2374,15 +2326,13 @@
         </is>
       </c>
       <c r="H10" s="24" t="inlineStr"/>
-      <c r="I10" s="69" t="inlineStr">
+      <c r="I10" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
       </c>
-      <c r="J10" s="55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="J10" s="55" t="n">
+        <v>0</v>
       </c>
       <c r="K10" s="56" t="n">
         <v>0</v>
@@ -2447,11 +2397,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP10" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP10" s="65" t="inlineStr"/>
       <c r="AQ10" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -2463,7 +2409,7 @@
         </is>
       </c>
       <c r="AS10" s="23" t="n"/>
-      <c r="AT10" s="67" t="inlineStr"/>
+      <c r="AT10" s="66" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="53" t="inlineStr">
@@ -2498,7 +2444,7 @@
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr"/>
-      <c r="I11" s="69" t="inlineStr">
+      <c r="I11" s="68" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
@@ -2569,11 +2515,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP11" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP11" s="65" t="inlineStr"/>
       <c r="AQ11" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -2585,10 +2527,10 @@
         </is>
       </c>
       <c r="AS11" s="23" t="n"/>
-      <c r="AT11" s="67" t="inlineStr"/>
+      <c r="AT11" s="66" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="68" t="inlineStr">
+      <c r="A12" s="67" t="inlineStr">
         <is>
           <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
@@ -2616,7 +2558,7 @@
       <c r="F12" s="23" t="inlineStr"/>
       <c r="G12" s="27" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H12" s="24" t="inlineStr"/>
@@ -2691,11 +2633,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP12" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP12" s="65" t="inlineStr"/>
       <c r="AQ12" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -2707,10 +2645,10 @@
         </is>
       </c>
       <c r="AS12" s="23" t="n"/>
-      <c r="AT12" s="67" t="inlineStr"/>
+      <c r="AT12" s="66" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="68" t="inlineStr">
+      <c r="A13" s="67" t="inlineStr">
         <is>
           <t>PS5-01-10 - Water Mist Package</t>
         </is>
@@ -2821,11 +2759,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP13" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP13" s="65" t="inlineStr"/>
       <c r="AQ13" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -2837,7 +2771,7 @@
         </is>
       </c>
       <c r="AS13" s="23" t="n"/>
-      <c r="AT13" s="67" t="inlineStr"/>
+      <c r="AT13" s="66" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="53" t="inlineStr">
@@ -2876,7 +2810,7 @@
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr"/>
-      <c r="I14" s="70" t="inlineStr">
+      <c r="I14" s="69" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -2947,15 +2881,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP14" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP14" s="65" t="inlineStr"/>
       <c r="AQ14" s="65" t="inlineStr"/>
       <c r="AR14" s="23" t="inlineStr"/>
       <c r="AS14" s="23" t="n"/>
-      <c r="AT14" s="67" t="inlineStr"/>
+      <c r="AT14" s="66" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="53" t="inlineStr">
@@ -2990,7 +2920,7 @@
         </is>
       </c>
       <c r="H15" s="24" t="inlineStr"/>
-      <c r="I15" s="70" t="inlineStr">
+      <c r="I15" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -3061,11 +2991,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP15" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP15" s="65" t="inlineStr"/>
       <c r="AQ15" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -3077,7 +3003,7 @@
         </is>
       </c>
       <c r="AS15" s="23" t="n"/>
-      <c r="AT15" s="67" t="inlineStr"/>
+      <c r="AT15" s="66" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="53" t="inlineStr">
@@ -3112,7 +3038,7 @@
         </is>
       </c>
       <c r="H16" s="24" t="inlineStr"/>
-      <c r="I16" s="70" t="inlineStr">
+      <c r="I16" s="69" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
@@ -3183,11 +3109,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP16" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP16" s="65" t="inlineStr"/>
       <c r="AQ16" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -3199,7 +3121,7 @@
         </is>
       </c>
       <c r="AS16" s="23" t="n"/>
-      <c r="AT16" s="67" t="inlineStr"/>
+      <c r="AT16" s="66" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="53" t="inlineStr">
@@ -3313,11 +3235,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP17" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP17" s="65" t="inlineStr"/>
       <c r="AQ17" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -3329,7 +3247,7 @@
         </is>
       </c>
       <c r="AS17" s="23" t="n"/>
-      <c r="AT17" s="67" t="inlineStr"/>
+      <c r="AT17" s="66" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="53" t="inlineStr">
@@ -3364,7 +3282,7 @@
         </is>
       </c>
       <c r="H18" s="24" t="inlineStr"/>
-      <c r="I18" s="70" t="inlineStr">
+      <c r="I18" s="69" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -3435,11 +3353,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP18" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP18" s="65" t="inlineStr"/>
       <c r="AQ18" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -3451,7 +3365,7 @@
         </is>
       </c>
       <c r="AS18" s="23" t="n"/>
-      <c r="AT18" s="67" t="inlineStr"/>
+      <c r="AT18" s="66" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="53" t="inlineStr">
@@ -3565,11 +3479,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP19" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP19" s="65" t="inlineStr"/>
       <c r="AQ19" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -3581,7 +3491,7 @@
         </is>
       </c>
       <c r="AS19" s="23" t="n"/>
-      <c r="AT19" s="67" t="inlineStr"/>
+      <c r="AT19" s="66" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="53" t="inlineStr">
@@ -3695,11 +3605,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP20" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP20" s="65" t="inlineStr"/>
       <c r="AQ20" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -3711,10 +3617,10 @@
         </is>
       </c>
       <c r="AS20" s="23" t="n"/>
-      <c r="AT20" s="67" t="inlineStr"/>
+      <c r="AT20" s="66" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="68" t="inlineStr">
+      <c r="A21" s="67" t="inlineStr">
         <is>
           <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
         </is>
@@ -3825,11 +3731,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP21" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP21" s="65" t="inlineStr"/>
       <c r="AQ21" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -3841,7 +3743,7 @@
         </is>
       </c>
       <c r="AS21" s="23" t="n"/>
-      <c r="AT21" s="67" t="inlineStr"/>
+      <c r="AT21" s="66" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="53" t="inlineStr">
@@ -3947,11 +3849,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP22" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP22" s="65" t="inlineStr"/>
       <c r="AQ22" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -3963,10 +3861,10 @@
         </is>
       </c>
       <c r="AS22" s="23" t="n"/>
-      <c r="AT22" s="67" t="inlineStr"/>
+      <c r="AT22" s="66" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="68" t="inlineStr">
+      <c r="A23" s="67" t="inlineStr">
         <is>
           <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
         </is>
@@ -4077,11 +3975,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP23" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP23" s="65" t="inlineStr"/>
       <c r="AQ23" s="65" t="inlineStr">
         <is>
           <t>Due to gland plate issue of SEA-0001 we cannot terminate the cablesof F&amp;G Instruments.</t>
@@ -4093,10 +3987,10 @@
         </is>
       </c>
       <c r="AS23" s="23" t="n"/>
-      <c r="AT23" s="67" t="inlineStr"/>
+      <c r="AT23" s="66" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="68" t="inlineStr">
+      <c r="A24" s="67" t="inlineStr">
         <is>
           <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
         </is>
@@ -4215,7 +4109,7 @@
       <c r="AQ24" s="65" t="inlineStr"/>
       <c r="AR24" s="23" t="inlineStr"/>
       <c r="AS24" s="23" t="n"/>
-      <c r="AT24" s="67" t="inlineStr"/>
+      <c r="AT24" s="66" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="53" t="inlineStr">
@@ -4325,11 +4219,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP25" s="65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="AP25" s="65" t="inlineStr"/>
       <c r="AQ25" s="65" t="inlineStr">
         <is>
           <t>PS5-03-GDIR-1101, PS5-03-GDIR-1102, PS5-03-GDIR-1103, PS5-03-GDIR-1104, PS5-03-GDIR-1106, PS5-03-GDIR-1107, PS5-03-GDIR-1108, PS5-03-GDIR-1109 INSTRUMENT Not arrived</t>
@@ -4341,7 +4231,7 @@
         </is>
       </c>
       <c r="AS25" s="23" t="n"/>
-      <c r="AT25" s="67" t="inlineStr"/>
+      <c r="AT25" s="66" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="53" t="inlineStr">
@@ -4447,11 +4337,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP26" s="65" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="AP26" s="65" t="inlineStr"/>
       <c r="AQ26" s="65" t="inlineStr">
         <is>
           <t>PS5-03-GDIR-1201, PS5-03-GDIR-1202, PS5-03-GDIR-1203, PS5-03-GDIR-1204 instrument not arrived</t>
@@ -4463,10 +4349,10 @@
         </is>
       </c>
       <c r="AS26" s="23" t="n"/>
-      <c r="AT26" s="67" t="inlineStr"/>
+      <c r="AT26" s="66" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="68" t="inlineStr">
+      <c r="A27" s="67" t="inlineStr">
         <is>
           <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
         </is>
@@ -4577,11 +4463,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP27" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP27" s="65" t="inlineStr"/>
       <c r="AQ27" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -4593,7 +4475,7 @@
         </is>
       </c>
       <c r="AS27" s="23" t="n"/>
-      <c r="AT27" s="67" t="inlineStr"/>
+      <c r="AT27" s="66" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="53" t="inlineStr">
@@ -4632,7 +4514,7 @@
         </is>
       </c>
       <c r="H28" s="24" t="inlineStr"/>
-      <c r="I28" s="70" t="inlineStr">
+      <c r="I28" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -4664,7 +4546,7 @@
       <c r="R28" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S28" s="71" t="inlineStr">
+      <c r="S28" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -4703,11 +4585,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP28" s="65" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
+      <c r="AP28" s="65" t="inlineStr"/>
       <c r="AQ28" s="65" t="inlineStr">
         <is>
           <t>cannot start termination due to unavailabiity of gland plate sketch.
@@ -4725,7 +4603,7 @@
         </is>
       </c>
       <c r="AS28" s="23" t="n"/>
-      <c r="AT28" s="67" t="inlineStr"/>
+      <c r="AT28" s="66" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="53" t="inlineStr">
@@ -4764,7 +4642,7 @@
         </is>
       </c>
       <c r="H29" s="24" t="inlineStr"/>
-      <c r="I29" s="70" t="inlineStr">
+      <c r="I29" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4835,11 +4713,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP29" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="AP29" s="65" t="inlineStr"/>
       <c r="AQ29" s="65" t="inlineStr">
         <is>
           <t>PS5-03-RDOS-1501/1502/1503 not arrived</t>
@@ -4851,7 +4725,7 @@
         </is>
       </c>
       <c r="AS29" s="23" t="n"/>
-      <c r="AT29" s="67" t="inlineStr"/>
+      <c r="AT29" s="66" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="53" t="inlineStr">
@@ -4890,7 +4764,7 @@
         </is>
       </c>
       <c r="H30" s="24" t="inlineStr"/>
-      <c r="I30" s="70" t="inlineStr">
+      <c r="I30" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4961,11 +4835,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP30" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="AP30" s="65" t="inlineStr"/>
       <c r="AQ30" s="65" t="inlineStr">
         <is>
           <t>PS5-03-RDOS-1601/1602/1603 not arrived yet</t>
@@ -4977,7 +4847,7 @@
         </is>
       </c>
       <c r="AS30" s="23" t="n"/>
-      <c r="AT30" s="67" t="inlineStr"/>
+      <c r="AT30" s="66" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="53" t="inlineStr">
@@ -5012,7 +4882,7 @@
         </is>
       </c>
       <c r="H31" s="24" t="inlineStr"/>
-      <c r="I31" s="70" t="inlineStr">
+      <c r="I31" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5083,11 +4953,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP31" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="AP31" s="65" t="inlineStr"/>
       <c r="AQ31" s="65" t="inlineStr">
         <is>
           <t>PS5-03-RDOS-1701, PS5-03-RDOS-1702, PS5-03-RDOS-1703 instrument not arrived</t>
@@ -5099,7 +4965,7 @@
         </is>
       </c>
       <c r="AS31" s="23" t="n"/>
-      <c r="AT31" s="67" t="inlineStr"/>
+      <c r="AT31" s="66" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="53" t="inlineStr">
@@ -5134,7 +5000,7 @@
         </is>
       </c>
       <c r="H32" s="24" t="inlineStr"/>
-      <c r="I32" s="70" t="inlineStr">
+      <c r="I32" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5205,11 +5071,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP32" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="AP32" s="65" t="inlineStr"/>
       <c r="AQ32" s="65" t="inlineStr">
         <is>
           <t>PS5-03-RDOS-1801, PS5-03-RDOS-1802, PS5-03-RDOS-1803 instrument not arrived</t>
@@ -5221,7 +5083,7 @@
         </is>
       </c>
       <c r="AS32" s="23" t="n"/>
-      <c r="AT32" s="67" t="inlineStr"/>
+      <c r="AT32" s="66" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="53" t="inlineStr">
@@ -5260,7 +5122,7 @@
         </is>
       </c>
       <c r="H33" s="24" t="inlineStr"/>
-      <c r="I33" s="70" t="inlineStr">
+      <c r="I33" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5331,11 +5193,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP33" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="AP33" s="65" t="inlineStr"/>
       <c r="AQ33" s="65" t="inlineStr">
         <is>
           <t>PS5-03-RDH-1901/1902/1903 not arrived</t>
@@ -5347,10 +5205,10 @@
         </is>
       </c>
       <c r="AS33" s="23" t="n"/>
-      <c r="AT33" s="67" t="inlineStr"/>
+      <c r="AT33" s="66" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="68" t="inlineStr">
+      <c r="A34" s="67" t="inlineStr">
         <is>
           <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
         </is>
@@ -5378,7 +5236,7 @@
       <c r="F34" s="23" t="inlineStr"/>
       <c r="G34" s="27" t="inlineStr">
         <is>
-          <t>07-Aug-26</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H34" s="24" t="inlineStr">
@@ -5457,11 +5315,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP34" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP34" s="65" t="inlineStr"/>
       <c r="AQ34" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -5473,7 +5327,7 @@
         </is>
       </c>
       <c r="AS34" s="23" t="n"/>
-      <c r="AT34" s="67" t="inlineStr"/>
+      <c r="AT34" s="66" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="53" t="inlineStr">
@@ -5508,7 +5362,7 @@
         </is>
       </c>
       <c r="H35" s="24" t="inlineStr"/>
-      <c r="I35" s="70" t="inlineStr">
+      <c r="I35" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5579,11 +5433,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP35" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="AP35" s="65" t="inlineStr"/>
       <c r="AQ35" s="65" t="inlineStr">
         <is>
           <t>PS5-03-RDOS-2101, PS5-03-RDOS-2102, PS5-03-RDOS-2103 not arrived</t>
@@ -5595,7 +5445,7 @@
         </is>
       </c>
       <c r="AS35" s="23" t="n"/>
-      <c r="AT35" s="67" t="inlineStr"/>
+      <c r="AT35" s="66" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="53" t="inlineStr">
@@ -5630,7 +5480,7 @@
         </is>
       </c>
       <c r="H36" s="24" t="inlineStr"/>
-      <c r="I36" s="70" t="inlineStr">
+      <c r="I36" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5701,11 +5551,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP36" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP36" s="65" t="inlineStr"/>
       <c r="AQ36" s="65" t="inlineStr">
         <is>
           <t>PS5-03-RDOS-G101A, PS5-03-RDOS-G101B
@@ -5719,7 +5565,7 @@
         </is>
       </c>
       <c r="AS36" s="23" t="n"/>
-      <c r="AT36" s="67" t="inlineStr"/>
+      <c r="AT36" s="66" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="53" t="inlineStr">
@@ -5803,7 +5649,7 @@
       <c r="AQ37" s="65" t="inlineStr"/>
       <c r="AR37" s="23" t="inlineStr"/>
       <c r="AS37" s="23" t="n"/>
-      <c r="AT37" s="67" t="inlineStr"/>
+      <c r="AT37" s="66" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="53" t="inlineStr">
@@ -5838,7 +5684,7 @@
         </is>
       </c>
       <c r="H38" s="24" t="inlineStr"/>
-      <c r="I38" s="70" t="inlineStr">
+      <c r="I38" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5909,11 +5755,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP38" s="65" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+      <c r="AP38" s="65" t="inlineStr"/>
       <c r="AQ38" s="65" t="inlineStr">
         <is>
           <t>all material not arrived</t>
@@ -5925,7 +5767,7 @@
         </is>
       </c>
       <c r="AS38" s="23" t="n"/>
-      <c r="AT38" s="67" t="inlineStr"/>
+      <c r="AT38" s="66" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="53" t="inlineStr">
@@ -5960,7 +5802,7 @@
         </is>
       </c>
       <c r="H39" s="24" t="inlineStr"/>
-      <c r="I39" s="70" t="inlineStr">
+      <c r="I39" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6031,11 +5873,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP39" s="65" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+      <c r="AP39" s="65" t="inlineStr"/>
       <c r="AQ39" s="65" t="inlineStr">
         <is>
           <t>all material not arrived</t>
@@ -6047,7 +5885,7 @@
         </is>
       </c>
       <c r="AS39" s="23" t="n"/>
-      <c r="AT39" s="67" t="inlineStr"/>
+      <c r="AT39" s="66" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="53" t="inlineStr">
@@ -6066,7 +5904,7 @@
         </is>
       </c>
       <c r="H40" s="24" t="inlineStr"/>
-      <c r="I40" s="70" t="inlineStr">
+      <c r="I40" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6098,7 +5936,7 @@
       <c r="R40" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S40" s="72" t="inlineStr">
+      <c r="S40" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6131,7 +5969,7 @@
       <c r="AQ40" s="65" t="inlineStr"/>
       <c r="AR40" s="23" t="inlineStr"/>
       <c r="AS40" s="23" t="n"/>
-      <c r="AT40" s="67" t="inlineStr"/>
+      <c r="AT40" s="66" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="53" t="inlineStr">
@@ -6166,7 +6004,7 @@
         </is>
       </c>
       <c r="H41" s="24" t="inlineStr"/>
-      <c r="I41" s="70" t="inlineStr">
+      <c r="I41" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6237,11 +6075,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP41" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP41" s="65" t="inlineStr"/>
       <c r="AQ41" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -6253,7 +6087,7 @@
         </is>
       </c>
       <c r="AS41" s="23" t="n"/>
-      <c r="AT41" s="67" t="inlineStr"/>
+      <c r="AT41" s="66" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="53" t="inlineStr">
@@ -6304,7 +6138,7 @@
       <c r="R42" s="62" t="n">
         <v>64</v>
       </c>
-      <c r="S42" s="73" t="inlineStr">
+      <c r="S42" s="72" t="inlineStr">
         <is>
           <t>98%</t>
         </is>
@@ -6337,7 +6171,7 @@
       <c r="AQ42" s="65" t="inlineStr"/>
       <c r="AR42" s="23" t="inlineStr"/>
       <c r="AS42" s="23" t="n"/>
-      <c r="AT42" s="67" t="inlineStr"/>
+      <c r="AT42" s="66" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="53" t="inlineStr">
@@ -6388,7 +6222,7 @@
       <c r="R43" s="62" t="n">
         <v>9</v>
       </c>
-      <c r="S43" s="73" t="inlineStr">
+      <c r="S43" s="72" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6421,7 +6255,7 @@
       <c r="AQ43" s="65" t="inlineStr"/>
       <c r="AR43" s="23" t="inlineStr"/>
       <c r="AS43" s="23" t="n"/>
-      <c r="AT43" s="67" t="inlineStr"/>
+      <c r="AT43" s="66" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="53" t="inlineStr">
@@ -6440,7 +6274,7 @@
         </is>
       </c>
       <c r="H44" s="24" t="inlineStr"/>
-      <c r="I44" s="69" t="inlineStr">
+      <c r="I44" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -6472,7 +6306,7 @@
       <c r="R44" s="62" t="n">
         <v>19</v>
       </c>
-      <c r="S44" s="73" t="inlineStr">
+      <c r="S44" s="72" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6505,10 +6339,10 @@
       <c r="AQ44" s="65" t="inlineStr"/>
       <c r="AR44" s="23" t="inlineStr"/>
       <c r="AS44" s="23" t="n"/>
-      <c r="AT44" s="67" t="inlineStr"/>
+      <c r="AT44" s="66" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="74" t="inlineStr">
+      <c r="A45" s="67" t="inlineStr">
         <is>
           <t>PS5-05-01 - Emergency Diesel Generator Package</t>
         </is>
@@ -6534,9 +6368,9 @@
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr"/>
-      <c r="G45" s="69" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="G45" s="27" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
       <c r="H45" s="24" t="inlineStr">
@@ -6587,65 +6421,59 @@
       <c r="AI45" s="23" t="n">
         <v>109</v>
       </c>
-      <c r="AJ45" s="23" t="inlineStr">
+      <c r="AJ45" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AL45" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM45" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN45" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AO45" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP45" s="65" t="inlineStr"/>
+      <c r="AQ45" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR45" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS45" s="23" t="n"/>
+      <c r="AT45" s="66" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="67" t="inlineStr">
+        <is>
+          <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AK45" s="29" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="AL45" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM45" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN45" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AO45" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP45" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ45" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR45" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS45" s="23" t="n"/>
-      <c r="AT45" s="67" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="75" t="inlineStr">
-        <is>
-          <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
-        </is>
-      </c>
-      <c r="B46" s="27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="C46" s="23" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -6662,9 +6490,9 @@
         </is>
       </c>
       <c r="F46" s="23" t="inlineStr"/>
-      <c r="G46" s="54" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
+      <c r="G46" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H46" s="24" t="inlineStr">
@@ -6743,11 +6571,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP46" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP46" s="65" t="inlineStr"/>
       <c r="AQ46" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -6759,7 +6583,7 @@
         </is>
       </c>
       <c r="AS46" s="23" t="n"/>
-      <c r="AT46" s="67" t="inlineStr"/>
+      <c r="AT46" s="66" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="53" t="inlineStr">
@@ -6778,7 +6602,7 @@
         </is>
       </c>
       <c r="H47" s="24" t="inlineStr"/>
-      <c r="I47" s="69" t="inlineStr">
+      <c r="I47" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -6810,7 +6634,7 @@
       <c r="R47" s="62" t="n">
         <v>12</v>
       </c>
-      <c r="S47" s="73" t="inlineStr">
+      <c r="S47" s="72" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6843,10 +6667,10 @@
       <c r="AQ47" s="65" t="inlineStr"/>
       <c r="AR47" s="23" t="inlineStr"/>
       <c r="AS47" s="23" t="n"/>
-      <c r="AT47" s="67" t="inlineStr"/>
+      <c r="AT47" s="66" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="68" t="inlineStr">
+      <c r="A48" s="67" t="inlineStr">
         <is>
           <t>PS5-06-02 - AC UPS - Power Generator Building</t>
         </is>
@@ -6957,11 +6781,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP48" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP48" s="65" t="inlineStr"/>
       <c r="AQ48" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -6973,7 +6793,7 @@
         </is>
       </c>
       <c r="AS48" s="23" t="n"/>
-      <c r="AT48" s="67" t="inlineStr"/>
+      <c r="AT48" s="66" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="53" t="inlineStr">
@@ -7008,7 +6828,7 @@
         </is>
       </c>
       <c r="H49" s="24" t="inlineStr"/>
-      <c r="I49" s="70" t="inlineStr">
+      <c r="I49" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7079,11 +6899,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP49" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP49" s="65" t="inlineStr"/>
       <c r="AQ49" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -7095,7 +6911,7 @@
         </is>
       </c>
       <c r="AS49" s="23" t="n"/>
-      <c r="AT49" s="67" t="inlineStr"/>
+      <c r="AT49" s="66" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="53" t="inlineStr">
@@ -7130,7 +6946,7 @@
         </is>
       </c>
       <c r="H50" s="24" t="inlineStr"/>
-      <c r="I50" s="70" t="inlineStr">
+      <c r="I50" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7201,11 +7017,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP50" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP50" s="65" t="inlineStr"/>
       <c r="AQ50" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -7217,7 +7029,7 @@
         </is>
       </c>
       <c r="AS50" s="23" t="n"/>
-      <c r="AT50" s="67" t="inlineStr"/>
+      <c r="AT50" s="66" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="53" t="inlineStr">
@@ -7252,7 +7064,7 @@
         </is>
       </c>
       <c r="H51" s="24" t="inlineStr"/>
-      <c r="I51" s="70" t="inlineStr">
+      <c r="I51" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7323,11 +7135,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP51" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP51" s="65" t="inlineStr"/>
       <c r="AQ51" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -7339,7 +7147,7 @@
         </is>
       </c>
       <c r="AS51" s="23" t="n"/>
-      <c r="AT51" s="67" t="inlineStr"/>
+      <c r="AT51" s="66" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="53" t="inlineStr">
@@ -7374,7 +7182,7 @@
         </is>
       </c>
       <c r="H52" s="24" t="inlineStr"/>
-      <c r="I52" s="70" t="inlineStr">
+      <c r="I52" s="69" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -7406,7 +7214,7 @@
       <c r="R52" s="62" t="n">
         <v>82</v>
       </c>
-      <c r="S52" s="72" t="inlineStr">
+      <c r="S52" s="71" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -7445,11 +7253,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP52" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP52" s="65" t="inlineStr"/>
       <c r="AQ52" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -7461,7 +7265,7 @@
         </is>
       </c>
       <c r="AS52" s="23" t="n"/>
-      <c r="AT52" s="67" t="inlineStr"/>
+      <c r="AT52" s="66" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="53" t="inlineStr">
@@ -7496,7 +7300,7 @@
         </is>
       </c>
       <c r="H53" s="24" t="inlineStr"/>
-      <c r="I53" s="70" t="inlineStr">
+      <c r="I53" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -7528,7 +7332,7 @@
       <c r="R53" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="S53" s="72" t="inlineStr">
+      <c r="S53" s="71" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -7567,11 +7371,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP53" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP53" s="65" t="inlineStr"/>
       <c r="AQ53" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -7583,7 +7383,7 @@
         </is>
       </c>
       <c r="AS53" s="23" t="n"/>
-      <c r="AT53" s="67" t="inlineStr"/>
+      <c r="AT53" s="66" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="53" t="inlineStr">
@@ -7602,7 +7402,7 @@
         </is>
       </c>
       <c r="H54" s="24" t="inlineStr"/>
-      <c r="I54" s="70" t="inlineStr">
+      <c r="I54" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7634,7 +7434,7 @@
       <c r="R54" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S54" s="72" t="inlineStr">
+      <c r="S54" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7667,7 +7467,7 @@
       <c r="AQ54" s="65" t="inlineStr"/>
       <c r="AR54" s="23" t="inlineStr"/>
       <c r="AS54" s="23" t="n"/>
-      <c r="AT54" s="67" t="inlineStr"/>
+      <c r="AT54" s="66" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="53" t="inlineStr">
@@ -7686,7 +7486,7 @@
         </is>
       </c>
       <c r="H55" s="24" t="inlineStr"/>
-      <c r="I55" s="70" t="inlineStr">
+      <c r="I55" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7718,7 +7518,7 @@
       <c r="R55" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S55" s="72" t="inlineStr">
+      <c r="S55" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7751,7 +7551,7 @@
       <c r="AQ55" s="65" t="inlineStr"/>
       <c r="AR55" s="23" t="inlineStr"/>
       <c r="AS55" s="23" t="n"/>
-      <c r="AT55" s="67" t="inlineStr"/>
+      <c r="AT55" s="66" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="53" t="inlineStr">
@@ -7786,7 +7586,7 @@
         </is>
       </c>
       <c r="H56" s="24" t="inlineStr"/>
-      <c r="I56" s="70" t="inlineStr">
+      <c r="I56" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -7857,11 +7657,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP56" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP56" s="65" t="inlineStr"/>
       <c r="AQ56" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -7873,7 +7669,7 @@
         </is>
       </c>
       <c r="AS56" s="23" t="n"/>
-      <c r="AT56" s="67" t="inlineStr"/>
+      <c r="AT56" s="66" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="53" t="inlineStr">
@@ -7908,7 +7704,7 @@
         </is>
       </c>
       <c r="H57" s="24" t="inlineStr"/>
-      <c r="I57" s="70" t="inlineStr">
+      <c r="I57" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7940,7 +7736,7 @@
       <c r="R57" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S57" s="72" t="inlineStr">
+      <c r="S57" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7979,11 +7775,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP57" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP57" s="65" t="inlineStr"/>
       <c r="AQ57" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -7995,7 +7787,7 @@
         </is>
       </c>
       <c r="AS57" s="23" t="n"/>
-      <c r="AT57" s="67" t="inlineStr"/>
+      <c r="AT57" s="66" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="53" t="inlineStr">
@@ -8030,7 +7822,7 @@
         </is>
       </c>
       <c r="H58" s="24" t="inlineStr"/>
-      <c r="I58" s="70" t="inlineStr">
+      <c r="I58" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8062,7 +7854,7 @@
       <c r="R58" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S58" s="72" t="inlineStr">
+      <c r="S58" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8101,11 +7893,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP58" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP58" s="65" t="inlineStr"/>
       <c r="AQ58" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8117,7 +7905,7 @@
         </is>
       </c>
       <c r="AS58" s="23" t="n"/>
-      <c r="AT58" s="67" t="inlineStr"/>
+      <c r="AT58" s="66" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="53" t="inlineStr">
@@ -8152,7 +7940,7 @@
         </is>
       </c>
       <c r="H59" s="24" t="inlineStr"/>
-      <c r="I59" s="70" t="inlineStr">
+      <c r="I59" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8184,7 +7972,7 @@
       <c r="R59" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S59" s="72" t="inlineStr">
+      <c r="S59" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8223,11 +8011,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP59" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP59" s="65" t="inlineStr"/>
       <c r="AQ59" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8239,7 +8023,7 @@
         </is>
       </c>
       <c r="AS59" s="23" t="n"/>
-      <c r="AT59" s="67" t="inlineStr"/>
+      <c r="AT59" s="66" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="53" t="inlineStr">
@@ -8274,7 +8058,7 @@
         </is>
       </c>
       <c r="H60" s="24" t="inlineStr"/>
-      <c r="I60" s="70" t="inlineStr">
+      <c r="I60" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8306,7 +8090,7 @@
       <c r="R60" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S60" s="72" t="inlineStr">
+      <c r="S60" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8345,11 +8129,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP60" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP60" s="65" t="inlineStr"/>
       <c r="AQ60" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8361,7 +8141,7 @@
         </is>
       </c>
       <c r="AS60" s="23" t="n"/>
-      <c r="AT60" s="67" t="inlineStr"/>
+      <c r="AT60" s="66" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="53" t="inlineStr">
@@ -8396,7 +8176,7 @@
         </is>
       </c>
       <c r="H61" s="24" t="inlineStr"/>
-      <c r="I61" s="70" t="inlineStr">
+      <c r="I61" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8428,7 +8208,7 @@
       <c r="R61" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S61" s="72" t="inlineStr">
+      <c r="S61" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8467,11 +8247,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP61" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP61" s="65" t="inlineStr"/>
       <c r="AQ61" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8483,7 +8259,7 @@
         </is>
       </c>
       <c r="AS61" s="23" t="n"/>
-      <c r="AT61" s="67" t="inlineStr"/>
+      <c r="AT61" s="66" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="53" t="inlineStr">
@@ -8518,7 +8294,7 @@
         </is>
       </c>
       <c r="H62" s="24" t="inlineStr"/>
-      <c r="I62" s="70" t="inlineStr">
+      <c r="I62" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8550,7 +8326,7 @@
       <c r="R62" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S62" s="72" t="inlineStr">
+      <c r="S62" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8589,11 +8365,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP62" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP62" s="65" t="inlineStr"/>
       <c r="AQ62" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8605,7 +8377,7 @@
         </is>
       </c>
       <c r="AS62" s="23" t="n"/>
-      <c r="AT62" s="67" t="inlineStr"/>
+      <c r="AT62" s="66" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="53" t="inlineStr">
@@ -8624,7 +8396,7 @@
         </is>
       </c>
       <c r="H63" s="24" t="inlineStr"/>
-      <c r="I63" s="69" t="inlineStr">
+      <c r="I63" s="68" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -8656,7 +8428,7 @@
       <c r="R63" s="62" t="n">
         <v>39</v>
       </c>
-      <c r="S63" s="71" t="inlineStr">
+      <c r="S63" s="70" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -8689,7 +8461,7 @@
       <c r="AQ63" s="65" t="inlineStr"/>
       <c r="AR63" s="23" t="inlineStr"/>
       <c r="AS63" s="23" t="n"/>
-      <c r="AT63" s="67" t="inlineStr"/>
+      <c r="AT63" s="66" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="53" t="inlineStr">
@@ -8724,7 +8496,7 @@
         </is>
       </c>
       <c r="H64" s="24" t="inlineStr"/>
-      <c r="I64" s="70" t="inlineStr">
+      <c r="I64" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8756,7 +8528,7 @@
       <c r="R64" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S64" s="72" t="inlineStr">
+      <c r="S64" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8795,11 +8567,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP64" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP64" s="65" t="inlineStr"/>
       <c r="AQ64" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8811,7 +8579,7 @@
         </is>
       </c>
       <c r="AS64" s="23" t="n"/>
-      <c r="AT64" s="67" t="inlineStr"/>
+      <c r="AT64" s="66" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="53" t="inlineStr">
@@ -8846,7 +8614,7 @@
         </is>
       </c>
       <c r="H65" s="24" t="inlineStr"/>
-      <c r="I65" s="70" t="inlineStr">
+      <c r="I65" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8878,7 +8646,7 @@
       <c r="R65" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S65" s="72" t="inlineStr">
+      <c r="S65" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8917,11 +8685,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP65" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP65" s="65" t="inlineStr"/>
       <c r="AQ65" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8933,7 +8697,7 @@
         </is>
       </c>
       <c r="AS65" s="23" t="n"/>
-      <c r="AT65" s="67" t="inlineStr"/>
+      <c r="AT65" s="66" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="53" t="inlineStr">
@@ -8968,7 +8732,7 @@
         </is>
       </c>
       <c r="H66" s="24" t="inlineStr"/>
-      <c r="I66" s="70" t="inlineStr">
+      <c r="I66" s="69" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -9000,7 +8764,7 @@
       <c r="R66" s="62" t="n">
         <v>22</v>
       </c>
-      <c r="S66" s="72" t="inlineStr">
+      <c r="S66" s="71" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -9039,11 +8803,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP66" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP66" s="65" t="inlineStr"/>
       <c r="AQ66" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -9055,7 +8815,7 @@
         </is>
       </c>
       <c r="AS66" s="23" t="n"/>
-      <c r="AT66" s="67" t="inlineStr"/>
+      <c r="AT66" s="66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="53" t="inlineStr">
@@ -9074,7 +8834,7 @@
         </is>
       </c>
       <c r="H67" s="24" t="inlineStr"/>
-      <c r="I67" s="70" t="inlineStr">
+      <c r="I67" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9106,7 +8866,7 @@
       <c r="R67" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S67" s="72" t="inlineStr">
+      <c r="S67" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9139,7 +8899,7 @@
       <c r="AQ67" s="65" t="inlineStr"/>
       <c r="AR67" s="23" t="inlineStr"/>
       <c r="AS67" s="23" t="n"/>
-      <c r="AT67" s="67" t="inlineStr"/>
+      <c r="AT67" s="66" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="53" t="inlineStr">
@@ -9174,7 +8934,7 @@
         </is>
       </c>
       <c r="H68" s="24" t="inlineStr"/>
-      <c r="I68" s="70" t="inlineStr">
+      <c r="I68" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9206,7 +8966,7 @@
       <c r="R68" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S68" s="72" t="inlineStr">
+      <c r="S68" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9245,11 +9005,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP68" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP68" s="65" t="inlineStr"/>
       <c r="AQ68" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -9261,7 +9017,7 @@
         </is>
       </c>
       <c r="AS68" s="23" t="n"/>
-      <c r="AT68" s="67" t="inlineStr"/>
+      <c r="AT68" s="66" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="53" t="inlineStr">
@@ -9296,7 +9052,7 @@
         </is>
       </c>
       <c r="H69" s="24" t="inlineStr"/>
-      <c r="I69" s="70" t="inlineStr">
+      <c r="I69" s="69" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -9328,7 +9084,7 @@
       <c r="R69" s="62" t="n">
         <v>10</v>
       </c>
-      <c r="S69" s="72" t="inlineStr">
+      <c r="S69" s="71" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -9367,11 +9123,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP69" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP69" s="65" t="inlineStr"/>
       <c r="AQ69" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -9383,7 +9135,7 @@
         </is>
       </c>
       <c r="AS69" s="23" t="n"/>
-      <c r="AT69" s="67" t="inlineStr"/>
+      <c r="AT69" s="66" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="53" t="inlineStr">
@@ -9418,7 +9170,7 @@
         </is>
       </c>
       <c r="H70" s="24" t="inlineStr"/>
-      <c r="I70" s="70" t="inlineStr">
+      <c r="I70" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9450,7 +9202,7 @@
       <c r="R70" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S70" s="72" t="inlineStr">
+      <c r="S70" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9489,11 +9241,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP70" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP70" s="65" t="inlineStr"/>
       <c r="AQ70" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -9505,7 +9253,7 @@
         </is>
       </c>
       <c r="AS70" s="23" t="n"/>
-      <c r="AT70" s="67" t="inlineStr"/>
+      <c r="AT70" s="66" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="53" t="inlineStr">
@@ -9524,7 +9272,7 @@
         </is>
       </c>
       <c r="H71" s="24" t="inlineStr"/>
-      <c r="I71" s="70" t="inlineStr">
+      <c r="I71" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9556,7 +9304,7 @@
       <c r="R71" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S71" s="72" t="inlineStr">
+      <c r="S71" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9589,7 +9337,7 @@
       <c r="AQ71" s="65" t="inlineStr"/>
       <c r="AR71" s="23" t="inlineStr"/>
       <c r="AS71" s="23" t="n"/>
-      <c r="AT71" s="67" t="inlineStr"/>
+      <c r="AT71" s="66" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="53" t="inlineStr">
@@ -9608,7 +9356,7 @@
         </is>
       </c>
       <c r="H72" s="24" t="inlineStr"/>
-      <c r="I72" s="70" t="inlineStr">
+      <c r="I72" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9640,7 +9388,7 @@
       <c r="R72" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S72" s="72" t="inlineStr">
+      <c r="S72" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9673,7 +9421,7 @@
       <c r="AQ72" s="65" t="inlineStr"/>
       <c r="AR72" s="23" t="inlineStr"/>
       <c r="AS72" s="23" t="n"/>
-      <c r="AT72" s="67" t="inlineStr"/>
+      <c r="AT72" s="66" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="53" t="inlineStr">
@@ -9708,7 +9456,7 @@
         </is>
       </c>
       <c r="H73" s="24" t="inlineStr"/>
-      <c r="I73" s="70" t="inlineStr">
+      <c r="I73" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9740,7 +9488,7 @@
       <c r="R73" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S73" s="72" t="inlineStr">
+      <c r="S73" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9779,11 +9527,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP73" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP73" s="65" t="inlineStr"/>
       <c r="AQ73" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -9795,7 +9539,7 @@
         </is>
       </c>
       <c r="AS73" s="23" t="n"/>
-      <c r="AT73" s="67" t="inlineStr"/>
+      <c r="AT73" s="66" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="53" t="inlineStr">
@@ -9830,7 +9574,7 @@
         </is>
       </c>
       <c r="H74" s="24" t="inlineStr"/>
-      <c r="I74" s="70" t="inlineStr">
+      <c r="I74" s="69" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -9862,7 +9606,7 @@
       <c r="R74" s="62" t="n">
         <v>31</v>
       </c>
-      <c r="S74" s="72" t="inlineStr">
+      <c r="S74" s="71" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
@@ -9901,11 +9645,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP74" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP74" s="65" t="inlineStr"/>
       <c r="AQ74" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -9917,7 +9657,7 @@
         </is>
       </c>
       <c r="AS74" s="23" t="n"/>
-      <c r="AT74" s="67" t="inlineStr"/>
+      <c r="AT74" s="66" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="53" t="inlineStr">
@@ -9936,7 +9676,7 @@
         </is>
       </c>
       <c r="H75" s="24" t="inlineStr"/>
-      <c r="I75" s="70" t="inlineStr">
+      <c r="I75" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9968,7 +9708,7 @@
       <c r="R75" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S75" s="72" t="inlineStr">
+      <c r="S75" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10001,7 +9741,7 @@
       <c r="AQ75" s="65" t="inlineStr"/>
       <c r="AR75" s="23" t="inlineStr"/>
       <c r="AS75" s="23" t="n"/>
-      <c r="AT75" s="67" t="inlineStr"/>
+      <c r="AT75" s="66" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="53" t="inlineStr">
@@ -10020,7 +9760,7 @@
         </is>
       </c>
       <c r="H76" s="24" t="inlineStr"/>
-      <c r="I76" s="70" t="inlineStr">
+      <c r="I76" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10052,7 +9792,7 @@
       <c r="R76" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S76" s="72" t="inlineStr">
+      <c r="S76" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10085,7 +9825,7 @@
       <c r="AQ76" s="65" t="inlineStr"/>
       <c r="AR76" s="23" t="inlineStr"/>
       <c r="AS76" s="23" t="n"/>
-      <c r="AT76" s="67" t="inlineStr"/>
+      <c r="AT76" s="66" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="53" t="inlineStr">
@@ -10120,7 +9860,7 @@
         </is>
       </c>
       <c r="H77" s="24" t="inlineStr"/>
-      <c r="I77" s="70" t="inlineStr">
+      <c r="I77" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10152,7 +9892,7 @@
       <c r="R77" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S77" s="72" t="inlineStr">
+      <c r="S77" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10191,11 +9931,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP77" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP77" s="65" t="inlineStr"/>
       <c r="AQ77" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -10207,7 +9943,7 @@
         </is>
       </c>
       <c r="AS77" s="23" t="n"/>
-      <c r="AT77" s="67" t="inlineStr"/>
+      <c r="AT77" s="66" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="53" t="inlineStr">
@@ -10242,7 +9978,7 @@
         </is>
       </c>
       <c r="H78" s="24" t="inlineStr"/>
-      <c r="I78" s="70" t="inlineStr">
+      <c r="I78" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10313,11 +10049,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP78" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP78" s="65" t="inlineStr"/>
       <c r="AQ78" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -10329,7 +10061,7 @@
         </is>
       </c>
       <c r="AS78" s="23" t="n"/>
-      <c r="AT78" s="67" t="inlineStr"/>
+      <c r="AT78" s="66" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="53" t="inlineStr">
@@ -10364,7 +10096,7 @@
         </is>
       </c>
       <c r="H79" s="24" t="inlineStr"/>
-      <c r="I79" s="70" t="inlineStr">
+      <c r="I79" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10435,11 +10167,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP79" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP79" s="65" t="inlineStr"/>
       <c r="AQ79" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -10451,7 +10179,7 @@
         </is>
       </c>
       <c r="AS79" s="23" t="n"/>
-      <c r="AT79" s="67" t="inlineStr"/>
+      <c r="AT79" s="66" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="53" t="inlineStr">
@@ -10486,7 +10214,7 @@
         </is>
       </c>
       <c r="H80" s="24" t="inlineStr"/>
-      <c r="I80" s="70" t="inlineStr">
+      <c r="I80" s="69" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -10518,7 +10246,7 @@
       <c r="R80" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S80" s="72" t="inlineStr">
+      <c r="S80" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10557,11 +10285,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP80" s="65" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
+      <c r="AP80" s="65" t="inlineStr"/>
       <c r="AQ80" s="65" t="inlineStr">
         <is>
           <t>54 IES (Local control switch not arrived) 
@@ -10577,7 +10301,7 @@
         </is>
       </c>
       <c r="AS80" s="23" t="n"/>
-      <c r="AT80" s="67" t="inlineStr"/>
+      <c r="AT80" s="66" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="53" t="inlineStr">
@@ -10612,7 +10336,7 @@
         </is>
       </c>
       <c r="H81" s="24" t="inlineStr"/>
-      <c r="I81" s="70" t="inlineStr">
+      <c r="I81" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10683,11 +10407,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP81" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP81" s="65" t="inlineStr"/>
       <c r="AQ81" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -10699,10 +10419,10 @@
         </is>
       </c>
       <c r="AS81" s="23" t="n"/>
-      <c r="AT81" s="67" t="inlineStr"/>
+      <c r="AT81" s="66" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="68" t="inlineStr">
+      <c r="A82" s="67" t="inlineStr">
         <is>
           <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
@@ -10805,15 +10525,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP82" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP82" s="65" t="inlineStr"/>
       <c r="AQ82" s="65" t="inlineStr"/>
       <c r="AR82" s="23" t="inlineStr"/>
       <c r="AS82" s="23" t="n"/>
-      <c r="AT82" s="67" t="inlineStr"/>
+      <c r="AT82" s="66" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="53" t="inlineStr">
@@ -10832,7 +10548,7 @@
         </is>
       </c>
       <c r="H83" s="24" t="inlineStr"/>
-      <c r="I83" s="69" t="inlineStr">
+      <c r="I83" s="68" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -10897,7 +10613,7 @@
       <c r="AQ83" s="65" t="inlineStr"/>
       <c r="AR83" s="23" t="inlineStr"/>
       <c r="AS83" s="23" t="n"/>
-      <c r="AT83" s="67" t="inlineStr"/>
+      <c r="AT83" s="66" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="53" t="inlineStr">
@@ -10932,7 +10648,7 @@
         </is>
       </c>
       <c r="H84" s="24" t="inlineStr"/>
-      <c r="I84" s="69" t="inlineStr">
+      <c r="I84" s="68" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -11003,11 +10719,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AP84" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP84" s="65" t="inlineStr"/>
       <c r="AQ84" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -11019,7 +10731,7 @@
         </is>
       </c>
       <c r="AS84" s="23" t="n"/>
-      <c r="AT84" s="67" t="inlineStr"/>
+      <c r="AT84" s="66" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="53" t="inlineStr">
@@ -11054,7 +10766,7 @@
         </is>
       </c>
       <c r="H85" s="24" t="inlineStr"/>
-      <c r="I85" s="69" t="inlineStr">
+      <c r="I85" s="68" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -11125,11 +10837,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP85" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP85" s="65" t="inlineStr"/>
       <c r="AQ85" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -11141,7 +10849,7 @@
         </is>
       </c>
       <c r="AS85" s="23" t="n"/>
-      <c r="AT85" s="67" t="inlineStr"/>
+      <c r="AT85" s="66" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="53" t="inlineStr">
@@ -11176,7 +10884,7 @@
         </is>
       </c>
       <c r="H86" s="24" t="inlineStr"/>
-      <c r="I86" s="69" t="inlineStr">
+      <c r="I86" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -11247,11 +10955,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP86" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP86" s="65" t="inlineStr"/>
       <c r="AQ86" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -11263,7 +10967,7 @@
         </is>
       </c>
       <c r="AS86" s="23" t="n"/>
-      <c r="AT86" s="67" t="inlineStr"/>
+      <c r="AT86" s="66" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="53" t="inlineStr">
@@ -11298,7 +11002,7 @@
         </is>
       </c>
       <c r="H87" s="24" t="inlineStr"/>
-      <c r="I87" s="69" t="inlineStr">
+      <c r="I87" s="68" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -11369,11 +11073,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP87" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP87" s="65" t="inlineStr"/>
       <c r="AQ87" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -11385,7 +11085,7 @@
         </is>
       </c>
       <c r="AS87" s="23" t="n"/>
-      <c r="AT87" s="67" t="inlineStr"/>
+      <c r="AT87" s="66" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="53" t="inlineStr">
@@ -11420,7 +11120,7 @@
         </is>
       </c>
       <c r="H88" s="24" t="inlineStr"/>
-      <c r="I88" s="69" t="inlineStr">
+      <c r="I88" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -11491,11 +11191,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP88" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP88" s="65" t="inlineStr"/>
       <c r="AQ88" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -11507,7 +11203,7 @@
         </is>
       </c>
       <c r="AS88" s="23" t="n"/>
-      <c r="AT88" s="67" t="inlineStr"/>
+      <c r="AT88" s="66" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="53" t="inlineStr">
@@ -11542,7 +11238,7 @@
         </is>
       </c>
       <c r="H89" s="24" t="inlineStr"/>
-      <c r="I89" s="69" t="inlineStr">
+      <c r="I89" s="68" t="inlineStr">
         <is>
           <t>57%</t>
         </is>
@@ -11613,11 +11309,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP89" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP89" s="65" t="inlineStr"/>
       <c r="AQ89" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -11629,7 +11321,7 @@
         </is>
       </c>
       <c r="AS89" s="23" t="n"/>
-      <c r="AT89" s="67" t="inlineStr"/>
+      <c r="AT89" s="66" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="53" t="inlineStr">
@@ -11664,7 +11356,7 @@
         </is>
       </c>
       <c r="H90" s="24" t="inlineStr"/>
-      <c r="I90" s="69" t="inlineStr">
+      <c r="I90" s="68" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -11735,11 +11427,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP90" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP90" s="65" t="inlineStr"/>
       <c r="AQ90" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -11751,7 +11439,7 @@
         </is>
       </c>
       <c r="AS90" s="23" t="n"/>
-      <c r="AT90" s="67" t="inlineStr"/>
+      <c r="AT90" s="66" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="53" t="inlineStr">
@@ -11786,7 +11474,7 @@
         </is>
       </c>
       <c r="H91" s="24" t="inlineStr"/>
-      <c r="I91" s="69" t="inlineStr">
+      <c r="I91" s="68" t="inlineStr">
         <is>
           <t>79%</t>
         </is>
@@ -11857,11 +11545,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP91" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP91" s="65" t="inlineStr"/>
       <c r="AQ91" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -11873,10 +11557,10 @@
         </is>
       </c>
       <c r="AS91" s="23" t="n"/>
-      <c r="AT91" s="67" t="inlineStr"/>
+      <c r="AT91" s="66" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="68" t="inlineStr">
+      <c r="A92" s="67" t="inlineStr">
         <is>
           <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
@@ -11983,11 +11667,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP92" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP92" s="65" t="inlineStr"/>
       <c r="AQ92" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -11999,7 +11679,7 @@
         </is>
       </c>
       <c r="AS92" s="23" t="n"/>
-      <c r="AT92" s="67" t="inlineStr"/>
+      <c r="AT92" s="66" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="53" t="inlineStr">
@@ -12034,7 +11714,7 @@
         </is>
       </c>
       <c r="H93" s="24" t="inlineStr"/>
-      <c r="I93" s="69" t="inlineStr">
+      <c r="I93" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -12105,11 +11785,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP93" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP93" s="65" t="inlineStr"/>
       <c r="AQ93" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -12121,7 +11797,7 @@
         </is>
       </c>
       <c r="AS93" s="23" t="n"/>
-      <c r="AT93" s="67" t="inlineStr"/>
+      <c r="AT93" s="66" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="53" t="inlineStr">
@@ -12235,11 +11911,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP94" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="AP94" s="65" t="inlineStr"/>
       <c r="AQ94" s="65" t="inlineStr">
         <is>
           <t>3 Cables cannot be terminated due to rusty heater</t>
@@ -12251,10 +11923,10 @@
         </is>
       </c>
       <c r="AS94" s="23" t="n"/>
-      <c r="AT94" s="67" t="inlineStr"/>
+      <c r="AT94" s="66" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="68" t="inlineStr">
+      <c r="A95" s="67" t="inlineStr">
         <is>
           <t>PS5-28-05 - HP Relief Header</t>
         </is>
@@ -12365,11 +12037,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP95" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP95" s="65" t="inlineStr"/>
       <c r="AQ95" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -12381,7 +12049,7 @@
         </is>
       </c>
       <c r="AS95" s="23" t="n"/>
-      <c r="AT95" s="67" t="inlineStr"/>
+      <c r="AT95" s="66" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="53" t="inlineStr">
@@ -12420,7 +12088,7 @@
         </is>
       </c>
       <c r="H96" s="24" t="inlineStr"/>
-      <c r="I96" s="69" t="inlineStr">
+      <c r="I96" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -12491,11 +12159,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP96" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP96" s="65" t="inlineStr"/>
       <c r="AQ96" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -12507,7 +12171,7 @@
         </is>
       </c>
       <c r="AS96" s="23" t="n"/>
-      <c r="AT96" s="67" t="inlineStr"/>
+      <c r="AT96" s="66" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="53" t="inlineStr">
@@ -12613,11 +12277,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP97" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP97" s="65" t="inlineStr"/>
       <c r="AQ97" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -12629,7 +12289,7 @@
         </is>
       </c>
       <c r="AS97" s="23" t="n"/>
-      <c r="AT97" s="67" t="inlineStr"/>
+      <c r="AT97" s="66" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="53" t="inlineStr">
@@ -12664,7 +12324,7 @@
         </is>
       </c>
       <c r="H98" s="24" t="inlineStr"/>
-      <c r="I98" s="70" t="inlineStr">
+      <c r="I98" s="69" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -12735,11 +12395,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP98" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP98" s="65" t="inlineStr"/>
       <c r="AQ98" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -12751,7 +12407,7 @@
         </is>
       </c>
       <c r="AS98" s="23" t="n"/>
-      <c r="AT98" s="67" t="inlineStr"/>
+      <c r="AT98" s="66" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="53" t="inlineStr">
@@ -12786,7 +12442,7 @@
         </is>
       </c>
       <c r="H99" s="24" t="inlineStr"/>
-      <c r="I99" s="69" t="inlineStr">
+      <c r="I99" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -12857,11 +12513,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP99" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP99" s="65" t="inlineStr"/>
       <c r="AQ99" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -12873,7 +12525,7 @@
         </is>
       </c>
       <c r="AS99" s="23" t="n"/>
-      <c r="AT99" s="67" t="inlineStr"/>
+      <c r="AT99" s="66" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="53" t="inlineStr">
@@ -12908,7 +12560,7 @@
         </is>
       </c>
       <c r="H100" s="24" t="inlineStr"/>
-      <c r="I100" s="70" t="inlineStr">
+      <c r="I100" s="69" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -12979,11 +12631,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP100" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP100" s="65" t="inlineStr"/>
       <c r="AQ100" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -12995,7 +12643,7 @@
         </is>
       </c>
       <c r="AS100" s="23" t="n"/>
-      <c r="AT100" s="67" t="inlineStr"/>
+      <c r="AT100" s="66" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="53" t="inlineStr">
@@ -13030,7 +12678,7 @@
         </is>
       </c>
       <c r="H101" s="24" t="inlineStr"/>
-      <c r="I101" s="69" t="inlineStr">
+      <c r="I101" s="68" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -13101,11 +12749,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP101" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP101" s="65" t="inlineStr"/>
       <c r="AQ101" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13117,7 +12761,7 @@
         </is>
       </c>
       <c r="AS101" s="23" t="n"/>
-      <c r="AT101" s="67" t="inlineStr"/>
+      <c r="AT101" s="66" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="53" t="inlineStr">
@@ -13152,7 +12796,7 @@
         </is>
       </c>
       <c r="H102" s="24" t="inlineStr"/>
-      <c r="I102" s="69" t="inlineStr">
+      <c r="I102" s="68" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -13223,11 +12867,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP102" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP102" s="65" t="inlineStr"/>
       <c r="AQ102" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13239,7 +12879,7 @@
         </is>
       </c>
       <c r="AS102" s="23" t="n"/>
-      <c r="AT102" s="67" t="inlineStr"/>
+      <c r="AT102" s="66" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="53" t="inlineStr">
@@ -13274,7 +12914,7 @@
         </is>
       </c>
       <c r="H103" s="24" t="inlineStr"/>
-      <c r="I103" s="69" t="inlineStr">
+      <c r="I103" s="68" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -13345,11 +12985,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP103" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP103" s="65" t="inlineStr"/>
       <c r="AQ103" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13361,7 +12997,7 @@
         </is>
       </c>
       <c r="AS103" s="23" t="n"/>
-      <c r="AT103" s="67" t="inlineStr"/>
+      <c r="AT103" s="66" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="53" t="inlineStr">
@@ -13396,7 +13032,7 @@
         </is>
       </c>
       <c r="H104" s="24" t="inlineStr"/>
-      <c r="I104" s="69" t="inlineStr">
+      <c r="I104" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -13467,11 +13103,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP104" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP104" s="65" t="inlineStr"/>
       <c r="AQ104" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13483,7 +13115,7 @@
         </is>
       </c>
       <c r="AS104" s="23" t="n"/>
-      <c r="AT104" s="67" t="inlineStr"/>
+      <c r="AT104" s="66" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="53" t="inlineStr">
@@ -13518,7 +13150,7 @@
         </is>
       </c>
       <c r="H105" s="24" t="inlineStr"/>
-      <c r="I105" s="69" t="inlineStr">
+      <c r="I105" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -13589,11 +13221,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP105" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP105" s="65" t="inlineStr"/>
       <c r="AQ105" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13605,7 +13233,7 @@
         </is>
       </c>
       <c r="AS105" s="23" t="n"/>
-      <c r="AT105" s="67" t="inlineStr"/>
+      <c r="AT105" s="66" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="53" t="inlineStr">
@@ -13640,7 +13268,7 @@
         </is>
       </c>
       <c r="H106" s="24" t="inlineStr"/>
-      <c r="I106" s="69" t="inlineStr">
+      <c r="I106" s="68" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -13711,11 +13339,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP106" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP106" s="65" t="inlineStr"/>
       <c r="AQ106" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13727,7 +13351,7 @@
         </is>
       </c>
       <c r="AS106" s="23" t="n"/>
-      <c r="AT106" s="67" t="inlineStr"/>
+      <c r="AT106" s="66" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="53" t="inlineStr">
@@ -13762,7 +13386,7 @@
         </is>
       </c>
       <c r="H107" s="24" t="inlineStr"/>
-      <c r="I107" s="69" t="inlineStr">
+      <c r="I107" s="68" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -13833,11 +13457,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP107" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="AP107" s="65" t="inlineStr"/>
       <c r="AQ107" s="65" t="inlineStr">
         <is>
           <t>PS5-28-PSV-3901B, PS5-28-PSV-3901A not arrived</t>
@@ -13849,7 +13469,7 @@
         </is>
       </c>
       <c r="AS107" s="23" t="n"/>
-      <c r="AT107" s="67" t="inlineStr"/>
+      <c r="AT107" s="66" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="53" t="inlineStr">
@@ -13884,7 +13504,7 @@
         </is>
       </c>
       <c r="H108" s="24" t="inlineStr"/>
-      <c r="I108" s="70" t="inlineStr">
+      <c r="I108" s="69" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -13955,11 +13575,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP108" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP108" s="65" t="inlineStr"/>
       <c r="AQ108" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13971,7 +13587,7 @@
         </is>
       </c>
       <c r="AS108" s="23" t="n"/>
-      <c r="AT108" s="67" t="inlineStr"/>
+      <c r="AT108" s="66" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="53" t="inlineStr">
@@ -14006,7 +13622,7 @@
         </is>
       </c>
       <c r="H109" s="24" t="inlineStr"/>
-      <c r="I109" s="70" t="inlineStr">
+      <c r="I109" s="69" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -14077,11 +13693,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP109" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP109" s="65" t="inlineStr"/>
       <c r="AQ109" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14093,7 +13705,7 @@
         </is>
       </c>
       <c r="AS109" s="23" t="n"/>
-      <c r="AT109" s="67" t="inlineStr"/>
+      <c r="AT109" s="66" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="53" t="inlineStr">
@@ -14128,7 +13740,7 @@
         </is>
       </c>
       <c r="H110" s="24" t="inlineStr"/>
-      <c r="I110" s="70" t="inlineStr">
+      <c r="I110" s="69" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -14199,11 +13811,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AP110" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP110" s="65" t="inlineStr"/>
       <c r="AQ110" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14215,10 +13823,10 @@
         </is>
       </c>
       <c r="AS110" s="23" t="n"/>
-      <c r="AT110" s="67" t="inlineStr"/>
+      <c r="AT110" s="66" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="74" t="inlineStr">
+      <c r="A111" s="73" t="inlineStr">
         <is>
           <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
@@ -14248,7 +13856,7 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="G111" s="69" t="inlineStr">
+      <c r="G111" s="68" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -14258,7 +13866,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I111" s="69" t="inlineStr">
+      <c r="I111" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -14329,11 +13937,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP111" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP111" s="65" t="inlineStr"/>
       <c r="AQ111" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14345,7 +13949,7 @@
         </is>
       </c>
       <c r="AS111" s="23" t="n"/>
-      <c r="AT111" s="67" t="inlineStr"/>
+      <c r="AT111" s="66" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="53" t="inlineStr">
@@ -14380,7 +13984,7 @@
         </is>
       </c>
       <c r="H112" s="24" t="inlineStr"/>
-      <c r="I112" s="69" t="inlineStr">
+      <c r="I112" s="68" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -14451,11 +14055,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP112" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP112" s="65" t="inlineStr"/>
       <c r="AQ112" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14467,7 +14067,7 @@
         </is>
       </c>
       <c r="AS112" s="23" t="n"/>
-      <c r="AT112" s="67" t="inlineStr"/>
+      <c r="AT112" s="66" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="53" t="inlineStr">
@@ -14502,7 +14102,7 @@
         </is>
       </c>
       <c r="H113" s="24" t="inlineStr"/>
-      <c r="I113" s="69" t="inlineStr">
+      <c r="I113" s="68" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -14573,11 +14173,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AP113" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP113" s="65" t="inlineStr"/>
       <c r="AQ113" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14589,7 +14185,7 @@
         </is>
       </c>
       <c r="AS113" s="23" t="n"/>
-      <c r="AT113" s="67" t="inlineStr"/>
+      <c r="AT113" s="66" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="53" t="inlineStr">
@@ -14624,7 +14220,7 @@
         </is>
       </c>
       <c r="H114" s="24" t="inlineStr"/>
-      <c r="I114" s="70" t="inlineStr">
+      <c r="I114" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14695,11 +14291,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AP114" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP114" s="65" t="inlineStr"/>
       <c r="AQ114" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14711,7 +14303,7 @@
         </is>
       </c>
       <c r="AS114" s="23" t="n"/>
-      <c r="AT114" s="67" t="inlineStr"/>
+      <c r="AT114" s="66" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="53" t="inlineStr">
@@ -14817,11 +14409,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP115" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP115" s="65" t="inlineStr"/>
       <c r="AQ115" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14833,7 +14421,7 @@
         </is>
       </c>
       <c r="AS115" s="23" t="n"/>
-      <c r="AT115" s="67" t="inlineStr"/>
+      <c r="AT115" s="66" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="53" t="inlineStr">
@@ -14872,7 +14460,7 @@
         </is>
       </c>
       <c r="H116" s="24" t="inlineStr"/>
-      <c r="I116" s="69" t="inlineStr">
+      <c r="I116" s="68" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -14943,11 +14531,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP116" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP116" s="65" t="inlineStr"/>
       <c r="AQ116" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14959,10 +14543,10 @@
         </is>
       </c>
       <c r="AS116" s="23" t="n"/>
-      <c r="AT116" s="67" t="inlineStr"/>
+      <c r="AT116" s="66" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="68" t="inlineStr">
+      <c r="A117" s="67" t="inlineStr">
         <is>
           <t>PS5-60-01 - Power Generation Package A</t>
         </is>
@@ -15073,11 +14657,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP117" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP117" s="65" t="inlineStr"/>
       <c r="AQ117" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -15089,10 +14669,10 @@
         </is>
       </c>
       <c r="AS117" s="23" t="n"/>
-      <c r="AT117" s="67" t="inlineStr"/>
+      <c r="AT117" s="66" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="68" t="inlineStr">
+      <c r="A118" s="67" t="inlineStr">
         <is>
           <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
@@ -15119,7 +14699,7 @@
       </c>
       <c r="F118" s="23" t="inlineStr">
         <is>
-          <t>20-Aug-26</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G118" s="27" t="inlineStr">
@@ -15129,7 +14709,7 @@
       </c>
       <c r="H118" s="24" t="inlineStr">
         <is>
-          <t>PS5 - Milestone B</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I118" s="54" t="inlineStr">
@@ -15203,11 +14783,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP118" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP118" s="65" t="inlineStr"/>
       <c r="AQ118" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -15215,11 +14791,11 @@
       </c>
       <c r="AR118" s="23" t="inlineStr">
         <is>
-          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS118" s="23" t="n"/>
-      <c r="AT118" s="67" t="inlineStr"/>
+      <c r="AT118" s="66" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="53" t="inlineStr">
@@ -15262,7 +14838,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I119" s="69" t="inlineStr">
+      <c r="I119" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -15294,7 +14870,7 @@
       <c r="R119" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S119" s="71" t="inlineStr">
+      <c r="S119" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15333,11 +14909,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP119" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP119" s="65" t="inlineStr"/>
       <c r="AQ119" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -15349,10 +14921,10 @@
         </is>
       </c>
       <c r="AS119" s="23" t="n"/>
-      <c r="AT119" s="67" t="inlineStr"/>
+      <c r="AT119" s="66" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="68" t="inlineStr">
+      <c r="A120" s="67" t="inlineStr">
         <is>
           <t>PS5-60-04 - Power Generation Package B</t>
         </is>
@@ -15463,11 +15035,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP120" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP120" s="65" t="inlineStr"/>
       <c r="AQ120" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -15479,7 +15047,7 @@
         </is>
       </c>
       <c r="AS120" s="23" t="n"/>
-      <c r="AT120" s="67" t="inlineStr"/>
+      <c r="AT120" s="66" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="53" t="inlineStr">
@@ -15554,7 +15122,7 @@
       <c r="R121" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="S121" s="71" t="inlineStr">
+      <c r="S121" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15593,15 +15161,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP121" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP121" s="65" t="inlineStr"/>
       <c r="AQ121" s="65" t="inlineStr"/>
       <c r="AR121" s="23" t="inlineStr"/>
       <c r="AS121" s="23" t="n"/>
-      <c r="AT121" s="67" t="inlineStr"/>
+      <c r="AT121" s="66" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="53" t="inlineStr">
@@ -15644,7 +15208,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I122" s="69" t="inlineStr">
+      <c r="I122" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -15676,7 +15240,7 @@
       <c r="R122" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S122" s="71" t="inlineStr">
+      <c r="S122" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15715,15 +15279,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP122" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP122" s="65" t="inlineStr"/>
       <c r="AQ122" s="65" t="inlineStr"/>
       <c r="AR122" s="23" t="inlineStr"/>
       <c r="AS122" s="23" t="n"/>
-      <c r="AT122" s="67" t="inlineStr"/>
+      <c r="AT122" s="66" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="53" t="inlineStr">
@@ -15837,11 +15397,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP123" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="AP123" s="65" t="inlineStr"/>
       <c r="AQ123" s="65" t="inlineStr">
         <is>
           <t>PS5-60-BI-0016C-CCO4 6T X 0.75 IS/OS FL RTD 131m
@@ -15855,7 +15411,7 @@
         </is>
       </c>
       <c r="AS123" s="23" t="n"/>
-      <c r="AT123" s="67" t="inlineStr"/>
+      <c r="AT123" s="66" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="53" t="inlineStr">
@@ -15930,7 +15486,7 @@
       <c r="R124" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="S124" s="71" t="inlineStr">
+      <c r="S124" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15969,15 +15525,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP124" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP124" s="65" t="inlineStr"/>
       <c r="AQ124" s="65" t="inlineStr"/>
       <c r="AR124" s="23" t="inlineStr"/>
       <c r="AS124" s="23" t="n"/>
-      <c r="AT124" s="67" t="inlineStr"/>
+      <c r="AT124" s="66" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="53" t="inlineStr">
@@ -16020,7 +15572,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I125" s="69" t="inlineStr">
+      <c r="I125" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -16052,7 +15604,7 @@
       <c r="R125" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S125" s="71" t="inlineStr">
+      <c r="S125" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16091,15 +15643,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP125" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP125" s="65" t="inlineStr"/>
       <c r="AQ125" s="65" t="inlineStr"/>
       <c r="AR125" s="23" t="inlineStr"/>
       <c r="AS125" s="23" t="n"/>
-      <c r="AT125" s="67" t="inlineStr"/>
+      <c r="AT125" s="66" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="53" t="inlineStr">
@@ -16174,7 +15722,7 @@
       <c r="R126" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="S126" s="71" t="inlineStr">
+      <c r="S126" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16213,11 +15761,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP126" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP126" s="65" t="inlineStr"/>
       <c r="AQ126" s="65" t="inlineStr">
         <is>
           <t>PS5-60-BI-0016D-CCO4 6T X 0.75 IS/OS FL RTD 121m</t>
@@ -16229,7 +15773,7 @@
         </is>
       </c>
       <c r="AS126" s="23" t="n"/>
-      <c r="AT126" s="67" t="inlineStr"/>
+      <c r="AT126" s="66" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="53" t="inlineStr">
@@ -16304,7 +15848,7 @@
       <c r="R127" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="S127" s="71" t="inlineStr">
+      <c r="S127" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16343,15 +15887,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP127" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP127" s="65" t="inlineStr"/>
       <c r="AQ127" s="65" t="inlineStr"/>
       <c r="AR127" s="23" t="inlineStr"/>
       <c r="AS127" s="23" t="n"/>
-      <c r="AT127" s="67" t="inlineStr"/>
+      <c r="AT127" s="66" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="53" t="inlineStr">
@@ -16394,7 +15934,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I128" s="69" t="inlineStr">
+      <c r="I128" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -16426,7 +15966,7 @@
       <c r="R128" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S128" s="71" t="inlineStr">
+      <c r="S128" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16465,15 +16005,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP128" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP128" s="65" t="inlineStr"/>
       <c r="AQ128" s="65" t="inlineStr"/>
       <c r="AR128" s="23" t="inlineStr"/>
       <c r="AS128" s="23" t="n"/>
-      <c r="AT128" s="67" t="inlineStr"/>
+      <c r="AT128" s="66" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="53" t="inlineStr">
@@ -16587,11 +16123,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP129" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP129" s="65" t="inlineStr"/>
       <c r="AQ129" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -16603,7 +16135,7 @@
         </is>
       </c>
       <c r="AS129" s="23" t="n"/>
-      <c r="AT129" s="67" t="inlineStr"/>
+      <c r="AT129" s="66" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="53" t="inlineStr">
@@ -16678,7 +16210,7 @@
       <c r="R130" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="S130" s="71" t="inlineStr">
+      <c r="S130" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16717,15 +16249,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP130" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP130" s="65" t="inlineStr"/>
       <c r="AQ130" s="65" t="inlineStr"/>
       <c r="AR130" s="23" t="inlineStr"/>
       <c r="AS130" s="23" t="n"/>
-      <c r="AT130" s="67" t="inlineStr"/>
+      <c r="AT130" s="66" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="53" t="inlineStr">
@@ -16768,7 +16296,7 @@
           <t>full</t>
         </is>
       </c>
-      <c r="I131" s="69" t="inlineStr">
+      <c r="I131" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -16800,7 +16328,7 @@
       <c r="R131" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S131" s="71" t="inlineStr">
+      <c r="S131" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16839,15 +16367,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP131" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP131" s="65" t="inlineStr"/>
       <c r="AQ131" s="65" t="inlineStr"/>
       <c r="AR131" s="23" t="inlineStr"/>
       <c r="AS131" s="23" t="n"/>
-      <c r="AT131" s="67" t="inlineStr"/>
+      <c r="AT131" s="66" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="53" t="inlineStr">
@@ -16918,7 +16442,7 @@
       <c r="R132" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="S132" s="71" t="inlineStr">
+      <c r="S132" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16957,11 +16481,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP132" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP132" s="65" t="inlineStr"/>
       <c r="AQ132" s="65" t="inlineStr">
         <is>
           <t>PS5-60-BI-0016F-CCO4 6T X 0.75 IS/OS FL RTD</t>
@@ -16973,7 +16493,7 @@
         </is>
       </c>
       <c r="AS132" s="23" t="n"/>
-      <c r="AT132" s="67" t="inlineStr"/>
+      <c r="AT132" s="66" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="53" t="inlineStr">
@@ -17008,7 +16528,7 @@
         </is>
       </c>
       <c r="H133" s="24" t="inlineStr"/>
-      <c r="I133" s="69" t="inlineStr">
+      <c r="I133" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -17040,7 +16560,7 @@
       <c r="R133" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="S133" s="71" t="inlineStr">
+      <c r="S133" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -17079,15 +16599,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP133" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP133" s="65" t="inlineStr"/>
       <c r="AQ133" s="65" t="inlineStr"/>
       <c r="AR133" s="23" t="inlineStr"/>
       <c r="AS133" s="23" t="n"/>
-      <c r="AT133" s="67" t="inlineStr"/>
+      <c r="AT133" s="66" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="53" t="inlineStr">
@@ -17126,7 +16642,7 @@
         </is>
       </c>
       <c r="H134" s="24" t="inlineStr"/>
-      <c r="I134" s="69" t="inlineStr">
+      <c r="I134" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -17158,7 +16674,7 @@
       <c r="R134" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S134" s="71" t="inlineStr">
+      <c r="S134" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -17197,15 +16713,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP134" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP134" s="65" t="inlineStr"/>
       <c r="AQ134" s="65" t="inlineStr"/>
       <c r="AR134" s="23" t="inlineStr"/>
       <c r="AS134" s="23" t="n"/>
-      <c r="AT134" s="67" t="inlineStr"/>
+      <c r="AT134" s="66" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="53" t="inlineStr">
@@ -17311,11 +16823,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP135" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP135" s="65" t="inlineStr"/>
       <c r="AQ135" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -17327,7 +16835,7 @@
         </is>
       </c>
       <c r="AS135" s="23" t="n"/>
-      <c r="AT135" s="67" t="inlineStr"/>
+      <c r="AT135" s="66" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="53" t="inlineStr">
@@ -17366,7 +16874,7 @@
         </is>
       </c>
       <c r="H136" s="24" t="inlineStr"/>
-      <c r="I136" s="69" t="inlineStr">
+      <c r="I136" s="68" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -17398,7 +16906,7 @@
       <c r="R136" s="62" t="n">
         <v>3</v>
       </c>
-      <c r="S136" s="71" t="inlineStr">
+      <c r="S136" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -17437,15 +16945,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP136" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP136" s="65" t="inlineStr"/>
       <c r="AQ136" s="65" t="inlineStr"/>
       <c r="AR136" s="23" t="inlineStr"/>
       <c r="AS136" s="23" t="n"/>
-      <c r="AT136" s="67" t="inlineStr"/>
+      <c r="AT136" s="66" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="53" t="inlineStr">
@@ -17484,7 +16988,7 @@
         </is>
       </c>
       <c r="H137" s="24" t="inlineStr"/>
-      <c r="I137" s="69" t="inlineStr">
+      <c r="I137" s="68" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -17516,7 +17020,7 @@
       <c r="R137" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S137" s="71" t="inlineStr">
+      <c r="S137" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -17555,15 +17059,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP137" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP137" s="65" t="inlineStr"/>
       <c r="AQ137" s="65" t="inlineStr"/>
       <c r="AR137" s="23" t="inlineStr"/>
       <c r="AS137" s="23" t="n"/>
-      <c r="AT137" s="67" t="inlineStr"/>
+      <c r="AT137" s="66" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="53" t="inlineStr">
@@ -17606,7 +17106,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I138" s="69" t="inlineStr">
+      <c r="I138" s="68" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -17638,7 +17138,7 @@
       <c r="R138" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="S138" s="71" t="inlineStr">
+      <c r="S138" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -17677,11 +17177,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP138" s="65" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="AP138" s="65" t="inlineStr"/>
       <c r="AQ138" s="65" t="inlineStr">
         <is>
           <t>Fiber optic cables cannot be terminated due to drawing issues
@@ -17695,10 +17191,10 @@
         </is>
       </c>
       <c r="AS138" s="23" t="n"/>
-      <c r="AT138" s="67" t="inlineStr"/>
+      <c r="AT138" s="66" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="68" t="inlineStr">
+      <c r="A139" s="67" t="inlineStr">
         <is>
           <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
@@ -17805,11 +17301,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP139" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP139" s="65" t="inlineStr"/>
       <c r="AQ139" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -17821,7 +17313,7 @@
         </is>
       </c>
       <c r="AS139" s="23" t="n"/>
-      <c r="AT139" s="67" t="inlineStr"/>
+      <c r="AT139" s="66" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="53" t="inlineStr">
@@ -17935,11 +17427,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP140" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="AP140" s="65" t="inlineStr"/>
       <c r="AQ140" s="65" t="inlineStr">
         <is>
           <t>PS5-60-LIT-4301 not arrived.</t>
@@ -17951,7 +17439,7 @@
         </is>
       </c>
       <c r="AS140" s="23" t="n"/>
-      <c r="AT140" s="67" t="inlineStr"/>
+      <c r="AT140" s="66" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="53" t="inlineStr">
@@ -18065,11 +17553,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP141" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="AP141" s="65" t="inlineStr"/>
       <c r="AQ141" s="65" t="inlineStr">
         <is>
           <t>PS5-60-LIT-4401 not arrived</t>
@@ -18081,10 +17565,10 @@
         </is>
       </c>
       <c r="AS141" s="23" t="n"/>
-      <c r="AT141" s="67" t="inlineStr"/>
+      <c r="AT141" s="66" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="68" t="inlineStr">
+      <c r="A142" s="67" t="inlineStr">
         <is>
           <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
@@ -18101,7 +17585,7 @@
       </c>
       <c r="D142" s="23" t="inlineStr">
         <is>
-          <t>walkdown complete</t>
+          <t>E,I,M,P</t>
         </is>
       </c>
       <c r="E142" s="23" t="inlineStr">
@@ -18195,11 +17679,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP142" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP142" s="65" t="inlineStr"/>
       <c r="AQ142" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -18211,10 +17691,10 @@
         </is>
       </c>
       <c r="AS142" s="23" t="n"/>
-      <c r="AT142" s="67" t="inlineStr"/>
+      <c r="AT142" s="66" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="68" t="inlineStr">
+      <c r="A143" s="67" t="inlineStr">
         <is>
           <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
@@ -18325,11 +17805,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP143" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP143" s="65" t="inlineStr"/>
       <c r="AQ143" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -18341,10 +17817,10 @@
         </is>
       </c>
       <c r="AS143" s="23" t="n"/>
-      <c r="AT143" s="67" t="inlineStr"/>
+      <c r="AT143" s="66" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="74" t="inlineStr">
+      <c r="A144" s="67" t="inlineStr">
         <is>
           <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
@@ -18374,9 +17850,9 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="G144" s="69" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="G144" s="27" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
       <c r="H144" s="24" t="inlineStr">
@@ -18455,11 +17931,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP144" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP144" s="65" t="inlineStr"/>
       <c r="AQ144" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -18471,10 +17943,10 @@
         </is>
       </c>
       <c r="AS144" s="23" t="n"/>
-      <c r="AT144" s="67" t="inlineStr"/>
+      <c r="AT144" s="66" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="68" t="inlineStr">
+      <c r="A145" s="67" t="inlineStr">
         <is>
           <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
@@ -18585,11 +18057,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP145" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP145" s="65" t="inlineStr"/>
       <c r="AQ145" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -18601,10 +18069,10 @@
         </is>
       </c>
       <c r="AS145" s="23" t="n"/>
-      <c r="AT145" s="67" t="inlineStr"/>
+      <c r="AT145" s="66" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="68" t="inlineStr">
+      <c r="A146" s="67" t="inlineStr">
         <is>
           <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
@@ -18715,11 +18183,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP146" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP146" s="65" t="inlineStr"/>
       <c r="AQ146" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -18731,10 +18195,10 @@
         </is>
       </c>
       <c r="AS146" s="23" t="n"/>
-      <c r="AT146" s="67" t="inlineStr"/>
+      <c r="AT146" s="66" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="68" t="inlineStr">
+      <c r="A147" s="67" t="inlineStr">
         <is>
           <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
@@ -18845,11 +18309,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP147" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP147" s="65" t="inlineStr"/>
       <c r="AQ147" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -18861,10 +18321,10 @@
         </is>
       </c>
       <c r="AS147" s="23" t="n"/>
-      <c r="AT147" s="67" t="inlineStr"/>
+      <c r="AT147" s="66" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="68" t="inlineStr">
+      <c r="A148" s="67" t="inlineStr">
         <is>
           <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
@@ -18975,11 +18435,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP148" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP148" s="65" t="inlineStr"/>
       <c r="AQ148" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -18991,10 +18447,10 @@
         </is>
       </c>
       <c r="AS148" s="23" t="n"/>
-      <c r="AT148" s="67" t="inlineStr"/>
+      <c r="AT148" s="66" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="68" t="inlineStr">
+      <c r="A149" s="67" t="inlineStr">
         <is>
           <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
@@ -19105,11 +18561,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP149" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP149" s="65" t="inlineStr"/>
       <c r="AQ149" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -19121,10 +18573,10 @@
         </is>
       </c>
       <c r="AS149" s="23" t="n"/>
-      <c r="AT149" s="67" t="inlineStr"/>
+      <c r="AT149" s="66" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="68" t="inlineStr">
+      <c r="A150" s="67" t="inlineStr">
         <is>
           <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
@@ -19235,11 +18687,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP150" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP150" s="65" t="inlineStr"/>
       <c r="AQ150" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -19251,10 +18699,10 @@
         </is>
       </c>
       <c r="AS150" s="23" t="n"/>
-      <c r="AT150" s="67" t="inlineStr"/>
+      <c r="AT150" s="66" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="75" t="inlineStr">
+      <c r="A151" s="67" t="inlineStr">
         <is>
           <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
@@ -19280,9 +18728,9 @@
         </is>
       </c>
       <c r="F151" s="23" t="inlineStr"/>
-      <c r="G151" s="54" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
+      <c r="G151" s="27" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
       <c r="H151" s="24" t="inlineStr">
@@ -19361,11 +18809,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP151" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP151" s="65" t="inlineStr"/>
       <c r="AQ151" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -19377,10 +18821,10 @@
         </is>
       </c>
       <c r="AS151" s="23" t="n"/>
-      <c r="AT151" s="67" t="inlineStr"/>
+      <c r="AT151" s="66" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="68" t="inlineStr">
+      <c r="A152" s="67" t="inlineStr">
         <is>
           <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
@@ -19487,11 +18931,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP152" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP152" s="65" t="inlineStr"/>
       <c r="AQ152" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -19503,10 +18943,10 @@
         </is>
       </c>
       <c r="AS152" s="23" t="n"/>
-      <c r="AT152" s="67" t="inlineStr"/>
+      <c r="AT152" s="66" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="68" t="inlineStr">
+      <c r="A153" s="67" t="inlineStr">
         <is>
           <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
@@ -19617,11 +19057,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP153" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP153" s="65" t="inlineStr"/>
       <c r="AQ153" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -19633,10 +19069,10 @@
         </is>
       </c>
       <c r="AS153" s="23" t="n"/>
-      <c r="AT153" s="67" t="inlineStr"/>
+      <c r="AT153" s="66" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="68" t="inlineStr">
+      <c r="A154" s="67" t="inlineStr">
         <is>
           <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
@@ -19747,11 +19183,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP154" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP154" s="65" t="inlineStr"/>
       <c r="AQ154" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -19763,10 +19195,10 @@
         </is>
       </c>
       <c r="AS154" s="23" t="n"/>
-      <c r="AT154" s="67" t="inlineStr"/>
+      <c r="AT154" s="66" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="68" t="inlineStr">
+      <c r="A155" s="67" t="inlineStr">
         <is>
           <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
@@ -19877,11 +19309,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP155" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP155" s="65" t="inlineStr"/>
       <c r="AQ155" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -19893,10 +19321,10 @@
         </is>
       </c>
       <c r="AS155" s="23" t="n"/>
-      <c r="AT155" s="67" t="inlineStr"/>
+      <c r="AT155" s="66" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="68" t="inlineStr">
+      <c r="A156" s="67" t="inlineStr">
         <is>
           <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
@@ -20007,11 +19435,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP156" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP156" s="65" t="inlineStr"/>
       <c r="AQ156" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -20023,7 +19447,7 @@
         </is>
       </c>
       <c r="AS156" s="23" t="n"/>
-      <c r="AT156" s="67" t="inlineStr"/>
+      <c r="AT156" s="66" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="53" t="inlineStr">
@@ -20062,7 +19486,7 @@
         </is>
       </c>
       <c r="H157" s="24" t="inlineStr"/>
-      <c r="I157" s="69" t="inlineStr">
+      <c r="I157" s="68" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -20133,11 +19557,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP157" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP157" s="65" t="inlineStr"/>
       <c r="AQ157" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -20149,10 +19569,10 @@
         </is>
       </c>
       <c r="AS157" s="23" t="n"/>
-      <c r="AT157" s="67" t="inlineStr"/>
+      <c r="AT157" s="66" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="75" t="inlineStr">
+      <c r="A158" s="67" t="inlineStr">
         <is>
           <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
@@ -20178,9 +19598,9 @@
         </is>
       </c>
       <c r="F158" s="23" t="inlineStr"/>
-      <c r="G158" s="54" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
+      <c r="G158" s="27" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
       <c r="H158" s="24" t="inlineStr">
@@ -20259,11 +19679,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP158" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP158" s="65" t="inlineStr"/>
       <c r="AQ158" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -20275,10 +19691,10 @@
         </is>
       </c>
       <c r="AS158" s="23" t="n"/>
-      <c r="AT158" s="67" t="inlineStr"/>
+      <c r="AT158" s="66" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="68" t="inlineStr">
+      <c r="A159" s="67" t="inlineStr">
         <is>
           <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
@@ -20385,11 +19801,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP159" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP159" s="65" t="inlineStr"/>
       <c r="AQ159" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -20401,10 +19813,10 @@
         </is>
       </c>
       <c r="AS159" s="23" t="n"/>
-      <c r="AT159" s="67" t="inlineStr"/>
+      <c r="AT159" s="66" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="68" t="inlineStr">
+      <c r="A160" s="67" t="inlineStr">
         <is>
           <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
@@ -20515,11 +19927,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP160" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP160" s="65" t="inlineStr"/>
       <c r="AQ160" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -20531,10 +19939,10 @@
         </is>
       </c>
       <c r="AS160" s="23" t="n"/>
-      <c r="AT160" s="67" t="inlineStr"/>
+      <c r="AT160" s="66" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="68" t="inlineStr">
+      <c r="A161" s="67" t="inlineStr">
         <is>
           <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
@@ -20645,11 +20053,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP161" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP161" s="65" t="inlineStr"/>
       <c r="AQ161" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -20661,10 +20065,10 @@
         </is>
       </c>
       <c r="AS161" s="23" t="n"/>
-      <c r="AT161" s="67" t="inlineStr"/>
+      <c r="AT161" s="66" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="68" t="inlineStr">
+      <c r="A162" s="67" t="inlineStr">
         <is>
           <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
@@ -20771,11 +20175,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP162" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP162" s="65" t="inlineStr"/>
       <c r="AQ162" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -20787,10 +20187,10 @@
         </is>
       </c>
       <c r="AS162" s="23" t="n"/>
-      <c r="AT162" s="67" t="inlineStr"/>
+      <c r="AT162" s="66" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="68" t="inlineStr">
+      <c r="A163" s="67" t="inlineStr">
         <is>
           <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
@@ -20901,11 +20301,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP163" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP163" s="65" t="inlineStr"/>
       <c r="AQ163" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -20917,7 +20313,7 @@
         </is>
       </c>
       <c r="AS163" s="23" t="n"/>
-      <c r="AT163" s="67" t="inlineStr"/>
+      <c r="AT163" s="66" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="53" t="inlineStr">
@@ -21023,11 +20419,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP164" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP164" s="65" t="inlineStr"/>
       <c r="AQ164" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -21039,7 +20431,7 @@
         </is>
       </c>
       <c r="AS164" s="23" t="n"/>
-      <c r="AT164" s="67" t="inlineStr"/>
+      <c r="AT164" s="66" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="53" t="inlineStr">
@@ -21114,7 +20506,7 @@
       <c r="R165" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S165" s="71" t="inlineStr">
+      <c r="S165" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21153,19 +20545,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP165" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP165" s="65" t="inlineStr"/>
       <c r="AQ165" s="65" t="inlineStr"/>
-      <c r="AR165" s="23" t="inlineStr">
-        <is>
-          <t>OBSERVATION -CLEANING ON PROGRESS</t>
-        </is>
-      </c>
+      <c r="AR165" s="23" t="inlineStr"/>
       <c r="AS165" s="23" t="n"/>
-      <c r="AT165" s="67" t="inlineStr"/>
+      <c r="AT165" s="66" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="53" t="inlineStr">
@@ -21240,7 +20624,7 @@
       <c r="R166" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S166" s="71" t="inlineStr">
+      <c r="S166" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21279,15 +20663,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP166" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP166" s="65" t="inlineStr"/>
       <c r="AQ166" s="65" t="inlineStr"/>
       <c r="AR166" s="23" t="inlineStr"/>
       <c r="AS166" s="23" t="n"/>
-      <c r="AT166" s="67" t="inlineStr"/>
+      <c r="AT166" s="66" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="53" t="inlineStr">
@@ -21362,7 +20742,7 @@
       <c r="R167" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S167" s="71" t="inlineStr">
+      <c r="S167" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21401,15 +20781,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP167" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP167" s="65" t="inlineStr"/>
       <c r="AQ167" s="65" t="inlineStr"/>
       <c r="AR167" s="23" t="inlineStr"/>
       <c r="AS167" s="23" t="n"/>
-      <c r="AT167" s="67" t="inlineStr"/>
+      <c r="AT167" s="66" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="53" t="inlineStr">
@@ -21452,7 +20828,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I168" s="69" t="inlineStr">
+      <c r="I168" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -21484,7 +20860,7 @@
       <c r="R168" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S168" s="71" t="inlineStr">
+      <c r="S168" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21523,15 +20899,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP168" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP168" s="65" t="inlineStr"/>
       <c r="AQ168" s="65" t="inlineStr"/>
       <c r="AR168" s="23" t="inlineStr"/>
       <c r="AS168" s="23" t="n"/>
-      <c r="AT168" s="67" t="inlineStr"/>
+      <c r="AT168" s="66" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="53" t="inlineStr">
@@ -21598,7 +20970,7 @@
       <c r="R169" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S169" s="71" t="inlineStr">
+      <c r="S169" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21637,15 +21009,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP169" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP169" s="65" t="inlineStr"/>
       <c r="AQ169" s="65" t="inlineStr"/>
       <c r="AR169" s="23" t="inlineStr"/>
       <c r="AS169" s="23" t="n"/>
-      <c r="AT169" s="67" t="inlineStr"/>
+      <c r="AT169" s="66" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="53" t="inlineStr">
@@ -21712,7 +21080,7 @@
       <c r="R170" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S170" s="71" t="inlineStr">
+      <c r="S170" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21751,15 +21119,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP170" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP170" s="65" t="inlineStr"/>
       <c r="AQ170" s="65" t="inlineStr"/>
       <c r="AR170" s="23" t="inlineStr"/>
       <c r="AS170" s="23" t="n"/>
-      <c r="AT170" s="67" t="inlineStr"/>
+      <c r="AT170" s="66" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="53" t="inlineStr">
@@ -21794,7 +21158,7 @@
         </is>
       </c>
       <c r="H171" s="24" t="inlineStr"/>
-      <c r="I171" s="69" t="inlineStr">
+      <c r="I171" s="68" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -21826,7 +21190,7 @@
       <c r="R171" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S171" s="71" t="inlineStr">
+      <c r="S171" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21865,18 +21229,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP171" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP171" s="65" t="inlineStr"/>
       <c r="AQ171" s="65" t="inlineStr"/>
       <c r="AR171" s="23" t="inlineStr"/>
       <c r="AS171" s="23" t="n"/>
-      <c r="AT171" s="67" t="inlineStr"/>
+      <c r="AT171" s="66" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="68" t="inlineStr">
+      <c r="A172" s="67" t="inlineStr">
         <is>
           <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
@@ -21987,15 +21347,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP172" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP172" s="65" t="inlineStr"/>
       <c r="AQ172" s="65" t="inlineStr"/>
       <c r="AR172" s="23" t="inlineStr"/>
       <c r="AS172" s="23" t="n"/>
-      <c r="AT172" s="67" t="inlineStr"/>
+      <c r="AT172" s="66" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="53" t="inlineStr">
@@ -22070,7 +21426,7 @@
       <c r="R173" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S173" s="71" t="inlineStr">
+      <c r="S173" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -22109,18 +21465,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP173" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP173" s="65" t="inlineStr"/>
       <c r="AQ173" s="65" t="inlineStr"/>
       <c r="AR173" s="23" t="inlineStr"/>
       <c r="AS173" s="23" t="n"/>
-      <c r="AT173" s="67" t="inlineStr"/>
+      <c r="AT173" s="66" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="68" t="inlineStr">
+      <c r="A174" s="67" t="inlineStr">
         <is>
           <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
@@ -22231,15 +21583,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP174" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP174" s="65" t="inlineStr"/>
       <c r="AQ174" s="65" t="inlineStr"/>
       <c r="AR174" s="23" t="inlineStr"/>
       <c r="AS174" s="23" t="n"/>
-      <c r="AT174" s="67" t="inlineStr"/>
+      <c r="AT174" s="66" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="53" t="inlineStr">
@@ -22314,7 +21662,7 @@
       <c r="R175" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S175" s="71" t="inlineStr">
+      <c r="S175" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -22353,18 +21701,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP175" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP175" s="65" t="inlineStr"/>
       <c r="AQ175" s="65" t="inlineStr"/>
       <c r="AR175" s="23" t="inlineStr"/>
       <c r="AS175" s="23" t="n"/>
-      <c r="AT175" s="67" t="inlineStr"/>
+      <c r="AT175" s="66" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="68" t="inlineStr">
+      <c r="A176" s="67" t="inlineStr">
         <is>
           <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
@@ -22475,15 +21819,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP176" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP176" s="65" t="inlineStr"/>
       <c r="AQ176" s="65" t="inlineStr"/>
       <c r="AR176" s="23" t="inlineStr"/>
       <c r="AS176" s="23" t="n"/>
-      <c r="AT176" s="67" t="inlineStr"/>
+      <c r="AT176" s="66" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="53" t="inlineStr">
@@ -22558,7 +21898,7 @@
       <c r="R177" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S177" s="71" t="inlineStr">
+      <c r="S177" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -22597,18 +21937,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP177" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP177" s="65" t="inlineStr"/>
       <c r="AQ177" s="65" t="inlineStr"/>
       <c r="AR177" s="23" t="inlineStr"/>
       <c r="AS177" s="23" t="n"/>
-      <c r="AT177" s="67" t="inlineStr"/>
+      <c r="AT177" s="66" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="68" t="inlineStr">
+      <c r="A178" s="67" t="inlineStr">
         <is>
           <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
@@ -22719,15 +22055,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP178" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP178" s="65" t="inlineStr"/>
       <c r="AQ178" s="65" t="inlineStr"/>
       <c r="AR178" s="23" t="inlineStr"/>
       <c r="AS178" s="23" t="n"/>
-      <c r="AT178" s="67" t="inlineStr"/>
+      <c r="AT178" s="66" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="53" t="inlineStr">
@@ -22802,7 +22134,7 @@
       <c r="R179" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S179" s="71" t="inlineStr">
+      <c r="S179" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -22841,15 +22173,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP179" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP179" s="65" t="inlineStr"/>
       <c r="AQ179" s="65" t="inlineStr"/>
       <c r="AR179" s="23" t="inlineStr"/>
       <c r="AS179" s="23" t="n"/>
-      <c r="AT179" s="67" t="inlineStr"/>
+      <c r="AT179" s="66" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="53" t="inlineStr">
@@ -22955,11 +22283,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP180" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP180" s="65" t="inlineStr"/>
       <c r="AQ180" s="65" t="inlineStr">
         <is>
           <t>Cables pending due to PIT location issue, colliding with pipes</t>
@@ -22971,7 +22295,7 @@
         </is>
       </c>
       <c r="AS180" s="23" t="n"/>
-      <c r="AT180" s="67" t="inlineStr"/>
+      <c r="AT180" s="66" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="53" t="inlineStr">
@@ -23010,7 +22334,7 @@
         </is>
       </c>
       <c r="H181" s="24" t="inlineStr"/>
-      <c r="I181" s="69" t="inlineStr">
+      <c r="I181" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -23042,7 +22366,7 @@
       <c r="R181" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S181" s="71" t="inlineStr">
+      <c r="S181" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -23081,15 +22405,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP181" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP181" s="65" t="inlineStr"/>
       <c r="AQ181" s="65" t="inlineStr"/>
       <c r="AR181" s="23" t="inlineStr"/>
       <c r="AS181" s="23" t="n"/>
-      <c r="AT181" s="67" t="inlineStr"/>
+      <c r="AT181" s="66" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="53" t="inlineStr">
@@ -23195,11 +22515,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP182" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP182" s="65" t="inlineStr"/>
       <c r="AQ182" s="65" t="inlineStr">
         <is>
           <t>Cables pending due to PIT location issue, colliding with pipes</t>
@@ -23211,7 +22527,7 @@
         </is>
       </c>
       <c r="AS182" s="23" t="n"/>
-      <c r="AT182" s="67" t="inlineStr"/>
+      <c r="AT182" s="66" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="53" t="inlineStr">
@@ -23250,7 +22566,7 @@
         </is>
       </c>
       <c r="H183" s="24" t="inlineStr"/>
-      <c r="I183" s="69" t="inlineStr">
+      <c r="I183" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -23282,7 +22598,7 @@
       <c r="R183" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S183" s="71" t="inlineStr">
+      <c r="S183" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -23321,15 +22637,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP183" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP183" s="65" t="inlineStr"/>
       <c r="AQ183" s="65" t="inlineStr"/>
       <c r="AR183" s="23" t="inlineStr"/>
       <c r="AS183" s="23" t="n"/>
-      <c r="AT183" s="67" t="inlineStr"/>
+      <c r="AT183" s="66" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="53" t="inlineStr">
@@ -23364,7 +22676,7 @@
         </is>
       </c>
       <c r="H184" s="24" t="inlineStr"/>
-      <c r="I184" s="69" t="inlineStr">
+      <c r="I184" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -23435,11 +22747,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP184" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP184" s="65" t="inlineStr"/>
       <c r="AQ184" s="65" t="inlineStr">
         <is>
           <t>Cables pending due to PIT location issue, colliding with pipes</t>
@@ -23451,7 +22759,7 @@
         </is>
       </c>
       <c r="AS184" s="23" t="n"/>
-      <c r="AT184" s="67" t="inlineStr"/>
+      <c r="AT184" s="66" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="53" t="inlineStr">
@@ -23490,7 +22798,7 @@
         </is>
       </c>
       <c r="H185" s="24" t="inlineStr"/>
-      <c r="I185" s="69" t="inlineStr">
+      <c r="I185" s="68" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -23522,7 +22830,7 @@
       <c r="R185" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S185" s="71" t="inlineStr">
+      <c r="S185" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -23561,18 +22869,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP185" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP185" s="65" t="inlineStr"/>
       <c r="AQ185" s="65" t="inlineStr"/>
       <c r="AR185" s="23" t="inlineStr"/>
       <c r="AS185" s="23" t="n"/>
-      <c r="AT185" s="67" t="inlineStr"/>
+      <c r="AT185" s="66" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="68" t="inlineStr">
+      <c r="A186" s="67" t="inlineStr">
         <is>
           <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
@@ -23683,11 +22987,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP186" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP186" s="65" t="inlineStr"/>
       <c r="AQ186" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -23699,10 +22999,10 @@
         </is>
       </c>
       <c r="AS186" s="23" t="n"/>
-      <c r="AT186" s="67" t="inlineStr"/>
+      <c r="AT186" s="66" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="68" t="inlineStr">
+      <c r="A187" s="67" t="inlineStr">
         <is>
           <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
@@ -23813,11 +23113,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP187" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP187" s="65" t="inlineStr"/>
       <c r="AQ187" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -23829,10 +23125,10 @@
         </is>
       </c>
       <c r="AS187" s="23" t="n"/>
-      <c r="AT187" s="67" t="inlineStr"/>
+      <c r="AT187" s="66" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="68" t="inlineStr">
+      <c r="A188" s="67" t="inlineStr">
         <is>
           <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
@@ -23943,11 +23239,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP188" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP188" s="65" t="inlineStr"/>
       <c r="AQ188" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -23959,10 +23251,10 @@
         </is>
       </c>
       <c r="AS188" s="23" t="n"/>
-      <c r="AT188" s="67" t="inlineStr"/>
+      <c r="AT188" s="66" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="68" t="inlineStr">
+      <c r="A189" s="67" t="inlineStr">
         <is>
           <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
@@ -24073,11 +23365,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP189" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP189" s="65" t="inlineStr"/>
       <c r="AQ189" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -24089,10 +23377,10 @@
         </is>
       </c>
       <c r="AS189" s="23" t="n"/>
-      <c r="AT189" s="67" t="inlineStr"/>
+      <c r="AT189" s="66" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="68" t="inlineStr">
+      <c r="A190" s="67" t="inlineStr">
         <is>
           <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
@@ -24203,11 +23491,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP190" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP190" s="65" t="inlineStr"/>
       <c r="AQ190" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -24219,10 +23503,10 @@
         </is>
       </c>
       <c r="AS190" s="23" t="n"/>
-      <c r="AT190" s="67" t="inlineStr"/>
+      <c r="AT190" s="66" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="68" t="inlineStr">
+      <c r="A191" s="67" t="inlineStr">
         <is>
           <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
@@ -24333,11 +23617,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP191" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP191" s="65" t="inlineStr"/>
       <c r="AQ191" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -24349,7 +23629,7 @@
         </is>
       </c>
       <c r="AS191" s="23" t="n"/>
-      <c r="AT191" s="67" t="inlineStr"/>
+      <c r="AT191" s="66" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="53" t="inlineStr">
@@ -24455,11 +23735,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP192" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP192" s="65" t="inlineStr"/>
       <c r="AQ192" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -24471,7 +23747,7 @@
         </is>
       </c>
       <c r="AS192" s="23" t="n"/>
-      <c r="AT192" s="67" t="inlineStr"/>
+      <c r="AT192" s="66" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="53" t="inlineStr">
@@ -24585,11 +23861,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP193" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="AP193" s="65" t="inlineStr"/>
       <c r="AQ193" s="65" t="inlineStr">
         <is>
           <t>Nut bolts not available for  termination in busbar
@@ -24603,7 +23875,7 @@
         </is>
       </c>
       <c r="AS193" s="23" t="n"/>
-      <c r="AT193" s="67" t="inlineStr"/>
+      <c r="AT193" s="66" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="53" t="inlineStr">
@@ -24638,7 +23910,7 @@
         </is>
       </c>
       <c r="H194" s="24" t="inlineStr"/>
-      <c r="I194" s="69" t="inlineStr">
+      <c r="I194" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -24709,11 +23981,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP194" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP194" s="65" t="inlineStr"/>
       <c r="AQ194" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -24725,7 +23993,7 @@
         </is>
       </c>
       <c r="AS194" s="23" t="n"/>
-      <c r="AT194" s="67" t="inlineStr"/>
+      <c r="AT194" s="66" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="53" t="inlineStr">
@@ -24760,7 +24028,7 @@
         </is>
       </c>
       <c r="H195" s="24" t="inlineStr"/>
-      <c r="I195" s="69" t="inlineStr">
+      <c r="I195" s="68" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -24831,11 +24099,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP195" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP195" s="65" t="inlineStr"/>
       <c r="AQ195" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -24847,7 +24111,7 @@
         </is>
       </c>
       <c r="AS195" s="23" t="n"/>
-      <c r="AT195" s="67" t="inlineStr"/>
+      <c r="AT195" s="66" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="53" t="inlineStr">
@@ -24886,7 +24150,7 @@
         </is>
       </c>
       <c r="H196" s="24" t="inlineStr"/>
-      <c r="I196" s="70" t="inlineStr">
+      <c r="I196" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -24957,11 +24221,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP196" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP196" s="65" t="inlineStr"/>
       <c r="AQ196" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -24973,10 +24233,10 @@
         </is>
       </c>
       <c r="AS196" s="23" t="n"/>
-      <c r="AT196" s="67" t="inlineStr"/>
+      <c r="AT196" s="66" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="68" t="inlineStr">
+      <c r="A197" s="67" t="inlineStr">
         <is>
           <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
@@ -25087,11 +24347,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP197" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP197" s="65" t="inlineStr"/>
       <c r="AQ197" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -25103,7 +24359,7 @@
         </is>
       </c>
       <c r="AS197" s="23" t="n"/>
-      <c r="AT197" s="67" t="inlineStr"/>
+      <c r="AT197" s="66" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="53" t="inlineStr">
@@ -25142,7 +24398,7 @@
         </is>
       </c>
       <c r="H198" s="24" t="inlineStr"/>
-      <c r="I198" s="69" t="inlineStr">
+      <c r="I198" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -25213,11 +24469,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP198" s="65" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
+      <c r="AP198" s="65" t="inlineStr"/>
       <c r="AQ198" s="65" t="inlineStr">
         <is>
           <t>Lugs not available, nut bolts not available</t>
@@ -25229,10 +24481,10 @@
         </is>
       </c>
       <c r="AS198" s="23" t="n"/>
-      <c r="AT198" s="67" t="inlineStr"/>
+      <c r="AT198" s="66" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="68" t="inlineStr">
+      <c r="A199" s="67" t="inlineStr">
         <is>
           <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
@@ -25343,11 +24595,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP199" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP199" s="65" t="inlineStr"/>
       <c r="AQ199" s="65" t="inlineStr">
         <is>
           <t>PS5-61-IV-0001B cannot close ITR due to transformer leakage issue.</t>
@@ -25359,7 +24607,7 @@
         </is>
       </c>
       <c r="AS199" s="23" t="n"/>
-      <c r="AT199" s="67" t="inlineStr"/>
+      <c r="AT199" s="66" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="53" t="inlineStr">
@@ -25394,7 +24642,7 @@
         </is>
       </c>
       <c r="H200" s="24" t="inlineStr"/>
-      <c r="I200" s="70" t="inlineStr">
+      <c r="I200" s="69" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -25465,11 +24713,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP200" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP200" s="65" t="inlineStr"/>
       <c r="AQ200" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -25481,7 +24725,7 @@
         </is>
       </c>
       <c r="AS200" s="23" t="n"/>
-      <c r="AT200" s="67" t="inlineStr"/>
+      <c r="AT200" s="66" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="53" t="inlineStr">
@@ -25520,7 +24764,7 @@
         </is>
       </c>
       <c r="H201" s="24" t="inlineStr"/>
-      <c r="I201" s="70" t="inlineStr">
+      <c r="I201" s="69" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -25591,11 +24835,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP201" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP201" s="65" t="inlineStr"/>
       <c r="AQ201" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -25607,10 +24847,10 @@
         </is>
       </c>
       <c r="AS201" s="23" t="n"/>
-      <c r="AT201" s="67" t="inlineStr"/>
+      <c r="AT201" s="66" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="68" t="inlineStr">
+      <c r="A202" s="67" t="inlineStr">
         <is>
           <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
@@ -25721,11 +24961,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP202" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP202" s="65" t="inlineStr"/>
       <c r="AQ202" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -25737,10 +24973,10 @@
         </is>
       </c>
       <c r="AS202" s="23" t="n"/>
-      <c r="AT202" s="67" t="inlineStr"/>
+      <c r="AT202" s="66" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="68" t="inlineStr">
+      <c r="A203" s="67" t="inlineStr">
         <is>
           <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
@@ -25851,11 +25087,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP203" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP203" s="65" t="inlineStr"/>
       <c r="AQ203" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -25867,7 +25099,7 @@
         </is>
       </c>
       <c r="AS203" s="23" t="n"/>
-      <c r="AT203" s="67" t="inlineStr"/>
+      <c r="AT203" s="66" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="53" t="inlineStr">
@@ -25886,7 +25118,7 @@
         </is>
       </c>
       <c r="H204" s="24" t="inlineStr"/>
-      <c r="I204" s="70" t="inlineStr">
+      <c r="I204" s="69" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -25951,7 +25183,7 @@
       <c r="AQ204" s="65" t="inlineStr"/>
       <c r="AR204" s="23" t="inlineStr"/>
       <c r="AS204" s="23" t="n"/>
-      <c r="AT204" s="67" t="inlineStr"/>
+      <c r="AT204" s="66" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="53" t="inlineStr">
@@ -25986,7 +25218,7 @@
         </is>
       </c>
       <c r="H205" s="24" t="inlineStr"/>
-      <c r="I205" s="70" t="inlineStr">
+      <c r="I205" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -26057,11 +25289,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP205" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP205" s="65" t="inlineStr"/>
       <c r="AQ205" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -26073,7 +25301,7 @@
         </is>
       </c>
       <c r="AS205" s="23" t="n"/>
-      <c r="AT205" s="67" t="inlineStr"/>
+      <c r="AT205" s="66" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="53" t="inlineStr">
@@ -26108,7 +25336,7 @@
         </is>
       </c>
       <c r="H206" s="24" t="inlineStr"/>
-      <c r="I206" s="70" t="inlineStr">
+      <c r="I206" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -26179,11 +25407,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP206" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP206" s="65" t="inlineStr"/>
       <c r="AQ206" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -26195,7 +25419,7 @@
         </is>
       </c>
       <c r="AS206" s="23" t="n"/>
-      <c r="AT206" s="67" t="inlineStr"/>
+      <c r="AT206" s="66" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="53" t="inlineStr">
@@ -26230,7 +25454,7 @@
         </is>
       </c>
       <c r="H207" s="24" t="inlineStr"/>
-      <c r="I207" s="70" t="inlineStr">
+      <c r="I207" s="69" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -26301,11 +25525,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP207" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP207" s="65" t="inlineStr"/>
       <c r="AQ207" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -26317,7 +25537,7 @@
         </is>
       </c>
       <c r="AS207" s="23" t="n"/>
-      <c r="AT207" s="67" t="inlineStr"/>
+      <c r="AT207" s="66" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="53" t="inlineStr">
@@ -26352,7 +25572,7 @@
         </is>
       </c>
       <c r="H208" s="24" t="inlineStr"/>
-      <c r="I208" s="70" t="inlineStr">
+      <c r="I208" s="69" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -26423,11 +25643,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP208" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP208" s="65" t="inlineStr"/>
       <c r="AQ208" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -26439,7 +25655,7 @@
         </is>
       </c>
       <c r="AS208" s="23" t="n"/>
-      <c r="AT208" s="67" t="inlineStr"/>
+      <c r="AT208" s="66" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="53" t="inlineStr">
@@ -26474,7 +25690,7 @@
         </is>
       </c>
       <c r="H209" s="24" t="inlineStr"/>
-      <c r="I209" s="69" t="inlineStr">
+      <c r="I209" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -26545,11 +25761,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP209" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP209" s="65" t="inlineStr"/>
       <c r="AQ209" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -26561,10 +25773,10 @@
         </is>
       </c>
       <c r="AS209" s="23" t="n"/>
-      <c r="AT209" s="67" t="inlineStr"/>
+      <c r="AT209" s="66" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="68" t="inlineStr">
+      <c r="A210" s="67" t="inlineStr">
         <is>
           <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
@@ -26675,11 +25887,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP210" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP210" s="65" t="inlineStr"/>
       <c r="AQ210" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -26691,7 +25899,7 @@
         </is>
       </c>
       <c r="AS210" s="23" t="n"/>
-      <c r="AT210" s="67" t="inlineStr"/>
+      <c r="AT210" s="66" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="53" t="inlineStr">
@@ -26726,7 +25934,7 @@
         </is>
       </c>
       <c r="H211" s="24" t="inlineStr"/>
-      <c r="I211" s="70" t="inlineStr">
+      <c r="I211" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -26797,11 +26005,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP211" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP211" s="65" t="inlineStr"/>
       <c r="AQ211" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -26813,7 +26017,7 @@
         </is>
       </c>
       <c r="AS211" s="23" t="n"/>
-      <c r="AT211" s="67" t="inlineStr"/>
+      <c r="AT211" s="66" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="53" t="inlineStr">
@@ -26856,7 +26060,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I212" s="70" t="inlineStr">
+      <c r="I212" s="69" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -26927,11 +26131,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP212" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP212" s="65" t="inlineStr"/>
       <c r="AQ212" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -26943,7 +26143,7 @@
         </is>
       </c>
       <c r="AS212" s="23" t="n"/>
-      <c r="AT212" s="67" t="inlineStr"/>
+      <c r="AT212" s="66" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="53" t="inlineStr">
@@ -26982,7 +26182,7 @@
         </is>
       </c>
       <c r="H213" s="24" t="inlineStr"/>
-      <c r="I213" s="70" t="inlineStr">
+      <c r="I213" s="69" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -27053,11 +26253,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP213" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP213" s="65" t="inlineStr"/>
       <c r="AQ213" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -27069,7 +26265,7 @@
         </is>
       </c>
       <c r="AS213" s="23" t="n"/>
-      <c r="AT213" s="67" t="inlineStr"/>
+      <c r="AT213" s="66" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="53" t="inlineStr">
@@ -27108,7 +26304,7 @@
         </is>
       </c>
       <c r="H214" s="24" t="inlineStr"/>
-      <c r="I214" s="70" t="inlineStr">
+      <c r="I214" s="69" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -27179,11 +26375,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP214" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP214" s="65" t="inlineStr"/>
       <c r="AQ214" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -27195,7 +26387,7 @@
         </is>
       </c>
       <c r="AS214" s="23" t="n"/>
-      <c r="AT214" s="67" t="inlineStr"/>
+      <c r="AT214" s="66" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="53" t="inlineStr">
@@ -27234,7 +26426,7 @@
         </is>
       </c>
       <c r="H215" s="24" t="inlineStr"/>
-      <c r="I215" s="70" t="inlineStr">
+      <c r="I215" s="69" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -27305,11 +26497,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP215" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP215" s="65" t="inlineStr"/>
       <c r="AQ215" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -27321,7 +26509,7 @@
         </is>
       </c>
       <c r="AS215" s="23" t="n"/>
-      <c r="AT215" s="67" t="inlineStr"/>
+      <c r="AT215" s="66" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="53" t="inlineStr">
@@ -27364,7 +26552,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I216" s="70" t="inlineStr">
+      <c r="I216" s="69" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -27435,11 +26623,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP216" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP216" s="65" t="inlineStr"/>
       <c r="AQ216" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -27451,7 +26635,7 @@
         </is>
       </c>
       <c r="AS216" s="23" t="n"/>
-      <c r="AT216" s="67" t="inlineStr"/>
+      <c r="AT216" s="66" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="53" t="inlineStr">
@@ -27490,7 +26674,7 @@
         </is>
       </c>
       <c r="H217" s="24" t="inlineStr"/>
-      <c r="I217" s="70" t="inlineStr">
+      <c r="I217" s="69" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -27561,11 +26745,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP217" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP217" s="65" t="inlineStr"/>
       <c r="AQ217" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -27577,7 +26757,7 @@
         </is>
       </c>
       <c r="AS217" s="23" t="n"/>
-      <c r="AT217" s="67" t="inlineStr"/>
+      <c r="AT217" s="66" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="53" t="inlineStr">
@@ -27661,7 +26841,7 @@
       <c r="AQ218" s="65" t="inlineStr"/>
       <c r="AR218" s="23" t="inlineStr"/>
       <c r="AS218" s="23" t="n"/>
-      <c r="AT218" s="67" t="inlineStr"/>
+      <c r="AT218" s="66" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="53" t="inlineStr">
@@ -27745,7 +26925,7 @@
       <c r="AQ219" s="65" t="inlineStr"/>
       <c r="AR219" s="23" t="inlineStr"/>
       <c r="AS219" s="23" t="n"/>
-      <c r="AT219" s="67" t="inlineStr"/>
+      <c r="AT219" s="66" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="53" t="inlineStr">
@@ -27780,7 +26960,7 @@
         </is>
       </c>
       <c r="H220" s="24" t="inlineStr"/>
-      <c r="I220" s="70" t="inlineStr">
+      <c r="I220" s="69" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -27851,11 +27031,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP220" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP220" s="65" t="inlineStr"/>
       <c r="AQ220" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -27867,7 +27043,7 @@
         </is>
       </c>
       <c r="AS220" s="23" t="n"/>
-      <c r="AT220" s="67" t="inlineStr"/>
+      <c r="AT220" s="66" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="53" t="inlineStr">
@@ -27902,7 +27078,7 @@
         </is>
       </c>
       <c r="H221" s="24" t="inlineStr"/>
-      <c r="I221" s="70" t="inlineStr">
+      <c r="I221" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -27973,11 +27149,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP221" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP221" s="65" t="inlineStr"/>
       <c r="AQ221" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -27989,7 +27161,7 @@
         </is>
       </c>
       <c r="AS221" s="23" t="n"/>
-      <c r="AT221" s="67" t="inlineStr"/>
+      <c r="AT221" s="66" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="53" t="inlineStr">
@@ -28024,7 +27196,7 @@
         </is>
       </c>
       <c r="H222" s="24" t="inlineStr"/>
-      <c r="I222" s="70" t="inlineStr">
+      <c r="I222" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -28095,11 +27267,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP222" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP222" s="65" t="inlineStr"/>
       <c r="AQ222" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -28111,7 +27279,7 @@
         </is>
       </c>
       <c r="AS222" s="23" t="n"/>
-      <c r="AT222" s="67" t="inlineStr"/>
+      <c r="AT222" s="66" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="53" t="inlineStr">
@@ -28146,7 +27314,7 @@
         </is>
       </c>
       <c r="H223" s="24" t="inlineStr"/>
-      <c r="I223" s="70" t="inlineStr">
+      <c r="I223" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -28217,11 +27385,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP223" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP223" s="65" t="inlineStr"/>
       <c r="AQ223" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -28233,7 +27397,7 @@
         </is>
       </c>
       <c r="AS223" s="23" t="n"/>
-      <c r="AT223" s="67" t="inlineStr"/>
+      <c r="AT223" s="66" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="53" t="inlineStr">
@@ -28268,7 +27432,7 @@
         </is>
       </c>
       <c r="H224" s="24" t="inlineStr"/>
-      <c r="I224" s="70" t="inlineStr">
+      <c r="I224" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -28339,11 +27503,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP224" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP224" s="65" t="inlineStr"/>
       <c r="AQ224" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -28355,7 +27515,7 @@
         </is>
       </c>
       <c r="AS224" s="23" t="n"/>
-      <c r="AT224" s="67" t="inlineStr"/>
+      <c r="AT224" s="66" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="53" t="inlineStr">
@@ -28390,7 +27550,7 @@
         </is>
       </c>
       <c r="H225" s="24" t="inlineStr"/>
-      <c r="I225" s="70" t="inlineStr">
+      <c r="I225" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -28461,11 +27621,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP225" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP225" s="65" t="inlineStr"/>
       <c r="AQ225" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -28477,7 +27633,7 @@
         </is>
       </c>
       <c r="AS225" s="23" t="n"/>
-      <c r="AT225" s="67" t="inlineStr"/>
+      <c r="AT225" s="66" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="53" t="inlineStr">
@@ -28512,7 +27668,7 @@
         </is>
       </c>
       <c r="H226" s="24" t="inlineStr"/>
-      <c r="I226" s="70" t="inlineStr">
+      <c r="I226" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -28583,11 +27739,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP226" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP226" s="65" t="inlineStr"/>
       <c r="AQ226" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -28599,7 +27751,7 @@
         </is>
       </c>
       <c r="AS226" s="23" t="n"/>
-      <c r="AT226" s="67" t="inlineStr"/>
+      <c r="AT226" s="66" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="53" t="inlineStr">
@@ -28642,7 +27794,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I227" s="70" t="inlineStr">
+      <c r="I227" s="69" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -28713,14 +27865,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP227" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP227" s="65" t="inlineStr"/>
       <c r="AQ227" s="65" t="inlineStr">
         <is>
-          <t>18 ITRs for lightning, 22 ITRs for grounding cannot be closed due to material issues.</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR227" s="23" t="inlineStr">
@@ -28729,7 +27877,7 @@
         </is>
       </c>
       <c r="AS227" s="23" t="n"/>
-      <c r="AT227" s="67" t="inlineStr"/>
+      <c r="AT227" s="66" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="53" t="inlineStr">
@@ -28764,7 +27912,7 @@
         </is>
       </c>
       <c r="H228" s="24" t="inlineStr"/>
-      <c r="I228" s="70" t="inlineStr">
+      <c r="I228" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -28835,11 +27983,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP228" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP228" s="65" t="inlineStr"/>
       <c r="AQ228" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -28851,7 +27995,7 @@
         </is>
       </c>
       <c r="AS228" s="23" t="n"/>
-      <c r="AT228" s="67" t="inlineStr"/>
+      <c r="AT228" s="66" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="53" t="inlineStr">
@@ -28894,7 +28038,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I229" s="69" t="inlineStr">
+      <c r="I229" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -28965,11 +28109,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP229" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP229" s="65" t="inlineStr"/>
       <c r="AQ229" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -28981,10 +28121,10 @@
         </is>
       </c>
       <c r="AS229" s="23" t="n"/>
-      <c r="AT229" s="67" t="inlineStr"/>
+      <c r="AT229" s="66" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="68" t="inlineStr">
+      <c r="A230" s="67" t="inlineStr">
         <is>
           <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
@@ -29065,7 +28205,7 @@
       <c r="AQ230" s="65" t="inlineStr"/>
       <c r="AR230" s="23" t="inlineStr"/>
       <c r="AS230" s="23" t="n"/>
-      <c r="AT230" s="67" t="inlineStr"/>
+      <c r="AT230" s="66" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="53" t="inlineStr">
@@ -29100,7 +28240,7 @@
         </is>
       </c>
       <c r="H231" s="24" t="inlineStr"/>
-      <c r="I231" s="70" t="inlineStr">
+      <c r="I231" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -29171,11 +28311,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP231" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP231" s="65" t="inlineStr"/>
       <c r="AQ231" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -29187,7 +28323,7 @@
         </is>
       </c>
       <c r="AS231" s="23" t="n"/>
-      <c r="AT231" s="67" t="inlineStr"/>
+      <c r="AT231" s="66" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="53" t="inlineStr">
@@ -29222,7 +28358,7 @@
         </is>
       </c>
       <c r="H232" s="24" t="inlineStr"/>
-      <c r="I232" s="70" t="inlineStr">
+      <c r="I232" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -29293,11 +28429,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP232" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP232" s="65" t="inlineStr"/>
       <c r="AQ232" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -29309,7 +28441,7 @@
         </is>
       </c>
       <c r="AS232" s="23" t="n"/>
-      <c r="AT232" s="67" t="inlineStr"/>
+      <c r="AT232" s="66" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="53" t="inlineStr">
@@ -29344,7 +28476,7 @@
         </is>
       </c>
       <c r="H233" s="24" t="inlineStr"/>
-      <c r="I233" s="70" t="inlineStr">
+      <c r="I233" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -29415,11 +28547,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP233" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP233" s="65" t="inlineStr"/>
       <c r="AQ233" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -29431,7 +28559,7 @@
         </is>
       </c>
       <c r="AS233" s="23" t="n"/>
-      <c r="AT233" s="67" t="inlineStr"/>
+      <c r="AT233" s="66" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="53" t="inlineStr">
@@ -29466,7 +28594,7 @@
         </is>
       </c>
       <c r="H234" s="24" t="inlineStr"/>
-      <c r="I234" s="70" t="inlineStr">
+      <c r="I234" s="69" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -29537,11 +28665,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP234" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP234" s="65" t="inlineStr"/>
       <c r="AQ234" s="65" t="inlineStr">
         <is>
           <t>PS5-71-TW-0007, PS5-71-TW-0003, PS5-71-TW-0004, PS5-71-TW-0006 not arrived</t>
@@ -29553,7 +28677,7 @@
         </is>
       </c>
       <c r="AS234" s="23" t="n"/>
-      <c r="AT234" s="67" t="inlineStr"/>
+      <c r="AT234" s="66" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="53" t="inlineStr">
@@ -29588,7 +28712,7 @@
         </is>
       </c>
       <c r="H235" s="24" t="inlineStr"/>
-      <c r="I235" s="69" t="inlineStr">
+      <c r="I235" s="68" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -29659,11 +28783,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP235" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP235" s="65" t="inlineStr"/>
       <c r="AQ235" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -29675,7 +28795,7 @@
         </is>
       </c>
       <c r="AS235" s="23" t="n"/>
-      <c r="AT235" s="67" t="inlineStr"/>
+      <c r="AT235" s="66" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="53" t="inlineStr">
@@ -29694,7 +28814,7 @@
         </is>
       </c>
       <c r="H236" s="24" t="inlineStr"/>
-      <c r="I236" s="70" t="inlineStr">
+      <c r="I236" s="69" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
@@ -29759,7 +28879,7 @@
       <c r="AQ236" s="65" t="inlineStr"/>
       <c r="AR236" s="23" t="inlineStr"/>
       <c r="AS236" s="23" t="n"/>
-      <c r="AT236" s="67" t="inlineStr"/>
+      <c r="AT236" s="66" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="53" t="inlineStr">
@@ -29794,7 +28914,7 @@
         </is>
       </c>
       <c r="H237" s="24" t="inlineStr"/>
-      <c r="I237" s="69" t="inlineStr">
+      <c r="I237" s="68" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
@@ -29865,11 +28985,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP237" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="AP237" s="65" t="inlineStr"/>
       <c r="AQ237" s="65" t="inlineStr">
         <is>
           <t>PS5-71-TW-4103, PS5-71-TW-4102
@@ -29883,7 +28999,7 @@
         </is>
       </c>
       <c r="AS237" s="23" t="n"/>
-      <c r="AT237" s="67" t="inlineStr"/>
+      <c r="AT237" s="66" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="53" t="inlineStr">
@@ -29918,7 +29034,7 @@
         </is>
       </c>
       <c r="H238" s="24" t="inlineStr"/>
-      <c r="I238" s="69" t="inlineStr">
+      <c r="I238" s="68" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -29989,11 +29105,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP238" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP238" s="65" t="inlineStr"/>
       <c r="AQ238" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -30005,7 +29117,7 @@
         </is>
       </c>
       <c r="AS238" s="23" t="n"/>
-      <c r="AT238" s="67" t="inlineStr"/>
+      <c r="AT238" s="66" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="53" t="inlineStr">
@@ -30044,7 +29156,7 @@
         </is>
       </c>
       <c r="H239" s="24" t="inlineStr"/>
-      <c r="I239" s="69" t="inlineStr">
+      <c r="I239" s="68" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
@@ -30115,11 +29227,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP239" s="65" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+      <c r="AP239" s="65" t="inlineStr"/>
       <c r="AQ239" s="65" t="inlineStr">
         <is>
           <t>PS5-71-BI-0001A-CC01 12P X 0.75 OS FL RTD 20m
@@ -30151,7 +29259,7 @@
         </is>
       </c>
       <c r="AS239" s="23" t="n"/>
-      <c r="AT239" s="67" t="inlineStr"/>
+      <c r="AT239" s="66" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="53" t="inlineStr">
@@ -30190,7 +29298,7 @@
         </is>
       </c>
       <c r="H240" s="24" t="inlineStr"/>
-      <c r="I240" s="69" t="inlineStr">
+      <c r="I240" s="68" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -30222,7 +29330,7 @@
       <c r="R240" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="S240" s="71" t="inlineStr">
+      <c r="S240" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -30261,11 +29369,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP240" s="65" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+      <c r="AP240" s="65" t="inlineStr"/>
       <c r="AQ240" s="65" t="inlineStr">
         <is>
           <t>cable drum not available for 24 cables, added in Rev09of cable schedule.
@@ -30279,7 +29383,7 @@
         </is>
       </c>
       <c r="AS240" s="23" t="n"/>
-      <c r="AT240" s="67" t="inlineStr"/>
+      <c r="AT240" s="66" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="53" t="inlineStr">
@@ -30393,11 +29497,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP241" s="65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="AP241" s="65" t="inlineStr"/>
       <c r="AQ241" s="65" t="inlineStr">
         <is>
           <t>PS5-71-BI-0003-CC04 6P X 0.75 OS FL RTD 20m
@@ -30411,7 +29511,7 @@
         </is>
       </c>
       <c r="AS241" s="23" t="n"/>
-      <c r="AT241" s="67" t="inlineStr"/>
+      <c r="AT241" s="66" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="53" t="inlineStr">
@@ -30486,7 +29586,7 @@
       <c r="R242" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S242" s="71" t="inlineStr">
+      <c r="S242" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -30525,15 +29625,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP242" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP242" s="65" t="inlineStr"/>
       <c r="AQ242" s="65" t="inlineStr"/>
       <c r="AR242" s="23" t="inlineStr"/>
       <c r="AS242" s="23" t="n"/>
-      <c r="AT242" s="67" t="inlineStr"/>
+      <c r="AT242" s="66" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="53" t="inlineStr">
@@ -30568,7 +29664,7 @@
         </is>
       </c>
       <c r="H243" s="24" t="inlineStr"/>
-      <c r="I243" s="69" t="inlineStr">
+      <c r="I243" s="68" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -30639,11 +29735,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP243" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="AP243" s="65" t="inlineStr"/>
       <c r="AQ243" s="65" t="inlineStr">
         <is>
           <t>PS5-71-TW-4203, PS5-71-TW-4202 not arrived</t>
@@ -30655,7 +29747,7 @@
         </is>
       </c>
       <c r="AS243" s="23" t="n"/>
-      <c r="AT243" s="67" t="inlineStr"/>
+      <c r="AT243" s="66" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="53" t="inlineStr">
@@ -30690,7 +29782,7 @@
         </is>
       </c>
       <c r="H244" s="24" t="inlineStr"/>
-      <c r="I244" s="69" t="inlineStr">
+      <c r="I244" s="68" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -30761,11 +29853,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP244" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP244" s="65" t="inlineStr"/>
       <c r="AQ244" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -30777,7 +29865,7 @@
         </is>
       </c>
       <c r="AS244" s="23" t="n"/>
-      <c r="AT244" s="67" t="inlineStr"/>
+      <c r="AT244" s="66" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="53" t="inlineStr">
@@ -30812,7 +29900,7 @@
         </is>
       </c>
       <c r="H245" s="24" t="inlineStr"/>
-      <c r="I245" s="69" t="inlineStr">
+      <c r="I245" s="68" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -30883,11 +29971,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP245" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP245" s="65" t="inlineStr"/>
       <c r="AQ245" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -30899,7 +29983,7 @@
         </is>
       </c>
       <c r="AS245" s="23" t="n"/>
-      <c r="AT245" s="67" t="inlineStr"/>
+      <c r="AT245" s="66" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="53" t="inlineStr">
@@ -30934,7 +30018,7 @@
         </is>
       </c>
       <c r="H246" s="24" t="inlineStr"/>
-      <c r="I246" s="69" t="inlineStr">
+      <c r="I246" s="68" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -31005,11 +30089,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP246" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP246" s="65" t="inlineStr"/>
       <c r="AQ246" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -31021,7 +30101,7 @@
         </is>
       </c>
       <c r="AS246" s="23" t="n"/>
-      <c r="AT246" s="67" t="inlineStr"/>
+      <c r="AT246" s="66" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="53" t="inlineStr">
@@ -31060,7 +30140,7 @@
         </is>
       </c>
       <c r="H247" s="24" t="inlineStr"/>
-      <c r="I247" s="69" t="inlineStr">
+      <c r="I247" s="68" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -31131,11 +30211,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP247" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP247" s="65" t="inlineStr"/>
       <c r="AQ247" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -31147,7 +30223,7 @@
         </is>
       </c>
       <c r="AS247" s="23" t="n"/>
-      <c r="AT247" s="67" t="inlineStr"/>
+      <c r="AT247" s="66" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="53" t="inlineStr">
@@ -31261,11 +30337,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP248" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP248" s="65" t="inlineStr"/>
       <c r="AQ248" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -31277,7 +30349,7 @@
         </is>
       </c>
       <c r="AS248" s="23" t="n"/>
-      <c r="AT248" s="67" t="inlineStr"/>
+      <c r="AT248" s="66" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="53" t="inlineStr">
@@ -31320,7 +30392,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I249" s="69" t="inlineStr">
+      <c r="I249" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -31391,11 +30463,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP249" s="65" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="AP249" s="65" t="inlineStr"/>
       <c r="AQ249" s="65" t="inlineStr">
         <is>
           <t>PS5-71-BI-0002-CC01, 155m ,Cable type:12P X 0.75 OS FL RTD
@@ -31411,7 +30479,7 @@
         </is>
       </c>
       <c r="AS249" s="23" t="n"/>
-      <c r="AT249" s="67" t="inlineStr"/>
+      <c r="AT249" s="66" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="53" t="inlineStr">
@@ -31450,7 +30518,7 @@
         </is>
       </c>
       <c r="H250" s="24" t="inlineStr"/>
-      <c r="I250" s="69" t="inlineStr">
+      <c r="I250" s="68" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -31482,7 +30550,7 @@
       <c r="R250" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="S250" s="71" t="inlineStr">
+      <c r="S250" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -31521,11 +30589,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP250" s="65" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="AP250" s="65" t="inlineStr"/>
       <c r="AQ250" s="65" t="inlineStr">
         <is>
           <t>PS5-71-BE-0005-CL01 4C+E 16 210m , PS5-71-BE-0005-CL02 2C+E 2.5 210m ,   PS5-71-BE-0005-CL03 4C+E 6 210m
@@ -31539,7 +30603,7 @@
         </is>
       </c>
       <c r="AS250" s="23" t="n"/>
-      <c r="AT250" s="67" t="inlineStr"/>
+      <c r="AT250" s="66" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="53" t="inlineStr">
@@ -31582,7 +30646,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I251" s="69" t="inlineStr">
+      <c r="I251" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -31653,11 +30717,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP251" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="AP251" s="65" t="inlineStr"/>
       <c r="AQ251" s="65" t="inlineStr">
         <is>
           <t>6 ITRS pending due to LIT 1201/1202 (not arrived yet)</t>
@@ -31669,7 +30729,7 @@
         </is>
       </c>
       <c r="AS251" s="23" t="n"/>
-      <c r="AT251" s="67" t="inlineStr"/>
+      <c r="AT251" s="66" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="53" t="inlineStr">
@@ -31783,11 +30843,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP252" s="65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="AP252" s="65" t="inlineStr"/>
       <c r="AQ252" s="65" t="inlineStr">
         <is>
           <t>PS5-71-21-0331 - Test Package - CPP Item Nipple and 1/2 Flange not available at site. CPY/EPS Supply Item PS5-71-FIT-0019 – SRN-01997, awaiting collection from vendor by MLC (airfreight).
@@ -31801,10 +30857,10 @@
         </is>
       </c>
       <c r="AS252" s="23" t="n"/>
-      <c r="AT252" s="67" t="inlineStr"/>
+      <c r="AT252" s="66" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="68" t="inlineStr">
+      <c r="A253" s="67" t="inlineStr">
         <is>
           <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
@@ -31836,7 +30892,7 @@
       </c>
       <c r="G253" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H253" s="24" t="inlineStr">
@@ -31915,11 +30971,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP253" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP253" s="65" t="inlineStr"/>
       <c r="AQ253" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -31931,7 +30983,7 @@
         </is>
       </c>
       <c r="AS253" s="23" t="n"/>
-      <c r="AT253" s="67" t="inlineStr"/>
+      <c r="AT253" s="66" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="53" t="inlineStr">
@@ -31974,7 +31026,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I254" s="69" t="inlineStr">
+      <c r="I254" s="68" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -32006,7 +31058,7 @@
       <c r="R254" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S254" s="71" t="inlineStr">
+      <c r="S254" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -32045,11 +31097,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP254" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="AP254" s="65" t="inlineStr"/>
       <c r="AQ254" s="65" t="inlineStr">
         <is>
           <t>PS5-71-BI-0005-CC01 12P X 0.75 OS FL RTD cable not available</t>
@@ -32061,7 +31109,7 @@
         </is>
       </c>
       <c r="AS254" s="23" t="n"/>
-      <c r="AT254" s="67" t="inlineStr"/>
+      <c r="AT254" s="66" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="53" t="inlineStr">
@@ -32104,7 +31152,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I255" s="69" t="inlineStr">
+      <c r="I255" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -32175,11 +31223,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP255" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP255" s="65" t="inlineStr"/>
       <c r="AQ255" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -32191,7 +31235,7 @@
         </is>
       </c>
       <c r="AS255" s="23" t="n"/>
-      <c r="AT255" s="67" t="inlineStr"/>
+      <c r="AT255" s="66" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="53" t="inlineStr">
@@ -32234,7 +31278,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I256" s="69" t="inlineStr">
+      <c r="I256" s="68" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -32305,11 +31349,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP256" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP256" s="65" t="inlineStr"/>
       <c r="AQ256" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -32321,10 +31361,10 @@
         </is>
       </c>
       <c r="AS256" s="23" t="n"/>
-      <c r="AT256" s="67" t="inlineStr"/>
+      <c r="AT256" s="66" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="68" t="inlineStr">
+      <c r="A257" s="67" t="inlineStr">
         <is>
           <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
@@ -32435,11 +31475,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP257" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP257" s="65" t="inlineStr"/>
       <c r="AQ257" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -32451,7 +31487,7 @@
         </is>
       </c>
       <c r="AS257" s="23" t="n"/>
-      <c r="AT257" s="67" t="inlineStr"/>
+      <c r="AT257" s="66" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="53" t="inlineStr">
@@ -32486,7 +31522,7 @@
         </is>
       </c>
       <c r="H258" s="24" t="inlineStr"/>
-      <c r="I258" s="69" t="inlineStr">
+      <c r="I258" s="68" t="inlineStr">
         <is>
           <t>81%</t>
         </is>
@@ -32557,11 +31593,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP258" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP258" s="65" t="inlineStr"/>
       <c r="AQ258" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -32573,7 +31605,7 @@
         </is>
       </c>
       <c r="AS258" s="23" t="n"/>
-      <c r="AT258" s="67" t="inlineStr"/>
+      <c r="AT258" s="66" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="53" t="inlineStr">
@@ -32608,7 +31640,7 @@
         </is>
       </c>
       <c r="H259" s="24" t="inlineStr"/>
-      <c r="I259" s="70" t="inlineStr">
+      <c r="I259" s="69" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
@@ -32679,11 +31711,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AP259" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP259" s="65" t="inlineStr"/>
       <c r="AQ259" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -32695,7 +31723,7 @@
         </is>
       </c>
       <c r="AS259" s="23" t="n"/>
-      <c r="AT259" s="67" t="inlineStr"/>
+      <c r="AT259" s="66" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="53" t="inlineStr">
@@ -32730,7 +31758,7 @@
         </is>
       </c>
       <c r="H260" s="24" t="inlineStr"/>
-      <c r="I260" s="69" t="inlineStr">
+      <c r="I260" s="68" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -32801,11 +31829,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP260" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP260" s="65" t="inlineStr"/>
       <c r="AQ260" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -32817,7 +31841,7 @@
         </is>
       </c>
       <c r="AS260" s="23" t="n"/>
-      <c r="AT260" s="67" t="inlineStr"/>
+      <c r="AT260" s="66" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="53" t="inlineStr">
@@ -32852,7 +31876,7 @@
         </is>
       </c>
       <c r="H261" s="24" t="inlineStr"/>
-      <c r="I261" s="69" t="inlineStr">
+      <c r="I261" s="68" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
@@ -32923,11 +31947,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP261" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP261" s="65" t="inlineStr"/>
       <c r="AQ261" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -32939,10 +31959,10 @@
         </is>
       </c>
       <c r="AS261" s="23" t="n"/>
-      <c r="AT261" s="67" t="inlineStr"/>
+      <c r="AT261" s="66" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="74" t="inlineStr">
+      <c r="A262" s="73" t="inlineStr">
         <is>
           <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
@@ -32968,7 +31988,7 @@
         </is>
       </c>
       <c r="F262" s="23" t="inlineStr"/>
-      <c r="G262" s="69" t="inlineStr">
+      <c r="G262" s="68" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -32978,7 +31998,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I262" s="69" t="inlineStr">
+      <c r="I262" s="68" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -33049,11 +32069,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP262" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP262" s="65" t="inlineStr"/>
       <c r="AQ262" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -33065,7 +32081,7 @@
         </is>
       </c>
       <c r="AS262" s="23" t="n"/>
-      <c r="AT262" s="67" t="inlineStr"/>
+      <c r="AT262" s="66" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="53" t="inlineStr">
@@ -33100,7 +32116,7 @@
         </is>
       </c>
       <c r="H263" s="24" t="inlineStr"/>
-      <c r="I263" s="70" t="inlineStr">
+      <c r="I263" s="69" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -33171,11 +32187,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP263" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP263" s="65" t="inlineStr"/>
       <c r="AQ263" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -33187,7 +32199,7 @@
         </is>
       </c>
       <c r="AS263" s="23" t="n"/>
-      <c r="AT263" s="67" t="inlineStr"/>
+      <c r="AT263" s="66" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="53" t="inlineStr">
@@ -33222,7 +32234,7 @@
         </is>
       </c>
       <c r="H264" s="24" t="inlineStr"/>
-      <c r="I264" s="70" t="inlineStr">
+      <c r="I264" s="69" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -33293,11 +32305,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP264" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP264" s="65" t="inlineStr"/>
       <c r="AQ264" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -33309,7 +32317,7 @@
         </is>
       </c>
       <c r="AS264" s="23" t="n"/>
-      <c r="AT264" s="67" t="inlineStr"/>
+      <c r="AT264" s="66" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="53" t="inlineStr">
@@ -33344,7 +32352,7 @@
         </is>
       </c>
       <c r="H265" s="24" t="inlineStr"/>
-      <c r="I265" s="70" t="inlineStr">
+      <c r="I265" s="69" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -33415,11 +32423,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP265" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP265" s="65" t="inlineStr"/>
       <c r="AQ265" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -33431,7 +32435,7 @@
         </is>
       </c>
       <c r="AS265" s="23" t="n"/>
-      <c r="AT265" s="67" t="inlineStr"/>
+      <c r="AT265" s="66" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="53" t="inlineStr">
@@ -33466,7 +32470,7 @@
         </is>
       </c>
       <c r="H266" s="24" t="inlineStr"/>
-      <c r="I266" s="70" t="inlineStr">
+      <c r="I266" s="69" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -33537,11 +32541,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP266" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP266" s="65" t="inlineStr"/>
       <c r="AQ266" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -33553,7 +32553,7 @@
         </is>
       </c>
       <c r="AS266" s="23" t="n"/>
-      <c r="AT266" s="67" t="inlineStr"/>
+      <c r="AT266" s="66" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="53" t="inlineStr">
@@ -33588,7 +32588,7 @@
         </is>
       </c>
       <c r="H267" s="24" t="inlineStr"/>
-      <c r="I267" s="70" t="inlineStr">
+      <c r="I267" s="69" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -33659,11 +32659,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP267" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP267" s="65" t="inlineStr"/>
       <c r="AQ267" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -33675,7 +32671,7 @@
         </is>
       </c>
       <c r="AS267" s="23" t="n"/>
-      <c r="AT267" s="67" t="inlineStr"/>
+      <c r="AT267" s="66" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="53" t="inlineStr">
@@ -33710,7 +32706,7 @@
         </is>
       </c>
       <c r="H268" s="24" t="inlineStr"/>
-      <c r="I268" s="70" t="inlineStr">
+      <c r="I268" s="69" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -33781,11 +32777,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP268" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP268" s="65" t="inlineStr"/>
       <c r="AQ268" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -33797,7 +32789,7 @@
         </is>
       </c>
       <c r="AS268" s="23" t="n"/>
-      <c r="AT268" s="67" t="inlineStr"/>
+      <c r="AT268" s="66" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="53" t="inlineStr">
@@ -33832,7 +32824,7 @@
         </is>
       </c>
       <c r="H269" s="24" t="inlineStr"/>
-      <c r="I269" s="70" t="inlineStr">
+      <c r="I269" s="69" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -33903,11 +32895,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP269" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP269" s="65" t="inlineStr"/>
       <c r="AQ269" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -33919,7 +32907,7 @@
         </is>
       </c>
       <c r="AS269" s="23" t="n"/>
-      <c r="AT269" s="67" t="inlineStr"/>
+      <c r="AT269" s="66" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="53" t="inlineStr">
@@ -33954,7 +32942,7 @@
         </is>
       </c>
       <c r="H270" s="24" t="inlineStr"/>
-      <c r="I270" s="70" t="inlineStr">
+      <c r="I270" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -34025,11 +33013,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP270" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP270" s="65" t="inlineStr"/>
       <c r="AQ270" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -34041,7 +33025,7 @@
         </is>
       </c>
       <c r="AS270" s="23" t="n"/>
-      <c r="AT270" s="67" t="inlineStr"/>
+      <c r="AT270" s="66" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="53" t="inlineStr">
@@ -34076,7 +33060,7 @@
         </is>
       </c>
       <c r="H271" s="24" t="inlineStr"/>
-      <c r="I271" s="70" t="inlineStr">
+      <c r="I271" s="69" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -34147,11 +33131,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP271" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP271" s="65" t="inlineStr"/>
       <c r="AQ271" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -34163,7 +33143,7 @@
         </is>
       </c>
       <c r="AS271" s="23" t="n"/>
-      <c r="AT271" s="67" t="inlineStr"/>
+      <c r="AT271" s="66" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="53" t="inlineStr">
@@ -34198,7 +33178,7 @@
         </is>
       </c>
       <c r="H272" s="24" t="inlineStr"/>
-      <c r="I272" s="70" t="inlineStr">
+      <c r="I272" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -34269,11 +33249,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP272" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP272" s="65" t="inlineStr"/>
       <c r="AQ272" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -34285,7 +33261,7 @@
         </is>
       </c>
       <c r="AS272" s="23" t="n"/>
-      <c r="AT272" s="67" t="inlineStr"/>
+      <c r="AT272" s="66" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="53" t="inlineStr">
@@ -34320,7 +33296,7 @@
         </is>
       </c>
       <c r="H273" s="24" t="inlineStr"/>
-      <c r="I273" s="70" t="inlineStr">
+      <c r="I273" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -34391,11 +33367,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP273" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP273" s="65" t="inlineStr"/>
       <c r="AQ273" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -34407,7 +33379,7 @@
         </is>
       </c>
       <c r="AS273" s="23" t="n"/>
-      <c r="AT273" s="67" t="inlineStr"/>
+      <c r="AT273" s="66" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="53" t="inlineStr">
@@ -34442,7 +33414,7 @@
         </is>
       </c>
       <c r="H274" s="24" t="inlineStr"/>
-      <c r="I274" s="70" t="inlineStr">
+      <c r="I274" s="69" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -34513,11 +33485,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP274" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP274" s="65" t="inlineStr"/>
       <c r="AQ274" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -34529,7 +33497,7 @@
         </is>
       </c>
       <c r="AS274" s="23" t="n"/>
-      <c r="AT274" s="67" t="inlineStr"/>
+      <c r="AT274" s="66" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="53" t="inlineStr">
@@ -34564,7 +33532,7 @@
         </is>
       </c>
       <c r="H275" s="24" t="inlineStr"/>
-      <c r="I275" s="69" t="inlineStr">
+      <c r="I275" s="68" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -34635,11 +33603,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP275" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP275" s="65" t="inlineStr"/>
       <c r="AQ275" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -34651,7 +33615,7 @@
         </is>
       </c>
       <c r="AS275" s="23" t="n"/>
-      <c r="AT275" s="67" t="inlineStr"/>
+      <c r="AT275" s="66" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="53" t="inlineStr">
@@ -34686,7 +33650,7 @@
         </is>
       </c>
       <c r="H276" s="24" t="inlineStr"/>
-      <c r="I276" s="70" t="inlineStr">
+      <c r="I276" s="69" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -34757,11 +33721,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP276" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP276" s="65" t="inlineStr"/>
       <c r="AQ276" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -34773,7 +33733,7 @@
         </is>
       </c>
       <c r="AS276" s="23" t="n"/>
-      <c r="AT276" s="67" t="inlineStr"/>
+      <c r="AT276" s="66" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="53" t="inlineStr">
@@ -34808,7 +33768,7 @@
         </is>
       </c>
       <c r="H277" s="24" t="inlineStr"/>
-      <c r="I277" s="70" t="inlineStr">
+      <c r="I277" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -34879,11 +33839,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP277" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP277" s="65" t="inlineStr"/>
       <c r="AQ277" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -34895,7 +33851,7 @@
         </is>
       </c>
       <c r="AS277" s="23" t="n"/>
-      <c r="AT277" s="67" t="inlineStr"/>
+      <c r="AT277" s="66" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="53" t="inlineStr">
@@ -34930,7 +33886,7 @@
         </is>
       </c>
       <c r="H278" s="24" t="inlineStr"/>
-      <c r="I278" s="69" t="inlineStr">
+      <c r="I278" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -35001,11 +33957,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP278" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP278" s="65" t="inlineStr"/>
       <c r="AQ278" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -35017,7 +33969,7 @@
         </is>
       </c>
       <c r="AS278" s="23" t="n"/>
-      <c r="AT278" s="67" t="inlineStr"/>
+      <c r="AT278" s="66" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="53" t="inlineStr">
@@ -35052,7 +34004,7 @@
         </is>
       </c>
       <c r="H279" s="24" t="inlineStr"/>
-      <c r="I279" s="70" t="inlineStr">
+      <c r="I279" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -35123,11 +34075,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP279" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP279" s="65" t="inlineStr"/>
       <c r="AQ279" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -35139,7 +34087,7 @@
         </is>
       </c>
       <c r="AS279" s="23" t="n"/>
-      <c r="AT279" s="67" t="inlineStr"/>
+      <c r="AT279" s="66" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="53" t="inlineStr">
@@ -35174,7 +34122,7 @@
         </is>
       </c>
       <c r="H280" s="24" t="inlineStr"/>
-      <c r="I280" s="70" t="inlineStr">
+      <c r="I280" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -35245,11 +34193,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP280" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP280" s="65" t="inlineStr"/>
       <c r="AQ280" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -35261,7 +34205,7 @@
         </is>
       </c>
       <c r="AS280" s="23" t="n"/>
-      <c r="AT280" s="67" t="inlineStr"/>
+      <c r="AT280" s="66" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="53" t="inlineStr">
@@ -35296,7 +34240,7 @@
         </is>
       </c>
       <c r="H281" s="24" t="inlineStr"/>
-      <c r="I281" s="70" t="inlineStr">
+      <c r="I281" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -35367,11 +34311,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP281" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP281" s="65" t="inlineStr"/>
       <c r="AQ281" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -35383,10 +34323,10 @@
         </is>
       </c>
       <c r="AS281" s="23" t="n"/>
-      <c r="AT281" s="67" t="inlineStr"/>
+      <c r="AT281" s="66" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="68" t="inlineStr">
+      <c r="A282" s="67" t="inlineStr">
         <is>
           <t>PS5-83-01 - EITS Building</t>
         </is>
@@ -35497,11 +34437,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP282" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP282" s="65" t="inlineStr"/>
       <c r="AQ282" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -35513,7 +34449,7 @@
         </is>
       </c>
       <c r="AS282" s="23" t="n"/>
-      <c r="AT282" s="67" t="inlineStr"/>
+      <c r="AT282" s="66" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="53" t="inlineStr">
@@ -35548,7 +34484,7 @@
         </is>
       </c>
       <c r="H283" s="24" t="inlineStr"/>
-      <c r="I283" s="70" t="inlineStr">
+      <c r="I283" s="69" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -35619,11 +34555,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP283" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP283" s="65" t="inlineStr"/>
       <c r="AQ283" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -35635,7 +34567,7 @@
         </is>
       </c>
       <c r="AS283" s="23" t="n"/>
-      <c r="AT283" s="67" t="inlineStr"/>
+      <c r="AT283" s="66" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="53" t="inlineStr">
@@ -35670,7 +34602,7 @@
         </is>
       </c>
       <c r="H284" s="24" t="inlineStr"/>
-      <c r="I284" s="70" t="inlineStr">
+      <c r="I284" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -35741,11 +34673,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP284" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP284" s="65" t="inlineStr"/>
       <c r="AQ284" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -35757,10 +34685,10 @@
         </is>
       </c>
       <c r="AS284" s="23" t="n"/>
-      <c r="AT284" s="67" t="inlineStr"/>
+      <c r="AT284" s="66" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="68" t="inlineStr">
+      <c r="A285" s="67" t="inlineStr">
         <is>
           <t>PS5-84-03 - Shelters</t>
         </is>
@@ -35867,11 +34795,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP285" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP285" s="65" t="inlineStr"/>
       <c r="AQ285" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -35883,10 +34807,10 @@
         </is>
       </c>
       <c r="AS285" s="23" t="n"/>
-      <c r="AT285" s="67" t="inlineStr"/>
+      <c r="AT285" s="66" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="68" t="inlineStr">
+      <c r="A286" s="67" t="inlineStr">
         <is>
           <t>PS5-86-01 - Shelters</t>
         </is>
@@ -35993,11 +34917,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP286" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP286" s="65" t="inlineStr"/>
       <c r="AQ286" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -36009,10 +34929,10 @@
         </is>
       </c>
       <c r="AS286" s="23" t="n"/>
-      <c r="AT286" s="67" t="inlineStr"/>
+      <c r="AT286" s="66" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="68" t="inlineStr">
+      <c r="A287" s="67" t="inlineStr">
         <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
@@ -36123,11 +35043,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP287" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP287" s="65" t="inlineStr"/>
       <c r="AQ287" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -36139,7 +35055,7 @@
         </is>
       </c>
       <c r="AS287" s="23" t="n"/>
-      <c r="AT287" s="67" t="inlineStr"/>
+      <c r="AT287" s="66" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="53" t="inlineStr">
@@ -36174,7 +35090,7 @@
         </is>
       </c>
       <c r="H288" s="24" t="inlineStr"/>
-      <c r="I288" s="70" t="inlineStr">
+      <c r="I288" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -36245,11 +35161,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP288" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP288" s="65" t="inlineStr"/>
       <c r="AQ288" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -36261,7 +35173,7 @@
         </is>
       </c>
       <c r="AS288" s="23" t="n"/>
-      <c r="AT288" s="67" t="inlineStr"/>
+      <c r="AT288" s="66" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="53" t="inlineStr">
@@ -36296,7 +35208,7 @@
         </is>
       </c>
       <c r="H289" s="24" t="inlineStr"/>
-      <c r="I289" s="70" t="inlineStr">
+      <c r="I289" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -36367,11 +35279,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP289" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP289" s="65" t="inlineStr"/>
       <c r="AQ289" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -36383,7 +35291,7 @@
         </is>
       </c>
       <c r="AS289" s="23" t="n"/>
-      <c r="AT289" s="67" t="inlineStr"/>
+      <c r="AT289" s="66" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="53" t="inlineStr">
@@ -36418,7 +35326,7 @@
         </is>
       </c>
       <c r="H290" s="24" t="inlineStr"/>
-      <c r="I290" s="70" t="inlineStr">
+      <c r="I290" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -36489,11 +35397,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP290" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP290" s="65" t="inlineStr"/>
       <c r="AQ290" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -36505,7 +35409,7 @@
         </is>
       </c>
       <c r="AS290" s="23" t="n"/>
-      <c r="AT290" s="67" t="inlineStr"/>
+      <c r="AT290" s="66" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="53" t="inlineStr">
@@ -36540,7 +35444,7 @@
         </is>
       </c>
       <c r="H291" s="24" t="inlineStr"/>
-      <c r="I291" s="70" t="inlineStr">
+      <c r="I291" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -36611,11 +35515,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP291" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP291" s="65" t="inlineStr"/>
       <c r="AQ291" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -36627,7 +35527,7 @@
         </is>
       </c>
       <c r="AS291" s="23" t="n"/>
-      <c r="AT291" s="67" t="inlineStr"/>
+      <c r="AT291" s="66" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="53" t="inlineStr">
@@ -36662,7 +35562,7 @@
         </is>
       </c>
       <c r="H292" s="24" t="inlineStr"/>
-      <c r="I292" s="70" t="inlineStr">
+      <c r="I292" s="69" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -36733,11 +35633,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP292" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP292" s="65" t="inlineStr"/>
       <c r="AQ292" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -36749,7 +35645,7 @@
         </is>
       </c>
       <c r="AS292" s="23" t="n"/>
-      <c r="AT292" s="67" t="inlineStr"/>
+      <c r="AT292" s="66" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="53" t="inlineStr">
@@ -36792,7 +35688,7 @@
           <t>RE WALKDOWN</t>
         </is>
       </c>
-      <c r="I293" s="69" t="inlineStr">
+      <c r="I293" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -36863,11 +35759,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP293" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP293" s="65" t="inlineStr"/>
       <c r="AQ293" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -36879,7 +35771,7 @@
         </is>
       </c>
       <c r="AS293" s="23" t="n"/>
-      <c r="AT293" s="67" t="inlineStr"/>
+      <c r="AT293" s="66" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:AT293"/>

--- a/EXCEL/2 - RFC PROGRESS.xlsx
+++ b/EXCEL/2 - RFC PROGRESS.xlsx
@@ -172,7 +172,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill/>
     </fill>
@@ -303,6 +303,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFfff8e1"/>
         <bgColor rgb="FFfff8e1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -498,7 +504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -512,9 +518,6 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -524,10 +527,10 @@
     <xf numFmtId="0" fontId="19" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -539,16 +542,19 @@
     <xf numFmtId="0" fontId="2" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -558,10 +564,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -573,21 +579,21 @@
     <xf numFmtId="0" fontId="10" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -677,10 +683,13 @@
     <xf numFmtId="0" fontId="11" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -698,7 +707,10 @@
     <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -710,7 +722,13 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -719,37 +737,37 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1191,51 +1209,51 @@
           <t>PS5 COMPLETION PLATFORM  |  2 · RFC PROGRESS</t>
         </is>
       </c>
-      <c r="B1" s="96" t="n"/>
-      <c r="C1" s="96" t="n"/>
-      <c r="D1" s="96" t="n"/>
-      <c r="E1" s="96" t="n"/>
-      <c r="F1" s="96" t="n"/>
-      <c r="G1" s="96" t="n"/>
-      <c r="H1" s="96" t="n"/>
-      <c r="I1" s="96" t="n"/>
-      <c r="J1" s="96" t="n"/>
-      <c r="K1" s="96" t="n"/>
-      <c r="L1" s="96" t="n"/>
-      <c r="M1" s="96" t="n"/>
-      <c r="N1" s="96" t="n"/>
-      <c r="O1" s="96" t="n"/>
-      <c r="P1" s="96" t="n"/>
-      <c r="Q1" s="96" t="n"/>
-      <c r="R1" s="96" t="n"/>
-      <c r="S1" s="96" t="n"/>
-      <c r="T1" s="96" t="n"/>
-      <c r="U1" s="96" t="n"/>
-      <c r="V1" s="96" t="n"/>
-      <c r="W1" s="96" t="n"/>
-      <c r="X1" s="96" t="n"/>
-      <c r="Y1" s="96" t="n"/>
-      <c r="Z1" s="96" t="n"/>
-      <c r="AA1" s="96" t="n"/>
-      <c r="AB1" s="96" t="n"/>
-      <c r="AC1" s="96" t="n"/>
-      <c r="AD1" s="96" t="n"/>
-      <c r="AE1" s="96" t="n"/>
-      <c r="AF1" s="96" t="n"/>
-      <c r="AG1" s="96" t="n"/>
-      <c r="AH1" s="96" t="n"/>
-      <c r="AI1" s="96" t="n"/>
-      <c r="AJ1" s="96" t="n"/>
-      <c r="AK1" s="96" t="n"/>
-      <c r="AL1" s="96" t="n"/>
-      <c r="AM1" s="96" t="n"/>
-      <c r="AN1" s="96" t="n"/>
-      <c r="AO1" s="96" t="n"/>
-      <c r="AP1" s="96" t="n"/>
-      <c r="AQ1" s="96" t="n"/>
-      <c r="AR1" s="96" t="n"/>
-      <c r="AS1" s="96" t="n"/>
-      <c r="AT1" s="97" t="n"/>
+      <c r="B1" s="100" t="n"/>
+      <c r="C1" s="100" t="n"/>
+      <c r="D1" s="100" t="n"/>
+      <c r="E1" s="100" t="n"/>
+      <c r="F1" s="100" t="n"/>
+      <c r="G1" s="100" t="n"/>
+      <c r="H1" s="100" t="n"/>
+      <c r="I1" s="100" t="n"/>
+      <c r="J1" s="100" t="n"/>
+      <c r="K1" s="100" t="n"/>
+      <c r="L1" s="100" t="n"/>
+      <c r="M1" s="100" t="n"/>
+      <c r="N1" s="100" t="n"/>
+      <c r="O1" s="100" t="n"/>
+      <c r="P1" s="100" t="n"/>
+      <c r="Q1" s="100" t="n"/>
+      <c r="R1" s="100" t="n"/>
+      <c r="S1" s="100" t="n"/>
+      <c r="T1" s="100" t="n"/>
+      <c r="U1" s="100" t="n"/>
+      <c r="V1" s="100" t="n"/>
+      <c r="W1" s="100" t="n"/>
+      <c r="X1" s="100" t="n"/>
+      <c r="Y1" s="100" t="n"/>
+      <c r="Z1" s="100" t="n"/>
+      <c r="AA1" s="100" t="n"/>
+      <c r="AB1" s="100" t="n"/>
+      <c r="AC1" s="100" t="n"/>
+      <c r="AD1" s="100" t="n"/>
+      <c r="AE1" s="100" t="n"/>
+      <c r="AF1" s="100" t="n"/>
+      <c r="AG1" s="100" t="n"/>
+      <c r="AH1" s="100" t="n"/>
+      <c r="AI1" s="100" t="n"/>
+      <c r="AJ1" s="100" t="n"/>
+      <c r="AK1" s="100" t="n"/>
+      <c r="AL1" s="100" t="n"/>
+      <c r="AM1" s="100" t="n"/>
+      <c r="AN1" s="100" t="n"/>
+      <c r="AO1" s="100" t="n"/>
+      <c r="AP1" s="100" t="n"/>
+      <c r="AQ1" s="100" t="n"/>
+      <c r="AR1" s="100" t="n"/>
+      <c r="AS1" s="100" t="n"/>
+      <c r="AT1" s="101" t="n"/>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
@@ -1567,7 +1585,7 @@
       </c>
       <c r="D4" s="23" t="inlineStr">
         <is>
-          <t>E,I,M,P</t>
+          <t>08-Sep-26</t>
         </is>
       </c>
       <c r="E4" s="23" t="inlineStr">
@@ -1587,7 +1605,7 @@
       </c>
       <c r="H4" s="24" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>DONE(partial)</t>
         </is>
       </c>
       <c r="I4" s="54" t="inlineStr">
@@ -1610,8 +1628,10 @@
       <c r="N4" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="O4" s="60" t="n">
-        <v>28</v>
+      <c r="O4" s="60" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="P4" s="61" t="n">
         <v>0</v>
@@ -1672,8 +1692,8 @@
           <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
         </is>
       </c>
-      <c r="AS4" s="23" t="n"/>
-      <c r="AT4" s="66" t="inlineStr"/>
+      <c r="AS4" s="66" t="n"/>
+      <c r="AT4" s="67" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="53" t="inlineStr">
@@ -1790,16 +1810,16 @@
       <c r="AP5" s="65" t="inlineStr"/>
       <c r="AQ5" s="65" t="inlineStr">
         <is>
+          <t>EACOP(MR.BENHER TBC)-EXPECTED 19-08-2026</t>
+        </is>
+      </c>
+      <c r="AR5" s="23" t="inlineStr">
+        <is>
           <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
         </is>
       </c>
-      <c r="AR5" s="23" t="inlineStr">
-        <is>
-          <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
-        </is>
-      </c>
       <c r="AS5" s="23" t="n"/>
-      <c r="AT5" s="66" t="inlineStr"/>
+      <c r="AT5" s="67" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="53" t="inlineStr">
@@ -1925,10 +1945,10 @@
         </is>
       </c>
       <c r="AS6" s="23" t="n"/>
-      <c r="AT6" s="66" t="inlineStr"/>
+      <c r="AT6" s="67" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="67" t="inlineStr">
+      <c r="A7" s="68" t="inlineStr">
         <is>
           <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
         </is>
@@ -2047,7 +2067,7 @@
         </is>
       </c>
       <c r="AS7" s="23" t="n"/>
-      <c r="AT7" s="66" t="inlineStr"/>
+      <c r="AT7" s="67" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="53" t="inlineStr">
@@ -2085,7 +2105,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H8" s="24" t="inlineStr"/>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>PS5 - Milestone F</t>
+        </is>
+      </c>
       <c r="I8" s="54" t="inlineStr">
         <is>
           <t>93%</t>
@@ -2169,10 +2193,10 @@
         </is>
       </c>
       <c r="AS8" s="23" t="n"/>
-      <c r="AT8" s="66" t="inlineStr"/>
+      <c r="AT8" s="67" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="67" t="inlineStr">
+      <c r="A9" s="68" t="inlineStr">
         <is>
           <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
@@ -2291,7 +2315,7 @@
         </is>
       </c>
       <c r="AS9" s="23" t="n"/>
-      <c r="AT9" s="66" t="inlineStr"/>
+      <c r="AT9" s="67" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="53" t="inlineStr">
@@ -2326,13 +2350,15 @@
         </is>
       </c>
       <c r="H10" s="24" t="inlineStr"/>
-      <c r="I10" s="68" t="inlineStr">
+      <c r="I10" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
       </c>
-      <c r="J10" s="55" t="n">
-        <v>0</v>
+      <c r="J10" s="55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K10" s="56" t="n">
         <v>0</v>
@@ -2409,7 +2435,7 @@
         </is>
       </c>
       <c r="AS10" s="23" t="n"/>
-      <c r="AT10" s="66" t="inlineStr"/>
+      <c r="AT10" s="67" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="53" t="inlineStr">
@@ -2444,7 +2470,7 @@
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr"/>
-      <c r="I11" s="68" t="inlineStr">
+      <c r="I11" s="69" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
@@ -2527,10 +2553,10 @@
         </is>
       </c>
       <c r="AS11" s="23" t="n"/>
-      <c r="AT11" s="66" t="inlineStr"/>
+      <c r="AT11" s="67" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="67" t="inlineStr">
+      <c r="A12" s="68" t="inlineStr">
         <is>
           <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
@@ -2558,7 +2584,7 @@
       <c r="F12" s="23" t="inlineStr"/>
       <c r="G12" s="27" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="H12" s="24" t="inlineStr"/>
@@ -2645,10 +2671,10 @@
         </is>
       </c>
       <c r="AS12" s="23" t="n"/>
-      <c r="AT12" s="66" t="inlineStr"/>
+      <c r="AT12" s="67" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="67" t="inlineStr">
+      <c r="A13" s="68" t="inlineStr">
         <is>
           <t>PS5-01-10 - Water Mist Package</t>
         </is>
@@ -2771,7 +2797,7 @@
         </is>
       </c>
       <c r="AS13" s="23" t="n"/>
-      <c r="AT13" s="66" t="inlineStr"/>
+      <c r="AT13" s="67" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="53" t="inlineStr">
@@ -2810,7 +2836,7 @@
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr"/>
-      <c r="I14" s="69" t="inlineStr">
+      <c r="I14" s="70" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -2885,7 +2911,7 @@
       <c r="AQ14" s="65" t="inlineStr"/>
       <c r="AR14" s="23" t="inlineStr"/>
       <c r="AS14" s="23" t="n"/>
-      <c r="AT14" s="66" t="inlineStr"/>
+      <c r="AT14" s="67" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="53" t="inlineStr">
@@ -2920,7 +2946,7 @@
         </is>
       </c>
       <c r="H15" s="24" t="inlineStr"/>
-      <c r="I15" s="69" t="inlineStr">
+      <c r="I15" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -3003,7 +3029,7 @@
         </is>
       </c>
       <c r="AS15" s="23" t="n"/>
-      <c r="AT15" s="66" t="inlineStr"/>
+      <c r="AT15" s="67" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="53" t="inlineStr">
@@ -3038,7 +3064,7 @@
         </is>
       </c>
       <c r="H16" s="24" t="inlineStr"/>
-      <c r="I16" s="69" t="inlineStr">
+      <c r="I16" s="70" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
@@ -3121,7 +3147,7 @@
         </is>
       </c>
       <c r="AS16" s="23" t="n"/>
-      <c r="AT16" s="66" t="inlineStr"/>
+      <c r="AT16" s="67" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="53" t="inlineStr">
@@ -3247,7 +3273,7 @@
         </is>
       </c>
       <c r="AS17" s="23" t="n"/>
-      <c r="AT17" s="66" t="inlineStr"/>
+      <c r="AT17" s="67" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="53" t="inlineStr">
@@ -3282,7 +3308,7 @@
         </is>
       </c>
       <c r="H18" s="24" t="inlineStr"/>
-      <c r="I18" s="69" t="inlineStr">
+      <c r="I18" s="70" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -3365,7 +3391,7 @@
         </is>
       </c>
       <c r="AS18" s="23" t="n"/>
-      <c r="AT18" s="66" t="inlineStr"/>
+      <c r="AT18" s="67" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="53" t="inlineStr">
@@ -3491,7 +3517,7 @@
         </is>
       </c>
       <c r="AS19" s="23" t="n"/>
-      <c r="AT19" s="66" t="inlineStr"/>
+      <c r="AT19" s="67" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="53" t="inlineStr">
@@ -3617,10 +3643,10 @@
         </is>
       </c>
       <c r="AS20" s="23" t="n"/>
-      <c r="AT20" s="66" t="inlineStr"/>
+      <c r="AT20" s="67" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="67" t="inlineStr">
+      <c r="A21" s="68" t="inlineStr">
         <is>
           <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
         </is>
@@ -3743,7 +3769,7 @@
         </is>
       </c>
       <c r="AS21" s="23" t="n"/>
-      <c r="AT21" s="66" t="inlineStr"/>
+      <c r="AT21" s="67" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="53" t="inlineStr">
@@ -3861,10 +3887,10 @@
         </is>
       </c>
       <c r="AS22" s="23" t="n"/>
-      <c r="AT22" s="66" t="inlineStr"/>
+      <c r="AT22" s="67" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="67" t="inlineStr">
+      <c r="A23" s="68" t="inlineStr">
         <is>
           <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
         </is>
@@ -3987,10 +4013,10 @@
         </is>
       </c>
       <c r="AS23" s="23" t="n"/>
-      <c r="AT23" s="66" t="inlineStr"/>
+      <c r="AT23" s="67" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="67" t="inlineStr">
+      <c r="A24" s="68" t="inlineStr">
         <is>
           <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
         </is>
@@ -4109,7 +4135,7 @@
       <c r="AQ24" s="65" t="inlineStr"/>
       <c r="AR24" s="23" t="inlineStr"/>
       <c r="AS24" s="23" t="n"/>
-      <c r="AT24" s="66" t="inlineStr"/>
+      <c r="AT24" s="67" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="53" t="inlineStr">
@@ -4231,7 +4257,7 @@
         </is>
       </c>
       <c r="AS25" s="23" t="n"/>
-      <c r="AT25" s="66" t="inlineStr"/>
+      <c r="AT25" s="67" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="53" t="inlineStr">
@@ -4349,10 +4375,10 @@
         </is>
       </c>
       <c r="AS26" s="23" t="n"/>
-      <c r="AT26" s="66" t="inlineStr"/>
+      <c r="AT26" s="67" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="67" t="inlineStr">
+      <c r="A27" s="68" t="inlineStr">
         <is>
           <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
         </is>
@@ -4475,7 +4501,7 @@
         </is>
       </c>
       <c r="AS27" s="23" t="n"/>
-      <c r="AT27" s="66" t="inlineStr"/>
+      <c r="AT27" s="67" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="53" t="inlineStr">
@@ -4514,7 +4540,7 @@
         </is>
       </c>
       <c r="H28" s="24" t="inlineStr"/>
-      <c r="I28" s="69" t="inlineStr">
+      <c r="I28" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -4546,7 +4572,7 @@
       <c r="R28" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S28" s="70" t="inlineStr">
+      <c r="S28" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -4603,7 +4629,7 @@
         </is>
       </c>
       <c r="AS28" s="23" t="n"/>
-      <c r="AT28" s="66" t="inlineStr"/>
+      <c r="AT28" s="67" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="53" t="inlineStr">
@@ -4642,7 +4668,7 @@
         </is>
       </c>
       <c r="H29" s="24" t="inlineStr"/>
-      <c r="I29" s="69" t="inlineStr">
+      <c r="I29" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4725,7 +4751,7 @@
         </is>
       </c>
       <c r="AS29" s="23" t="n"/>
-      <c r="AT29" s="66" t="inlineStr"/>
+      <c r="AT29" s="67" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="53" t="inlineStr">
@@ -4764,7 +4790,7 @@
         </is>
       </c>
       <c r="H30" s="24" t="inlineStr"/>
-      <c r="I30" s="69" t="inlineStr">
+      <c r="I30" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4847,7 +4873,7 @@
         </is>
       </c>
       <c r="AS30" s="23" t="n"/>
-      <c r="AT30" s="66" t="inlineStr"/>
+      <c r="AT30" s="67" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="53" t="inlineStr">
@@ -4882,7 +4908,7 @@
         </is>
       </c>
       <c r="H31" s="24" t="inlineStr"/>
-      <c r="I31" s="69" t="inlineStr">
+      <c r="I31" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4965,7 +4991,7 @@
         </is>
       </c>
       <c r="AS31" s="23" t="n"/>
-      <c r="AT31" s="66" t="inlineStr"/>
+      <c r="AT31" s="67" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="53" t="inlineStr">
@@ -5000,7 +5026,7 @@
         </is>
       </c>
       <c r="H32" s="24" t="inlineStr"/>
-      <c r="I32" s="69" t="inlineStr">
+      <c r="I32" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5083,7 +5109,7 @@
         </is>
       </c>
       <c r="AS32" s="23" t="n"/>
-      <c r="AT32" s="66" t="inlineStr"/>
+      <c r="AT32" s="67" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="53" t="inlineStr">
@@ -5122,7 +5148,7 @@
         </is>
       </c>
       <c r="H33" s="24" t="inlineStr"/>
-      <c r="I33" s="69" t="inlineStr">
+      <c r="I33" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5205,10 +5231,10 @@
         </is>
       </c>
       <c r="AS33" s="23" t="n"/>
-      <c r="AT33" s="66" t="inlineStr"/>
+      <c r="AT33" s="67" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="67" t="inlineStr">
+      <c r="A34" s="68" t="inlineStr">
         <is>
           <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
         </is>
@@ -5236,7 +5262,7 @@
       <c r="F34" s="23" t="inlineStr"/>
       <c r="G34" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>07-Aug-26</t>
         </is>
       </c>
       <c r="H34" s="24" t="inlineStr">
@@ -5327,7 +5353,7 @@
         </is>
       </c>
       <c r="AS34" s="23" t="n"/>
-      <c r="AT34" s="66" t="inlineStr"/>
+      <c r="AT34" s="67" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="53" t="inlineStr">
@@ -5362,7 +5388,7 @@
         </is>
       </c>
       <c r="H35" s="24" t="inlineStr"/>
-      <c r="I35" s="69" t="inlineStr">
+      <c r="I35" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5445,7 +5471,7 @@
         </is>
       </c>
       <c r="AS35" s="23" t="n"/>
-      <c r="AT35" s="66" t="inlineStr"/>
+      <c r="AT35" s="67" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="53" t="inlineStr">
@@ -5480,7 +5506,7 @@
         </is>
       </c>
       <c r="H36" s="24" t="inlineStr"/>
-      <c r="I36" s="69" t="inlineStr">
+      <c r="I36" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5565,7 +5591,7 @@
         </is>
       </c>
       <c r="AS36" s="23" t="n"/>
-      <c r="AT36" s="66" t="inlineStr"/>
+      <c r="AT36" s="67" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="53" t="inlineStr">
@@ -5649,7 +5675,7 @@
       <c r="AQ37" s="65" t="inlineStr"/>
       <c r="AR37" s="23" t="inlineStr"/>
       <c r="AS37" s="23" t="n"/>
-      <c r="AT37" s="66" t="inlineStr"/>
+      <c r="AT37" s="67" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="53" t="inlineStr">
@@ -5684,7 +5710,7 @@
         </is>
       </c>
       <c r="H38" s="24" t="inlineStr"/>
-      <c r="I38" s="69" t="inlineStr">
+      <c r="I38" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5767,7 +5793,7 @@
         </is>
       </c>
       <c r="AS38" s="23" t="n"/>
-      <c r="AT38" s="66" t="inlineStr"/>
+      <c r="AT38" s="67" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="53" t="inlineStr">
@@ -5802,7 +5828,7 @@
         </is>
       </c>
       <c r="H39" s="24" t="inlineStr"/>
-      <c r="I39" s="69" t="inlineStr">
+      <c r="I39" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5885,7 +5911,7 @@
         </is>
       </c>
       <c r="AS39" s="23" t="n"/>
-      <c r="AT39" s="66" t="inlineStr"/>
+      <c r="AT39" s="67" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="53" t="inlineStr">
@@ -5904,7 +5930,7 @@
         </is>
       </c>
       <c r="H40" s="24" t="inlineStr"/>
-      <c r="I40" s="69" t="inlineStr">
+      <c r="I40" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5936,7 +5962,7 @@
       <c r="R40" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S40" s="71" t="inlineStr">
+      <c r="S40" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5969,7 +5995,7 @@
       <c r="AQ40" s="65" t="inlineStr"/>
       <c r="AR40" s="23" t="inlineStr"/>
       <c r="AS40" s="23" t="n"/>
-      <c r="AT40" s="66" t="inlineStr"/>
+      <c r="AT40" s="67" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="53" t="inlineStr">
@@ -6004,7 +6030,7 @@
         </is>
       </c>
       <c r="H41" s="24" t="inlineStr"/>
-      <c r="I41" s="69" t="inlineStr">
+      <c r="I41" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6087,7 +6113,7 @@
         </is>
       </c>
       <c r="AS41" s="23" t="n"/>
-      <c r="AT41" s="66" t="inlineStr"/>
+      <c r="AT41" s="67" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="53" t="inlineStr">
@@ -6138,7 +6164,7 @@
       <c r="R42" s="62" t="n">
         <v>64</v>
       </c>
-      <c r="S42" s="72" t="inlineStr">
+      <c r="S42" s="73" t="inlineStr">
         <is>
           <t>98%</t>
         </is>
@@ -6171,7 +6197,7 @@
       <c r="AQ42" s="65" t="inlineStr"/>
       <c r="AR42" s="23" t="inlineStr"/>
       <c r="AS42" s="23" t="n"/>
-      <c r="AT42" s="66" t="inlineStr"/>
+      <c r="AT42" s="67" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="53" t="inlineStr">
@@ -6222,7 +6248,7 @@
       <c r="R43" s="62" t="n">
         <v>9</v>
       </c>
-      <c r="S43" s="72" t="inlineStr">
+      <c r="S43" s="73" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6255,7 +6281,7 @@
       <c r="AQ43" s="65" t="inlineStr"/>
       <c r="AR43" s="23" t="inlineStr"/>
       <c r="AS43" s="23" t="n"/>
-      <c r="AT43" s="66" t="inlineStr"/>
+      <c r="AT43" s="67" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="53" t="inlineStr">
@@ -6274,7 +6300,7 @@
         </is>
       </c>
       <c r="H44" s="24" t="inlineStr"/>
-      <c r="I44" s="68" t="inlineStr">
+      <c r="I44" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -6306,7 +6332,7 @@
       <c r="R44" s="62" t="n">
         <v>19</v>
       </c>
-      <c r="S44" s="72" t="inlineStr">
+      <c r="S44" s="73" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6339,10 +6365,10 @@
       <c r="AQ44" s="65" t="inlineStr"/>
       <c r="AR44" s="23" t="inlineStr"/>
       <c r="AS44" s="23" t="n"/>
-      <c r="AT44" s="66" t="inlineStr"/>
+      <c r="AT44" s="67" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="67" t="inlineStr">
+      <c r="A45" s="74" t="inlineStr">
         <is>
           <t>PS5-05-01 - Emergency Diesel Generator Package</t>
         </is>
@@ -6368,9 +6394,9 @@
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr"/>
-      <c r="G45" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
+      <c r="G45" s="69" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="H45" s="24" t="inlineStr">
@@ -6421,8 +6447,10 @@
       <c r="AI45" s="23" t="n">
         <v>109</v>
       </c>
-      <c r="AJ45" s="23" t="n">
-        <v>0</v>
+      <c r="AJ45" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="AK45" s="29" t="inlineStr">
         <is>
@@ -6461,10 +6489,10 @@
         </is>
       </c>
       <c r="AS45" s="23" t="n"/>
-      <c r="AT45" s="66" t="inlineStr"/>
+      <c r="AT45" s="67" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="67" t="inlineStr">
+      <c r="A46" s="75" t="inlineStr">
         <is>
           <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
         </is>
@@ -6490,9 +6518,9 @@
         </is>
       </c>
       <c r="F46" s="23" t="inlineStr"/>
-      <c r="G46" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G46" s="54" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="H46" s="24" t="inlineStr">
@@ -6583,7 +6611,7 @@
         </is>
       </c>
       <c r="AS46" s="23" t="n"/>
-      <c r="AT46" s="66" t="inlineStr"/>
+      <c r="AT46" s="67" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="53" t="inlineStr">
@@ -6602,7 +6630,7 @@
         </is>
       </c>
       <c r="H47" s="24" t="inlineStr"/>
-      <c r="I47" s="68" t="inlineStr">
+      <c r="I47" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -6634,7 +6662,7 @@
       <c r="R47" s="62" t="n">
         <v>12</v>
       </c>
-      <c r="S47" s="72" t="inlineStr">
+      <c r="S47" s="73" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6667,10 +6695,10 @@
       <c r="AQ47" s="65" t="inlineStr"/>
       <c r="AR47" s="23" t="inlineStr"/>
       <c r="AS47" s="23" t="n"/>
-      <c r="AT47" s="66" t="inlineStr"/>
+      <c r="AT47" s="67" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="67" t="inlineStr">
+      <c r="A48" s="68" t="inlineStr">
         <is>
           <t>PS5-06-02 - AC UPS - Power Generator Building</t>
         </is>
@@ -6793,7 +6821,7 @@
         </is>
       </c>
       <c r="AS48" s="23" t="n"/>
-      <c r="AT48" s="66" t="inlineStr"/>
+      <c r="AT48" s="67" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="53" t="inlineStr">
@@ -6828,7 +6856,7 @@
         </is>
       </c>
       <c r="H49" s="24" t="inlineStr"/>
-      <c r="I49" s="69" t="inlineStr">
+      <c r="I49" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6911,7 +6939,7 @@
         </is>
       </c>
       <c r="AS49" s="23" t="n"/>
-      <c r="AT49" s="66" t="inlineStr"/>
+      <c r="AT49" s="67" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="53" t="inlineStr">
@@ -6946,7 +6974,7 @@
         </is>
       </c>
       <c r="H50" s="24" t="inlineStr"/>
-      <c r="I50" s="69" t="inlineStr">
+      <c r="I50" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7029,7 +7057,7 @@
         </is>
       </c>
       <c r="AS50" s="23" t="n"/>
-      <c r="AT50" s="66" t="inlineStr"/>
+      <c r="AT50" s="67" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="53" t="inlineStr">
@@ -7064,7 +7092,7 @@
         </is>
       </c>
       <c r="H51" s="24" t="inlineStr"/>
-      <c r="I51" s="69" t="inlineStr">
+      <c r="I51" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7147,7 +7175,7 @@
         </is>
       </c>
       <c r="AS51" s="23" t="n"/>
-      <c r="AT51" s="66" t="inlineStr"/>
+      <c r="AT51" s="67" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="53" t="inlineStr">
@@ -7182,7 +7210,7 @@
         </is>
       </c>
       <c r="H52" s="24" t="inlineStr"/>
-      <c r="I52" s="69" t="inlineStr">
+      <c r="I52" s="70" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -7214,7 +7242,7 @@
       <c r="R52" s="62" t="n">
         <v>82</v>
       </c>
-      <c r="S52" s="71" t="inlineStr">
+      <c r="S52" s="72" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -7265,7 +7293,7 @@
         </is>
       </c>
       <c r="AS52" s="23" t="n"/>
-      <c r="AT52" s="66" t="inlineStr"/>
+      <c r="AT52" s="67" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="53" t="inlineStr">
@@ -7300,7 +7328,7 @@
         </is>
       </c>
       <c r="H53" s="24" t="inlineStr"/>
-      <c r="I53" s="69" t="inlineStr">
+      <c r="I53" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -7332,7 +7360,7 @@
       <c r="R53" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="S53" s="71" t="inlineStr">
+      <c r="S53" s="72" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -7383,7 +7411,7 @@
         </is>
       </c>
       <c r="AS53" s="23" t="n"/>
-      <c r="AT53" s="66" t="inlineStr"/>
+      <c r="AT53" s="67" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="53" t="inlineStr">
@@ -7402,7 +7430,7 @@
         </is>
       </c>
       <c r="H54" s="24" t="inlineStr"/>
-      <c r="I54" s="69" t="inlineStr">
+      <c r="I54" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7434,7 +7462,7 @@
       <c r="R54" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S54" s="71" t="inlineStr">
+      <c r="S54" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7467,7 +7495,7 @@
       <c r="AQ54" s="65" t="inlineStr"/>
       <c r="AR54" s="23" t="inlineStr"/>
       <c r="AS54" s="23" t="n"/>
-      <c r="AT54" s="66" t="inlineStr"/>
+      <c r="AT54" s="67" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="53" t="inlineStr">
@@ -7486,7 +7514,7 @@
         </is>
       </c>
       <c r="H55" s="24" t="inlineStr"/>
-      <c r="I55" s="69" t="inlineStr">
+      <c r="I55" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7518,7 +7546,7 @@
       <c r="R55" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S55" s="71" t="inlineStr">
+      <c r="S55" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7551,7 +7579,7 @@
       <c r="AQ55" s="65" t="inlineStr"/>
       <c r="AR55" s="23" t="inlineStr"/>
       <c r="AS55" s="23" t="n"/>
-      <c r="AT55" s="66" t="inlineStr"/>
+      <c r="AT55" s="67" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="53" t="inlineStr">
@@ -7586,7 +7614,7 @@
         </is>
       </c>
       <c r="H56" s="24" t="inlineStr"/>
-      <c r="I56" s="69" t="inlineStr">
+      <c r="I56" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -7669,7 +7697,7 @@
         </is>
       </c>
       <c r="AS56" s="23" t="n"/>
-      <c r="AT56" s="66" t="inlineStr"/>
+      <c r="AT56" s="67" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="53" t="inlineStr">
@@ -7704,7 +7732,7 @@
         </is>
       </c>
       <c r="H57" s="24" t="inlineStr"/>
-      <c r="I57" s="69" t="inlineStr">
+      <c r="I57" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7736,7 +7764,7 @@
       <c r="R57" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S57" s="71" t="inlineStr">
+      <c r="S57" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7787,7 +7815,7 @@
         </is>
       </c>
       <c r="AS57" s="23" t="n"/>
-      <c r="AT57" s="66" t="inlineStr"/>
+      <c r="AT57" s="67" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="53" t="inlineStr">
@@ -7822,7 +7850,7 @@
         </is>
       </c>
       <c r="H58" s="24" t="inlineStr"/>
-      <c r="I58" s="69" t="inlineStr">
+      <c r="I58" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7854,7 +7882,7 @@
       <c r="R58" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S58" s="71" t="inlineStr">
+      <c r="S58" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7905,7 +7933,7 @@
         </is>
       </c>
       <c r="AS58" s="23" t="n"/>
-      <c r="AT58" s="66" t="inlineStr"/>
+      <c r="AT58" s="67" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="53" t="inlineStr">
@@ -7940,7 +7968,7 @@
         </is>
       </c>
       <c r="H59" s="24" t="inlineStr"/>
-      <c r="I59" s="69" t="inlineStr">
+      <c r="I59" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7972,7 +8000,7 @@
       <c r="R59" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S59" s="71" t="inlineStr">
+      <c r="S59" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8023,7 +8051,7 @@
         </is>
       </c>
       <c r="AS59" s="23" t="n"/>
-      <c r="AT59" s="66" t="inlineStr"/>
+      <c r="AT59" s="67" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="53" t="inlineStr">
@@ -8058,7 +8086,7 @@
         </is>
       </c>
       <c r="H60" s="24" t="inlineStr"/>
-      <c r="I60" s="69" t="inlineStr">
+      <c r="I60" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8090,7 +8118,7 @@
       <c r="R60" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S60" s="71" t="inlineStr">
+      <c r="S60" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8141,7 +8169,7 @@
         </is>
       </c>
       <c r="AS60" s="23" t="n"/>
-      <c r="AT60" s="66" t="inlineStr"/>
+      <c r="AT60" s="67" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="53" t="inlineStr">
@@ -8176,7 +8204,7 @@
         </is>
       </c>
       <c r="H61" s="24" t="inlineStr"/>
-      <c r="I61" s="69" t="inlineStr">
+      <c r="I61" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8208,7 +8236,7 @@
       <c r="R61" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S61" s="71" t="inlineStr">
+      <c r="S61" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8259,7 +8287,7 @@
         </is>
       </c>
       <c r="AS61" s="23" t="n"/>
-      <c r="AT61" s="66" t="inlineStr"/>
+      <c r="AT61" s="67" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="53" t="inlineStr">
@@ -8294,7 +8322,7 @@
         </is>
       </c>
       <c r="H62" s="24" t="inlineStr"/>
-      <c r="I62" s="69" t="inlineStr">
+      <c r="I62" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8326,7 +8354,7 @@
       <c r="R62" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S62" s="71" t="inlineStr">
+      <c r="S62" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8377,7 +8405,7 @@
         </is>
       </c>
       <c r="AS62" s="23" t="n"/>
-      <c r="AT62" s="66" t="inlineStr"/>
+      <c r="AT62" s="67" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="53" t="inlineStr">
@@ -8396,7 +8424,7 @@
         </is>
       </c>
       <c r="H63" s="24" t="inlineStr"/>
-      <c r="I63" s="68" t="inlineStr">
+      <c r="I63" s="69" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -8428,7 +8456,7 @@
       <c r="R63" s="62" t="n">
         <v>39</v>
       </c>
-      <c r="S63" s="70" t="inlineStr">
+      <c r="S63" s="71" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -8461,7 +8489,7 @@
       <c r="AQ63" s="65" t="inlineStr"/>
       <c r="AR63" s="23" t="inlineStr"/>
       <c r="AS63" s="23" t="n"/>
-      <c r="AT63" s="66" t="inlineStr"/>
+      <c r="AT63" s="67" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="53" t="inlineStr">
@@ -8496,7 +8524,7 @@
         </is>
       </c>
       <c r="H64" s="24" t="inlineStr"/>
-      <c r="I64" s="69" t="inlineStr">
+      <c r="I64" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8528,7 +8556,7 @@
       <c r="R64" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S64" s="71" t="inlineStr">
+      <c r="S64" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8579,7 +8607,7 @@
         </is>
       </c>
       <c r="AS64" s="23" t="n"/>
-      <c r="AT64" s="66" t="inlineStr"/>
+      <c r="AT64" s="67" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="53" t="inlineStr">
@@ -8614,7 +8642,7 @@
         </is>
       </c>
       <c r="H65" s="24" t="inlineStr"/>
-      <c r="I65" s="69" t="inlineStr">
+      <c r="I65" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8646,7 +8674,7 @@
       <c r="R65" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S65" s="71" t="inlineStr">
+      <c r="S65" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8697,7 +8725,7 @@
         </is>
       </c>
       <c r="AS65" s="23" t="n"/>
-      <c r="AT65" s="66" t="inlineStr"/>
+      <c r="AT65" s="67" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="53" t="inlineStr">
@@ -8732,7 +8760,7 @@
         </is>
       </c>
       <c r="H66" s="24" t="inlineStr"/>
-      <c r="I66" s="69" t="inlineStr">
+      <c r="I66" s="70" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -8764,7 +8792,7 @@
       <c r="R66" s="62" t="n">
         <v>22</v>
       </c>
-      <c r="S66" s="71" t="inlineStr">
+      <c r="S66" s="72" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -8815,7 +8843,7 @@
         </is>
       </c>
       <c r="AS66" s="23" t="n"/>
-      <c r="AT66" s="66" t="inlineStr"/>
+      <c r="AT66" s="67" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="53" t="inlineStr">
@@ -8834,7 +8862,7 @@
         </is>
       </c>
       <c r="H67" s="24" t="inlineStr"/>
-      <c r="I67" s="69" t="inlineStr">
+      <c r="I67" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8866,7 +8894,7 @@
       <c r="R67" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S67" s="71" t="inlineStr">
+      <c r="S67" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8899,7 +8927,7 @@
       <c r="AQ67" s="65" t="inlineStr"/>
       <c r="AR67" s="23" t="inlineStr"/>
       <c r="AS67" s="23" t="n"/>
-      <c r="AT67" s="66" t="inlineStr"/>
+      <c r="AT67" s="67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="53" t="inlineStr">
@@ -8934,7 +8962,7 @@
         </is>
       </c>
       <c r="H68" s="24" t="inlineStr"/>
-      <c r="I68" s="69" t="inlineStr">
+      <c r="I68" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8966,7 +8994,7 @@
       <c r="R68" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S68" s="71" t="inlineStr">
+      <c r="S68" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9017,7 +9045,7 @@
         </is>
       </c>
       <c r="AS68" s="23" t="n"/>
-      <c r="AT68" s="66" t="inlineStr"/>
+      <c r="AT68" s="67" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="53" t="inlineStr">
@@ -9052,7 +9080,7 @@
         </is>
       </c>
       <c r="H69" s="24" t="inlineStr"/>
-      <c r="I69" s="69" t="inlineStr">
+      <c r="I69" s="70" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -9084,7 +9112,7 @@
       <c r="R69" s="62" t="n">
         <v>10</v>
       </c>
-      <c r="S69" s="71" t="inlineStr">
+      <c r="S69" s="72" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -9135,7 +9163,7 @@
         </is>
       </c>
       <c r="AS69" s="23" t="n"/>
-      <c r="AT69" s="66" t="inlineStr"/>
+      <c r="AT69" s="67" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="53" t="inlineStr">
@@ -9170,7 +9198,7 @@
         </is>
       </c>
       <c r="H70" s="24" t="inlineStr"/>
-      <c r="I70" s="69" t="inlineStr">
+      <c r="I70" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9202,7 +9230,7 @@
       <c r="R70" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S70" s="71" t="inlineStr">
+      <c r="S70" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9253,7 +9281,7 @@
         </is>
       </c>
       <c r="AS70" s="23" t="n"/>
-      <c r="AT70" s="66" t="inlineStr"/>
+      <c r="AT70" s="67" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="53" t="inlineStr">
@@ -9272,7 +9300,7 @@
         </is>
       </c>
       <c r="H71" s="24" t="inlineStr"/>
-      <c r="I71" s="69" t="inlineStr">
+      <c r="I71" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9304,7 +9332,7 @@
       <c r="R71" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S71" s="71" t="inlineStr">
+      <c r="S71" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9337,7 +9365,7 @@
       <c r="AQ71" s="65" t="inlineStr"/>
       <c r="AR71" s="23" t="inlineStr"/>
       <c r="AS71" s="23" t="n"/>
-      <c r="AT71" s="66" t="inlineStr"/>
+      <c r="AT71" s="67" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="53" t="inlineStr">
@@ -9356,7 +9384,7 @@
         </is>
       </c>
       <c r="H72" s="24" t="inlineStr"/>
-      <c r="I72" s="69" t="inlineStr">
+      <c r="I72" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9388,7 +9416,7 @@
       <c r="R72" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S72" s="71" t="inlineStr">
+      <c r="S72" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9421,7 +9449,7 @@
       <c r="AQ72" s="65" t="inlineStr"/>
       <c r="AR72" s="23" t="inlineStr"/>
       <c r="AS72" s="23" t="n"/>
-      <c r="AT72" s="66" t="inlineStr"/>
+      <c r="AT72" s="67" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="53" t="inlineStr">
@@ -9456,7 +9484,7 @@
         </is>
       </c>
       <c r="H73" s="24" t="inlineStr"/>
-      <c r="I73" s="69" t="inlineStr">
+      <c r="I73" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9488,7 +9516,7 @@
       <c r="R73" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S73" s="71" t="inlineStr">
+      <c r="S73" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9539,7 +9567,7 @@
         </is>
       </c>
       <c r="AS73" s="23" t="n"/>
-      <c r="AT73" s="66" t="inlineStr"/>
+      <c r="AT73" s="67" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="53" t="inlineStr">
@@ -9574,7 +9602,7 @@
         </is>
       </c>
       <c r="H74" s="24" t="inlineStr"/>
-      <c r="I74" s="69" t="inlineStr">
+      <c r="I74" s="70" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -9606,7 +9634,7 @@
       <c r="R74" s="62" t="n">
         <v>31</v>
       </c>
-      <c r="S74" s="71" t="inlineStr">
+      <c r="S74" s="72" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
@@ -9657,7 +9685,7 @@
         </is>
       </c>
       <c r="AS74" s="23" t="n"/>
-      <c r="AT74" s="66" t="inlineStr"/>
+      <c r="AT74" s="67" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="53" t="inlineStr">
@@ -9676,7 +9704,7 @@
         </is>
       </c>
       <c r="H75" s="24" t="inlineStr"/>
-      <c r="I75" s="69" t="inlineStr">
+      <c r="I75" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9708,7 +9736,7 @@
       <c r="R75" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S75" s="71" t="inlineStr">
+      <c r="S75" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9741,7 +9769,7 @@
       <c r="AQ75" s="65" t="inlineStr"/>
       <c r="AR75" s="23" t="inlineStr"/>
       <c r="AS75" s="23" t="n"/>
-      <c r="AT75" s="66" t="inlineStr"/>
+      <c r="AT75" s="67" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="53" t="inlineStr">
@@ -9760,7 +9788,7 @@
         </is>
       </c>
       <c r="H76" s="24" t="inlineStr"/>
-      <c r="I76" s="69" t="inlineStr">
+      <c r="I76" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9792,7 +9820,7 @@
       <c r="R76" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S76" s="71" t="inlineStr">
+      <c r="S76" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9825,7 +9853,7 @@
       <c r="AQ76" s="65" t="inlineStr"/>
       <c r="AR76" s="23" t="inlineStr"/>
       <c r="AS76" s="23" t="n"/>
-      <c r="AT76" s="66" t="inlineStr"/>
+      <c r="AT76" s="67" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="53" t="inlineStr">
@@ -9860,7 +9888,7 @@
         </is>
       </c>
       <c r="H77" s="24" t="inlineStr"/>
-      <c r="I77" s="69" t="inlineStr">
+      <c r="I77" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9892,7 +9920,7 @@
       <c r="R77" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S77" s="71" t="inlineStr">
+      <c r="S77" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9943,7 +9971,7 @@
         </is>
       </c>
       <c r="AS77" s="23" t="n"/>
-      <c r="AT77" s="66" t="inlineStr"/>
+      <c r="AT77" s="67" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="53" t="inlineStr">
@@ -9978,7 +10006,7 @@
         </is>
       </c>
       <c r="H78" s="24" t="inlineStr"/>
-      <c r="I78" s="69" t="inlineStr">
+      <c r="I78" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10061,7 +10089,7 @@
         </is>
       </c>
       <c r="AS78" s="23" t="n"/>
-      <c r="AT78" s="66" t="inlineStr"/>
+      <c r="AT78" s="67" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="53" t="inlineStr">
@@ -10096,7 +10124,7 @@
         </is>
       </c>
       <c r="H79" s="24" t="inlineStr"/>
-      <c r="I79" s="69" t="inlineStr">
+      <c r="I79" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10179,7 +10207,7 @@
         </is>
       </c>
       <c r="AS79" s="23" t="n"/>
-      <c r="AT79" s="66" t="inlineStr"/>
+      <c r="AT79" s="67" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="53" t="inlineStr">
@@ -10214,7 +10242,7 @@
         </is>
       </c>
       <c r="H80" s="24" t="inlineStr"/>
-      <c r="I80" s="69" t="inlineStr">
+      <c r="I80" s="70" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -10246,7 +10274,7 @@
       <c r="R80" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S80" s="71" t="inlineStr">
+      <c r="S80" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10301,7 +10329,7 @@
         </is>
       </c>
       <c r="AS80" s="23" t="n"/>
-      <c r="AT80" s="66" t="inlineStr"/>
+      <c r="AT80" s="67" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="53" t="inlineStr">
@@ -10336,7 +10364,7 @@
         </is>
       </c>
       <c r="H81" s="24" t="inlineStr"/>
-      <c r="I81" s="69" t="inlineStr">
+      <c r="I81" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10419,10 +10447,10 @@
         </is>
       </c>
       <c r="AS81" s="23" t="n"/>
-      <c r="AT81" s="66" t="inlineStr"/>
+      <c r="AT81" s="67" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="67" t="inlineStr">
+      <c r="A82" s="68" t="inlineStr">
         <is>
           <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
@@ -10529,7 +10557,7 @@
       <c r="AQ82" s="65" t="inlineStr"/>
       <c r="AR82" s="23" t="inlineStr"/>
       <c r="AS82" s="23" t="n"/>
-      <c r="AT82" s="66" t="inlineStr"/>
+      <c r="AT82" s="67" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="53" t="inlineStr">
@@ -10548,7 +10576,7 @@
         </is>
       </c>
       <c r="H83" s="24" t="inlineStr"/>
-      <c r="I83" s="68" t="inlineStr">
+      <c r="I83" s="69" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -10613,7 +10641,7 @@
       <c r="AQ83" s="65" t="inlineStr"/>
       <c r="AR83" s="23" t="inlineStr"/>
       <c r="AS83" s="23" t="n"/>
-      <c r="AT83" s="66" t="inlineStr"/>
+      <c r="AT83" s="67" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="53" t="inlineStr">
@@ -10648,7 +10676,7 @@
         </is>
       </c>
       <c r="H84" s="24" t="inlineStr"/>
-      <c r="I84" s="68" t="inlineStr">
+      <c r="I84" s="69" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -10731,7 +10759,7 @@
         </is>
       </c>
       <c r="AS84" s="23" t="n"/>
-      <c r="AT84" s="66" t="inlineStr"/>
+      <c r="AT84" s="67" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="53" t="inlineStr">
@@ -10766,7 +10794,7 @@
         </is>
       </c>
       <c r="H85" s="24" t="inlineStr"/>
-      <c r="I85" s="68" t="inlineStr">
+      <c r="I85" s="69" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -10849,7 +10877,7 @@
         </is>
       </c>
       <c r="AS85" s="23" t="n"/>
-      <c r="AT85" s="66" t="inlineStr"/>
+      <c r="AT85" s="67" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="53" t="inlineStr">
@@ -10884,7 +10912,7 @@
         </is>
       </c>
       <c r="H86" s="24" t="inlineStr"/>
-      <c r="I86" s="68" t="inlineStr">
+      <c r="I86" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -10967,7 +10995,7 @@
         </is>
       </c>
       <c r="AS86" s="23" t="n"/>
-      <c r="AT86" s="66" t="inlineStr"/>
+      <c r="AT86" s="67" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="53" t="inlineStr">
@@ -11002,7 +11030,7 @@
         </is>
       </c>
       <c r="H87" s="24" t="inlineStr"/>
-      <c r="I87" s="68" t="inlineStr">
+      <c r="I87" s="69" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -11085,7 +11113,7 @@
         </is>
       </c>
       <c r="AS87" s="23" t="n"/>
-      <c r="AT87" s="66" t="inlineStr"/>
+      <c r="AT87" s="67" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="53" t="inlineStr">
@@ -11120,7 +11148,7 @@
         </is>
       </c>
       <c r="H88" s="24" t="inlineStr"/>
-      <c r="I88" s="68" t="inlineStr">
+      <c r="I88" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -11203,7 +11231,7 @@
         </is>
       </c>
       <c r="AS88" s="23" t="n"/>
-      <c r="AT88" s="66" t="inlineStr"/>
+      <c r="AT88" s="67" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="53" t="inlineStr">
@@ -11238,7 +11266,7 @@
         </is>
       </c>
       <c r="H89" s="24" t="inlineStr"/>
-      <c r="I89" s="68" t="inlineStr">
+      <c r="I89" s="69" t="inlineStr">
         <is>
           <t>57%</t>
         </is>
@@ -11321,7 +11349,7 @@
         </is>
       </c>
       <c r="AS89" s="23" t="n"/>
-      <c r="AT89" s="66" t="inlineStr"/>
+      <c r="AT89" s="67" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="53" t="inlineStr">
@@ -11356,7 +11384,7 @@
         </is>
       </c>
       <c r="H90" s="24" t="inlineStr"/>
-      <c r="I90" s="68" t="inlineStr">
+      <c r="I90" s="69" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -11439,7 +11467,7 @@
         </is>
       </c>
       <c r="AS90" s="23" t="n"/>
-      <c r="AT90" s="66" t="inlineStr"/>
+      <c r="AT90" s="67" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="53" t="inlineStr">
@@ -11474,7 +11502,7 @@
         </is>
       </c>
       <c r="H91" s="24" t="inlineStr"/>
-      <c r="I91" s="68" t="inlineStr">
+      <c r="I91" s="69" t="inlineStr">
         <is>
           <t>79%</t>
         </is>
@@ -11557,10 +11585,10 @@
         </is>
       </c>
       <c r="AS91" s="23" t="n"/>
-      <c r="AT91" s="66" t="inlineStr"/>
+      <c r="AT91" s="67" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="67" t="inlineStr">
+      <c r="A92" s="68" t="inlineStr">
         <is>
           <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
@@ -11679,7 +11707,7 @@
         </is>
       </c>
       <c r="AS92" s="23" t="n"/>
-      <c r="AT92" s="66" t="inlineStr"/>
+      <c r="AT92" s="67" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="53" t="inlineStr">
@@ -11714,7 +11742,7 @@
         </is>
       </c>
       <c r="H93" s="24" t="inlineStr"/>
-      <c r="I93" s="68" t="inlineStr">
+      <c r="I93" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -11797,7 +11825,7 @@
         </is>
       </c>
       <c r="AS93" s="23" t="n"/>
-      <c r="AT93" s="66" t="inlineStr"/>
+      <c r="AT93" s="67" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="53" t="inlineStr">
@@ -11923,10 +11951,10 @@
         </is>
       </c>
       <c r="AS94" s="23" t="n"/>
-      <c r="AT94" s="66" t="inlineStr"/>
+      <c r="AT94" s="67" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="67" t="inlineStr">
+      <c r="A95" s="68" t="inlineStr">
         <is>
           <t>PS5-28-05 - HP Relief Header</t>
         </is>
@@ -12049,7 +12077,7 @@
         </is>
       </c>
       <c r="AS95" s="23" t="n"/>
-      <c r="AT95" s="66" t="inlineStr"/>
+      <c r="AT95" s="67" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="53" t="inlineStr">
@@ -12088,7 +12116,7 @@
         </is>
       </c>
       <c r="H96" s="24" t="inlineStr"/>
-      <c r="I96" s="68" t="inlineStr">
+      <c r="I96" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -12171,7 +12199,7 @@
         </is>
       </c>
       <c r="AS96" s="23" t="n"/>
-      <c r="AT96" s="66" t="inlineStr"/>
+      <c r="AT96" s="67" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="53" t="inlineStr">
@@ -12289,7 +12317,7 @@
         </is>
       </c>
       <c r="AS97" s="23" t="n"/>
-      <c r="AT97" s="66" t="inlineStr"/>
+      <c r="AT97" s="67" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="53" t="inlineStr">
@@ -12324,7 +12352,7 @@
         </is>
       </c>
       <c r="H98" s="24" t="inlineStr"/>
-      <c r="I98" s="69" t="inlineStr">
+      <c r="I98" s="70" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -12407,7 +12435,7 @@
         </is>
       </c>
       <c r="AS98" s="23" t="n"/>
-      <c r="AT98" s="66" t="inlineStr"/>
+      <c r="AT98" s="67" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="53" t="inlineStr">
@@ -12442,7 +12470,7 @@
         </is>
       </c>
       <c r="H99" s="24" t="inlineStr"/>
-      <c r="I99" s="68" t="inlineStr">
+      <c r="I99" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -12525,7 +12553,7 @@
         </is>
       </c>
       <c r="AS99" s="23" t="n"/>
-      <c r="AT99" s="66" t="inlineStr"/>
+      <c r="AT99" s="67" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="53" t="inlineStr">
@@ -12560,7 +12588,7 @@
         </is>
       </c>
       <c r="H100" s="24" t="inlineStr"/>
-      <c r="I100" s="69" t="inlineStr">
+      <c r="I100" s="70" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -12643,7 +12671,7 @@
         </is>
       </c>
       <c r="AS100" s="23" t="n"/>
-      <c r="AT100" s="66" t="inlineStr"/>
+      <c r="AT100" s="67" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="53" t="inlineStr">
@@ -12678,7 +12706,7 @@
         </is>
       </c>
       <c r="H101" s="24" t="inlineStr"/>
-      <c r="I101" s="68" t="inlineStr">
+      <c r="I101" s="69" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -12761,7 +12789,7 @@
         </is>
       </c>
       <c r="AS101" s="23" t="n"/>
-      <c r="AT101" s="66" t="inlineStr"/>
+      <c r="AT101" s="67" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="53" t="inlineStr">
@@ -12796,7 +12824,7 @@
         </is>
       </c>
       <c r="H102" s="24" t="inlineStr"/>
-      <c r="I102" s="68" t="inlineStr">
+      <c r="I102" s="69" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -12879,7 +12907,7 @@
         </is>
       </c>
       <c r="AS102" s="23" t="n"/>
-      <c r="AT102" s="66" t="inlineStr"/>
+      <c r="AT102" s="67" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="53" t="inlineStr">
@@ -12914,7 +12942,7 @@
         </is>
       </c>
       <c r="H103" s="24" t="inlineStr"/>
-      <c r="I103" s="68" t="inlineStr">
+      <c r="I103" s="69" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -12997,7 +13025,7 @@
         </is>
       </c>
       <c r="AS103" s="23" t="n"/>
-      <c r="AT103" s="66" t="inlineStr"/>
+      <c r="AT103" s="67" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="53" t="inlineStr">
@@ -13032,7 +13060,7 @@
         </is>
       </c>
       <c r="H104" s="24" t="inlineStr"/>
-      <c r="I104" s="68" t="inlineStr">
+      <c r="I104" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -13115,7 +13143,7 @@
         </is>
       </c>
       <c r="AS104" s="23" t="n"/>
-      <c r="AT104" s="66" t="inlineStr"/>
+      <c r="AT104" s="67" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="53" t="inlineStr">
@@ -13150,7 +13178,7 @@
         </is>
       </c>
       <c r="H105" s="24" t="inlineStr"/>
-      <c r="I105" s="68" t="inlineStr">
+      <c r="I105" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -13233,7 +13261,7 @@
         </is>
       </c>
       <c r="AS105" s="23" t="n"/>
-      <c r="AT105" s="66" t="inlineStr"/>
+      <c r="AT105" s="67" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="53" t="inlineStr">
@@ -13268,7 +13296,7 @@
         </is>
       </c>
       <c r="H106" s="24" t="inlineStr"/>
-      <c r="I106" s="68" t="inlineStr">
+      <c r="I106" s="69" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -13351,7 +13379,7 @@
         </is>
       </c>
       <c r="AS106" s="23" t="n"/>
-      <c r="AT106" s="66" t="inlineStr"/>
+      <c r="AT106" s="67" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="53" t="inlineStr">
@@ -13386,7 +13414,7 @@
         </is>
       </c>
       <c r="H107" s="24" t="inlineStr"/>
-      <c r="I107" s="68" t="inlineStr">
+      <c r="I107" s="69" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -13469,7 +13497,7 @@
         </is>
       </c>
       <c r="AS107" s="23" t="n"/>
-      <c r="AT107" s="66" t="inlineStr"/>
+      <c r="AT107" s="67" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="53" t="inlineStr">
@@ -13504,7 +13532,7 @@
         </is>
       </c>
       <c r="H108" s="24" t="inlineStr"/>
-      <c r="I108" s="69" t="inlineStr">
+      <c r="I108" s="70" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -13587,7 +13615,7 @@
         </is>
       </c>
       <c r="AS108" s="23" t="n"/>
-      <c r="AT108" s="66" t="inlineStr"/>
+      <c r="AT108" s="67" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="53" t="inlineStr">
@@ -13622,7 +13650,7 @@
         </is>
       </c>
       <c r="H109" s="24" t="inlineStr"/>
-      <c r="I109" s="69" t="inlineStr">
+      <c r="I109" s="70" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -13705,7 +13733,7 @@
         </is>
       </c>
       <c r="AS109" s="23" t="n"/>
-      <c r="AT109" s="66" t="inlineStr"/>
+      <c r="AT109" s="67" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="53" t="inlineStr">
@@ -13740,7 +13768,7 @@
         </is>
       </c>
       <c r="H110" s="24" t="inlineStr"/>
-      <c r="I110" s="69" t="inlineStr">
+      <c r="I110" s="70" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -13823,10 +13851,10 @@
         </is>
       </c>
       <c r="AS110" s="23" t="n"/>
-      <c r="AT110" s="66" t="inlineStr"/>
+      <c r="AT110" s="67" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="73" t="inlineStr">
+      <c r="A111" s="74" t="inlineStr">
         <is>
           <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
@@ -13856,7 +13884,7 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="G111" s="68" t="inlineStr">
+      <c r="G111" s="69" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -13866,7 +13894,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I111" s="68" t="inlineStr">
+      <c r="I111" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -13949,7 +13977,7 @@
         </is>
       </c>
       <c r="AS111" s="23" t="n"/>
-      <c r="AT111" s="66" t="inlineStr"/>
+      <c r="AT111" s="67" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="53" t="inlineStr">
@@ -13984,7 +14012,7 @@
         </is>
       </c>
       <c r="H112" s="24" t="inlineStr"/>
-      <c r="I112" s="68" t="inlineStr">
+      <c r="I112" s="69" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -14067,7 +14095,7 @@
         </is>
       </c>
       <c r="AS112" s="23" t="n"/>
-      <c r="AT112" s="66" t="inlineStr"/>
+      <c r="AT112" s="67" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="53" t="inlineStr">
@@ -14102,7 +14130,7 @@
         </is>
       </c>
       <c r="H113" s="24" t="inlineStr"/>
-      <c r="I113" s="68" t="inlineStr">
+      <c r="I113" s="69" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -14185,7 +14213,7 @@
         </is>
       </c>
       <c r="AS113" s="23" t="n"/>
-      <c r="AT113" s="66" t="inlineStr"/>
+      <c r="AT113" s="67" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="53" t="inlineStr">
@@ -14220,7 +14248,7 @@
         </is>
       </c>
       <c r="H114" s="24" t="inlineStr"/>
-      <c r="I114" s="69" t="inlineStr">
+      <c r="I114" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14303,7 +14331,7 @@
         </is>
       </c>
       <c r="AS114" s="23" t="n"/>
-      <c r="AT114" s="66" t="inlineStr"/>
+      <c r="AT114" s="67" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="53" t="inlineStr">
@@ -14421,7 +14449,7 @@
         </is>
       </c>
       <c r="AS115" s="23" t="n"/>
-      <c r="AT115" s="66" t="inlineStr"/>
+      <c r="AT115" s="67" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="53" t="inlineStr">
@@ -14460,7 +14488,7 @@
         </is>
       </c>
       <c r="H116" s="24" t="inlineStr"/>
-      <c r="I116" s="68" t="inlineStr">
+      <c r="I116" s="69" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -14543,10 +14571,10 @@
         </is>
       </c>
       <c r="AS116" s="23" t="n"/>
-      <c r="AT116" s="66" t="inlineStr"/>
+      <c r="AT116" s="67" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="67" t="inlineStr">
+      <c r="A117" s="68" t="inlineStr">
         <is>
           <t>PS5-60-01 - Power Generation Package A</t>
         </is>
@@ -14669,10 +14697,10 @@
         </is>
       </c>
       <c r="AS117" s="23" t="n"/>
-      <c r="AT117" s="66" t="inlineStr"/>
+      <c r="AT117" s="67" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="67" t="inlineStr">
+      <c r="A118" s="68" t="inlineStr">
         <is>
           <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
@@ -14699,7 +14727,7 @@
       </c>
       <c r="F118" s="23" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>20-Aug-26</t>
         </is>
       </c>
       <c r="G118" s="27" t="inlineStr">
@@ -14709,7 +14737,7 @@
       </c>
       <c r="H118" s="24" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>PS5 - Milestone B</t>
         </is>
       </c>
       <c r="I118" s="54" t="inlineStr">
@@ -14791,11 +14819,11 @@
       </c>
       <c r="AR118" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
         </is>
       </c>
       <c r="AS118" s="23" t="n"/>
-      <c r="AT118" s="66" t="inlineStr"/>
+      <c r="AT118" s="67" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="53" t="inlineStr">
@@ -14838,7 +14866,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I119" s="68" t="inlineStr">
+      <c r="I119" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -14870,7 +14898,7 @@
       <c r="R119" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S119" s="70" t="inlineStr">
+      <c r="S119" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -14921,10 +14949,10 @@
         </is>
       </c>
       <c r="AS119" s="23" t="n"/>
-      <c r="AT119" s="66" t="inlineStr"/>
+      <c r="AT119" s="67" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="67" t="inlineStr">
+      <c r="A120" s="68" t="inlineStr">
         <is>
           <t>PS5-60-04 - Power Generation Package B</t>
         </is>
@@ -15047,7 +15075,7 @@
         </is>
       </c>
       <c r="AS120" s="23" t="n"/>
-      <c r="AT120" s="66" t="inlineStr"/>
+      <c r="AT120" s="67" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="53" t="inlineStr">
@@ -15122,7 +15150,7 @@
       <c r="R121" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="S121" s="70" t="inlineStr">
+      <c r="S121" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15165,7 +15193,7 @@
       <c r="AQ121" s="65" t="inlineStr"/>
       <c r="AR121" s="23" t="inlineStr"/>
       <c r="AS121" s="23" t="n"/>
-      <c r="AT121" s="66" t="inlineStr"/>
+      <c r="AT121" s="67" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="53" t="inlineStr">
@@ -15208,7 +15236,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I122" s="68" t="inlineStr">
+      <c r="I122" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -15240,7 +15268,7 @@
       <c r="R122" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S122" s="70" t="inlineStr">
+      <c r="S122" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15283,7 +15311,7 @@
       <c r="AQ122" s="65" t="inlineStr"/>
       <c r="AR122" s="23" t="inlineStr"/>
       <c r="AS122" s="23" t="n"/>
-      <c r="AT122" s="66" t="inlineStr"/>
+      <c r="AT122" s="67" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="53" t="inlineStr">
@@ -15411,7 +15439,7 @@
         </is>
       </c>
       <c r="AS123" s="23" t="n"/>
-      <c r="AT123" s="66" t="inlineStr"/>
+      <c r="AT123" s="67" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="53" t="inlineStr">
@@ -15486,7 +15514,7 @@
       <c r="R124" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="S124" s="70" t="inlineStr">
+      <c r="S124" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15529,7 +15557,7 @@
       <c r="AQ124" s="65" t="inlineStr"/>
       <c r="AR124" s="23" t="inlineStr"/>
       <c r="AS124" s="23" t="n"/>
-      <c r="AT124" s="66" t="inlineStr"/>
+      <c r="AT124" s="67" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="53" t="inlineStr">
@@ -15572,7 +15600,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I125" s="68" t="inlineStr">
+      <c r="I125" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -15604,7 +15632,7 @@
       <c r="R125" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S125" s="70" t="inlineStr">
+      <c r="S125" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15647,7 +15675,7 @@
       <c r="AQ125" s="65" t="inlineStr"/>
       <c r="AR125" s="23" t="inlineStr"/>
       <c r="AS125" s="23" t="n"/>
-      <c r="AT125" s="66" t="inlineStr"/>
+      <c r="AT125" s="67" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="53" t="inlineStr">
@@ -15722,7 +15750,7 @@
       <c r="R126" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="S126" s="70" t="inlineStr">
+      <c r="S126" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15773,7 +15801,7 @@
         </is>
       </c>
       <c r="AS126" s="23" t="n"/>
-      <c r="AT126" s="66" t="inlineStr"/>
+      <c r="AT126" s="67" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="53" t="inlineStr">
@@ -15848,7 +15876,7 @@
       <c r="R127" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="S127" s="70" t="inlineStr">
+      <c r="S127" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15891,7 +15919,7 @@
       <c r="AQ127" s="65" t="inlineStr"/>
       <c r="AR127" s="23" t="inlineStr"/>
       <c r="AS127" s="23" t="n"/>
-      <c r="AT127" s="66" t="inlineStr"/>
+      <c r="AT127" s="67" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="53" t="inlineStr">
@@ -15934,7 +15962,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I128" s="68" t="inlineStr">
+      <c r="I128" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -15966,7 +15994,7 @@
       <c r="R128" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S128" s="70" t="inlineStr">
+      <c r="S128" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16009,7 +16037,7 @@
       <c r="AQ128" s="65" t="inlineStr"/>
       <c r="AR128" s="23" t="inlineStr"/>
       <c r="AS128" s="23" t="n"/>
-      <c r="AT128" s="66" t="inlineStr"/>
+      <c r="AT128" s="67" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="53" t="inlineStr">
@@ -16135,7 +16163,7 @@
         </is>
       </c>
       <c r="AS129" s="23" t="n"/>
-      <c r="AT129" s="66" t="inlineStr"/>
+      <c r="AT129" s="67" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="53" t="inlineStr">
@@ -16210,7 +16238,7 @@
       <c r="R130" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="S130" s="70" t="inlineStr">
+      <c r="S130" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16253,7 +16281,7 @@
       <c r="AQ130" s="65" t="inlineStr"/>
       <c r="AR130" s="23" t="inlineStr"/>
       <c r="AS130" s="23" t="n"/>
-      <c r="AT130" s="66" t="inlineStr"/>
+      <c r="AT130" s="67" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="53" t="inlineStr">
@@ -16296,7 +16324,7 @@
           <t>full</t>
         </is>
       </c>
-      <c r="I131" s="68" t="inlineStr">
+      <c r="I131" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -16328,7 +16356,7 @@
       <c r="R131" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S131" s="70" t="inlineStr">
+      <c r="S131" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16371,7 +16399,7 @@
       <c r="AQ131" s="65" t="inlineStr"/>
       <c r="AR131" s="23" t="inlineStr"/>
       <c r="AS131" s="23" t="n"/>
-      <c r="AT131" s="66" t="inlineStr"/>
+      <c r="AT131" s="67" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="53" t="inlineStr">
@@ -16442,7 +16470,7 @@
       <c r="R132" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="S132" s="70" t="inlineStr">
+      <c r="S132" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16493,7 +16521,7 @@
         </is>
       </c>
       <c r="AS132" s="23" t="n"/>
-      <c r="AT132" s="66" t="inlineStr"/>
+      <c r="AT132" s="67" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="53" t="inlineStr">
@@ -16528,7 +16556,7 @@
         </is>
       </c>
       <c r="H133" s="24" t="inlineStr"/>
-      <c r="I133" s="68" t="inlineStr">
+      <c r="I133" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -16560,7 +16588,7 @@
       <c r="R133" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="S133" s="70" t="inlineStr">
+      <c r="S133" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16603,7 +16631,7 @@
       <c r="AQ133" s="65" t="inlineStr"/>
       <c r="AR133" s="23" t="inlineStr"/>
       <c r="AS133" s="23" t="n"/>
-      <c r="AT133" s="66" t="inlineStr"/>
+      <c r="AT133" s="67" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="53" t="inlineStr">
@@ -16642,7 +16670,7 @@
         </is>
       </c>
       <c r="H134" s="24" t="inlineStr"/>
-      <c r="I134" s="68" t="inlineStr">
+      <c r="I134" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -16674,7 +16702,7 @@
       <c r="R134" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S134" s="70" t="inlineStr">
+      <c r="S134" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16717,7 +16745,7 @@
       <c r="AQ134" s="65" t="inlineStr"/>
       <c r="AR134" s="23" t="inlineStr"/>
       <c r="AS134" s="23" t="n"/>
-      <c r="AT134" s="66" t="inlineStr"/>
+      <c r="AT134" s="67" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="53" t="inlineStr">
@@ -16835,7 +16863,7 @@
         </is>
       </c>
       <c r="AS135" s="23" t="n"/>
-      <c r="AT135" s="66" t="inlineStr"/>
+      <c r="AT135" s="67" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="53" t="inlineStr">
@@ -16874,7 +16902,7 @@
         </is>
       </c>
       <c r="H136" s="24" t="inlineStr"/>
-      <c r="I136" s="68" t="inlineStr">
+      <c r="I136" s="69" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -16906,7 +16934,7 @@
       <c r="R136" s="62" t="n">
         <v>3</v>
       </c>
-      <c r="S136" s="70" t="inlineStr">
+      <c r="S136" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16949,7 +16977,7 @@
       <c r="AQ136" s="65" t="inlineStr"/>
       <c r="AR136" s="23" t="inlineStr"/>
       <c r="AS136" s="23" t="n"/>
-      <c r="AT136" s="66" t="inlineStr"/>
+      <c r="AT136" s="67" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="53" t="inlineStr">
@@ -16988,7 +17016,7 @@
         </is>
       </c>
       <c r="H137" s="24" t="inlineStr"/>
-      <c r="I137" s="68" t="inlineStr">
+      <c r="I137" s="69" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -17020,7 +17048,7 @@
       <c r="R137" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S137" s="70" t="inlineStr">
+      <c r="S137" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -17063,7 +17091,7 @@
       <c r="AQ137" s="65" t="inlineStr"/>
       <c r="AR137" s="23" t="inlineStr"/>
       <c r="AS137" s="23" t="n"/>
-      <c r="AT137" s="66" t="inlineStr"/>
+      <c r="AT137" s="67" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="53" t="inlineStr">
@@ -17106,7 +17134,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I138" s="68" t="inlineStr">
+      <c r="I138" s="69" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -17138,7 +17166,7 @@
       <c r="R138" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="S138" s="70" t="inlineStr">
+      <c r="S138" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -17191,10 +17219,10 @@
         </is>
       </c>
       <c r="AS138" s="23" t="n"/>
-      <c r="AT138" s="66" t="inlineStr"/>
+      <c r="AT138" s="67" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="67" t="inlineStr">
+      <c r="A139" s="68" t="inlineStr">
         <is>
           <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
@@ -17313,7 +17341,7 @@
         </is>
       </c>
       <c r="AS139" s="23" t="n"/>
-      <c r="AT139" s="66" t="inlineStr"/>
+      <c r="AT139" s="67" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="53" t="inlineStr">
@@ -17439,7 +17467,7 @@
         </is>
       </c>
       <c r="AS140" s="23" t="n"/>
-      <c r="AT140" s="66" t="inlineStr"/>
+      <c r="AT140" s="67" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="53" t="inlineStr">
@@ -17565,10 +17593,10 @@
         </is>
       </c>
       <c r="AS141" s="23" t="n"/>
-      <c r="AT141" s="66" t="inlineStr"/>
+      <c r="AT141" s="67" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="67" t="inlineStr">
+      <c r="A142" s="68" t="inlineStr">
         <is>
           <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
@@ -17585,7 +17613,7 @@
       </c>
       <c r="D142" s="23" t="inlineStr">
         <is>
-          <t>E,I,M,P</t>
+          <t>walkdown complete</t>
         </is>
       </c>
       <c r="E142" s="23" t="inlineStr">
@@ -17691,10 +17719,10 @@
         </is>
       </c>
       <c r="AS142" s="23" t="n"/>
-      <c r="AT142" s="66" t="inlineStr"/>
+      <c r="AT142" s="67" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="67" t="inlineStr">
+      <c r="A143" s="68" t="inlineStr">
         <is>
           <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
@@ -17817,10 +17845,10 @@
         </is>
       </c>
       <c r="AS143" s="23" t="n"/>
-      <c r="AT143" s="66" t="inlineStr"/>
+      <c r="AT143" s="67" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="67" t="inlineStr">
+      <c r="A144" s="74" t="inlineStr">
         <is>
           <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
@@ -17850,9 +17878,9 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="G144" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
+      <c r="G144" s="69" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="H144" s="24" t="inlineStr">
@@ -17943,10 +17971,10 @@
         </is>
       </c>
       <c r="AS144" s="23" t="n"/>
-      <c r="AT144" s="66" t="inlineStr"/>
+      <c r="AT144" s="67" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="67" t="inlineStr">
+      <c r="A145" s="68" t="inlineStr">
         <is>
           <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
@@ -18069,10 +18097,10 @@
         </is>
       </c>
       <c r="AS145" s="23" t="n"/>
-      <c r="AT145" s="66" t="inlineStr"/>
+      <c r="AT145" s="67" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="67" t="inlineStr">
+      <c r="A146" s="68" t="inlineStr">
         <is>
           <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
@@ -18195,10 +18223,10 @@
         </is>
       </c>
       <c r="AS146" s="23" t="n"/>
-      <c r="AT146" s="66" t="inlineStr"/>
+      <c r="AT146" s="67" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="67" t="inlineStr">
+      <c r="A147" s="68" t="inlineStr">
         <is>
           <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
@@ -18321,10 +18349,10 @@
         </is>
       </c>
       <c r="AS147" s="23" t="n"/>
-      <c r="AT147" s="66" t="inlineStr"/>
+      <c r="AT147" s="67" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="67" t="inlineStr">
+      <c r="A148" s="68" t="inlineStr">
         <is>
           <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
@@ -18447,10 +18475,10 @@
         </is>
       </c>
       <c r="AS148" s="23" t="n"/>
-      <c r="AT148" s="66" t="inlineStr"/>
+      <c r="AT148" s="67" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="67" t="inlineStr">
+      <c r="A149" s="68" t="inlineStr">
         <is>
           <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
@@ -18573,10 +18601,10 @@
         </is>
       </c>
       <c r="AS149" s="23" t="n"/>
-      <c r="AT149" s="66" t="inlineStr"/>
+      <c r="AT149" s="67" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="67" t="inlineStr">
+      <c r="A150" s="68" t="inlineStr">
         <is>
           <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
@@ -18699,10 +18727,10 @@
         </is>
       </c>
       <c r="AS150" s="23" t="n"/>
-      <c r="AT150" s="66" t="inlineStr"/>
+      <c r="AT150" s="67" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="67" t="inlineStr">
+      <c r="A151" s="75" t="inlineStr">
         <is>
           <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
@@ -18728,9 +18756,9 @@
         </is>
       </c>
       <c r="F151" s="23" t="inlineStr"/>
-      <c r="G151" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
+      <c r="G151" s="54" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="H151" s="24" t="inlineStr">
@@ -18821,10 +18849,10 @@
         </is>
       </c>
       <c r="AS151" s="23" t="n"/>
-      <c r="AT151" s="66" t="inlineStr"/>
+      <c r="AT151" s="67" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="67" t="inlineStr">
+      <c r="A152" s="68" t="inlineStr">
         <is>
           <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
@@ -18943,10 +18971,10 @@
         </is>
       </c>
       <c r="AS152" s="23" t="n"/>
-      <c r="AT152" s="66" t="inlineStr"/>
+      <c r="AT152" s="67" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="67" t="inlineStr">
+      <c r="A153" s="68" t="inlineStr">
         <is>
           <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
@@ -19069,10 +19097,10 @@
         </is>
       </c>
       <c r="AS153" s="23" t="n"/>
-      <c r="AT153" s="66" t="inlineStr"/>
+      <c r="AT153" s="67" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="67" t="inlineStr">
+      <c r="A154" s="68" t="inlineStr">
         <is>
           <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
@@ -19195,10 +19223,10 @@
         </is>
       </c>
       <c r="AS154" s="23" t="n"/>
-      <c r="AT154" s="66" t="inlineStr"/>
+      <c r="AT154" s="67" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="67" t="inlineStr">
+      <c r="A155" s="68" t="inlineStr">
         <is>
           <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
@@ -19321,10 +19349,10 @@
         </is>
       </c>
       <c r="AS155" s="23" t="n"/>
-      <c r="AT155" s="66" t="inlineStr"/>
+      <c r="AT155" s="67" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="67" t="inlineStr">
+      <c r="A156" s="68" t="inlineStr">
         <is>
           <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
@@ -19447,7 +19475,7 @@
         </is>
       </c>
       <c r="AS156" s="23" t="n"/>
-      <c r="AT156" s="66" t="inlineStr"/>
+      <c r="AT156" s="67" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="53" t="inlineStr">
@@ -19486,7 +19514,7 @@
         </is>
       </c>
       <c r="H157" s="24" t="inlineStr"/>
-      <c r="I157" s="68" t="inlineStr">
+      <c r="I157" s="69" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -19569,10 +19597,10 @@
         </is>
       </c>
       <c r="AS157" s="23" t="n"/>
-      <c r="AT157" s="66" t="inlineStr"/>
+      <c r="AT157" s="67" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="67" t="inlineStr">
+      <c r="A158" s="75" t="inlineStr">
         <is>
           <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
@@ -19598,9 +19626,9 @@
         </is>
       </c>
       <c r="F158" s="23" t="inlineStr"/>
-      <c r="G158" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
+      <c r="G158" s="54" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="H158" s="24" t="inlineStr">
@@ -19691,10 +19719,10 @@
         </is>
       </c>
       <c r="AS158" s="23" t="n"/>
-      <c r="AT158" s="66" t="inlineStr"/>
+      <c r="AT158" s="67" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="67" t="inlineStr">
+      <c r="A159" s="68" t="inlineStr">
         <is>
           <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
@@ -19813,10 +19841,10 @@
         </is>
       </c>
       <c r="AS159" s="23" t="n"/>
-      <c r="AT159" s="66" t="inlineStr"/>
+      <c r="AT159" s="67" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="67" t="inlineStr">
+      <c r="A160" s="68" t="inlineStr">
         <is>
           <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
@@ -19939,10 +19967,10 @@
         </is>
       </c>
       <c r="AS160" s="23" t="n"/>
-      <c r="AT160" s="66" t="inlineStr"/>
+      <c r="AT160" s="67" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="67" t="inlineStr">
+      <c r="A161" s="68" t="inlineStr">
         <is>
           <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
@@ -20065,10 +20093,10 @@
         </is>
       </c>
       <c r="AS161" s="23" t="n"/>
-      <c r="AT161" s="66" t="inlineStr"/>
+      <c r="AT161" s="67" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="67" t="inlineStr">
+      <c r="A162" s="68" t="inlineStr">
         <is>
           <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
@@ -20187,10 +20215,10 @@
         </is>
       </c>
       <c r="AS162" s="23" t="n"/>
-      <c r="AT162" s="66" t="inlineStr"/>
+      <c r="AT162" s="67" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="67" t="inlineStr">
+      <c r="A163" s="68" t="inlineStr">
         <is>
           <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
@@ -20313,7 +20341,7 @@
         </is>
       </c>
       <c r="AS163" s="23" t="n"/>
-      <c r="AT163" s="66" t="inlineStr"/>
+      <c r="AT163" s="67" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="53" t="inlineStr">
@@ -20431,7 +20459,7 @@
         </is>
       </c>
       <c r="AS164" s="23" t="n"/>
-      <c r="AT164" s="66" t="inlineStr"/>
+      <c r="AT164" s="67" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="53" t="inlineStr">
@@ -20506,7 +20534,7 @@
       <c r="R165" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S165" s="70" t="inlineStr">
+      <c r="S165" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -20547,9 +20575,13 @@
       </c>
       <c r="AP165" s="65" t="inlineStr"/>
       <c r="AQ165" s="65" t="inlineStr"/>
-      <c r="AR165" s="23" t="inlineStr"/>
+      <c r="AR165" s="23" t="inlineStr">
+        <is>
+          <t>OBSERVATION -CLEANING ON PROGRESS</t>
+        </is>
+      </c>
       <c r="AS165" s="23" t="n"/>
-      <c r="AT165" s="66" t="inlineStr"/>
+      <c r="AT165" s="67" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="53" t="inlineStr">
@@ -20624,7 +20656,7 @@
       <c r="R166" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S166" s="70" t="inlineStr">
+      <c r="S166" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -20667,7 +20699,7 @@
       <c r="AQ166" s="65" t="inlineStr"/>
       <c r="AR166" s="23" t="inlineStr"/>
       <c r="AS166" s="23" t="n"/>
-      <c r="AT166" s="66" t="inlineStr"/>
+      <c r="AT166" s="67" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="53" t="inlineStr">
@@ -20742,7 +20774,7 @@
       <c r="R167" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S167" s="70" t="inlineStr">
+      <c r="S167" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -20785,7 +20817,7 @@
       <c r="AQ167" s="65" t="inlineStr"/>
       <c r="AR167" s="23" t="inlineStr"/>
       <c r="AS167" s="23" t="n"/>
-      <c r="AT167" s="66" t="inlineStr"/>
+      <c r="AT167" s="67" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="53" t="inlineStr">
@@ -20828,7 +20860,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I168" s="68" t="inlineStr">
+      <c r="I168" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -20860,7 +20892,7 @@
       <c r="R168" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S168" s="70" t="inlineStr">
+      <c r="S168" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -20903,7 +20935,7 @@
       <c r="AQ168" s="65" t="inlineStr"/>
       <c r="AR168" s="23" t="inlineStr"/>
       <c r="AS168" s="23" t="n"/>
-      <c r="AT168" s="66" t="inlineStr"/>
+      <c r="AT168" s="67" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="53" t="inlineStr">
@@ -20970,7 +21002,7 @@
       <c r="R169" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S169" s="70" t="inlineStr">
+      <c r="S169" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21013,7 +21045,7 @@
       <c r="AQ169" s="65" t="inlineStr"/>
       <c r="AR169" s="23" t="inlineStr"/>
       <c r="AS169" s="23" t="n"/>
-      <c r="AT169" s="66" t="inlineStr"/>
+      <c r="AT169" s="67" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="53" t="inlineStr">
@@ -21080,7 +21112,7 @@
       <c r="R170" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S170" s="70" t="inlineStr">
+      <c r="S170" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21123,7 +21155,7 @@
       <c r="AQ170" s="65" t="inlineStr"/>
       <c r="AR170" s="23" t="inlineStr"/>
       <c r="AS170" s="23" t="n"/>
-      <c r="AT170" s="66" t="inlineStr"/>
+      <c r="AT170" s="67" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="53" t="inlineStr">
@@ -21158,7 +21190,7 @@
         </is>
       </c>
       <c r="H171" s="24" t="inlineStr"/>
-      <c r="I171" s="68" t="inlineStr">
+      <c r="I171" s="69" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -21190,7 +21222,7 @@
       <c r="R171" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S171" s="70" t="inlineStr">
+      <c r="S171" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21233,10 +21265,10 @@
       <c r="AQ171" s="65" t="inlineStr"/>
       <c r="AR171" s="23" t="inlineStr"/>
       <c r="AS171" s="23" t="n"/>
-      <c r="AT171" s="66" t="inlineStr"/>
+      <c r="AT171" s="67" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="67" t="inlineStr">
+      <c r="A172" s="68" t="inlineStr">
         <is>
           <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
@@ -21351,7 +21383,7 @@
       <c r="AQ172" s="65" t="inlineStr"/>
       <c r="AR172" s="23" t="inlineStr"/>
       <c r="AS172" s="23" t="n"/>
-      <c r="AT172" s="66" t="inlineStr"/>
+      <c r="AT172" s="67" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="53" t="inlineStr">
@@ -21426,7 +21458,7 @@
       <c r="R173" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S173" s="70" t="inlineStr">
+      <c r="S173" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21469,10 +21501,10 @@
       <c r="AQ173" s="65" t="inlineStr"/>
       <c r="AR173" s="23" t="inlineStr"/>
       <c r="AS173" s="23" t="n"/>
-      <c r="AT173" s="66" t="inlineStr"/>
+      <c r="AT173" s="67" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="67" t="inlineStr">
+      <c r="A174" s="68" t="inlineStr">
         <is>
           <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
@@ -21587,7 +21619,7 @@
       <c r="AQ174" s="65" t="inlineStr"/>
       <c r="AR174" s="23" t="inlineStr"/>
       <c r="AS174" s="23" t="n"/>
-      <c r="AT174" s="66" t="inlineStr"/>
+      <c r="AT174" s="67" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="53" t="inlineStr">
@@ -21662,7 +21694,7 @@
       <c r="R175" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S175" s="70" t="inlineStr">
+      <c r="S175" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21705,10 +21737,10 @@
       <c r="AQ175" s="65" t="inlineStr"/>
       <c r="AR175" s="23" t="inlineStr"/>
       <c r="AS175" s="23" t="n"/>
-      <c r="AT175" s="66" t="inlineStr"/>
+      <c r="AT175" s="67" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="67" t="inlineStr">
+      <c r="A176" s="68" t="inlineStr">
         <is>
           <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
@@ -21823,7 +21855,7 @@
       <c r="AQ176" s="65" t="inlineStr"/>
       <c r="AR176" s="23" t="inlineStr"/>
       <c r="AS176" s="23" t="n"/>
-      <c r="AT176" s="66" t="inlineStr"/>
+      <c r="AT176" s="67" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="53" t="inlineStr">
@@ -21898,7 +21930,7 @@
       <c r="R177" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S177" s="70" t="inlineStr">
+      <c r="S177" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21941,10 +21973,10 @@
       <c r="AQ177" s="65" t="inlineStr"/>
       <c r="AR177" s="23" t="inlineStr"/>
       <c r="AS177" s="23" t="n"/>
-      <c r="AT177" s="66" t="inlineStr"/>
+      <c r="AT177" s="67" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="67" t="inlineStr">
+      <c r="A178" s="68" t="inlineStr">
         <is>
           <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
@@ -22059,7 +22091,7 @@
       <c r="AQ178" s="65" t="inlineStr"/>
       <c r="AR178" s="23" t="inlineStr"/>
       <c r="AS178" s="23" t="n"/>
-      <c r="AT178" s="66" t="inlineStr"/>
+      <c r="AT178" s="67" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="53" t="inlineStr">
@@ -22134,7 +22166,7 @@
       <c r="R179" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S179" s="70" t="inlineStr">
+      <c r="S179" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -22177,7 +22209,7 @@
       <c r="AQ179" s="65" t="inlineStr"/>
       <c r="AR179" s="23" t="inlineStr"/>
       <c r="AS179" s="23" t="n"/>
-      <c r="AT179" s="66" t="inlineStr"/>
+      <c r="AT179" s="67" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="53" t="inlineStr">
@@ -22295,7 +22327,7 @@
         </is>
       </c>
       <c r="AS180" s="23" t="n"/>
-      <c r="AT180" s="66" t="inlineStr"/>
+      <c r="AT180" s="67" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="53" t="inlineStr">
@@ -22334,7 +22366,7 @@
         </is>
       </c>
       <c r="H181" s="24" t="inlineStr"/>
-      <c r="I181" s="68" t="inlineStr">
+      <c r="I181" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -22366,7 +22398,7 @@
       <c r="R181" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S181" s="70" t="inlineStr">
+      <c r="S181" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -22409,7 +22441,7 @@
       <c r="AQ181" s="65" t="inlineStr"/>
       <c r="AR181" s="23" t="inlineStr"/>
       <c r="AS181" s="23" t="n"/>
-      <c r="AT181" s="66" t="inlineStr"/>
+      <c r="AT181" s="67" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="53" t="inlineStr">
@@ -22527,7 +22559,7 @@
         </is>
       </c>
       <c r="AS182" s="23" t="n"/>
-      <c r="AT182" s="66" t="inlineStr"/>
+      <c r="AT182" s="67" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="53" t="inlineStr">
@@ -22566,7 +22598,7 @@
         </is>
       </c>
       <c r="H183" s="24" t="inlineStr"/>
-      <c r="I183" s="68" t="inlineStr">
+      <c r="I183" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -22598,7 +22630,7 @@
       <c r="R183" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S183" s="70" t="inlineStr">
+      <c r="S183" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -22641,7 +22673,7 @@
       <c r="AQ183" s="65" t="inlineStr"/>
       <c r="AR183" s="23" t="inlineStr"/>
       <c r="AS183" s="23" t="n"/>
-      <c r="AT183" s="66" t="inlineStr"/>
+      <c r="AT183" s="67" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="53" t="inlineStr">
@@ -22676,7 +22708,7 @@
         </is>
       </c>
       <c r="H184" s="24" t="inlineStr"/>
-      <c r="I184" s="68" t="inlineStr">
+      <c r="I184" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -22759,7 +22791,7 @@
         </is>
       </c>
       <c r="AS184" s="23" t="n"/>
-      <c r="AT184" s="66" t="inlineStr"/>
+      <c r="AT184" s="67" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="53" t="inlineStr">
@@ -22798,7 +22830,7 @@
         </is>
       </c>
       <c r="H185" s="24" t="inlineStr"/>
-      <c r="I185" s="68" t="inlineStr">
+      <c r="I185" s="69" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -22830,7 +22862,7 @@
       <c r="R185" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S185" s="70" t="inlineStr">
+      <c r="S185" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -22873,10 +22905,10 @@
       <c r="AQ185" s="65" t="inlineStr"/>
       <c r="AR185" s="23" t="inlineStr"/>
       <c r="AS185" s="23" t="n"/>
-      <c r="AT185" s="66" t="inlineStr"/>
+      <c r="AT185" s="67" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="67" t="inlineStr">
+      <c r="A186" s="68" t="inlineStr">
         <is>
           <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
@@ -22999,10 +23031,10 @@
         </is>
       </c>
       <c r="AS186" s="23" t="n"/>
-      <c r="AT186" s="66" t="inlineStr"/>
+      <c r="AT186" s="67" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="67" t="inlineStr">
+      <c r="A187" s="68" t="inlineStr">
         <is>
           <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
@@ -23125,10 +23157,10 @@
         </is>
       </c>
       <c r="AS187" s="23" t="n"/>
-      <c r="AT187" s="66" t="inlineStr"/>
+      <c r="AT187" s="67" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="67" t="inlineStr">
+      <c r="A188" s="68" t="inlineStr">
         <is>
           <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
@@ -23251,10 +23283,10 @@
         </is>
       </c>
       <c r="AS188" s="23" t="n"/>
-      <c r="AT188" s="66" t="inlineStr"/>
+      <c r="AT188" s="67" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="67" t="inlineStr">
+      <c r="A189" s="68" t="inlineStr">
         <is>
           <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
@@ -23377,10 +23409,10 @@
         </is>
       </c>
       <c r="AS189" s="23" t="n"/>
-      <c r="AT189" s="66" t="inlineStr"/>
+      <c r="AT189" s="67" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="67" t="inlineStr">
+      <c r="A190" s="68" t="inlineStr">
         <is>
           <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
@@ -23503,10 +23535,10 @@
         </is>
       </c>
       <c r="AS190" s="23" t="n"/>
-      <c r="AT190" s="66" t="inlineStr"/>
+      <c r="AT190" s="67" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="67" t="inlineStr">
+      <c r="A191" s="68" t="inlineStr">
         <is>
           <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
@@ -23629,7 +23661,7 @@
         </is>
       </c>
       <c r="AS191" s="23" t="n"/>
-      <c r="AT191" s="66" t="inlineStr"/>
+      <c r="AT191" s="67" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="53" t="inlineStr">
@@ -23747,7 +23779,7 @@
         </is>
       </c>
       <c r="AS192" s="23" t="n"/>
-      <c r="AT192" s="66" t="inlineStr"/>
+      <c r="AT192" s="67" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="53" t="inlineStr">
@@ -23875,7 +23907,7 @@
         </is>
       </c>
       <c r="AS193" s="23" t="n"/>
-      <c r="AT193" s="66" t="inlineStr"/>
+      <c r="AT193" s="67" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="53" t="inlineStr">
@@ -23910,7 +23942,7 @@
         </is>
       </c>
       <c r="H194" s="24" t="inlineStr"/>
-      <c r="I194" s="68" t="inlineStr">
+      <c r="I194" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -23993,7 +24025,7 @@
         </is>
       </c>
       <c r="AS194" s="23" t="n"/>
-      <c r="AT194" s="66" t="inlineStr"/>
+      <c r="AT194" s="67" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="53" t="inlineStr">
@@ -24028,7 +24060,7 @@
         </is>
       </c>
       <c r="H195" s="24" t="inlineStr"/>
-      <c r="I195" s="68" t="inlineStr">
+      <c r="I195" s="69" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -24111,7 +24143,7 @@
         </is>
       </c>
       <c r="AS195" s="23" t="n"/>
-      <c r="AT195" s="66" t="inlineStr"/>
+      <c r="AT195" s="67" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="53" t="inlineStr">
@@ -24150,7 +24182,7 @@
         </is>
       </c>
       <c r="H196" s="24" t="inlineStr"/>
-      <c r="I196" s="69" t="inlineStr">
+      <c r="I196" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -24233,10 +24265,10 @@
         </is>
       </c>
       <c r="AS196" s="23" t="n"/>
-      <c r="AT196" s="66" t="inlineStr"/>
+      <c r="AT196" s="67" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="67" t="inlineStr">
+      <c r="A197" s="68" t="inlineStr">
         <is>
           <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
@@ -24359,7 +24391,7 @@
         </is>
       </c>
       <c r="AS197" s="23" t="n"/>
-      <c r="AT197" s="66" t="inlineStr"/>
+      <c r="AT197" s="67" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="53" t="inlineStr">
@@ -24398,7 +24430,7 @@
         </is>
       </c>
       <c r="H198" s="24" t="inlineStr"/>
-      <c r="I198" s="68" t="inlineStr">
+      <c r="I198" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -24481,10 +24513,10 @@
         </is>
       </c>
       <c r="AS198" s="23" t="n"/>
-      <c r="AT198" s="66" t="inlineStr"/>
+      <c r="AT198" s="67" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="67" t="inlineStr">
+      <c r="A199" s="68" t="inlineStr">
         <is>
           <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
@@ -24607,7 +24639,7 @@
         </is>
       </c>
       <c r="AS199" s="23" t="n"/>
-      <c r="AT199" s="66" t="inlineStr"/>
+      <c r="AT199" s="67" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="53" t="inlineStr">
@@ -24642,7 +24674,7 @@
         </is>
       </c>
       <c r="H200" s="24" t="inlineStr"/>
-      <c r="I200" s="69" t="inlineStr">
+      <c r="I200" s="70" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -24725,7 +24757,7 @@
         </is>
       </c>
       <c r="AS200" s="23" t="n"/>
-      <c r="AT200" s="66" t="inlineStr"/>
+      <c r="AT200" s="67" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="53" t="inlineStr">
@@ -24764,7 +24796,7 @@
         </is>
       </c>
       <c r="H201" s="24" t="inlineStr"/>
-      <c r="I201" s="69" t="inlineStr">
+      <c r="I201" s="70" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -24847,10 +24879,10 @@
         </is>
       </c>
       <c r="AS201" s="23" t="n"/>
-      <c r="AT201" s="66" t="inlineStr"/>
+      <c r="AT201" s="67" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="67" t="inlineStr">
+      <c r="A202" s="68" t="inlineStr">
         <is>
           <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
@@ -24973,10 +25005,10 @@
         </is>
       </c>
       <c r="AS202" s="23" t="n"/>
-      <c r="AT202" s="66" t="inlineStr"/>
+      <c r="AT202" s="67" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="67" t="inlineStr">
+      <c r="A203" s="68" t="inlineStr">
         <is>
           <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
@@ -25099,7 +25131,7 @@
         </is>
       </c>
       <c r="AS203" s="23" t="n"/>
-      <c r="AT203" s="66" t="inlineStr"/>
+      <c r="AT203" s="67" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="53" t="inlineStr">
@@ -25118,7 +25150,7 @@
         </is>
       </c>
       <c r="H204" s="24" t="inlineStr"/>
-      <c r="I204" s="69" t="inlineStr">
+      <c r="I204" s="70" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -25183,7 +25215,7 @@
       <c r="AQ204" s="65" t="inlineStr"/>
       <c r="AR204" s="23" t="inlineStr"/>
       <c r="AS204" s="23" t="n"/>
-      <c r="AT204" s="66" t="inlineStr"/>
+      <c r="AT204" s="67" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="53" t="inlineStr">
@@ -25218,7 +25250,7 @@
         </is>
       </c>
       <c r="H205" s="24" t="inlineStr"/>
-      <c r="I205" s="69" t="inlineStr">
+      <c r="I205" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -25301,7 +25333,7 @@
         </is>
       </c>
       <c r="AS205" s="23" t="n"/>
-      <c r="AT205" s="66" t="inlineStr"/>
+      <c r="AT205" s="67" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="53" t="inlineStr">
@@ -25336,7 +25368,7 @@
         </is>
       </c>
       <c r="H206" s="24" t="inlineStr"/>
-      <c r="I206" s="69" t="inlineStr">
+      <c r="I206" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -25419,7 +25451,7 @@
         </is>
       </c>
       <c r="AS206" s="23" t="n"/>
-      <c r="AT206" s="66" t="inlineStr"/>
+      <c r="AT206" s="67" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="53" t="inlineStr">
@@ -25454,7 +25486,7 @@
         </is>
       </c>
       <c r="H207" s="24" t="inlineStr"/>
-      <c r="I207" s="69" t="inlineStr">
+      <c r="I207" s="70" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -25537,7 +25569,7 @@
         </is>
       </c>
       <c r="AS207" s="23" t="n"/>
-      <c r="AT207" s="66" t="inlineStr"/>
+      <c r="AT207" s="67" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="53" t="inlineStr">
@@ -25572,7 +25604,7 @@
         </is>
       </c>
       <c r="H208" s="24" t="inlineStr"/>
-      <c r="I208" s="69" t="inlineStr">
+      <c r="I208" s="70" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -25655,7 +25687,7 @@
         </is>
       </c>
       <c r="AS208" s="23" t="n"/>
-      <c r="AT208" s="66" t="inlineStr"/>
+      <c r="AT208" s="67" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="53" t="inlineStr">
@@ -25690,7 +25722,7 @@
         </is>
       </c>
       <c r="H209" s="24" t="inlineStr"/>
-      <c r="I209" s="68" t="inlineStr">
+      <c r="I209" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -25773,10 +25805,10 @@
         </is>
       </c>
       <c r="AS209" s="23" t="n"/>
-      <c r="AT209" s="66" t="inlineStr"/>
+      <c r="AT209" s="67" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="67" t="inlineStr">
+      <c r="A210" s="68" t="inlineStr">
         <is>
           <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
@@ -25899,7 +25931,7 @@
         </is>
       </c>
       <c r="AS210" s="23" t="n"/>
-      <c r="AT210" s="66" t="inlineStr"/>
+      <c r="AT210" s="67" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="53" t="inlineStr">
@@ -25934,7 +25966,7 @@
         </is>
       </c>
       <c r="H211" s="24" t="inlineStr"/>
-      <c r="I211" s="69" t="inlineStr">
+      <c r="I211" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -26017,7 +26049,7 @@
         </is>
       </c>
       <c r="AS211" s="23" t="n"/>
-      <c r="AT211" s="66" t="inlineStr"/>
+      <c r="AT211" s="67" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="53" t="inlineStr">
@@ -26060,7 +26092,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I212" s="69" t="inlineStr">
+      <c r="I212" s="70" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -26143,7 +26175,7 @@
         </is>
       </c>
       <c r="AS212" s="23" t="n"/>
-      <c r="AT212" s="66" t="inlineStr"/>
+      <c r="AT212" s="67" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="53" t="inlineStr">
@@ -26182,7 +26214,7 @@
         </is>
       </c>
       <c r="H213" s="24" t="inlineStr"/>
-      <c r="I213" s="69" t="inlineStr">
+      <c r="I213" s="70" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -26265,7 +26297,7 @@
         </is>
       </c>
       <c r="AS213" s="23" t="n"/>
-      <c r="AT213" s="66" t="inlineStr"/>
+      <c r="AT213" s="67" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="53" t="inlineStr">
@@ -26304,7 +26336,7 @@
         </is>
       </c>
       <c r="H214" s="24" t="inlineStr"/>
-      <c r="I214" s="69" t="inlineStr">
+      <c r="I214" s="70" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -26387,7 +26419,7 @@
         </is>
       </c>
       <c r="AS214" s="23" t="n"/>
-      <c r="AT214" s="66" t="inlineStr"/>
+      <c r="AT214" s="67" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="53" t="inlineStr">
@@ -26426,7 +26458,7 @@
         </is>
       </c>
       <c r="H215" s="24" t="inlineStr"/>
-      <c r="I215" s="69" t="inlineStr">
+      <c r="I215" s="70" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -26509,7 +26541,7 @@
         </is>
       </c>
       <c r="AS215" s="23" t="n"/>
-      <c r="AT215" s="66" t="inlineStr"/>
+      <c r="AT215" s="67" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="53" t="inlineStr">
@@ -26552,7 +26584,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I216" s="69" t="inlineStr">
+      <c r="I216" s="70" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -26635,7 +26667,7 @@
         </is>
       </c>
       <c r="AS216" s="23" t="n"/>
-      <c r="AT216" s="66" t="inlineStr"/>
+      <c r="AT216" s="67" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="53" t="inlineStr">
@@ -26674,7 +26706,7 @@
         </is>
       </c>
       <c r="H217" s="24" t="inlineStr"/>
-      <c r="I217" s="69" t="inlineStr">
+      <c r="I217" s="70" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -26757,7 +26789,7 @@
         </is>
       </c>
       <c r="AS217" s="23" t="n"/>
-      <c r="AT217" s="66" t="inlineStr"/>
+      <c r="AT217" s="67" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="53" t="inlineStr">
@@ -26841,7 +26873,7 @@
       <c r="AQ218" s="65" t="inlineStr"/>
       <c r="AR218" s="23" t="inlineStr"/>
       <c r="AS218" s="23" t="n"/>
-      <c r="AT218" s="66" t="inlineStr"/>
+      <c r="AT218" s="67" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="53" t="inlineStr">
@@ -26925,7 +26957,7 @@
       <c r="AQ219" s="65" t="inlineStr"/>
       <c r="AR219" s="23" t="inlineStr"/>
       <c r="AS219" s="23" t="n"/>
-      <c r="AT219" s="66" t="inlineStr"/>
+      <c r="AT219" s="67" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="53" t="inlineStr">
@@ -26960,7 +26992,7 @@
         </is>
       </c>
       <c r="H220" s="24" t="inlineStr"/>
-      <c r="I220" s="69" t="inlineStr">
+      <c r="I220" s="70" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -27043,7 +27075,7 @@
         </is>
       </c>
       <c r="AS220" s="23" t="n"/>
-      <c r="AT220" s="66" t="inlineStr"/>
+      <c r="AT220" s="67" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="53" t="inlineStr">
@@ -27078,7 +27110,7 @@
         </is>
       </c>
       <c r="H221" s="24" t="inlineStr"/>
-      <c r="I221" s="69" t="inlineStr">
+      <c r="I221" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -27161,7 +27193,7 @@
         </is>
       </c>
       <c r="AS221" s="23" t="n"/>
-      <c r="AT221" s="66" t="inlineStr"/>
+      <c r="AT221" s="67" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="53" t="inlineStr">
@@ -27196,7 +27228,7 @@
         </is>
       </c>
       <c r="H222" s="24" t="inlineStr"/>
-      <c r="I222" s="69" t="inlineStr">
+      <c r="I222" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -27279,7 +27311,7 @@
         </is>
       </c>
       <c r="AS222" s="23" t="n"/>
-      <c r="AT222" s="66" t="inlineStr"/>
+      <c r="AT222" s="67" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="53" t="inlineStr">
@@ -27314,7 +27346,7 @@
         </is>
       </c>
       <c r="H223" s="24" t="inlineStr"/>
-      <c r="I223" s="69" t="inlineStr">
+      <c r="I223" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -27397,7 +27429,7 @@
         </is>
       </c>
       <c r="AS223" s="23" t="n"/>
-      <c r="AT223" s="66" t="inlineStr"/>
+      <c r="AT223" s="67" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="53" t="inlineStr">
@@ -27432,7 +27464,7 @@
         </is>
       </c>
       <c r="H224" s="24" t="inlineStr"/>
-      <c r="I224" s="69" t="inlineStr">
+      <c r="I224" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -27515,7 +27547,7 @@
         </is>
       </c>
       <c r="AS224" s="23" t="n"/>
-      <c r="AT224" s="66" t="inlineStr"/>
+      <c r="AT224" s="67" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="53" t="inlineStr">
@@ -27550,7 +27582,7 @@
         </is>
       </c>
       <c r="H225" s="24" t="inlineStr"/>
-      <c r="I225" s="69" t="inlineStr">
+      <c r="I225" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -27633,7 +27665,7 @@
         </is>
       </c>
       <c r="AS225" s="23" t="n"/>
-      <c r="AT225" s="66" t="inlineStr"/>
+      <c r="AT225" s="67" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="53" t="inlineStr">
@@ -27668,7 +27700,7 @@
         </is>
       </c>
       <c r="H226" s="24" t="inlineStr"/>
-      <c r="I226" s="69" t="inlineStr">
+      <c r="I226" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -27751,7 +27783,7 @@
         </is>
       </c>
       <c r="AS226" s="23" t="n"/>
-      <c r="AT226" s="66" t="inlineStr"/>
+      <c r="AT226" s="67" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="53" t="inlineStr">
@@ -27794,7 +27826,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I227" s="69" t="inlineStr">
+      <c r="I227" s="70" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -27868,7 +27900,7 @@
       <c r="AP227" s="65" t="inlineStr"/>
       <c r="AQ227" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18 ITRs for lightning, 22 ITRs for grounding cannot be closed due to material issues.</t>
         </is>
       </c>
       <c r="AR227" s="23" t="inlineStr">
@@ -27877,7 +27909,7 @@
         </is>
       </c>
       <c r="AS227" s="23" t="n"/>
-      <c r="AT227" s="66" t="inlineStr"/>
+      <c r="AT227" s="67" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="53" t="inlineStr">
@@ -27912,7 +27944,7 @@
         </is>
       </c>
       <c r="H228" s="24" t="inlineStr"/>
-      <c r="I228" s="69" t="inlineStr">
+      <c r="I228" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -27995,7 +28027,7 @@
         </is>
       </c>
       <c r="AS228" s="23" t="n"/>
-      <c r="AT228" s="66" t="inlineStr"/>
+      <c r="AT228" s="67" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="53" t="inlineStr">
@@ -28038,7 +28070,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I229" s="68" t="inlineStr">
+      <c r="I229" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -28121,10 +28153,10 @@
         </is>
       </c>
       <c r="AS229" s="23" t="n"/>
-      <c r="AT229" s="66" t="inlineStr"/>
+      <c r="AT229" s="67" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="67" t="inlineStr">
+      <c r="A230" s="68" t="inlineStr">
         <is>
           <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
@@ -28205,7 +28237,7 @@
       <c r="AQ230" s="65" t="inlineStr"/>
       <c r="AR230" s="23" t="inlineStr"/>
       <c r="AS230" s="23" t="n"/>
-      <c r="AT230" s="66" t="inlineStr"/>
+      <c r="AT230" s="67" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="53" t="inlineStr">
@@ -28240,7 +28272,7 @@
         </is>
       </c>
       <c r="H231" s="24" t="inlineStr"/>
-      <c r="I231" s="69" t="inlineStr">
+      <c r="I231" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -28323,7 +28355,7 @@
         </is>
       </c>
       <c r="AS231" s="23" t="n"/>
-      <c r="AT231" s="66" t="inlineStr"/>
+      <c r="AT231" s="67" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="53" t="inlineStr">
@@ -28358,7 +28390,7 @@
         </is>
       </c>
       <c r="H232" s="24" t="inlineStr"/>
-      <c r="I232" s="69" t="inlineStr">
+      <c r="I232" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -28441,7 +28473,7 @@
         </is>
       </c>
       <c r="AS232" s="23" t="n"/>
-      <c r="AT232" s="66" t="inlineStr"/>
+      <c r="AT232" s="67" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="53" t="inlineStr">
@@ -28476,7 +28508,7 @@
         </is>
       </c>
       <c r="H233" s="24" t="inlineStr"/>
-      <c r="I233" s="69" t="inlineStr">
+      <c r="I233" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -28559,7 +28591,7 @@
         </is>
       </c>
       <c r="AS233" s="23" t="n"/>
-      <c r="AT233" s="66" t="inlineStr"/>
+      <c r="AT233" s="67" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="53" t="inlineStr">
@@ -28594,7 +28626,7 @@
         </is>
       </c>
       <c r="H234" s="24" t="inlineStr"/>
-      <c r="I234" s="69" t="inlineStr">
+      <c r="I234" s="70" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -28665,7 +28697,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP234" s="65" t="inlineStr"/>
+      <c r="AP234" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ234" s="65" t="inlineStr">
         <is>
           <t>PS5-71-TW-0007, PS5-71-TW-0003, PS5-71-TW-0004, PS5-71-TW-0006 not arrived</t>
@@ -28677,7 +28713,7 @@
         </is>
       </c>
       <c r="AS234" s="23" t="n"/>
-      <c r="AT234" s="66" t="inlineStr"/>
+      <c r="AT234" s="67" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="53" t="inlineStr">
@@ -28712,7 +28748,7 @@
         </is>
       </c>
       <c r="H235" s="24" t="inlineStr"/>
-      <c r="I235" s="68" t="inlineStr">
+      <c r="I235" s="69" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -28795,7 +28831,7 @@
         </is>
       </c>
       <c r="AS235" s="23" t="n"/>
-      <c r="AT235" s="66" t="inlineStr"/>
+      <c r="AT235" s="67" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="53" t="inlineStr">
@@ -28814,7 +28850,7 @@
         </is>
       </c>
       <c r="H236" s="24" t="inlineStr"/>
-      <c r="I236" s="69" t="inlineStr">
+      <c r="I236" s="70" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
@@ -28879,7 +28915,7 @@
       <c r="AQ236" s="65" t="inlineStr"/>
       <c r="AR236" s="23" t="inlineStr"/>
       <c r="AS236" s="23" t="n"/>
-      <c r="AT236" s="66" t="inlineStr"/>
+      <c r="AT236" s="67" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="53" t="inlineStr">
@@ -28914,7 +28950,7 @@
         </is>
       </c>
       <c r="H237" s="24" t="inlineStr"/>
-      <c r="I237" s="68" t="inlineStr">
+      <c r="I237" s="69" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
@@ -28999,7 +29035,7 @@
         </is>
       </c>
       <c r="AS237" s="23" t="n"/>
-      <c r="AT237" s="66" t="inlineStr"/>
+      <c r="AT237" s="67" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="53" t="inlineStr">
@@ -29034,7 +29070,7 @@
         </is>
       </c>
       <c r="H238" s="24" t="inlineStr"/>
-      <c r="I238" s="68" t="inlineStr">
+      <c r="I238" s="69" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -29117,7 +29153,7 @@
         </is>
       </c>
       <c r="AS238" s="23" t="n"/>
-      <c r="AT238" s="66" t="inlineStr"/>
+      <c r="AT238" s="67" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="53" t="inlineStr">
@@ -29156,7 +29192,7 @@
         </is>
       </c>
       <c r="H239" s="24" t="inlineStr"/>
-      <c r="I239" s="68" t="inlineStr">
+      <c r="I239" s="69" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
@@ -29259,7 +29295,7 @@
         </is>
       </c>
       <c r="AS239" s="23" t="n"/>
-      <c r="AT239" s="66" t="inlineStr"/>
+      <c r="AT239" s="67" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="53" t="inlineStr">
@@ -29298,7 +29334,7 @@
         </is>
       </c>
       <c r="H240" s="24" t="inlineStr"/>
-      <c r="I240" s="68" t="inlineStr">
+      <c r="I240" s="69" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -29330,7 +29366,7 @@
       <c r="R240" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="S240" s="70" t="inlineStr">
+      <c r="S240" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -29383,7 +29419,7 @@
         </is>
       </c>
       <c r="AS240" s="23" t="n"/>
-      <c r="AT240" s="66" t="inlineStr"/>
+      <c r="AT240" s="67" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="53" t="inlineStr">
@@ -29511,7 +29547,7 @@
         </is>
       </c>
       <c r="AS241" s="23" t="n"/>
-      <c r="AT241" s="66" t="inlineStr"/>
+      <c r="AT241" s="67" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="53" t="inlineStr">
@@ -29586,7 +29622,7 @@
       <c r="R242" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S242" s="70" t="inlineStr">
+      <c r="S242" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -29629,7 +29665,7 @@
       <c r="AQ242" s="65" t="inlineStr"/>
       <c r="AR242" s="23" t="inlineStr"/>
       <c r="AS242" s="23" t="n"/>
-      <c r="AT242" s="66" t="inlineStr"/>
+      <c r="AT242" s="67" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="53" t="inlineStr">
@@ -29664,7 +29700,7 @@
         </is>
       </c>
       <c r="H243" s="24" t="inlineStr"/>
-      <c r="I243" s="68" t="inlineStr">
+      <c r="I243" s="69" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -29747,7 +29783,7 @@
         </is>
       </c>
       <c r="AS243" s="23" t="n"/>
-      <c r="AT243" s="66" t="inlineStr"/>
+      <c r="AT243" s="67" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="53" t="inlineStr">
@@ -29782,7 +29818,7 @@
         </is>
       </c>
       <c r="H244" s="24" t="inlineStr"/>
-      <c r="I244" s="68" t="inlineStr">
+      <c r="I244" s="69" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -29865,7 +29901,7 @@
         </is>
       </c>
       <c r="AS244" s="23" t="n"/>
-      <c r="AT244" s="66" t="inlineStr"/>
+      <c r="AT244" s="67" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="53" t="inlineStr">
@@ -29900,7 +29936,7 @@
         </is>
       </c>
       <c r="H245" s="24" t="inlineStr"/>
-      <c r="I245" s="68" t="inlineStr">
+      <c r="I245" s="69" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -29983,7 +30019,7 @@
         </is>
       </c>
       <c r="AS245" s="23" t="n"/>
-      <c r="AT245" s="66" t="inlineStr"/>
+      <c r="AT245" s="67" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="53" t="inlineStr">
@@ -30018,7 +30054,7 @@
         </is>
       </c>
       <c r="H246" s="24" t="inlineStr"/>
-      <c r="I246" s="68" t="inlineStr">
+      <c r="I246" s="69" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -30101,7 +30137,7 @@
         </is>
       </c>
       <c r="AS246" s="23" t="n"/>
-      <c r="AT246" s="66" t="inlineStr"/>
+      <c r="AT246" s="67" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="53" t="inlineStr">
@@ -30140,7 +30176,7 @@
         </is>
       </c>
       <c r="H247" s="24" t="inlineStr"/>
-      <c r="I247" s="68" t="inlineStr">
+      <c r="I247" s="69" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -30223,7 +30259,7 @@
         </is>
       </c>
       <c r="AS247" s="23" t="n"/>
-      <c r="AT247" s="66" t="inlineStr"/>
+      <c r="AT247" s="67" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="53" t="inlineStr">
@@ -30349,7 +30385,7 @@
         </is>
       </c>
       <c r="AS248" s="23" t="n"/>
-      <c r="AT248" s="66" t="inlineStr"/>
+      <c r="AT248" s="67" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="53" t="inlineStr">
@@ -30392,7 +30428,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I249" s="68" t="inlineStr">
+      <c r="I249" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -30479,7 +30515,7 @@
         </is>
       </c>
       <c r="AS249" s="23" t="n"/>
-      <c r="AT249" s="66" t="inlineStr"/>
+      <c r="AT249" s="67" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="53" t="inlineStr">
@@ -30518,7 +30554,7 @@
         </is>
       </c>
       <c r="H250" s="24" t="inlineStr"/>
-      <c r="I250" s="68" t="inlineStr">
+      <c r="I250" s="69" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -30550,7 +30586,7 @@
       <c r="R250" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="S250" s="70" t="inlineStr">
+      <c r="S250" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -30603,7 +30639,7 @@
         </is>
       </c>
       <c r="AS250" s="23" t="n"/>
-      <c r="AT250" s="66" t="inlineStr"/>
+      <c r="AT250" s="67" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="53" t="inlineStr">
@@ -30646,7 +30682,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I251" s="68" t="inlineStr">
+      <c r="I251" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -30729,7 +30765,7 @@
         </is>
       </c>
       <c r="AS251" s="23" t="n"/>
-      <c r="AT251" s="66" t="inlineStr"/>
+      <c r="AT251" s="67" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="53" t="inlineStr">
@@ -30857,10 +30893,10 @@
         </is>
       </c>
       <c r="AS252" s="23" t="n"/>
-      <c r="AT252" s="66" t="inlineStr"/>
+      <c r="AT252" s="67" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="67" t="inlineStr">
+      <c r="A253" s="68" t="inlineStr">
         <is>
           <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
@@ -30892,7 +30928,7 @@
       </c>
       <c r="G253" s="27" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>DONE(full)</t>
         </is>
       </c>
       <c r="H253" s="24" t="inlineStr">
@@ -30983,7 +31019,7 @@
         </is>
       </c>
       <c r="AS253" s="23" t="n"/>
-      <c r="AT253" s="66" t="inlineStr"/>
+      <c r="AT253" s="67" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="53" t="inlineStr">
@@ -31026,7 +31062,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I254" s="68" t="inlineStr">
+      <c r="I254" s="69" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -31058,7 +31094,7 @@
       <c r="R254" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S254" s="70" t="inlineStr">
+      <c r="S254" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -31109,7 +31145,7 @@
         </is>
       </c>
       <c r="AS254" s="23" t="n"/>
-      <c r="AT254" s="66" t="inlineStr"/>
+      <c r="AT254" s="67" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="53" t="inlineStr">
@@ -31152,7 +31188,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I255" s="68" t="inlineStr">
+      <c r="I255" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -31235,7 +31271,7 @@
         </is>
       </c>
       <c r="AS255" s="23" t="n"/>
-      <c r="AT255" s="66" t="inlineStr"/>
+      <c r="AT255" s="67" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="53" t="inlineStr">
@@ -31278,7 +31314,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I256" s="68" t="inlineStr">
+      <c r="I256" s="69" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -31361,10 +31397,10 @@
         </is>
       </c>
       <c r="AS256" s="23" t="n"/>
-      <c r="AT256" s="66" t="inlineStr"/>
+      <c r="AT256" s="67" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="67" t="inlineStr">
+      <c r="A257" s="68" t="inlineStr">
         <is>
           <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
@@ -31487,7 +31523,7 @@
         </is>
       </c>
       <c r="AS257" s="23" t="n"/>
-      <c r="AT257" s="66" t="inlineStr"/>
+      <c r="AT257" s="67" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="53" t="inlineStr">
@@ -31522,7 +31558,7 @@
         </is>
       </c>
       <c r="H258" s="24" t="inlineStr"/>
-      <c r="I258" s="68" t="inlineStr">
+      <c r="I258" s="69" t="inlineStr">
         <is>
           <t>81%</t>
         </is>
@@ -31605,7 +31641,7 @@
         </is>
       </c>
       <c r="AS258" s="23" t="n"/>
-      <c r="AT258" s="66" t="inlineStr"/>
+      <c r="AT258" s="67" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="53" t="inlineStr">
@@ -31640,7 +31676,7 @@
         </is>
       </c>
       <c r="H259" s="24" t="inlineStr"/>
-      <c r="I259" s="69" t="inlineStr">
+      <c r="I259" s="70" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
@@ -31723,7 +31759,7 @@
         </is>
       </c>
       <c r="AS259" s="23" t="n"/>
-      <c r="AT259" s="66" t="inlineStr"/>
+      <c r="AT259" s="67" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="53" t="inlineStr">
@@ -31758,7 +31794,7 @@
         </is>
       </c>
       <c r="H260" s="24" t="inlineStr"/>
-      <c r="I260" s="68" t="inlineStr">
+      <c r="I260" s="69" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -31841,7 +31877,7 @@
         </is>
       </c>
       <c r="AS260" s="23" t="n"/>
-      <c r="AT260" s="66" t="inlineStr"/>
+      <c r="AT260" s="67" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="53" t="inlineStr">
@@ -31876,7 +31912,7 @@
         </is>
       </c>
       <c r="H261" s="24" t="inlineStr"/>
-      <c r="I261" s="68" t="inlineStr">
+      <c r="I261" s="69" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
@@ -31959,10 +31995,10 @@
         </is>
       </c>
       <c r="AS261" s="23" t="n"/>
-      <c r="AT261" s="66" t="inlineStr"/>
+      <c r="AT261" s="67" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="73" t="inlineStr">
+      <c r="A262" s="74" t="inlineStr">
         <is>
           <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
@@ -31988,7 +32024,7 @@
         </is>
       </c>
       <c r="F262" s="23" t="inlineStr"/>
-      <c r="G262" s="68" t="inlineStr">
+      <c r="G262" s="69" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -31998,7 +32034,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I262" s="68" t="inlineStr">
+      <c r="I262" s="69" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -32081,7 +32117,7 @@
         </is>
       </c>
       <c r="AS262" s="23" t="n"/>
-      <c r="AT262" s="66" t="inlineStr"/>
+      <c r="AT262" s="67" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="53" t="inlineStr">
@@ -32116,7 +32152,7 @@
         </is>
       </c>
       <c r="H263" s="24" t="inlineStr"/>
-      <c r="I263" s="69" t="inlineStr">
+      <c r="I263" s="70" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -32199,7 +32235,7 @@
         </is>
       </c>
       <c r="AS263" s="23" t="n"/>
-      <c r="AT263" s="66" t="inlineStr"/>
+      <c r="AT263" s="67" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="53" t="inlineStr">
@@ -32234,7 +32270,7 @@
         </is>
       </c>
       <c r="H264" s="24" t="inlineStr"/>
-      <c r="I264" s="69" t="inlineStr">
+      <c r="I264" s="70" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -32317,7 +32353,7 @@
         </is>
       </c>
       <c r="AS264" s="23" t="n"/>
-      <c r="AT264" s="66" t="inlineStr"/>
+      <c r="AT264" s="67" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="53" t="inlineStr">
@@ -32352,7 +32388,7 @@
         </is>
       </c>
       <c r="H265" s="24" t="inlineStr"/>
-      <c r="I265" s="69" t="inlineStr">
+      <c r="I265" s="70" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -32435,7 +32471,7 @@
         </is>
       </c>
       <c r="AS265" s="23" t="n"/>
-      <c r="AT265" s="66" t="inlineStr"/>
+      <c r="AT265" s="67" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="53" t="inlineStr">
@@ -32470,7 +32506,7 @@
         </is>
       </c>
       <c r="H266" s="24" t="inlineStr"/>
-      <c r="I266" s="69" t="inlineStr">
+      <c r="I266" s="70" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -32553,7 +32589,7 @@
         </is>
       </c>
       <c r="AS266" s="23" t="n"/>
-      <c r="AT266" s="66" t="inlineStr"/>
+      <c r="AT266" s="67" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="53" t="inlineStr">
@@ -32588,7 +32624,7 @@
         </is>
       </c>
       <c r="H267" s="24" t="inlineStr"/>
-      <c r="I267" s="69" t="inlineStr">
+      <c r="I267" s="70" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -32671,7 +32707,7 @@
         </is>
       </c>
       <c r="AS267" s="23" t="n"/>
-      <c r="AT267" s="66" t="inlineStr"/>
+      <c r="AT267" s="67" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="53" t="inlineStr">
@@ -32706,7 +32742,7 @@
         </is>
       </c>
       <c r="H268" s="24" t="inlineStr"/>
-      <c r="I268" s="69" t="inlineStr">
+      <c r="I268" s="70" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -32789,7 +32825,7 @@
         </is>
       </c>
       <c r="AS268" s="23" t="n"/>
-      <c r="AT268" s="66" t="inlineStr"/>
+      <c r="AT268" s="67" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="53" t="inlineStr">
@@ -32824,7 +32860,7 @@
         </is>
       </c>
       <c r="H269" s="24" t="inlineStr"/>
-      <c r="I269" s="69" t="inlineStr">
+      <c r="I269" s="70" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -32907,7 +32943,7 @@
         </is>
       </c>
       <c r="AS269" s="23" t="n"/>
-      <c r="AT269" s="66" t="inlineStr"/>
+      <c r="AT269" s="67" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="53" t="inlineStr">
@@ -32942,7 +32978,7 @@
         </is>
       </c>
       <c r="H270" s="24" t="inlineStr"/>
-      <c r="I270" s="69" t="inlineStr">
+      <c r="I270" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -33025,7 +33061,7 @@
         </is>
       </c>
       <c r="AS270" s="23" t="n"/>
-      <c r="AT270" s="66" t="inlineStr"/>
+      <c r="AT270" s="67" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="53" t="inlineStr">
@@ -33060,7 +33096,7 @@
         </is>
       </c>
       <c r="H271" s="24" t="inlineStr"/>
-      <c r="I271" s="69" t="inlineStr">
+      <c r="I271" s="70" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -33143,7 +33179,7 @@
         </is>
       </c>
       <c r="AS271" s="23" t="n"/>
-      <c r="AT271" s="66" t="inlineStr"/>
+      <c r="AT271" s="67" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="53" t="inlineStr">
@@ -33178,7 +33214,7 @@
         </is>
       </c>
       <c r="H272" s="24" t="inlineStr"/>
-      <c r="I272" s="69" t="inlineStr">
+      <c r="I272" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -33261,7 +33297,7 @@
         </is>
       </c>
       <c r="AS272" s="23" t="n"/>
-      <c r="AT272" s="66" t="inlineStr"/>
+      <c r="AT272" s="67" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="53" t="inlineStr">
@@ -33296,7 +33332,7 @@
         </is>
       </c>
       <c r="H273" s="24" t="inlineStr"/>
-      <c r="I273" s="69" t="inlineStr">
+      <c r="I273" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -33379,7 +33415,7 @@
         </is>
       </c>
       <c r="AS273" s="23" t="n"/>
-      <c r="AT273" s="66" t="inlineStr"/>
+      <c r="AT273" s="67" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="53" t="inlineStr">
@@ -33414,7 +33450,7 @@
         </is>
       </c>
       <c r="H274" s="24" t="inlineStr"/>
-      <c r="I274" s="69" t="inlineStr">
+      <c r="I274" s="70" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -33497,7 +33533,7 @@
         </is>
       </c>
       <c r="AS274" s="23" t="n"/>
-      <c r="AT274" s="66" t="inlineStr"/>
+      <c r="AT274" s="67" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="53" t="inlineStr">
@@ -33532,7 +33568,7 @@
         </is>
       </c>
       <c r="H275" s="24" t="inlineStr"/>
-      <c r="I275" s="68" t="inlineStr">
+      <c r="I275" s="69" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -33615,7 +33651,7 @@
         </is>
       </c>
       <c r="AS275" s="23" t="n"/>
-      <c r="AT275" s="66" t="inlineStr"/>
+      <c r="AT275" s="67" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="53" t="inlineStr">
@@ -33650,7 +33686,7 @@
         </is>
       </c>
       <c r="H276" s="24" t="inlineStr"/>
-      <c r="I276" s="69" t="inlineStr">
+      <c r="I276" s="70" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -33733,7 +33769,7 @@
         </is>
       </c>
       <c r="AS276" s="23" t="n"/>
-      <c r="AT276" s="66" t="inlineStr"/>
+      <c r="AT276" s="67" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="53" t="inlineStr">
@@ -33768,7 +33804,7 @@
         </is>
       </c>
       <c r="H277" s="24" t="inlineStr"/>
-      <c r="I277" s="69" t="inlineStr">
+      <c r="I277" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -33851,7 +33887,7 @@
         </is>
       </c>
       <c r="AS277" s="23" t="n"/>
-      <c r="AT277" s="66" t="inlineStr"/>
+      <c r="AT277" s="67" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="53" t="inlineStr">
@@ -33886,7 +33922,7 @@
         </is>
       </c>
       <c r="H278" s="24" t="inlineStr"/>
-      <c r="I278" s="68" t="inlineStr">
+      <c r="I278" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -33969,7 +34005,7 @@
         </is>
       </c>
       <c r="AS278" s="23" t="n"/>
-      <c r="AT278" s="66" t="inlineStr"/>
+      <c r="AT278" s="67" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="53" t="inlineStr">
@@ -34004,7 +34040,7 @@
         </is>
       </c>
       <c r="H279" s="24" t="inlineStr"/>
-      <c r="I279" s="69" t="inlineStr">
+      <c r="I279" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -34087,7 +34123,7 @@
         </is>
       </c>
       <c r="AS279" s="23" t="n"/>
-      <c r="AT279" s="66" t="inlineStr"/>
+      <c r="AT279" s="67" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="53" t="inlineStr">
@@ -34122,7 +34158,7 @@
         </is>
       </c>
       <c r="H280" s="24" t="inlineStr"/>
-      <c r="I280" s="69" t="inlineStr">
+      <c r="I280" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -34205,7 +34241,7 @@
         </is>
       </c>
       <c r="AS280" s="23" t="n"/>
-      <c r="AT280" s="66" t="inlineStr"/>
+      <c r="AT280" s="67" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="53" t="inlineStr">
@@ -34240,7 +34276,7 @@
         </is>
       </c>
       <c r="H281" s="24" t="inlineStr"/>
-      <c r="I281" s="69" t="inlineStr">
+      <c r="I281" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -34323,10 +34359,10 @@
         </is>
       </c>
       <c r="AS281" s="23" t="n"/>
-      <c r="AT281" s="66" t="inlineStr"/>
+      <c r="AT281" s="67" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="67" t="inlineStr">
+      <c r="A282" s="68" t="inlineStr">
         <is>
           <t>PS5-83-01 - EITS Building</t>
         </is>
@@ -34449,7 +34485,7 @@
         </is>
       </c>
       <c r="AS282" s="23" t="n"/>
-      <c r="AT282" s="66" t="inlineStr"/>
+      <c r="AT282" s="67" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="53" t="inlineStr">
@@ -34484,7 +34520,7 @@
         </is>
       </c>
       <c r="H283" s="24" t="inlineStr"/>
-      <c r="I283" s="69" t="inlineStr">
+      <c r="I283" s="70" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -34567,7 +34603,7 @@
         </is>
       </c>
       <c r="AS283" s="23" t="n"/>
-      <c r="AT283" s="66" t="inlineStr"/>
+      <c r="AT283" s="67" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="53" t="inlineStr">
@@ -34602,7 +34638,7 @@
         </is>
       </c>
       <c r="H284" s="24" t="inlineStr"/>
-      <c r="I284" s="69" t="inlineStr">
+      <c r="I284" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -34685,10 +34721,10 @@
         </is>
       </c>
       <c r="AS284" s="23" t="n"/>
-      <c r="AT284" s="66" t="inlineStr"/>
+      <c r="AT284" s="67" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="67" t="inlineStr">
+      <c r="A285" s="68" t="inlineStr">
         <is>
           <t>PS5-84-03 - Shelters</t>
         </is>
@@ -34807,10 +34843,10 @@
         </is>
       </c>
       <c r="AS285" s="23" t="n"/>
-      <c r="AT285" s="66" t="inlineStr"/>
+      <c r="AT285" s="67" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="67" t="inlineStr">
+      <c r="A286" s="68" t="inlineStr">
         <is>
           <t>PS5-86-01 - Shelters</t>
         </is>
@@ -34929,10 +34965,10 @@
         </is>
       </c>
       <c r="AS286" s="23" t="n"/>
-      <c r="AT286" s="66" t="inlineStr"/>
+      <c r="AT286" s="67" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="67" t="inlineStr">
+      <c r="A287" s="68" t="inlineStr">
         <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
@@ -35055,7 +35091,7 @@
         </is>
       </c>
       <c r="AS287" s="23" t="n"/>
-      <c r="AT287" s="66" t="inlineStr"/>
+      <c r="AT287" s="67" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="53" t="inlineStr">
@@ -35090,7 +35126,7 @@
         </is>
       </c>
       <c r="H288" s="24" t="inlineStr"/>
-      <c r="I288" s="69" t="inlineStr">
+      <c r="I288" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -35173,7 +35209,7 @@
         </is>
       </c>
       <c r="AS288" s="23" t="n"/>
-      <c r="AT288" s="66" t="inlineStr"/>
+      <c r="AT288" s="67" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="53" t="inlineStr">
@@ -35208,7 +35244,7 @@
         </is>
       </c>
       <c r="H289" s="24" t="inlineStr"/>
-      <c r="I289" s="69" t="inlineStr">
+      <c r="I289" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -35291,7 +35327,7 @@
         </is>
       </c>
       <c r="AS289" s="23" t="n"/>
-      <c r="AT289" s="66" t="inlineStr"/>
+      <c r="AT289" s="67" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="53" t="inlineStr">
@@ -35326,7 +35362,7 @@
         </is>
       </c>
       <c r="H290" s="24" t="inlineStr"/>
-      <c r="I290" s="69" t="inlineStr">
+      <c r="I290" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -35409,7 +35445,7 @@
         </is>
       </c>
       <c r="AS290" s="23" t="n"/>
-      <c r="AT290" s="66" t="inlineStr"/>
+      <c r="AT290" s="67" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="53" t="inlineStr">
@@ -35444,7 +35480,7 @@
         </is>
       </c>
       <c r="H291" s="24" t="inlineStr"/>
-      <c r="I291" s="69" t="inlineStr">
+      <c r="I291" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -35527,7 +35563,7 @@
         </is>
       </c>
       <c r="AS291" s="23" t="n"/>
-      <c r="AT291" s="66" t="inlineStr"/>
+      <c r="AT291" s="67" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="53" t="inlineStr">
@@ -35562,7 +35598,7 @@
         </is>
       </c>
       <c r="H292" s="24" t="inlineStr"/>
-      <c r="I292" s="69" t="inlineStr">
+      <c r="I292" s="70" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -35645,7 +35681,7 @@
         </is>
       </c>
       <c r="AS292" s="23" t="n"/>
-      <c r="AT292" s="66" t="inlineStr"/>
+      <c r="AT292" s="67" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="53" t="inlineStr">
@@ -35688,7 +35724,7 @@
           <t>RE WALKDOWN</t>
         </is>
       </c>
-      <c r="I293" s="68" t="inlineStr">
+      <c r="I293" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -35771,7 +35807,7 @@
         </is>
       </c>
       <c r="AS293" s="23" t="n"/>
-      <c r="AT293" s="66" t="inlineStr"/>
+      <c r="AT293" s="67" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:AT293"/>

--- a/EXCEL/2 - RFC PROGRESS.xlsx
+++ b/EXCEL/2 - RFC PROGRESS.xlsx
@@ -241,6 +241,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFffeb9c"/>
+        <bgColor rgb="FFffeb9c"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFe8d5c4"/>
         <bgColor rgb="FFe8d5c4"/>
       </patternFill>
@@ -309,12 +315,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFBDD7EE"/>
         <bgColor rgb="FFBDD7EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFffeb9c"/>
-        <bgColor rgb="FFffeb9c"/>
       </patternFill>
     </fill>
     <fill>
@@ -576,7 +576,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -644,13 +644,10 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -674,22 +671,25 @@
     <xf numFmtId="0" fontId="6" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -698,13 +698,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -722,10 +722,10 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -740,7 +740,7 @@
     <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -773,16 +773,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1593,11 +1593,7 @@
           <t>2026-09-08 00:00:00</t>
         </is>
       </c>
-      <c r="F4" s="23" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
+      <c r="F4" s="23" t="inlineStr"/>
       <c r="G4" s="27" t="inlineStr">
         <is>
           <t>Full</t>
@@ -1610,7 +1606,7 @@
       </c>
       <c r="I4" s="54" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J4" s="55" t="n">
@@ -1651,14 +1647,14 @@
         <v>86</v>
       </c>
       <c r="AI4" s="23" t="n">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AJ4" s="23" t="n">
-        <v>6</v>
+        <v>-16</v>
       </c>
       <c r="AK4" s="29" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="AL4" s="23" t="inlineStr">
@@ -1696,7 +1692,7 @@
       <c r="AT4" s="67" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="53" t="inlineStr">
+      <c r="A5" s="68" t="inlineStr">
         <is>
           <t>PS5-01-02 - Fire Water Pump A</t>
         </is>
@@ -1822,7 +1818,7 @@
       <c r="AT5" s="67" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="53" t="inlineStr">
+      <c r="A6" s="68" t="inlineStr">
         <is>
           <t>PS5-01-03 - Fire Water Pump B</t>
         </is>
@@ -1847,11 +1843,7 @@
           <t>2026-09-08 00:00:00</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
+      <c r="F6" s="23" t="inlineStr"/>
       <c r="G6" s="27" t="inlineStr">
         <is>
           <t>Full</t>
@@ -1948,7 +1940,7 @@
       <c r="AT6" s="67" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="68" t="inlineStr">
+      <c r="A7" s="53" t="inlineStr">
         <is>
           <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
         </is>
@@ -2070,7 +2062,7 @@
       <c r="AT7" s="67" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="53" t="inlineStr">
+      <c r="A8" s="68" t="inlineStr">
         <is>
           <t>PS5-01-05 - Foam Skid</t>
         </is>
@@ -2196,7 +2188,7 @@
       <c r="AT8" s="67" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="68" t="inlineStr">
+      <c r="A9" s="53" t="inlineStr">
         <is>
           <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
@@ -2318,7 +2310,7 @@
       <c r="AT9" s="67" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="53" t="inlineStr">
+      <c r="A10" s="68" t="inlineStr">
         <is>
           <t>PS5-01-07 - Fire Water Ring Main &amp; Distribution</t>
         </is>
@@ -2438,7 +2430,7 @@
       <c r="AT10" s="67" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="53" t="inlineStr">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t>PS5-01-08 - PS5 Deluge Valve Skid (PS5-01-UK-6100)</t>
         </is>
@@ -2556,7 +2548,7 @@
       <c r="AT11" s="67" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="68" t="inlineStr">
+      <c r="A12" s="53" t="inlineStr">
         <is>
           <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
@@ -2674,7 +2666,7 @@
       <c r="AT12" s="67" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="68" t="inlineStr">
+      <c r="A13" s="53" t="inlineStr">
         <is>
           <t>PS5-01-10 - Water Mist Package</t>
         </is>
@@ -2800,7 +2792,7 @@
       <c r="AT13" s="67" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="53" t="inlineStr">
+      <c r="A14" s="68" t="inlineStr">
         <is>
           <t>PS5-01-11 - Inergen for Power Gen Building</t>
         </is>
@@ -2914,7 +2906,7 @@
       <c r="AT14" s="67" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="53" t="inlineStr">
+      <c r="A15" s="68" t="inlineStr">
         <is>
           <t>PS5-02-01 - Miscellaneous Safety equipment</t>
         </is>
@@ -2924,11 +2916,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="C15" s="23" t="inlineStr"/>
       <c r="D15" s="23" t="inlineStr">
         <is>
           <t>E,M,S</t>
@@ -3032,7 +3020,7 @@
       <c r="AT15" s="67" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="53" t="inlineStr">
+      <c r="A16" s="68" t="inlineStr">
         <is>
           <t>PS5-02-02 - Portable Fire Fighting Equipments</t>
         </is>
@@ -3150,7 +3138,7 @@
       <c r="AT16" s="67" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="53" t="inlineStr">
+      <c r="A17" s="68" t="inlineStr">
         <is>
           <t>PS5-03-01 - FZ-01 - Process Area</t>
         </is>
@@ -3276,7 +3264,7 @@
       <c r="AT17" s="67" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="53" t="inlineStr">
+      <c r="A18" s="68" t="inlineStr">
         <is>
           <t>PS5-03-03 - FZ-03 - Buildings Area</t>
         </is>
@@ -3394,7 +3382,7 @@
       <c r="AT18" s="67" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="53" t="inlineStr">
+      <c r="A19" s="68" t="inlineStr">
         <is>
           <t>PS5-03-04 - FZ-04 - Utilities - Diesel and Firewater Pumps Areas</t>
         </is>
@@ -3429,11 +3417,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H19" s="24" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
+      <c r="H19" s="24" t="inlineStr"/>
       <c r="I19" s="54" t="inlineStr">
         <is>
           <t>91%</t>
@@ -3520,7 +3504,7 @@
       <c r="AT19" s="67" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="53" t="inlineStr">
+      <c r="A20" s="68" t="inlineStr">
         <is>
           <t>PS5-03-06 - FZ-06 - Transformer Area</t>
         </is>
@@ -3646,7 +3630,7 @@
       <c r="AT20" s="67" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="68" t="inlineStr">
+      <c r="A21" s="53" t="inlineStr">
         <is>
           <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
         </is>
@@ -3772,7 +3756,7 @@
       <c r="AT21" s="67" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="53" t="inlineStr">
+      <c r="A22" s="68" t="inlineStr">
         <is>
           <t>PS5-03-08 - FZ-08 - Utilities - Power Generation Area - External</t>
         </is>
@@ -3890,7 +3874,7 @@
       <c r="AT22" s="67" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="68" t="inlineStr">
+      <c r="A23" s="53" t="inlineStr">
         <is>
           <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
         </is>
@@ -4016,7 +4000,7 @@
       <c r="AT23" s="67" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="68" t="inlineStr">
+      <c r="A24" s="53" t="inlineStr">
         <is>
           <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
         </is>
@@ -4138,7 +4122,7 @@
       <c r="AT24" s="67" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="53" t="inlineStr">
+      <c r="A25" s="68" t="inlineStr">
         <is>
           <t>PS5-03-11 - FZ-11 - Power Generation Building - Engine Bay 3</t>
         </is>
@@ -4260,7 +4244,7 @@
       <c r="AT25" s="67" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="53" t="inlineStr">
+      <c r="A26" s="68" t="inlineStr">
         <is>
           <t>PS5-03-12 - FZ-12 - Power Generation Building - Engine Bay 4</t>
         </is>
@@ -4378,7 +4362,7 @@
       <c r="AT26" s="67" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="68" t="inlineStr">
+      <c r="A27" s="53" t="inlineStr">
         <is>
           <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
         </is>
@@ -4504,7 +4488,7 @@
       <c r="AT27" s="67" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="53" t="inlineStr">
+      <c r="A28" s="68" t="inlineStr">
         <is>
           <t>PS5-03-14 - FZ-14 - Power Generation Building - Switchgear Room</t>
         </is>
@@ -4632,7 +4616,7 @@
       <c r="AT28" s="67" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="53" t="inlineStr">
+      <c r="A29" s="68" t="inlineStr">
         <is>
           <t>PS5-03-15 - FZ-15 - Power Generation Building - Generator Room 1</t>
         </is>
@@ -4754,7 +4738,7 @@
       <c r="AT29" s="67" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="53" t="inlineStr">
+      <c r="A30" s="68" t="inlineStr">
         <is>
           <t>PS5-03-16 - FZ-16 - Power Generation Building - Generator Room 2</t>
         </is>
@@ -4876,7 +4860,7 @@
       <c r="AT30" s="67" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="53" t="inlineStr">
+      <c r="A31" s="68" t="inlineStr">
         <is>
           <t>PS5-03-17 - FZ-17 - Power Generation Building - Generator Room 3</t>
         </is>
@@ -4994,7 +4978,7 @@
       <c r="AT31" s="67" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="53" t="inlineStr">
+      <c r="A32" s="68" t="inlineStr">
         <is>
           <t>PS5-03-18 - FZ-18 - Power Generation Building - Generator Room 4</t>
         </is>
@@ -5112,7 +5096,7 @@
       <c r="AT32" s="67" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="53" t="inlineStr">
+      <c r="A33" s="68" t="inlineStr">
         <is>
           <t>PS5-03-19 - FZ-19 - Power Generation Building - Battery Room</t>
         </is>
@@ -5234,7 +5218,7 @@
       <c r="AT33" s="67" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="68" t="inlineStr">
+      <c r="A34" s="53" t="inlineStr">
         <is>
           <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
         </is>
@@ -5356,7 +5340,7 @@
       <c r="AT34" s="67" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="53" t="inlineStr">
+      <c r="A35" s="68" t="inlineStr">
         <is>
           <t>PS5-03-21 - FZ-21 - Power Generation Building - Air Handling Unit</t>
         </is>
@@ -5474,7 +5458,7 @@
       <c r="AT35" s="67" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="53" t="inlineStr">
+      <c r="A36" s="68" t="inlineStr">
         <is>
           <t>PS5-03-22 - FZ-G1 - Guard House</t>
         </is>
@@ -5594,7 +5578,7 @@
       <c r="AT36" s="67" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="53" t="inlineStr">
+      <c r="A37" s="68" t="inlineStr">
         <is>
           <t>PS5-03-23 - FZ-E1 to E3 - EITS Building</t>
         </is>
@@ -5678,7 +5662,7 @@
       <c r="AT37" s="67" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="53" t="inlineStr">
+      <c r="A38" s="68" t="inlineStr">
         <is>
           <t>PS5-03-24 - FZ - Office and Facilities Building</t>
         </is>
@@ -5796,7 +5780,7 @@
       <c r="AT38" s="67" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="53" t="inlineStr">
+      <c r="A39" s="68" t="inlineStr">
         <is>
           <t>PS5-03-25 - FZ - Workshop &amp; Warehouse</t>
         </is>
@@ -5914,7 +5898,7 @@
       <c r="AT39" s="67" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="53" t="inlineStr">
+      <c r="A40" s="68" t="inlineStr">
         <is>
           <t>PS5-04-01 - Office Building PCS System</t>
         </is>
@@ -5998,7 +5982,7 @@
       <c r="AT40" s="67" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="53" t="inlineStr">
+      <c r="A41" s="68" t="inlineStr">
         <is>
           <t>PS5-04-02 - Office Building SIS/FGS System</t>
         </is>
@@ -6116,7 +6100,7 @@
       <c r="AT41" s="67" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="53" t="inlineStr">
+      <c r="A42" s="68" t="inlineStr">
         <is>
           <t>PS5-04-03 - 33kV ICSS System</t>
         </is>
@@ -6200,7 +6184,7 @@
       <c r="AT42" s="67" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="53" t="inlineStr">
+      <c r="A43" s="68" t="inlineStr">
         <is>
           <t>PS5-04-04 - 33kV PCS System</t>
         </is>
@@ -6284,7 +6268,7 @@
       <c r="AT43" s="67" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="53" t="inlineStr">
+      <c r="A44" s="68" t="inlineStr">
         <is>
           <t>PS5-04-05 - 33kV SIS/FGS System</t>
         </is>
@@ -6614,7 +6598,7 @@
       <c r="AT46" s="67" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="53" t="inlineStr">
+      <c r="A47" s="68" t="inlineStr">
         <is>
           <t>PS5-06-01 - AC UPS - EITS Building</t>
         </is>
@@ -6698,7 +6682,7 @@
       <c r="AT47" s="67" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="68" t="inlineStr">
+      <c r="A48" s="53" t="inlineStr">
         <is>
           <t>PS5-06-02 - AC UPS - Power Generator Building</t>
         </is>
@@ -6824,7 +6808,7 @@
       <c r="AT48" s="67" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="53" t="inlineStr">
+      <c r="A49" s="68" t="inlineStr">
         <is>
           <t>PS5-06-03 - AC UPS - Office &amp; Facilities Building</t>
         </is>
@@ -6942,7 +6926,7 @@
       <c r="AT49" s="67" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="53" t="inlineStr">
+      <c r="A50" s="68" t="inlineStr">
         <is>
           <t>PS5-06-04 - AC UPS - Guard House</t>
         </is>
@@ -7060,7 +7044,7 @@
       <c r="AT50" s="67" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="53" t="inlineStr">
+      <c r="A51" s="68" t="inlineStr">
         <is>
           <t>PS5-06-05 - AC UPS - Workshop &amp; Warehouse</t>
         </is>
@@ -7178,7 +7162,7 @@
       <c r="AT51" s="67" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="53" t="inlineStr">
+      <c r="A52" s="68" t="inlineStr">
         <is>
           <t>PS5-08-01 - PAGA</t>
         </is>
@@ -7296,7 +7280,7 @@
       <c r="AT52" s="67" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="53" t="inlineStr">
+      <c r="A53" s="68" t="inlineStr">
         <is>
           <t>PS5-08-03 - Telephone</t>
         </is>
@@ -7414,7 +7398,7 @@
       <c r="AT53" s="67" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="53" t="inlineStr">
+      <c r="A54" s="68" t="inlineStr">
         <is>
           <t>PS5-08-04 - Hotline</t>
         </is>
@@ -7498,7 +7482,7 @@
       <c r="AT54" s="67" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="53" t="inlineStr">
+      <c r="A55" s="68" t="inlineStr">
         <is>
           <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
         </is>
@@ -7582,7 +7566,7 @@
       <c r="AT55" s="67" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="53" t="inlineStr">
+      <c r="A56" s="68" t="inlineStr">
         <is>
           <t>PS5-08-11 - Corporate LAN  (SIE)</t>
         </is>
@@ -7700,7 +7684,7 @@
       <c r="AT56" s="67" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="53" t="inlineStr">
+      <c r="A57" s="68" t="inlineStr">
         <is>
           <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
         </is>
@@ -7818,7 +7802,7 @@
       <c r="AT57" s="67" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="53" t="inlineStr">
+      <c r="A58" s="68" t="inlineStr">
         <is>
           <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
         </is>
@@ -7936,7 +7920,7 @@
       <c r="AT58" s="67" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="53" t="inlineStr">
+      <c r="A59" s="68" t="inlineStr">
         <is>
           <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
         </is>
@@ -8054,7 +8038,7 @@
       <c r="AT59" s="67" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="53" t="inlineStr">
+      <c r="A60" s="68" t="inlineStr">
         <is>
           <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
         </is>
@@ -8172,7 +8156,7 @@
       <c r="AT60" s="67" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="53" t="inlineStr">
+      <c r="A61" s="68" t="inlineStr">
         <is>
           <t>PS5-08-23 - VHF Trunk Radio System</t>
         </is>
@@ -8290,7 +8274,7 @@
       <c r="AT61" s="67" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="53" t="inlineStr">
+      <c r="A62" s="68" t="inlineStr">
         <is>
           <t>PS5-08-34 - Satphone</t>
         </is>
@@ -8408,7 +8392,7 @@
       <c r="AT62" s="67" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="53" t="inlineStr">
+      <c r="A63" s="68" t="inlineStr">
         <is>
           <t>PS5-08-35 - Optical Transport Network</t>
         </is>
@@ -8492,7 +8476,7 @@
       <c r="AT63" s="67" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="53" t="inlineStr">
+      <c r="A64" s="68" t="inlineStr">
         <is>
           <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
         </is>
@@ -8610,7 +8594,7 @@
       <c r="AT64" s="67" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="53" t="inlineStr">
+      <c r="A65" s="68" t="inlineStr">
         <is>
           <t>PS5-08-51 - Entertainment</t>
         </is>
@@ -8728,7 +8712,7 @@
       <c r="AT65" s="67" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="53" t="inlineStr">
+      <c r="A66" s="68" t="inlineStr">
         <is>
           <t>PS5-08-52 - Process &amp; Security CCTV</t>
         </is>
@@ -8846,7 +8830,7 @@
       <c r="AT66" s="67" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="53" t="inlineStr">
+      <c r="A67" s="68" t="inlineStr">
         <is>
           <t>PS5-08-55 - Videoconference</t>
         </is>
@@ -8930,7 +8914,7 @@
       <c r="AT67" s="67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="53" t="inlineStr">
+      <c r="A68" s="68" t="inlineStr">
         <is>
           <t>PS5-08-61 - Meteocean</t>
         </is>
@@ -9048,7 +9032,7 @@
       <c r="AT68" s="67" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="53" t="inlineStr">
+      <c r="A69" s="68" t="inlineStr">
         <is>
           <t>PS5-08-71 - Structured Cabling (CAT6)</t>
         </is>
@@ -9166,7 +9150,7 @@
       <c r="AT69" s="67" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="53" t="inlineStr">
+      <c r="A70" s="68" t="inlineStr">
         <is>
           <t>PS5-08-72 - Structured Cabling (FO)</t>
         </is>
@@ -9284,7 +9268,7 @@
       <c r="AT70" s="67" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="53" t="inlineStr">
+      <c r="A71" s="68" t="inlineStr">
         <is>
           <t>PS5-08-81 - Guard tour</t>
         </is>
@@ -9368,7 +9352,7 @@
       <c r="AT71" s="67" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="53" t="inlineStr">
+      <c r="A72" s="68" t="inlineStr">
         <is>
           <t>PS5-08-82 - Key Management</t>
         </is>
@@ -9452,7 +9436,7 @@
       <c r="AT72" s="67" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="53" t="inlineStr">
+      <c r="A73" s="68" t="inlineStr">
         <is>
           <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
         </is>
@@ -9570,7 +9554,7 @@
       <c r="AT73" s="67" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="53" t="inlineStr">
+      <c r="A74" s="68" t="inlineStr">
         <is>
           <t>PS5-08-85 - Access Control, POB &amp; e-Mustering</t>
         </is>
@@ -9688,7 +9672,7 @@
       <c r="AT74" s="67" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="53" t="inlineStr">
+      <c r="A75" s="68" t="inlineStr">
         <is>
           <t>PS5-08-86 - Integrated Security Management System</t>
         </is>
@@ -9772,7 +9756,7 @@
       <c r="AT75" s="67" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="53" t="inlineStr">
+      <c r="A76" s="68" t="inlineStr">
         <is>
           <t>PS5-08-92 - Telecom Mast</t>
         </is>
@@ -9856,7 +9840,7 @@
       <c r="AT76" s="67" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="53" t="inlineStr">
+      <c r="A77" s="68" t="inlineStr">
         <is>
           <t>PS5-08-93 - Telecom Monitoring System</t>
         </is>
@@ -9974,7 +9958,7 @@
       <c r="AT77" s="67" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="53" t="inlineStr">
+      <c r="A78" s="68" t="inlineStr">
         <is>
           <t>PS5-09-01 - HVAC for Office and Facilities building</t>
         </is>
@@ -10092,7 +10076,7 @@
       <c r="AT78" s="67" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="53" t="inlineStr">
+      <c r="A79" s="68" t="inlineStr">
         <is>
           <t>PS5-09-02 - HVAC for Guard House</t>
         </is>
@@ -10210,7 +10194,7 @@
       <c r="AT79" s="67" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="53" t="inlineStr">
+      <c r="A80" s="68" t="inlineStr">
         <is>
           <t>PS5-09-03 - HVAC for Generator Building</t>
         </is>
@@ -10332,7 +10316,7 @@
       <c r="AT80" s="67" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="53" t="inlineStr">
+      <c r="A81" s="68" t="inlineStr">
         <is>
           <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
         </is>
@@ -10450,7 +10434,7 @@
       <c r="AT81" s="67" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="68" t="inlineStr">
+      <c r="A82" s="53" t="inlineStr">
         <is>
           <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
@@ -10560,7 +10544,7 @@
       <c r="AT82" s="67" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="53" t="inlineStr">
+      <c r="A83" s="68" t="inlineStr">
         <is>
           <t>PS5-0H-01 - HIPPS</t>
         </is>
@@ -10644,7 +10628,7 @@
       <c r="AT83" s="67" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="53" t="inlineStr">
+      <c r="A84" s="68" t="inlineStr">
         <is>
           <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
         </is>
@@ -10762,7 +10746,7 @@
       <c r="AT84" s="67" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="53" t="inlineStr">
+      <c r="A85" s="68" t="inlineStr">
         <is>
           <t>PS5-25-02 - Crude Oil Export Pump A</t>
         </is>
@@ -10880,7 +10864,7 @@
       <c r="AT85" s="67" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="53" t="inlineStr">
+      <c r="A86" s="68" t="inlineStr">
         <is>
           <t>PS5-25-03 - Crude Oil Export Pump B</t>
         </is>
@@ -10998,7 +10982,7 @@
       <c r="AT86" s="67" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="53" t="inlineStr">
+      <c r="A87" s="68" t="inlineStr">
         <is>
           <t>PS5-25-04 - Crude Oil Export Pump C</t>
         </is>
@@ -11116,7 +11100,7 @@
       <c r="AT87" s="67" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="53" t="inlineStr">
+      <c r="A88" s="68" t="inlineStr">
         <is>
           <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
         </is>
@@ -11234,7 +11218,7 @@
       <c r="AT88" s="67" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="53" t="inlineStr">
+      <c r="A89" s="68" t="inlineStr">
         <is>
           <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
         </is>
@@ -11352,7 +11336,7 @@
       <c r="AT89" s="67" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="53" t="inlineStr">
+      <c r="A90" s="68" t="inlineStr">
         <is>
           <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
         </is>
@@ -11470,7 +11454,7 @@
       <c r="AT90" s="67" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="53" t="inlineStr">
+      <c r="A91" s="68" t="inlineStr">
         <is>
           <t>PS5-28-01 - Closed Drain Header 1</t>
         </is>
@@ -11588,7 +11572,7 @@
       <c r="AT91" s="67" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="68" t="inlineStr">
+      <c r="A92" s="53" t="inlineStr">
         <is>
           <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
@@ -11710,7 +11694,7 @@
       <c r="AT92" s="67" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="53" t="inlineStr">
+      <c r="A93" s="68" t="inlineStr">
         <is>
           <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
         </is>
@@ -11828,7 +11812,7 @@
       <c r="AT93" s="67" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="53" t="inlineStr">
+      <c r="A94" s="68" t="inlineStr">
         <is>
           <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
         </is>
@@ -11954,7 +11938,7 @@
       <c r="AT94" s="67" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="68" t="inlineStr">
+      <c r="A95" s="53" t="inlineStr">
         <is>
           <t>PS5-28-05 - HP Relief Header</t>
         </is>
@@ -12080,7 +12064,7 @@
       <c r="AT95" s="67" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="53" t="inlineStr">
+      <c r="A96" s="68" t="inlineStr">
         <is>
           <t>PS5-28-06 - Relief Drum and Pump</t>
         </is>
@@ -12202,7 +12186,7 @@
       <c r="AT96" s="67" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="53" t="inlineStr">
+      <c r="A97" s="68" t="inlineStr">
         <is>
           <t>PS5-28-07 - Open Drains (OD2)</t>
         </is>
@@ -12320,7 +12304,7 @@
       <c r="AT97" s="67" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="53" t="inlineStr">
+      <c r="A98" s="68" t="inlineStr">
         <is>
           <t>PS5-28-08 - Open Drain Sump and Pumps</t>
         </is>
@@ -12438,7 +12422,7 @@
       <c r="AT98" s="67" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="53" t="inlineStr">
+      <c r="A99" s="68" t="inlineStr">
         <is>
           <t>PS5-28-09 - Observation Basin</t>
         </is>
@@ -12556,7 +12540,7 @@
       <c r="AT99" s="67" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="53" t="inlineStr">
+      <c r="A100" s="68" t="inlineStr">
         <is>
           <t>PS5-28-10 - Oil Skimmer Package</t>
         </is>
@@ -12674,7 +12658,7 @@
       <c r="AT100" s="67" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="53" t="inlineStr">
+      <c r="A101" s="68" t="inlineStr">
         <is>
           <t>PS5-28-11 - Open Drain Interceptor</t>
         </is>
@@ -12792,7 +12776,7 @@
       <c r="AT101" s="67" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="53" t="inlineStr">
+      <c r="A102" s="68" t="inlineStr">
         <is>
           <t>PS5-28-12 - Open Drains (OD3)</t>
         </is>
@@ -12910,7 +12894,7 @@
       <c r="AT102" s="67" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="53" t="inlineStr">
+      <c r="A103" s="68" t="inlineStr">
         <is>
           <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
         </is>
@@ -13028,7 +13012,7 @@
       <c r="AT103" s="67" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="53" t="inlineStr">
+      <c r="A104" s="68" t="inlineStr">
         <is>
           <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
         </is>
@@ -13146,7 +13130,7 @@
       <c r="AT104" s="67" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="53" t="inlineStr">
+      <c r="A105" s="68" t="inlineStr">
         <is>
           <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
         </is>
@@ -13264,7 +13248,7 @@
       <c r="AT105" s="67" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="53" t="inlineStr">
+      <c r="A106" s="68" t="inlineStr">
         <is>
           <t>PS5-28-16 - LP Relief Header</t>
         </is>
@@ -13382,7 +13366,7 @@
       <c r="AT106" s="67" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="53" t="inlineStr">
+      <c r="A107" s="68" t="inlineStr">
         <is>
           <t>PS5-28-17 - Reinjection Pump</t>
         </is>
@@ -13500,7 +13484,7 @@
       <c r="AT107" s="67" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="53" t="inlineStr">
+      <c r="A108" s="68" t="inlineStr">
         <is>
           <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
         </is>
@@ -13618,7 +13602,7 @@
       <c r="AT108" s="67" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="53" t="inlineStr">
+      <c r="A109" s="68" t="inlineStr">
         <is>
           <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
         </is>
@@ -13736,7 +13720,7 @@
       <c r="AT109" s="67" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="53" t="inlineStr">
+      <c r="A110" s="68" t="inlineStr">
         <is>
           <t>PS5-50-03 - Water Pre-Treatment Package</t>
         </is>
@@ -13980,7 +13964,7 @@
       <c r="AT111" s="67" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="53" t="inlineStr">
+      <c r="A112" s="68" t="inlineStr">
         <is>
           <t>PS5-53-02 - Water Distribution Pump A/B</t>
         </is>
@@ -14098,7 +14082,7 @@
       <c r="AT112" s="67" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="53" t="inlineStr">
+      <c r="A113" s="68" t="inlineStr">
         <is>
           <t>PS5-53-03 - Water Softener Package</t>
         </is>
@@ -14216,7 +14200,7 @@
       <c r="AT113" s="67" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="53" t="inlineStr">
+      <c r="A114" s="68" t="inlineStr">
         <is>
           <t>PS5-53-04 - Water Treatment Purification Package</t>
         </is>
@@ -14334,7 +14318,7 @@
       <c r="AT114" s="67" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="53" t="inlineStr">
+      <c r="A115" s="68" t="inlineStr">
         <is>
           <t>PS5-53-05 - Water Distribution Header</t>
         </is>
@@ -14452,7 +14436,7 @@
       <c r="AT115" s="67" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="53" t="inlineStr">
+      <c r="A116" s="68" t="inlineStr">
         <is>
           <t>PS5-53-06 - Water Distribution Consumers</t>
         </is>
@@ -14574,7 +14558,7 @@
       <c r="AT116" s="67" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="68" t="inlineStr">
+      <c r="A117" s="53" t="inlineStr">
         <is>
           <t>PS5-60-01 - Power Generation Package A</t>
         </is>
@@ -14700,7 +14684,7 @@
       <c r="AT117" s="67" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="68" t="inlineStr">
+      <c r="A118" s="53" t="inlineStr">
         <is>
           <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
@@ -14826,7 +14810,7 @@
       <c r="AT118" s="67" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="53" t="inlineStr">
+      <c r="A119" s="68" t="inlineStr">
         <is>
           <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -14952,7 +14936,7 @@
       <c r="AT119" s="67" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="68" t="inlineStr">
+      <c r="A120" s="53" t="inlineStr">
         <is>
           <t>PS5-60-04 - Power Generation Package B</t>
         </is>
@@ -15078,7 +15062,7 @@
       <c r="AT120" s="67" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="53" t="inlineStr">
+      <c r="A121" s="68" t="inlineStr">
         <is>
           <t>PS5-60-05 - Power Gen Package B (UCP)</t>
         </is>
@@ -15196,7 +15180,7 @@
       <c r="AT121" s="67" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="53" t="inlineStr">
+      <c r="A122" s="68" t="inlineStr">
         <is>
           <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -15314,7 +15298,7 @@
       <c r="AT122" s="67" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="53" t="inlineStr">
+      <c r="A123" s="68" t="inlineStr">
         <is>
           <t>PS5-60-07 - Power Generation Package C</t>
         </is>
@@ -15442,7 +15426,7 @@
       <c r="AT123" s="67" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="53" t="inlineStr">
+      <c r="A124" s="68" t="inlineStr">
         <is>
           <t>PS5-60-08 - Power Gen Package C (UCP)</t>
         </is>
@@ -15560,7 +15544,7 @@
       <c r="AT124" s="67" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="53" t="inlineStr">
+      <c r="A125" s="68" t="inlineStr">
         <is>
           <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -15678,7 +15662,7 @@
       <c r="AT125" s="67" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="53" t="inlineStr">
+      <c r="A126" s="68" t="inlineStr">
         <is>
           <t>PS5-60-10 - Power Generation Package D</t>
         </is>
@@ -15804,7 +15788,7 @@
       <c r="AT126" s="67" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="53" t="inlineStr">
+      <c r="A127" s="68" t="inlineStr">
         <is>
           <t>PS5-60-11 - Power Gen Package D (UCP)</t>
         </is>
@@ -15922,7 +15906,7 @@
       <c r="AT127" s="67" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="53" t="inlineStr">
+      <c r="A128" s="68" t="inlineStr">
         <is>
           <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -16040,7 +16024,7 @@
       <c r="AT128" s="67" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="53" t="inlineStr">
+      <c r="A129" s="68" t="inlineStr">
         <is>
           <t>PS5-60-13 - Power Generation Package E</t>
         </is>
@@ -16166,7 +16150,7 @@
       <c r="AT129" s="67" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="53" t="inlineStr">
+      <c r="A130" s="68" t="inlineStr">
         <is>
           <t>PS5-60-14 - Power Gen Package E (UCP)</t>
         </is>
@@ -16284,7 +16268,7 @@
       <c r="AT130" s="67" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="53" t="inlineStr">
+      <c r="A131" s="68" t="inlineStr">
         <is>
           <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -16402,7 +16386,7 @@
       <c r="AT131" s="67" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="53" t="inlineStr">
+      <c r="A132" s="68" t="inlineStr">
         <is>
           <t>PS5-60-16 - Power Generation Package F</t>
         </is>
@@ -16524,7 +16508,7 @@
       <c r="AT132" s="67" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="53" t="inlineStr">
+      <c r="A133" s="68" t="inlineStr">
         <is>
           <t>PS5-60-17 - Power Gen Package F (UCP)</t>
         </is>
@@ -16634,7 +16618,7 @@
       <c r="AT133" s="67" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="53" t="inlineStr">
+      <c r="A134" s="68" t="inlineStr">
         <is>
           <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -16748,7 +16732,7 @@
       <c r="AT134" s="67" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="53" t="inlineStr">
+      <c r="A135" s="68" t="inlineStr">
         <is>
           <t>PS5-60-19 - Power Generation Package G</t>
         </is>
@@ -16866,7 +16850,7 @@
       <c r="AT135" s="67" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="53" t="inlineStr">
+      <c r="A136" s="68" t="inlineStr">
         <is>
           <t>PS5-60-20 - Power Gen Package G (UCP)</t>
         </is>
@@ -16980,7 +16964,7 @@
       <c r="AT136" s="67" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="53" t="inlineStr">
+      <c r="A137" s="68" t="inlineStr">
         <is>
           <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -17094,7 +17078,7 @@
       <c r="AT137" s="67" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="53" t="inlineStr">
+      <c r="A138" s="68" t="inlineStr">
         <is>
           <t>PS5-60-22 - Power Gen Master UCP</t>
         </is>
@@ -17222,7 +17206,7 @@
       <c r="AT138" s="67" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="68" t="inlineStr">
+      <c r="A139" s="53" t="inlineStr">
         <is>
           <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
@@ -17344,7 +17328,7 @@
       <c r="AT139" s="67" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="53" t="inlineStr">
+      <c r="A140" s="68" t="inlineStr">
         <is>
           <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
         </is>
@@ -17470,7 +17454,7 @@
       <c r="AT140" s="67" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="53" t="inlineStr">
+      <c r="A141" s="68" t="inlineStr">
         <is>
           <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
         </is>
@@ -17596,7 +17580,7 @@
       <c r="AT141" s="67" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="68" t="inlineStr">
+      <c r="A142" s="53" t="inlineStr">
         <is>
           <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
@@ -17722,7 +17706,7 @@
       <c r="AT142" s="67" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="68" t="inlineStr">
+      <c r="A143" s="53" t="inlineStr">
         <is>
           <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
@@ -17974,7 +17958,7 @@
       <c r="AT144" s="67" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="68" t="inlineStr">
+      <c r="A145" s="53" t="inlineStr">
         <is>
           <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
@@ -18100,7 +18084,7 @@
       <c r="AT145" s="67" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="68" t="inlineStr">
+      <c r="A146" s="53" t="inlineStr">
         <is>
           <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
@@ -18226,7 +18210,7 @@
       <c r="AT146" s="67" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="68" t="inlineStr">
+      <c r="A147" s="53" t="inlineStr">
         <is>
           <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
@@ -18352,7 +18336,7 @@
       <c r="AT147" s="67" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="68" t="inlineStr">
+      <c r="A148" s="53" t="inlineStr">
         <is>
           <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
@@ -18478,7 +18462,7 @@
       <c r="AT148" s="67" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="68" t="inlineStr">
+      <c r="A149" s="53" t="inlineStr">
         <is>
           <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
@@ -18604,7 +18588,7 @@
       <c r="AT149" s="67" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="68" t="inlineStr">
+      <c r="A150" s="53" t="inlineStr">
         <is>
           <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
@@ -18852,7 +18836,7 @@
       <c r="AT151" s="67" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="68" t="inlineStr">
+      <c r="A152" s="53" t="inlineStr">
         <is>
           <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
@@ -18974,7 +18958,7 @@
       <c r="AT152" s="67" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="68" t="inlineStr">
+      <c r="A153" s="53" t="inlineStr">
         <is>
           <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
@@ -19100,7 +19084,7 @@
       <c r="AT153" s="67" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="68" t="inlineStr">
+      <c r="A154" s="53" t="inlineStr">
         <is>
           <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
@@ -19226,7 +19210,7 @@
       <c r="AT154" s="67" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="68" t="inlineStr">
+      <c r="A155" s="53" t="inlineStr">
         <is>
           <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
@@ -19352,7 +19336,7 @@
       <c r="AT155" s="67" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="68" t="inlineStr">
+      <c r="A156" s="53" t="inlineStr">
         <is>
           <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
@@ -19478,7 +19462,7 @@
       <c r="AT156" s="67" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="53" t="inlineStr">
+      <c r="A157" s="68" t="inlineStr">
         <is>
           <t>PS5-60-41 - Injector Tip Cooling Module G</t>
         </is>
@@ -19722,7 +19706,7 @@
       <c r="AT158" s="67" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="68" t="inlineStr">
+      <c r="A159" s="53" t="inlineStr">
         <is>
           <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
@@ -19844,7 +19828,7 @@
       <c r="AT159" s="67" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="68" t="inlineStr">
+      <c r="A160" s="53" t="inlineStr">
         <is>
           <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
@@ -19970,7 +19954,7 @@
       <c r="AT160" s="67" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="68" t="inlineStr">
+      <c r="A161" s="53" t="inlineStr">
         <is>
           <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
@@ -20096,7 +20080,7 @@
       <c r="AT161" s="67" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="68" t="inlineStr">
+      <c r="A162" s="53" t="inlineStr">
         <is>
           <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
@@ -20218,7 +20202,7 @@
       <c r="AT162" s="67" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="68" t="inlineStr">
+      <c r="A163" s="53" t="inlineStr">
         <is>
           <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
@@ -20344,7 +20328,7 @@
       <c r="AT163" s="67" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="53" t="inlineStr">
+      <c r="A164" s="68" t="inlineStr">
         <is>
           <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
         </is>
@@ -20462,7 +20446,7 @@
       <c r="AT164" s="67" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="53" t="inlineStr">
+      <c r="A165" s="68" t="inlineStr">
         <is>
           <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
         </is>
@@ -20584,7 +20568,7 @@
       <c r="AT165" s="67" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="53" t="inlineStr">
+      <c r="A166" s="68" t="inlineStr">
         <is>
           <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
         </is>
@@ -20702,7 +20686,7 @@
       <c r="AT166" s="67" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="53" t="inlineStr">
+      <c r="A167" s="68" t="inlineStr">
         <is>
           <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
         </is>
@@ -20820,7 +20804,7 @@
       <c r="AT167" s="67" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="53" t="inlineStr">
+      <c r="A168" s="68" t="inlineStr">
         <is>
           <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
         </is>
@@ -20938,7 +20922,7 @@
       <c r="AT168" s="67" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="53" t="inlineStr">
+      <c r="A169" s="68" t="inlineStr">
         <is>
           <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
         </is>
@@ -21048,7 +21032,7 @@
       <c r="AT169" s="67" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="53" t="inlineStr">
+      <c r="A170" s="68" t="inlineStr">
         <is>
           <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
         </is>
@@ -21158,7 +21142,7 @@
       <c r="AT170" s="67" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="53" t="inlineStr">
+      <c r="A171" s="68" t="inlineStr">
         <is>
           <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
         </is>
@@ -21268,7 +21252,7 @@
       <c r="AT171" s="67" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="68" t="inlineStr">
+      <c r="A172" s="53" t="inlineStr">
         <is>
           <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
@@ -21386,7 +21370,7 @@
       <c r="AT172" s="67" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="53" t="inlineStr">
+      <c r="A173" s="68" t="inlineStr">
         <is>
           <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
         </is>
@@ -21504,7 +21488,7 @@
       <c r="AT173" s="67" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="68" t="inlineStr">
+      <c r="A174" s="53" t="inlineStr">
         <is>
           <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
@@ -21622,7 +21606,7 @@
       <c r="AT174" s="67" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="53" t="inlineStr">
+      <c r="A175" s="68" t="inlineStr">
         <is>
           <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
         </is>
@@ -21740,7 +21724,7 @@
       <c r="AT175" s="67" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="68" t="inlineStr">
+      <c r="A176" s="53" t="inlineStr">
         <is>
           <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
@@ -21858,7 +21842,7 @@
       <c r="AT176" s="67" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="53" t="inlineStr">
+      <c r="A177" s="68" t="inlineStr">
         <is>
           <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
         </is>
@@ -21976,7 +21960,7 @@
       <c r="AT177" s="67" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="68" t="inlineStr">
+      <c r="A178" s="53" t="inlineStr">
         <is>
           <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
@@ -22094,7 +22078,7 @@
       <c r="AT178" s="67" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="53" t="inlineStr">
+      <c r="A179" s="68" t="inlineStr">
         <is>
           <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
         </is>
@@ -22212,7 +22196,7 @@
       <c r="AT179" s="67" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="53" t="inlineStr">
+      <c r="A180" s="68" t="inlineStr">
         <is>
           <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
         </is>
@@ -22330,7 +22314,7 @@
       <c r="AT180" s="67" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="53" t="inlineStr">
+      <c r="A181" s="68" t="inlineStr">
         <is>
           <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
         </is>
@@ -22444,7 +22428,7 @@
       <c r="AT181" s="67" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="53" t="inlineStr">
+      <c r="A182" s="68" t="inlineStr">
         <is>
           <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
         </is>
@@ -22562,7 +22546,7 @@
       <c r="AT182" s="67" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="53" t="inlineStr">
+      <c r="A183" s="68" t="inlineStr">
         <is>
           <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
         </is>
@@ -22676,7 +22660,7 @@
       <c r="AT183" s="67" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="53" t="inlineStr">
+      <c r="A184" s="68" t="inlineStr">
         <is>
           <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
         </is>
@@ -22794,7 +22778,7 @@
       <c r="AT184" s="67" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="53" t="inlineStr">
+      <c r="A185" s="68" t="inlineStr">
         <is>
           <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
         </is>
@@ -22908,7 +22892,7 @@
       <c r="AT185" s="67" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="68" t="inlineStr">
+      <c r="A186" s="53" t="inlineStr">
         <is>
           <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
@@ -23034,7 +23018,7 @@
       <c r="AT186" s="67" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="68" t="inlineStr">
+      <c r="A187" s="53" t="inlineStr">
         <is>
           <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
@@ -23160,7 +23144,7 @@
       <c r="AT187" s="67" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="68" t="inlineStr">
+      <c r="A188" s="53" t="inlineStr">
         <is>
           <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
@@ -23286,7 +23270,7 @@
       <c r="AT188" s="67" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="68" t="inlineStr">
+      <c r="A189" s="53" t="inlineStr">
         <is>
           <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
@@ -23412,7 +23396,7 @@
       <c r="AT189" s="67" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="68" t="inlineStr">
+      <c r="A190" s="53" t="inlineStr">
         <is>
           <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
@@ -23538,7 +23522,7 @@
       <c r="AT190" s="67" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="68" t="inlineStr">
+      <c r="A191" s="53" t="inlineStr">
         <is>
           <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
@@ -23664,7 +23648,7 @@
       <c r="AT191" s="67" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="53" t="inlineStr">
+      <c r="A192" s="68" t="inlineStr">
         <is>
           <t>PS5-60-76 - Engine G Cooling system</t>
         </is>
@@ -23782,7 +23766,7 @@
       <c r="AT192" s="67" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="53" t="inlineStr">
+      <c r="A193" s="68" t="inlineStr">
         <is>
           <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
         </is>
@@ -23910,7 +23894,7 @@
       <c r="AT193" s="67" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="53" t="inlineStr">
+      <c r="A194" s="68" t="inlineStr">
         <is>
           <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
         </is>
@@ -24028,7 +24012,7 @@
       <c r="AT194" s="67" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="53" t="inlineStr">
+      <c r="A195" s="68" t="inlineStr">
         <is>
           <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
         </is>
@@ -24146,7 +24130,7 @@
       <c r="AT195" s="67" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="53" t="inlineStr">
+      <c r="A196" s="68" t="inlineStr">
         <is>
           <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
         </is>
@@ -24268,7 +24252,7 @@
       <c r="AT196" s="67" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="68" t="inlineStr">
+      <c r="A197" s="53" t="inlineStr">
         <is>
           <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
@@ -24394,7 +24378,7 @@
       <c r="AT197" s="67" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="53" t="inlineStr">
+      <c r="A198" s="68" t="inlineStr">
         <is>
           <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
         </is>
@@ -24516,7 +24500,7 @@
       <c r="AT198" s="67" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="68" t="inlineStr">
+      <c r="A199" s="53" t="inlineStr">
         <is>
           <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
@@ -24642,7 +24626,7 @@
       <c r="AT199" s="67" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="53" t="inlineStr">
+      <c r="A200" s="68" t="inlineStr">
         <is>
           <t>PS5-61-08 - Electrical Control System</t>
         </is>
@@ -24760,7 +24744,7 @@
       <c r="AT200" s="67" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="53" t="inlineStr">
+      <c r="A201" s="68" t="inlineStr">
         <is>
           <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
         </is>
@@ -24882,7 +24866,7 @@
       <c r="AT201" s="67" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="68" t="inlineStr">
+      <c r="A202" s="53" t="inlineStr">
         <is>
           <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
@@ -25008,7 +24992,7 @@
       <c r="AT202" s="67" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="68" t="inlineStr">
+      <c r="A203" s="53" t="inlineStr">
         <is>
           <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
@@ -25134,7 +25118,7 @@
       <c r="AT203" s="67" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="53" t="inlineStr">
+      <c r="A204" s="68" t="inlineStr">
         <is>
           <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
         </is>
@@ -25218,7 +25202,7 @@
       <c r="AT204" s="67" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="53" t="inlineStr">
+      <c r="A205" s="68" t="inlineStr">
         <is>
           <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
         </is>
@@ -25336,7 +25320,7 @@
       <c r="AT205" s="67" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="53" t="inlineStr">
+      <c r="A206" s="68" t="inlineStr">
         <is>
           <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
         </is>
@@ -25454,7 +25438,7 @@
       <c r="AT206" s="67" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="53" t="inlineStr">
+      <c r="A207" s="68" t="inlineStr">
         <is>
           <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
         </is>
@@ -25572,7 +25556,7 @@
       <c r="AT207" s="67" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="53" t="inlineStr">
+      <c r="A208" s="68" t="inlineStr">
         <is>
           <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
         </is>
@@ -25690,7 +25674,7 @@
       <c r="AT208" s="67" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="53" t="inlineStr">
+      <c r="A209" s="68" t="inlineStr">
         <is>
           <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
         </is>
@@ -25808,7 +25792,7 @@
       <c r="AT209" s="67" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="68" t="inlineStr">
+      <c r="A210" s="53" t="inlineStr">
         <is>
           <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
@@ -25934,7 +25918,7 @@
       <c r="AT210" s="67" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="53" t="inlineStr">
+      <c r="A211" s="68" t="inlineStr">
         <is>
           <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
         </is>
@@ -26052,7 +26036,7 @@
       <c r="AT211" s="67" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="53" t="inlineStr">
+      <c r="A212" s="68" t="inlineStr">
         <is>
           <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
         </is>
@@ -26178,7 +26162,7 @@
       <c r="AT212" s="67" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="53" t="inlineStr">
+      <c r="A213" s="68" t="inlineStr">
         <is>
           <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
         </is>
@@ -26300,7 +26284,7 @@
       <c r="AT213" s="67" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="53" t="inlineStr">
+      <c r="A214" s="68" t="inlineStr">
         <is>
           <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
         </is>
@@ -26422,7 +26406,7 @@
       <c r="AT214" s="67" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="53" t="inlineStr">
+      <c r="A215" s="68" t="inlineStr">
         <is>
           <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
         </is>
@@ -26544,7 +26528,7 @@
       <c r="AT215" s="67" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="53" t="inlineStr">
+      <c r="A216" s="68" t="inlineStr">
         <is>
           <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
         </is>
@@ -26670,7 +26654,7 @@
       <c r="AT216" s="67" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="53" t="inlineStr">
+      <c r="A217" s="68" t="inlineStr">
         <is>
           <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
         </is>
@@ -26792,7 +26776,7 @@
       <c r="AT217" s="67" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="53" t="inlineStr">
+      <c r="A218" s="68" t="inlineStr">
         <is>
           <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
         </is>
@@ -26876,7 +26860,7 @@
       <c r="AT218" s="67" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="53" t="inlineStr">
+      <c r="A219" s="68" t="inlineStr">
         <is>
           <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
         </is>
@@ -26960,7 +26944,7 @@
       <c r="AT219" s="67" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="53" t="inlineStr">
+      <c r="A220" s="68" t="inlineStr">
         <is>
           <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
         </is>
@@ -27078,7 +27062,7 @@
       <c r="AT220" s="67" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="53" t="inlineStr">
+      <c r="A221" s="68" t="inlineStr">
         <is>
           <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
         </is>
@@ -27196,7 +27180,7 @@
       <c r="AT221" s="67" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="53" t="inlineStr">
+      <c r="A222" s="68" t="inlineStr">
         <is>
           <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
         </is>
@@ -27314,7 +27298,7 @@
       <c r="AT222" s="67" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="53" t="inlineStr">
+      <c r="A223" s="68" t="inlineStr">
         <is>
           <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
         </is>
@@ -27432,7 +27416,7 @@
       <c r="AT223" s="67" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="53" t="inlineStr">
+      <c r="A224" s="68" t="inlineStr">
         <is>
           <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
         </is>
@@ -27550,7 +27534,7 @@
       <c r="AT224" s="67" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="53" t="inlineStr">
+      <c r="A225" s="68" t="inlineStr">
         <is>
           <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
         </is>
@@ -27668,7 +27652,7 @@
       <c r="AT225" s="67" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="53" t="inlineStr">
+      <c r="A226" s="68" t="inlineStr">
         <is>
           <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
         </is>
@@ -27786,7 +27770,7 @@
       <c r="AT226" s="67" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="53" t="inlineStr">
+      <c r="A227" s="68" t="inlineStr">
         <is>
           <t>PS5-63-01 - Electrical Earthing</t>
         </is>
@@ -27912,7 +27896,7 @@
       <c r="AT227" s="67" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="53" t="inlineStr">
+      <c r="A228" s="68" t="inlineStr">
         <is>
           <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
         </is>
@@ -28030,7 +28014,7 @@
       <c r="AT228" s="67" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="53" t="inlineStr">
+      <c r="A229" s="68" t="inlineStr">
         <is>
           <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
         </is>
@@ -28156,7 +28140,7 @@
       <c r="AT229" s="67" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="68" t="inlineStr">
+      <c r="A230" s="53" t="inlineStr">
         <is>
           <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
@@ -28240,7 +28224,7 @@
       <c r="AT230" s="67" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="53" t="inlineStr">
+      <c r="A231" s="68" t="inlineStr">
         <is>
           <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
         </is>
@@ -28358,7 +28342,7 @@
       <c r="AT231" s="67" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="53" t="inlineStr">
+      <c r="A232" s="68" t="inlineStr">
         <is>
           <t>PS5-63-06 - Electrical Earthing - Guard House</t>
         </is>
@@ -28476,7 +28460,7 @@
       <c r="AT232" s="67" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="53" t="inlineStr">
+      <c r="A233" s="68" t="inlineStr">
         <is>
           <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
         </is>
@@ -28594,7 +28578,7 @@
       <c r="AT233" s="67" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="53" t="inlineStr">
+      <c r="A234" s="68" t="inlineStr">
         <is>
           <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
         </is>
@@ -28716,7 +28700,7 @@
       <c r="AT234" s="67" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="53" t="inlineStr">
+      <c r="A235" s="68" t="inlineStr">
         <is>
           <t>PS5-71-02 - CFO Allocation Metering Package</t>
         </is>
@@ -28834,7 +28818,7 @@
       <c r="AT235" s="67" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="53" t="inlineStr">
+      <c r="A236" s="68" t="inlineStr">
         <is>
           <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
         </is>
@@ -28918,7 +28902,7 @@
       <c r="AT236" s="67" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="53" t="inlineStr">
+      <c r="A237" s="68" t="inlineStr">
         <is>
           <t>PS5-71-04 - CFO Storage Tank</t>
         </is>
@@ -29038,7 +29022,7 @@
       <c r="AT237" s="67" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="53" t="inlineStr">
+      <c r="A238" s="68" t="inlineStr">
         <is>
           <t>PS5-71-05 - CFO Transfer Pump A/B</t>
         </is>
@@ -29156,7 +29140,7 @@
       <c r="AT238" s="67" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="53" t="inlineStr">
+      <c r="A239" s="68" t="inlineStr">
         <is>
           <t>PS5-71-06 - Crude Fuel Separation Module</t>
         </is>
@@ -29298,7 +29282,7 @@
       <c r="AT239" s="67" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="53" t="inlineStr">
+      <c r="A240" s="68" t="inlineStr">
         <is>
           <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
         </is>
@@ -29422,7 +29406,7 @@
       <c r="AT240" s="67" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="53" t="inlineStr">
+      <c r="A241" s="68" t="inlineStr">
         <is>
           <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
         </is>
@@ -29550,7 +29534,7 @@
       <c r="AT241" s="67" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="53" t="inlineStr">
+      <c r="A242" s="68" t="inlineStr">
         <is>
           <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
         </is>
@@ -29668,7 +29652,7 @@
       <c r="AT242" s="67" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="53" t="inlineStr">
+      <c r="A243" s="68" t="inlineStr">
         <is>
           <t>PS5-71-12 - CFO Service Tank</t>
         </is>
@@ -29786,7 +29770,7 @@
       <c r="AT243" s="67" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="53" t="inlineStr">
+      <c r="A244" s="68" t="inlineStr">
         <is>
           <t>PS5-71-13 - CFO Service Pump A/B</t>
         </is>
@@ -29904,7 +29888,7 @@
       <c r="AT244" s="67" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="53" t="inlineStr">
+      <c r="A245" s="68" t="inlineStr">
         <is>
           <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
@@ -30022,7 +30006,7 @@
       <c r="AT245" s="67" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="53" t="inlineStr">
+      <c r="A246" s="68" t="inlineStr">
         <is>
           <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
         </is>
@@ -30140,7 +30124,7 @@
       <c r="AT246" s="67" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="53" t="inlineStr">
+      <c r="A247" s="68" t="inlineStr">
         <is>
           <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
@@ -30262,7 +30246,7 @@
       <c r="AT247" s="67" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="53" t="inlineStr">
+      <c r="A248" s="68" t="inlineStr">
         <is>
           <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
         </is>
@@ -30388,7 +30372,7 @@
       <c r="AT248" s="67" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="53" t="inlineStr">
+      <c r="A249" s="68" t="inlineStr">
         <is>
           <t>PS5-71-18 - Diesel Separator Module</t>
         </is>
@@ -30518,7 +30502,7 @@
       <c r="AT249" s="67" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="53" t="inlineStr">
+      <c r="A250" s="68" t="inlineStr">
         <is>
           <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
         </is>
@@ -30642,7 +30626,7 @@
       <c r="AT250" s="67" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="53" t="inlineStr">
+      <c r="A251" s="68" t="inlineStr">
         <is>
           <t>PS5-71-20 - Diesel Fuel Day Tank</t>
         </is>
@@ -30768,7 +30752,7 @@
       <c r="AT251" s="67" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="53" t="inlineStr">
+      <c r="A252" s="68" t="inlineStr">
         <is>
           <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
         </is>
@@ -30896,7 +30880,7 @@
       <c r="AT252" s="67" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="68" t="inlineStr">
+      <c r="A253" s="53" t="inlineStr">
         <is>
           <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
@@ -31022,7 +31006,7 @@
       <c r="AT253" s="67" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="53" t="inlineStr">
+      <c r="A254" s="68" t="inlineStr">
         <is>
           <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
         </is>
@@ -31148,7 +31132,7 @@
       <c r="AT254" s="67" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="53" t="inlineStr">
+      <c r="A255" s="68" t="inlineStr">
         <is>
           <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
@@ -31274,7 +31258,7 @@
       <c r="AT255" s="67" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="53" t="inlineStr">
+      <c r="A256" s="68" t="inlineStr">
         <is>
           <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
         </is>
@@ -31400,7 +31384,7 @@
       <c r="AT256" s="67" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="68" t="inlineStr">
+      <c r="A257" s="53" t="inlineStr">
         <is>
           <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
@@ -31526,7 +31510,7 @@
       <c r="AT257" s="67" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="53" t="inlineStr">
+      <c r="A258" s="68" t="inlineStr">
         <is>
           <t>PS5-74-04 - Nitrogen Distribution Header</t>
         </is>
@@ -31644,7 +31628,7 @@
       <c r="AT258" s="67" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="53" t="inlineStr">
+      <c r="A259" s="68" t="inlineStr">
         <is>
           <t>PS5-75-01 - DRA Injection Package</t>
         </is>
@@ -31762,7 +31746,7 @@
       <c r="AT259" s="67" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="53" t="inlineStr">
+      <c r="A260" s="68" t="inlineStr">
         <is>
           <t>PS5-75-02 - Biocide Injection Package</t>
         </is>
@@ -31880,7 +31864,7 @@
       <c r="AT260" s="67" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="53" t="inlineStr">
+      <c r="A261" s="68" t="inlineStr">
         <is>
           <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
         </is>
@@ -32120,7 +32104,7 @@
       <c r="AT262" s="67" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="53" t="inlineStr">
+      <c r="A263" s="68" t="inlineStr">
         <is>
           <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
         </is>
@@ -32238,7 +32222,7 @@
       <c r="AT263" s="67" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="53" t="inlineStr">
+      <c r="A264" s="68" t="inlineStr">
         <is>
           <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
         </is>
@@ -32356,7 +32340,7 @@
       <c r="AT264" s="67" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" s="53" t="inlineStr">
+      <c r="A265" s="68" t="inlineStr">
         <is>
           <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
         </is>
@@ -32474,7 +32458,7 @@
       <c r="AT265" s="67" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" s="53" t="inlineStr">
+      <c r="A266" s="68" t="inlineStr">
         <is>
           <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
         </is>
@@ -32592,7 +32576,7 @@
       <c r="AT266" s="67" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" s="53" t="inlineStr">
+      <c r="A267" s="68" t="inlineStr">
         <is>
           <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
         </is>
@@ -32710,7 +32694,7 @@
       <c r="AT267" s="67" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="53" t="inlineStr">
+      <c r="A268" s="68" t="inlineStr">
         <is>
           <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
         </is>
@@ -32828,7 +32812,7 @@
       <c r="AT268" s="67" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="53" t="inlineStr">
+      <c r="A269" s="68" t="inlineStr">
         <is>
           <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
         </is>
@@ -32946,7 +32930,7 @@
       <c r="AT269" s="67" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="53" t="inlineStr">
+      <c r="A270" s="68" t="inlineStr">
         <is>
           <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
         </is>
@@ -33064,7 +33048,7 @@
       <c r="AT270" s="67" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="53" t="inlineStr">
+      <c r="A271" s="68" t="inlineStr">
         <is>
           <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
         </is>
@@ -33182,7 +33166,7 @@
       <c r="AT271" s="67" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" s="53" t="inlineStr">
+      <c r="A272" s="68" t="inlineStr">
         <is>
           <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
         </is>
@@ -33300,7 +33284,7 @@
       <c r="AT272" s="67" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="53" t="inlineStr">
+      <c r="A273" s="68" t="inlineStr">
         <is>
           <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
         </is>
@@ -33418,7 +33402,7 @@
       <c r="AT273" s="67" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="53" t="inlineStr">
+      <c r="A274" s="68" t="inlineStr">
         <is>
           <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
         </is>
@@ -33536,7 +33520,7 @@
       <c r="AT274" s="67" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" s="53" t="inlineStr">
+      <c r="A275" s="68" t="inlineStr">
         <is>
           <t>PS5-82-01 - Sanitary Sewage Collection</t>
         </is>
@@ -33654,7 +33638,7 @@
       <c r="AT275" s="67" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="53" t="inlineStr">
+      <c r="A276" s="68" t="inlineStr">
         <is>
           <t>PS5-82-02 - Sewage Treatment Plant Package</t>
         </is>
@@ -33772,7 +33756,7 @@
       <c r="AT276" s="67" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" s="53" t="inlineStr">
+      <c r="A277" s="68" t="inlineStr">
         <is>
           <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
         </is>
@@ -33890,7 +33874,7 @@
       <c r="AT277" s="67" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="53" t="inlineStr">
+      <c r="A278" s="68" t="inlineStr">
         <is>
           <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
         </is>
@@ -34008,7 +33992,7 @@
       <c r="AT278" s="67" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="53" t="inlineStr">
+      <c r="A279" s="68" t="inlineStr">
         <is>
           <t>PS5-82-05 - Office and Facilities building</t>
         </is>
@@ -34126,7 +34110,7 @@
       <c r="AT279" s="67" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="53" t="inlineStr">
+      <c r="A280" s="68" t="inlineStr">
         <is>
           <t>PS5-82-06 - Guard House Building</t>
         </is>
@@ -34244,7 +34228,7 @@
       <c r="AT280" s="67" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="53" t="inlineStr">
+      <c r="A281" s="68" t="inlineStr">
         <is>
           <t>PS5-82-07 - Guard Huts</t>
         </is>
@@ -34362,7 +34346,7 @@
       <c r="AT281" s="67" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="68" t="inlineStr">
+      <c r="A282" s="53" t="inlineStr">
         <is>
           <t>PS5-83-01 - EITS Building</t>
         </is>
@@ -34488,7 +34472,7 @@
       <c r="AT282" s="67" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" s="53" t="inlineStr">
+      <c r="A283" s="68" t="inlineStr">
         <is>
           <t>PS5-84-01 - Generator Building</t>
         </is>
@@ -34606,7 +34590,7 @@
       <c r="AT283" s="67" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" s="53" t="inlineStr">
+      <c r="A284" s="68" t="inlineStr">
         <is>
           <t>PS5-84-02 - Workshop &amp; Warehouse</t>
         </is>
@@ -34724,7 +34708,7 @@
       <c r="AT284" s="67" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="68" t="inlineStr">
+      <c r="A285" s="53" t="inlineStr">
         <is>
           <t>PS5-84-03 - Shelters</t>
         </is>
@@ -34846,7 +34830,7 @@
       <c r="AT285" s="67" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="68" t="inlineStr">
+      <c r="A286" s="53" t="inlineStr">
         <is>
           <t>PS5-86-01 - Shelters</t>
         </is>
@@ -34968,7 +34952,7 @@
       <c r="AT286" s="67" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="68" t="inlineStr">
+      <c r="A287" s="53" t="inlineStr">
         <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
@@ -35094,7 +35078,7 @@
       <c r="AT287" s="67" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="53" t="inlineStr">
+      <c r="A288" s="68" t="inlineStr">
         <is>
           <t>PS5-99-01 - Area Completion for Building area</t>
         </is>
@@ -35212,7 +35196,7 @@
       <c r="AT288" s="67" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="53" t="inlineStr">
+      <c r="A289" s="68" t="inlineStr">
         <is>
           <t>PS5-99-02 - Area Completion for Utility area</t>
         </is>
@@ -35330,7 +35314,7 @@
       <c r="AT289" s="67" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="53" t="inlineStr">
+      <c r="A290" s="68" t="inlineStr">
         <is>
           <t>PS5-99-03 - Area Completion for Power Distribution area</t>
         </is>
@@ -35448,7 +35432,7 @@
       <c r="AT290" s="67" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" s="53" t="inlineStr">
+      <c r="A291" s="68" t="inlineStr">
         <is>
           <t>PS5-99-04 - Area Completion for Process area</t>
         </is>
@@ -35566,7 +35550,7 @@
       <c r="AT291" s="67" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" s="53" t="inlineStr">
+      <c r="A292" s="68" t="inlineStr">
         <is>
           <t>PS5-99-05 - Area Completion for CFO area</t>
         </is>
@@ -35684,7 +35668,7 @@
       <c r="AT292" s="67" t="inlineStr"/>
     </row>
     <row r="293">
-      <c r="A293" s="53" t="inlineStr">
+      <c r="A293" s="68" t="inlineStr">
         <is>
           <t>PS5-99-06 - Area Completion for Power Generation area</t>
         </is>

--- a/EXCEL/2 - RFC PROGRESS.xlsx
+++ b/EXCEL/2 - RFC PROGRESS.xlsx
@@ -172,7 +172,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill/>
     </fill>
@@ -309,12 +309,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFfff8e1"/>
         <bgColor rgb="FFfff8e1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
-        <bgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -504,7 +498,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -518,6 +512,9 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -527,10 +524,10 @@
     <xf numFmtId="0" fontId="19" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -542,19 +539,16 @@
     <xf numFmtId="0" fontId="2" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -564,10 +558,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -579,21 +573,21 @@
     <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -683,9 +677,6 @@
     <xf numFmtId="0" fontId="11" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -707,10 +698,10 @@
     <xf numFmtId="0" fontId="7" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -722,13 +713,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -737,7 +722,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -746,28 +731,28 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1209,51 +1194,51 @@
           <t>PS5 COMPLETION PLATFORM  |  2 · RFC PROGRESS</t>
         </is>
       </c>
-      <c r="B1" s="100" t="n"/>
-      <c r="C1" s="100" t="n"/>
-      <c r="D1" s="100" t="n"/>
-      <c r="E1" s="100" t="n"/>
-      <c r="F1" s="100" t="n"/>
-      <c r="G1" s="100" t="n"/>
-      <c r="H1" s="100" t="n"/>
-      <c r="I1" s="100" t="n"/>
-      <c r="J1" s="100" t="n"/>
-      <c r="K1" s="100" t="n"/>
-      <c r="L1" s="100" t="n"/>
-      <c r="M1" s="100" t="n"/>
-      <c r="N1" s="100" t="n"/>
-      <c r="O1" s="100" t="n"/>
-      <c r="P1" s="100" t="n"/>
-      <c r="Q1" s="100" t="n"/>
-      <c r="R1" s="100" t="n"/>
-      <c r="S1" s="100" t="n"/>
-      <c r="T1" s="100" t="n"/>
-      <c r="U1" s="100" t="n"/>
-      <c r="V1" s="100" t="n"/>
-      <c r="W1" s="100" t="n"/>
-      <c r="X1" s="100" t="n"/>
-      <c r="Y1" s="100" t="n"/>
-      <c r="Z1" s="100" t="n"/>
-      <c r="AA1" s="100" t="n"/>
-      <c r="AB1" s="100" t="n"/>
-      <c r="AC1" s="100" t="n"/>
-      <c r="AD1" s="100" t="n"/>
-      <c r="AE1" s="100" t="n"/>
-      <c r="AF1" s="100" t="n"/>
-      <c r="AG1" s="100" t="n"/>
-      <c r="AH1" s="100" t="n"/>
-      <c r="AI1" s="100" t="n"/>
-      <c r="AJ1" s="100" t="n"/>
-      <c r="AK1" s="100" t="n"/>
-      <c r="AL1" s="100" t="n"/>
-      <c r="AM1" s="100" t="n"/>
-      <c r="AN1" s="100" t="n"/>
-      <c r="AO1" s="100" t="n"/>
-      <c r="AP1" s="100" t="n"/>
-      <c r="AQ1" s="100" t="n"/>
-      <c r="AR1" s="100" t="n"/>
-      <c r="AS1" s="100" t="n"/>
-      <c r="AT1" s="101" t="n"/>
+      <c r="B1" s="97" t="n"/>
+      <c r="C1" s="97" t="n"/>
+      <c r="D1" s="97" t="n"/>
+      <c r="E1" s="97" t="n"/>
+      <c r="F1" s="97" t="n"/>
+      <c r="G1" s="97" t="n"/>
+      <c r="H1" s="97" t="n"/>
+      <c r="I1" s="97" t="n"/>
+      <c r="J1" s="97" t="n"/>
+      <c r="K1" s="97" t="n"/>
+      <c r="L1" s="97" t="n"/>
+      <c r="M1" s="97" t="n"/>
+      <c r="N1" s="97" t="n"/>
+      <c r="O1" s="97" t="n"/>
+      <c r="P1" s="97" t="n"/>
+      <c r="Q1" s="97" t="n"/>
+      <c r="R1" s="97" t="n"/>
+      <c r="S1" s="97" t="n"/>
+      <c r="T1" s="97" t="n"/>
+      <c r="U1" s="97" t="n"/>
+      <c r="V1" s="97" t="n"/>
+      <c r="W1" s="97" t="n"/>
+      <c r="X1" s="97" t="n"/>
+      <c r="Y1" s="97" t="n"/>
+      <c r="Z1" s="97" t="n"/>
+      <c r="AA1" s="97" t="n"/>
+      <c r="AB1" s="97" t="n"/>
+      <c r="AC1" s="97" t="n"/>
+      <c r="AD1" s="97" t="n"/>
+      <c r="AE1" s="97" t="n"/>
+      <c r="AF1" s="97" t="n"/>
+      <c r="AG1" s="97" t="n"/>
+      <c r="AH1" s="97" t="n"/>
+      <c r="AI1" s="97" t="n"/>
+      <c r="AJ1" s="97" t="n"/>
+      <c r="AK1" s="97" t="n"/>
+      <c r="AL1" s="97" t="n"/>
+      <c r="AM1" s="97" t="n"/>
+      <c r="AN1" s="97" t="n"/>
+      <c r="AO1" s="97" t="n"/>
+      <c r="AP1" s="97" t="n"/>
+      <c r="AQ1" s="97" t="n"/>
+      <c r="AR1" s="97" t="n"/>
+      <c r="AS1" s="97" t="n"/>
+      <c r="AT1" s="98" t="n"/>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
@@ -1624,10 +1609,8 @@
       <c r="N4" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="O4" s="60" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="O4" s="60" t="n">
+        <v>28</v>
       </c>
       <c r="P4" s="61" t="n">
         <v>0</v>
@@ -1688,11 +1671,11 @@
           <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
         </is>
       </c>
-      <c r="AS4" s="66" t="n"/>
-      <c r="AT4" s="67" t="inlineStr"/>
+      <c r="AS4" s="23" t="n"/>
+      <c r="AT4" s="66" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="68" t="inlineStr">
+      <c r="A5" s="67" t="inlineStr">
         <is>
           <t>PS5-01-02 - Fire Water Pump A</t>
         </is>
@@ -1806,7 +1789,7 @@
       <c r="AP5" s="65" t="inlineStr"/>
       <c r="AQ5" s="65" t="inlineStr">
         <is>
-          <t>EACOP(MR.BENHER TBC)-EXPECTED 19-08-2026</t>
+          <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
         </is>
       </c>
       <c r="AR5" s="23" t="inlineStr">
@@ -1815,10 +1798,10 @@
         </is>
       </c>
       <c r="AS5" s="23" t="n"/>
-      <c r="AT5" s="67" t="inlineStr"/>
+      <c r="AT5" s="66" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="68" t="inlineStr">
+      <c r="A6" s="67" t="inlineStr">
         <is>
           <t>PS5-01-03 - Fire Water Pump B</t>
         </is>
@@ -1937,7 +1920,7 @@
         </is>
       </c>
       <c r="AS6" s="23" t="n"/>
-      <c r="AT6" s="67" t="inlineStr"/>
+      <c r="AT6" s="66" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="53" t="inlineStr">
@@ -2059,10 +2042,10 @@
         </is>
       </c>
       <c r="AS7" s="23" t="n"/>
-      <c r="AT7" s="67" t="inlineStr"/>
+      <c r="AT7" s="66" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="68" t="inlineStr">
+      <c r="A8" s="67" t="inlineStr">
         <is>
           <t>PS5-01-05 - Foam Skid</t>
         </is>
@@ -2185,7 +2168,7 @@
         </is>
       </c>
       <c r="AS8" s="23" t="n"/>
-      <c r="AT8" s="67" t="inlineStr"/>
+      <c r="AT8" s="66" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="53" t="inlineStr">
@@ -2307,10 +2290,10 @@
         </is>
       </c>
       <c r="AS9" s="23" t="n"/>
-      <c r="AT9" s="67" t="inlineStr"/>
+      <c r="AT9" s="66" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="68" t="inlineStr">
+      <c r="A10" s="67" t="inlineStr">
         <is>
           <t>PS5-01-07 - Fire Water Ring Main &amp; Distribution</t>
         </is>
@@ -2342,15 +2325,13 @@
         </is>
       </c>
       <c r="H10" s="24" t="inlineStr"/>
-      <c r="I10" s="69" t="inlineStr">
+      <c r="I10" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
       </c>
-      <c r="J10" s="55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="J10" s="55" t="n">
+        <v>0</v>
       </c>
       <c r="K10" s="56" t="n">
         <v>0</v>
@@ -2427,10 +2408,10 @@
         </is>
       </c>
       <c r="AS10" s="23" t="n"/>
-      <c r="AT10" s="67" t="inlineStr"/>
+      <c r="AT10" s="66" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="68" t="inlineStr">
+      <c r="A11" s="67" t="inlineStr">
         <is>
           <t>PS5-01-08 - PS5 Deluge Valve Skid (PS5-01-UK-6100)</t>
         </is>
@@ -2462,7 +2443,7 @@
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr"/>
-      <c r="I11" s="69" t="inlineStr">
+      <c r="I11" s="68" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
@@ -2545,7 +2526,7 @@
         </is>
       </c>
       <c r="AS11" s="23" t="n"/>
-      <c r="AT11" s="67" t="inlineStr"/>
+      <c r="AT11" s="66" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="53" t="inlineStr">
@@ -2663,7 +2644,7 @@
         </is>
       </c>
       <c r="AS12" s="23" t="n"/>
-      <c r="AT12" s="67" t="inlineStr"/>
+      <c r="AT12" s="66" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="53" t="inlineStr">
@@ -2789,10 +2770,10 @@
         </is>
       </c>
       <c r="AS13" s="23" t="n"/>
-      <c r="AT13" s="67" t="inlineStr"/>
+      <c r="AT13" s="66" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="68" t="inlineStr">
+      <c r="A14" s="67" t="inlineStr">
         <is>
           <t>PS5-01-11 - Inergen for Power Gen Building</t>
         </is>
@@ -2828,7 +2809,7 @@
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr"/>
-      <c r="I14" s="70" t="inlineStr">
+      <c r="I14" s="69" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -2903,10 +2884,10 @@
       <c r="AQ14" s="65" t="inlineStr"/>
       <c r="AR14" s="23" t="inlineStr"/>
       <c r="AS14" s="23" t="n"/>
-      <c r="AT14" s="67" t="inlineStr"/>
+      <c r="AT14" s="66" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="68" t="inlineStr">
+      <c r="A15" s="67" t="inlineStr">
         <is>
           <t>PS5-02-01 - Miscellaneous Safety equipment</t>
         </is>
@@ -2934,7 +2915,7 @@
         </is>
       </c>
       <c r="H15" s="24" t="inlineStr"/>
-      <c r="I15" s="70" t="inlineStr">
+      <c r="I15" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -3017,10 +2998,10 @@
         </is>
       </c>
       <c r="AS15" s="23" t="n"/>
-      <c r="AT15" s="67" t="inlineStr"/>
+      <c r="AT15" s="66" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="68" t="inlineStr">
+      <c r="A16" s="67" t="inlineStr">
         <is>
           <t>PS5-02-02 - Portable Fire Fighting Equipments</t>
         </is>
@@ -3052,7 +3033,7 @@
         </is>
       </c>
       <c r="H16" s="24" t="inlineStr"/>
-      <c r="I16" s="70" t="inlineStr">
+      <c r="I16" s="69" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
@@ -3135,10 +3116,10 @@
         </is>
       </c>
       <c r="AS16" s="23" t="n"/>
-      <c r="AT16" s="67" t="inlineStr"/>
+      <c r="AT16" s="66" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="68" t="inlineStr">
+      <c r="A17" s="67" t="inlineStr">
         <is>
           <t>PS5-03-01 - FZ-01 - Process Area</t>
         </is>
@@ -3261,10 +3242,10 @@
         </is>
       </c>
       <c r="AS17" s="23" t="n"/>
-      <c r="AT17" s="67" t="inlineStr"/>
+      <c r="AT17" s="66" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="68" t="inlineStr">
+      <c r="A18" s="67" t="inlineStr">
         <is>
           <t>PS5-03-03 - FZ-03 - Buildings Area</t>
         </is>
@@ -3296,7 +3277,7 @@
         </is>
       </c>
       <c r="H18" s="24" t="inlineStr"/>
-      <c r="I18" s="70" t="inlineStr">
+      <c r="I18" s="69" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -3379,10 +3360,10 @@
         </is>
       </c>
       <c r="AS18" s="23" t="n"/>
-      <c r="AT18" s="67" t="inlineStr"/>
+      <c r="AT18" s="66" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="68" t="inlineStr">
+      <c r="A19" s="67" t="inlineStr">
         <is>
           <t>PS5-03-04 - FZ-04 - Utilities - Diesel and Firewater Pumps Areas</t>
         </is>
@@ -3501,10 +3482,10 @@
         </is>
       </c>
       <c r="AS19" s="23" t="n"/>
-      <c r="AT19" s="67" t="inlineStr"/>
+      <c r="AT19" s="66" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="68" t="inlineStr">
+      <c r="A20" s="67" t="inlineStr">
         <is>
           <t>PS5-03-06 - FZ-06 - Transformer Area</t>
         </is>
@@ -3627,7 +3608,7 @@
         </is>
       </c>
       <c r="AS20" s="23" t="n"/>
-      <c r="AT20" s="67" t="inlineStr"/>
+      <c r="AT20" s="66" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="53" t="inlineStr">
@@ -3753,10 +3734,10 @@
         </is>
       </c>
       <c r="AS21" s="23" t="n"/>
-      <c r="AT21" s="67" t="inlineStr"/>
+      <c r="AT21" s="66" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="68" t="inlineStr">
+      <c r="A22" s="67" t="inlineStr">
         <is>
           <t>PS5-03-08 - FZ-08 - Utilities - Power Generation Area - External</t>
         </is>
@@ -3871,7 +3852,7 @@
         </is>
       </c>
       <c r="AS22" s="23" t="n"/>
-      <c r="AT22" s="67" t="inlineStr"/>
+      <c r="AT22" s="66" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="53" t="inlineStr">
@@ -3997,7 +3978,7 @@
         </is>
       </c>
       <c r="AS23" s="23" t="n"/>
-      <c r="AT23" s="67" t="inlineStr"/>
+      <c r="AT23" s="66" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="53" t="inlineStr">
@@ -4119,10 +4100,10 @@
       <c r="AQ24" s="65" t="inlineStr"/>
       <c r="AR24" s="23" t="inlineStr"/>
       <c r="AS24" s="23" t="n"/>
-      <c r="AT24" s="67" t="inlineStr"/>
+      <c r="AT24" s="66" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="68" t="inlineStr">
+      <c r="A25" s="67" t="inlineStr">
         <is>
           <t>PS5-03-11 - FZ-11 - Power Generation Building - Engine Bay 3</t>
         </is>
@@ -4241,10 +4222,10 @@
         </is>
       </c>
       <c r="AS25" s="23" t="n"/>
-      <c r="AT25" s="67" t="inlineStr"/>
+      <c r="AT25" s="66" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="68" t="inlineStr">
+      <c r="A26" s="67" t="inlineStr">
         <is>
           <t>PS5-03-12 - FZ-12 - Power Generation Building - Engine Bay 4</t>
         </is>
@@ -4359,7 +4340,7 @@
         </is>
       </c>
       <c r="AS26" s="23" t="n"/>
-      <c r="AT26" s="67" t="inlineStr"/>
+      <c r="AT26" s="66" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="53" t="inlineStr">
@@ -4485,10 +4466,10 @@
         </is>
       </c>
       <c r="AS27" s="23" t="n"/>
-      <c r="AT27" s="67" t="inlineStr"/>
+      <c r="AT27" s="66" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="68" t="inlineStr">
+      <c r="A28" s="67" t="inlineStr">
         <is>
           <t>PS5-03-14 - FZ-14 - Power Generation Building - Switchgear Room</t>
         </is>
@@ -4524,7 +4505,7 @@
         </is>
       </c>
       <c r="H28" s="24" t="inlineStr"/>
-      <c r="I28" s="70" t="inlineStr">
+      <c r="I28" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -4556,7 +4537,7 @@
       <c r="R28" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S28" s="71" t="inlineStr">
+      <c r="S28" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -4613,10 +4594,10 @@
         </is>
       </c>
       <c r="AS28" s="23" t="n"/>
-      <c r="AT28" s="67" t="inlineStr"/>
+      <c r="AT28" s="66" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="68" t="inlineStr">
+      <c r="A29" s="67" t="inlineStr">
         <is>
           <t>PS5-03-15 - FZ-15 - Power Generation Building - Generator Room 1</t>
         </is>
@@ -4652,7 +4633,7 @@
         </is>
       </c>
       <c r="H29" s="24" t="inlineStr"/>
-      <c r="I29" s="70" t="inlineStr">
+      <c r="I29" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4735,10 +4716,10 @@
         </is>
       </c>
       <c r="AS29" s="23" t="n"/>
-      <c r="AT29" s="67" t="inlineStr"/>
+      <c r="AT29" s="66" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="68" t="inlineStr">
+      <c r="A30" s="67" t="inlineStr">
         <is>
           <t>PS5-03-16 - FZ-16 - Power Generation Building - Generator Room 2</t>
         </is>
@@ -4774,7 +4755,7 @@
         </is>
       </c>
       <c r="H30" s="24" t="inlineStr"/>
-      <c r="I30" s="70" t="inlineStr">
+      <c r="I30" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4857,10 +4838,10 @@
         </is>
       </c>
       <c r="AS30" s="23" t="n"/>
-      <c r="AT30" s="67" t="inlineStr"/>
+      <c r="AT30" s="66" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="68" t="inlineStr">
+      <c r="A31" s="67" t="inlineStr">
         <is>
           <t>PS5-03-17 - FZ-17 - Power Generation Building - Generator Room 3</t>
         </is>
@@ -4892,7 +4873,7 @@
         </is>
       </c>
       <c r="H31" s="24" t="inlineStr"/>
-      <c r="I31" s="70" t="inlineStr">
+      <c r="I31" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4975,10 +4956,10 @@
         </is>
       </c>
       <c r="AS31" s="23" t="n"/>
-      <c r="AT31" s="67" t="inlineStr"/>
+      <c r="AT31" s="66" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="68" t="inlineStr">
+      <c r="A32" s="67" t="inlineStr">
         <is>
           <t>PS5-03-18 - FZ-18 - Power Generation Building - Generator Room 4</t>
         </is>
@@ -5010,7 +4991,7 @@
         </is>
       </c>
       <c r="H32" s="24" t="inlineStr"/>
-      <c r="I32" s="70" t="inlineStr">
+      <c r="I32" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5093,10 +5074,10 @@
         </is>
       </c>
       <c r="AS32" s="23" t="n"/>
-      <c r="AT32" s="67" t="inlineStr"/>
+      <c r="AT32" s="66" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="68" t="inlineStr">
+      <c r="A33" s="67" t="inlineStr">
         <is>
           <t>PS5-03-19 - FZ-19 - Power Generation Building - Battery Room</t>
         </is>
@@ -5132,7 +5113,7 @@
         </is>
       </c>
       <c r="H33" s="24" t="inlineStr"/>
-      <c r="I33" s="70" t="inlineStr">
+      <c r="I33" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5215,7 +5196,7 @@
         </is>
       </c>
       <c r="AS33" s="23" t="n"/>
-      <c r="AT33" s="67" t="inlineStr"/>
+      <c r="AT33" s="66" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="53" t="inlineStr">
@@ -5337,10 +5318,10 @@
         </is>
       </c>
       <c r="AS34" s="23" t="n"/>
-      <c r="AT34" s="67" t="inlineStr"/>
+      <c r="AT34" s="66" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="68" t="inlineStr">
+      <c r="A35" s="67" t="inlineStr">
         <is>
           <t>PS5-03-21 - FZ-21 - Power Generation Building - Air Handling Unit</t>
         </is>
@@ -5372,7 +5353,7 @@
         </is>
       </c>
       <c r="H35" s="24" t="inlineStr"/>
-      <c r="I35" s="70" t="inlineStr">
+      <c r="I35" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5455,10 +5436,10 @@
         </is>
       </c>
       <c r="AS35" s="23" t="n"/>
-      <c r="AT35" s="67" t="inlineStr"/>
+      <c r="AT35" s="66" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="68" t="inlineStr">
+      <c r="A36" s="67" t="inlineStr">
         <is>
           <t>PS5-03-22 - FZ-G1 - Guard House</t>
         </is>
@@ -5490,7 +5471,7 @@
         </is>
       </c>
       <c r="H36" s="24" t="inlineStr"/>
-      <c r="I36" s="70" t="inlineStr">
+      <c r="I36" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5575,10 +5556,10 @@
         </is>
       </c>
       <c r="AS36" s="23" t="n"/>
-      <c r="AT36" s="67" t="inlineStr"/>
+      <c r="AT36" s="66" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="68" t="inlineStr">
+      <c r="A37" s="67" t="inlineStr">
         <is>
           <t>PS5-03-23 - FZ-E1 to E3 - EITS Building</t>
         </is>
@@ -5659,10 +5640,10 @@
       <c r="AQ37" s="65" t="inlineStr"/>
       <c r="AR37" s="23" t="inlineStr"/>
       <c r="AS37" s="23" t="n"/>
-      <c r="AT37" s="67" t="inlineStr"/>
+      <c r="AT37" s="66" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="68" t="inlineStr">
+      <c r="A38" s="67" t="inlineStr">
         <is>
           <t>PS5-03-24 - FZ - Office and Facilities Building</t>
         </is>
@@ -5694,7 +5675,7 @@
         </is>
       </c>
       <c r="H38" s="24" t="inlineStr"/>
-      <c r="I38" s="70" t="inlineStr">
+      <c r="I38" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5777,10 +5758,10 @@
         </is>
       </c>
       <c r="AS38" s="23" t="n"/>
-      <c r="AT38" s="67" t="inlineStr"/>
+      <c r="AT38" s="66" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="68" t="inlineStr">
+      <c r="A39" s="67" t="inlineStr">
         <is>
           <t>PS5-03-25 - FZ - Workshop &amp; Warehouse</t>
         </is>
@@ -5812,7 +5793,7 @@
         </is>
       </c>
       <c r="H39" s="24" t="inlineStr"/>
-      <c r="I39" s="70" t="inlineStr">
+      <c r="I39" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5895,10 +5876,10 @@
         </is>
       </c>
       <c r="AS39" s="23" t="n"/>
-      <c r="AT39" s="67" t="inlineStr"/>
+      <c r="AT39" s="66" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="68" t="inlineStr">
+      <c r="A40" s="67" t="inlineStr">
         <is>
           <t>PS5-04-01 - Office Building PCS System</t>
         </is>
@@ -5914,7 +5895,7 @@
         </is>
       </c>
       <c r="H40" s="24" t="inlineStr"/>
-      <c r="I40" s="70" t="inlineStr">
+      <c r="I40" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5946,7 +5927,7 @@
       <c r="R40" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S40" s="72" t="inlineStr">
+      <c r="S40" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5979,10 +5960,10 @@
       <c r="AQ40" s="65" t="inlineStr"/>
       <c r="AR40" s="23" t="inlineStr"/>
       <c r="AS40" s="23" t="n"/>
-      <c r="AT40" s="67" t="inlineStr"/>
+      <c r="AT40" s="66" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="68" t="inlineStr">
+      <c r="A41" s="67" t="inlineStr">
         <is>
           <t>PS5-04-02 - Office Building SIS/FGS System</t>
         </is>
@@ -6014,7 +5995,7 @@
         </is>
       </c>
       <c r="H41" s="24" t="inlineStr"/>
-      <c r="I41" s="70" t="inlineStr">
+      <c r="I41" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6097,10 +6078,10 @@
         </is>
       </c>
       <c r="AS41" s="23" t="n"/>
-      <c r="AT41" s="67" t="inlineStr"/>
+      <c r="AT41" s="66" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="68" t="inlineStr">
+      <c r="A42" s="67" t="inlineStr">
         <is>
           <t>PS5-04-03 - 33kV ICSS System</t>
         </is>
@@ -6148,7 +6129,7 @@
       <c r="R42" s="62" t="n">
         <v>64</v>
       </c>
-      <c r="S42" s="73" t="inlineStr">
+      <c r="S42" s="72" t="inlineStr">
         <is>
           <t>98%</t>
         </is>
@@ -6181,10 +6162,10 @@
       <c r="AQ42" s="65" t="inlineStr"/>
       <c r="AR42" s="23" t="inlineStr"/>
       <c r="AS42" s="23" t="n"/>
-      <c r="AT42" s="67" t="inlineStr"/>
+      <c r="AT42" s="66" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="68" t="inlineStr">
+      <c r="A43" s="67" t="inlineStr">
         <is>
           <t>PS5-04-04 - 33kV PCS System</t>
         </is>
@@ -6232,7 +6213,7 @@
       <c r="R43" s="62" t="n">
         <v>9</v>
       </c>
-      <c r="S43" s="73" t="inlineStr">
+      <c r="S43" s="72" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6265,10 +6246,10 @@
       <c r="AQ43" s="65" t="inlineStr"/>
       <c r="AR43" s="23" t="inlineStr"/>
       <c r="AS43" s="23" t="n"/>
-      <c r="AT43" s="67" t="inlineStr"/>
+      <c r="AT43" s="66" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="68" t="inlineStr">
+      <c r="A44" s="67" t="inlineStr">
         <is>
           <t>PS5-04-05 - 33kV SIS/FGS System</t>
         </is>
@@ -6284,7 +6265,7 @@
         </is>
       </c>
       <c r="H44" s="24" t="inlineStr"/>
-      <c r="I44" s="69" t="inlineStr">
+      <c r="I44" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -6316,7 +6297,7 @@
       <c r="R44" s="62" t="n">
         <v>19</v>
       </c>
-      <c r="S44" s="73" t="inlineStr">
+      <c r="S44" s="72" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6349,10 +6330,10 @@
       <c r="AQ44" s="65" t="inlineStr"/>
       <c r="AR44" s="23" t="inlineStr"/>
       <c r="AS44" s="23" t="n"/>
-      <c r="AT44" s="67" t="inlineStr"/>
+      <c r="AT44" s="66" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="74" t="inlineStr">
+      <c r="A45" s="73" t="inlineStr">
         <is>
           <t>PS5-05-01 - Emergency Diesel Generator Package</t>
         </is>
@@ -6378,7 +6359,7 @@
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr"/>
-      <c r="G45" s="69" t="inlineStr">
+      <c r="G45" s="68" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6431,10 +6412,8 @@
       <c r="AI45" s="23" t="n">
         <v>109</v>
       </c>
-      <c r="AJ45" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AJ45" s="23" t="n">
+        <v>0</v>
       </c>
       <c r="AK45" s="29" t="inlineStr">
         <is>
@@ -6473,10 +6452,10 @@
         </is>
       </c>
       <c r="AS45" s="23" t="n"/>
-      <c r="AT45" s="67" t="inlineStr"/>
+      <c r="AT45" s="66" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="75" t="inlineStr">
+      <c r="A46" s="74" t="inlineStr">
         <is>
           <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
         </is>
@@ -6595,10 +6574,10 @@
         </is>
       </c>
       <c r="AS46" s="23" t="n"/>
-      <c r="AT46" s="67" t="inlineStr"/>
+      <c r="AT46" s="66" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="68" t="inlineStr">
+      <c r="A47" s="67" t="inlineStr">
         <is>
           <t>PS5-06-01 - AC UPS - EITS Building</t>
         </is>
@@ -6614,7 +6593,7 @@
         </is>
       </c>
       <c r="H47" s="24" t="inlineStr"/>
-      <c r="I47" s="69" t="inlineStr">
+      <c r="I47" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -6646,7 +6625,7 @@
       <c r="R47" s="62" t="n">
         <v>12</v>
       </c>
-      <c r="S47" s="73" t="inlineStr">
+      <c r="S47" s="72" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6679,7 +6658,7 @@
       <c r="AQ47" s="65" t="inlineStr"/>
       <c r="AR47" s="23" t="inlineStr"/>
       <c r="AS47" s="23" t="n"/>
-      <c r="AT47" s="67" t="inlineStr"/>
+      <c r="AT47" s="66" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="53" t="inlineStr">
@@ -6805,10 +6784,10 @@
         </is>
       </c>
       <c r="AS48" s="23" t="n"/>
-      <c r="AT48" s="67" t="inlineStr"/>
+      <c r="AT48" s="66" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="68" t="inlineStr">
+      <c r="A49" s="67" t="inlineStr">
         <is>
           <t>PS5-06-03 - AC UPS - Office &amp; Facilities Building</t>
         </is>
@@ -6840,7 +6819,7 @@
         </is>
       </c>
       <c r="H49" s="24" t="inlineStr"/>
-      <c r="I49" s="70" t="inlineStr">
+      <c r="I49" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6923,10 +6902,10 @@
         </is>
       </c>
       <c r="AS49" s="23" t="n"/>
-      <c r="AT49" s="67" t="inlineStr"/>
+      <c r="AT49" s="66" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="68" t="inlineStr">
+      <c r="A50" s="67" t="inlineStr">
         <is>
           <t>PS5-06-04 - AC UPS - Guard House</t>
         </is>
@@ -6958,7 +6937,7 @@
         </is>
       </c>
       <c r="H50" s="24" t="inlineStr"/>
-      <c r="I50" s="70" t="inlineStr">
+      <c r="I50" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7041,10 +7020,10 @@
         </is>
       </c>
       <c r="AS50" s="23" t="n"/>
-      <c r="AT50" s="67" t="inlineStr"/>
+      <c r="AT50" s="66" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="68" t="inlineStr">
+      <c r="A51" s="67" t="inlineStr">
         <is>
           <t>PS5-06-05 - AC UPS - Workshop &amp; Warehouse</t>
         </is>
@@ -7076,7 +7055,7 @@
         </is>
       </c>
       <c r="H51" s="24" t="inlineStr"/>
-      <c r="I51" s="70" t="inlineStr">
+      <c r="I51" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7159,10 +7138,10 @@
         </is>
       </c>
       <c r="AS51" s="23" t="n"/>
-      <c r="AT51" s="67" t="inlineStr"/>
+      <c r="AT51" s="66" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="68" t="inlineStr">
+      <c r="A52" s="67" t="inlineStr">
         <is>
           <t>PS5-08-01 - PAGA</t>
         </is>
@@ -7194,7 +7173,7 @@
         </is>
       </c>
       <c r="H52" s="24" t="inlineStr"/>
-      <c r="I52" s="70" t="inlineStr">
+      <c r="I52" s="69" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -7226,7 +7205,7 @@
       <c r="R52" s="62" t="n">
         <v>82</v>
       </c>
-      <c r="S52" s="72" t="inlineStr">
+      <c r="S52" s="71" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -7277,10 +7256,10 @@
         </is>
       </c>
       <c r="AS52" s="23" t="n"/>
-      <c r="AT52" s="67" t="inlineStr"/>
+      <c r="AT52" s="66" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="68" t="inlineStr">
+      <c r="A53" s="67" t="inlineStr">
         <is>
           <t>PS5-08-03 - Telephone</t>
         </is>
@@ -7312,7 +7291,7 @@
         </is>
       </c>
       <c r="H53" s="24" t="inlineStr"/>
-      <c r="I53" s="70" t="inlineStr">
+      <c r="I53" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -7344,7 +7323,7 @@
       <c r="R53" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="S53" s="72" t="inlineStr">
+      <c r="S53" s="71" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -7395,10 +7374,10 @@
         </is>
       </c>
       <c r="AS53" s="23" t="n"/>
-      <c r="AT53" s="67" t="inlineStr"/>
+      <c r="AT53" s="66" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="68" t="inlineStr">
+      <c r="A54" s="67" t="inlineStr">
         <is>
           <t>PS5-08-04 - Hotline</t>
         </is>
@@ -7414,7 +7393,7 @@
         </is>
       </c>
       <c r="H54" s="24" t="inlineStr"/>
-      <c r="I54" s="70" t="inlineStr">
+      <c r="I54" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7446,7 +7425,7 @@
       <c r="R54" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S54" s="72" t="inlineStr">
+      <c r="S54" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7479,10 +7458,10 @@
       <c r="AQ54" s="65" t="inlineStr"/>
       <c r="AR54" s="23" t="inlineStr"/>
       <c r="AS54" s="23" t="n"/>
-      <c r="AT54" s="67" t="inlineStr"/>
+      <c r="AT54" s="66" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="68" t="inlineStr">
+      <c r="A55" s="67" t="inlineStr">
         <is>
           <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
         </is>
@@ -7498,7 +7477,7 @@
         </is>
       </c>
       <c r="H55" s="24" t="inlineStr"/>
-      <c r="I55" s="70" t="inlineStr">
+      <c r="I55" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7530,7 +7509,7 @@
       <c r="R55" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S55" s="72" t="inlineStr">
+      <c r="S55" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7563,10 +7542,10 @@
       <c r="AQ55" s="65" t="inlineStr"/>
       <c r="AR55" s="23" t="inlineStr"/>
       <c r="AS55" s="23" t="n"/>
-      <c r="AT55" s="67" t="inlineStr"/>
+      <c r="AT55" s="66" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="68" t="inlineStr">
+      <c r="A56" s="67" t="inlineStr">
         <is>
           <t>PS5-08-11 - Corporate LAN  (SIE)</t>
         </is>
@@ -7598,7 +7577,7 @@
         </is>
       </c>
       <c r="H56" s="24" t="inlineStr"/>
-      <c r="I56" s="70" t="inlineStr">
+      <c r="I56" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -7681,10 +7660,10 @@
         </is>
       </c>
       <c r="AS56" s="23" t="n"/>
-      <c r="AT56" s="67" t="inlineStr"/>
+      <c r="AT56" s="66" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="68" t="inlineStr">
+      <c r="A57" s="67" t="inlineStr">
         <is>
           <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
         </is>
@@ -7716,7 +7695,7 @@
         </is>
       </c>
       <c r="H57" s="24" t="inlineStr"/>
-      <c r="I57" s="70" t="inlineStr">
+      <c r="I57" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7748,7 +7727,7 @@
       <c r="R57" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S57" s="72" t="inlineStr">
+      <c r="S57" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7799,10 +7778,10 @@
         </is>
       </c>
       <c r="AS57" s="23" t="n"/>
-      <c r="AT57" s="67" t="inlineStr"/>
+      <c r="AT57" s="66" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="68" t="inlineStr">
+      <c r="A58" s="67" t="inlineStr">
         <is>
           <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
         </is>
@@ -7834,7 +7813,7 @@
         </is>
       </c>
       <c r="H58" s="24" t="inlineStr"/>
-      <c r="I58" s="70" t="inlineStr">
+      <c r="I58" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7866,7 +7845,7 @@
       <c r="R58" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S58" s="72" t="inlineStr">
+      <c r="S58" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7917,10 +7896,10 @@
         </is>
       </c>
       <c r="AS58" s="23" t="n"/>
-      <c r="AT58" s="67" t="inlineStr"/>
+      <c r="AT58" s="66" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="68" t="inlineStr">
+      <c r="A59" s="67" t="inlineStr">
         <is>
           <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
         </is>
@@ -7952,7 +7931,7 @@
         </is>
       </c>
       <c r="H59" s="24" t="inlineStr"/>
-      <c r="I59" s="70" t="inlineStr">
+      <c r="I59" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7984,7 +7963,7 @@
       <c r="R59" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S59" s="72" t="inlineStr">
+      <c r="S59" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8035,10 +8014,10 @@
         </is>
       </c>
       <c r="AS59" s="23" t="n"/>
-      <c r="AT59" s="67" t="inlineStr"/>
+      <c r="AT59" s="66" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="68" t="inlineStr">
+      <c r="A60" s="67" t="inlineStr">
         <is>
           <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
         </is>
@@ -8070,7 +8049,7 @@
         </is>
       </c>
       <c r="H60" s="24" t="inlineStr"/>
-      <c r="I60" s="70" t="inlineStr">
+      <c r="I60" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8102,7 +8081,7 @@
       <c r="R60" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S60" s="72" t="inlineStr">
+      <c r="S60" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8153,10 +8132,10 @@
         </is>
       </c>
       <c r="AS60" s="23" t="n"/>
-      <c r="AT60" s="67" t="inlineStr"/>
+      <c r="AT60" s="66" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="68" t="inlineStr">
+      <c r="A61" s="67" t="inlineStr">
         <is>
           <t>PS5-08-23 - VHF Trunk Radio System</t>
         </is>
@@ -8188,7 +8167,7 @@
         </is>
       </c>
       <c r="H61" s="24" t="inlineStr"/>
-      <c r="I61" s="70" t="inlineStr">
+      <c r="I61" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8220,7 +8199,7 @@
       <c r="R61" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S61" s="72" t="inlineStr">
+      <c r="S61" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8271,10 +8250,10 @@
         </is>
       </c>
       <c r="AS61" s="23" t="n"/>
-      <c r="AT61" s="67" t="inlineStr"/>
+      <c r="AT61" s="66" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="68" t="inlineStr">
+      <c r="A62" s="67" t="inlineStr">
         <is>
           <t>PS5-08-34 - Satphone</t>
         </is>
@@ -8306,7 +8285,7 @@
         </is>
       </c>
       <c r="H62" s="24" t="inlineStr"/>
-      <c r="I62" s="70" t="inlineStr">
+      <c r="I62" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8338,7 +8317,7 @@
       <c r="R62" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S62" s="72" t="inlineStr">
+      <c r="S62" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8389,10 +8368,10 @@
         </is>
       </c>
       <c r="AS62" s="23" t="n"/>
-      <c r="AT62" s="67" t="inlineStr"/>
+      <c r="AT62" s="66" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="68" t="inlineStr">
+      <c r="A63" s="67" t="inlineStr">
         <is>
           <t>PS5-08-35 - Optical Transport Network</t>
         </is>
@@ -8408,7 +8387,7 @@
         </is>
       </c>
       <c r="H63" s="24" t="inlineStr"/>
-      <c r="I63" s="69" t="inlineStr">
+      <c r="I63" s="68" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -8440,7 +8419,7 @@
       <c r="R63" s="62" t="n">
         <v>39</v>
       </c>
-      <c r="S63" s="71" t="inlineStr">
+      <c r="S63" s="70" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -8473,10 +8452,10 @@
       <c r="AQ63" s="65" t="inlineStr"/>
       <c r="AR63" s="23" t="inlineStr"/>
       <c r="AS63" s="23" t="n"/>
-      <c r="AT63" s="67" t="inlineStr"/>
+      <c r="AT63" s="66" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="68" t="inlineStr">
+      <c r="A64" s="67" t="inlineStr">
         <is>
           <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
         </is>
@@ -8508,7 +8487,7 @@
         </is>
       </c>
       <c r="H64" s="24" t="inlineStr"/>
-      <c r="I64" s="70" t="inlineStr">
+      <c r="I64" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8540,7 +8519,7 @@
       <c r="R64" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S64" s="72" t="inlineStr">
+      <c r="S64" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8591,10 +8570,10 @@
         </is>
       </c>
       <c r="AS64" s="23" t="n"/>
-      <c r="AT64" s="67" t="inlineStr"/>
+      <c r="AT64" s="66" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="68" t="inlineStr">
+      <c r="A65" s="67" t="inlineStr">
         <is>
           <t>PS5-08-51 - Entertainment</t>
         </is>
@@ -8626,7 +8605,7 @@
         </is>
       </c>
       <c r="H65" s="24" t="inlineStr"/>
-      <c r="I65" s="70" t="inlineStr">
+      <c r="I65" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8658,7 +8637,7 @@
       <c r="R65" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S65" s="72" t="inlineStr">
+      <c r="S65" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8709,10 +8688,10 @@
         </is>
       </c>
       <c r="AS65" s="23" t="n"/>
-      <c r="AT65" s="67" t="inlineStr"/>
+      <c r="AT65" s="66" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="68" t="inlineStr">
+      <c r="A66" s="67" t="inlineStr">
         <is>
           <t>PS5-08-52 - Process &amp; Security CCTV</t>
         </is>
@@ -8744,7 +8723,7 @@
         </is>
       </c>
       <c r="H66" s="24" t="inlineStr"/>
-      <c r="I66" s="70" t="inlineStr">
+      <c r="I66" s="69" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -8776,7 +8755,7 @@
       <c r="R66" s="62" t="n">
         <v>22</v>
       </c>
-      <c r="S66" s="72" t="inlineStr">
+      <c r="S66" s="71" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -8827,10 +8806,10 @@
         </is>
       </c>
       <c r="AS66" s="23" t="n"/>
-      <c r="AT66" s="67" t="inlineStr"/>
+      <c r="AT66" s="66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="68" t="inlineStr">
+      <c r="A67" s="67" t="inlineStr">
         <is>
           <t>PS5-08-55 - Videoconference</t>
         </is>
@@ -8846,7 +8825,7 @@
         </is>
       </c>
       <c r="H67" s="24" t="inlineStr"/>
-      <c r="I67" s="70" t="inlineStr">
+      <c r="I67" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8878,7 +8857,7 @@
       <c r="R67" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S67" s="72" t="inlineStr">
+      <c r="S67" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8911,10 +8890,10 @@
       <c r="AQ67" s="65" t="inlineStr"/>
       <c r="AR67" s="23" t="inlineStr"/>
       <c r="AS67" s="23" t="n"/>
-      <c r="AT67" s="67" t="inlineStr"/>
+      <c r="AT67" s="66" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="68" t="inlineStr">
+      <c r="A68" s="67" t="inlineStr">
         <is>
           <t>PS5-08-61 - Meteocean</t>
         </is>
@@ -8946,7 +8925,7 @@
         </is>
       </c>
       <c r="H68" s="24" t="inlineStr"/>
-      <c r="I68" s="70" t="inlineStr">
+      <c r="I68" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8978,7 +8957,7 @@
       <c r="R68" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S68" s="72" t="inlineStr">
+      <c r="S68" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9029,10 +9008,10 @@
         </is>
       </c>
       <c r="AS68" s="23" t="n"/>
-      <c r="AT68" s="67" t="inlineStr"/>
+      <c r="AT68" s="66" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="68" t="inlineStr">
+      <c r="A69" s="67" t="inlineStr">
         <is>
           <t>PS5-08-71 - Structured Cabling (CAT6)</t>
         </is>
@@ -9064,7 +9043,7 @@
         </is>
       </c>
       <c r="H69" s="24" t="inlineStr"/>
-      <c r="I69" s="70" t="inlineStr">
+      <c r="I69" s="69" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -9096,7 +9075,7 @@
       <c r="R69" s="62" t="n">
         <v>10</v>
       </c>
-      <c r="S69" s="72" t="inlineStr">
+      <c r="S69" s="71" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -9147,10 +9126,10 @@
         </is>
       </c>
       <c r="AS69" s="23" t="n"/>
-      <c r="AT69" s="67" t="inlineStr"/>
+      <c r="AT69" s="66" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="68" t="inlineStr">
+      <c r="A70" s="67" t="inlineStr">
         <is>
           <t>PS5-08-72 - Structured Cabling (FO)</t>
         </is>
@@ -9182,7 +9161,7 @@
         </is>
       </c>
       <c r="H70" s="24" t="inlineStr"/>
-      <c r="I70" s="70" t="inlineStr">
+      <c r="I70" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9214,7 +9193,7 @@
       <c r="R70" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S70" s="72" t="inlineStr">
+      <c r="S70" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9265,10 +9244,10 @@
         </is>
       </c>
       <c r="AS70" s="23" t="n"/>
-      <c r="AT70" s="67" t="inlineStr"/>
+      <c r="AT70" s="66" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="68" t="inlineStr">
+      <c r="A71" s="67" t="inlineStr">
         <is>
           <t>PS5-08-81 - Guard tour</t>
         </is>
@@ -9284,7 +9263,7 @@
         </is>
       </c>
       <c r="H71" s="24" t="inlineStr"/>
-      <c r="I71" s="70" t="inlineStr">
+      <c r="I71" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9316,7 +9295,7 @@
       <c r="R71" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S71" s="72" t="inlineStr">
+      <c r="S71" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9349,10 +9328,10 @@
       <c r="AQ71" s="65" t="inlineStr"/>
       <c r="AR71" s="23" t="inlineStr"/>
       <c r="AS71" s="23" t="n"/>
-      <c r="AT71" s="67" t="inlineStr"/>
+      <c r="AT71" s="66" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="68" t="inlineStr">
+      <c r="A72" s="67" t="inlineStr">
         <is>
           <t>PS5-08-82 - Key Management</t>
         </is>
@@ -9368,7 +9347,7 @@
         </is>
       </c>
       <c r="H72" s="24" t="inlineStr"/>
-      <c r="I72" s="70" t="inlineStr">
+      <c r="I72" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9400,7 +9379,7 @@
       <c r="R72" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S72" s="72" t="inlineStr">
+      <c r="S72" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9433,10 +9412,10 @@
       <c r="AQ72" s="65" t="inlineStr"/>
       <c r="AR72" s="23" t="inlineStr"/>
       <c r="AS72" s="23" t="n"/>
-      <c r="AT72" s="67" t="inlineStr"/>
+      <c r="AT72" s="66" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="68" t="inlineStr">
+      <c r="A73" s="67" t="inlineStr">
         <is>
           <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
         </is>
@@ -9468,7 +9447,7 @@
         </is>
       </c>
       <c r="H73" s="24" t="inlineStr"/>
-      <c r="I73" s="70" t="inlineStr">
+      <c r="I73" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9500,7 +9479,7 @@
       <c r="R73" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S73" s="72" t="inlineStr">
+      <c r="S73" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9551,10 +9530,10 @@
         </is>
       </c>
       <c r="AS73" s="23" t="n"/>
-      <c r="AT73" s="67" t="inlineStr"/>
+      <c r="AT73" s="66" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="68" t="inlineStr">
+      <c r="A74" s="67" t="inlineStr">
         <is>
           <t>PS5-08-85 - Access Control, POB &amp; e-Mustering</t>
         </is>
@@ -9586,7 +9565,7 @@
         </is>
       </c>
       <c r="H74" s="24" t="inlineStr"/>
-      <c r="I74" s="70" t="inlineStr">
+      <c r="I74" s="69" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -9618,7 +9597,7 @@
       <c r="R74" s="62" t="n">
         <v>31</v>
       </c>
-      <c r="S74" s="72" t="inlineStr">
+      <c r="S74" s="71" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
@@ -9669,10 +9648,10 @@
         </is>
       </c>
       <c r="AS74" s="23" t="n"/>
-      <c r="AT74" s="67" t="inlineStr"/>
+      <c r="AT74" s="66" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="68" t="inlineStr">
+      <c r="A75" s="67" t="inlineStr">
         <is>
           <t>PS5-08-86 - Integrated Security Management System</t>
         </is>
@@ -9688,7 +9667,7 @@
         </is>
       </c>
       <c r="H75" s="24" t="inlineStr"/>
-      <c r="I75" s="70" t="inlineStr">
+      <c r="I75" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9720,7 +9699,7 @@
       <c r="R75" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S75" s="72" t="inlineStr">
+      <c r="S75" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9753,10 +9732,10 @@
       <c r="AQ75" s="65" t="inlineStr"/>
       <c r="AR75" s="23" t="inlineStr"/>
       <c r="AS75" s="23" t="n"/>
-      <c r="AT75" s="67" t="inlineStr"/>
+      <c r="AT75" s="66" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="68" t="inlineStr">
+      <c r="A76" s="67" t="inlineStr">
         <is>
           <t>PS5-08-92 - Telecom Mast</t>
         </is>
@@ -9772,7 +9751,7 @@
         </is>
       </c>
       <c r="H76" s="24" t="inlineStr"/>
-      <c r="I76" s="70" t="inlineStr">
+      <c r="I76" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9804,7 +9783,7 @@
       <c r="R76" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S76" s="72" t="inlineStr">
+      <c r="S76" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9837,10 +9816,10 @@
       <c r="AQ76" s="65" t="inlineStr"/>
       <c r="AR76" s="23" t="inlineStr"/>
       <c r="AS76" s="23" t="n"/>
-      <c r="AT76" s="67" t="inlineStr"/>
+      <c r="AT76" s="66" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="68" t="inlineStr">
+      <c r="A77" s="67" t="inlineStr">
         <is>
           <t>PS5-08-93 - Telecom Monitoring System</t>
         </is>
@@ -9872,7 +9851,7 @@
         </is>
       </c>
       <c r="H77" s="24" t="inlineStr"/>
-      <c r="I77" s="70" t="inlineStr">
+      <c r="I77" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9904,7 +9883,7 @@
       <c r="R77" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S77" s="72" t="inlineStr">
+      <c r="S77" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9955,10 +9934,10 @@
         </is>
       </c>
       <c r="AS77" s="23" t="n"/>
-      <c r="AT77" s="67" t="inlineStr"/>
+      <c r="AT77" s="66" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="68" t="inlineStr">
+      <c r="A78" s="67" t="inlineStr">
         <is>
           <t>PS5-09-01 - HVAC for Office and Facilities building</t>
         </is>
@@ -9990,7 +9969,7 @@
         </is>
       </c>
       <c r="H78" s="24" t="inlineStr"/>
-      <c r="I78" s="70" t="inlineStr">
+      <c r="I78" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10073,10 +10052,10 @@
         </is>
       </c>
       <c r="AS78" s="23" t="n"/>
-      <c r="AT78" s="67" t="inlineStr"/>
+      <c r="AT78" s="66" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="68" t="inlineStr">
+      <c r="A79" s="67" t="inlineStr">
         <is>
           <t>PS5-09-02 - HVAC for Guard House</t>
         </is>
@@ -10108,7 +10087,7 @@
         </is>
       </c>
       <c r="H79" s="24" t="inlineStr"/>
-      <c r="I79" s="70" t="inlineStr">
+      <c r="I79" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10191,10 +10170,10 @@
         </is>
       </c>
       <c r="AS79" s="23" t="n"/>
-      <c r="AT79" s="67" t="inlineStr"/>
+      <c r="AT79" s="66" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="68" t="inlineStr">
+      <c r="A80" s="67" t="inlineStr">
         <is>
           <t>PS5-09-03 - HVAC for Generator Building</t>
         </is>
@@ -10226,7 +10205,7 @@
         </is>
       </c>
       <c r="H80" s="24" t="inlineStr"/>
-      <c r="I80" s="70" t="inlineStr">
+      <c r="I80" s="69" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -10258,7 +10237,7 @@
       <c r="R80" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S80" s="72" t="inlineStr">
+      <c r="S80" s="71" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10313,10 +10292,10 @@
         </is>
       </c>
       <c r="AS80" s="23" t="n"/>
-      <c r="AT80" s="67" t="inlineStr"/>
+      <c r="AT80" s="66" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="68" t="inlineStr">
+      <c r="A81" s="67" t="inlineStr">
         <is>
           <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
         </is>
@@ -10348,7 +10327,7 @@
         </is>
       </c>
       <c r="H81" s="24" t="inlineStr"/>
-      <c r="I81" s="70" t="inlineStr">
+      <c r="I81" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10431,7 +10410,7 @@
         </is>
       </c>
       <c r="AS81" s="23" t="n"/>
-      <c r="AT81" s="67" t="inlineStr"/>
+      <c r="AT81" s="66" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="53" t="inlineStr">
@@ -10541,10 +10520,10 @@
       <c r="AQ82" s="65" t="inlineStr"/>
       <c r="AR82" s="23" t="inlineStr"/>
       <c r="AS82" s="23" t="n"/>
-      <c r="AT82" s="67" t="inlineStr"/>
+      <c r="AT82" s="66" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="68" t="inlineStr">
+      <c r="A83" s="67" t="inlineStr">
         <is>
           <t>PS5-0H-01 - HIPPS</t>
         </is>
@@ -10560,7 +10539,7 @@
         </is>
       </c>
       <c r="H83" s="24" t="inlineStr"/>
-      <c r="I83" s="69" t="inlineStr">
+      <c r="I83" s="68" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -10625,10 +10604,10 @@
       <c r="AQ83" s="65" t="inlineStr"/>
       <c r="AR83" s="23" t="inlineStr"/>
       <c r="AS83" s="23" t="n"/>
-      <c r="AT83" s="67" t="inlineStr"/>
+      <c r="AT83" s="66" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="68" t="inlineStr">
+      <c r="A84" s="67" t="inlineStr">
         <is>
           <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
         </is>
@@ -10660,7 +10639,7 @@
         </is>
       </c>
       <c r="H84" s="24" t="inlineStr"/>
-      <c r="I84" s="69" t="inlineStr">
+      <c r="I84" s="68" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -10743,10 +10722,10 @@
         </is>
       </c>
       <c r="AS84" s="23" t="n"/>
-      <c r="AT84" s="67" t="inlineStr"/>
+      <c r="AT84" s="66" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="68" t="inlineStr">
+      <c r="A85" s="67" t="inlineStr">
         <is>
           <t>PS5-25-02 - Crude Oil Export Pump A</t>
         </is>
@@ -10778,7 +10757,7 @@
         </is>
       </c>
       <c r="H85" s="24" t="inlineStr"/>
-      <c r="I85" s="69" t="inlineStr">
+      <c r="I85" s="68" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -10861,10 +10840,10 @@
         </is>
       </c>
       <c r="AS85" s="23" t="n"/>
-      <c r="AT85" s="67" t="inlineStr"/>
+      <c r="AT85" s="66" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="68" t="inlineStr">
+      <c r="A86" s="67" t="inlineStr">
         <is>
           <t>PS5-25-03 - Crude Oil Export Pump B</t>
         </is>
@@ -10896,7 +10875,7 @@
         </is>
       </c>
       <c r="H86" s="24" t="inlineStr"/>
-      <c r="I86" s="69" t="inlineStr">
+      <c r="I86" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -10979,10 +10958,10 @@
         </is>
       </c>
       <c r="AS86" s="23" t="n"/>
-      <c r="AT86" s="67" t="inlineStr"/>
+      <c r="AT86" s="66" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="68" t="inlineStr">
+      <c r="A87" s="67" t="inlineStr">
         <is>
           <t>PS5-25-04 - Crude Oil Export Pump C</t>
         </is>
@@ -11014,7 +10993,7 @@
         </is>
       </c>
       <c r="H87" s="24" t="inlineStr"/>
-      <c r="I87" s="69" t="inlineStr">
+      <c r="I87" s="68" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -11097,10 +11076,10 @@
         </is>
       </c>
       <c r="AS87" s="23" t="n"/>
-      <c r="AT87" s="67" t="inlineStr"/>
+      <c r="AT87" s="66" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="68" t="inlineStr">
+      <c r="A88" s="67" t="inlineStr">
         <is>
           <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
         </is>
@@ -11132,7 +11111,7 @@
         </is>
       </c>
       <c r="H88" s="24" t="inlineStr"/>
-      <c r="I88" s="69" t="inlineStr">
+      <c r="I88" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -11215,10 +11194,10 @@
         </is>
       </c>
       <c r="AS88" s="23" t="n"/>
-      <c r="AT88" s="67" t="inlineStr"/>
+      <c r="AT88" s="66" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="68" t="inlineStr">
+      <c r="A89" s="67" t="inlineStr">
         <is>
           <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
         </is>
@@ -11250,7 +11229,7 @@
         </is>
       </c>
       <c r="H89" s="24" t="inlineStr"/>
-      <c r="I89" s="69" t="inlineStr">
+      <c r="I89" s="68" t="inlineStr">
         <is>
           <t>57%</t>
         </is>
@@ -11333,10 +11312,10 @@
         </is>
       </c>
       <c r="AS89" s="23" t="n"/>
-      <c r="AT89" s="67" t="inlineStr"/>
+      <c r="AT89" s="66" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="68" t="inlineStr">
+      <c r="A90" s="67" t="inlineStr">
         <is>
           <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
         </is>
@@ -11368,7 +11347,7 @@
         </is>
       </c>
       <c r="H90" s="24" t="inlineStr"/>
-      <c r="I90" s="69" t="inlineStr">
+      <c r="I90" s="68" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -11451,10 +11430,10 @@
         </is>
       </c>
       <c r="AS90" s="23" t="n"/>
-      <c r="AT90" s="67" t="inlineStr"/>
+      <c r="AT90" s="66" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="68" t="inlineStr">
+      <c r="A91" s="67" t="inlineStr">
         <is>
           <t>PS5-28-01 - Closed Drain Header 1</t>
         </is>
@@ -11486,7 +11465,7 @@
         </is>
       </c>
       <c r="H91" s="24" t="inlineStr"/>
-      <c r="I91" s="69" t="inlineStr">
+      <c r="I91" s="68" t="inlineStr">
         <is>
           <t>79%</t>
         </is>
@@ -11569,7 +11548,7 @@
         </is>
       </c>
       <c r="AS91" s="23" t="n"/>
-      <c r="AT91" s="67" t="inlineStr"/>
+      <c r="AT91" s="66" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="53" t="inlineStr">
@@ -11691,10 +11670,10 @@
         </is>
       </c>
       <c r="AS92" s="23" t="n"/>
-      <c r="AT92" s="67" t="inlineStr"/>
+      <c r="AT92" s="66" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="68" t="inlineStr">
+      <c r="A93" s="67" t="inlineStr">
         <is>
           <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
         </is>
@@ -11726,7 +11705,7 @@
         </is>
       </c>
       <c r="H93" s="24" t="inlineStr"/>
-      <c r="I93" s="69" t="inlineStr">
+      <c r="I93" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -11809,10 +11788,10 @@
         </is>
       </c>
       <c r="AS93" s="23" t="n"/>
-      <c r="AT93" s="67" t="inlineStr"/>
+      <c r="AT93" s="66" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="68" t="inlineStr">
+      <c r="A94" s="67" t="inlineStr">
         <is>
           <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
         </is>
@@ -11935,7 +11914,7 @@
         </is>
       </c>
       <c r="AS94" s="23" t="n"/>
-      <c r="AT94" s="67" t="inlineStr"/>
+      <c r="AT94" s="66" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="53" t="inlineStr">
@@ -12061,10 +12040,10 @@
         </is>
       </c>
       <c r="AS95" s="23" t="n"/>
-      <c r="AT95" s="67" t="inlineStr"/>
+      <c r="AT95" s="66" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="68" t="inlineStr">
+      <c r="A96" s="67" t="inlineStr">
         <is>
           <t>PS5-28-06 - Relief Drum and Pump</t>
         </is>
@@ -12100,7 +12079,7 @@
         </is>
       </c>
       <c r="H96" s="24" t="inlineStr"/>
-      <c r="I96" s="69" t="inlineStr">
+      <c r="I96" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -12183,10 +12162,10 @@
         </is>
       </c>
       <c r="AS96" s="23" t="n"/>
-      <c r="AT96" s="67" t="inlineStr"/>
+      <c r="AT96" s="66" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="68" t="inlineStr">
+      <c r="A97" s="67" t="inlineStr">
         <is>
           <t>PS5-28-07 - Open Drains (OD2)</t>
         </is>
@@ -12301,10 +12280,10 @@
         </is>
       </c>
       <c r="AS97" s="23" t="n"/>
-      <c r="AT97" s="67" t="inlineStr"/>
+      <c r="AT97" s="66" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="68" t="inlineStr">
+      <c r="A98" s="67" t="inlineStr">
         <is>
           <t>PS5-28-08 - Open Drain Sump and Pumps</t>
         </is>
@@ -12336,7 +12315,7 @@
         </is>
       </c>
       <c r="H98" s="24" t="inlineStr"/>
-      <c r="I98" s="70" t="inlineStr">
+      <c r="I98" s="69" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -12419,10 +12398,10 @@
         </is>
       </c>
       <c r="AS98" s="23" t="n"/>
-      <c r="AT98" s="67" t="inlineStr"/>
+      <c r="AT98" s="66" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="68" t="inlineStr">
+      <c r="A99" s="67" t="inlineStr">
         <is>
           <t>PS5-28-09 - Observation Basin</t>
         </is>
@@ -12454,7 +12433,7 @@
         </is>
       </c>
       <c r="H99" s="24" t="inlineStr"/>
-      <c r="I99" s="69" t="inlineStr">
+      <c r="I99" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -12537,10 +12516,10 @@
         </is>
       </c>
       <c r="AS99" s="23" t="n"/>
-      <c r="AT99" s="67" t="inlineStr"/>
+      <c r="AT99" s="66" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="68" t="inlineStr">
+      <c r="A100" s="67" t="inlineStr">
         <is>
           <t>PS5-28-10 - Oil Skimmer Package</t>
         </is>
@@ -12572,7 +12551,7 @@
         </is>
       </c>
       <c r="H100" s="24" t="inlineStr"/>
-      <c r="I100" s="70" t="inlineStr">
+      <c r="I100" s="69" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -12655,10 +12634,10 @@
         </is>
       </c>
       <c r="AS100" s="23" t="n"/>
-      <c r="AT100" s="67" t="inlineStr"/>
+      <c r="AT100" s="66" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="68" t="inlineStr">
+      <c r="A101" s="67" t="inlineStr">
         <is>
           <t>PS5-28-11 - Open Drain Interceptor</t>
         </is>
@@ -12690,7 +12669,7 @@
         </is>
       </c>
       <c r="H101" s="24" t="inlineStr"/>
-      <c r="I101" s="69" t="inlineStr">
+      <c r="I101" s="68" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -12773,10 +12752,10 @@
         </is>
       </c>
       <c r="AS101" s="23" t="n"/>
-      <c r="AT101" s="67" t="inlineStr"/>
+      <c r="AT101" s="66" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="68" t="inlineStr">
+      <c r="A102" s="67" t="inlineStr">
         <is>
           <t>PS5-28-12 - Open Drains (OD3)</t>
         </is>
@@ -12808,7 +12787,7 @@
         </is>
       </c>
       <c r="H102" s="24" t="inlineStr"/>
-      <c r="I102" s="69" t="inlineStr">
+      <c r="I102" s="68" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -12891,10 +12870,10 @@
         </is>
       </c>
       <c r="AS102" s="23" t="n"/>
-      <c r="AT102" s="67" t="inlineStr"/>
+      <c r="AT102" s="66" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="68" t="inlineStr">
+      <c r="A103" s="67" t="inlineStr">
         <is>
           <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
         </is>
@@ -12926,7 +12905,7 @@
         </is>
       </c>
       <c r="H103" s="24" t="inlineStr"/>
-      <c r="I103" s="69" t="inlineStr">
+      <c r="I103" s="68" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -13009,10 +12988,10 @@
         </is>
       </c>
       <c r="AS103" s="23" t="n"/>
-      <c r="AT103" s="67" t="inlineStr"/>
+      <c r="AT103" s="66" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="68" t="inlineStr">
+      <c r="A104" s="67" t="inlineStr">
         <is>
           <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
         </is>
@@ -13044,7 +13023,7 @@
         </is>
       </c>
       <c r="H104" s="24" t="inlineStr"/>
-      <c r="I104" s="69" t="inlineStr">
+      <c r="I104" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -13127,10 +13106,10 @@
         </is>
       </c>
       <c r="AS104" s="23" t="n"/>
-      <c r="AT104" s="67" t="inlineStr"/>
+      <c r="AT104" s="66" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="68" t="inlineStr">
+      <c r="A105" s="67" t="inlineStr">
         <is>
           <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
         </is>
@@ -13162,7 +13141,7 @@
         </is>
       </c>
       <c r="H105" s="24" t="inlineStr"/>
-      <c r="I105" s="69" t="inlineStr">
+      <c r="I105" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -13245,10 +13224,10 @@
         </is>
       </c>
       <c r="AS105" s="23" t="n"/>
-      <c r="AT105" s="67" t="inlineStr"/>
+      <c r="AT105" s="66" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="68" t="inlineStr">
+      <c r="A106" s="67" t="inlineStr">
         <is>
           <t>PS5-28-16 - LP Relief Header</t>
         </is>
@@ -13280,7 +13259,7 @@
         </is>
       </c>
       <c r="H106" s="24" t="inlineStr"/>
-      <c r="I106" s="69" t="inlineStr">
+      <c r="I106" s="68" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -13363,10 +13342,10 @@
         </is>
       </c>
       <c r="AS106" s="23" t="n"/>
-      <c r="AT106" s="67" t="inlineStr"/>
+      <c r="AT106" s="66" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="68" t="inlineStr">
+      <c r="A107" s="67" t="inlineStr">
         <is>
           <t>PS5-28-17 - Reinjection Pump</t>
         </is>
@@ -13398,7 +13377,7 @@
         </is>
       </c>
       <c r="H107" s="24" t="inlineStr"/>
-      <c r="I107" s="69" t="inlineStr">
+      <c r="I107" s="68" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -13481,10 +13460,10 @@
         </is>
       </c>
       <c r="AS107" s="23" t="n"/>
-      <c r="AT107" s="67" t="inlineStr"/>
+      <c r="AT107" s="66" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="68" t="inlineStr">
+      <c r="A108" s="67" t="inlineStr">
         <is>
           <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
         </is>
@@ -13516,7 +13495,7 @@
         </is>
       </c>
       <c r="H108" s="24" t="inlineStr"/>
-      <c r="I108" s="70" t="inlineStr">
+      <c r="I108" s="69" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -13599,10 +13578,10 @@
         </is>
       </c>
       <c r="AS108" s="23" t="n"/>
-      <c r="AT108" s="67" t="inlineStr"/>
+      <c r="AT108" s="66" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="68" t="inlineStr">
+      <c r="A109" s="67" t="inlineStr">
         <is>
           <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
         </is>
@@ -13634,7 +13613,7 @@
         </is>
       </c>
       <c r="H109" s="24" t="inlineStr"/>
-      <c r="I109" s="70" t="inlineStr">
+      <c r="I109" s="69" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -13717,10 +13696,10 @@
         </is>
       </c>
       <c r="AS109" s="23" t="n"/>
-      <c r="AT109" s="67" t="inlineStr"/>
+      <c r="AT109" s="66" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="68" t="inlineStr">
+      <c r="A110" s="67" t="inlineStr">
         <is>
           <t>PS5-50-03 - Water Pre-Treatment Package</t>
         </is>
@@ -13752,7 +13731,7 @@
         </is>
       </c>
       <c r="H110" s="24" t="inlineStr"/>
-      <c r="I110" s="70" t="inlineStr">
+      <c r="I110" s="69" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -13835,10 +13814,10 @@
         </is>
       </c>
       <c r="AS110" s="23" t="n"/>
-      <c r="AT110" s="67" t="inlineStr"/>
+      <c r="AT110" s="66" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="74" t="inlineStr">
+      <c r="A111" s="73" t="inlineStr">
         <is>
           <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
@@ -13868,7 +13847,7 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="G111" s="69" t="inlineStr">
+      <c r="G111" s="68" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -13878,7 +13857,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I111" s="69" t="inlineStr">
+      <c r="I111" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -13961,10 +13940,10 @@
         </is>
       </c>
       <c r="AS111" s="23" t="n"/>
-      <c r="AT111" s="67" t="inlineStr"/>
+      <c r="AT111" s="66" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="68" t="inlineStr">
+      <c r="A112" s="67" t="inlineStr">
         <is>
           <t>PS5-53-02 - Water Distribution Pump A/B</t>
         </is>
@@ -13996,7 +13975,7 @@
         </is>
       </c>
       <c r="H112" s="24" t="inlineStr"/>
-      <c r="I112" s="69" t="inlineStr">
+      <c r="I112" s="68" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -14079,10 +14058,10 @@
         </is>
       </c>
       <c r="AS112" s="23" t="n"/>
-      <c r="AT112" s="67" t="inlineStr"/>
+      <c r="AT112" s="66" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="68" t="inlineStr">
+      <c r="A113" s="67" t="inlineStr">
         <is>
           <t>PS5-53-03 - Water Softener Package</t>
         </is>
@@ -14114,7 +14093,7 @@
         </is>
       </c>
       <c r="H113" s="24" t="inlineStr"/>
-      <c r="I113" s="69" t="inlineStr">
+      <c r="I113" s="68" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -14197,10 +14176,10 @@
         </is>
       </c>
       <c r="AS113" s="23" t="n"/>
-      <c r="AT113" s="67" t="inlineStr"/>
+      <c r="AT113" s="66" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="68" t="inlineStr">
+      <c r="A114" s="67" t="inlineStr">
         <is>
           <t>PS5-53-04 - Water Treatment Purification Package</t>
         </is>
@@ -14232,7 +14211,7 @@
         </is>
       </c>
       <c r="H114" s="24" t="inlineStr"/>
-      <c r="I114" s="70" t="inlineStr">
+      <c r="I114" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14315,10 +14294,10 @@
         </is>
       </c>
       <c r="AS114" s="23" t="n"/>
-      <c r="AT114" s="67" t="inlineStr"/>
+      <c r="AT114" s="66" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="68" t="inlineStr">
+      <c r="A115" s="67" t="inlineStr">
         <is>
           <t>PS5-53-05 - Water Distribution Header</t>
         </is>
@@ -14433,10 +14412,10 @@
         </is>
       </c>
       <c r="AS115" s="23" t="n"/>
-      <c r="AT115" s="67" t="inlineStr"/>
+      <c r="AT115" s="66" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="68" t="inlineStr">
+      <c r="A116" s="67" t="inlineStr">
         <is>
           <t>PS5-53-06 - Water Distribution Consumers</t>
         </is>
@@ -14472,7 +14451,7 @@
         </is>
       </c>
       <c r="H116" s="24" t="inlineStr"/>
-      <c r="I116" s="69" t="inlineStr">
+      <c r="I116" s="68" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -14555,7 +14534,7 @@
         </is>
       </c>
       <c r="AS116" s="23" t="n"/>
-      <c r="AT116" s="67" t="inlineStr"/>
+      <c r="AT116" s="66" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="53" t="inlineStr">
@@ -14681,7 +14660,7 @@
         </is>
       </c>
       <c r="AS117" s="23" t="n"/>
-      <c r="AT117" s="67" t="inlineStr"/>
+      <c r="AT117" s="66" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="53" t="inlineStr">
@@ -14803,14 +14782,14 @@
       </c>
       <c r="AR118" s="23" t="inlineStr">
         <is>
-          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS118" s="23" t="n"/>
-      <c r="AT118" s="67" t="inlineStr"/>
+      <c r="AT118" s="66" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="68" t="inlineStr">
+      <c r="A119" s="67" t="inlineStr">
         <is>
           <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -14850,7 +14829,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I119" s="69" t="inlineStr">
+      <c r="I119" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -14882,7 +14861,7 @@
       <c r="R119" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S119" s="71" t="inlineStr">
+      <c r="S119" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -14933,7 +14912,7 @@
         </is>
       </c>
       <c r="AS119" s="23" t="n"/>
-      <c r="AT119" s="67" t="inlineStr"/>
+      <c r="AT119" s="66" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="53" t="inlineStr">
@@ -15059,10 +15038,10 @@
         </is>
       </c>
       <c r="AS120" s="23" t="n"/>
-      <c r="AT120" s="67" t="inlineStr"/>
+      <c r="AT120" s="66" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="68" t="inlineStr">
+      <c r="A121" s="67" t="inlineStr">
         <is>
           <t>PS5-60-05 - Power Gen Package B (UCP)</t>
         </is>
@@ -15134,7 +15113,7 @@
       <c r="R121" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="S121" s="71" t="inlineStr">
+      <c r="S121" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15177,10 +15156,10 @@
       <c r="AQ121" s="65" t="inlineStr"/>
       <c r="AR121" s="23" t="inlineStr"/>
       <c r="AS121" s="23" t="n"/>
-      <c r="AT121" s="67" t="inlineStr"/>
+      <c r="AT121" s="66" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="68" t="inlineStr">
+      <c r="A122" s="67" t="inlineStr">
         <is>
           <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -15220,7 +15199,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I122" s="69" t="inlineStr">
+      <c r="I122" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -15252,7 +15231,7 @@
       <c r="R122" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S122" s="71" t="inlineStr">
+      <c r="S122" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15295,10 +15274,10 @@
       <c r="AQ122" s="65" t="inlineStr"/>
       <c r="AR122" s="23" t="inlineStr"/>
       <c r="AS122" s="23" t="n"/>
-      <c r="AT122" s="67" t="inlineStr"/>
+      <c r="AT122" s="66" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="68" t="inlineStr">
+      <c r="A123" s="67" t="inlineStr">
         <is>
           <t>PS5-60-07 - Power Generation Package C</t>
         </is>
@@ -15423,10 +15402,10 @@
         </is>
       </c>
       <c r="AS123" s="23" t="n"/>
-      <c r="AT123" s="67" t="inlineStr"/>
+      <c r="AT123" s="66" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="68" t="inlineStr">
+      <c r="A124" s="67" t="inlineStr">
         <is>
           <t>PS5-60-08 - Power Gen Package C (UCP)</t>
         </is>
@@ -15498,7 +15477,7 @@
       <c r="R124" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="S124" s="71" t="inlineStr">
+      <c r="S124" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15541,10 +15520,10 @@
       <c r="AQ124" s="65" t="inlineStr"/>
       <c r="AR124" s="23" t="inlineStr"/>
       <c r="AS124" s="23" t="n"/>
-      <c r="AT124" s="67" t="inlineStr"/>
+      <c r="AT124" s="66" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="68" t="inlineStr">
+      <c r="A125" s="67" t="inlineStr">
         <is>
           <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -15584,7 +15563,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I125" s="69" t="inlineStr">
+      <c r="I125" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -15616,7 +15595,7 @@
       <c r="R125" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S125" s="71" t="inlineStr">
+      <c r="S125" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15659,10 +15638,10 @@
       <c r="AQ125" s="65" t="inlineStr"/>
       <c r="AR125" s="23" t="inlineStr"/>
       <c r="AS125" s="23" t="n"/>
-      <c r="AT125" s="67" t="inlineStr"/>
+      <c r="AT125" s="66" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="68" t="inlineStr">
+      <c r="A126" s="67" t="inlineStr">
         <is>
           <t>PS5-60-10 - Power Generation Package D</t>
         </is>
@@ -15734,7 +15713,7 @@
       <c r="R126" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="S126" s="71" t="inlineStr">
+      <c r="S126" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15785,10 +15764,10 @@
         </is>
       </c>
       <c r="AS126" s="23" t="n"/>
-      <c r="AT126" s="67" t="inlineStr"/>
+      <c r="AT126" s="66" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="68" t="inlineStr">
+      <c r="A127" s="67" t="inlineStr">
         <is>
           <t>PS5-60-11 - Power Gen Package D (UCP)</t>
         </is>
@@ -15860,7 +15839,7 @@
       <c r="R127" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="S127" s="71" t="inlineStr">
+      <c r="S127" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15903,10 +15882,10 @@
       <c r="AQ127" s="65" t="inlineStr"/>
       <c r="AR127" s="23" t="inlineStr"/>
       <c r="AS127" s="23" t="n"/>
-      <c r="AT127" s="67" t="inlineStr"/>
+      <c r="AT127" s="66" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="68" t="inlineStr">
+      <c r="A128" s="67" t="inlineStr">
         <is>
           <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -15946,7 +15925,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I128" s="69" t="inlineStr">
+      <c r="I128" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -15978,7 +15957,7 @@
       <c r="R128" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S128" s="71" t="inlineStr">
+      <c r="S128" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16021,10 +16000,10 @@
       <c r="AQ128" s="65" t="inlineStr"/>
       <c r="AR128" s="23" t="inlineStr"/>
       <c r="AS128" s="23" t="n"/>
-      <c r="AT128" s="67" t="inlineStr"/>
+      <c r="AT128" s="66" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="68" t="inlineStr">
+      <c r="A129" s="67" t="inlineStr">
         <is>
           <t>PS5-60-13 - Power Generation Package E</t>
         </is>
@@ -16147,10 +16126,10 @@
         </is>
       </c>
       <c r="AS129" s="23" t="n"/>
-      <c r="AT129" s="67" t="inlineStr"/>
+      <c r="AT129" s="66" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="68" t="inlineStr">
+      <c r="A130" s="67" t="inlineStr">
         <is>
           <t>PS5-60-14 - Power Gen Package E (UCP)</t>
         </is>
@@ -16222,7 +16201,7 @@
       <c r="R130" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="S130" s="71" t="inlineStr">
+      <c r="S130" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16265,10 +16244,10 @@
       <c r="AQ130" s="65" t="inlineStr"/>
       <c r="AR130" s="23" t="inlineStr"/>
       <c r="AS130" s="23" t="n"/>
-      <c r="AT130" s="67" t="inlineStr"/>
+      <c r="AT130" s="66" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="68" t="inlineStr">
+      <c r="A131" s="67" t="inlineStr">
         <is>
           <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -16308,7 +16287,7 @@
           <t>full</t>
         </is>
       </c>
-      <c r="I131" s="69" t="inlineStr">
+      <c r="I131" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -16340,7 +16319,7 @@
       <c r="R131" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S131" s="71" t="inlineStr">
+      <c r="S131" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16383,10 +16362,10 @@
       <c r="AQ131" s="65" t="inlineStr"/>
       <c r="AR131" s="23" t="inlineStr"/>
       <c r="AS131" s="23" t="n"/>
-      <c r="AT131" s="67" t="inlineStr"/>
+      <c r="AT131" s="66" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="68" t="inlineStr">
+      <c r="A132" s="67" t="inlineStr">
         <is>
           <t>PS5-60-16 - Power Generation Package F</t>
         </is>
@@ -16454,7 +16433,7 @@
       <c r="R132" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="S132" s="71" t="inlineStr">
+      <c r="S132" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16505,10 +16484,10 @@
         </is>
       </c>
       <c r="AS132" s="23" t="n"/>
-      <c r="AT132" s="67" t="inlineStr"/>
+      <c r="AT132" s="66" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="68" t="inlineStr">
+      <c r="A133" s="67" t="inlineStr">
         <is>
           <t>PS5-60-17 - Power Gen Package F (UCP)</t>
         </is>
@@ -16540,7 +16519,7 @@
         </is>
       </c>
       <c r="H133" s="24" t="inlineStr"/>
-      <c r="I133" s="69" t="inlineStr">
+      <c r="I133" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -16572,7 +16551,7 @@
       <c r="R133" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="S133" s="71" t="inlineStr">
+      <c r="S133" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16615,10 +16594,10 @@
       <c r="AQ133" s="65" t="inlineStr"/>
       <c r="AR133" s="23" t="inlineStr"/>
       <c r="AS133" s="23" t="n"/>
-      <c r="AT133" s="67" t="inlineStr"/>
+      <c r="AT133" s="66" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="68" t="inlineStr">
+      <c r="A134" s="67" t="inlineStr">
         <is>
           <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -16654,7 +16633,7 @@
         </is>
       </c>
       <c r="H134" s="24" t="inlineStr"/>
-      <c r="I134" s="69" t="inlineStr">
+      <c r="I134" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -16686,7 +16665,7 @@
       <c r="R134" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S134" s="71" t="inlineStr">
+      <c r="S134" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16729,10 +16708,10 @@
       <c r="AQ134" s="65" t="inlineStr"/>
       <c r="AR134" s="23" t="inlineStr"/>
       <c r="AS134" s="23" t="n"/>
-      <c r="AT134" s="67" t="inlineStr"/>
+      <c r="AT134" s="66" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="68" t="inlineStr">
+      <c r="A135" s="67" t="inlineStr">
         <is>
           <t>PS5-60-19 - Power Generation Package G</t>
         </is>
@@ -16847,10 +16826,10 @@
         </is>
       </c>
       <c r="AS135" s="23" t="n"/>
-      <c r="AT135" s="67" t="inlineStr"/>
+      <c r="AT135" s="66" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="68" t="inlineStr">
+      <c r="A136" s="67" t="inlineStr">
         <is>
           <t>PS5-60-20 - Power Gen Package G (UCP)</t>
         </is>
@@ -16886,7 +16865,7 @@
         </is>
       </c>
       <c r="H136" s="24" t="inlineStr"/>
-      <c r="I136" s="69" t="inlineStr">
+      <c r="I136" s="68" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -16918,7 +16897,7 @@
       <c r="R136" s="62" t="n">
         <v>3</v>
       </c>
-      <c r="S136" s="71" t="inlineStr">
+      <c r="S136" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16961,10 +16940,10 @@
       <c r="AQ136" s="65" t="inlineStr"/>
       <c r="AR136" s="23" t="inlineStr"/>
       <c r="AS136" s="23" t="n"/>
-      <c r="AT136" s="67" t="inlineStr"/>
+      <c r="AT136" s="66" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="68" t="inlineStr">
+      <c r="A137" s="67" t="inlineStr">
         <is>
           <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -17000,7 +16979,7 @@
         </is>
       </c>
       <c r="H137" s="24" t="inlineStr"/>
-      <c r="I137" s="69" t="inlineStr">
+      <c r="I137" s="68" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -17032,7 +17011,7 @@
       <c r="R137" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S137" s="71" t="inlineStr">
+      <c r="S137" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -17075,10 +17054,10 @@
       <c r="AQ137" s="65" t="inlineStr"/>
       <c r="AR137" s="23" t="inlineStr"/>
       <c r="AS137" s="23" t="n"/>
-      <c r="AT137" s="67" t="inlineStr"/>
+      <c r="AT137" s="66" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="68" t="inlineStr">
+      <c r="A138" s="67" t="inlineStr">
         <is>
           <t>PS5-60-22 - Power Gen Master UCP</t>
         </is>
@@ -17118,7 +17097,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I138" s="69" t="inlineStr">
+      <c r="I138" s="68" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -17150,7 +17129,7 @@
       <c r="R138" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="S138" s="71" t="inlineStr">
+      <c r="S138" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -17203,7 +17182,7 @@
         </is>
       </c>
       <c r="AS138" s="23" t="n"/>
-      <c r="AT138" s="67" t="inlineStr"/>
+      <c r="AT138" s="66" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="53" t="inlineStr">
@@ -17325,10 +17304,10 @@
         </is>
       </c>
       <c r="AS139" s="23" t="n"/>
-      <c r="AT139" s="67" t="inlineStr"/>
+      <c r="AT139" s="66" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="68" t="inlineStr">
+      <c r="A140" s="67" t="inlineStr">
         <is>
           <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
         </is>
@@ -17451,10 +17430,10 @@
         </is>
       </c>
       <c r="AS140" s="23" t="n"/>
-      <c r="AT140" s="67" t="inlineStr"/>
+      <c r="AT140" s="66" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="68" t="inlineStr">
+      <c r="A141" s="67" t="inlineStr">
         <is>
           <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
         </is>
@@ -17577,7 +17556,7 @@
         </is>
       </c>
       <c r="AS141" s="23" t="n"/>
-      <c r="AT141" s="67" t="inlineStr"/>
+      <c r="AT141" s="66" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="53" t="inlineStr">
@@ -17703,7 +17682,7 @@
         </is>
       </c>
       <c r="AS142" s="23" t="n"/>
-      <c r="AT142" s="67" t="inlineStr"/>
+      <c r="AT142" s="66" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="53" t="inlineStr">
@@ -17829,10 +17808,10 @@
         </is>
       </c>
       <c r="AS143" s="23" t="n"/>
-      <c r="AT143" s="67" t="inlineStr"/>
+      <c r="AT143" s="66" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="74" t="inlineStr">
+      <c r="A144" s="73" t="inlineStr">
         <is>
           <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
@@ -17862,7 +17841,7 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="G144" s="69" t="inlineStr">
+      <c r="G144" s="68" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -17955,7 +17934,7 @@
         </is>
       </c>
       <c r="AS144" s="23" t="n"/>
-      <c r="AT144" s="67" t="inlineStr"/>
+      <c r="AT144" s="66" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="53" t="inlineStr">
@@ -18081,7 +18060,7 @@
         </is>
       </c>
       <c r="AS145" s="23" t="n"/>
-      <c r="AT145" s="67" t="inlineStr"/>
+      <c r="AT145" s="66" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="53" t="inlineStr">
@@ -18207,7 +18186,7 @@
         </is>
       </c>
       <c r="AS146" s="23" t="n"/>
-      <c r="AT146" s="67" t="inlineStr"/>
+      <c r="AT146" s="66" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="53" t="inlineStr">
@@ -18333,7 +18312,7 @@
         </is>
       </c>
       <c r="AS147" s="23" t="n"/>
-      <c r="AT147" s="67" t="inlineStr"/>
+      <c r="AT147" s="66" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="53" t="inlineStr">
@@ -18459,7 +18438,7 @@
         </is>
       </c>
       <c r="AS148" s="23" t="n"/>
-      <c r="AT148" s="67" t="inlineStr"/>
+      <c r="AT148" s="66" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="53" t="inlineStr">
@@ -18585,7 +18564,7 @@
         </is>
       </c>
       <c r="AS149" s="23" t="n"/>
-      <c r="AT149" s="67" t="inlineStr"/>
+      <c r="AT149" s="66" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="53" t="inlineStr">
@@ -18711,10 +18690,10 @@
         </is>
       </c>
       <c r="AS150" s="23" t="n"/>
-      <c r="AT150" s="67" t="inlineStr"/>
+      <c r="AT150" s="66" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="75" t="inlineStr">
+      <c r="A151" s="74" t="inlineStr">
         <is>
           <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
@@ -18833,7 +18812,7 @@
         </is>
       </c>
       <c r="AS151" s="23" t="n"/>
-      <c r="AT151" s="67" t="inlineStr"/>
+      <c r="AT151" s="66" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="53" t="inlineStr">
@@ -18955,7 +18934,7 @@
         </is>
       </c>
       <c r="AS152" s="23" t="n"/>
-      <c r="AT152" s="67" t="inlineStr"/>
+      <c r="AT152" s="66" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="53" t="inlineStr">
@@ -19081,7 +19060,7 @@
         </is>
       </c>
       <c r="AS153" s="23" t="n"/>
-      <c r="AT153" s="67" t="inlineStr"/>
+      <c r="AT153" s="66" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="53" t="inlineStr">
@@ -19207,7 +19186,7 @@
         </is>
       </c>
       <c r="AS154" s="23" t="n"/>
-      <c r="AT154" s="67" t="inlineStr"/>
+      <c r="AT154" s="66" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="53" t="inlineStr">
@@ -19333,7 +19312,7 @@
         </is>
       </c>
       <c r="AS155" s="23" t="n"/>
-      <c r="AT155" s="67" t="inlineStr"/>
+      <c r="AT155" s="66" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="53" t="inlineStr">
@@ -19459,10 +19438,10 @@
         </is>
       </c>
       <c r="AS156" s="23" t="n"/>
-      <c r="AT156" s="67" t="inlineStr"/>
+      <c r="AT156" s="66" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="68" t="inlineStr">
+      <c r="A157" s="67" t="inlineStr">
         <is>
           <t>PS5-60-41 - Injector Tip Cooling Module G</t>
         </is>
@@ -19498,7 +19477,7 @@
         </is>
       </c>
       <c r="H157" s="24" t="inlineStr"/>
-      <c r="I157" s="69" t="inlineStr">
+      <c r="I157" s="68" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -19581,10 +19560,10 @@
         </is>
       </c>
       <c r="AS157" s="23" t="n"/>
-      <c r="AT157" s="67" t="inlineStr"/>
+      <c r="AT157" s="66" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="75" t="inlineStr">
+      <c r="A158" s="74" t="inlineStr">
         <is>
           <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
@@ -19703,7 +19682,7 @@
         </is>
       </c>
       <c r="AS158" s="23" t="n"/>
-      <c r="AT158" s="67" t="inlineStr"/>
+      <c r="AT158" s="66" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="53" t="inlineStr">
@@ -19825,7 +19804,7 @@
         </is>
       </c>
       <c r="AS159" s="23" t="n"/>
-      <c r="AT159" s="67" t="inlineStr"/>
+      <c r="AT159" s="66" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="53" t="inlineStr">
@@ -19951,7 +19930,7 @@
         </is>
       </c>
       <c r="AS160" s="23" t="n"/>
-      <c r="AT160" s="67" t="inlineStr"/>
+      <c r="AT160" s="66" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="53" t="inlineStr">
@@ -20077,7 +20056,7 @@
         </is>
       </c>
       <c r="AS161" s="23" t="n"/>
-      <c r="AT161" s="67" t="inlineStr"/>
+      <c r="AT161" s="66" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="53" t="inlineStr">
@@ -20199,7 +20178,7 @@
         </is>
       </c>
       <c r="AS162" s="23" t="n"/>
-      <c r="AT162" s="67" t="inlineStr"/>
+      <c r="AT162" s="66" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="53" t="inlineStr">
@@ -20325,10 +20304,10 @@
         </is>
       </c>
       <c r="AS163" s="23" t="n"/>
-      <c r="AT163" s="67" t="inlineStr"/>
+      <c r="AT163" s="66" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="68" t="inlineStr">
+      <c r="A164" s="67" t="inlineStr">
         <is>
           <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
         </is>
@@ -20443,10 +20422,10 @@
         </is>
       </c>
       <c r="AS164" s="23" t="n"/>
-      <c r="AT164" s="67" t="inlineStr"/>
+      <c r="AT164" s="66" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="68" t="inlineStr">
+      <c r="A165" s="67" t="inlineStr">
         <is>
           <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
         </is>
@@ -20518,7 +20497,7 @@
       <c r="R165" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S165" s="71" t="inlineStr">
+      <c r="S165" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -20559,16 +20538,12 @@
       </c>
       <c r="AP165" s="65" t="inlineStr"/>
       <c r="AQ165" s="65" t="inlineStr"/>
-      <c r="AR165" s="23" t="inlineStr">
-        <is>
-          <t>OBSERVATION -CLEANING ON PROGRESS</t>
-        </is>
-      </c>
+      <c r="AR165" s="23" t="inlineStr"/>
       <c r="AS165" s="23" t="n"/>
-      <c r="AT165" s="67" t="inlineStr"/>
+      <c r="AT165" s="66" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="68" t="inlineStr">
+      <c r="A166" s="67" t="inlineStr">
         <is>
           <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
         </is>
@@ -20640,7 +20615,7 @@
       <c r="R166" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S166" s="71" t="inlineStr">
+      <c r="S166" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -20683,10 +20658,10 @@
       <c r="AQ166" s="65" t="inlineStr"/>
       <c r="AR166" s="23" t="inlineStr"/>
       <c r="AS166" s="23" t="n"/>
-      <c r="AT166" s="67" t="inlineStr"/>
+      <c r="AT166" s="66" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="68" t="inlineStr">
+      <c r="A167" s="67" t="inlineStr">
         <is>
           <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
         </is>
@@ -20758,7 +20733,7 @@
       <c r="R167" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S167" s="71" t="inlineStr">
+      <c r="S167" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -20801,10 +20776,10 @@
       <c r="AQ167" s="65" t="inlineStr"/>
       <c r="AR167" s="23" t="inlineStr"/>
       <c r="AS167" s="23" t="n"/>
-      <c r="AT167" s="67" t="inlineStr"/>
+      <c r="AT167" s="66" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="68" t="inlineStr">
+      <c r="A168" s="67" t="inlineStr">
         <is>
           <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
         </is>
@@ -20844,7 +20819,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I168" s="69" t="inlineStr">
+      <c r="I168" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -20876,7 +20851,7 @@
       <c r="R168" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S168" s="71" t="inlineStr">
+      <c r="S168" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -20919,10 +20894,10 @@
       <c r="AQ168" s="65" t="inlineStr"/>
       <c r="AR168" s="23" t="inlineStr"/>
       <c r="AS168" s="23" t="n"/>
-      <c r="AT168" s="67" t="inlineStr"/>
+      <c r="AT168" s="66" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="68" t="inlineStr">
+      <c r="A169" s="67" t="inlineStr">
         <is>
           <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
         </is>
@@ -20986,7 +20961,7 @@
       <c r="R169" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S169" s="71" t="inlineStr">
+      <c r="S169" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21029,10 +21004,10 @@
       <c r="AQ169" s="65" t="inlineStr"/>
       <c r="AR169" s="23" t="inlineStr"/>
       <c r="AS169" s="23" t="n"/>
-      <c r="AT169" s="67" t="inlineStr"/>
+      <c r="AT169" s="66" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="68" t="inlineStr">
+      <c r="A170" s="67" t="inlineStr">
         <is>
           <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
         </is>
@@ -21096,7 +21071,7 @@
       <c r="R170" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S170" s="71" t="inlineStr">
+      <c r="S170" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21139,10 +21114,10 @@
       <c r="AQ170" s="65" t="inlineStr"/>
       <c r="AR170" s="23" t="inlineStr"/>
       <c r="AS170" s="23" t="n"/>
-      <c r="AT170" s="67" t="inlineStr"/>
+      <c r="AT170" s="66" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="68" t="inlineStr">
+      <c r="A171" s="67" t="inlineStr">
         <is>
           <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
         </is>
@@ -21174,7 +21149,7 @@
         </is>
       </c>
       <c r="H171" s="24" t="inlineStr"/>
-      <c r="I171" s="69" t="inlineStr">
+      <c r="I171" s="68" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -21206,7 +21181,7 @@
       <c r="R171" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S171" s="71" t="inlineStr">
+      <c r="S171" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21249,7 +21224,7 @@
       <c r="AQ171" s="65" t="inlineStr"/>
       <c r="AR171" s="23" t="inlineStr"/>
       <c r="AS171" s="23" t="n"/>
-      <c r="AT171" s="67" t="inlineStr"/>
+      <c r="AT171" s="66" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="53" t="inlineStr">
@@ -21367,10 +21342,10 @@
       <c r="AQ172" s="65" t="inlineStr"/>
       <c r="AR172" s="23" t="inlineStr"/>
       <c r="AS172" s="23" t="n"/>
-      <c r="AT172" s="67" t="inlineStr"/>
+      <c r="AT172" s="66" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="68" t="inlineStr">
+      <c r="A173" s="67" t="inlineStr">
         <is>
           <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
         </is>
@@ -21442,7 +21417,7 @@
       <c r="R173" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S173" s="71" t="inlineStr">
+      <c r="S173" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21485,7 +21460,7 @@
       <c r="AQ173" s="65" t="inlineStr"/>
       <c r="AR173" s="23" t="inlineStr"/>
       <c r="AS173" s="23" t="n"/>
-      <c r="AT173" s="67" t="inlineStr"/>
+      <c r="AT173" s="66" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="53" t="inlineStr">
@@ -21603,10 +21578,10 @@
       <c r="AQ174" s="65" t="inlineStr"/>
       <c r="AR174" s="23" t="inlineStr"/>
       <c r="AS174" s="23" t="n"/>
-      <c r="AT174" s="67" t="inlineStr"/>
+      <c r="AT174" s="66" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="68" t="inlineStr">
+      <c r="A175" s="67" t="inlineStr">
         <is>
           <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
         </is>
@@ -21678,7 +21653,7 @@
       <c r="R175" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S175" s="71" t="inlineStr">
+      <c r="S175" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21721,7 +21696,7 @@
       <c r="AQ175" s="65" t="inlineStr"/>
       <c r="AR175" s="23" t="inlineStr"/>
       <c r="AS175" s="23" t="n"/>
-      <c r="AT175" s="67" t="inlineStr"/>
+      <c r="AT175" s="66" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="53" t="inlineStr">
@@ -21839,10 +21814,10 @@
       <c r="AQ176" s="65" t="inlineStr"/>
       <c r="AR176" s="23" t="inlineStr"/>
       <c r="AS176" s="23" t="n"/>
-      <c r="AT176" s="67" t="inlineStr"/>
+      <c r="AT176" s="66" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="68" t="inlineStr">
+      <c r="A177" s="67" t="inlineStr">
         <is>
           <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
         </is>
@@ -21914,7 +21889,7 @@
       <c r="R177" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S177" s="71" t="inlineStr">
+      <c r="S177" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21957,7 +21932,7 @@
       <c r="AQ177" s="65" t="inlineStr"/>
       <c r="AR177" s="23" t="inlineStr"/>
       <c r="AS177" s="23" t="n"/>
-      <c r="AT177" s="67" t="inlineStr"/>
+      <c r="AT177" s="66" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="53" t="inlineStr">
@@ -22075,10 +22050,10 @@
       <c r="AQ178" s="65" t="inlineStr"/>
       <c r="AR178" s="23" t="inlineStr"/>
       <c r="AS178" s="23" t="n"/>
-      <c r="AT178" s="67" t="inlineStr"/>
+      <c r="AT178" s="66" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="68" t="inlineStr">
+      <c r="A179" s="67" t="inlineStr">
         <is>
           <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
         </is>
@@ -22150,7 +22125,7 @@
       <c r="R179" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S179" s="71" t="inlineStr">
+      <c r="S179" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -22193,10 +22168,10 @@
       <c r="AQ179" s="65" t="inlineStr"/>
       <c r="AR179" s="23" t="inlineStr"/>
       <c r="AS179" s="23" t="n"/>
-      <c r="AT179" s="67" t="inlineStr"/>
+      <c r="AT179" s="66" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="68" t="inlineStr">
+      <c r="A180" s="67" t="inlineStr">
         <is>
           <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
         </is>
@@ -22311,10 +22286,10 @@
         </is>
       </c>
       <c r="AS180" s="23" t="n"/>
-      <c r="AT180" s="67" t="inlineStr"/>
+      <c r="AT180" s="66" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="68" t="inlineStr">
+      <c r="A181" s="67" t="inlineStr">
         <is>
           <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
         </is>
@@ -22350,7 +22325,7 @@
         </is>
       </c>
       <c r="H181" s="24" t="inlineStr"/>
-      <c r="I181" s="69" t="inlineStr">
+      <c r="I181" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -22382,7 +22357,7 @@
       <c r="R181" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S181" s="71" t="inlineStr">
+      <c r="S181" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -22425,10 +22400,10 @@
       <c r="AQ181" s="65" t="inlineStr"/>
       <c r="AR181" s="23" t="inlineStr"/>
       <c r="AS181" s="23" t="n"/>
-      <c r="AT181" s="67" t="inlineStr"/>
+      <c r="AT181" s="66" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="68" t="inlineStr">
+      <c r="A182" s="67" t="inlineStr">
         <is>
           <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
         </is>
@@ -22543,10 +22518,10 @@
         </is>
       </c>
       <c r="AS182" s="23" t="n"/>
-      <c r="AT182" s="67" t="inlineStr"/>
+      <c r="AT182" s="66" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="68" t="inlineStr">
+      <c r="A183" s="67" t="inlineStr">
         <is>
           <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
         </is>
@@ -22582,7 +22557,7 @@
         </is>
       </c>
       <c r="H183" s="24" t="inlineStr"/>
-      <c r="I183" s="69" t="inlineStr">
+      <c r="I183" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -22614,7 +22589,7 @@
       <c r="R183" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S183" s="71" t="inlineStr">
+      <c r="S183" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -22657,10 +22632,10 @@
       <c r="AQ183" s="65" t="inlineStr"/>
       <c r="AR183" s="23" t="inlineStr"/>
       <c r="AS183" s="23" t="n"/>
-      <c r="AT183" s="67" t="inlineStr"/>
+      <c r="AT183" s="66" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="68" t="inlineStr">
+      <c r="A184" s="67" t="inlineStr">
         <is>
           <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
         </is>
@@ -22692,7 +22667,7 @@
         </is>
       </c>
       <c r="H184" s="24" t="inlineStr"/>
-      <c r="I184" s="69" t="inlineStr">
+      <c r="I184" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -22775,10 +22750,10 @@
         </is>
       </c>
       <c r="AS184" s="23" t="n"/>
-      <c r="AT184" s="67" t="inlineStr"/>
+      <c r="AT184" s="66" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="68" t="inlineStr">
+      <c r="A185" s="67" t="inlineStr">
         <is>
           <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
         </is>
@@ -22814,7 +22789,7 @@
         </is>
       </c>
       <c r="H185" s="24" t="inlineStr"/>
-      <c r="I185" s="69" t="inlineStr">
+      <c r="I185" s="68" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -22846,7 +22821,7 @@
       <c r="R185" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S185" s="71" t="inlineStr">
+      <c r="S185" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -22889,7 +22864,7 @@
       <c r="AQ185" s="65" t="inlineStr"/>
       <c r="AR185" s="23" t="inlineStr"/>
       <c r="AS185" s="23" t="n"/>
-      <c r="AT185" s="67" t="inlineStr"/>
+      <c r="AT185" s="66" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="53" t="inlineStr">
@@ -23015,7 +22990,7 @@
         </is>
       </c>
       <c r="AS186" s="23" t="n"/>
-      <c r="AT186" s="67" t="inlineStr"/>
+      <c r="AT186" s="66" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="53" t="inlineStr">
@@ -23141,7 +23116,7 @@
         </is>
       </c>
       <c r="AS187" s="23" t="n"/>
-      <c r="AT187" s="67" t="inlineStr"/>
+      <c r="AT187" s="66" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="53" t="inlineStr">
@@ -23267,7 +23242,7 @@
         </is>
       </c>
       <c r="AS188" s="23" t="n"/>
-      <c r="AT188" s="67" t="inlineStr"/>
+      <c r="AT188" s="66" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="53" t="inlineStr">
@@ -23393,7 +23368,7 @@
         </is>
       </c>
       <c r="AS189" s="23" t="n"/>
-      <c r="AT189" s="67" t="inlineStr"/>
+      <c r="AT189" s="66" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="53" t="inlineStr">
@@ -23519,7 +23494,7 @@
         </is>
       </c>
       <c r="AS190" s="23" t="n"/>
-      <c r="AT190" s="67" t="inlineStr"/>
+      <c r="AT190" s="66" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="53" t="inlineStr">
@@ -23645,10 +23620,10 @@
         </is>
       </c>
       <c r="AS191" s="23" t="n"/>
-      <c r="AT191" s="67" t="inlineStr"/>
+      <c r="AT191" s="66" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="68" t="inlineStr">
+      <c r="A192" s="67" t="inlineStr">
         <is>
           <t>PS5-60-76 - Engine G Cooling system</t>
         </is>
@@ -23763,10 +23738,10 @@
         </is>
       </c>
       <c r="AS192" s="23" t="n"/>
-      <c r="AT192" s="67" t="inlineStr"/>
+      <c r="AT192" s="66" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="68" t="inlineStr">
+      <c r="A193" s="67" t="inlineStr">
         <is>
           <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
         </is>
@@ -23891,10 +23866,10 @@
         </is>
       </c>
       <c r="AS193" s="23" t="n"/>
-      <c r="AT193" s="67" t="inlineStr"/>
+      <c r="AT193" s="66" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="68" t="inlineStr">
+      <c r="A194" s="67" t="inlineStr">
         <is>
           <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
         </is>
@@ -23926,7 +23901,7 @@
         </is>
       </c>
       <c r="H194" s="24" t="inlineStr"/>
-      <c r="I194" s="69" t="inlineStr">
+      <c r="I194" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -24009,10 +23984,10 @@
         </is>
       </c>
       <c r="AS194" s="23" t="n"/>
-      <c r="AT194" s="67" t="inlineStr"/>
+      <c r="AT194" s="66" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="68" t="inlineStr">
+      <c r="A195" s="67" t="inlineStr">
         <is>
           <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
         </is>
@@ -24044,7 +24019,7 @@
         </is>
       </c>
       <c r="H195" s="24" t="inlineStr"/>
-      <c r="I195" s="69" t="inlineStr">
+      <c r="I195" s="68" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -24127,10 +24102,10 @@
         </is>
       </c>
       <c r="AS195" s="23" t="n"/>
-      <c r="AT195" s="67" t="inlineStr"/>
+      <c r="AT195" s="66" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="68" t="inlineStr">
+      <c r="A196" s="67" t="inlineStr">
         <is>
           <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
         </is>
@@ -24166,7 +24141,7 @@
         </is>
       </c>
       <c r="H196" s="24" t="inlineStr"/>
-      <c r="I196" s="70" t="inlineStr">
+      <c r="I196" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -24249,7 +24224,7 @@
         </is>
       </c>
       <c r="AS196" s="23" t="n"/>
-      <c r="AT196" s="67" t="inlineStr"/>
+      <c r="AT196" s="66" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="53" t="inlineStr">
@@ -24375,10 +24350,10 @@
         </is>
       </c>
       <c r="AS197" s="23" t="n"/>
-      <c r="AT197" s="67" t="inlineStr"/>
+      <c r="AT197" s="66" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="68" t="inlineStr">
+      <c r="A198" s="67" t="inlineStr">
         <is>
           <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
         </is>
@@ -24414,7 +24389,7 @@
         </is>
       </c>
       <c r="H198" s="24" t="inlineStr"/>
-      <c r="I198" s="69" t="inlineStr">
+      <c r="I198" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -24497,7 +24472,7 @@
         </is>
       </c>
       <c r="AS198" s="23" t="n"/>
-      <c r="AT198" s="67" t="inlineStr"/>
+      <c r="AT198" s="66" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="53" t="inlineStr">
@@ -24623,10 +24598,10 @@
         </is>
       </c>
       <c r="AS199" s="23" t="n"/>
-      <c r="AT199" s="67" t="inlineStr"/>
+      <c r="AT199" s="66" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="68" t="inlineStr">
+      <c r="A200" s="67" t="inlineStr">
         <is>
           <t>PS5-61-08 - Electrical Control System</t>
         </is>
@@ -24658,7 +24633,7 @@
         </is>
       </c>
       <c r="H200" s="24" t="inlineStr"/>
-      <c r="I200" s="70" t="inlineStr">
+      <c r="I200" s="69" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -24741,10 +24716,10 @@
         </is>
       </c>
       <c r="AS200" s="23" t="n"/>
-      <c r="AT200" s="67" t="inlineStr"/>
+      <c r="AT200" s="66" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="68" t="inlineStr">
+      <c r="A201" s="67" t="inlineStr">
         <is>
           <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
         </is>
@@ -24780,7 +24755,7 @@
         </is>
       </c>
       <c r="H201" s="24" t="inlineStr"/>
-      <c r="I201" s="70" t="inlineStr">
+      <c r="I201" s="69" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -24863,7 +24838,7 @@
         </is>
       </c>
       <c r="AS201" s="23" t="n"/>
-      <c r="AT201" s="67" t="inlineStr"/>
+      <c r="AT201" s="66" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="53" t="inlineStr">
@@ -24989,7 +24964,7 @@
         </is>
       </c>
       <c r="AS202" s="23" t="n"/>
-      <c r="AT202" s="67" t="inlineStr"/>
+      <c r="AT202" s="66" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="53" t="inlineStr">
@@ -25115,10 +25090,10 @@
         </is>
       </c>
       <c r="AS203" s="23" t="n"/>
-      <c r="AT203" s="67" t="inlineStr"/>
+      <c r="AT203" s="66" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="68" t="inlineStr">
+      <c r="A204" s="67" t="inlineStr">
         <is>
           <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
         </is>
@@ -25134,7 +25109,7 @@
         </is>
       </c>
       <c r="H204" s="24" t="inlineStr"/>
-      <c r="I204" s="70" t="inlineStr">
+      <c r="I204" s="69" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -25199,10 +25174,10 @@
       <c r="AQ204" s="65" t="inlineStr"/>
       <c r="AR204" s="23" t="inlineStr"/>
       <c r="AS204" s="23" t="n"/>
-      <c r="AT204" s="67" t="inlineStr"/>
+      <c r="AT204" s="66" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="68" t="inlineStr">
+      <c r="A205" s="67" t="inlineStr">
         <is>
           <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
         </is>
@@ -25234,7 +25209,7 @@
         </is>
       </c>
       <c r="H205" s="24" t="inlineStr"/>
-      <c r="I205" s="70" t="inlineStr">
+      <c r="I205" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -25317,10 +25292,10 @@
         </is>
       </c>
       <c r="AS205" s="23" t="n"/>
-      <c r="AT205" s="67" t="inlineStr"/>
+      <c r="AT205" s="66" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="68" t="inlineStr">
+      <c r="A206" s="67" t="inlineStr">
         <is>
           <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
         </is>
@@ -25352,7 +25327,7 @@
         </is>
       </c>
       <c r="H206" s="24" t="inlineStr"/>
-      <c r="I206" s="70" t="inlineStr">
+      <c r="I206" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -25435,10 +25410,10 @@
         </is>
       </c>
       <c r="AS206" s="23" t="n"/>
-      <c r="AT206" s="67" t="inlineStr"/>
+      <c r="AT206" s="66" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="68" t="inlineStr">
+      <c r="A207" s="67" t="inlineStr">
         <is>
           <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
         </is>
@@ -25470,7 +25445,7 @@
         </is>
       </c>
       <c r="H207" s="24" t="inlineStr"/>
-      <c r="I207" s="70" t="inlineStr">
+      <c r="I207" s="69" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -25553,10 +25528,10 @@
         </is>
       </c>
       <c r="AS207" s="23" t="n"/>
-      <c r="AT207" s="67" t="inlineStr"/>
+      <c r="AT207" s="66" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="68" t="inlineStr">
+      <c r="A208" s="67" t="inlineStr">
         <is>
           <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
         </is>
@@ -25588,7 +25563,7 @@
         </is>
       </c>
       <c r="H208" s="24" t="inlineStr"/>
-      <c r="I208" s="70" t="inlineStr">
+      <c r="I208" s="69" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -25671,10 +25646,10 @@
         </is>
       </c>
       <c r="AS208" s="23" t="n"/>
-      <c r="AT208" s="67" t="inlineStr"/>
+      <c r="AT208" s="66" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="68" t="inlineStr">
+      <c r="A209" s="67" t="inlineStr">
         <is>
           <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
         </is>
@@ -25706,7 +25681,7 @@
         </is>
       </c>
       <c r="H209" s="24" t="inlineStr"/>
-      <c r="I209" s="69" t="inlineStr">
+      <c r="I209" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -25789,7 +25764,7 @@
         </is>
       </c>
       <c r="AS209" s="23" t="n"/>
-      <c r="AT209" s="67" t="inlineStr"/>
+      <c r="AT209" s="66" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="53" t="inlineStr">
@@ -25915,10 +25890,10 @@
         </is>
       </c>
       <c r="AS210" s="23" t="n"/>
-      <c r="AT210" s="67" t="inlineStr"/>
+      <c r="AT210" s="66" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="68" t="inlineStr">
+      <c r="A211" s="67" t="inlineStr">
         <is>
           <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
         </is>
@@ -25950,7 +25925,7 @@
         </is>
       </c>
       <c r="H211" s="24" t="inlineStr"/>
-      <c r="I211" s="70" t="inlineStr">
+      <c r="I211" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -26033,10 +26008,10 @@
         </is>
       </c>
       <c r="AS211" s="23" t="n"/>
-      <c r="AT211" s="67" t="inlineStr"/>
+      <c r="AT211" s="66" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="68" t="inlineStr">
+      <c r="A212" s="67" t="inlineStr">
         <is>
           <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
         </is>
@@ -26076,7 +26051,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I212" s="70" t="inlineStr">
+      <c r="I212" s="69" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -26159,10 +26134,10 @@
         </is>
       </c>
       <c r="AS212" s="23" t="n"/>
-      <c r="AT212" s="67" t="inlineStr"/>
+      <c r="AT212" s="66" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="68" t="inlineStr">
+      <c r="A213" s="67" t="inlineStr">
         <is>
           <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
         </is>
@@ -26198,7 +26173,7 @@
         </is>
       </c>
       <c r="H213" s="24" t="inlineStr"/>
-      <c r="I213" s="70" t="inlineStr">
+      <c r="I213" s="69" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -26281,10 +26256,10 @@
         </is>
       </c>
       <c r="AS213" s="23" t="n"/>
-      <c r="AT213" s="67" t="inlineStr"/>
+      <c r="AT213" s="66" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="68" t="inlineStr">
+      <c r="A214" s="67" t="inlineStr">
         <is>
           <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
         </is>
@@ -26320,7 +26295,7 @@
         </is>
       </c>
       <c r="H214" s="24" t="inlineStr"/>
-      <c r="I214" s="70" t="inlineStr">
+      <c r="I214" s="69" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -26403,10 +26378,10 @@
         </is>
       </c>
       <c r="AS214" s="23" t="n"/>
-      <c r="AT214" s="67" t="inlineStr"/>
+      <c r="AT214" s="66" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="68" t="inlineStr">
+      <c r="A215" s="67" t="inlineStr">
         <is>
           <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
         </is>
@@ -26442,7 +26417,7 @@
         </is>
       </c>
       <c r="H215" s="24" t="inlineStr"/>
-      <c r="I215" s="70" t="inlineStr">
+      <c r="I215" s="69" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -26525,10 +26500,10 @@
         </is>
       </c>
       <c r="AS215" s="23" t="n"/>
-      <c r="AT215" s="67" t="inlineStr"/>
+      <c r="AT215" s="66" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="68" t="inlineStr">
+      <c r="A216" s="67" t="inlineStr">
         <is>
           <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
         </is>
@@ -26568,7 +26543,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I216" s="70" t="inlineStr">
+      <c r="I216" s="69" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -26651,10 +26626,10 @@
         </is>
       </c>
       <c r="AS216" s="23" t="n"/>
-      <c r="AT216" s="67" t="inlineStr"/>
+      <c r="AT216" s="66" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="68" t="inlineStr">
+      <c r="A217" s="67" t="inlineStr">
         <is>
           <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
         </is>
@@ -26690,7 +26665,7 @@
         </is>
       </c>
       <c r="H217" s="24" t="inlineStr"/>
-      <c r="I217" s="70" t="inlineStr">
+      <c r="I217" s="69" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -26773,10 +26748,10 @@
         </is>
       </c>
       <c r="AS217" s="23" t="n"/>
-      <c r="AT217" s="67" t="inlineStr"/>
+      <c r="AT217" s="66" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="68" t="inlineStr">
+      <c r="A218" s="67" t="inlineStr">
         <is>
           <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
         </is>
@@ -26857,10 +26832,10 @@
       <c r="AQ218" s="65" t="inlineStr"/>
       <c r="AR218" s="23" t="inlineStr"/>
       <c r="AS218" s="23" t="n"/>
-      <c r="AT218" s="67" t="inlineStr"/>
+      <c r="AT218" s="66" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="68" t="inlineStr">
+      <c r="A219" s="67" t="inlineStr">
         <is>
           <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
         </is>
@@ -26941,10 +26916,10 @@
       <c r="AQ219" s="65" t="inlineStr"/>
       <c r="AR219" s="23" t="inlineStr"/>
       <c r="AS219" s="23" t="n"/>
-      <c r="AT219" s="67" t="inlineStr"/>
+      <c r="AT219" s="66" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="68" t="inlineStr">
+      <c r="A220" s="67" t="inlineStr">
         <is>
           <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
         </is>
@@ -26976,7 +26951,7 @@
         </is>
       </c>
       <c r="H220" s="24" t="inlineStr"/>
-      <c r="I220" s="70" t="inlineStr">
+      <c r="I220" s="69" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -27059,10 +27034,10 @@
         </is>
       </c>
       <c r="AS220" s="23" t="n"/>
-      <c r="AT220" s="67" t="inlineStr"/>
+      <c r="AT220" s="66" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="68" t="inlineStr">
+      <c r="A221" s="67" t="inlineStr">
         <is>
           <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
         </is>
@@ -27094,7 +27069,7 @@
         </is>
       </c>
       <c r="H221" s="24" t="inlineStr"/>
-      <c r="I221" s="70" t="inlineStr">
+      <c r="I221" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -27177,10 +27152,10 @@
         </is>
       </c>
       <c r="AS221" s="23" t="n"/>
-      <c r="AT221" s="67" t="inlineStr"/>
+      <c r="AT221" s="66" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="68" t="inlineStr">
+      <c r="A222" s="67" t="inlineStr">
         <is>
           <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
         </is>
@@ -27212,7 +27187,7 @@
         </is>
       </c>
       <c r="H222" s="24" t="inlineStr"/>
-      <c r="I222" s="70" t="inlineStr">
+      <c r="I222" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -27295,10 +27270,10 @@
         </is>
       </c>
       <c r="AS222" s="23" t="n"/>
-      <c r="AT222" s="67" t="inlineStr"/>
+      <c r="AT222" s="66" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="68" t="inlineStr">
+      <c r="A223" s="67" t="inlineStr">
         <is>
           <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
         </is>
@@ -27330,7 +27305,7 @@
         </is>
       </c>
       <c r="H223" s="24" t="inlineStr"/>
-      <c r="I223" s="70" t="inlineStr">
+      <c r="I223" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -27413,10 +27388,10 @@
         </is>
       </c>
       <c r="AS223" s="23" t="n"/>
-      <c r="AT223" s="67" t="inlineStr"/>
+      <c r="AT223" s="66" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="68" t="inlineStr">
+      <c r="A224" s="67" t="inlineStr">
         <is>
           <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
         </is>
@@ -27448,7 +27423,7 @@
         </is>
       </c>
       <c r="H224" s="24" t="inlineStr"/>
-      <c r="I224" s="70" t="inlineStr">
+      <c r="I224" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -27531,10 +27506,10 @@
         </is>
       </c>
       <c r="AS224" s="23" t="n"/>
-      <c r="AT224" s="67" t="inlineStr"/>
+      <c r="AT224" s="66" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="68" t="inlineStr">
+      <c r="A225" s="67" t="inlineStr">
         <is>
           <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
         </is>
@@ -27566,7 +27541,7 @@
         </is>
       </c>
       <c r="H225" s="24" t="inlineStr"/>
-      <c r="I225" s="70" t="inlineStr">
+      <c r="I225" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -27649,10 +27624,10 @@
         </is>
       </c>
       <c r="AS225" s="23" t="n"/>
-      <c r="AT225" s="67" t="inlineStr"/>
+      <c r="AT225" s="66" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="68" t="inlineStr">
+      <c r="A226" s="67" t="inlineStr">
         <is>
           <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
         </is>
@@ -27684,7 +27659,7 @@
         </is>
       </c>
       <c r="H226" s="24" t="inlineStr"/>
-      <c r="I226" s="70" t="inlineStr">
+      <c r="I226" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -27767,10 +27742,10 @@
         </is>
       </c>
       <c r="AS226" s="23" t="n"/>
-      <c r="AT226" s="67" t="inlineStr"/>
+      <c r="AT226" s="66" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="68" t="inlineStr">
+      <c r="A227" s="67" t="inlineStr">
         <is>
           <t>PS5-63-01 - Electrical Earthing</t>
         </is>
@@ -27810,7 +27785,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I227" s="70" t="inlineStr">
+      <c r="I227" s="69" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -27884,7 +27859,7 @@
       <c r="AP227" s="65" t="inlineStr"/>
       <c r="AQ227" s="65" t="inlineStr">
         <is>
-          <t>18 ITRs for lightning, 22 ITRs for grounding cannot be closed due to material issues.</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR227" s="23" t="inlineStr">
@@ -27893,10 +27868,10 @@
         </is>
       </c>
       <c r="AS227" s="23" t="n"/>
-      <c r="AT227" s="67" t="inlineStr"/>
+      <c r="AT227" s="66" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="68" t="inlineStr">
+      <c r="A228" s="67" t="inlineStr">
         <is>
           <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
         </is>
@@ -27928,7 +27903,7 @@
         </is>
       </c>
       <c r="H228" s="24" t="inlineStr"/>
-      <c r="I228" s="70" t="inlineStr">
+      <c r="I228" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -28011,10 +27986,10 @@
         </is>
       </c>
       <c r="AS228" s="23" t="n"/>
-      <c r="AT228" s="67" t="inlineStr"/>
+      <c r="AT228" s="66" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="68" t="inlineStr">
+      <c r="A229" s="67" t="inlineStr">
         <is>
           <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
         </is>
@@ -28054,7 +28029,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I229" s="69" t="inlineStr">
+      <c r="I229" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -28137,7 +28112,7 @@
         </is>
       </c>
       <c r="AS229" s="23" t="n"/>
-      <c r="AT229" s="67" t="inlineStr"/>
+      <c r="AT229" s="66" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="53" t="inlineStr">
@@ -28221,10 +28196,10 @@
       <c r="AQ230" s="65" t="inlineStr"/>
       <c r="AR230" s="23" t="inlineStr"/>
       <c r="AS230" s="23" t="n"/>
-      <c r="AT230" s="67" t="inlineStr"/>
+      <c r="AT230" s="66" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="68" t="inlineStr">
+      <c r="A231" s="67" t="inlineStr">
         <is>
           <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
         </is>
@@ -28256,7 +28231,7 @@
         </is>
       </c>
       <c r="H231" s="24" t="inlineStr"/>
-      <c r="I231" s="70" t="inlineStr">
+      <c r="I231" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -28339,10 +28314,10 @@
         </is>
       </c>
       <c r="AS231" s="23" t="n"/>
-      <c r="AT231" s="67" t="inlineStr"/>
+      <c r="AT231" s="66" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="68" t="inlineStr">
+      <c r="A232" s="67" t="inlineStr">
         <is>
           <t>PS5-63-06 - Electrical Earthing - Guard House</t>
         </is>
@@ -28374,7 +28349,7 @@
         </is>
       </c>
       <c r="H232" s="24" t="inlineStr"/>
-      <c r="I232" s="70" t="inlineStr">
+      <c r="I232" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -28457,10 +28432,10 @@
         </is>
       </c>
       <c r="AS232" s="23" t="n"/>
-      <c r="AT232" s="67" t="inlineStr"/>
+      <c r="AT232" s="66" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="68" t="inlineStr">
+      <c r="A233" s="67" t="inlineStr">
         <is>
           <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
         </is>
@@ -28492,7 +28467,7 @@
         </is>
       </c>
       <c r="H233" s="24" t="inlineStr"/>
-      <c r="I233" s="70" t="inlineStr">
+      <c r="I233" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -28575,10 +28550,10 @@
         </is>
       </c>
       <c r="AS233" s="23" t="n"/>
-      <c r="AT233" s="67" t="inlineStr"/>
+      <c r="AT233" s="66" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="68" t="inlineStr">
+      <c r="A234" s="67" t="inlineStr">
         <is>
           <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
         </is>
@@ -28610,7 +28585,7 @@
         </is>
       </c>
       <c r="H234" s="24" t="inlineStr"/>
-      <c r="I234" s="70" t="inlineStr">
+      <c r="I234" s="69" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -28681,11 +28656,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP234" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP234" s="65" t="inlineStr"/>
       <c r="AQ234" s="65" t="inlineStr">
         <is>
           <t>PS5-71-TW-0007, PS5-71-TW-0003, PS5-71-TW-0004, PS5-71-TW-0006 not arrived</t>
@@ -28697,10 +28668,10 @@
         </is>
       </c>
       <c r="AS234" s="23" t="n"/>
-      <c r="AT234" s="67" t="inlineStr"/>
+      <c r="AT234" s="66" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="68" t="inlineStr">
+      <c r="A235" s="67" t="inlineStr">
         <is>
           <t>PS5-71-02 - CFO Allocation Metering Package</t>
         </is>
@@ -28732,7 +28703,7 @@
         </is>
       </c>
       <c r="H235" s="24" t="inlineStr"/>
-      <c r="I235" s="69" t="inlineStr">
+      <c r="I235" s="68" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -28815,10 +28786,10 @@
         </is>
       </c>
       <c r="AS235" s="23" t="n"/>
-      <c r="AT235" s="67" t="inlineStr"/>
+      <c r="AT235" s="66" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="68" t="inlineStr">
+      <c r="A236" s="67" t="inlineStr">
         <is>
           <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
         </is>
@@ -28834,7 +28805,7 @@
         </is>
       </c>
       <c r="H236" s="24" t="inlineStr"/>
-      <c r="I236" s="70" t="inlineStr">
+      <c r="I236" s="69" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
@@ -28899,10 +28870,10 @@
       <c r="AQ236" s="65" t="inlineStr"/>
       <c r="AR236" s="23" t="inlineStr"/>
       <c r="AS236" s="23" t="n"/>
-      <c r="AT236" s="67" t="inlineStr"/>
+      <c r="AT236" s="66" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="68" t="inlineStr">
+      <c r="A237" s="67" t="inlineStr">
         <is>
           <t>PS5-71-04 - CFO Storage Tank</t>
         </is>
@@ -28934,7 +28905,7 @@
         </is>
       </c>
       <c r="H237" s="24" t="inlineStr"/>
-      <c r="I237" s="69" t="inlineStr">
+      <c r="I237" s="68" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
@@ -29019,10 +28990,10 @@
         </is>
       </c>
       <c r="AS237" s="23" t="n"/>
-      <c r="AT237" s="67" t="inlineStr"/>
+      <c r="AT237" s="66" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="68" t="inlineStr">
+      <c r="A238" s="67" t="inlineStr">
         <is>
           <t>PS5-71-05 - CFO Transfer Pump A/B</t>
         </is>
@@ -29054,7 +29025,7 @@
         </is>
       </c>
       <c r="H238" s="24" t="inlineStr"/>
-      <c r="I238" s="69" t="inlineStr">
+      <c r="I238" s="68" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -29137,10 +29108,10 @@
         </is>
       </c>
       <c r="AS238" s="23" t="n"/>
-      <c r="AT238" s="67" t="inlineStr"/>
+      <c r="AT238" s="66" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="68" t="inlineStr">
+      <c r="A239" s="67" t="inlineStr">
         <is>
           <t>PS5-71-06 - Crude Fuel Separation Module</t>
         </is>
@@ -29176,7 +29147,7 @@
         </is>
       </c>
       <c r="H239" s="24" t="inlineStr"/>
-      <c r="I239" s="69" t="inlineStr">
+      <c r="I239" s="68" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
@@ -29279,10 +29250,10 @@
         </is>
       </c>
       <c r="AS239" s="23" t="n"/>
-      <c r="AT239" s="67" t="inlineStr"/>
+      <c r="AT239" s="66" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="68" t="inlineStr">
+      <c r="A240" s="67" t="inlineStr">
         <is>
           <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
         </is>
@@ -29318,7 +29289,7 @@
         </is>
       </c>
       <c r="H240" s="24" t="inlineStr"/>
-      <c r="I240" s="69" t="inlineStr">
+      <c r="I240" s="68" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -29350,7 +29321,7 @@
       <c r="R240" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="S240" s="71" t="inlineStr">
+      <c r="S240" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -29403,10 +29374,10 @@
         </is>
       </c>
       <c r="AS240" s="23" t="n"/>
-      <c r="AT240" s="67" t="inlineStr"/>
+      <c r="AT240" s="66" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="68" t="inlineStr">
+      <c r="A241" s="67" t="inlineStr">
         <is>
           <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
         </is>
@@ -29531,10 +29502,10 @@
         </is>
       </c>
       <c r="AS241" s="23" t="n"/>
-      <c r="AT241" s="67" t="inlineStr"/>
+      <c r="AT241" s="66" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="68" t="inlineStr">
+      <c r="A242" s="67" t="inlineStr">
         <is>
           <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
         </is>
@@ -29606,7 +29577,7 @@
       <c r="R242" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S242" s="71" t="inlineStr">
+      <c r="S242" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -29649,10 +29620,10 @@
       <c r="AQ242" s="65" t="inlineStr"/>
       <c r="AR242" s="23" t="inlineStr"/>
       <c r="AS242" s="23" t="n"/>
-      <c r="AT242" s="67" t="inlineStr"/>
+      <c r="AT242" s="66" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="68" t="inlineStr">
+      <c r="A243" s="67" t="inlineStr">
         <is>
           <t>PS5-71-12 - CFO Service Tank</t>
         </is>
@@ -29684,7 +29655,7 @@
         </is>
       </c>
       <c r="H243" s="24" t="inlineStr"/>
-      <c r="I243" s="69" t="inlineStr">
+      <c r="I243" s="68" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -29767,10 +29738,10 @@
         </is>
       </c>
       <c r="AS243" s="23" t="n"/>
-      <c r="AT243" s="67" t="inlineStr"/>
+      <c r="AT243" s="66" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="68" t="inlineStr">
+      <c r="A244" s="67" t="inlineStr">
         <is>
           <t>PS5-71-13 - CFO Service Pump A/B</t>
         </is>
@@ -29802,7 +29773,7 @@
         </is>
       </c>
       <c r="H244" s="24" t="inlineStr"/>
-      <c r="I244" s="69" t="inlineStr">
+      <c r="I244" s="68" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -29885,10 +29856,10 @@
         </is>
       </c>
       <c r="AS244" s="23" t="n"/>
-      <c r="AT244" s="67" t="inlineStr"/>
+      <c r="AT244" s="66" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="68" t="inlineStr">
+      <c r="A245" s="67" t="inlineStr">
         <is>
           <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
@@ -29920,7 +29891,7 @@
         </is>
       </c>
       <c r="H245" s="24" t="inlineStr"/>
-      <c r="I245" s="69" t="inlineStr">
+      <c r="I245" s="68" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -30003,10 +29974,10 @@
         </is>
       </c>
       <c r="AS245" s="23" t="n"/>
-      <c r="AT245" s="67" t="inlineStr"/>
+      <c r="AT245" s="66" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="68" t="inlineStr">
+      <c r="A246" s="67" t="inlineStr">
         <is>
           <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
         </is>
@@ -30038,7 +30009,7 @@
         </is>
       </c>
       <c r="H246" s="24" t="inlineStr"/>
-      <c r="I246" s="69" t="inlineStr">
+      <c r="I246" s="68" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -30121,10 +30092,10 @@
         </is>
       </c>
       <c r="AS246" s="23" t="n"/>
-      <c r="AT246" s="67" t="inlineStr"/>
+      <c r="AT246" s="66" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="68" t="inlineStr">
+      <c r="A247" s="67" t="inlineStr">
         <is>
           <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
@@ -30160,7 +30131,7 @@
         </is>
       </c>
       <c r="H247" s="24" t="inlineStr"/>
-      <c r="I247" s="69" t="inlineStr">
+      <c r="I247" s="68" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -30243,10 +30214,10 @@
         </is>
       </c>
       <c r="AS247" s="23" t="n"/>
-      <c r="AT247" s="67" t="inlineStr"/>
+      <c r="AT247" s="66" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="68" t="inlineStr">
+      <c r="A248" s="67" t="inlineStr">
         <is>
           <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
         </is>
@@ -30369,10 +30340,10 @@
         </is>
       </c>
       <c r="AS248" s="23" t="n"/>
-      <c r="AT248" s="67" t="inlineStr"/>
+      <c r="AT248" s="66" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="68" t="inlineStr">
+      <c r="A249" s="67" t="inlineStr">
         <is>
           <t>PS5-71-18 - Diesel Separator Module</t>
         </is>
@@ -30412,7 +30383,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I249" s="69" t="inlineStr">
+      <c r="I249" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -30499,10 +30470,10 @@
         </is>
       </c>
       <c r="AS249" s="23" t="n"/>
-      <c r="AT249" s="67" t="inlineStr"/>
+      <c r="AT249" s="66" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="68" t="inlineStr">
+      <c r="A250" s="67" t="inlineStr">
         <is>
           <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
         </is>
@@ -30538,7 +30509,7 @@
         </is>
       </c>
       <c r="H250" s="24" t="inlineStr"/>
-      <c r="I250" s="69" t="inlineStr">
+      <c r="I250" s="68" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -30570,7 +30541,7 @@
       <c r="R250" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="S250" s="71" t="inlineStr">
+      <c r="S250" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -30623,10 +30594,10 @@
         </is>
       </c>
       <c r="AS250" s="23" t="n"/>
-      <c r="AT250" s="67" t="inlineStr"/>
+      <c r="AT250" s="66" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="68" t="inlineStr">
+      <c r="A251" s="67" t="inlineStr">
         <is>
           <t>PS5-71-20 - Diesel Fuel Day Tank</t>
         </is>
@@ -30666,7 +30637,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I251" s="69" t="inlineStr">
+      <c r="I251" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -30749,10 +30720,10 @@
         </is>
       </c>
       <c r="AS251" s="23" t="n"/>
-      <c r="AT251" s="67" t="inlineStr"/>
+      <c r="AT251" s="66" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="68" t="inlineStr">
+      <c r="A252" s="67" t="inlineStr">
         <is>
           <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
         </is>
@@ -30877,7 +30848,7 @@
         </is>
       </c>
       <c r="AS252" s="23" t="n"/>
-      <c r="AT252" s="67" t="inlineStr"/>
+      <c r="AT252" s="66" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="53" t="inlineStr">
@@ -31003,10 +30974,10 @@
         </is>
       </c>
       <c r="AS253" s="23" t="n"/>
-      <c r="AT253" s="67" t="inlineStr"/>
+      <c r="AT253" s="66" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="68" t="inlineStr">
+      <c r="A254" s="67" t="inlineStr">
         <is>
           <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
         </is>
@@ -31046,7 +31017,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I254" s="69" t="inlineStr">
+      <c r="I254" s="68" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -31078,7 +31049,7 @@
       <c r="R254" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S254" s="71" t="inlineStr">
+      <c r="S254" s="70" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -31129,10 +31100,10 @@
         </is>
       </c>
       <c r="AS254" s="23" t="n"/>
-      <c r="AT254" s="67" t="inlineStr"/>
+      <c r="AT254" s="66" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="68" t="inlineStr">
+      <c r="A255" s="67" t="inlineStr">
         <is>
           <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
@@ -31172,7 +31143,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I255" s="69" t="inlineStr">
+      <c r="I255" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -31255,10 +31226,10 @@
         </is>
       </c>
       <c r="AS255" s="23" t="n"/>
-      <c r="AT255" s="67" t="inlineStr"/>
+      <c r="AT255" s="66" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="68" t="inlineStr">
+      <c r="A256" s="67" t="inlineStr">
         <is>
           <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
         </is>
@@ -31298,7 +31269,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I256" s="69" t="inlineStr">
+      <c r="I256" s="68" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -31381,7 +31352,7 @@
         </is>
       </c>
       <c r="AS256" s="23" t="n"/>
-      <c r="AT256" s="67" t="inlineStr"/>
+      <c r="AT256" s="66" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="53" t="inlineStr">
@@ -31507,10 +31478,10 @@
         </is>
       </c>
       <c r="AS257" s="23" t="n"/>
-      <c r="AT257" s="67" t="inlineStr"/>
+      <c r="AT257" s="66" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="68" t="inlineStr">
+      <c r="A258" s="67" t="inlineStr">
         <is>
           <t>PS5-74-04 - Nitrogen Distribution Header</t>
         </is>
@@ -31542,7 +31513,7 @@
         </is>
       </c>
       <c r="H258" s="24" t="inlineStr"/>
-      <c r="I258" s="69" t="inlineStr">
+      <c r="I258" s="68" t="inlineStr">
         <is>
           <t>81%</t>
         </is>
@@ -31625,10 +31596,10 @@
         </is>
       </c>
       <c r="AS258" s="23" t="n"/>
-      <c r="AT258" s="67" t="inlineStr"/>
+      <c r="AT258" s="66" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="68" t="inlineStr">
+      <c r="A259" s="67" t="inlineStr">
         <is>
           <t>PS5-75-01 - DRA Injection Package</t>
         </is>
@@ -31660,7 +31631,7 @@
         </is>
       </c>
       <c r="H259" s="24" t="inlineStr"/>
-      <c r="I259" s="70" t="inlineStr">
+      <c r="I259" s="69" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
@@ -31743,10 +31714,10 @@
         </is>
       </c>
       <c r="AS259" s="23" t="n"/>
-      <c r="AT259" s="67" t="inlineStr"/>
+      <c r="AT259" s="66" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="68" t="inlineStr">
+      <c r="A260" s="67" t="inlineStr">
         <is>
           <t>PS5-75-02 - Biocide Injection Package</t>
         </is>
@@ -31778,7 +31749,7 @@
         </is>
       </c>
       <c r="H260" s="24" t="inlineStr"/>
-      <c r="I260" s="69" t="inlineStr">
+      <c r="I260" s="68" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -31861,10 +31832,10 @@
         </is>
       </c>
       <c r="AS260" s="23" t="n"/>
-      <c r="AT260" s="67" t="inlineStr"/>
+      <c r="AT260" s="66" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="68" t="inlineStr">
+      <c r="A261" s="67" t="inlineStr">
         <is>
           <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
         </is>
@@ -31896,7 +31867,7 @@
         </is>
       </c>
       <c r="H261" s="24" t="inlineStr"/>
-      <c r="I261" s="69" t="inlineStr">
+      <c r="I261" s="68" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
@@ -31979,10 +31950,10 @@
         </is>
       </c>
       <c r="AS261" s="23" t="n"/>
-      <c r="AT261" s="67" t="inlineStr"/>
+      <c r="AT261" s="66" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="74" t="inlineStr">
+      <c r="A262" s="73" t="inlineStr">
         <is>
           <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
@@ -32008,7 +31979,7 @@
         </is>
       </c>
       <c r="F262" s="23" t="inlineStr"/>
-      <c r="G262" s="69" t="inlineStr">
+      <c r="G262" s="68" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -32018,7 +31989,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I262" s="69" t="inlineStr">
+      <c r="I262" s="68" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -32101,10 +32072,10 @@
         </is>
       </c>
       <c r="AS262" s="23" t="n"/>
-      <c r="AT262" s="67" t="inlineStr"/>
+      <c r="AT262" s="66" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="68" t="inlineStr">
+      <c r="A263" s="67" t="inlineStr">
         <is>
           <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
         </is>
@@ -32136,7 +32107,7 @@
         </is>
       </c>
       <c r="H263" s="24" t="inlineStr"/>
-      <c r="I263" s="70" t="inlineStr">
+      <c r="I263" s="69" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -32219,10 +32190,10 @@
         </is>
       </c>
       <c r="AS263" s="23" t="n"/>
-      <c r="AT263" s="67" t="inlineStr"/>
+      <c r="AT263" s="66" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="68" t="inlineStr">
+      <c r="A264" s="67" t="inlineStr">
         <is>
           <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
         </is>
@@ -32254,7 +32225,7 @@
         </is>
       </c>
       <c r="H264" s="24" t="inlineStr"/>
-      <c r="I264" s="70" t="inlineStr">
+      <c r="I264" s="69" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -32337,10 +32308,10 @@
         </is>
       </c>
       <c r="AS264" s="23" t="n"/>
-      <c r="AT264" s="67" t="inlineStr"/>
+      <c r="AT264" s="66" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" s="68" t="inlineStr">
+      <c r="A265" s="67" t="inlineStr">
         <is>
           <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
         </is>
@@ -32372,7 +32343,7 @@
         </is>
       </c>
       <c r="H265" s="24" t="inlineStr"/>
-      <c r="I265" s="70" t="inlineStr">
+      <c r="I265" s="69" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -32455,10 +32426,10 @@
         </is>
       </c>
       <c r="AS265" s="23" t="n"/>
-      <c r="AT265" s="67" t="inlineStr"/>
+      <c r="AT265" s="66" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" s="68" t="inlineStr">
+      <c r="A266" s="67" t="inlineStr">
         <is>
           <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
         </is>
@@ -32490,7 +32461,7 @@
         </is>
       </c>
       <c r="H266" s="24" t="inlineStr"/>
-      <c r="I266" s="70" t="inlineStr">
+      <c r="I266" s="69" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -32573,10 +32544,10 @@
         </is>
       </c>
       <c r="AS266" s="23" t="n"/>
-      <c r="AT266" s="67" t="inlineStr"/>
+      <c r="AT266" s="66" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" s="68" t="inlineStr">
+      <c r="A267" s="67" t="inlineStr">
         <is>
           <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
         </is>
@@ -32608,7 +32579,7 @@
         </is>
       </c>
       <c r="H267" s="24" t="inlineStr"/>
-      <c r="I267" s="70" t="inlineStr">
+      <c r="I267" s="69" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -32691,10 +32662,10 @@
         </is>
       </c>
       <c r="AS267" s="23" t="n"/>
-      <c r="AT267" s="67" t="inlineStr"/>
+      <c r="AT267" s="66" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="68" t="inlineStr">
+      <c r="A268" s="67" t="inlineStr">
         <is>
           <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
         </is>
@@ -32726,7 +32697,7 @@
         </is>
       </c>
       <c r="H268" s="24" t="inlineStr"/>
-      <c r="I268" s="70" t="inlineStr">
+      <c r="I268" s="69" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -32809,10 +32780,10 @@
         </is>
       </c>
       <c r="AS268" s="23" t="n"/>
-      <c r="AT268" s="67" t="inlineStr"/>
+      <c r="AT268" s="66" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="68" t="inlineStr">
+      <c r="A269" s="67" t="inlineStr">
         <is>
           <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
         </is>
@@ -32844,7 +32815,7 @@
         </is>
       </c>
       <c r="H269" s="24" t="inlineStr"/>
-      <c r="I269" s="70" t="inlineStr">
+      <c r="I269" s="69" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -32927,10 +32898,10 @@
         </is>
       </c>
       <c r="AS269" s="23" t="n"/>
-      <c r="AT269" s="67" t="inlineStr"/>
+      <c r="AT269" s="66" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="68" t="inlineStr">
+      <c r="A270" s="67" t="inlineStr">
         <is>
           <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
         </is>
@@ -32962,7 +32933,7 @@
         </is>
       </c>
       <c r="H270" s="24" t="inlineStr"/>
-      <c r="I270" s="70" t="inlineStr">
+      <c r="I270" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -33045,10 +33016,10 @@
         </is>
       </c>
       <c r="AS270" s="23" t="n"/>
-      <c r="AT270" s="67" t="inlineStr"/>
+      <c r="AT270" s="66" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="68" t="inlineStr">
+      <c r="A271" s="67" t="inlineStr">
         <is>
           <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
         </is>
@@ -33080,7 +33051,7 @@
         </is>
       </c>
       <c r="H271" s="24" t="inlineStr"/>
-      <c r="I271" s="70" t="inlineStr">
+      <c r="I271" s="69" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -33163,10 +33134,10 @@
         </is>
       </c>
       <c r="AS271" s="23" t="n"/>
-      <c r="AT271" s="67" t="inlineStr"/>
+      <c r="AT271" s="66" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" s="68" t="inlineStr">
+      <c r="A272" s="67" t="inlineStr">
         <is>
           <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
         </is>
@@ -33198,7 +33169,7 @@
         </is>
       </c>
       <c r="H272" s="24" t="inlineStr"/>
-      <c r="I272" s="70" t="inlineStr">
+      <c r="I272" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -33281,10 +33252,10 @@
         </is>
       </c>
       <c r="AS272" s="23" t="n"/>
-      <c r="AT272" s="67" t="inlineStr"/>
+      <c r="AT272" s="66" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="68" t="inlineStr">
+      <c r="A273" s="67" t="inlineStr">
         <is>
           <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
         </is>
@@ -33316,7 +33287,7 @@
         </is>
       </c>
       <c r="H273" s="24" t="inlineStr"/>
-      <c r="I273" s="70" t="inlineStr">
+      <c r="I273" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -33399,10 +33370,10 @@
         </is>
       </c>
       <c r="AS273" s="23" t="n"/>
-      <c r="AT273" s="67" t="inlineStr"/>
+      <c r="AT273" s="66" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="68" t="inlineStr">
+      <c r="A274" s="67" t="inlineStr">
         <is>
           <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
         </is>
@@ -33434,7 +33405,7 @@
         </is>
       </c>
       <c r="H274" s="24" t="inlineStr"/>
-      <c r="I274" s="70" t="inlineStr">
+      <c r="I274" s="69" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -33517,10 +33488,10 @@
         </is>
       </c>
       <c r="AS274" s="23" t="n"/>
-      <c r="AT274" s="67" t="inlineStr"/>
+      <c r="AT274" s="66" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" s="68" t="inlineStr">
+      <c r="A275" s="67" t="inlineStr">
         <is>
           <t>PS5-82-01 - Sanitary Sewage Collection</t>
         </is>
@@ -33552,7 +33523,7 @@
         </is>
       </c>
       <c r="H275" s="24" t="inlineStr"/>
-      <c r="I275" s="69" t="inlineStr">
+      <c r="I275" s="68" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -33635,10 +33606,10 @@
         </is>
       </c>
       <c r="AS275" s="23" t="n"/>
-      <c r="AT275" s="67" t="inlineStr"/>
+      <c r="AT275" s="66" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="68" t="inlineStr">
+      <c r="A276" s="67" t="inlineStr">
         <is>
           <t>PS5-82-02 - Sewage Treatment Plant Package</t>
         </is>
@@ -33670,7 +33641,7 @@
         </is>
       </c>
       <c r="H276" s="24" t="inlineStr"/>
-      <c r="I276" s="70" t="inlineStr">
+      <c r="I276" s="69" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -33753,10 +33724,10 @@
         </is>
       </c>
       <c r="AS276" s="23" t="n"/>
-      <c r="AT276" s="67" t="inlineStr"/>
+      <c r="AT276" s="66" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" s="68" t="inlineStr">
+      <c r="A277" s="67" t="inlineStr">
         <is>
           <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
         </is>
@@ -33788,7 +33759,7 @@
         </is>
       </c>
       <c r="H277" s="24" t="inlineStr"/>
-      <c r="I277" s="70" t="inlineStr">
+      <c r="I277" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -33871,10 +33842,10 @@
         </is>
       </c>
       <c r="AS277" s="23" t="n"/>
-      <c r="AT277" s="67" t="inlineStr"/>
+      <c r="AT277" s="66" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="68" t="inlineStr">
+      <c r="A278" s="67" t="inlineStr">
         <is>
           <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
         </is>
@@ -33906,7 +33877,7 @@
         </is>
       </c>
       <c r="H278" s="24" t="inlineStr"/>
-      <c r="I278" s="69" t="inlineStr">
+      <c r="I278" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -33989,10 +33960,10 @@
         </is>
       </c>
       <c r="AS278" s="23" t="n"/>
-      <c r="AT278" s="67" t="inlineStr"/>
+      <c r="AT278" s="66" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="68" t="inlineStr">
+      <c r="A279" s="67" t="inlineStr">
         <is>
           <t>PS5-82-05 - Office and Facilities building</t>
         </is>
@@ -34024,7 +33995,7 @@
         </is>
       </c>
       <c r="H279" s="24" t="inlineStr"/>
-      <c r="I279" s="70" t="inlineStr">
+      <c r="I279" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -34107,10 +34078,10 @@
         </is>
       </c>
       <c r="AS279" s="23" t="n"/>
-      <c r="AT279" s="67" t="inlineStr"/>
+      <c r="AT279" s="66" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="68" t="inlineStr">
+      <c r="A280" s="67" t="inlineStr">
         <is>
           <t>PS5-82-06 - Guard House Building</t>
         </is>
@@ -34142,7 +34113,7 @@
         </is>
       </c>
       <c r="H280" s="24" t="inlineStr"/>
-      <c r="I280" s="70" t="inlineStr">
+      <c r="I280" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -34225,10 +34196,10 @@
         </is>
       </c>
       <c r="AS280" s="23" t="n"/>
-      <c r="AT280" s="67" t="inlineStr"/>
+      <c r="AT280" s="66" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="68" t="inlineStr">
+      <c r="A281" s="67" t="inlineStr">
         <is>
           <t>PS5-82-07 - Guard Huts</t>
         </is>
@@ -34260,7 +34231,7 @@
         </is>
       </c>
       <c r="H281" s="24" t="inlineStr"/>
-      <c r="I281" s="70" t="inlineStr">
+      <c r="I281" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -34343,7 +34314,7 @@
         </is>
       </c>
       <c r="AS281" s="23" t="n"/>
-      <c r="AT281" s="67" t="inlineStr"/>
+      <c r="AT281" s="66" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="53" t="inlineStr">
@@ -34469,10 +34440,10 @@
         </is>
       </c>
       <c r="AS282" s="23" t="n"/>
-      <c r="AT282" s="67" t="inlineStr"/>
+      <c r="AT282" s="66" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" s="68" t="inlineStr">
+      <c r="A283" s="67" t="inlineStr">
         <is>
           <t>PS5-84-01 - Generator Building</t>
         </is>
@@ -34504,7 +34475,7 @@
         </is>
       </c>
       <c r="H283" s="24" t="inlineStr"/>
-      <c r="I283" s="70" t="inlineStr">
+      <c r="I283" s="69" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -34587,10 +34558,10 @@
         </is>
       </c>
       <c r="AS283" s="23" t="n"/>
-      <c r="AT283" s="67" t="inlineStr"/>
+      <c r="AT283" s="66" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" s="68" t="inlineStr">
+      <c r="A284" s="67" t="inlineStr">
         <is>
           <t>PS5-84-02 - Workshop &amp; Warehouse</t>
         </is>
@@ -34622,7 +34593,7 @@
         </is>
       </c>
       <c r="H284" s="24" t="inlineStr"/>
-      <c r="I284" s="70" t="inlineStr">
+      <c r="I284" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -34705,7 +34676,7 @@
         </is>
       </c>
       <c r="AS284" s="23" t="n"/>
-      <c r="AT284" s="67" t="inlineStr"/>
+      <c r="AT284" s="66" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="53" t="inlineStr">
@@ -34827,7 +34798,7 @@
         </is>
       </c>
       <c r="AS285" s="23" t="n"/>
-      <c r="AT285" s="67" t="inlineStr"/>
+      <c r="AT285" s="66" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="53" t="inlineStr">
@@ -34949,7 +34920,7 @@
         </is>
       </c>
       <c r="AS286" s="23" t="n"/>
-      <c r="AT286" s="67" t="inlineStr"/>
+      <c r="AT286" s="66" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="53" t="inlineStr">
@@ -35075,10 +35046,10 @@
         </is>
       </c>
       <c r="AS287" s="23" t="n"/>
-      <c r="AT287" s="67" t="inlineStr"/>
+      <c r="AT287" s="66" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="68" t="inlineStr">
+      <c r="A288" s="67" t="inlineStr">
         <is>
           <t>PS5-99-01 - Area Completion for Building area</t>
         </is>
@@ -35110,7 +35081,7 @@
         </is>
       </c>
       <c r="H288" s="24" t="inlineStr"/>
-      <c r="I288" s="70" t="inlineStr">
+      <c r="I288" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -35193,10 +35164,10 @@
         </is>
       </c>
       <c r="AS288" s="23" t="n"/>
-      <c r="AT288" s="67" t="inlineStr"/>
+      <c r="AT288" s="66" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="68" t="inlineStr">
+      <c r="A289" s="67" t="inlineStr">
         <is>
           <t>PS5-99-02 - Area Completion for Utility area</t>
         </is>
@@ -35228,7 +35199,7 @@
         </is>
       </c>
       <c r="H289" s="24" t="inlineStr"/>
-      <c r="I289" s="70" t="inlineStr">
+      <c r="I289" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -35311,10 +35282,10 @@
         </is>
       </c>
       <c r="AS289" s="23" t="n"/>
-      <c r="AT289" s="67" t="inlineStr"/>
+      <c r="AT289" s="66" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="68" t="inlineStr">
+      <c r="A290" s="67" t="inlineStr">
         <is>
           <t>PS5-99-03 - Area Completion for Power Distribution area</t>
         </is>
@@ -35346,7 +35317,7 @@
         </is>
       </c>
       <c r="H290" s="24" t="inlineStr"/>
-      <c r="I290" s="70" t="inlineStr">
+      <c r="I290" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -35429,10 +35400,10 @@
         </is>
       </c>
       <c r="AS290" s="23" t="n"/>
-      <c r="AT290" s="67" t="inlineStr"/>
+      <c r="AT290" s="66" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" s="68" t="inlineStr">
+      <c r="A291" s="67" t="inlineStr">
         <is>
           <t>PS5-99-04 - Area Completion for Process area</t>
         </is>
@@ -35464,7 +35435,7 @@
         </is>
       </c>
       <c r="H291" s="24" t="inlineStr"/>
-      <c r="I291" s="70" t="inlineStr">
+      <c r="I291" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -35547,10 +35518,10 @@
         </is>
       </c>
       <c r="AS291" s="23" t="n"/>
-      <c r="AT291" s="67" t="inlineStr"/>
+      <c r="AT291" s="66" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" s="68" t="inlineStr">
+      <c r="A292" s="67" t="inlineStr">
         <is>
           <t>PS5-99-05 - Area Completion for CFO area</t>
         </is>
@@ -35582,7 +35553,7 @@
         </is>
       </c>
       <c r="H292" s="24" t="inlineStr"/>
-      <c r="I292" s="70" t="inlineStr">
+      <c r="I292" s="69" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -35665,10 +35636,10 @@
         </is>
       </c>
       <c r="AS292" s="23" t="n"/>
-      <c r="AT292" s="67" t="inlineStr"/>
+      <c r="AT292" s="66" t="inlineStr"/>
     </row>
     <row r="293">
-      <c r="A293" s="68" t="inlineStr">
+      <c r="A293" s="67" t="inlineStr">
         <is>
           <t>PS5-99-06 - Area Completion for Power Generation area</t>
         </is>
@@ -35708,7 +35679,7 @@
           <t>RE WALKDOWN</t>
         </is>
       </c>
-      <c r="I293" s="69" t="inlineStr">
+      <c r="I293" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -35791,7 +35762,7 @@
         </is>
       </c>
       <c r="AS293" s="23" t="n"/>
-      <c r="AT293" s="67" t="inlineStr"/>
+      <c r="AT293" s="66" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:AT293"/>

--- a/EXCEL/2 - RFC PROGRESS.xlsx
+++ b/EXCEL/2 - RFC PROGRESS.xlsx
@@ -172,7 +172,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill/>
     </fill>
@@ -309,6 +309,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFfff8e1"/>
         <bgColor rgb="FFfff8e1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -498,7 +504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -512,9 +518,6 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -524,10 +527,10 @@
     <xf numFmtId="0" fontId="19" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -539,16 +542,19 @@
     <xf numFmtId="0" fontId="2" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -558,10 +564,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -573,21 +579,21 @@
     <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -677,6 +683,9 @@
     <xf numFmtId="0" fontId="11" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -698,10 +707,10 @@
     <xf numFmtId="0" fontId="7" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -713,7 +722,13 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -722,7 +737,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -731,28 +746,28 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1194,51 +1209,51 @@
           <t>PS5 COMPLETION PLATFORM  |  2 · RFC PROGRESS</t>
         </is>
       </c>
-      <c r="B1" s="97" t="n"/>
-      <c r="C1" s="97" t="n"/>
-      <c r="D1" s="97" t="n"/>
-      <c r="E1" s="97" t="n"/>
-      <c r="F1" s="97" t="n"/>
-      <c r="G1" s="97" t="n"/>
-      <c r="H1" s="97" t="n"/>
-      <c r="I1" s="97" t="n"/>
-      <c r="J1" s="97" t="n"/>
-      <c r="K1" s="97" t="n"/>
-      <c r="L1" s="97" t="n"/>
-      <c r="M1" s="97" t="n"/>
-      <c r="N1" s="97" t="n"/>
-      <c r="O1" s="97" t="n"/>
-      <c r="P1" s="97" t="n"/>
-      <c r="Q1" s="97" t="n"/>
-      <c r="R1" s="97" t="n"/>
-      <c r="S1" s="97" t="n"/>
-      <c r="T1" s="97" t="n"/>
-      <c r="U1" s="97" t="n"/>
-      <c r="V1" s="97" t="n"/>
-      <c r="W1" s="97" t="n"/>
-      <c r="X1" s="97" t="n"/>
-      <c r="Y1" s="97" t="n"/>
-      <c r="Z1" s="97" t="n"/>
-      <c r="AA1" s="97" t="n"/>
-      <c r="AB1" s="97" t="n"/>
-      <c r="AC1" s="97" t="n"/>
-      <c r="AD1" s="97" t="n"/>
-      <c r="AE1" s="97" t="n"/>
-      <c r="AF1" s="97" t="n"/>
-      <c r="AG1" s="97" t="n"/>
-      <c r="AH1" s="97" t="n"/>
-      <c r="AI1" s="97" t="n"/>
-      <c r="AJ1" s="97" t="n"/>
-      <c r="AK1" s="97" t="n"/>
-      <c r="AL1" s="97" t="n"/>
-      <c r="AM1" s="97" t="n"/>
-      <c r="AN1" s="97" t="n"/>
-      <c r="AO1" s="97" t="n"/>
-      <c r="AP1" s="97" t="n"/>
-      <c r="AQ1" s="97" t="n"/>
-      <c r="AR1" s="97" t="n"/>
-      <c r="AS1" s="97" t="n"/>
-      <c r="AT1" s="98" t="n"/>
+      <c r="B1" s="100" t="n"/>
+      <c r="C1" s="100" t="n"/>
+      <c r="D1" s="100" t="n"/>
+      <c r="E1" s="100" t="n"/>
+      <c r="F1" s="100" t="n"/>
+      <c r="G1" s="100" t="n"/>
+      <c r="H1" s="100" t="n"/>
+      <c r="I1" s="100" t="n"/>
+      <c r="J1" s="100" t="n"/>
+      <c r="K1" s="100" t="n"/>
+      <c r="L1" s="100" t="n"/>
+      <c r="M1" s="100" t="n"/>
+      <c r="N1" s="100" t="n"/>
+      <c r="O1" s="100" t="n"/>
+      <c r="P1" s="100" t="n"/>
+      <c r="Q1" s="100" t="n"/>
+      <c r="R1" s="100" t="n"/>
+      <c r="S1" s="100" t="n"/>
+      <c r="T1" s="100" t="n"/>
+      <c r="U1" s="100" t="n"/>
+      <c r="V1" s="100" t="n"/>
+      <c r="W1" s="100" t="n"/>
+      <c r="X1" s="100" t="n"/>
+      <c r="Y1" s="100" t="n"/>
+      <c r="Z1" s="100" t="n"/>
+      <c r="AA1" s="100" t="n"/>
+      <c r="AB1" s="100" t="n"/>
+      <c r="AC1" s="100" t="n"/>
+      <c r="AD1" s="100" t="n"/>
+      <c r="AE1" s="100" t="n"/>
+      <c r="AF1" s="100" t="n"/>
+      <c r="AG1" s="100" t="n"/>
+      <c r="AH1" s="100" t="n"/>
+      <c r="AI1" s="100" t="n"/>
+      <c r="AJ1" s="100" t="n"/>
+      <c r="AK1" s="100" t="n"/>
+      <c r="AL1" s="100" t="n"/>
+      <c r="AM1" s="100" t="n"/>
+      <c r="AN1" s="100" t="n"/>
+      <c r="AO1" s="100" t="n"/>
+      <c r="AP1" s="100" t="n"/>
+      <c r="AQ1" s="100" t="n"/>
+      <c r="AR1" s="100" t="n"/>
+      <c r="AS1" s="100" t="n"/>
+      <c r="AT1" s="101" t="n"/>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
@@ -1609,8 +1624,10 @@
       <c r="N4" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="O4" s="60" t="n">
-        <v>28</v>
+      <c r="O4" s="60" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="P4" s="61" t="n">
         <v>0</v>
@@ -1671,11 +1688,11 @@
           <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
         </is>
       </c>
-      <c r="AS4" s="23" t="n"/>
-      <c r="AT4" s="66" t="inlineStr"/>
+      <c r="AS4" s="66" t="n"/>
+      <c r="AT4" s="67" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="67" t="inlineStr">
+      <c r="A5" s="68" t="inlineStr">
         <is>
           <t>PS5-01-02 - Fire Water Pump A</t>
         </is>
@@ -1789,19 +1806,19 @@
       <c r="AP5" s="65" t="inlineStr"/>
       <c r="AQ5" s="65" t="inlineStr">
         <is>
+          <t>EACOP(MR.BENHER TBC)-EXPECTED 19-08-2026</t>
+        </is>
+      </c>
+      <c r="AR5" s="23" t="inlineStr">
+        <is>
           <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
         </is>
       </c>
-      <c r="AR5" s="23" t="inlineStr">
-        <is>
-          <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
-        </is>
-      </c>
       <c r="AS5" s="23" t="n"/>
-      <c r="AT5" s="66" t="inlineStr"/>
+      <c r="AT5" s="67" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="67" t="inlineStr">
+      <c r="A6" s="68" t="inlineStr">
         <is>
           <t>PS5-01-03 - Fire Water Pump B</t>
         </is>
@@ -1920,7 +1937,7 @@
         </is>
       </c>
       <c r="AS6" s="23" t="n"/>
-      <c r="AT6" s="66" t="inlineStr"/>
+      <c r="AT6" s="67" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="53" t="inlineStr">
@@ -2042,10 +2059,10 @@
         </is>
       </c>
       <c r="AS7" s="23" t="n"/>
-      <c r="AT7" s="66" t="inlineStr"/>
+      <c r="AT7" s="67" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="67" t="inlineStr">
+      <c r="A8" s="68" t="inlineStr">
         <is>
           <t>PS5-01-05 - Foam Skid</t>
         </is>
@@ -2168,7 +2185,7 @@
         </is>
       </c>
       <c r="AS8" s="23" t="n"/>
-      <c r="AT8" s="66" t="inlineStr"/>
+      <c r="AT8" s="67" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="53" t="inlineStr">
@@ -2290,10 +2307,10 @@
         </is>
       </c>
       <c r="AS9" s="23" t="n"/>
-      <c r="AT9" s="66" t="inlineStr"/>
+      <c r="AT9" s="67" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="67" t="inlineStr">
+      <c r="A10" s="68" t="inlineStr">
         <is>
           <t>PS5-01-07 - Fire Water Ring Main &amp; Distribution</t>
         </is>
@@ -2325,13 +2342,15 @@
         </is>
       </c>
       <c r="H10" s="24" t="inlineStr"/>
-      <c r="I10" s="68" t="inlineStr">
+      <c r="I10" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
       </c>
-      <c r="J10" s="55" t="n">
-        <v>0</v>
+      <c r="J10" s="55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K10" s="56" t="n">
         <v>0</v>
@@ -2408,10 +2427,10 @@
         </is>
       </c>
       <c r="AS10" s="23" t="n"/>
-      <c r="AT10" s="66" t="inlineStr"/>
+      <c r="AT10" s="67" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="67" t="inlineStr">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t>PS5-01-08 - PS5 Deluge Valve Skid (PS5-01-UK-6100)</t>
         </is>
@@ -2443,7 +2462,7 @@
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr"/>
-      <c r="I11" s="68" t="inlineStr">
+      <c r="I11" s="69" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
@@ -2526,7 +2545,7 @@
         </is>
       </c>
       <c r="AS11" s="23" t="n"/>
-      <c r="AT11" s="66" t="inlineStr"/>
+      <c r="AT11" s="67" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="53" t="inlineStr">
@@ -2644,7 +2663,7 @@
         </is>
       </c>
       <c r="AS12" s="23" t="n"/>
-      <c r="AT12" s="66" t="inlineStr"/>
+      <c r="AT12" s="67" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="53" t="inlineStr">
@@ -2770,10 +2789,10 @@
         </is>
       </c>
       <c r="AS13" s="23" t="n"/>
-      <c r="AT13" s="66" t="inlineStr"/>
+      <c r="AT13" s="67" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="67" t="inlineStr">
+      <c r="A14" s="68" t="inlineStr">
         <is>
           <t>PS5-01-11 - Inergen for Power Gen Building</t>
         </is>
@@ -2809,7 +2828,7 @@
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr"/>
-      <c r="I14" s="69" t="inlineStr">
+      <c r="I14" s="70" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -2884,10 +2903,10 @@
       <c r="AQ14" s="65" t="inlineStr"/>
       <c r="AR14" s="23" t="inlineStr"/>
       <c r="AS14" s="23" t="n"/>
-      <c r="AT14" s="66" t="inlineStr"/>
+      <c r="AT14" s="67" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="67" t="inlineStr">
+      <c r="A15" s="68" t="inlineStr">
         <is>
           <t>PS5-02-01 - Miscellaneous Safety equipment</t>
         </is>
@@ -2915,7 +2934,7 @@
         </is>
       </c>
       <c r="H15" s="24" t="inlineStr"/>
-      <c r="I15" s="69" t="inlineStr">
+      <c r="I15" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -2998,10 +3017,10 @@
         </is>
       </c>
       <c r="AS15" s="23" t="n"/>
-      <c r="AT15" s="66" t="inlineStr"/>
+      <c r="AT15" s="67" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="67" t="inlineStr">
+      <c r="A16" s="68" t="inlineStr">
         <is>
           <t>PS5-02-02 - Portable Fire Fighting Equipments</t>
         </is>
@@ -3033,7 +3052,7 @@
         </is>
       </c>
       <c r="H16" s="24" t="inlineStr"/>
-      <c r="I16" s="69" t="inlineStr">
+      <c r="I16" s="70" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
@@ -3116,10 +3135,10 @@
         </is>
       </c>
       <c r="AS16" s="23" t="n"/>
-      <c r="AT16" s="66" t="inlineStr"/>
+      <c r="AT16" s="67" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="67" t="inlineStr">
+      <c r="A17" s="68" t="inlineStr">
         <is>
           <t>PS5-03-01 - FZ-01 - Process Area</t>
         </is>
@@ -3242,10 +3261,10 @@
         </is>
       </c>
       <c r="AS17" s="23" t="n"/>
-      <c r="AT17" s="66" t="inlineStr"/>
+      <c r="AT17" s="67" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="67" t="inlineStr">
+      <c r="A18" s="68" t="inlineStr">
         <is>
           <t>PS5-03-03 - FZ-03 - Buildings Area</t>
         </is>
@@ -3277,7 +3296,7 @@
         </is>
       </c>
       <c r="H18" s="24" t="inlineStr"/>
-      <c r="I18" s="69" t="inlineStr">
+      <c r="I18" s="70" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -3360,10 +3379,10 @@
         </is>
       </c>
       <c r="AS18" s="23" t="n"/>
-      <c r="AT18" s="66" t="inlineStr"/>
+      <c r="AT18" s="67" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="67" t="inlineStr">
+      <c r="A19" s="68" t="inlineStr">
         <is>
           <t>PS5-03-04 - FZ-04 - Utilities - Diesel and Firewater Pumps Areas</t>
         </is>
@@ -3482,10 +3501,10 @@
         </is>
       </c>
       <c r="AS19" s="23" t="n"/>
-      <c r="AT19" s="66" t="inlineStr"/>
+      <c r="AT19" s="67" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="67" t="inlineStr">
+      <c r="A20" s="68" t="inlineStr">
         <is>
           <t>PS5-03-06 - FZ-06 - Transformer Area</t>
         </is>
@@ -3608,7 +3627,7 @@
         </is>
       </c>
       <c r="AS20" s="23" t="n"/>
-      <c r="AT20" s="66" t="inlineStr"/>
+      <c r="AT20" s="67" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="53" t="inlineStr">
@@ -3734,10 +3753,10 @@
         </is>
       </c>
       <c r="AS21" s="23" t="n"/>
-      <c r="AT21" s="66" t="inlineStr"/>
+      <c r="AT21" s="67" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="67" t="inlineStr">
+      <c r="A22" s="68" t="inlineStr">
         <is>
           <t>PS5-03-08 - FZ-08 - Utilities - Power Generation Area - External</t>
         </is>
@@ -3852,7 +3871,7 @@
         </is>
       </c>
       <c r="AS22" s="23" t="n"/>
-      <c r="AT22" s="66" t="inlineStr"/>
+      <c r="AT22" s="67" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="53" t="inlineStr">
@@ -3978,7 +3997,7 @@
         </is>
       </c>
       <c r="AS23" s="23" t="n"/>
-      <c r="AT23" s="66" t="inlineStr"/>
+      <c r="AT23" s="67" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="53" t="inlineStr">
@@ -4100,10 +4119,10 @@
       <c r="AQ24" s="65" t="inlineStr"/>
       <c r="AR24" s="23" t="inlineStr"/>
       <c r="AS24" s="23" t="n"/>
-      <c r="AT24" s="66" t="inlineStr"/>
+      <c r="AT24" s="67" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="67" t="inlineStr">
+      <c r="A25" s="68" t="inlineStr">
         <is>
           <t>PS5-03-11 - FZ-11 - Power Generation Building - Engine Bay 3</t>
         </is>
@@ -4222,10 +4241,10 @@
         </is>
       </c>
       <c r="AS25" s="23" t="n"/>
-      <c r="AT25" s="66" t="inlineStr"/>
+      <c r="AT25" s="67" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="67" t="inlineStr">
+      <c r="A26" s="68" t="inlineStr">
         <is>
           <t>PS5-03-12 - FZ-12 - Power Generation Building - Engine Bay 4</t>
         </is>
@@ -4340,7 +4359,7 @@
         </is>
       </c>
       <c r="AS26" s="23" t="n"/>
-      <c r="AT26" s="66" t="inlineStr"/>
+      <c r="AT26" s="67" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="53" t="inlineStr">
@@ -4466,10 +4485,10 @@
         </is>
       </c>
       <c r="AS27" s="23" t="n"/>
-      <c r="AT27" s="66" t="inlineStr"/>
+      <c r="AT27" s="67" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="67" t="inlineStr">
+      <c r="A28" s="68" t="inlineStr">
         <is>
           <t>PS5-03-14 - FZ-14 - Power Generation Building - Switchgear Room</t>
         </is>
@@ -4505,7 +4524,7 @@
         </is>
       </c>
       <c r="H28" s="24" t="inlineStr"/>
-      <c r="I28" s="69" t="inlineStr">
+      <c r="I28" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -4537,7 +4556,7 @@
       <c r="R28" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S28" s="70" t="inlineStr">
+      <c r="S28" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -4594,10 +4613,10 @@
         </is>
       </c>
       <c r="AS28" s="23" t="n"/>
-      <c r="AT28" s="66" t="inlineStr"/>
+      <c r="AT28" s="67" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="67" t="inlineStr">
+      <c r="A29" s="68" t="inlineStr">
         <is>
           <t>PS5-03-15 - FZ-15 - Power Generation Building - Generator Room 1</t>
         </is>
@@ -4633,7 +4652,7 @@
         </is>
       </c>
       <c r="H29" s="24" t="inlineStr"/>
-      <c r="I29" s="69" t="inlineStr">
+      <c r="I29" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4716,10 +4735,10 @@
         </is>
       </c>
       <c r="AS29" s="23" t="n"/>
-      <c r="AT29" s="66" t="inlineStr"/>
+      <c r="AT29" s="67" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="67" t="inlineStr">
+      <c r="A30" s="68" t="inlineStr">
         <is>
           <t>PS5-03-16 - FZ-16 - Power Generation Building - Generator Room 2</t>
         </is>
@@ -4755,7 +4774,7 @@
         </is>
       </c>
       <c r="H30" s="24" t="inlineStr"/>
-      <c r="I30" s="69" t="inlineStr">
+      <c r="I30" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4838,10 +4857,10 @@
         </is>
       </c>
       <c r="AS30" s="23" t="n"/>
-      <c r="AT30" s="66" t="inlineStr"/>
+      <c r="AT30" s="67" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="67" t="inlineStr">
+      <c r="A31" s="68" t="inlineStr">
         <is>
           <t>PS5-03-17 - FZ-17 - Power Generation Building - Generator Room 3</t>
         </is>
@@ -4873,7 +4892,7 @@
         </is>
       </c>
       <c r="H31" s="24" t="inlineStr"/>
-      <c r="I31" s="69" t="inlineStr">
+      <c r="I31" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4956,10 +4975,10 @@
         </is>
       </c>
       <c r="AS31" s="23" t="n"/>
-      <c r="AT31" s="66" t="inlineStr"/>
+      <c r="AT31" s="67" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="67" t="inlineStr">
+      <c r="A32" s="68" t="inlineStr">
         <is>
           <t>PS5-03-18 - FZ-18 - Power Generation Building - Generator Room 4</t>
         </is>
@@ -4991,7 +5010,7 @@
         </is>
       </c>
       <c r="H32" s="24" t="inlineStr"/>
-      <c r="I32" s="69" t="inlineStr">
+      <c r="I32" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5074,10 +5093,10 @@
         </is>
       </c>
       <c r="AS32" s="23" t="n"/>
-      <c r="AT32" s="66" t="inlineStr"/>
+      <c r="AT32" s="67" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="67" t="inlineStr">
+      <c r="A33" s="68" t="inlineStr">
         <is>
           <t>PS5-03-19 - FZ-19 - Power Generation Building - Battery Room</t>
         </is>
@@ -5113,7 +5132,7 @@
         </is>
       </c>
       <c r="H33" s="24" t="inlineStr"/>
-      <c r="I33" s="69" t="inlineStr">
+      <c r="I33" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5196,7 +5215,7 @@
         </is>
       </c>
       <c r="AS33" s="23" t="n"/>
-      <c r="AT33" s="66" t="inlineStr"/>
+      <c r="AT33" s="67" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="53" t="inlineStr">
@@ -5318,10 +5337,10 @@
         </is>
       </c>
       <c r="AS34" s="23" t="n"/>
-      <c r="AT34" s="66" t="inlineStr"/>
+      <c r="AT34" s="67" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="67" t="inlineStr">
+      <c r="A35" s="68" t="inlineStr">
         <is>
           <t>PS5-03-21 - FZ-21 - Power Generation Building - Air Handling Unit</t>
         </is>
@@ -5353,7 +5372,7 @@
         </is>
       </c>
       <c r="H35" s="24" t="inlineStr"/>
-      <c r="I35" s="69" t="inlineStr">
+      <c r="I35" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5436,10 +5455,10 @@
         </is>
       </c>
       <c r="AS35" s="23" t="n"/>
-      <c r="AT35" s="66" t="inlineStr"/>
+      <c r="AT35" s="67" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="67" t="inlineStr">
+      <c r="A36" s="68" t="inlineStr">
         <is>
           <t>PS5-03-22 - FZ-G1 - Guard House</t>
         </is>
@@ -5471,7 +5490,7 @@
         </is>
       </c>
       <c r="H36" s="24" t="inlineStr"/>
-      <c r="I36" s="69" t="inlineStr">
+      <c r="I36" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5556,10 +5575,10 @@
         </is>
       </c>
       <c r="AS36" s="23" t="n"/>
-      <c r="AT36" s="66" t="inlineStr"/>
+      <c r="AT36" s="67" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="67" t="inlineStr">
+      <c r="A37" s="68" t="inlineStr">
         <is>
           <t>PS5-03-23 - FZ-E1 to E3 - EITS Building</t>
         </is>
@@ -5640,10 +5659,10 @@
       <c r="AQ37" s="65" t="inlineStr"/>
       <c r="AR37" s="23" t="inlineStr"/>
       <c r="AS37" s="23" t="n"/>
-      <c r="AT37" s="66" t="inlineStr"/>
+      <c r="AT37" s="67" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="67" t="inlineStr">
+      <c r="A38" s="68" t="inlineStr">
         <is>
           <t>PS5-03-24 - FZ - Office and Facilities Building</t>
         </is>
@@ -5675,7 +5694,7 @@
         </is>
       </c>
       <c r="H38" s="24" t="inlineStr"/>
-      <c r="I38" s="69" t="inlineStr">
+      <c r="I38" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5758,10 +5777,10 @@
         </is>
       </c>
       <c r="AS38" s="23" t="n"/>
-      <c r="AT38" s="66" t="inlineStr"/>
+      <c r="AT38" s="67" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="67" t="inlineStr">
+      <c r="A39" s="68" t="inlineStr">
         <is>
           <t>PS5-03-25 - FZ - Workshop &amp; Warehouse</t>
         </is>
@@ -5793,7 +5812,7 @@
         </is>
       </c>
       <c r="H39" s="24" t="inlineStr"/>
-      <c r="I39" s="69" t="inlineStr">
+      <c r="I39" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5876,10 +5895,10 @@
         </is>
       </c>
       <c r="AS39" s="23" t="n"/>
-      <c r="AT39" s="66" t="inlineStr"/>
+      <c r="AT39" s="67" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="67" t="inlineStr">
+      <c r="A40" s="68" t="inlineStr">
         <is>
           <t>PS5-04-01 - Office Building PCS System</t>
         </is>
@@ -5895,7 +5914,7 @@
         </is>
       </c>
       <c r="H40" s="24" t="inlineStr"/>
-      <c r="I40" s="69" t="inlineStr">
+      <c r="I40" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5927,7 +5946,7 @@
       <c r="R40" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S40" s="71" t="inlineStr">
+      <c r="S40" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5960,10 +5979,10 @@
       <c r="AQ40" s="65" t="inlineStr"/>
       <c r="AR40" s="23" t="inlineStr"/>
       <c r="AS40" s="23" t="n"/>
-      <c r="AT40" s="66" t="inlineStr"/>
+      <c r="AT40" s="67" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="67" t="inlineStr">
+      <c r="A41" s="68" t="inlineStr">
         <is>
           <t>PS5-04-02 - Office Building SIS/FGS System</t>
         </is>
@@ -5995,7 +6014,7 @@
         </is>
       </c>
       <c r="H41" s="24" t="inlineStr"/>
-      <c r="I41" s="69" t="inlineStr">
+      <c r="I41" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6078,10 +6097,10 @@
         </is>
       </c>
       <c r="AS41" s="23" t="n"/>
-      <c r="AT41" s="66" t="inlineStr"/>
+      <c r="AT41" s="67" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="67" t="inlineStr">
+      <c r="A42" s="68" t="inlineStr">
         <is>
           <t>PS5-04-03 - 33kV ICSS System</t>
         </is>
@@ -6129,7 +6148,7 @@
       <c r="R42" s="62" t="n">
         <v>64</v>
       </c>
-      <c r="S42" s="72" t="inlineStr">
+      <c r="S42" s="73" t="inlineStr">
         <is>
           <t>98%</t>
         </is>
@@ -6162,10 +6181,10 @@
       <c r="AQ42" s="65" t="inlineStr"/>
       <c r="AR42" s="23" t="inlineStr"/>
       <c r="AS42" s="23" t="n"/>
-      <c r="AT42" s="66" t="inlineStr"/>
+      <c r="AT42" s="67" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="67" t="inlineStr">
+      <c r="A43" s="68" t="inlineStr">
         <is>
           <t>PS5-04-04 - 33kV PCS System</t>
         </is>
@@ -6213,7 +6232,7 @@
       <c r="R43" s="62" t="n">
         <v>9</v>
       </c>
-      <c r="S43" s="72" t="inlineStr">
+      <c r="S43" s="73" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6246,10 +6265,10 @@
       <c r="AQ43" s="65" t="inlineStr"/>
       <c r="AR43" s="23" t="inlineStr"/>
       <c r="AS43" s="23" t="n"/>
-      <c r="AT43" s="66" t="inlineStr"/>
+      <c r="AT43" s="67" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="67" t="inlineStr">
+      <c r="A44" s="68" t="inlineStr">
         <is>
           <t>PS5-04-05 - 33kV SIS/FGS System</t>
         </is>
@@ -6265,7 +6284,7 @@
         </is>
       </c>
       <c r="H44" s="24" t="inlineStr"/>
-      <c r="I44" s="68" t="inlineStr">
+      <c r="I44" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -6297,7 +6316,7 @@
       <c r="R44" s="62" t="n">
         <v>19</v>
       </c>
-      <c r="S44" s="72" t="inlineStr">
+      <c r="S44" s="73" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6330,10 +6349,10 @@
       <c r="AQ44" s="65" t="inlineStr"/>
       <c r="AR44" s="23" t="inlineStr"/>
       <c r="AS44" s="23" t="n"/>
-      <c r="AT44" s="66" t="inlineStr"/>
+      <c r="AT44" s="67" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="73" t="inlineStr">
+      <c r="A45" s="74" t="inlineStr">
         <is>
           <t>PS5-05-01 - Emergency Diesel Generator Package</t>
         </is>
@@ -6359,7 +6378,7 @@
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr"/>
-      <c r="G45" s="68" t="inlineStr">
+      <c r="G45" s="69" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6412,8 +6431,10 @@
       <c r="AI45" s="23" t="n">
         <v>109</v>
       </c>
-      <c r="AJ45" s="23" t="n">
-        <v>0</v>
+      <c r="AJ45" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="AK45" s="29" t="inlineStr">
         <is>
@@ -6452,10 +6473,10 @@
         </is>
       </c>
       <c r="AS45" s="23" t="n"/>
-      <c r="AT45" s="66" t="inlineStr"/>
+      <c r="AT45" s="67" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="74" t="inlineStr">
+      <c r="A46" s="75" t="inlineStr">
         <is>
           <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
         </is>
@@ -6574,10 +6595,10 @@
         </is>
       </c>
       <c r="AS46" s="23" t="n"/>
-      <c r="AT46" s="66" t="inlineStr"/>
+      <c r="AT46" s="67" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="67" t="inlineStr">
+      <c r="A47" s="68" t="inlineStr">
         <is>
           <t>PS5-06-01 - AC UPS - EITS Building</t>
         </is>
@@ -6593,7 +6614,7 @@
         </is>
       </c>
       <c r="H47" s="24" t="inlineStr"/>
-      <c r="I47" s="68" t="inlineStr">
+      <c r="I47" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -6625,7 +6646,7 @@
       <c r="R47" s="62" t="n">
         <v>12</v>
       </c>
-      <c r="S47" s="72" t="inlineStr">
+      <c r="S47" s="73" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6658,7 +6679,7 @@
       <c r="AQ47" s="65" t="inlineStr"/>
       <c r="AR47" s="23" t="inlineStr"/>
       <c r="AS47" s="23" t="n"/>
-      <c r="AT47" s="66" t="inlineStr"/>
+      <c r="AT47" s="67" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="53" t="inlineStr">
@@ -6784,10 +6805,10 @@
         </is>
       </c>
       <c r="AS48" s="23" t="n"/>
-      <c r="AT48" s="66" t="inlineStr"/>
+      <c r="AT48" s="67" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="67" t="inlineStr">
+      <c r="A49" s="68" t="inlineStr">
         <is>
           <t>PS5-06-03 - AC UPS - Office &amp; Facilities Building</t>
         </is>
@@ -6819,7 +6840,7 @@
         </is>
       </c>
       <c r="H49" s="24" t="inlineStr"/>
-      <c r="I49" s="69" t="inlineStr">
+      <c r="I49" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6902,10 +6923,10 @@
         </is>
       </c>
       <c r="AS49" s="23" t="n"/>
-      <c r="AT49" s="66" t="inlineStr"/>
+      <c r="AT49" s="67" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="67" t="inlineStr">
+      <c r="A50" s="68" t="inlineStr">
         <is>
           <t>PS5-06-04 - AC UPS - Guard House</t>
         </is>
@@ -6937,7 +6958,7 @@
         </is>
       </c>
       <c r="H50" s="24" t="inlineStr"/>
-      <c r="I50" s="69" t="inlineStr">
+      <c r="I50" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7020,10 +7041,10 @@
         </is>
       </c>
       <c r="AS50" s="23" t="n"/>
-      <c r="AT50" s="66" t="inlineStr"/>
+      <c r="AT50" s="67" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="67" t="inlineStr">
+      <c r="A51" s="68" t="inlineStr">
         <is>
           <t>PS5-06-05 - AC UPS - Workshop &amp; Warehouse</t>
         </is>
@@ -7055,7 +7076,7 @@
         </is>
       </c>
       <c r="H51" s="24" t="inlineStr"/>
-      <c r="I51" s="69" t="inlineStr">
+      <c r="I51" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7138,10 +7159,10 @@
         </is>
       </c>
       <c r="AS51" s="23" t="n"/>
-      <c r="AT51" s="66" t="inlineStr"/>
+      <c r="AT51" s="67" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="67" t="inlineStr">
+      <c r="A52" s="68" t="inlineStr">
         <is>
           <t>PS5-08-01 - PAGA</t>
         </is>
@@ -7173,7 +7194,7 @@
         </is>
       </c>
       <c r="H52" s="24" t="inlineStr"/>
-      <c r="I52" s="69" t="inlineStr">
+      <c r="I52" s="70" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -7205,7 +7226,7 @@
       <c r="R52" s="62" t="n">
         <v>82</v>
       </c>
-      <c r="S52" s="71" t="inlineStr">
+      <c r="S52" s="72" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -7256,10 +7277,10 @@
         </is>
       </c>
       <c r="AS52" s="23" t="n"/>
-      <c r="AT52" s="66" t="inlineStr"/>
+      <c r="AT52" s="67" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="67" t="inlineStr">
+      <c r="A53" s="68" t="inlineStr">
         <is>
           <t>PS5-08-03 - Telephone</t>
         </is>
@@ -7291,7 +7312,7 @@
         </is>
       </c>
       <c r="H53" s="24" t="inlineStr"/>
-      <c r="I53" s="69" t="inlineStr">
+      <c r="I53" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -7323,7 +7344,7 @@
       <c r="R53" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="S53" s="71" t="inlineStr">
+      <c r="S53" s="72" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -7374,10 +7395,10 @@
         </is>
       </c>
       <c r="AS53" s="23" t="n"/>
-      <c r="AT53" s="66" t="inlineStr"/>
+      <c r="AT53" s="67" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="67" t="inlineStr">
+      <c r="A54" s="68" t="inlineStr">
         <is>
           <t>PS5-08-04 - Hotline</t>
         </is>
@@ -7393,7 +7414,7 @@
         </is>
       </c>
       <c r="H54" s="24" t="inlineStr"/>
-      <c r="I54" s="69" t="inlineStr">
+      <c r="I54" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7425,7 +7446,7 @@
       <c r="R54" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S54" s="71" t="inlineStr">
+      <c r="S54" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7458,10 +7479,10 @@
       <c r="AQ54" s="65" t="inlineStr"/>
       <c r="AR54" s="23" t="inlineStr"/>
       <c r="AS54" s="23" t="n"/>
-      <c r="AT54" s="66" t="inlineStr"/>
+      <c r="AT54" s="67" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="67" t="inlineStr">
+      <c r="A55" s="68" t="inlineStr">
         <is>
           <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
         </is>
@@ -7477,7 +7498,7 @@
         </is>
       </c>
       <c r="H55" s="24" t="inlineStr"/>
-      <c r="I55" s="69" t="inlineStr">
+      <c r="I55" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7509,7 +7530,7 @@
       <c r="R55" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S55" s="71" t="inlineStr">
+      <c r="S55" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7542,10 +7563,10 @@
       <c r="AQ55" s="65" t="inlineStr"/>
       <c r="AR55" s="23" t="inlineStr"/>
       <c r="AS55" s="23" t="n"/>
-      <c r="AT55" s="66" t="inlineStr"/>
+      <c r="AT55" s="67" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="67" t="inlineStr">
+      <c r="A56" s="68" t="inlineStr">
         <is>
           <t>PS5-08-11 - Corporate LAN  (SIE)</t>
         </is>
@@ -7577,7 +7598,7 @@
         </is>
       </c>
       <c r="H56" s="24" t="inlineStr"/>
-      <c r="I56" s="69" t="inlineStr">
+      <c r="I56" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -7660,10 +7681,10 @@
         </is>
       </c>
       <c r="AS56" s="23" t="n"/>
-      <c r="AT56" s="66" t="inlineStr"/>
+      <c r="AT56" s="67" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="67" t="inlineStr">
+      <c r="A57" s="68" t="inlineStr">
         <is>
           <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
         </is>
@@ -7695,7 +7716,7 @@
         </is>
       </c>
       <c r="H57" s="24" t="inlineStr"/>
-      <c r="I57" s="69" t="inlineStr">
+      <c r="I57" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7727,7 +7748,7 @@
       <c r="R57" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S57" s="71" t="inlineStr">
+      <c r="S57" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7778,10 +7799,10 @@
         </is>
       </c>
       <c r="AS57" s="23" t="n"/>
-      <c r="AT57" s="66" t="inlineStr"/>
+      <c r="AT57" s="67" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="67" t="inlineStr">
+      <c r="A58" s="68" t="inlineStr">
         <is>
           <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
         </is>
@@ -7813,7 +7834,7 @@
         </is>
       </c>
       <c r="H58" s="24" t="inlineStr"/>
-      <c r="I58" s="69" t="inlineStr">
+      <c r="I58" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7845,7 +7866,7 @@
       <c r="R58" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S58" s="71" t="inlineStr">
+      <c r="S58" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7896,10 +7917,10 @@
         </is>
       </c>
       <c r="AS58" s="23" t="n"/>
-      <c r="AT58" s="66" t="inlineStr"/>
+      <c r="AT58" s="67" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="67" t="inlineStr">
+      <c r="A59" s="68" t="inlineStr">
         <is>
           <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
         </is>
@@ -7931,7 +7952,7 @@
         </is>
       </c>
       <c r="H59" s="24" t="inlineStr"/>
-      <c r="I59" s="69" t="inlineStr">
+      <c r="I59" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7963,7 +7984,7 @@
       <c r="R59" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S59" s="71" t="inlineStr">
+      <c r="S59" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8014,10 +8035,10 @@
         </is>
       </c>
       <c r="AS59" s="23" t="n"/>
-      <c r="AT59" s="66" t="inlineStr"/>
+      <c r="AT59" s="67" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="67" t="inlineStr">
+      <c r="A60" s="68" t="inlineStr">
         <is>
           <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
         </is>
@@ -8049,7 +8070,7 @@
         </is>
       </c>
       <c r="H60" s="24" t="inlineStr"/>
-      <c r="I60" s="69" t="inlineStr">
+      <c r="I60" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8081,7 +8102,7 @@
       <c r="R60" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S60" s="71" t="inlineStr">
+      <c r="S60" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8132,10 +8153,10 @@
         </is>
       </c>
       <c r="AS60" s="23" t="n"/>
-      <c r="AT60" s="66" t="inlineStr"/>
+      <c r="AT60" s="67" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="67" t="inlineStr">
+      <c r="A61" s="68" t="inlineStr">
         <is>
           <t>PS5-08-23 - VHF Trunk Radio System</t>
         </is>
@@ -8167,7 +8188,7 @@
         </is>
       </c>
       <c r="H61" s="24" t="inlineStr"/>
-      <c r="I61" s="69" t="inlineStr">
+      <c r="I61" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8199,7 +8220,7 @@
       <c r="R61" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S61" s="71" t="inlineStr">
+      <c r="S61" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8250,10 +8271,10 @@
         </is>
       </c>
       <c r="AS61" s="23" t="n"/>
-      <c r="AT61" s="66" t="inlineStr"/>
+      <c r="AT61" s="67" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="67" t="inlineStr">
+      <c r="A62" s="68" t="inlineStr">
         <is>
           <t>PS5-08-34 - Satphone</t>
         </is>
@@ -8285,7 +8306,7 @@
         </is>
       </c>
       <c r="H62" s="24" t="inlineStr"/>
-      <c r="I62" s="69" t="inlineStr">
+      <c r="I62" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8317,7 +8338,7 @@
       <c r="R62" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S62" s="71" t="inlineStr">
+      <c r="S62" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8368,10 +8389,10 @@
         </is>
       </c>
       <c r="AS62" s="23" t="n"/>
-      <c r="AT62" s="66" t="inlineStr"/>
+      <c r="AT62" s="67" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="67" t="inlineStr">
+      <c r="A63" s="68" t="inlineStr">
         <is>
           <t>PS5-08-35 - Optical Transport Network</t>
         </is>
@@ -8387,7 +8408,7 @@
         </is>
       </c>
       <c r="H63" s="24" t="inlineStr"/>
-      <c r="I63" s="68" t="inlineStr">
+      <c r="I63" s="69" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -8419,7 +8440,7 @@
       <c r="R63" s="62" t="n">
         <v>39</v>
       </c>
-      <c r="S63" s="70" t="inlineStr">
+      <c r="S63" s="71" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -8452,10 +8473,10 @@
       <c r="AQ63" s="65" t="inlineStr"/>
       <c r="AR63" s="23" t="inlineStr"/>
       <c r="AS63" s="23" t="n"/>
-      <c r="AT63" s="66" t="inlineStr"/>
+      <c r="AT63" s="67" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="67" t="inlineStr">
+      <c r="A64" s="68" t="inlineStr">
         <is>
           <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
         </is>
@@ -8487,7 +8508,7 @@
         </is>
       </c>
       <c r="H64" s="24" t="inlineStr"/>
-      <c r="I64" s="69" t="inlineStr">
+      <c r="I64" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8519,7 +8540,7 @@
       <c r="R64" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S64" s="71" t="inlineStr">
+      <c r="S64" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8570,10 +8591,10 @@
         </is>
       </c>
       <c r="AS64" s="23" t="n"/>
-      <c r="AT64" s="66" t="inlineStr"/>
+      <c r="AT64" s="67" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="67" t="inlineStr">
+      <c r="A65" s="68" t="inlineStr">
         <is>
           <t>PS5-08-51 - Entertainment</t>
         </is>
@@ -8605,7 +8626,7 @@
         </is>
       </c>
       <c r="H65" s="24" t="inlineStr"/>
-      <c r="I65" s="69" t="inlineStr">
+      <c r="I65" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8637,7 +8658,7 @@
       <c r="R65" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S65" s="71" t="inlineStr">
+      <c r="S65" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8688,10 +8709,10 @@
         </is>
       </c>
       <c r="AS65" s="23" t="n"/>
-      <c r="AT65" s="66" t="inlineStr"/>
+      <c r="AT65" s="67" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="67" t="inlineStr">
+      <c r="A66" s="68" t="inlineStr">
         <is>
           <t>PS5-08-52 - Process &amp; Security CCTV</t>
         </is>
@@ -8723,7 +8744,7 @@
         </is>
       </c>
       <c r="H66" s="24" t="inlineStr"/>
-      <c r="I66" s="69" t="inlineStr">
+      <c r="I66" s="70" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -8755,7 +8776,7 @@
       <c r="R66" s="62" t="n">
         <v>22</v>
       </c>
-      <c r="S66" s="71" t="inlineStr">
+      <c r="S66" s="72" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -8806,10 +8827,10 @@
         </is>
       </c>
       <c r="AS66" s="23" t="n"/>
-      <c r="AT66" s="66" t="inlineStr"/>
+      <c r="AT66" s="67" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="67" t="inlineStr">
+      <c r="A67" s="68" t="inlineStr">
         <is>
           <t>PS5-08-55 - Videoconference</t>
         </is>
@@ -8825,7 +8846,7 @@
         </is>
       </c>
       <c r="H67" s="24" t="inlineStr"/>
-      <c r="I67" s="69" t="inlineStr">
+      <c r="I67" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8857,7 +8878,7 @@
       <c r="R67" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S67" s="71" t="inlineStr">
+      <c r="S67" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8890,10 +8911,10 @@
       <c r="AQ67" s="65" t="inlineStr"/>
       <c r="AR67" s="23" t="inlineStr"/>
       <c r="AS67" s="23" t="n"/>
-      <c r="AT67" s="66" t="inlineStr"/>
+      <c r="AT67" s="67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="67" t="inlineStr">
+      <c r="A68" s="68" t="inlineStr">
         <is>
           <t>PS5-08-61 - Meteocean</t>
         </is>
@@ -8925,7 +8946,7 @@
         </is>
       </c>
       <c r="H68" s="24" t="inlineStr"/>
-      <c r="I68" s="69" t="inlineStr">
+      <c r="I68" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8957,7 +8978,7 @@
       <c r="R68" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S68" s="71" t="inlineStr">
+      <c r="S68" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9008,10 +9029,10 @@
         </is>
       </c>
       <c r="AS68" s="23" t="n"/>
-      <c r="AT68" s="66" t="inlineStr"/>
+      <c r="AT68" s="67" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="67" t="inlineStr">
+      <c r="A69" s="68" t="inlineStr">
         <is>
           <t>PS5-08-71 - Structured Cabling (CAT6)</t>
         </is>
@@ -9043,7 +9064,7 @@
         </is>
       </c>
       <c r="H69" s="24" t="inlineStr"/>
-      <c r="I69" s="69" t="inlineStr">
+      <c r="I69" s="70" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -9075,7 +9096,7 @@
       <c r="R69" s="62" t="n">
         <v>10</v>
       </c>
-      <c r="S69" s="71" t="inlineStr">
+      <c r="S69" s="72" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -9126,10 +9147,10 @@
         </is>
       </c>
       <c r="AS69" s="23" t="n"/>
-      <c r="AT69" s="66" t="inlineStr"/>
+      <c r="AT69" s="67" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="67" t="inlineStr">
+      <c r="A70" s="68" t="inlineStr">
         <is>
           <t>PS5-08-72 - Structured Cabling (FO)</t>
         </is>
@@ -9161,7 +9182,7 @@
         </is>
       </c>
       <c r="H70" s="24" t="inlineStr"/>
-      <c r="I70" s="69" t="inlineStr">
+      <c r="I70" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9193,7 +9214,7 @@
       <c r="R70" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S70" s="71" t="inlineStr">
+      <c r="S70" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9244,10 +9265,10 @@
         </is>
       </c>
       <c r="AS70" s="23" t="n"/>
-      <c r="AT70" s="66" t="inlineStr"/>
+      <c r="AT70" s="67" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="67" t="inlineStr">
+      <c r="A71" s="68" t="inlineStr">
         <is>
           <t>PS5-08-81 - Guard tour</t>
         </is>
@@ -9263,7 +9284,7 @@
         </is>
       </c>
       <c r="H71" s="24" t="inlineStr"/>
-      <c r="I71" s="69" t="inlineStr">
+      <c r="I71" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9295,7 +9316,7 @@
       <c r="R71" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S71" s="71" t="inlineStr">
+      <c r="S71" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9328,10 +9349,10 @@
       <c r="AQ71" s="65" t="inlineStr"/>
       <c r="AR71" s="23" t="inlineStr"/>
       <c r="AS71" s="23" t="n"/>
-      <c r="AT71" s="66" t="inlineStr"/>
+      <c r="AT71" s="67" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="67" t="inlineStr">
+      <c r="A72" s="68" t="inlineStr">
         <is>
           <t>PS5-08-82 - Key Management</t>
         </is>
@@ -9347,7 +9368,7 @@
         </is>
       </c>
       <c r="H72" s="24" t="inlineStr"/>
-      <c r="I72" s="69" t="inlineStr">
+      <c r="I72" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9379,7 +9400,7 @@
       <c r="R72" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S72" s="71" t="inlineStr">
+      <c r="S72" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9412,10 +9433,10 @@
       <c r="AQ72" s="65" t="inlineStr"/>
       <c r="AR72" s="23" t="inlineStr"/>
       <c r="AS72" s="23" t="n"/>
-      <c r="AT72" s="66" t="inlineStr"/>
+      <c r="AT72" s="67" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="67" t="inlineStr">
+      <c r="A73" s="68" t="inlineStr">
         <is>
           <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
         </is>
@@ -9447,7 +9468,7 @@
         </is>
       </c>
       <c r="H73" s="24" t="inlineStr"/>
-      <c r="I73" s="69" t="inlineStr">
+      <c r="I73" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9479,7 +9500,7 @@
       <c r="R73" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S73" s="71" t="inlineStr">
+      <c r="S73" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9530,10 +9551,10 @@
         </is>
       </c>
       <c r="AS73" s="23" t="n"/>
-      <c r="AT73" s="66" t="inlineStr"/>
+      <c r="AT73" s="67" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="67" t="inlineStr">
+      <c r="A74" s="68" t="inlineStr">
         <is>
           <t>PS5-08-85 - Access Control, POB &amp; e-Mustering</t>
         </is>
@@ -9565,7 +9586,7 @@
         </is>
       </c>
       <c r="H74" s="24" t="inlineStr"/>
-      <c r="I74" s="69" t="inlineStr">
+      <c r="I74" s="70" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -9597,7 +9618,7 @@
       <c r="R74" s="62" t="n">
         <v>31</v>
       </c>
-      <c r="S74" s="71" t="inlineStr">
+      <c r="S74" s="72" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
@@ -9648,10 +9669,10 @@
         </is>
       </c>
       <c r="AS74" s="23" t="n"/>
-      <c r="AT74" s="66" t="inlineStr"/>
+      <c r="AT74" s="67" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="67" t="inlineStr">
+      <c r="A75" s="68" t="inlineStr">
         <is>
           <t>PS5-08-86 - Integrated Security Management System</t>
         </is>
@@ -9667,7 +9688,7 @@
         </is>
       </c>
       <c r="H75" s="24" t="inlineStr"/>
-      <c r="I75" s="69" t="inlineStr">
+      <c r="I75" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9699,7 +9720,7 @@
       <c r="R75" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S75" s="71" t="inlineStr">
+      <c r="S75" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9732,10 +9753,10 @@
       <c r="AQ75" s="65" t="inlineStr"/>
       <c r="AR75" s="23" t="inlineStr"/>
       <c r="AS75" s="23" t="n"/>
-      <c r="AT75" s="66" t="inlineStr"/>
+      <c r="AT75" s="67" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="67" t="inlineStr">
+      <c r="A76" s="68" t="inlineStr">
         <is>
           <t>PS5-08-92 - Telecom Mast</t>
         </is>
@@ -9751,7 +9772,7 @@
         </is>
       </c>
       <c r="H76" s="24" t="inlineStr"/>
-      <c r="I76" s="69" t="inlineStr">
+      <c r="I76" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9783,7 +9804,7 @@
       <c r="R76" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S76" s="71" t="inlineStr">
+      <c r="S76" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9816,10 +9837,10 @@
       <c r="AQ76" s="65" t="inlineStr"/>
       <c r="AR76" s="23" t="inlineStr"/>
       <c r="AS76" s="23" t="n"/>
-      <c r="AT76" s="66" t="inlineStr"/>
+      <c r="AT76" s="67" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="67" t="inlineStr">
+      <c r="A77" s="68" t="inlineStr">
         <is>
           <t>PS5-08-93 - Telecom Monitoring System</t>
         </is>
@@ -9851,7 +9872,7 @@
         </is>
       </c>
       <c r="H77" s="24" t="inlineStr"/>
-      <c r="I77" s="69" t="inlineStr">
+      <c r="I77" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9883,7 +9904,7 @@
       <c r="R77" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S77" s="71" t="inlineStr">
+      <c r="S77" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9934,10 +9955,10 @@
         </is>
       </c>
       <c r="AS77" s="23" t="n"/>
-      <c r="AT77" s="66" t="inlineStr"/>
+      <c r="AT77" s="67" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="67" t="inlineStr">
+      <c r="A78" s="68" t="inlineStr">
         <is>
           <t>PS5-09-01 - HVAC for Office and Facilities building</t>
         </is>
@@ -9969,7 +9990,7 @@
         </is>
       </c>
       <c r="H78" s="24" t="inlineStr"/>
-      <c r="I78" s="69" t="inlineStr">
+      <c r="I78" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10052,10 +10073,10 @@
         </is>
       </c>
       <c r="AS78" s="23" t="n"/>
-      <c r="AT78" s="66" t="inlineStr"/>
+      <c r="AT78" s="67" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="67" t="inlineStr">
+      <c r="A79" s="68" t="inlineStr">
         <is>
           <t>PS5-09-02 - HVAC for Guard House</t>
         </is>
@@ -10087,7 +10108,7 @@
         </is>
       </c>
       <c r="H79" s="24" t="inlineStr"/>
-      <c r="I79" s="69" t="inlineStr">
+      <c r="I79" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10170,10 +10191,10 @@
         </is>
       </c>
       <c r="AS79" s="23" t="n"/>
-      <c r="AT79" s="66" t="inlineStr"/>
+      <c r="AT79" s="67" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="67" t="inlineStr">
+      <c r="A80" s="68" t="inlineStr">
         <is>
           <t>PS5-09-03 - HVAC for Generator Building</t>
         </is>
@@ -10205,7 +10226,7 @@
         </is>
       </c>
       <c r="H80" s="24" t="inlineStr"/>
-      <c r="I80" s="69" t="inlineStr">
+      <c r="I80" s="70" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -10237,7 +10258,7 @@
       <c r="R80" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="S80" s="71" t="inlineStr">
+      <c r="S80" s="72" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10292,10 +10313,10 @@
         </is>
       </c>
       <c r="AS80" s="23" t="n"/>
-      <c r="AT80" s="66" t="inlineStr"/>
+      <c r="AT80" s="67" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="67" t="inlineStr">
+      <c r="A81" s="68" t="inlineStr">
         <is>
           <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
         </is>
@@ -10327,7 +10348,7 @@
         </is>
       </c>
       <c r="H81" s="24" t="inlineStr"/>
-      <c r="I81" s="69" t="inlineStr">
+      <c r="I81" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10410,7 +10431,7 @@
         </is>
       </c>
       <c r="AS81" s="23" t="n"/>
-      <c r="AT81" s="66" t="inlineStr"/>
+      <c r="AT81" s="67" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="53" t="inlineStr">
@@ -10520,10 +10541,10 @@
       <c r="AQ82" s="65" t="inlineStr"/>
       <c r="AR82" s="23" t="inlineStr"/>
       <c r="AS82" s="23" t="n"/>
-      <c r="AT82" s="66" t="inlineStr"/>
+      <c r="AT82" s="67" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="67" t="inlineStr">
+      <c r="A83" s="68" t="inlineStr">
         <is>
           <t>PS5-0H-01 - HIPPS</t>
         </is>
@@ -10539,7 +10560,7 @@
         </is>
       </c>
       <c r="H83" s="24" t="inlineStr"/>
-      <c r="I83" s="68" t="inlineStr">
+      <c r="I83" s="69" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -10604,10 +10625,10 @@
       <c r="AQ83" s="65" t="inlineStr"/>
       <c r="AR83" s="23" t="inlineStr"/>
       <c r="AS83" s="23" t="n"/>
-      <c r="AT83" s="66" t="inlineStr"/>
+      <c r="AT83" s="67" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="67" t="inlineStr">
+      <c r="A84" s="68" t="inlineStr">
         <is>
           <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
         </is>
@@ -10639,7 +10660,7 @@
         </is>
       </c>
       <c r="H84" s="24" t="inlineStr"/>
-      <c r="I84" s="68" t="inlineStr">
+      <c r="I84" s="69" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -10722,10 +10743,10 @@
         </is>
       </c>
       <c r="AS84" s="23" t="n"/>
-      <c r="AT84" s="66" t="inlineStr"/>
+      <c r="AT84" s="67" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="67" t="inlineStr">
+      <c r="A85" s="68" t="inlineStr">
         <is>
           <t>PS5-25-02 - Crude Oil Export Pump A</t>
         </is>
@@ -10757,7 +10778,7 @@
         </is>
       </c>
       <c r="H85" s="24" t="inlineStr"/>
-      <c r="I85" s="68" t="inlineStr">
+      <c r="I85" s="69" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -10840,10 +10861,10 @@
         </is>
       </c>
       <c r="AS85" s="23" t="n"/>
-      <c r="AT85" s="66" t="inlineStr"/>
+      <c r="AT85" s="67" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="67" t="inlineStr">
+      <c r="A86" s="68" t="inlineStr">
         <is>
           <t>PS5-25-03 - Crude Oil Export Pump B</t>
         </is>
@@ -10875,7 +10896,7 @@
         </is>
       </c>
       <c r="H86" s="24" t="inlineStr"/>
-      <c r="I86" s="68" t="inlineStr">
+      <c r="I86" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -10958,10 +10979,10 @@
         </is>
       </c>
       <c r="AS86" s="23" t="n"/>
-      <c r="AT86" s="66" t="inlineStr"/>
+      <c r="AT86" s="67" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="67" t="inlineStr">
+      <c r="A87" s="68" t="inlineStr">
         <is>
           <t>PS5-25-04 - Crude Oil Export Pump C</t>
         </is>
@@ -10993,7 +11014,7 @@
         </is>
       </c>
       <c r="H87" s="24" t="inlineStr"/>
-      <c r="I87" s="68" t="inlineStr">
+      <c r="I87" s="69" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -11076,10 +11097,10 @@
         </is>
       </c>
       <c r="AS87" s="23" t="n"/>
-      <c r="AT87" s="66" t="inlineStr"/>
+      <c r="AT87" s="67" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="67" t="inlineStr">
+      <c r="A88" s="68" t="inlineStr">
         <is>
           <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
         </is>
@@ -11111,7 +11132,7 @@
         </is>
       </c>
       <c r="H88" s="24" t="inlineStr"/>
-      <c r="I88" s="68" t="inlineStr">
+      <c r="I88" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -11194,10 +11215,10 @@
         </is>
       </c>
       <c r="AS88" s="23" t="n"/>
-      <c r="AT88" s="66" t="inlineStr"/>
+      <c r="AT88" s="67" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="67" t="inlineStr">
+      <c r="A89" s="68" t="inlineStr">
         <is>
           <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
         </is>
@@ -11229,7 +11250,7 @@
         </is>
       </c>
       <c r="H89" s="24" t="inlineStr"/>
-      <c r="I89" s="68" t="inlineStr">
+      <c r="I89" s="69" t="inlineStr">
         <is>
           <t>57%</t>
         </is>
@@ -11312,10 +11333,10 @@
         </is>
       </c>
       <c r="AS89" s="23" t="n"/>
-      <c r="AT89" s="66" t="inlineStr"/>
+      <c r="AT89" s="67" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="67" t="inlineStr">
+      <c r="A90" s="68" t="inlineStr">
         <is>
           <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
         </is>
@@ -11347,7 +11368,7 @@
         </is>
       </c>
       <c r="H90" s="24" t="inlineStr"/>
-      <c r="I90" s="68" t="inlineStr">
+      <c r="I90" s="69" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -11430,10 +11451,10 @@
         </is>
       </c>
       <c r="AS90" s="23" t="n"/>
-      <c r="AT90" s="66" t="inlineStr"/>
+      <c r="AT90" s="67" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="67" t="inlineStr">
+      <c r="A91" s="68" t="inlineStr">
         <is>
           <t>PS5-28-01 - Closed Drain Header 1</t>
         </is>
@@ -11465,7 +11486,7 @@
         </is>
       </c>
       <c r="H91" s="24" t="inlineStr"/>
-      <c r="I91" s="68" t="inlineStr">
+      <c r="I91" s="69" t="inlineStr">
         <is>
           <t>79%</t>
         </is>
@@ -11548,7 +11569,7 @@
         </is>
       </c>
       <c r="AS91" s="23" t="n"/>
-      <c r="AT91" s="66" t="inlineStr"/>
+      <c r="AT91" s="67" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="53" t="inlineStr">
@@ -11670,10 +11691,10 @@
         </is>
       </c>
       <c r="AS92" s="23" t="n"/>
-      <c r="AT92" s="66" t="inlineStr"/>
+      <c r="AT92" s="67" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="67" t="inlineStr">
+      <c r="A93" s="68" t="inlineStr">
         <is>
           <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
         </is>
@@ -11705,7 +11726,7 @@
         </is>
       </c>
       <c r="H93" s="24" t="inlineStr"/>
-      <c r="I93" s="68" t="inlineStr">
+      <c r="I93" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -11788,10 +11809,10 @@
         </is>
       </c>
       <c r="AS93" s="23" t="n"/>
-      <c r="AT93" s="66" t="inlineStr"/>
+      <c r="AT93" s="67" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="67" t="inlineStr">
+      <c r="A94" s="68" t="inlineStr">
         <is>
           <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
         </is>
@@ -11914,7 +11935,7 @@
         </is>
       </c>
       <c r="AS94" s="23" t="n"/>
-      <c r="AT94" s="66" t="inlineStr"/>
+      <c r="AT94" s="67" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="53" t="inlineStr">
@@ -12040,10 +12061,10 @@
         </is>
       </c>
       <c r="AS95" s="23" t="n"/>
-      <c r="AT95" s="66" t="inlineStr"/>
+      <c r="AT95" s="67" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="67" t="inlineStr">
+      <c r="A96" s="68" t="inlineStr">
         <is>
           <t>PS5-28-06 - Relief Drum and Pump</t>
         </is>
@@ -12079,7 +12100,7 @@
         </is>
       </c>
       <c r="H96" s="24" t="inlineStr"/>
-      <c r="I96" s="68" t="inlineStr">
+      <c r="I96" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -12162,10 +12183,10 @@
         </is>
       </c>
       <c r="AS96" s="23" t="n"/>
-      <c r="AT96" s="66" t="inlineStr"/>
+      <c r="AT96" s="67" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="67" t="inlineStr">
+      <c r="A97" s="68" t="inlineStr">
         <is>
           <t>PS5-28-07 - Open Drains (OD2)</t>
         </is>
@@ -12280,10 +12301,10 @@
         </is>
       </c>
       <c r="AS97" s="23" t="n"/>
-      <c r="AT97" s="66" t="inlineStr"/>
+      <c r="AT97" s="67" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="67" t="inlineStr">
+      <c r="A98" s="68" t="inlineStr">
         <is>
           <t>PS5-28-08 - Open Drain Sump and Pumps</t>
         </is>
@@ -12315,7 +12336,7 @@
         </is>
       </c>
       <c r="H98" s="24" t="inlineStr"/>
-      <c r="I98" s="69" t="inlineStr">
+      <c r="I98" s="70" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -12398,10 +12419,10 @@
         </is>
       </c>
       <c r="AS98" s="23" t="n"/>
-      <c r="AT98" s="66" t="inlineStr"/>
+      <c r="AT98" s="67" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="67" t="inlineStr">
+      <c r="A99" s="68" t="inlineStr">
         <is>
           <t>PS5-28-09 - Observation Basin</t>
         </is>
@@ -12433,7 +12454,7 @@
         </is>
       </c>
       <c r="H99" s="24" t="inlineStr"/>
-      <c r="I99" s="68" t="inlineStr">
+      <c r="I99" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -12516,10 +12537,10 @@
         </is>
       </c>
       <c r="AS99" s="23" t="n"/>
-      <c r="AT99" s="66" t="inlineStr"/>
+      <c r="AT99" s="67" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="67" t="inlineStr">
+      <c r="A100" s="68" t="inlineStr">
         <is>
           <t>PS5-28-10 - Oil Skimmer Package</t>
         </is>
@@ -12551,7 +12572,7 @@
         </is>
       </c>
       <c r="H100" s="24" t="inlineStr"/>
-      <c r="I100" s="69" t="inlineStr">
+      <c r="I100" s="70" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -12634,10 +12655,10 @@
         </is>
       </c>
       <c r="AS100" s="23" t="n"/>
-      <c r="AT100" s="66" t="inlineStr"/>
+      <c r="AT100" s="67" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="67" t="inlineStr">
+      <c r="A101" s="68" t="inlineStr">
         <is>
           <t>PS5-28-11 - Open Drain Interceptor</t>
         </is>
@@ -12669,7 +12690,7 @@
         </is>
       </c>
       <c r="H101" s="24" t="inlineStr"/>
-      <c r="I101" s="68" t="inlineStr">
+      <c r="I101" s="69" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -12752,10 +12773,10 @@
         </is>
       </c>
       <c r="AS101" s="23" t="n"/>
-      <c r="AT101" s="66" t="inlineStr"/>
+      <c r="AT101" s="67" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="67" t="inlineStr">
+      <c r="A102" s="68" t="inlineStr">
         <is>
           <t>PS5-28-12 - Open Drains (OD3)</t>
         </is>
@@ -12787,7 +12808,7 @@
         </is>
       </c>
       <c r="H102" s="24" t="inlineStr"/>
-      <c r="I102" s="68" t="inlineStr">
+      <c r="I102" s="69" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -12870,10 +12891,10 @@
         </is>
       </c>
       <c r="AS102" s="23" t="n"/>
-      <c r="AT102" s="66" t="inlineStr"/>
+      <c r="AT102" s="67" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="67" t="inlineStr">
+      <c r="A103" s="68" t="inlineStr">
         <is>
           <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
         </is>
@@ -12905,7 +12926,7 @@
         </is>
       </c>
       <c r="H103" s="24" t="inlineStr"/>
-      <c r="I103" s="68" t="inlineStr">
+      <c r="I103" s="69" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -12988,10 +13009,10 @@
         </is>
       </c>
       <c r="AS103" s="23" t="n"/>
-      <c r="AT103" s="66" t="inlineStr"/>
+      <c r="AT103" s="67" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="67" t="inlineStr">
+      <c r="A104" s="68" t="inlineStr">
         <is>
           <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
         </is>
@@ -13023,7 +13044,7 @@
         </is>
       </c>
       <c r="H104" s="24" t="inlineStr"/>
-      <c r="I104" s="68" t="inlineStr">
+      <c r="I104" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -13106,10 +13127,10 @@
         </is>
       </c>
       <c r="AS104" s="23" t="n"/>
-      <c r="AT104" s="66" t="inlineStr"/>
+      <c r="AT104" s="67" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="67" t="inlineStr">
+      <c r="A105" s="68" t="inlineStr">
         <is>
           <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
         </is>
@@ -13141,7 +13162,7 @@
         </is>
       </c>
       <c r="H105" s="24" t="inlineStr"/>
-      <c r="I105" s="68" t="inlineStr">
+      <c r="I105" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -13224,10 +13245,10 @@
         </is>
       </c>
       <c r="AS105" s="23" t="n"/>
-      <c r="AT105" s="66" t="inlineStr"/>
+      <c r="AT105" s="67" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="67" t="inlineStr">
+      <c r="A106" s="68" t="inlineStr">
         <is>
           <t>PS5-28-16 - LP Relief Header</t>
         </is>
@@ -13259,7 +13280,7 @@
         </is>
       </c>
       <c r="H106" s="24" t="inlineStr"/>
-      <c r="I106" s="68" t="inlineStr">
+      <c r="I106" s="69" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -13342,10 +13363,10 @@
         </is>
       </c>
       <c r="AS106" s="23" t="n"/>
-      <c r="AT106" s="66" t="inlineStr"/>
+      <c r="AT106" s="67" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="67" t="inlineStr">
+      <c r="A107" s="68" t="inlineStr">
         <is>
           <t>PS5-28-17 - Reinjection Pump</t>
         </is>
@@ -13377,7 +13398,7 @@
         </is>
       </c>
       <c r="H107" s="24" t="inlineStr"/>
-      <c r="I107" s="68" t="inlineStr">
+      <c r="I107" s="69" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -13460,10 +13481,10 @@
         </is>
       </c>
       <c r="AS107" s="23" t="n"/>
-      <c r="AT107" s="66" t="inlineStr"/>
+      <c r="AT107" s="67" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="67" t="inlineStr">
+      <c r="A108" s="68" t="inlineStr">
         <is>
           <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
         </is>
@@ -13495,7 +13516,7 @@
         </is>
       </c>
       <c r="H108" s="24" t="inlineStr"/>
-      <c r="I108" s="69" t="inlineStr">
+      <c r="I108" s="70" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -13578,10 +13599,10 @@
         </is>
       </c>
       <c r="AS108" s="23" t="n"/>
-      <c r="AT108" s="66" t="inlineStr"/>
+      <c r="AT108" s="67" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="67" t="inlineStr">
+      <c r="A109" s="68" t="inlineStr">
         <is>
           <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
         </is>
@@ -13613,7 +13634,7 @@
         </is>
       </c>
       <c r="H109" s="24" t="inlineStr"/>
-      <c r="I109" s="69" t="inlineStr">
+      <c r="I109" s="70" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -13696,10 +13717,10 @@
         </is>
       </c>
       <c r="AS109" s="23" t="n"/>
-      <c r="AT109" s="66" t="inlineStr"/>
+      <c r="AT109" s="67" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="67" t="inlineStr">
+      <c r="A110" s="68" t="inlineStr">
         <is>
           <t>PS5-50-03 - Water Pre-Treatment Package</t>
         </is>
@@ -13731,7 +13752,7 @@
         </is>
       </c>
       <c r="H110" s="24" t="inlineStr"/>
-      <c r="I110" s="69" t="inlineStr">
+      <c r="I110" s="70" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -13814,10 +13835,10 @@
         </is>
       </c>
       <c r="AS110" s="23" t="n"/>
-      <c r="AT110" s="66" t="inlineStr"/>
+      <c r="AT110" s="67" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="73" t="inlineStr">
+      <c r="A111" s="74" t="inlineStr">
         <is>
           <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
@@ -13847,7 +13868,7 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="G111" s="68" t="inlineStr">
+      <c r="G111" s="69" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -13857,7 +13878,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I111" s="68" t="inlineStr">
+      <c r="I111" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -13940,10 +13961,10 @@
         </is>
       </c>
       <c r="AS111" s="23" t="n"/>
-      <c r="AT111" s="66" t="inlineStr"/>
+      <c r="AT111" s="67" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="67" t="inlineStr">
+      <c r="A112" s="68" t="inlineStr">
         <is>
           <t>PS5-53-02 - Water Distribution Pump A/B</t>
         </is>
@@ -13975,7 +13996,7 @@
         </is>
       </c>
       <c r="H112" s="24" t="inlineStr"/>
-      <c r="I112" s="68" t="inlineStr">
+      <c r="I112" s="69" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -14058,10 +14079,10 @@
         </is>
       </c>
       <c r="AS112" s="23" t="n"/>
-      <c r="AT112" s="66" t="inlineStr"/>
+      <c r="AT112" s="67" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="67" t="inlineStr">
+      <c r="A113" s="68" t="inlineStr">
         <is>
           <t>PS5-53-03 - Water Softener Package</t>
         </is>
@@ -14093,7 +14114,7 @@
         </is>
       </c>
       <c r="H113" s="24" t="inlineStr"/>
-      <c r="I113" s="68" t="inlineStr">
+      <c r="I113" s="69" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -14176,10 +14197,10 @@
         </is>
       </c>
       <c r="AS113" s="23" t="n"/>
-      <c r="AT113" s="66" t="inlineStr"/>
+      <c r="AT113" s="67" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="67" t="inlineStr">
+      <c r="A114" s="68" t="inlineStr">
         <is>
           <t>PS5-53-04 - Water Treatment Purification Package</t>
         </is>
@@ -14211,7 +14232,7 @@
         </is>
       </c>
       <c r="H114" s="24" t="inlineStr"/>
-      <c r="I114" s="69" t="inlineStr">
+      <c r="I114" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14294,10 +14315,10 @@
         </is>
       </c>
       <c r="AS114" s="23" t="n"/>
-      <c r="AT114" s="66" t="inlineStr"/>
+      <c r="AT114" s="67" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="67" t="inlineStr">
+      <c r="A115" s="68" t="inlineStr">
         <is>
           <t>PS5-53-05 - Water Distribution Header</t>
         </is>
@@ -14412,10 +14433,10 @@
         </is>
       </c>
       <c r="AS115" s="23" t="n"/>
-      <c r="AT115" s="66" t="inlineStr"/>
+      <c r="AT115" s="67" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="67" t="inlineStr">
+      <c r="A116" s="68" t="inlineStr">
         <is>
           <t>PS5-53-06 - Water Distribution Consumers</t>
         </is>
@@ -14451,7 +14472,7 @@
         </is>
       </c>
       <c r="H116" s="24" t="inlineStr"/>
-      <c r="I116" s="68" t="inlineStr">
+      <c r="I116" s="69" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -14534,7 +14555,7 @@
         </is>
       </c>
       <c r="AS116" s="23" t="n"/>
-      <c r="AT116" s="66" t="inlineStr"/>
+      <c r="AT116" s="67" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="53" t="inlineStr">
@@ -14660,7 +14681,7 @@
         </is>
       </c>
       <c r="AS117" s="23" t="n"/>
-      <c r="AT117" s="66" t="inlineStr"/>
+      <c r="AT117" s="67" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="53" t="inlineStr">
@@ -14782,14 +14803,14 @@
       </c>
       <c r="AR118" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
         </is>
       </c>
       <c r="AS118" s="23" t="n"/>
-      <c r="AT118" s="66" t="inlineStr"/>
+      <c r="AT118" s="67" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="67" t="inlineStr">
+      <c r="A119" s="68" t="inlineStr">
         <is>
           <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -14829,7 +14850,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I119" s="68" t="inlineStr">
+      <c r="I119" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -14861,7 +14882,7 @@
       <c r="R119" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S119" s="70" t="inlineStr">
+      <c r="S119" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -14912,7 +14933,7 @@
         </is>
       </c>
       <c r="AS119" s="23" t="n"/>
-      <c r="AT119" s="66" t="inlineStr"/>
+      <c r="AT119" s="67" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="53" t="inlineStr">
@@ -15038,10 +15059,10 @@
         </is>
       </c>
       <c r="AS120" s="23" t="n"/>
-      <c r="AT120" s="66" t="inlineStr"/>
+      <c r="AT120" s="67" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="67" t="inlineStr">
+      <c r="A121" s="68" t="inlineStr">
         <is>
           <t>PS5-60-05 - Power Gen Package B (UCP)</t>
         </is>
@@ -15113,7 +15134,7 @@
       <c r="R121" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="S121" s="70" t="inlineStr">
+      <c r="S121" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15156,10 +15177,10 @@
       <c r="AQ121" s="65" t="inlineStr"/>
       <c r="AR121" s="23" t="inlineStr"/>
       <c r="AS121" s="23" t="n"/>
-      <c r="AT121" s="66" t="inlineStr"/>
+      <c r="AT121" s="67" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="67" t="inlineStr">
+      <c r="A122" s="68" t="inlineStr">
         <is>
           <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -15199,7 +15220,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I122" s="68" t="inlineStr">
+      <c r="I122" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -15231,7 +15252,7 @@
       <c r="R122" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S122" s="70" t="inlineStr">
+      <c r="S122" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15274,10 +15295,10 @@
       <c r="AQ122" s="65" t="inlineStr"/>
       <c r="AR122" s="23" t="inlineStr"/>
       <c r="AS122" s="23" t="n"/>
-      <c r="AT122" s="66" t="inlineStr"/>
+      <c r="AT122" s="67" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="67" t="inlineStr">
+      <c r="A123" s="68" t="inlineStr">
         <is>
           <t>PS5-60-07 - Power Generation Package C</t>
         </is>
@@ -15402,10 +15423,10 @@
         </is>
       </c>
       <c r="AS123" s="23" t="n"/>
-      <c r="AT123" s="66" t="inlineStr"/>
+      <c r="AT123" s="67" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="67" t="inlineStr">
+      <c r="A124" s="68" t="inlineStr">
         <is>
           <t>PS5-60-08 - Power Gen Package C (UCP)</t>
         </is>
@@ -15477,7 +15498,7 @@
       <c r="R124" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="S124" s="70" t="inlineStr">
+      <c r="S124" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15520,10 +15541,10 @@
       <c r="AQ124" s="65" t="inlineStr"/>
       <c r="AR124" s="23" t="inlineStr"/>
       <c r="AS124" s="23" t="n"/>
-      <c r="AT124" s="66" t="inlineStr"/>
+      <c r="AT124" s="67" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="67" t="inlineStr">
+      <c r="A125" s="68" t="inlineStr">
         <is>
           <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -15563,7 +15584,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I125" s="68" t="inlineStr">
+      <c r="I125" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -15595,7 +15616,7 @@
       <c r="R125" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S125" s="70" t="inlineStr">
+      <c r="S125" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15638,10 +15659,10 @@
       <c r="AQ125" s="65" t="inlineStr"/>
       <c r="AR125" s="23" t="inlineStr"/>
       <c r="AS125" s="23" t="n"/>
-      <c r="AT125" s="66" t="inlineStr"/>
+      <c r="AT125" s="67" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="67" t="inlineStr">
+      <c r="A126" s="68" t="inlineStr">
         <is>
           <t>PS5-60-10 - Power Generation Package D</t>
         </is>
@@ -15713,7 +15734,7 @@
       <c r="R126" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="S126" s="70" t="inlineStr">
+      <c r="S126" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15764,10 +15785,10 @@
         </is>
       </c>
       <c r="AS126" s="23" t="n"/>
-      <c r="AT126" s="66" t="inlineStr"/>
+      <c r="AT126" s="67" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="67" t="inlineStr">
+      <c r="A127" s="68" t="inlineStr">
         <is>
           <t>PS5-60-11 - Power Gen Package D (UCP)</t>
         </is>
@@ -15839,7 +15860,7 @@
       <c r="R127" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="S127" s="70" t="inlineStr">
+      <c r="S127" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15882,10 +15903,10 @@
       <c r="AQ127" s="65" t="inlineStr"/>
       <c r="AR127" s="23" t="inlineStr"/>
       <c r="AS127" s="23" t="n"/>
-      <c r="AT127" s="66" t="inlineStr"/>
+      <c r="AT127" s="67" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="67" t="inlineStr">
+      <c r="A128" s="68" t="inlineStr">
         <is>
           <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -15925,7 +15946,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I128" s="68" t="inlineStr">
+      <c r="I128" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -15957,7 +15978,7 @@
       <c r="R128" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S128" s="70" t="inlineStr">
+      <c r="S128" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16000,10 +16021,10 @@
       <c r="AQ128" s="65" t="inlineStr"/>
       <c r="AR128" s="23" t="inlineStr"/>
       <c r="AS128" s="23" t="n"/>
-      <c r="AT128" s="66" t="inlineStr"/>
+      <c r="AT128" s="67" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="67" t="inlineStr">
+      <c r="A129" s="68" t="inlineStr">
         <is>
           <t>PS5-60-13 - Power Generation Package E</t>
         </is>
@@ -16126,10 +16147,10 @@
         </is>
       </c>
       <c r="AS129" s="23" t="n"/>
-      <c r="AT129" s="66" t="inlineStr"/>
+      <c r="AT129" s="67" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="67" t="inlineStr">
+      <c r="A130" s="68" t="inlineStr">
         <is>
           <t>PS5-60-14 - Power Gen Package E (UCP)</t>
         </is>
@@ -16201,7 +16222,7 @@
       <c r="R130" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="S130" s="70" t="inlineStr">
+      <c r="S130" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16244,10 +16265,10 @@
       <c r="AQ130" s="65" t="inlineStr"/>
       <c r="AR130" s="23" t="inlineStr"/>
       <c r="AS130" s="23" t="n"/>
-      <c r="AT130" s="66" t="inlineStr"/>
+      <c r="AT130" s="67" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="67" t="inlineStr">
+      <c r="A131" s="68" t="inlineStr">
         <is>
           <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -16287,7 +16308,7 @@
           <t>full</t>
         </is>
       </c>
-      <c r="I131" s="68" t="inlineStr">
+      <c r="I131" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -16319,7 +16340,7 @@
       <c r="R131" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S131" s="70" t="inlineStr">
+      <c r="S131" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16362,10 +16383,10 @@
       <c r="AQ131" s="65" t="inlineStr"/>
       <c r="AR131" s="23" t="inlineStr"/>
       <c r="AS131" s="23" t="n"/>
-      <c r="AT131" s="66" t="inlineStr"/>
+      <c r="AT131" s="67" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="67" t="inlineStr">
+      <c r="A132" s="68" t="inlineStr">
         <is>
           <t>PS5-60-16 - Power Generation Package F</t>
         </is>
@@ -16433,7 +16454,7 @@
       <c r="R132" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="S132" s="70" t="inlineStr">
+      <c r="S132" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16484,10 +16505,10 @@
         </is>
       </c>
       <c r="AS132" s="23" t="n"/>
-      <c r="AT132" s="66" t="inlineStr"/>
+      <c r="AT132" s="67" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="67" t="inlineStr">
+      <c r="A133" s="68" t="inlineStr">
         <is>
           <t>PS5-60-17 - Power Gen Package F (UCP)</t>
         </is>
@@ -16519,7 +16540,7 @@
         </is>
       </c>
       <c r="H133" s="24" t="inlineStr"/>
-      <c r="I133" s="68" t="inlineStr">
+      <c r="I133" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -16551,7 +16572,7 @@
       <c r="R133" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="S133" s="70" t="inlineStr">
+      <c r="S133" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16594,10 +16615,10 @@
       <c r="AQ133" s="65" t="inlineStr"/>
       <c r="AR133" s="23" t="inlineStr"/>
       <c r="AS133" s="23" t="n"/>
-      <c r="AT133" s="66" t="inlineStr"/>
+      <c r="AT133" s="67" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="67" t="inlineStr">
+      <c r="A134" s="68" t="inlineStr">
         <is>
           <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -16633,7 +16654,7 @@
         </is>
       </c>
       <c r="H134" s="24" t="inlineStr"/>
-      <c r="I134" s="68" t="inlineStr">
+      <c r="I134" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -16665,7 +16686,7 @@
       <c r="R134" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S134" s="70" t="inlineStr">
+      <c r="S134" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16708,10 +16729,10 @@
       <c r="AQ134" s="65" t="inlineStr"/>
       <c r="AR134" s="23" t="inlineStr"/>
       <c r="AS134" s="23" t="n"/>
-      <c r="AT134" s="66" t="inlineStr"/>
+      <c r="AT134" s="67" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="67" t="inlineStr">
+      <c r="A135" s="68" t="inlineStr">
         <is>
           <t>PS5-60-19 - Power Generation Package G</t>
         </is>
@@ -16826,10 +16847,10 @@
         </is>
       </c>
       <c r="AS135" s="23" t="n"/>
-      <c r="AT135" s="66" t="inlineStr"/>
+      <c r="AT135" s="67" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="67" t="inlineStr">
+      <c r="A136" s="68" t="inlineStr">
         <is>
           <t>PS5-60-20 - Power Gen Package G (UCP)</t>
         </is>
@@ -16865,7 +16886,7 @@
         </is>
       </c>
       <c r="H136" s="24" t="inlineStr"/>
-      <c r="I136" s="68" t="inlineStr">
+      <c r="I136" s="69" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -16897,7 +16918,7 @@
       <c r="R136" s="62" t="n">
         <v>3</v>
       </c>
-      <c r="S136" s="70" t="inlineStr">
+      <c r="S136" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16940,10 +16961,10 @@
       <c r="AQ136" s="65" t="inlineStr"/>
       <c r="AR136" s="23" t="inlineStr"/>
       <c r="AS136" s="23" t="n"/>
-      <c r="AT136" s="66" t="inlineStr"/>
+      <c r="AT136" s="67" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="67" t="inlineStr">
+      <c r="A137" s="68" t="inlineStr">
         <is>
           <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -16979,7 +17000,7 @@
         </is>
       </c>
       <c r="H137" s="24" t="inlineStr"/>
-      <c r="I137" s="68" t="inlineStr">
+      <c r="I137" s="69" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -17011,7 +17032,7 @@
       <c r="R137" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S137" s="70" t="inlineStr">
+      <c r="S137" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -17054,10 +17075,10 @@
       <c r="AQ137" s="65" t="inlineStr"/>
       <c r="AR137" s="23" t="inlineStr"/>
       <c r="AS137" s="23" t="n"/>
-      <c r="AT137" s="66" t="inlineStr"/>
+      <c r="AT137" s="67" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="67" t="inlineStr">
+      <c r="A138" s="68" t="inlineStr">
         <is>
           <t>PS5-60-22 - Power Gen Master UCP</t>
         </is>
@@ -17097,7 +17118,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I138" s="68" t="inlineStr">
+      <c r="I138" s="69" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -17129,7 +17150,7 @@
       <c r="R138" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="S138" s="70" t="inlineStr">
+      <c r="S138" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -17182,7 +17203,7 @@
         </is>
       </c>
       <c r="AS138" s="23" t="n"/>
-      <c r="AT138" s="66" t="inlineStr"/>
+      <c r="AT138" s="67" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="53" t="inlineStr">
@@ -17304,10 +17325,10 @@
         </is>
       </c>
       <c r="AS139" s="23" t="n"/>
-      <c r="AT139" s="66" t="inlineStr"/>
+      <c r="AT139" s="67" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="67" t="inlineStr">
+      <c r="A140" s="68" t="inlineStr">
         <is>
           <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
         </is>
@@ -17430,10 +17451,10 @@
         </is>
       </c>
       <c r="AS140" s="23" t="n"/>
-      <c r="AT140" s="66" t="inlineStr"/>
+      <c r="AT140" s="67" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="67" t="inlineStr">
+      <c r="A141" s="68" t="inlineStr">
         <is>
           <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
         </is>
@@ -17556,7 +17577,7 @@
         </is>
       </c>
       <c r="AS141" s="23" t="n"/>
-      <c r="AT141" s="66" t="inlineStr"/>
+      <c r="AT141" s="67" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="53" t="inlineStr">
@@ -17682,7 +17703,7 @@
         </is>
       </c>
       <c r="AS142" s="23" t="n"/>
-      <c r="AT142" s="66" t="inlineStr"/>
+      <c r="AT142" s="67" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="53" t="inlineStr">
@@ -17808,10 +17829,10 @@
         </is>
       </c>
       <c r="AS143" s="23" t="n"/>
-      <c r="AT143" s="66" t="inlineStr"/>
+      <c r="AT143" s="67" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="73" t="inlineStr">
+      <c r="A144" s="74" t="inlineStr">
         <is>
           <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
@@ -17841,7 +17862,7 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="G144" s="68" t="inlineStr">
+      <c r="G144" s="69" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -17934,7 +17955,7 @@
         </is>
       </c>
       <c r="AS144" s="23" t="n"/>
-      <c r="AT144" s="66" t="inlineStr"/>
+      <c r="AT144" s="67" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="53" t="inlineStr">
@@ -18060,7 +18081,7 @@
         </is>
       </c>
       <c r="AS145" s="23" t="n"/>
-      <c r="AT145" s="66" t="inlineStr"/>
+      <c r="AT145" s="67" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="53" t="inlineStr">
@@ -18186,7 +18207,7 @@
         </is>
       </c>
       <c r="AS146" s="23" t="n"/>
-      <c r="AT146" s="66" t="inlineStr"/>
+      <c r="AT146" s="67" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="53" t="inlineStr">
@@ -18312,7 +18333,7 @@
         </is>
       </c>
       <c r="AS147" s="23" t="n"/>
-      <c r="AT147" s="66" t="inlineStr"/>
+      <c r="AT147" s="67" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="53" t="inlineStr">
@@ -18438,7 +18459,7 @@
         </is>
       </c>
       <c r="AS148" s="23" t="n"/>
-      <c r="AT148" s="66" t="inlineStr"/>
+      <c r="AT148" s="67" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="53" t="inlineStr">
@@ -18564,7 +18585,7 @@
         </is>
       </c>
       <c r="AS149" s="23" t="n"/>
-      <c r="AT149" s="66" t="inlineStr"/>
+      <c r="AT149" s="67" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="53" t="inlineStr">
@@ -18690,10 +18711,10 @@
         </is>
       </c>
       <c r="AS150" s="23" t="n"/>
-      <c r="AT150" s="66" t="inlineStr"/>
+      <c r="AT150" s="67" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="74" t="inlineStr">
+      <c r="A151" s="75" t="inlineStr">
         <is>
           <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
@@ -18812,7 +18833,7 @@
         </is>
       </c>
       <c r="AS151" s="23" t="n"/>
-      <c r="AT151" s="66" t="inlineStr"/>
+      <c r="AT151" s="67" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="53" t="inlineStr">
@@ -18934,7 +18955,7 @@
         </is>
       </c>
       <c r="AS152" s="23" t="n"/>
-      <c r="AT152" s="66" t="inlineStr"/>
+      <c r="AT152" s="67" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="53" t="inlineStr">
@@ -19060,7 +19081,7 @@
         </is>
       </c>
       <c r="AS153" s="23" t="n"/>
-      <c r="AT153" s="66" t="inlineStr"/>
+      <c r="AT153" s="67" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="53" t="inlineStr">
@@ -19186,7 +19207,7 @@
         </is>
       </c>
       <c r="AS154" s="23" t="n"/>
-      <c r="AT154" s="66" t="inlineStr"/>
+      <c r="AT154" s="67" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="53" t="inlineStr">
@@ -19312,7 +19333,7 @@
         </is>
       </c>
       <c r="AS155" s="23" t="n"/>
-      <c r="AT155" s="66" t="inlineStr"/>
+      <c r="AT155" s="67" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="53" t="inlineStr">
@@ -19438,10 +19459,10 @@
         </is>
       </c>
       <c r="AS156" s="23" t="n"/>
-      <c r="AT156" s="66" t="inlineStr"/>
+      <c r="AT156" s="67" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="67" t="inlineStr">
+      <c r="A157" s="68" t="inlineStr">
         <is>
           <t>PS5-60-41 - Injector Tip Cooling Module G</t>
         </is>
@@ -19477,7 +19498,7 @@
         </is>
       </c>
       <c r="H157" s="24" t="inlineStr"/>
-      <c r="I157" s="68" t="inlineStr">
+      <c r="I157" s="69" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -19560,10 +19581,10 @@
         </is>
       </c>
       <c r="AS157" s="23" t="n"/>
-      <c r="AT157" s="66" t="inlineStr"/>
+      <c r="AT157" s="67" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="74" t="inlineStr">
+      <c r="A158" s="75" t="inlineStr">
         <is>
           <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
@@ -19682,7 +19703,7 @@
         </is>
       </c>
       <c r="AS158" s="23" t="n"/>
-      <c r="AT158" s="66" t="inlineStr"/>
+      <c r="AT158" s="67" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="53" t="inlineStr">
@@ -19804,7 +19825,7 @@
         </is>
       </c>
       <c r="AS159" s="23" t="n"/>
-      <c r="AT159" s="66" t="inlineStr"/>
+      <c r="AT159" s="67" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="53" t="inlineStr">
@@ -19930,7 +19951,7 @@
         </is>
       </c>
       <c r="AS160" s="23" t="n"/>
-      <c r="AT160" s="66" t="inlineStr"/>
+      <c r="AT160" s="67" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="53" t="inlineStr">
@@ -20056,7 +20077,7 @@
         </is>
       </c>
       <c r="AS161" s="23" t="n"/>
-      <c r="AT161" s="66" t="inlineStr"/>
+      <c r="AT161" s="67" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="53" t="inlineStr">
@@ -20178,7 +20199,7 @@
         </is>
       </c>
       <c r="AS162" s="23" t="n"/>
-      <c r="AT162" s="66" t="inlineStr"/>
+      <c r="AT162" s="67" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="53" t="inlineStr">
@@ -20304,10 +20325,10 @@
         </is>
       </c>
       <c r="AS163" s="23" t="n"/>
-      <c r="AT163" s="66" t="inlineStr"/>
+      <c r="AT163" s="67" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="67" t="inlineStr">
+      <c r="A164" s="68" t="inlineStr">
         <is>
           <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
         </is>
@@ -20422,10 +20443,10 @@
         </is>
       </c>
       <c r="AS164" s="23" t="n"/>
-      <c r="AT164" s="66" t="inlineStr"/>
+      <c r="AT164" s="67" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="67" t="inlineStr">
+      <c r="A165" s="68" t="inlineStr">
         <is>
           <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
         </is>
@@ -20497,7 +20518,7 @@
       <c r="R165" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S165" s="70" t="inlineStr">
+      <c r="S165" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -20538,12 +20559,16 @@
       </c>
       <c r="AP165" s="65" t="inlineStr"/>
       <c r="AQ165" s="65" t="inlineStr"/>
-      <c r="AR165" s="23" t="inlineStr"/>
+      <c r="AR165" s="23" t="inlineStr">
+        <is>
+          <t>OBSERVATION -CLEANING ON PROGRESS</t>
+        </is>
+      </c>
       <c r="AS165" s="23" t="n"/>
-      <c r="AT165" s="66" t="inlineStr"/>
+      <c r="AT165" s="67" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="67" t="inlineStr">
+      <c r="A166" s="68" t="inlineStr">
         <is>
           <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
         </is>
@@ -20615,7 +20640,7 @@
       <c r="R166" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S166" s="70" t="inlineStr">
+      <c r="S166" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -20658,10 +20683,10 @@
       <c r="AQ166" s="65" t="inlineStr"/>
       <c r="AR166" s="23" t="inlineStr"/>
       <c r="AS166" s="23" t="n"/>
-      <c r="AT166" s="66" t="inlineStr"/>
+      <c r="AT166" s="67" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="67" t="inlineStr">
+      <c r="A167" s="68" t="inlineStr">
         <is>
           <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
         </is>
@@ -20733,7 +20758,7 @@
       <c r="R167" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S167" s="70" t="inlineStr">
+      <c r="S167" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -20776,10 +20801,10 @@
       <c r="AQ167" s="65" t="inlineStr"/>
       <c r="AR167" s="23" t="inlineStr"/>
       <c r="AS167" s="23" t="n"/>
-      <c r="AT167" s="66" t="inlineStr"/>
+      <c r="AT167" s="67" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="67" t="inlineStr">
+      <c r="A168" s="68" t="inlineStr">
         <is>
           <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
         </is>
@@ -20819,7 +20844,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I168" s="68" t="inlineStr">
+      <c r="I168" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -20851,7 +20876,7 @@
       <c r="R168" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S168" s="70" t="inlineStr">
+      <c r="S168" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -20894,10 +20919,10 @@
       <c r="AQ168" s="65" t="inlineStr"/>
       <c r="AR168" s="23" t="inlineStr"/>
       <c r="AS168" s="23" t="n"/>
-      <c r="AT168" s="66" t="inlineStr"/>
+      <c r="AT168" s="67" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="67" t="inlineStr">
+      <c r="A169" s="68" t="inlineStr">
         <is>
           <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
         </is>
@@ -20961,7 +20986,7 @@
       <c r="R169" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S169" s="70" t="inlineStr">
+      <c r="S169" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21004,10 +21029,10 @@
       <c r="AQ169" s="65" t="inlineStr"/>
       <c r="AR169" s="23" t="inlineStr"/>
       <c r="AS169" s="23" t="n"/>
-      <c r="AT169" s="66" t="inlineStr"/>
+      <c r="AT169" s="67" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="67" t="inlineStr">
+      <c r="A170" s="68" t="inlineStr">
         <is>
           <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
         </is>
@@ -21071,7 +21096,7 @@
       <c r="R170" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S170" s="70" t="inlineStr">
+      <c r="S170" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21114,10 +21139,10 @@
       <c r="AQ170" s="65" t="inlineStr"/>
       <c r="AR170" s="23" t="inlineStr"/>
       <c r="AS170" s="23" t="n"/>
-      <c r="AT170" s="66" t="inlineStr"/>
+      <c r="AT170" s="67" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="67" t="inlineStr">
+      <c r="A171" s="68" t="inlineStr">
         <is>
           <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
         </is>
@@ -21149,7 +21174,7 @@
         </is>
       </c>
       <c r="H171" s="24" t="inlineStr"/>
-      <c r="I171" s="68" t="inlineStr">
+      <c r="I171" s="69" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -21181,7 +21206,7 @@
       <c r="R171" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S171" s="70" t="inlineStr">
+      <c r="S171" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21224,7 +21249,7 @@
       <c r="AQ171" s="65" t="inlineStr"/>
       <c r="AR171" s="23" t="inlineStr"/>
       <c r="AS171" s="23" t="n"/>
-      <c r="AT171" s="66" t="inlineStr"/>
+      <c r="AT171" s="67" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="53" t="inlineStr">
@@ -21342,10 +21367,10 @@
       <c r="AQ172" s="65" t="inlineStr"/>
       <c r="AR172" s="23" t="inlineStr"/>
       <c r="AS172" s="23" t="n"/>
-      <c r="AT172" s="66" t="inlineStr"/>
+      <c r="AT172" s="67" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="67" t="inlineStr">
+      <c r="A173" s="68" t="inlineStr">
         <is>
           <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
         </is>
@@ -21417,7 +21442,7 @@
       <c r="R173" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S173" s="70" t="inlineStr">
+      <c r="S173" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21460,7 +21485,7 @@
       <c r="AQ173" s="65" t="inlineStr"/>
       <c r="AR173" s="23" t="inlineStr"/>
       <c r="AS173" s="23" t="n"/>
-      <c r="AT173" s="66" t="inlineStr"/>
+      <c r="AT173" s="67" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="53" t="inlineStr">
@@ -21578,10 +21603,10 @@
       <c r="AQ174" s="65" t="inlineStr"/>
       <c r="AR174" s="23" t="inlineStr"/>
       <c r="AS174" s="23" t="n"/>
-      <c r="AT174" s="66" t="inlineStr"/>
+      <c r="AT174" s="67" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="67" t="inlineStr">
+      <c r="A175" s="68" t="inlineStr">
         <is>
           <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
         </is>
@@ -21653,7 +21678,7 @@
       <c r="R175" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S175" s="70" t="inlineStr">
+      <c r="S175" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21696,7 +21721,7 @@
       <c r="AQ175" s="65" t="inlineStr"/>
       <c r="AR175" s="23" t="inlineStr"/>
       <c r="AS175" s="23" t="n"/>
-      <c r="AT175" s="66" t="inlineStr"/>
+      <c r="AT175" s="67" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="53" t="inlineStr">
@@ -21814,10 +21839,10 @@
       <c r="AQ176" s="65" t="inlineStr"/>
       <c r="AR176" s="23" t="inlineStr"/>
       <c r="AS176" s="23" t="n"/>
-      <c r="AT176" s="66" t="inlineStr"/>
+      <c r="AT176" s="67" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="67" t="inlineStr">
+      <c r="A177" s="68" t="inlineStr">
         <is>
           <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
         </is>
@@ -21889,7 +21914,7 @@
       <c r="R177" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S177" s="70" t="inlineStr">
+      <c r="S177" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -21932,7 +21957,7 @@
       <c r="AQ177" s="65" t="inlineStr"/>
       <c r="AR177" s="23" t="inlineStr"/>
       <c r="AS177" s="23" t="n"/>
-      <c r="AT177" s="66" t="inlineStr"/>
+      <c r="AT177" s="67" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="53" t="inlineStr">
@@ -22050,10 +22075,10 @@
       <c r="AQ178" s="65" t="inlineStr"/>
       <c r="AR178" s="23" t="inlineStr"/>
       <c r="AS178" s="23" t="n"/>
-      <c r="AT178" s="66" t="inlineStr"/>
+      <c r="AT178" s="67" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="67" t="inlineStr">
+      <c r="A179" s="68" t="inlineStr">
         <is>
           <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
         </is>
@@ -22125,7 +22150,7 @@
       <c r="R179" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S179" s="70" t="inlineStr">
+      <c r="S179" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -22168,10 +22193,10 @@
       <c r="AQ179" s="65" t="inlineStr"/>
       <c r="AR179" s="23" t="inlineStr"/>
       <c r="AS179" s="23" t="n"/>
-      <c r="AT179" s="66" t="inlineStr"/>
+      <c r="AT179" s="67" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="67" t="inlineStr">
+      <c r="A180" s="68" t="inlineStr">
         <is>
           <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
         </is>
@@ -22286,10 +22311,10 @@
         </is>
       </c>
       <c r="AS180" s="23" t="n"/>
-      <c r="AT180" s="66" t="inlineStr"/>
+      <c r="AT180" s="67" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="67" t="inlineStr">
+      <c r="A181" s="68" t="inlineStr">
         <is>
           <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
         </is>
@@ -22325,7 +22350,7 @@
         </is>
       </c>
       <c r="H181" s="24" t="inlineStr"/>
-      <c r="I181" s="68" t="inlineStr">
+      <c r="I181" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -22357,7 +22382,7 @@
       <c r="R181" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S181" s="70" t="inlineStr">
+      <c r="S181" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -22400,10 +22425,10 @@
       <c r="AQ181" s="65" t="inlineStr"/>
       <c r="AR181" s="23" t="inlineStr"/>
       <c r="AS181" s="23" t="n"/>
-      <c r="AT181" s="66" t="inlineStr"/>
+      <c r="AT181" s="67" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="67" t="inlineStr">
+      <c r="A182" s="68" t="inlineStr">
         <is>
           <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
         </is>
@@ -22518,10 +22543,10 @@
         </is>
       </c>
       <c r="AS182" s="23" t="n"/>
-      <c r="AT182" s="66" t="inlineStr"/>
+      <c r="AT182" s="67" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="67" t="inlineStr">
+      <c r="A183" s="68" t="inlineStr">
         <is>
           <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
         </is>
@@ -22557,7 +22582,7 @@
         </is>
       </c>
       <c r="H183" s="24" t="inlineStr"/>
-      <c r="I183" s="68" t="inlineStr">
+      <c r="I183" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -22589,7 +22614,7 @@
       <c r="R183" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S183" s="70" t="inlineStr">
+      <c r="S183" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -22632,10 +22657,10 @@
       <c r="AQ183" s="65" t="inlineStr"/>
       <c r="AR183" s="23" t="inlineStr"/>
       <c r="AS183" s="23" t="n"/>
-      <c r="AT183" s="66" t="inlineStr"/>
+      <c r="AT183" s="67" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="67" t="inlineStr">
+      <c r="A184" s="68" t="inlineStr">
         <is>
           <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
         </is>
@@ -22667,7 +22692,7 @@
         </is>
       </c>
       <c r="H184" s="24" t="inlineStr"/>
-      <c r="I184" s="68" t="inlineStr">
+      <c r="I184" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -22750,10 +22775,10 @@
         </is>
       </c>
       <c r="AS184" s="23" t="n"/>
-      <c r="AT184" s="66" t="inlineStr"/>
+      <c r="AT184" s="67" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="67" t="inlineStr">
+      <c r="A185" s="68" t="inlineStr">
         <is>
           <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
         </is>
@@ -22789,7 +22814,7 @@
         </is>
       </c>
       <c r="H185" s="24" t="inlineStr"/>
-      <c r="I185" s="68" t="inlineStr">
+      <c r="I185" s="69" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -22821,7 +22846,7 @@
       <c r="R185" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S185" s="70" t="inlineStr">
+      <c r="S185" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -22864,7 +22889,7 @@
       <c r="AQ185" s="65" t="inlineStr"/>
       <c r="AR185" s="23" t="inlineStr"/>
       <c r="AS185" s="23" t="n"/>
-      <c r="AT185" s="66" t="inlineStr"/>
+      <c r="AT185" s="67" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="53" t="inlineStr">
@@ -22990,7 +23015,7 @@
         </is>
       </c>
       <c r="AS186" s="23" t="n"/>
-      <c r="AT186" s="66" t="inlineStr"/>
+      <c r="AT186" s="67" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="53" t="inlineStr">
@@ -23116,7 +23141,7 @@
         </is>
       </c>
       <c r="AS187" s="23" t="n"/>
-      <c r="AT187" s="66" t="inlineStr"/>
+      <c r="AT187" s="67" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="53" t="inlineStr">
@@ -23242,7 +23267,7 @@
         </is>
       </c>
       <c r="AS188" s="23" t="n"/>
-      <c r="AT188" s="66" t="inlineStr"/>
+      <c r="AT188" s="67" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="53" t="inlineStr">
@@ -23368,7 +23393,7 @@
         </is>
       </c>
       <c r="AS189" s="23" t="n"/>
-      <c r="AT189" s="66" t="inlineStr"/>
+      <c r="AT189" s="67" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="53" t="inlineStr">
@@ -23494,7 +23519,7 @@
         </is>
       </c>
       <c r="AS190" s="23" t="n"/>
-      <c r="AT190" s="66" t="inlineStr"/>
+      <c r="AT190" s="67" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="53" t="inlineStr">
@@ -23620,10 +23645,10 @@
         </is>
       </c>
       <c r="AS191" s="23" t="n"/>
-      <c r="AT191" s="66" t="inlineStr"/>
+      <c r="AT191" s="67" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="67" t="inlineStr">
+      <c r="A192" s="68" t="inlineStr">
         <is>
           <t>PS5-60-76 - Engine G Cooling system</t>
         </is>
@@ -23738,10 +23763,10 @@
         </is>
       </c>
       <c r="AS192" s="23" t="n"/>
-      <c r="AT192" s="66" t="inlineStr"/>
+      <c r="AT192" s="67" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="67" t="inlineStr">
+      <c r="A193" s="68" t="inlineStr">
         <is>
           <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
         </is>
@@ -23866,10 +23891,10 @@
         </is>
       </c>
       <c r="AS193" s="23" t="n"/>
-      <c r="AT193" s="66" t="inlineStr"/>
+      <c r="AT193" s="67" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="67" t="inlineStr">
+      <c r="A194" s="68" t="inlineStr">
         <is>
           <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
         </is>
@@ -23901,7 +23926,7 @@
         </is>
       </c>
       <c r="H194" s="24" t="inlineStr"/>
-      <c r="I194" s="68" t="inlineStr">
+      <c r="I194" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -23984,10 +24009,10 @@
         </is>
       </c>
       <c r="AS194" s="23" t="n"/>
-      <c r="AT194" s="66" t="inlineStr"/>
+      <c r="AT194" s="67" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="67" t="inlineStr">
+      <c r="A195" s="68" t="inlineStr">
         <is>
           <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
         </is>
@@ -24019,7 +24044,7 @@
         </is>
       </c>
       <c r="H195" s="24" t="inlineStr"/>
-      <c r="I195" s="68" t="inlineStr">
+      <c r="I195" s="69" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -24102,10 +24127,10 @@
         </is>
       </c>
       <c r="AS195" s="23" t="n"/>
-      <c r="AT195" s="66" t="inlineStr"/>
+      <c r="AT195" s="67" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="67" t="inlineStr">
+      <c r="A196" s="68" t="inlineStr">
         <is>
           <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
         </is>
@@ -24141,7 +24166,7 @@
         </is>
       </c>
       <c r="H196" s="24" t="inlineStr"/>
-      <c r="I196" s="69" t="inlineStr">
+      <c r="I196" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -24224,7 +24249,7 @@
         </is>
       </c>
       <c r="AS196" s="23" t="n"/>
-      <c r="AT196" s="66" t="inlineStr"/>
+      <c r="AT196" s="67" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="53" t="inlineStr">
@@ -24350,10 +24375,10 @@
         </is>
       </c>
       <c r="AS197" s="23" t="n"/>
-      <c r="AT197" s="66" t="inlineStr"/>
+      <c r="AT197" s="67" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="67" t="inlineStr">
+      <c r="A198" s="68" t="inlineStr">
         <is>
           <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
         </is>
@@ -24389,7 +24414,7 @@
         </is>
       </c>
       <c r="H198" s="24" t="inlineStr"/>
-      <c r="I198" s="68" t="inlineStr">
+      <c r="I198" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -24472,7 +24497,7 @@
         </is>
       </c>
       <c r="AS198" s="23" t="n"/>
-      <c r="AT198" s="66" t="inlineStr"/>
+      <c r="AT198" s="67" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="53" t="inlineStr">
@@ -24598,10 +24623,10 @@
         </is>
       </c>
       <c r="AS199" s="23" t="n"/>
-      <c r="AT199" s="66" t="inlineStr"/>
+      <c r="AT199" s="67" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="67" t="inlineStr">
+      <c r="A200" s="68" t="inlineStr">
         <is>
           <t>PS5-61-08 - Electrical Control System</t>
         </is>
@@ -24633,7 +24658,7 @@
         </is>
       </c>
       <c r="H200" s="24" t="inlineStr"/>
-      <c r="I200" s="69" t="inlineStr">
+      <c r="I200" s="70" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -24716,10 +24741,10 @@
         </is>
       </c>
       <c r="AS200" s="23" t="n"/>
-      <c r="AT200" s="66" t="inlineStr"/>
+      <c r="AT200" s="67" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="67" t="inlineStr">
+      <c r="A201" s="68" t="inlineStr">
         <is>
           <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
         </is>
@@ -24755,7 +24780,7 @@
         </is>
       </c>
       <c r="H201" s="24" t="inlineStr"/>
-      <c r="I201" s="69" t="inlineStr">
+      <c r="I201" s="70" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -24838,7 +24863,7 @@
         </is>
       </c>
       <c r="AS201" s="23" t="n"/>
-      <c r="AT201" s="66" t="inlineStr"/>
+      <c r="AT201" s="67" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="53" t="inlineStr">
@@ -24964,7 +24989,7 @@
         </is>
       </c>
       <c r="AS202" s="23" t="n"/>
-      <c r="AT202" s="66" t="inlineStr"/>
+      <c r="AT202" s="67" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="53" t="inlineStr">
@@ -25090,10 +25115,10 @@
         </is>
       </c>
       <c r="AS203" s="23" t="n"/>
-      <c r="AT203" s="66" t="inlineStr"/>
+      <c r="AT203" s="67" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="67" t="inlineStr">
+      <c r="A204" s="68" t="inlineStr">
         <is>
           <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
         </is>
@@ -25109,7 +25134,7 @@
         </is>
       </c>
       <c r="H204" s="24" t="inlineStr"/>
-      <c r="I204" s="69" t="inlineStr">
+      <c r="I204" s="70" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -25174,10 +25199,10 @@
       <c r="AQ204" s="65" t="inlineStr"/>
       <c r="AR204" s="23" t="inlineStr"/>
       <c r="AS204" s="23" t="n"/>
-      <c r="AT204" s="66" t="inlineStr"/>
+      <c r="AT204" s="67" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="67" t="inlineStr">
+      <c r="A205" s="68" t="inlineStr">
         <is>
           <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
         </is>
@@ -25209,7 +25234,7 @@
         </is>
       </c>
       <c r="H205" s="24" t="inlineStr"/>
-      <c r="I205" s="69" t="inlineStr">
+      <c r="I205" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -25292,10 +25317,10 @@
         </is>
       </c>
       <c r="AS205" s="23" t="n"/>
-      <c r="AT205" s="66" t="inlineStr"/>
+      <c r="AT205" s="67" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="67" t="inlineStr">
+      <c r="A206" s="68" t="inlineStr">
         <is>
           <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
         </is>
@@ -25327,7 +25352,7 @@
         </is>
       </c>
       <c r="H206" s="24" t="inlineStr"/>
-      <c r="I206" s="69" t="inlineStr">
+      <c r="I206" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -25410,10 +25435,10 @@
         </is>
       </c>
       <c r="AS206" s="23" t="n"/>
-      <c r="AT206" s="66" t="inlineStr"/>
+      <c r="AT206" s="67" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="67" t="inlineStr">
+      <c r="A207" s="68" t="inlineStr">
         <is>
           <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
         </is>
@@ -25445,7 +25470,7 @@
         </is>
       </c>
       <c r="H207" s="24" t="inlineStr"/>
-      <c r="I207" s="69" t="inlineStr">
+      <c r="I207" s="70" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -25528,10 +25553,10 @@
         </is>
       </c>
       <c r="AS207" s="23" t="n"/>
-      <c r="AT207" s="66" t="inlineStr"/>
+      <c r="AT207" s="67" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="67" t="inlineStr">
+      <c r="A208" s="68" t="inlineStr">
         <is>
           <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
         </is>
@@ -25563,7 +25588,7 @@
         </is>
       </c>
       <c r="H208" s="24" t="inlineStr"/>
-      <c r="I208" s="69" t="inlineStr">
+      <c r="I208" s="70" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -25646,10 +25671,10 @@
         </is>
       </c>
       <c r="AS208" s="23" t="n"/>
-      <c r="AT208" s="66" t="inlineStr"/>
+      <c r="AT208" s="67" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="67" t="inlineStr">
+      <c r="A209" s="68" t="inlineStr">
         <is>
           <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
         </is>
@@ -25681,7 +25706,7 @@
         </is>
       </c>
       <c r="H209" s="24" t="inlineStr"/>
-      <c r="I209" s="68" t="inlineStr">
+      <c r="I209" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -25764,7 +25789,7 @@
         </is>
       </c>
       <c r="AS209" s="23" t="n"/>
-      <c r="AT209" s="66" t="inlineStr"/>
+      <c r="AT209" s="67" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="53" t="inlineStr">
@@ -25890,10 +25915,10 @@
         </is>
       </c>
       <c r="AS210" s="23" t="n"/>
-      <c r="AT210" s="66" t="inlineStr"/>
+      <c r="AT210" s="67" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="67" t="inlineStr">
+      <c r="A211" s="68" t="inlineStr">
         <is>
           <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
         </is>
@@ -25925,7 +25950,7 @@
         </is>
       </c>
       <c r="H211" s="24" t="inlineStr"/>
-      <c r="I211" s="69" t="inlineStr">
+      <c r="I211" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -26008,10 +26033,10 @@
         </is>
       </c>
       <c r="AS211" s="23" t="n"/>
-      <c r="AT211" s="66" t="inlineStr"/>
+      <c r="AT211" s="67" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="67" t="inlineStr">
+      <c r="A212" s="68" t="inlineStr">
         <is>
           <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
         </is>
@@ -26051,7 +26076,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I212" s="69" t="inlineStr">
+      <c r="I212" s="70" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -26134,10 +26159,10 @@
         </is>
       </c>
       <c r="AS212" s="23" t="n"/>
-      <c r="AT212" s="66" t="inlineStr"/>
+      <c r="AT212" s="67" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="67" t="inlineStr">
+      <c r="A213" s="68" t="inlineStr">
         <is>
           <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
         </is>
@@ -26173,7 +26198,7 @@
         </is>
       </c>
       <c r="H213" s="24" t="inlineStr"/>
-      <c r="I213" s="69" t="inlineStr">
+      <c r="I213" s="70" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -26256,10 +26281,10 @@
         </is>
       </c>
       <c r="AS213" s="23" t="n"/>
-      <c r="AT213" s="66" t="inlineStr"/>
+      <c r="AT213" s="67" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="67" t="inlineStr">
+      <c r="A214" s="68" t="inlineStr">
         <is>
           <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
         </is>
@@ -26295,7 +26320,7 @@
         </is>
       </c>
       <c r="H214" s="24" t="inlineStr"/>
-      <c r="I214" s="69" t="inlineStr">
+      <c r="I214" s="70" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -26378,10 +26403,10 @@
         </is>
       </c>
       <c r="AS214" s="23" t="n"/>
-      <c r="AT214" s="66" t="inlineStr"/>
+      <c r="AT214" s="67" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="67" t="inlineStr">
+      <c r="A215" s="68" t="inlineStr">
         <is>
           <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
         </is>
@@ -26417,7 +26442,7 @@
         </is>
       </c>
       <c r="H215" s="24" t="inlineStr"/>
-      <c r="I215" s="69" t="inlineStr">
+      <c r="I215" s="70" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -26500,10 +26525,10 @@
         </is>
       </c>
       <c r="AS215" s="23" t="n"/>
-      <c r="AT215" s="66" t="inlineStr"/>
+      <c r="AT215" s="67" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="67" t="inlineStr">
+      <c r="A216" s="68" t="inlineStr">
         <is>
           <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
         </is>
@@ -26543,7 +26568,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I216" s="69" t="inlineStr">
+      <c r="I216" s="70" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -26626,10 +26651,10 @@
         </is>
       </c>
       <c r="AS216" s="23" t="n"/>
-      <c r="AT216" s="66" t="inlineStr"/>
+      <c r="AT216" s="67" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="67" t="inlineStr">
+      <c r="A217" s="68" t="inlineStr">
         <is>
           <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
         </is>
@@ -26665,7 +26690,7 @@
         </is>
       </c>
       <c r="H217" s="24" t="inlineStr"/>
-      <c r="I217" s="69" t="inlineStr">
+      <c r="I217" s="70" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -26748,10 +26773,10 @@
         </is>
       </c>
       <c r="AS217" s="23" t="n"/>
-      <c r="AT217" s="66" t="inlineStr"/>
+      <c r="AT217" s="67" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="67" t="inlineStr">
+      <c r="A218" s="68" t="inlineStr">
         <is>
           <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
         </is>
@@ -26832,10 +26857,10 @@
       <c r="AQ218" s="65" t="inlineStr"/>
       <c r="AR218" s="23" t="inlineStr"/>
       <c r="AS218" s="23" t="n"/>
-      <c r="AT218" s="66" t="inlineStr"/>
+      <c r="AT218" s="67" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="67" t="inlineStr">
+      <c r="A219" s="68" t="inlineStr">
         <is>
           <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
         </is>
@@ -26916,10 +26941,10 @@
       <c r="AQ219" s="65" t="inlineStr"/>
       <c r="AR219" s="23" t="inlineStr"/>
       <c r="AS219" s="23" t="n"/>
-      <c r="AT219" s="66" t="inlineStr"/>
+      <c r="AT219" s="67" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="67" t="inlineStr">
+      <c r="A220" s="68" t="inlineStr">
         <is>
           <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
         </is>
@@ -26951,7 +26976,7 @@
         </is>
       </c>
       <c r="H220" s="24" t="inlineStr"/>
-      <c r="I220" s="69" t="inlineStr">
+      <c r="I220" s="70" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -27034,10 +27059,10 @@
         </is>
       </c>
       <c r="AS220" s="23" t="n"/>
-      <c r="AT220" s="66" t="inlineStr"/>
+      <c r="AT220" s="67" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="67" t="inlineStr">
+      <c r="A221" s="68" t="inlineStr">
         <is>
           <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
         </is>
@@ -27069,7 +27094,7 @@
         </is>
       </c>
       <c r="H221" s="24" t="inlineStr"/>
-      <c r="I221" s="69" t="inlineStr">
+      <c r="I221" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -27152,10 +27177,10 @@
         </is>
       </c>
       <c r="AS221" s="23" t="n"/>
-      <c r="AT221" s="66" t="inlineStr"/>
+      <c r="AT221" s="67" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="67" t="inlineStr">
+      <c r="A222" s="68" t="inlineStr">
         <is>
           <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
         </is>
@@ -27187,7 +27212,7 @@
         </is>
       </c>
       <c r="H222" s="24" t="inlineStr"/>
-      <c r="I222" s="69" t="inlineStr">
+      <c r="I222" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -27270,10 +27295,10 @@
         </is>
       </c>
       <c r="AS222" s="23" t="n"/>
-      <c r="AT222" s="66" t="inlineStr"/>
+      <c r="AT222" s="67" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="67" t="inlineStr">
+      <c r="A223" s="68" t="inlineStr">
         <is>
           <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
         </is>
@@ -27305,7 +27330,7 @@
         </is>
       </c>
       <c r="H223" s="24" t="inlineStr"/>
-      <c r="I223" s="69" t="inlineStr">
+      <c r="I223" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -27388,10 +27413,10 @@
         </is>
       </c>
       <c r="AS223" s="23" t="n"/>
-      <c r="AT223" s="66" t="inlineStr"/>
+      <c r="AT223" s="67" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="67" t="inlineStr">
+      <c r="A224" s="68" t="inlineStr">
         <is>
           <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
         </is>
@@ -27423,7 +27448,7 @@
         </is>
       </c>
       <c r="H224" s="24" t="inlineStr"/>
-      <c r="I224" s="69" t="inlineStr">
+      <c r="I224" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -27506,10 +27531,10 @@
         </is>
       </c>
       <c r="AS224" s="23" t="n"/>
-      <c r="AT224" s="66" t="inlineStr"/>
+      <c r="AT224" s="67" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="67" t="inlineStr">
+      <c r="A225" s="68" t="inlineStr">
         <is>
           <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
         </is>
@@ -27541,7 +27566,7 @@
         </is>
       </c>
       <c r="H225" s="24" t="inlineStr"/>
-      <c r="I225" s="69" t="inlineStr">
+      <c r="I225" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -27624,10 +27649,10 @@
         </is>
       </c>
       <c r="AS225" s="23" t="n"/>
-      <c r="AT225" s="66" t="inlineStr"/>
+      <c r="AT225" s="67" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="67" t="inlineStr">
+      <c r="A226" s="68" t="inlineStr">
         <is>
           <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
         </is>
@@ -27659,7 +27684,7 @@
         </is>
       </c>
       <c r="H226" s="24" t="inlineStr"/>
-      <c r="I226" s="69" t="inlineStr">
+      <c r="I226" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -27742,10 +27767,10 @@
         </is>
       </c>
       <c r="AS226" s="23" t="n"/>
-      <c r="AT226" s="66" t="inlineStr"/>
+      <c r="AT226" s="67" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="67" t="inlineStr">
+      <c r="A227" s="68" t="inlineStr">
         <is>
           <t>PS5-63-01 - Electrical Earthing</t>
         </is>
@@ -27785,7 +27810,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I227" s="69" t="inlineStr">
+      <c r="I227" s="70" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -27859,7 +27884,7 @@
       <c r="AP227" s="65" t="inlineStr"/>
       <c r="AQ227" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18 ITRs for lightning, 22 ITRs for grounding cannot be closed due to material issues.</t>
         </is>
       </c>
       <c r="AR227" s="23" t="inlineStr">
@@ -27868,10 +27893,10 @@
         </is>
       </c>
       <c r="AS227" s="23" t="n"/>
-      <c r="AT227" s="66" t="inlineStr"/>
+      <c r="AT227" s="67" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="67" t="inlineStr">
+      <c r="A228" s="68" t="inlineStr">
         <is>
           <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
         </is>
@@ -27903,7 +27928,7 @@
         </is>
       </c>
       <c r="H228" s="24" t="inlineStr"/>
-      <c r="I228" s="69" t="inlineStr">
+      <c r="I228" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -27986,10 +28011,10 @@
         </is>
       </c>
       <c r="AS228" s="23" t="n"/>
-      <c r="AT228" s="66" t="inlineStr"/>
+      <c r="AT228" s="67" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="67" t="inlineStr">
+      <c r="A229" s="68" t="inlineStr">
         <is>
           <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
         </is>
@@ -28029,7 +28054,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I229" s="68" t="inlineStr">
+      <c r="I229" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -28112,7 +28137,7 @@
         </is>
       </c>
       <c r="AS229" s="23" t="n"/>
-      <c r="AT229" s="66" t="inlineStr"/>
+      <c r="AT229" s="67" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="53" t="inlineStr">
@@ -28196,10 +28221,10 @@
       <c r="AQ230" s="65" t="inlineStr"/>
       <c r="AR230" s="23" t="inlineStr"/>
       <c r="AS230" s="23" t="n"/>
-      <c r="AT230" s="66" t="inlineStr"/>
+      <c r="AT230" s="67" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="67" t="inlineStr">
+      <c r="A231" s="68" t="inlineStr">
         <is>
           <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
         </is>
@@ -28231,7 +28256,7 @@
         </is>
       </c>
       <c r="H231" s="24" t="inlineStr"/>
-      <c r="I231" s="69" t="inlineStr">
+      <c r="I231" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -28314,10 +28339,10 @@
         </is>
       </c>
       <c r="AS231" s="23" t="n"/>
-      <c r="AT231" s="66" t="inlineStr"/>
+      <c r="AT231" s="67" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="67" t="inlineStr">
+      <c r="A232" s="68" t="inlineStr">
         <is>
           <t>PS5-63-06 - Electrical Earthing - Guard House</t>
         </is>
@@ -28349,7 +28374,7 @@
         </is>
       </c>
       <c r="H232" s="24" t="inlineStr"/>
-      <c r="I232" s="69" t="inlineStr">
+      <c r="I232" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -28432,10 +28457,10 @@
         </is>
       </c>
       <c r="AS232" s="23" t="n"/>
-      <c r="AT232" s="66" t="inlineStr"/>
+      <c r="AT232" s="67" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="67" t="inlineStr">
+      <c r="A233" s="68" t="inlineStr">
         <is>
           <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
         </is>
@@ -28467,7 +28492,7 @@
         </is>
       </c>
       <c r="H233" s="24" t="inlineStr"/>
-      <c r="I233" s="69" t="inlineStr">
+      <c r="I233" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -28550,10 +28575,10 @@
         </is>
       </c>
       <c r="AS233" s="23" t="n"/>
-      <c r="AT233" s="66" t="inlineStr"/>
+      <c r="AT233" s="67" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="67" t="inlineStr">
+      <c r="A234" s="68" t="inlineStr">
         <is>
           <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
         </is>
@@ -28585,7 +28610,7 @@
         </is>
       </c>
       <c r="H234" s="24" t="inlineStr"/>
-      <c r="I234" s="69" t="inlineStr">
+      <c r="I234" s="70" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -28656,7 +28681,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP234" s="65" t="inlineStr"/>
+      <c r="AP234" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ234" s="65" t="inlineStr">
         <is>
           <t>PS5-71-TW-0007, PS5-71-TW-0003, PS5-71-TW-0004, PS5-71-TW-0006 not arrived</t>
@@ -28668,10 +28697,10 @@
         </is>
       </c>
       <c r="AS234" s="23" t="n"/>
-      <c r="AT234" s="66" t="inlineStr"/>
+      <c r="AT234" s="67" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="67" t="inlineStr">
+      <c r="A235" s="68" t="inlineStr">
         <is>
           <t>PS5-71-02 - CFO Allocation Metering Package</t>
         </is>
@@ -28703,7 +28732,7 @@
         </is>
       </c>
       <c r="H235" s="24" t="inlineStr"/>
-      <c r="I235" s="68" t="inlineStr">
+      <c r="I235" s="69" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -28786,10 +28815,10 @@
         </is>
       </c>
       <c r="AS235" s="23" t="n"/>
-      <c r="AT235" s="66" t="inlineStr"/>
+      <c r="AT235" s="67" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="67" t="inlineStr">
+      <c r="A236" s="68" t="inlineStr">
         <is>
           <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
         </is>
@@ -28805,7 +28834,7 @@
         </is>
       </c>
       <c r="H236" s="24" t="inlineStr"/>
-      <c r="I236" s="69" t="inlineStr">
+      <c r="I236" s="70" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
@@ -28870,10 +28899,10 @@
       <c r="AQ236" s="65" t="inlineStr"/>
       <c r="AR236" s="23" t="inlineStr"/>
       <c r="AS236" s="23" t="n"/>
-      <c r="AT236" s="66" t="inlineStr"/>
+      <c r="AT236" s="67" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="67" t="inlineStr">
+      <c r="A237" s="68" t="inlineStr">
         <is>
           <t>PS5-71-04 - CFO Storage Tank</t>
         </is>
@@ -28905,7 +28934,7 @@
         </is>
       </c>
       <c r="H237" s="24" t="inlineStr"/>
-      <c r="I237" s="68" t="inlineStr">
+      <c r="I237" s="69" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
@@ -28990,10 +29019,10 @@
         </is>
       </c>
       <c r="AS237" s="23" t="n"/>
-      <c r="AT237" s="66" t="inlineStr"/>
+      <c r="AT237" s="67" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="67" t="inlineStr">
+      <c r="A238" s="68" t="inlineStr">
         <is>
           <t>PS5-71-05 - CFO Transfer Pump A/B</t>
         </is>
@@ -29025,7 +29054,7 @@
         </is>
       </c>
       <c r="H238" s="24" t="inlineStr"/>
-      <c r="I238" s="68" t="inlineStr">
+      <c r="I238" s="69" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -29108,10 +29137,10 @@
         </is>
       </c>
       <c r="AS238" s="23" t="n"/>
-      <c r="AT238" s="66" t="inlineStr"/>
+      <c r="AT238" s="67" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="67" t="inlineStr">
+      <c r="A239" s="68" t="inlineStr">
         <is>
           <t>PS5-71-06 - Crude Fuel Separation Module</t>
         </is>
@@ -29147,7 +29176,7 @@
         </is>
       </c>
       <c r="H239" s="24" t="inlineStr"/>
-      <c r="I239" s="68" t="inlineStr">
+      <c r="I239" s="69" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
@@ -29250,10 +29279,10 @@
         </is>
       </c>
       <c r="AS239" s="23" t="n"/>
-      <c r="AT239" s="66" t="inlineStr"/>
+      <c r="AT239" s="67" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="67" t="inlineStr">
+      <c r="A240" s="68" t="inlineStr">
         <is>
           <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
         </is>
@@ -29289,7 +29318,7 @@
         </is>
       </c>
       <c r="H240" s="24" t="inlineStr"/>
-      <c r="I240" s="68" t="inlineStr">
+      <c r="I240" s="69" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -29321,7 +29350,7 @@
       <c r="R240" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="S240" s="70" t="inlineStr">
+      <c r="S240" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -29374,10 +29403,10 @@
         </is>
       </c>
       <c r="AS240" s="23" t="n"/>
-      <c r="AT240" s="66" t="inlineStr"/>
+      <c r="AT240" s="67" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="67" t="inlineStr">
+      <c r="A241" s="68" t="inlineStr">
         <is>
           <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
         </is>
@@ -29502,10 +29531,10 @@
         </is>
       </c>
       <c r="AS241" s="23" t="n"/>
-      <c r="AT241" s="66" t="inlineStr"/>
+      <c r="AT241" s="67" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="67" t="inlineStr">
+      <c r="A242" s="68" t="inlineStr">
         <is>
           <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
         </is>
@@ -29577,7 +29606,7 @@
       <c r="R242" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S242" s="70" t="inlineStr">
+      <c r="S242" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -29620,10 +29649,10 @@
       <c r="AQ242" s="65" t="inlineStr"/>
       <c r="AR242" s="23" t="inlineStr"/>
       <c r="AS242" s="23" t="n"/>
-      <c r="AT242" s="66" t="inlineStr"/>
+      <c r="AT242" s="67" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="67" t="inlineStr">
+      <c r="A243" s="68" t="inlineStr">
         <is>
           <t>PS5-71-12 - CFO Service Tank</t>
         </is>
@@ -29655,7 +29684,7 @@
         </is>
       </c>
       <c r="H243" s="24" t="inlineStr"/>
-      <c r="I243" s="68" t="inlineStr">
+      <c r="I243" s="69" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -29738,10 +29767,10 @@
         </is>
       </c>
       <c r="AS243" s="23" t="n"/>
-      <c r="AT243" s="66" t="inlineStr"/>
+      <c r="AT243" s="67" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="67" t="inlineStr">
+      <c r="A244" s="68" t="inlineStr">
         <is>
           <t>PS5-71-13 - CFO Service Pump A/B</t>
         </is>
@@ -29773,7 +29802,7 @@
         </is>
       </c>
       <c r="H244" s="24" t="inlineStr"/>
-      <c r="I244" s="68" t="inlineStr">
+      <c r="I244" s="69" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -29856,10 +29885,10 @@
         </is>
       </c>
       <c r="AS244" s="23" t="n"/>
-      <c r="AT244" s="66" t="inlineStr"/>
+      <c r="AT244" s="67" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="67" t="inlineStr">
+      <c r="A245" s="68" t="inlineStr">
         <is>
           <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
@@ -29891,7 +29920,7 @@
         </is>
       </c>
       <c r="H245" s="24" t="inlineStr"/>
-      <c r="I245" s="68" t="inlineStr">
+      <c r="I245" s="69" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -29974,10 +30003,10 @@
         </is>
       </c>
       <c r="AS245" s="23" t="n"/>
-      <c r="AT245" s="66" t="inlineStr"/>
+      <c r="AT245" s="67" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="67" t="inlineStr">
+      <c r="A246" s="68" t="inlineStr">
         <is>
           <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
         </is>
@@ -30009,7 +30038,7 @@
         </is>
       </c>
       <c r="H246" s="24" t="inlineStr"/>
-      <c r="I246" s="68" t="inlineStr">
+      <c r="I246" s="69" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -30092,10 +30121,10 @@
         </is>
       </c>
       <c r="AS246" s="23" t="n"/>
-      <c r="AT246" s="66" t="inlineStr"/>
+      <c r="AT246" s="67" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="67" t="inlineStr">
+      <c r="A247" s="68" t="inlineStr">
         <is>
           <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
@@ -30131,7 +30160,7 @@
         </is>
       </c>
       <c r="H247" s="24" t="inlineStr"/>
-      <c r="I247" s="68" t="inlineStr">
+      <c r="I247" s="69" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -30214,10 +30243,10 @@
         </is>
       </c>
       <c r="AS247" s="23" t="n"/>
-      <c r="AT247" s="66" t="inlineStr"/>
+      <c r="AT247" s="67" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="67" t="inlineStr">
+      <c r="A248" s="68" t="inlineStr">
         <is>
           <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
         </is>
@@ -30340,10 +30369,10 @@
         </is>
       </c>
       <c r="AS248" s="23" t="n"/>
-      <c r="AT248" s="66" t="inlineStr"/>
+      <c r="AT248" s="67" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="67" t="inlineStr">
+      <c r="A249" s="68" t="inlineStr">
         <is>
           <t>PS5-71-18 - Diesel Separator Module</t>
         </is>
@@ -30383,7 +30412,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I249" s="68" t="inlineStr">
+      <c r="I249" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -30470,10 +30499,10 @@
         </is>
       </c>
       <c r="AS249" s="23" t="n"/>
-      <c r="AT249" s="66" t="inlineStr"/>
+      <c r="AT249" s="67" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="67" t="inlineStr">
+      <c r="A250" s="68" t="inlineStr">
         <is>
           <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
         </is>
@@ -30509,7 +30538,7 @@
         </is>
       </c>
       <c r="H250" s="24" t="inlineStr"/>
-      <c r="I250" s="68" t="inlineStr">
+      <c r="I250" s="69" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -30541,7 +30570,7 @@
       <c r="R250" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="S250" s="70" t="inlineStr">
+      <c r="S250" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -30594,10 +30623,10 @@
         </is>
       </c>
       <c r="AS250" s="23" t="n"/>
-      <c r="AT250" s="66" t="inlineStr"/>
+      <c r="AT250" s="67" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="67" t="inlineStr">
+      <c r="A251" s="68" t="inlineStr">
         <is>
           <t>PS5-71-20 - Diesel Fuel Day Tank</t>
         </is>
@@ -30637,7 +30666,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I251" s="68" t="inlineStr">
+      <c r="I251" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -30720,10 +30749,10 @@
         </is>
       </c>
       <c r="AS251" s="23" t="n"/>
-      <c r="AT251" s="66" t="inlineStr"/>
+      <c r="AT251" s="67" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="67" t="inlineStr">
+      <c r="A252" s="68" t="inlineStr">
         <is>
           <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
         </is>
@@ -30848,7 +30877,7 @@
         </is>
       </c>
       <c r="AS252" s="23" t="n"/>
-      <c r="AT252" s="66" t="inlineStr"/>
+      <c r="AT252" s="67" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="53" t="inlineStr">
@@ -30974,10 +31003,10 @@
         </is>
       </c>
       <c r="AS253" s="23" t="n"/>
-      <c r="AT253" s="66" t="inlineStr"/>
+      <c r="AT253" s="67" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="67" t="inlineStr">
+      <c r="A254" s="68" t="inlineStr">
         <is>
           <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
         </is>
@@ -31017,7 +31046,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I254" s="68" t="inlineStr">
+      <c r="I254" s="69" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -31049,7 +31078,7 @@
       <c r="R254" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="S254" s="70" t="inlineStr">
+      <c r="S254" s="71" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -31100,10 +31129,10 @@
         </is>
       </c>
       <c r="AS254" s="23" t="n"/>
-      <c r="AT254" s="66" t="inlineStr"/>
+      <c r="AT254" s="67" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="67" t="inlineStr">
+      <c r="A255" s="68" t="inlineStr">
         <is>
           <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
@@ -31143,7 +31172,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I255" s="68" t="inlineStr">
+      <c r="I255" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -31226,10 +31255,10 @@
         </is>
       </c>
       <c r="AS255" s="23" t="n"/>
-      <c r="AT255" s="66" t="inlineStr"/>
+      <c r="AT255" s="67" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="67" t="inlineStr">
+      <c r="A256" s="68" t="inlineStr">
         <is>
           <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
         </is>
@@ -31269,7 +31298,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I256" s="68" t="inlineStr">
+      <c r="I256" s="69" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -31352,7 +31381,7 @@
         </is>
       </c>
       <c r="AS256" s="23" t="n"/>
-      <c r="AT256" s="66" t="inlineStr"/>
+      <c r="AT256" s="67" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="53" t="inlineStr">
@@ -31478,10 +31507,10 @@
         </is>
       </c>
       <c r="AS257" s="23" t="n"/>
-      <c r="AT257" s="66" t="inlineStr"/>
+      <c r="AT257" s="67" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="67" t="inlineStr">
+      <c r="A258" s="68" t="inlineStr">
         <is>
           <t>PS5-74-04 - Nitrogen Distribution Header</t>
         </is>
@@ -31513,7 +31542,7 @@
         </is>
       </c>
       <c r="H258" s="24" t="inlineStr"/>
-      <c r="I258" s="68" t="inlineStr">
+      <c r="I258" s="69" t="inlineStr">
         <is>
           <t>81%</t>
         </is>
@@ -31596,10 +31625,10 @@
         </is>
       </c>
       <c r="AS258" s="23" t="n"/>
-      <c r="AT258" s="66" t="inlineStr"/>
+      <c r="AT258" s="67" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="67" t="inlineStr">
+      <c r="A259" s="68" t="inlineStr">
         <is>
           <t>PS5-75-01 - DRA Injection Package</t>
         </is>
@@ -31631,7 +31660,7 @@
         </is>
       </c>
       <c r="H259" s="24" t="inlineStr"/>
-      <c r="I259" s="69" t="inlineStr">
+      <c r="I259" s="70" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
@@ -31714,10 +31743,10 @@
         </is>
       </c>
       <c r="AS259" s="23" t="n"/>
-      <c r="AT259" s="66" t="inlineStr"/>
+      <c r="AT259" s="67" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="67" t="inlineStr">
+      <c r="A260" s="68" t="inlineStr">
         <is>
           <t>PS5-75-02 - Biocide Injection Package</t>
         </is>
@@ -31749,7 +31778,7 @@
         </is>
       </c>
       <c r="H260" s="24" t="inlineStr"/>
-      <c r="I260" s="68" t="inlineStr">
+      <c r="I260" s="69" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -31832,10 +31861,10 @@
         </is>
       </c>
       <c r="AS260" s="23" t="n"/>
-      <c r="AT260" s="66" t="inlineStr"/>
+      <c r="AT260" s="67" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="67" t="inlineStr">
+      <c r="A261" s="68" t="inlineStr">
         <is>
           <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
         </is>
@@ -31867,7 +31896,7 @@
         </is>
       </c>
       <c r="H261" s="24" t="inlineStr"/>
-      <c r="I261" s="68" t="inlineStr">
+      <c r="I261" s="69" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
@@ -31950,10 +31979,10 @@
         </is>
       </c>
       <c r="AS261" s="23" t="n"/>
-      <c r="AT261" s="66" t="inlineStr"/>
+      <c r="AT261" s="67" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="73" t="inlineStr">
+      <c r="A262" s="74" t="inlineStr">
         <is>
           <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
@@ -31979,7 +32008,7 @@
         </is>
       </c>
       <c r="F262" s="23" t="inlineStr"/>
-      <c r="G262" s="68" t="inlineStr">
+      <c r="G262" s="69" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -31989,7 +32018,7 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="I262" s="68" t="inlineStr">
+      <c r="I262" s="69" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -32072,10 +32101,10 @@
         </is>
       </c>
       <c r="AS262" s="23" t="n"/>
-      <c r="AT262" s="66" t="inlineStr"/>
+      <c r="AT262" s="67" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="67" t="inlineStr">
+      <c r="A263" s="68" t="inlineStr">
         <is>
           <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
         </is>
@@ -32107,7 +32136,7 @@
         </is>
       </c>
       <c r="H263" s="24" t="inlineStr"/>
-      <c r="I263" s="69" t="inlineStr">
+      <c r="I263" s="70" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -32190,10 +32219,10 @@
         </is>
       </c>
       <c r="AS263" s="23" t="n"/>
-      <c r="AT263" s="66" t="inlineStr"/>
+      <c r="AT263" s="67" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="67" t="inlineStr">
+      <c r="A264" s="68" t="inlineStr">
         <is>
           <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
         </is>
@@ -32225,7 +32254,7 @@
         </is>
       </c>
       <c r="H264" s="24" t="inlineStr"/>
-      <c r="I264" s="69" t="inlineStr">
+      <c r="I264" s="70" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -32308,10 +32337,10 @@
         </is>
       </c>
       <c r="AS264" s="23" t="n"/>
-      <c r="AT264" s="66" t="inlineStr"/>
+      <c r="AT264" s="67" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" s="67" t="inlineStr">
+      <c r="A265" s="68" t="inlineStr">
         <is>
           <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
         </is>
@@ -32343,7 +32372,7 @@
         </is>
       </c>
       <c r="H265" s="24" t="inlineStr"/>
-      <c r="I265" s="69" t="inlineStr">
+      <c r="I265" s="70" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -32426,10 +32455,10 @@
         </is>
       </c>
       <c r="AS265" s="23" t="n"/>
-      <c r="AT265" s="66" t="inlineStr"/>
+      <c r="AT265" s="67" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" s="67" t="inlineStr">
+      <c r="A266" s="68" t="inlineStr">
         <is>
           <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
         </is>
@@ -32461,7 +32490,7 @@
         </is>
       </c>
       <c r="H266" s="24" t="inlineStr"/>
-      <c r="I266" s="69" t="inlineStr">
+      <c r="I266" s="70" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -32544,10 +32573,10 @@
         </is>
       </c>
       <c r="AS266" s="23" t="n"/>
-      <c r="AT266" s="66" t="inlineStr"/>
+      <c r="AT266" s="67" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" s="67" t="inlineStr">
+      <c r="A267" s="68" t="inlineStr">
         <is>
           <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
         </is>
@@ -32579,7 +32608,7 @@
         </is>
       </c>
       <c r="H267" s="24" t="inlineStr"/>
-      <c r="I267" s="69" t="inlineStr">
+      <c r="I267" s="70" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -32662,10 +32691,10 @@
         </is>
       </c>
       <c r="AS267" s="23" t="n"/>
-      <c r="AT267" s="66" t="inlineStr"/>
+      <c r="AT267" s="67" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="67" t="inlineStr">
+      <c r="A268" s="68" t="inlineStr">
         <is>
           <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
         </is>
@@ -32697,7 +32726,7 @@
         </is>
       </c>
       <c r="H268" s="24" t="inlineStr"/>
-      <c r="I268" s="69" t="inlineStr">
+      <c r="I268" s="70" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -32780,10 +32809,10 @@
         </is>
       </c>
       <c r="AS268" s="23" t="n"/>
-      <c r="AT268" s="66" t="inlineStr"/>
+      <c r="AT268" s="67" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="67" t="inlineStr">
+      <c r="A269" s="68" t="inlineStr">
         <is>
           <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
         </is>
@@ -32815,7 +32844,7 @@
         </is>
       </c>
       <c r="H269" s="24" t="inlineStr"/>
-      <c r="I269" s="69" t="inlineStr">
+      <c r="I269" s="70" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -32898,10 +32927,10 @@
         </is>
       </c>
       <c r="AS269" s="23" t="n"/>
-      <c r="AT269" s="66" t="inlineStr"/>
+      <c r="AT269" s="67" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="67" t="inlineStr">
+      <c r="A270" s="68" t="inlineStr">
         <is>
           <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
         </is>
@@ -32933,7 +32962,7 @@
         </is>
       </c>
       <c r="H270" s="24" t="inlineStr"/>
-      <c r="I270" s="69" t="inlineStr">
+      <c r="I270" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -33016,10 +33045,10 @@
         </is>
       </c>
       <c r="AS270" s="23" t="n"/>
-      <c r="AT270" s="66" t="inlineStr"/>
+      <c r="AT270" s="67" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="67" t="inlineStr">
+      <c r="A271" s="68" t="inlineStr">
         <is>
           <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
         </is>
@@ -33051,7 +33080,7 @@
         </is>
       </c>
       <c r="H271" s="24" t="inlineStr"/>
-      <c r="I271" s="69" t="inlineStr">
+      <c r="I271" s="70" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -33134,10 +33163,10 @@
         </is>
       </c>
       <c r="AS271" s="23" t="n"/>
-      <c r="AT271" s="66" t="inlineStr"/>
+      <c r="AT271" s="67" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" s="67" t="inlineStr">
+      <c r="A272" s="68" t="inlineStr">
         <is>
           <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
         </is>
@@ -33169,7 +33198,7 @@
         </is>
       </c>
       <c r="H272" s="24" t="inlineStr"/>
-      <c r="I272" s="69" t="inlineStr">
+      <c r="I272" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -33252,10 +33281,10 @@
         </is>
       </c>
       <c r="AS272" s="23" t="n"/>
-      <c r="AT272" s="66" t="inlineStr"/>
+      <c r="AT272" s="67" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="67" t="inlineStr">
+      <c r="A273" s="68" t="inlineStr">
         <is>
           <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
         </is>
@@ -33287,7 +33316,7 @@
         </is>
       </c>
       <c r="H273" s="24" t="inlineStr"/>
-      <c r="I273" s="69" t="inlineStr">
+      <c r="I273" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -33370,10 +33399,10 @@
         </is>
       </c>
       <c r="AS273" s="23" t="n"/>
-      <c r="AT273" s="66" t="inlineStr"/>
+      <c r="AT273" s="67" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="67" t="inlineStr">
+      <c r="A274" s="68" t="inlineStr">
         <is>
           <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
         </is>
@@ -33405,7 +33434,7 @@
         </is>
       </c>
       <c r="H274" s="24" t="inlineStr"/>
-      <c r="I274" s="69" t="inlineStr">
+      <c r="I274" s="70" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -33488,10 +33517,10 @@
         </is>
       </c>
       <c r="AS274" s="23" t="n"/>
-      <c r="AT274" s="66" t="inlineStr"/>
+      <c r="AT274" s="67" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" s="67" t="inlineStr">
+      <c r="A275" s="68" t="inlineStr">
         <is>
           <t>PS5-82-01 - Sanitary Sewage Collection</t>
         </is>
@@ -33523,7 +33552,7 @@
         </is>
       </c>
       <c r="H275" s="24" t="inlineStr"/>
-      <c r="I275" s="68" t="inlineStr">
+      <c r="I275" s="69" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -33606,10 +33635,10 @@
         </is>
       </c>
       <c r="AS275" s="23" t="n"/>
-      <c r="AT275" s="66" t="inlineStr"/>
+      <c r="AT275" s="67" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="67" t="inlineStr">
+      <c r="A276" s="68" t="inlineStr">
         <is>
           <t>PS5-82-02 - Sewage Treatment Plant Package</t>
         </is>
@@ -33641,7 +33670,7 @@
         </is>
       </c>
       <c r="H276" s="24" t="inlineStr"/>
-      <c r="I276" s="69" t="inlineStr">
+      <c r="I276" s="70" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -33724,10 +33753,10 @@
         </is>
       </c>
       <c r="AS276" s="23" t="n"/>
-      <c r="AT276" s="66" t="inlineStr"/>
+      <c r="AT276" s="67" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" s="67" t="inlineStr">
+      <c r="A277" s="68" t="inlineStr">
         <is>
           <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
         </is>
@@ -33759,7 +33788,7 @@
         </is>
       </c>
       <c r="H277" s="24" t="inlineStr"/>
-      <c r="I277" s="69" t="inlineStr">
+      <c r="I277" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -33842,10 +33871,10 @@
         </is>
       </c>
       <c r="AS277" s="23" t="n"/>
-      <c r="AT277" s="66" t="inlineStr"/>
+      <c r="AT277" s="67" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="67" t="inlineStr">
+      <c r="A278" s="68" t="inlineStr">
         <is>
           <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
         </is>
@@ -33877,7 +33906,7 @@
         </is>
       </c>
       <c r="H278" s="24" t="inlineStr"/>
-      <c r="I278" s="68" t="inlineStr">
+      <c r="I278" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -33960,10 +33989,10 @@
         </is>
       </c>
       <c r="AS278" s="23" t="n"/>
-      <c r="AT278" s="66" t="inlineStr"/>
+      <c r="AT278" s="67" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="67" t="inlineStr">
+      <c r="A279" s="68" t="inlineStr">
         <is>
           <t>PS5-82-05 - Office and Facilities building</t>
         </is>
@@ -33995,7 +34024,7 @@
         </is>
       </c>
       <c r="H279" s="24" t="inlineStr"/>
-      <c r="I279" s="69" t="inlineStr">
+      <c r="I279" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -34078,10 +34107,10 @@
         </is>
       </c>
       <c r="AS279" s="23" t="n"/>
-      <c r="AT279" s="66" t="inlineStr"/>
+      <c r="AT279" s="67" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="67" t="inlineStr">
+      <c r="A280" s="68" t="inlineStr">
         <is>
           <t>PS5-82-06 - Guard House Building</t>
         </is>
@@ -34113,7 +34142,7 @@
         </is>
       </c>
       <c r="H280" s="24" t="inlineStr"/>
-      <c r="I280" s="69" t="inlineStr">
+      <c r="I280" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -34196,10 +34225,10 @@
         </is>
       </c>
       <c r="AS280" s="23" t="n"/>
-      <c r="AT280" s="66" t="inlineStr"/>
+      <c r="AT280" s="67" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="67" t="inlineStr">
+      <c r="A281" s="68" t="inlineStr">
         <is>
           <t>PS5-82-07 - Guard Huts</t>
         </is>
@@ -34231,7 +34260,7 @@
         </is>
       </c>
       <c r="H281" s="24" t="inlineStr"/>
-      <c r="I281" s="69" t="inlineStr">
+      <c r="I281" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -34314,7 +34343,7 @@
         </is>
       </c>
       <c r="AS281" s="23" t="n"/>
-      <c r="AT281" s="66" t="inlineStr"/>
+      <c r="AT281" s="67" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="53" t="inlineStr">
@@ -34440,10 +34469,10 @@
         </is>
       </c>
       <c r="AS282" s="23" t="n"/>
-      <c r="AT282" s="66" t="inlineStr"/>
+      <c r="AT282" s="67" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" s="67" t="inlineStr">
+      <c r="A283" s="68" t="inlineStr">
         <is>
           <t>PS5-84-01 - Generator Building</t>
         </is>
@@ -34475,7 +34504,7 @@
         </is>
       </c>
       <c r="H283" s="24" t="inlineStr"/>
-      <c r="I283" s="69" t="inlineStr">
+      <c r="I283" s="70" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -34558,10 +34587,10 @@
         </is>
       </c>
       <c r="AS283" s="23" t="n"/>
-      <c r="AT283" s="66" t="inlineStr"/>
+      <c r="AT283" s="67" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" s="67" t="inlineStr">
+      <c r="A284" s="68" t="inlineStr">
         <is>
           <t>PS5-84-02 - Workshop &amp; Warehouse</t>
         </is>
@@ -34593,7 +34622,7 @@
         </is>
       </c>
       <c r="H284" s="24" t="inlineStr"/>
-      <c r="I284" s="69" t="inlineStr">
+      <c r="I284" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -34676,7 +34705,7 @@
         </is>
       </c>
       <c r="AS284" s="23" t="n"/>
-      <c r="AT284" s="66" t="inlineStr"/>
+      <c r="AT284" s="67" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="53" t="inlineStr">
@@ -34798,7 +34827,7 @@
         </is>
       </c>
       <c r="AS285" s="23" t="n"/>
-      <c r="AT285" s="66" t="inlineStr"/>
+      <c r="AT285" s="67" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="53" t="inlineStr">
@@ -34920,7 +34949,7 @@
         </is>
       </c>
       <c r="AS286" s="23" t="n"/>
-      <c r="AT286" s="66" t="inlineStr"/>
+      <c r="AT286" s="67" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="53" t="inlineStr">
@@ -35046,10 +35075,10 @@
         </is>
       </c>
       <c r="AS287" s="23" t="n"/>
-      <c r="AT287" s="66" t="inlineStr"/>
+      <c r="AT287" s="67" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="67" t="inlineStr">
+      <c r="A288" s="68" t="inlineStr">
         <is>
           <t>PS5-99-01 - Area Completion for Building area</t>
         </is>
@@ -35081,7 +35110,7 @@
         </is>
       </c>
       <c r="H288" s="24" t="inlineStr"/>
-      <c r="I288" s="69" t="inlineStr">
+      <c r="I288" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -35164,10 +35193,10 @@
         </is>
       </c>
       <c r="AS288" s="23" t="n"/>
-      <c r="AT288" s="66" t="inlineStr"/>
+      <c r="AT288" s="67" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="67" t="inlineStr">
+      <c r="A289" s="68" t="inlineStr">
         <is>
           <t>PS5-99-02 - Area Completion for Utility area</t>
         </is>
@@ -35199,7 +35228,7 @@
         </is>
       </c>
       <c r="H289" s="24" t="inlineStr"/>
-      <c r="I289" s="69" t="inlineStr">
+      <c r="I289" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -35282,10 +35311,10 @@
         </is>
       </c>
       <c r="AS289" s="23" t="n"/>
-      <c r="AT289" s="66" t="inlineStr"/>
+      <c r="AT289" s="67" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="67" t="inlineStr">
+      <c r="A290" s="68" t="inlineStr">
         <is>
           <t>PS5-99-03 - Area Completion for Power Distribution area</t>
         </is>
@@ -35317,7 +35346,7 @@
         </is>
       </c>
       <c r="H290" s="24" t="inlineStr"/>
-      <c r="I290" s="69" t="inlineStr">
+      <c r="I290" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -35400,10 +35429,10 @@
         </is>
       </c>
       <c r="AS290" s="23" t="n"/>
-      <c r="AT290" s="66" t="inlineStr"/>
+      <c r="AT290" s="67" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" s="67" t="inlineStr">
+      <c r="A291" s="68" t="inlineStr">
         <is>
           <t>PS5-99-04 - Area Completion for Process area</t>
         </is>
@@ -35435,7 +35464,7 @@
         </is>
       </c>
       <c r="H291" s="24" t="inlineStr"/>
-      <c r="I291" s="69" t="inlineStr">
+      <c r="I291" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -35518,10 +35547,10 @@
         </is>
       </c>
       <c r="AS291" s="23" t="n"/>
-      <c r="AT291" s="66" t="inlineStr"/>
+      <c r="AT291" s="67" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" s="67" t="inlineStr">
+      <c r="A292" s="68" t="inlineStr">
         <is>
           <t>PS5-99-05 - Area Completion for CFO area</t>
         </is>
@@ -35553,7 +35582,7 @@
         </is>
       </c>
       <c r="H292" s="24" t="inlineStr"/>
-      <c r="I292" s="69" t="inlineStr">
+      <c r="I292" s="70" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -35636,10 +35665,10 @@
         </is>
       </c>
       <c r="AS292" s="23" t="n"/>
-      <c r="AT292" s="66" t="inlineStr"/>
+      <c r="AT292" s="67" t="inlineStr"/>
     </row>
     <row r="293">
-      <c r="A293" s="67" t="inlineStr">
+      <c r="A293" s="68" t="inlineStr">
         <is>
           <t>PS5-99-06 - Area Completion for Power Generation area</t>
         </is>
@@ -35679,7 +35708,7 @@
           <t>RE WALKDOWN</t>
         </is>
       </c>
-      <c r="I293" s="68" t="inlineStr">
+      <c r="I293" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -35762,7 +35791,7 @@
         </is>
       </c>
       <c r="AS293" s="23" t="n"/>
-      <c r="AT293" s="66" t="inlineStr"/>
+      <c r="AT293" s="67" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:AT293"/>

--- a/EXCEL/2 - RFC PROGRESS.xlsx
+++ b/EXCEL/2 - RFC PROGRESS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 · RFC PROGRESS" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIDMAP" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="2 · RFC PROGRESS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SIDMAP" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2 · RFC PROGRESS'!$A$3:$AT$298</definedName>

--- a/EXCEL/2 - RFC PROGRESS.xlsx
+++ b/EXCEL/2 - RFC PROGRESS.xlsx
@@ -6614,9 +6614,9 @@
         </is>
       </c>
       <c r="H47" s="24" t="inlineStr"/>
-      <c r="I47" s="69" t="inlineStr">
-        <is>
-          <t>78%</t>
+      <c r="I47" s="54" t="inlineStr">
+        <is>
+          <t>99%</t>
         </is>
       </c>
       <c r="J47" s="55" t="n">
@@ -6655,14 +6655,14 @@
         <v>183</v>
       </c>
       <c r="AI47" s="23" t="n">
-        <v>142</v>
+        <v>182</v>
       </c>
       <c r="AJ47" s="23" t="n">
-        <v>41</v>
-      </c>
-      <c r="AK47" s="26" t="inlineStr">
-        <is>
-          <t>78%</t>
+        <v>1</v>
+      </c>
+      <c r="AK47" s="27" t="inlineStr">
+        <is>
+          <t>99%</t>
         </is>
       </c>
       <c r="AL47" s="23" t="n">
@@ -8460,7 +8460,7 @@
       <c r="H64" s="24" t="inlineStr"/>
       <c r="I64" s="69" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="J64" s="55" t="n">
@@ -8488,25 +8488,25 @@
         <v>46</v>
       </c>
       <c r="R64" s="62" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S64" s="71" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="AH64" s="28" t="n">
         <v>61</v>
       </c>
       <c r="AI64" s="23" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AJ64" s="23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AK64" s="26" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="AL64" s="23" t="n">
@@ -25284,9 +25284,9 @@
         </is>
       </c>
       <c r="H207" s="24" t="inlineStr"/>
-      <c r="I207" s="70" t="inlineStr">
-        <is>
-          <t>32%</t>
+      <c r="I207" s="54" t="inlineStr">
+        <is>
+          <t>92%</t>
         </is>
       </c>
       <c r="J207" s="55" t="n">
@@ -25325,14 +25325,14 @@
         <v>25</v>
       </c>
       <c r="AI207" s="23" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="AJ207" s="23" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK207" s="25" t="inlineStr">
-        <is>
-          <t>32%</t>
+        <v>2</v>
+      </c>
+      <c r="AK207" s="27" t="inlineStr">
+        <is>
+          <t>92%</t>
         </is>
       </c>
       <c r="AL207" s="23" t="n">
@@ -28986,7 +28986,7 @@
       <c r="H239" s="24" t="inlineStr"/>
       <c r="I239" s="69" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="J239" s="55" t="n">
@@ -29025,14 +29025,14 @@
         <v>15</v>
       </c>
       <c r="AI239" s="23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AJ239" s="23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AK239" s="26" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="AL239" s="23" t="n">

--- a/EXCEL/2 - RFC PROGRESS.xlsx
+++ b/EXCEL/2 - RFC PROGRESS.xlsx
@@ -241,6 +241,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFffeb9c"/>
+        <bgColor rgb="FFffeb9c"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFe8d5c4"/>
         <bgColor rgb="FFe8d5c4"/>
       </patternFill>
@@ -309,12 +315,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFBDD7EE"/>
         <bgColor rgb="FFBDD7EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFffeb9c"/>
-        <bgColor rgb="FFffeb9c"/>
       </patternFill>
     </fill>
     <fill>
@@ -570,7 +570,7 @@
     <xf numFmtId="0" fontId="9" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -644,13 +644,10 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -674,22 +671,25 @@
     <xf numFmtId="0" fontId="6" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -698,10 +698,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -710,7 +710,7 @@
     <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -722,10 +722,10 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -740,7 +740,7 @@
     <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -773,16 +773,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1593,11 +1593,7 @@
           <t>2026-09-08 00:00:00</t>
         </is>
       </c>
-      <c r="F4" s="23" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
+      <c r="F4" s="23" t="inlineStr"/>
       <c r="G4" s="28" t="inlineStr">
         <is>
           <t>Full</t>
@@ -1610,7 +1606,7 @@
       </c>
       <c r="I4" s="54" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J4" s="55" t="n">
@@ -1651,14 +1647,14 @@
         <v>86</v>
       </c>
       <c r="AI4" s="23" t="n">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AJ4" s="23" t="n">
-        <v>4</v>
+        <v>-18</v>
       </c>
       <c r="AK4" s="27" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="AL4" s="23" t="inlineStr">
@@ -1681,18 +1677,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP4" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP4" s="65" t="inlineStr"/>
       <c r="AQ4" s="65" t="inlineStr"/>
       <c r="AR4" s="23" t="inlineStr"/>
       <c r="AS4" s="66" t="n"/>
       <c r="AT4" s="67" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="53" t="inlineStr">
+      <c r="A5" s="68" t="inlineStr">
         <is>
           <t>PS5-01-02 - Fire Water Pump A</t>
         </is>
@@ -1803,11 +1795,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP5" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP5" s="65" t="inlineStr"/>
       <c r="AQ5" s="65" t="inlineStr">
         <is>
           <t>EACOP(MR.BENHER TBC)-EXPECTED 19-08-2026</t>
@@ -1822,7 +1810,7 @@
       <c r="AT5" s="67" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="53" t="inlineStr">
+      <c r="A6" s="68" t="inlineStr">
         <is>
           <t>PS5-01-03 - Fire Water Pump B</t>
         </is>
@@ -1847,11 +1835,7 @@
           <t>2026-09-08 00:00:00</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
+      <c r="F6" s="23" t="inlineStr"/>
       <c r="G6" s="28" t="inlineStr">
         <is>
           <t>Full</t>
@@ -1933,11 +1917,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP6" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP6" s="65" t="inlineStr"/>
       <c r="AQ6" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -1952,7 +1932,7 @@
       <c r="AT6" s="67" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="68" t="inlineStr">
+      <c r="A7" s="53" t="inlineStr">
         <is>
           <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
         </is>
@@ -2059,18 +2039,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP7" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP7" s="65" t="inlineStr"/>
       <c r="AQ7" s="65" t="inlineStr"/>
       <c r="AR7" s="23" t="inlineStr"/>
       <c r="AS7" s="23" t="n"/>
       <c r="AT7" s="67" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="68" t="inlineStr">
+      <c r="A8" s="53" t="inlineStr">
         <is>
           <t>PS5-01-05 - Foam Skid</t>
         </is>
@@ -2181,18 +2157,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP8" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP8" s="65" t="inlineStr"/>
       <c r="AQ8" s="65" t="inlineStr"/>
       <c r="AR8" s="23" t="inlineStr"/>
       <c r="AS8" s="23" t="n"/>
       <c r="AT8" s="67" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="68" t="inlineStr">
+      <c r="A9" s="53" t="inlineStr">
         <is>
           <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
@@ -2299,18 +2271,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP9" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP9" s="65" t="inlineStr"/>
       <c r="AQ9" s="65" t="inlineStr"/>
       <c r="AR9" s="23" t="inlineStr"/>
       <c r="AS9" s="23" t="n"/>
       <c r="AT9" s="67" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="53" t="inlineStr">
+      <c r="A10" s="68" t="inlineStr">
         <is>
           <t>PS5-01-07 - Fire Water Ring Main &amp; Distribution</t>
         </is>
@@ -2419,26 +2387,22 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP10" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP10" s="65" t="inlineStr"/>
       <c r="AQ10" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR10" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AS10" s="23" t="n"/>
       <c r="AT10" s="67" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="53" t="inlineStr">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t>PS5-01-08 - PS5 Deluge Valve Skid (PS5-01-UK-6100)</t>
         </is>
@@ -2549,18 +2513,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP11" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP11" s="65" t="inlineStr"/>
       <c r="AQ11" s="65" t="inlineStr"/>
       <c r="AR11" s="23" t="inlineStr"/>
       <c r="AS11" s="23" t="n"/>
       <c r="AT11" s="67" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="68" t="inlineStr">
+      <c r="A12" s="53" t="inlineStr">
         <is>
           <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
@@ -2663,18 +2623,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP12" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP12" s="65" t="inlineStr"/>
       <c r="AQ12" s="65" t="inlineStr"/>
       <c r="AR12" s="23" t="inlineStr"/>
       <c r="AS12" s="23" t="n"/>
       <c r="AT12" s="67" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="68" t="inlineStr">
+      <c r="A13" s="53" t="inlineStr">
         <is>
           <t>PS5-01-10 - Water Mist Package</t>
         </is>
@@ -2785,18 +2741,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP13" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP13" s="65" t="inlineStr"/>
       <c r="AQ13" s="65" t="inlineStr"/>
       <c r="AR13" s="23" t="inlineStr"/>
       <c r="AS13" s="23" t="n"/>
       <c r="AT13" s="67" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="68" t="inlineStr">
+      <c r="A14" s="53" t="inlineStr">
         <is>
           <t>PS5-01-11 - Inergen for Power Gen Building</t>
         </is>
@@ -2907,18 +2859,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP14" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP14" s="65" t="inlineStr"/>
       <c r="AQ14" s="65" t="inlineStr"/>
       <c r="AR14" s="23" t="inlineStr"/>
       <c r="AS14" s="23" t="n"/>
       <c r="AT14" s="67" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="53" t="inlineStr">
+      <c r="A15" s="68" t="inlineStr">
         <is>
           <t>PS5-02-01 - Miscellaneous Safety equipment</t>
         </is>
@@ -2928,11 +2876,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="C15" s="23" t="inlineStr"/>
       <c r="D15" s="23" t="inlineStr">
         <is>
           <t>E,M,S</t>
@@ -3025,11 +2969,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP15" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP15" s="65" t="inlineStr"/>
       <c r="AQ15" s="65" t="inlineStr">
         <is>
           <t>18</t>
@@ -3044,7 +2984,7 @@
       <c r="AT15" s="67" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="53" t="inlineStr">
+      <c r="A16" s="68" t="inlineStr">
         <is>
           <t>PS5-02-02 - Portable Fire Fighting Equipments</t>
         </is>
@@ -3151,11 +3091,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP16" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP16" s="65" t="inlineStr"/>
       <c r="AQ16" s="65" t="inlineStr">
         <is>
           <t>48</t>
@@ -3170,7 +3106,7 @@
       <c r="AT16" s="67" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="68" t="inlineStr">
+      <c r="A17" s="53" t="inlineStr">
         <is>
           <t>PS5-03-01 - FZ-01 - Process Area</t>
         </is>
@@ -3281,18 +3217,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP17" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP17" s="65" t="inlineStr"/>
       <c r="AQ17" s="65" t="inlineStr"/>
       <c r="AR17" s="23" t="inlineStr"/>
       <c r="AS17" s="23" t="n"/>
       <c r="AT17" s="67" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="53" t="inlineStr">
+      <c r="A18" s="68" t="inlineStr">
         <is>
           <t>PS5-03-03 - FZ-03 - Buildings Area</t>
         </is>
@@ -3395,18 +3327,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP18" s="65" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="AP18" s="65" t="inlineStr"/>
       <c r="AQ18" s="65" t="inlineStr"/>
       <c r="AR18" s="23" t="inlineStr"/>
       <c r="AS18" s="23" t="n"/>
       <c r="AT18" s="67" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="53" t="inlineStr">
+      <c r="A19" s="68" t="inlineStr">
         <is>
           <t>PS5-03-04 - FZ-04 - Utilities - Diesel and Firewater Pumps Areas</t>
         </is>
@@ -3441,11 +3369,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H19" s="24" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
+      <c r="H19" s="24" t="inlineStr"/>
       <c r="I19" s="54" t="inlineStr">
         <is>
           <t>94%</t>
@@ -3517,11 +3441,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP19" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP19" s="65" t="inlineStr"/>
       <c r="AQ19" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -3536,7 +3456,7 @@
       <c r="AT19" s="67" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="68" t="inlineStr">
+      <c r="A20" s="53" t="inlineStr">
         <is>
           <t>PS5-03-06 - FZ-06 - Transformer Area</t>
         </is>
@@ -3647,18 +3567,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP20" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP20" s="65" t="inlineStr"/>
       <c r="AQ20" s="65" t="inlineStr"/>
       <c r="AR20" s="23" t="inlineStr"/>
       <c r="AS20" s="23" t="n"/>
       <c r="AT20" s="67" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="68" t="inlineStr">
+      <c r="A21" s="53" t="inlineStr">
         <is>
           <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
         </is>
@@ -3769,18 +3685,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP21" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP21" s="65" t="inlineStr"/>
       <c r="AQ21" s="65" t="inlineStr"/>
       <c r="AR21" s="23" t="inlineStr"/>
       <c r="AS21" s="23" t="n"/>
       <c r="AT21" s="67" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="53" t="inlineStr">
+      <c r="A22" s="68" t="inlineStr">
         <is>
           <t>PS5-03-08 - FZ-08 - Utilities - Power Generation Area - External</t>
         </is>
@@ -3891,11 +3803,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP22" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP22" s="65" t="inlineStr"/>
       <c r="AQ22" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -3910,7 +3818,7 @@
       <c r="AT22" s="67" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="68" t="inlineStr">
+      <c r="A23" s="53" t="inlineStr">
         <is>
           <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
         </is>
@@ -4021,18 +3929,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP23" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP23" s="65" t="inlineStr"/>
       <c r="AQ23" s="65" t="inlineStr"/>
       <c r="AR23" s="23" t="inlineStr"/>
       <c r="AS23" s="23" t="n"/>
       <c r="AT23" s="67" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="68" t="inlineStr">
+      <c r="A24" s="53" t="inlineStr">
         <is>
           <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
         </is>
@@ -4143,18 +4047,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP24" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP24" s="65" t="inlineStr"/>
       <c r="AQ24" s="65" t="inlineStr"/>
       <c r="AR24" s="23" t="inlineStr"/>
       <c r="AS24" s="23" t="n"/>
       <c r="AT24" s="67" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="68" t="inlineStr">
+      <c r="A25" s="53" t="inlineStr">
         <is>
           <t>PS5-03-11 - FZ-11 - Power Generation Building - Engine Bay 3</t>
         </is>
@@ -4265,18 +4165,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP25" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP25" s="65" t="inlineStr"/>
       <c r="AQ25" s="65" t="inlineStr"/>
       <c r="AR25" s="23" t="inlineStr"/>
       <c r="AS25" s="23" t="n"/>
       <c r="AT25" s="67" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="68" t="inlineStr">
+      <c r="A26" s="53" t="inlineStr">
         <is>
           <t>PS5-03-12 - FZ-12 - Power Generation Building - Engine Bay 4</t>
         </is>
@@ -4387,18 +4283,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP26" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP26" s="65" t="inlineStr"/>
       <c r="AQ26" s="65" t="inlineStr"/>
       <c r="AR26" s="23" t="inlineStr"/>
       <c r="AS26" s="23" t="n"/>
       <c r="AT26" s="67" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="68" t="inlineStr">
+      <c r="A27" s="53" t="inlineStr">
         <is>
           <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
         </is>
@@ -4509,18 +4401,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP27" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP27" s="65" t="inlineStr"/>
       <c r="AQ27" s="65" t="inlineStr"/>
       <c r="AR27" s="23" t="inlineStr"/>
       <c r="AS27" s="23" t="n"/>
       <c r="AT27" s="67" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="53" t="inlineStr">
+      <c r="A28" s="68" t="inlineStr">
         <is>
           <t>PS5-03-14 - FZ-14 - Power Generation Building - Switchgear Room</t>
         </is>
@@ -4627,18 +4515,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP28" s="65" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
+      <c r="AP28" s="65" t="inlineStr"/>
       <c r="AQ28" s="65" t="inlineStr"/>
       <c r="AR28" s="23" t="inlineStr"/>
       <c r="AS28" s="23" t="n"/>
       <c r="AT28" s="67" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="53" t="inlineStr">
+      <c r="A29" s="68" t="inlineStr">
         <is>
           <t>PS5-03-15 - FZ-15 - Power Generation Building - Generator Room 1</t>
         </is>
@@ -4745,18 +4629,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP29" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="AP29" s="65" t="inlineStr"/>
       <c r="AQ29" s="65" t="inlineStr"/>
       <c r="AR29" s="23" t="inlineStr"/>
       <c r="AS29" s="23" t="n"/>
       <c r="AT29" s="67" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="53" t="inlineStr">
+      <c r="A30" s="68" t="inlineStr">
         <is>
           <t>PS5-03-16 - FZ-16 - Power Generation Building - Generator Room 2</t>
         </is>
@@ -4863,18 +4743,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP30" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="AP30" s="65" t="inlineStr"/>
       <c r="AQ30" s="65" t="inlineStr"/>
       <c r="AR30" s="23" t="inlineStr"/>
       <c r="AS30" s="23" t="n"/>
       <c r="AT30" s="67" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="53" t="inlineStr">
+      <c r="A31" s="68" t="inlineStr">
         <is>
           <t>PS5-03-17 - FZ-17 - Power Generation Building - Generator Room 3</t>
         </is>
@@ -4981,18 +4857,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP31" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="AP31" s="65" t="inlineStr"/>
       <c r="AQ31" s="65" t="inlineStr"/>
       <c r="AR31" s="23" t="inlineStr"/>
       <c r="AS31" s="23" t="n"/>
       <c r="AT31" s="67" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="53" t="inlineStr">
+      <c r="A32" s="68" t="inlineStr">
         <is>
           <t>PS5-03-18 - FZ-18 - Power Generation Building - Generator Room 4</t>
         </is>
@@ -5099,18 +4971,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP32" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="AP32" s="65" t="inlineStr"/>
       <c r="AQ32" s="65" t="inlineStr"/>
       <c r="AR32" s="23" t="inlineStr"/>
       <c r="AS32" s="23" t="n"/>
       <c r="AT32" s="67" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="53" t="inlineStr">
+      <c r="A33" s="68" t="inlineStr">
         <is>
           <t>PS5-03-19 - FZ-19 - Power Generation Building - Battery Room</t>
         </is>
@@ -5217,18 +5085,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP33" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="AP33" s="65" t="inlineStr"/>
       <c r="AQ33" s="65" t="inlineStr"/>
       <c r="AR33" s="23" t="inlineStr"/>
       <c r="AS33" s="23" t="n"/>
       <c r="AT33" s="67" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="68" t="inlineStr">
+      <c r="A34" s="53" t="inlineStr">
         <is>
           <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
         </is>
@@ -5335,18 +5199,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP34" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP34" s="65" t="inlineStr"/>
       <c r="AQ34" s="65" t="inlineStr"/>
       <c r="AR34" s="23" t="inlineStr"/>
       <c r="AS34" s="23" t="n"/>
       <c r="AT34" s="67" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="53" t="inlineStr">
+      <c r="A35" s="68" t="inlineStr">
         <is>
           <t>PS5-03-21 - FZ-21 - Power Generation Building - Air Handling Unit</t>
         </is>
@@ -5449,18 +5309,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP35" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="AP35" s="65" t="inlineStr"/>
       <c r="AQ35" s="65" t="inlineStr"/>
       <c r="AR35" s="23" t="inlineStr"/>
       <c r="AS35" s="23" t="n"/>
       <c r="AT35" s="67" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="53" t="inlineStr">
+      <c r="A36" s="68" t="inlineStr">
         <is>
           <t>PS5-03-22 - FZ-G1 - Guard House</t>
         </is>
@@ -5563,18 +5419,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP36" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP36" s="65" t="inlineStr"/>
       <c r="AQ36" s="65" t="inlineStr"/>
       <c r="AR36" s="23" t="inlineStr"/>
       <c r="AS36" s="23" t="n"/>
       <c r="AT36" s="67" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="53" t="inlineStr">
+      <c r="A37" s="68" t="inlineStr">
         <is>
           <t>PS5-03-23 - FZ-E1 to E3 - EITS Building</t>
         </is>
@@ -5658,7 +5510,7 @@
       <c r="AT37" s="67" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="53" t="inlineStr">
+      <c r="A38" s="68" t="inlineStr">
         <is>
           <t>PS5-03-24 - FZ - Office and Facilities Building</t>
         </is>
@@ -5761,18 +5613,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP38" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP38" s="65" t="inlineStr"/>
       <c r="AQ38" s="65" t="inlineStr"/>
       <c r="AR38" s="23" t="inlineStr"/>
       <c r="AS38" s="23" t="n"/>
       <c r="AT38" s="67" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="53" t="inlineStr">
+      <c r="A39" s="68" t="inlineStr">
         <is>
           <t>PS5-03-25 - FZ - Workshop &amp; Warehouse</t>
         </is>
@@ -5875,18 +5723,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP39" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP39" s="65" t="inlineStr"/>
       <c r="AQ39" s="65" t="inlineStr"/>
       <c r="AR39" s="23" t="inlineStr"/>
       <c r="AS39" s="23" t="n"/>
       <c r="AT39" s="67" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="53" t="inlineStr">
+      <c r="A40" s="68" t="inlineStr">
         <is>
           <t>PS5-04-01 - Office Building PCS System</t>
         </is>
@@ -5970,7 +5814,7 @@
       <c r="AT40" s="67" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="53" t="inlineStr">
+      <c r="A41" s="68" t="inlineStr">
         <is>
           <t>PS5-04-02 - Office Building SIS/FGS System</t>
         </is>
@@ -6073,11 +5917,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP41" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="AP41" s="65" t="inlineStr"/>
       <c r="AQ41" s="65" t="inlineStr">
         <is>
           <t>3</t>
@@ -6092,7 +5932,7 @@
       <c r="AT41" s="67" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="53" t="inlineStr">
+      <c r="A42" s="68" t="inlineStr">
         <is>
           <t>PS5-04-03 - 33kV ICSS System</t>
         </is>
@@ -6110,7 +5950,7 @@
       <c r="H42" s="24" t="inlineStr"/>
       <c r="I42" s="54" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="J42" s="55" t="n">
@@ -6138,25 +5978,25 @@
         <v>65</v>
       </c>
       <c r="R42" s="62" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S42" s="71" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="AH42" s="28" t="n">
         <v>82</v>
       </c>
       <c r="AI42" s="23" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="AJ42" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AK42" s="27" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="AL42" s="23" t="n">
@@ -6176,7 +6016,7 @@
       <c r="AT42" s="67" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="53" t="inlineStr">
+      <c r="A43" s="68" t="inlineStr">
         <is>
           <t>PS5-04-04 - 33kV PCS System</t>
         </is>
@@ -6260,7 +6100,7 @@
       <c r="AT43" s="67" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="53" t="inlineStr">
+      <c r="A44" s="68" t="inlineStr">
         <is>
           <t>PS5-04-05 - 33kV SIS/FGS System</t>
         </is>
@@ -6453,11 +6293,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP45" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP45" s="65" t="inlineStr"/>
       <c r="AQ45" s="65" t="inlineStr"/>
       <c r="AR45" s="23" t="inlineStr"/>
       <c r="AS45" s="23" t="n"/>
@@ -6571,18 +6407,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP46" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP46" s="65" t="inlineStr"/>
       <c r="AQ46" s="65" t="inlineStr"/>
       <c r="AR46" s="23" t="inlineStr"/>
       <c r="AS46" s="23" t="n"/>
       <c r="AT46" s="67" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="53" t="inlineStr">
+      <c r="A47" s="68" t="inlineStr">
         <is>
           <t>PS5-06-01 - AC UPS - EITS Building</t>
         </is>
@@ -6666,7 +6498,7 @@
       <c r="AT47" s="67" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="68" t="inlineStr">
+      <c r="A48" s="53" t="inlineStr">
         <is>
           <t>PS5-06-02 - AC UPS - Power Generator Building</t>
         </is>
@@ -6777,18 +6609,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP48" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP48" s="65" t="inlineStr"/>
       <c r="AQ48" s="65" t="inlineStr"/>
       <c r="AR48" s="23" t="inlineStr"/>
       <c r="AS48" s="23" t="n"/>
       <c r="AT48" s="67" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="53" t="inlineStr">
+      <c r="A49" s="68" t="inlineStr">
         <is>
           <t>PS5-06-03 - AC UPS - Office &amp; Facilities Building</t>
         </is>
@@ -6891,18 +6719,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP49" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP49" s="65" t="inlineStr"/>
       <c r="AQ49" s="65" t="inlineStr"/>
       <c r="AR49" s="23" t="inlineStr"/>
       <c r="AS49" s="23" t="n"/>
       <c r="AT49" s="67" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="53" t="inlineStr">
+      <c r="A50" s="68" t="inlineStr">
         <is>
           <t>PS5-06-04 - AC UPS - Guard House</t>
         </is>
@@ -7005,18 +6829,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP50" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP50" s="65" t="inlineStr"/>
       <c r="AQ50" s="65" t="inlineStr"/>
       <c r="AR50" s="23" t="inlineStr"/>
       <c r="AS50" s="23" t="n"/>
       <c r="AT50" s="67" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="53" t="inlineStr">
+      <c r="A51" s="68" t="inlineStr">
         <is>
           <t>PS5-06-05 - AC UPS - Workshop &amp; Warehouse</t>
         </is>
@@ -7119,18 +6939,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP51" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP51" s="65" t="inlineStr"/>
       <c r="AQ51" s="65" t="inlineStr"/>
       <c r="AR51" s="23" t="inlineStr"/>
       <c r="AS51" s="23" t="n"/>
       <c r="AT51" s="67" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="53" t="inlineStr">
+      <c r="A52" s="68" t="inlineStr">
         <is>
           <t>PS5-08-01</t>
         </is>
@@ -7233,11 +7049,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP52" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP52" s="65" t="inlineStr"/>
       <c r="AQ52" s="65" t="inlineStr">
         <is>
           <t>148</t>
@@ -7252,7 +7064,7 @@
       <c r="AT52" s="67" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="53" t="inlineStr">
+      <c r="A53" s="68" t="inlineStr">
         <is>
           <t>PS5-08-01a - PAGA (Required for SU)</t>
         </is>
@@ -7336,7 +7148,7 @@
       <c r="AT53" s="67" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="53" t="inlineStr">
+      <c r="A54" s="68" t="inlineStr">
         <is>
           <t>PS5-08-01b - PAGA (Not required for SU)</t>
         </is>
@@ -7420,7 +7232,7 @@
       <c r="AT54" s="67" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="53" t="inlineStr">
+      <c r="A55" s="68" t="inlineStr">
         <is>
           <t>PS5-08-03 - Telephone</t>
         </is>
@@ -7523,11 +7335,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP55" s="65" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="AP55" s="65" t="inlineStr"/>
       <c r="AQ55" s="65" t="inlineStr">
         <is>
           <t>7</t>
@@ -7542,7 +7350,7 @@
       <c r="AT55" s="67" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="53" t="inlineStr">
+      <c r="A56" s="68" t="inlineStr">
         <is>
           <t>PS5-08-04 - Hotline</t>
         </is>
@@ -7626,7 +7434,7 @@
       <c r="AT56" s="67" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="53" t="inlineStr">
+      <c r="A57" s="68" t="inlineStr">
         <is>
           <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
         </is>
@@ -7710,7 +7518,7 @@
       <c r="AT57" s="67" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="53" t="inlineStr">
+      <c r="A58" s="68" t="inlineStr">
         <is>
           <t>PS5-08-11 - Corporate LAN  (SIE)</t>
         </is>
@@ -7813,11 +7621,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP58" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP58" s="65" t="inlineStr"/>
       <c r="AQ58" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -7832,7 +7636,7 @@
       <c r="AT58" s="67" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="53" t="inlineStr">
+      <c r="A59" s="68" t="inlineStr">
         <is>
           <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
         </is>
@@ -7935,11 +7739,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP59" s="65" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+      <c r="AP59" s="65" t="inlineStr"/>
       <c r="AQ59" s="65" t="inlineStr">
         <is>
           <t>9</t>
@@ -7954,7 +7754,7 @@
       <c r="AT59" s="67" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="53" t="inlineStr">
+      <c r="A60" s="68" t="inlineStr">
         <is>
           <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
         </is>
@@ -8057,11 +7857,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP60" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP60" s="65" t="inlineStr"/>
       <c r="AQ60" s="65" t="inlineStr">
         <is>
           <t>13</t>
@@ -8076,7 +7872,7 @@
       <c r="AT60" s="67" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="53" t="inlineStr">
+      <c r="A61" s="68" t="inlineStr">
         <is>
           <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
         </is>
@@ -8179,11 +7975,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP61" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP61" s="65" t="inlineStr"/>
       <c r="AQ61" s="65" t="inlineStr">
         <is>
           <t>12</t>
@@ -8198,7 +7990,7 @@
       <c r="AT61" s="67" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="53" t="inlineStr">
+      <c r="A62" s="68" t="inlineStr">
         <is>
           <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
         </is>
@@ -8301,11 +8093,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP62" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP62" s="65" t="inlineStr"/>
       <c r="AQ62" s="65" t="inlineStr">
         <is>
           <t>9</t>
@@ -8320,7 +8108,7 @@
       <c r="AT62" s="67" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="53" t="inlineStr">
+      <c r="A63" s="68" t="inlineStr">
         <is>
           <t>PS5-08-23 - VHF Trunk Radio System</t>
         </is>
@@ -8423,11 +8211,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP63" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP63" s="65" t="inlineStr"/>
       <c r="AQ63" s="65" t="inlineStr">
         <is>
           <t>11</t>
@@ -8442,7 +8226,7 @@
       <c r="AT63" s="67" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="53" t="inlineStr">
+      <c r="A64" s="68" t="inlineStr">
         <is>
           <t>PS5-08-34 - Satphone</t>
         </is>
@@ -8545,11 +8329,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP64" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP64" s="65" t="inlineStr"/>
       <c r="AQ64" s="65" t="inlineStr">
         <is>
           <t>4</t>
@@ -8564,7 +8344,7 @@
       <c r="AT64" s="67" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="53" t="inlineStr">
+      <c r="A65" s="68" t="inlineStr">
         <is>
           <t>PS5-08-35 - Optical Transport Network</t>
         </is>
@@ -8648,7 +8428,7 @@
       <c r="AT65" s="67" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="53" t="inlineStr">
+      <c r="A66" s="68" t="inlineStr">
         <is>
           <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
         </is>
@@ -8751,18 +8531,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP66" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP66" s="65" t="inlineStr"/>
       <c r="AQ66" s="65" t="inlineStr"/>
       <c r="AR66" s="23" t="inlineStr"/>
       <c r="AS66" s="23" t="n"/>
       <c r="AT66" s="67" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="53" t="inlineStr">
+      <c r="A67" s="68" t="inlineStr">
         <is>
           <t>PS5-08-51 - Entertainment</t>
         </is>
@@ -8865,11 +8641,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP67" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP67" s="65" t="inlineStr"/>
       <c r="AQ67" s="65" t="inlineStr">
         <is>
           <t>18</t>
@@ -8884,7 +8656,7 @@
       <c r="AT67" s="67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="53" t="inlineStr">
+      <c r="A68" s="68" t="inlineStr">
         <is>
           <t>PS5-08-52a - Process &amp; Security CCTV (Required for SU)</t>
         </is>
@@ -8968,7 +8740,7 @@
       <c r="AT68" s="67" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="53" t="inlineStr">
+      <c r="A69" s="68" t="inlineStr">
         <is>
           <t>PS5-08-52b - Process &amp; Security CCTV (Not required for SU)</t>
         </is>
@@ -9052,7 +8824,7 @@
       <c r="AT69" s="67" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="53" t="inlineStr">
+      <c r="A70" s="68" t="inlineStr">
         <is>
           <t>PS5-08-55 - Videoconference</t>
         </is>
@@ -9136,7 +8908,7 @@
       <c r="AT70" s="67" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="53" t="inlineStr">
+      <c r="A71" s="68" t="inlineStr">
         <is>
           <t>PS5-08-61 - Meteocean</t>
         </is>
@@ -9239,11 +9011,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP71" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP71" s="65" t="inlineStr"/>
       <c r="AQ71" s="65" t="inlineStr">
         <is>
           <t>10</t>
@@ -9258,7 +9026,7 @@
       <c r="AT71" s="67" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="53" t="inlineStr">
+      <c r="A72" s="68" t="inlineStr">
         <is>
           <t>PS5-08-71 - Structured Cabling (CAT6)</t>
         </is>
@@ -9361,11 +9129,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP72" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP72" s="65" t="inlineStr"/>
       <c r="AQ72" s="65" t="inlineStr">
         <is>
           <t>240</t>
@@ -9380,7 +9144,7 @@
       <c r="AT72" s="67" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="53" t="inlineStr">
+      <c r="A73" s="68" t="inlineStr">
         <is>
           <t>PS5-08-72 - Structured Cabling (FO)</t>
         </is>
@@ -9483,11 +9247,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP73" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP73" s="65" t="inlineStr"/>
       <c r="AQ73" s="65" t="inlineStr">
         <is>
           <t>6</t>
@@ -9502,7 +9262,7 @@
       <c r="AT73" s="67" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="53" t="inlineStr">
+      <c r="A74" s="68" t="inlineStr">
         <is>
           <t>PS5-08-81 - Guard tour</t>
         </is>
@@ -9586,7 +9346,7 @@
       <c r="AT74" s="67" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="53" t="inlineStr">
+      <c r="A75" s="68" t="inlineStr">
         <is>
           <t>PS5-08-82 - Key Management</t>
         </is>
@@ -9670,7 +9430,7 @@
       <c r="AT75" s="67" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="53" t="inlineStr">
+      <c r="A76" s="68" t="inlineStr">
         <is>
           <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
         </is>
@@ -9773,18 +9533,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP76" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP76" s="65" t="inlineStr"/>
       <c r="AQ76" s="65" t="inlineStr"/>
       <c r="AR76" s="23" t="inlineStr"/>
       <c r="AS76" s="23" t="n"/>
       <c r="AT76" s="67" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="53" t="inlineStr">
+      <c r="A77" s="68" t="inlineStr">
         <is>
           <t>PS5-08-85</t>
         </is>
@@ -9872,7 +9628,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM77" s="64" t="inlineStr">
+      <c r="AM77" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9887,18 +9643,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP77" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="AP77" s="65" t="inlineStr"/>
       <c r="AQ77" s="65" t="inlineStr"/>
       <c r="AR77" s="23" t="inlineStr"/>
       <c r="AS77" s="23" t="n"/>
       <c r="AT77" s="67" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="53" t="inlineStr">
+      <c r="A78" s="68" t="inlineStr">
         <is>
           <t>PS5-08-85a - Access Control, POB &amp; e-Mustering (Required for SU)</t>
         </is>
@@ -9982,7 +9734,7 @@
       <c r="AT78" s="67" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="53" t="inlineStr">
+      <c r="A79" s="68" t="inlineStr">
         <is>
           <t>PS5-08-85b - Access Control, POB &amp; e-Mustering (Not required for SU)</t>
         </is>
@@ -10066,7 +9818,7 @@
       <c r="AT79" s="67" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="53" t="inlineStr">
+      <c r="A80" s="68" t="inlineStr">
         <is>
           <t>PS5-08-86 - Integrated Security Management System</t>
         </is>
@@ -10150,7 +9902,7 @@
       <c r="AT80" s="67" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="53" t="inlineStr">
+      <c r="A81" s="68" t="inlineStr">
         <is>
           <t>PS5-08-92 - Telecom Mast</t>
         </is>
@@ -10234,7 +9986,7 @@
       <c r="AT81" s="67" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="53" t="inlineStr">
+      <c r="A82" s="68" t="inlineStr">
         <is>
           <t>PS5-08-93 - Telecom Monitoring System</t>
         </is>
@@ -10337,11 +10089,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP82" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP82" s="65" t="inlineStr"/>
       <c r="AQ82" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -10356,7 +10104,7 @@
       <c r="AT82" s="67" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="53" t="inlineStr">
+      <c r="A83" s="68" t="inlineStr">
         <is>
           <t>PS5-09-01 - HVAC for Office and Facilities building</t>
         </is>
@@ -10459,18 +10207,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP83" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP83" s="65" t="inlineStr"/>
       <c r="AQ83" s="65" t="inlineStr"/>
       <c r="AR83" s="23" t="inlineStr"/>
       <c r="AS83" s="23" t="n"/>
       <c r="AT83" s="67" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="53" t="inlineStr">
+      <c r="A84" s="68" t="inlineStr">
         <is>
           <t>PS5-09-02 - HVAC for Guard House</t>
         </is>
@@ -10573,18 +10317,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP84" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP84" s="65" t="inlineStr"/>
       <c r="AQ84" s="65" t="inlineStr"/>
       <c r="AR84" s="23" t="inlineStr"/>
       <c r="AS84" s="23" t="n"/>
       <c r="AT84" s="67" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="53" t="inlineStr">
+      <c r="A85" s="68" t="inlineStr">
         <is>
           <t>PS5-09-03 - HVAC for Generator Building</t>
         </is>
@@ -10622,7 +10362,7 @@
       <c r="H85" s="24" t="inlineStr"/>
       <c r="I85" s="70" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="J85" s="55" t="n">
@@ -10661,14 +10401,14 @@
         <v>1106</v>
       </c>
       <c r="AI85" s="23" t="n">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="AJ85" s="23" t="n">
-        <v>969</v>
+        <v>944</v>
       </c>
       <c r="AK85" s="25" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="AL85" s="64" t="inlineStr">
@@ -10691,26 +10431,22 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AP85" s="65" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+      <c r="AP85" s="65" t="inlineStr"/>
       <c r="AQ85" s="65" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>706</t>
         </is>
       </c>
       <c r="AR85" s="23" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>706</t>
         </is>
       </c>
       <c r="AS85" s="23" t="n"/>
       <c r="AT85" s="67" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="53" t="inlineStr">
+      <c r="A86" s="68" t="inlineStr">
         <is>
           <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
         </is>
@@ -10813,18 +10549,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP86" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP86" s="65" t="inlineStr"/>
       <c r="AQ86" s="65" t="inlineStr"/>
       <c r="AR86" s="23" t="inlineStr"/>
       <c r="AS86" s="23" t="n"/>
       <c r="AT86" s="67" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="68" t="inlineStr">
+      <c r="A87" s="53" t="inlineStr">
         <is>
           <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
@@ -10927,18 +10659,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP87" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP87" s="65" t="inlineStr"/>
       <c r="AQ87" s="65" t="inlineStr"/>
       <c r="AR87" s="23" t="inlineStr"/>
       <c r="AS87" s="23" t="n"/>
       <c r="AT87" s="67" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="53" t="inlineStr">
+      <c r="A88" s="68" t="inlineStr">
         <is>
           <t>PS5-0H-01 - HIPPS</t>
         </is>
@@ -10956,7 +10684,7 @@
       <c r="H88" s="24" t="inlineStr"/>
       <c r="I88" s="69" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="J88" s="55" t="n">
@@ -10995,14 +10723,14 @@
         <v>28</v>
       </c>
       <c r="AI88" s="23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AJ88" s="23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AK88" s="26" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="AL88" s="23" t="n">
@@ -11022,7 +10750,7 @@
       <c r="AT88" s="67" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="53" t="inlineStr">
+      <c r="A89" s="68" t="inlineStr">
         <is>
           <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
         </is>
@@ -11125,11 +10853,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AP89" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP89" s="65" t="inlineStr"/>
       <c r="AQ89" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -11144,7 +10868,7 @@
       <c r="AT89" s="67" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="53" t="inlineStr">
+      <c r="A90" s="68" t="inlineStr">
         <is>
           <t>PS5-25-02 - Crude Oil Export Pump A</t>
         </is>
@@ -11247,18 +10971,22 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP90" s="65" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AQ90" s="65" t="inlineStr"/>
-      <c r="AR90" s="23" t="inlineStr"/>
+      <c r="AP90" s="65" t="inlineStr"/>
+      <c r="AQ90" s="65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AR90" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="AS90" s="23" t="n"/>
       <c r="AT90" s="67" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="53" t="inlineStr">
+      <c r="A91" s="68" t="inlineStr">
         <is>
           <t>PS5-25-03 - Crude Oil Export Pump B</t>
         </is>
@@ -11361,18 +11089,22 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP91" s="65" t="inlineStr">
+      <c r="AP91" s="65" t="inlineStr"/>
+      <c r="AQ91" s="65" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AQ91" s="65" t="inlineStr"/>
-      <c r="AR91" s="23" t="inlineStr"/>
+      <c r="AR91" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AS91" s="23" t="n"/>
       <c r="AT91" s="67" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="53" t="inlineStr">
+      <c r="A92" s="68" t="inlineStr">
         <is>
           <t>PS5-25-04 - Crude Oil Export Pump C</t>
         </is>
@@ -11475,18 +11207,22 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP92" s="65" t="inlineStr">
+      <c r="AP92" s="65" t="inlineStr"/>
+      <c r="AQ92" s="65" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AQ92" s="65" t="inlineStr"/>
-      <c r="AR92" s="23" t="inlineStr"/>
+      <c r="AR92" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AS92" s="23" t="n"/>
       <c r="AT92" s="67" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="68" t="inlineStr">
+      <c r="A93" s="53" t="inlineStr">
         <is>
           <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
         </is>
@@ -11593,18 +11329,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP93" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP93" s="65" t="inlineStr"/>
       <c r="AQ93" s="65" t="inlineStr"/>
       <c r="AR93" s="23" t="inlineStr"/>
       <c r="AS93" s="23" t="n"/>
       <c r="AT93" s="67" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="53" t="inlineStr">
+      <c r="A94" s="68" t="inlineStr">
         <is>
           <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
         </is>
@@ -11707,11 +11439,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP94" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP94" s="65" t="inlineStr"/>
       <c r="AQ94" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -11726,7 +11454,7 @@
       <c r="AT94" s="67" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="53" t="inlineStr">
+      <c r="A95" s="68" t="inlineStr">
         <is>
           <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
         </is>
@@ -11829,18 +11557,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP95" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP95" s="65" t="inlineStr"/>
       <c r="AQ95" s="65" t="inlineStr"/>
       <c r="AR95" s="23" t="inlineStr"/>
       <c r="AS95" s="23" t="n"/>
       <c r="AT95" s="67" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="53" t="inlineStr">
+      <c r="A96" s="68" t="inlineStr">
         <is>
           <t>PS5-28-01 - Closed Drain Header 1</t>
         </is>
@@ -11947,11 +11671,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP96" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP96" s="65" t="inlineStr"/>
       <c r="AQ96" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -11966,7 +11686,7 @@
       <c r="AT96" s="67" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="68" t="inlineStr">
+      <c r="A97" s="53" t="inlineStr">
         <is>
           <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
@@ -12073,18 +11793,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP97" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP97" s="65" t="inlineStr"/>
       <c r="AQ97" s="65" t="inlineStr"/>
       <c r="AR97" s="23" t="inlineStr"/>
       <c r="AS97" s="23" t="n"/>
       <c r="AT97" s="67" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="53" t="inlineStr">
+      <c r="A98" s="68" t="inlineStr">
         <is>
           <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
         </is>
@@ -12195,18 +11911,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP98" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP98" s="65" t="inlineStr"/>
       <c r="AQ98" s="65" t="inlineStr"/>
       <c r="AR98" s="23" t="inlineStr"/>
       <c r="AS98" s="23" t="n"/>
       <c r="AT98" s="67" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="53" t="inlineStr">
+      <c r="A99" s="68" t="inlineStr">
         <is>
           <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
         </is>
@@ -12317,11 +12029,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP99" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP99" s="65" t="inlineStr"/>
       <c r="AQ99" s="65" t="inlineStr">
         <is>
           <t>4</t>
@@ -12336,7 +12044,7 @@
       <c r="AT99" s="67" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="68" t="inlineStr">
+      <c r="A100" s="53" t="inlineStr">
         <is>
           <t>PS5-28-05 - HP Relief Header</t>
         </is>
@@ -12447,18 +12155,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP100" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP100" s="65" t="inlineStr"/>
       <c r="AQ100" s="65" t="inlineStr"/>
       <c r="AR100" s="23" t="inlineStr"/>
       <c r="AS100" s="23" t="n"/>
       <c r="AT100" s="67" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="68" t="inlineStr">
+      <c r="A101" s="53" t="inlineStr">
         <is>
           <t>PS5-28-06 - Relief Drum and Pump</t>
         </is>
@@ -12569,18 +12273,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP101" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP101" s="65" t="inlineStr"/>
       <c r="AQ101" s="65" t="inlineStr"/>
       <c r="AR101" s="23" t="inlineStr"/>
       <c r="AS101" s="23" t="n"/>
       <c r="AT101" s="67" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="68" t="inlineStr">
+      <c r="A102" s="53" t="inlineStr">
         <is>
           <t>PS5-28-07 - Open Drains (OD2)</t>
         </is>
@@ -12687,11 +12387,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP102" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP102" s="65" t="inlineStr"/>
       <c r="AQ102" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -12817,11 +12513,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP103" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP103" s="65" t="inlineStr"/>
       <c r="AQ103" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -12836,7 +12528,7 @@
       <c r="AT103" s="67" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="53" t="inlineStr">
+      <c r="A104" s="68" t="inlineStr">
         <is>
           <t>PS5-28-09 - Observation Basin</t>
         </is>
@@ -12939,11 +12631,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP104" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP104" s="65" t="inlineStr"/>
       <c r="AQ104" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -12958,7 +12646,7 @@
       <c r="AT104" s="67" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="53" t="inlineStr">
+      <c r="A105" s="68" t="inlineStr">
         <is>
           <t>PS5-28-10 - Oil Skimmer Package</t>
         </is>
@@ -13061,11 +12749,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP105" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP105" s="65" t="inlineStr"/>
       <c r="AQ105" s="65" t="inlineStr">
         <is>
           <t>7</t>
@@ -13080,7 +12764,7 @@
       <c r="AT105" s="67" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="68" t="inlineStr">
+      <c r="A106" s="53" t="inlineStr">
         <is>
           <t>PS5-28-11 - Open Drain Interceptor</t>
         </is>
@@ -13191,18 +12875,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP106" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP106" s="65" t="inlineStr"/>
       <c r="AQ106" s="65" t="inlineStr"/>
       <c r="AR106" s="23" t="inlineStr"/>
       <c r="AS106" s="23" t="n"/>
       <c r="AT106" s="67" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="68" t="inlineStr">
+      <c r="A107" s="53" t="inlineStr">
         <is>
           <t>PS5-28-12 - Open Drains (OD3)</t>
         </is>
@@ -13309,18 +12989,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP107" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP107" s="65" t="inlineStr"/>
       <c r="AQ107" s="65" t="inlineStr"/>
       <c r="AR107" s="23" t="inlineStr"/>
       <c r="AS107" s="23" t="n"/>
       <c r="AT107" s="67" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="53" t="inlineStr">
+      <c r="A108" s="68" t="inlineStr">
         <is>
           <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
         </is>
@@ -13345,11 +13021,7 @@
           <t>2026-10-15 00:00:00</t>
         </is>
       </c>
-      <c r="F108" s="23" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
+      <c r="F108" s="23" t="inlineStr"/>
       <c r="G108" s="28" t="inlineStr">
         <is>
           <t>FULL</t>
@@ -13431,18 +13103,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP108" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP108" s="65" t="inlineStr"/>
       <c r="AQ108" s="65" t="inlineStr"/>
       <c r="AR108" s="23" t="inlineStr"/>
       <c r="AS108" s="23" t="n"/>
       <c r="AT108" s="67" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="53" t="inlineStr">
+      <c r="A109" s="68" t="inlineStr">
         <is>
           <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
         </is>
@@ -13553,18 +13221,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP109" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP109" s="65" t="inlineStr"/>
       <c r="AQ109" s="65" t="inlineStr"/>
       <c r="AR109" s="23" t="inlineStr"/>
       <c r="AS109" s="23" t="n"/>
       <c r="AT109" s="67" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="53" t="inlineStr">
+      <c r="A110" s="68" t="inlineStr">
         <is>
           <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
         </is>
@@ -13671,18 +13335,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP110" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP110" s="65" t="inlineStr"/>
       <c r="AQ110" s="65" t="inlineStr"/>
       <c r="AR110" s="23" t="inlineStr"/>
       <c r="AS110" s="23" t="n"/>
       <c r="AT110" s="67" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="68" t="inlineStr">
+      <c r="A111" s="53" t="inlineStr">
         <is>
           <t>PS5-28-16 - LP Relief Header</t>
         </is>
@@ -13789,18 +13449,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP111" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP111" s="65" t="inlineStr"/>
       <c r="AQ111" s="65" t="inlineStr"/>
       <c r="AR111" s="23" t="inlineStr"/>
       <c r="AS111" s="23" t="n"/>
       <c r="AT111" s="67" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="53" t="inlineStr">
+      <c r="A112" s="68" t="inlineStr">
         <is>
           <t>PS5-28-17 - Reinjection Pump</t>
         </is>
@@ -13907,18 +13563,22 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP112" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ112" s="65" t="inlineStr"/>
-      <c r="AR112" s="23" t="inlineStr"/>
+      <c r="AP112" s="65" t="inlineStr"/>
+      <c r="AQ112" s="65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AR112" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="AS112" s="23" t="n"/>
       <c r="AT112" s="67" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="53" t="inlineStr">
+      <c r="A113" s="68" t="inlineStr">
         <is>
           <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
         </is>
@@ -14021,11 +13681,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP113" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP113" s="65" t="inlineStr"/>
       <c r="AQ113" s="65" t="inlineStr">
         <is>
           <t>11</t>
@@ -14040,7 +13696,7 @@
       <c r="AT113" s="67" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="53" t="inlineStr">
+      <c r="A114" s="68" t="inlineStr">
         <is>
           <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
         </is>
@@ -14143,11 +13799,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP114" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP114" s="65" t="inlineStr"/>
       <c r="AQ114" s="65" t="inlineStr">
         <is>
           <t>11</t>
@@ -14162,7 +13814,7 @@
       <c r="AT114" s="67" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="53" t="inlineStr">
+      <c r="A115" s="68" t="inlineStr">
         <is>
           <t>PS5-50-03 - Water Pre-Treatment Package</t>
         </is>
@@ -14269,11 +13921,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP115" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP115" s="65" t="inlineStr"/>
       <c r="AQ115" s="65" t="inlineStr">
         <is>
           <t>5</t>
@@ -14399,11 +14047,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP116" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP116" s="65" t="inlineStr"/>
       <c r="AQ116" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -14418,7 +14062,7 @@
       <c r="AT116" s="67" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="68" t="inlineStr">
+      <c r="A117" s="53" t="inlineStr">
         <is>
           <t>PS5-53-02 - Water Distribution Pump A/B</t>
         </is>
@@ -14529,18 +14173,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP117" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP117" s="65" t="inlineStr"/>
       <c r="AQ117" s="65" t="inlineStr"/>
       <c r="AR117" s="23" t="inlineStr"/>
       <c r="AS117" s="23" t="n"/>
       <c r="AT117" s="67" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="53" t="inlineStr">
+      <c r="A118" s="68" t="inlineStr">
         <is>
           <t>PS5-53-03 - Water Softener Package</t>
         </is>
@@ -14651,11 +14291,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP118" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP118" s="65" t="inlineStr"/>
       <c r="AQ118" s="65" t="inlineStr">
         <is>
           <t>3</t>
@@ -14670,7 +14306,7 @@
       <c r="AT118" s="67" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="53" t="inlineStr">
+      <c r="A119" s="68" t="inlineStr">
         <is>
           <t>PS5-53-04 - Water Treatment Purification Package</t>
         </is>
@@ -14777,11 +14413,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP119" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP119" s="65" t="inlineStr"/>
       <c r="AQ119" s="65" t="inlineStr">
         <is>
           <t>4</t>
@@ -14796,7 +14428,7 @@
       <c r="AT119" s="67" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="68" t="inlineStr">
+      <c r="A120" s="53" t="inlineStr">
         <is>
           <t>PS5-53-05 - Water Distribution Header</t>
         </is>
@@ -14907,18 +14539,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP120" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP120" s="65" t="inlineStr"/>
       <c r="AQ120" s="65" t="inlineStr"/>
       <c r="AR120" s="23" t="inlineStr"/>
       <c r="AS120" s="23" t="n"/>
       <c r="AT120" s="67" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="53" t="inlineStr">
+      <c r="A121" s="68" t="inlineStr">
         <is>
           <t>PS5-53-06 - Water Distribution Consumers</t>
         </is>
@@ -15025,18 +14653,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP121" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP121" s="65" t="inlineStr"/>
       <c r="AQ121" s="65" t="inlineStr"/>
       <c r="AR121" s="23" t="inlineStr"/>
       <c r="AS121" s="23" t="n"/>
       <c r="AT121" s="67" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="68" t="inlineStr">
+      <c r="A122" s="53" t="inlineStr">
         <is>
           <t>PS5-60-01 - Power Generation Package A</t>
         </is>
@@ -15147,18 +14771,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP122" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP122" s="65" t="inlineStr"/>
       <c r="AQ122" s="65" t="inlineStr"/>
       <c r="AR122" s="23" t="inlineStr"/>
       <c r="AS122" s="23" t="n"/>
       <c r="AT122" s="67" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="68" t="inlineStr">
+      <c r="A123" s="53" t="inlineStr">
         <is>
           <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
@@ -15269,11 +14889,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP123" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP123" s="65" t="inlineStr"/>
       <c r="AQ123" s="65" t="inlineStr"/>
       <c r="AR123" s="23" t="inlineStr">
         <is>
@@ -15284,7 +14900,7 @@
       <c r="AT123" s="67" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="68" t="inlineStr">
+      <c r="A124" s="53" t="inlineStr">
         <is>
           <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -15395,18 +15011,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP124" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP124" s="65" t="inlineStr"/>
       <c r="AQ124" s="65" t="inlineStr"/>
       <c r="AR124" s="23" t="inlineStr"/>
       <c r="AS124" s="23" t="n"/>
       <c r="AT124" s="67" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="68" t="inlineStr">
+      <c r="A125" s="53" t="inlineStr">
         <is>
           <t>PS5-60-04 - Power Generation Package B</t>
         </is>
@@ -15517,18 +15129,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP125" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP125" s="65" t="inlineStr"/>
       <c r="AQ125" s="65" t="inlineStr"/>
       <c r="AR125" s="23" t="inlineStr"/>
       <c r="AS125" s="23" t="n"/>
       <c r="AT125" s="67" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="68" t="inlineStr">
+      <c r="A126" s="53" t="inlineStr">
         <is>
           <t>PS5-60-05 - Power Gen Package B (UCP)</t>
         </is>
@@ -15639,18 +15247,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP126" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP126" s="65" t="inlineStr"/>
       <c r="AQ126" s="65" t="inlineStr"/>
       <c r="AR126" s="23" t="inlineStr"/>
       <c r="AS126" s="23" t="n"/>
       <c r="AT126" s="67" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="68" t="inlineStr">
+      <c r="A127" s="53" t="inlineStr">
         <is>
           <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -15761,18 +15365,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP127" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP127" s="65" t="inlineStr"/>
       <c r="AQ127" s="65" t="inlineStr"/>
       <c r="AR127" s="23" t="inlineStr"/>
       <c r="AS127" s="23" t="n"/>
       <c r="AT127" s="67" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="53" t="inlineStr">
+      <c r="A128" s="68" t="inlineStr">
         <is>
           <t>PS5-60-07 - Power Generation Package C</t>
         </is>
@@ -15883,18 +15483,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP128" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP128" s="65" t="inlineStr"/>
       <c r="AQ128" s="65" t="inlineStr"/>
       <c r="AR128" s="23" t="inlineStr"/>
       <c r="AS128" s="23" t="n"/>
       <c r="AT128" s="67" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="68" t="inlineStr">
+      <c r="A129" s="53" t="inlineStr">
         <is>
           <t>PS5-60-08 - Power Gen Package C (UCP)</t>
         </is>
@@ -16005,18 +15601,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP129" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP129" s="65" t="inlineStr"/>
       <c r="AQ129" s="65" t="inlineStr"/>
       <c r="AR129" s="23" t="inlineStr"/>
       <c r="AS129" s="23" t="n"/>
       <c r="AT129" s="67" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="68" t="inlineStr">
+      <c r="A130" s="53" t="inlineStr">
         <is>
           <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -16127,18 +15719,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP130" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP130" s="65" t="inlineStr"/>
       <c r="AQ130" s="65" t="inlineStr"/>
       <c r="AR130" s="23" t="inlineStr"/>
       <c r="AS130" s="23" t="n"/>
       <c r="AT130" s="67" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="53" t="inlineStr">
+      <c r="A131" s="68" t="inlineStr">
         <is>
           <t>PS5-60-10 - Power Generation Package D</t>
         </is>
@@ -16249,18 +15837,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP131" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP131" s="65" t="inlineStr"/>
       <c r="AQ131" s="65" t="inlineStr"/>
       <c r="AR131" s="23" t="inlineStr"/>
       <c r="AS131" s="23" t="n"/>
       <c r="AT131" s="67" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="68" t="inlineStr">
+      <c r="A132" s="53" t="inlineStr">
         <is>
           <t>PS5-60-11 - Power Gen Package D (UCP)</t>
         </is>
@@ -16371,18 +15955,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP132" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP132" s="65" t="inlineStr"/>
       <c r="AQ132" s="65" t="inlineStr"/>
       <c r="AR132" s="23" t="inlineStr"/>
       <c r="AS132" s="23" t="n"/>
       <c r="AT132" s="67" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="68" t="inlineStr">
+      <c r="A133" s="53" t="inlineStr">
         <is>
           <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -16493,18 +16073,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP133" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP133" s="65" t="inlineStr"/>
       <c r="AQ133" s="65" t="inlineStr"/>
       <c r="AR133" s="23" t="inlineStr"/>
       <c r="AS133" s="23" t="n"/>
       <c r="AT133" s="67" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="68" t="inlineStr">
+      <c r="A134" s="53" t="inlineStr">
         <is>
           <t>PS5-60-13 - Power Generation Package E</t>
         </is>
@@ -16615,18 +16191,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP134" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP134" s="65" t="inlineStr"/>
       <c r="AQ134" s="65" t="inlineStr"/>
       <c r="AR134" s="23" t="inlineStr"/>
       <c r="AS134" s="23" t="n"/>
       <c r="AT134" s="67" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="68" t="inlineStr">
+      <c r="A135" s="53" t="inlineStr">
         <is>
           <t>PS5-60-14 - Power Gen Package E (UCP)</t>
         </is>
@@ -16737,18 +16309,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP135" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP135" s="65" t="inlineStr"/>
       <c r="AQ135" s="65" t="inlineStr"/>
       <c r="AR135" s="23" t="inlineStr"/>
       <c r="AS135" s="23" t="n"/>
       <c r="AT135" s="67" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="68" t="inlineStr">
+      <c r="A136" s="53" t="inlineStr">
         <is>
           <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -16859,18 +16427,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP136" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP136" s="65" t="inlineStr"/>
       <c r="AQ136" s="65" t="inlineStr"/>
       <c r="AR136" s="23" t="inlineStr"/>
       <c r="AS136" s="23" t="n"/>
       <c r="AT136" s="67" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="53" t="inlineStr">
+      <c r="A137" s="68" t="inlineStr">
         <is>
           <t>PS5-60-16 - Power Generation Package F</t>
         </is>
@@ -16981,18 +16545,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP137" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP137" s="65" t="inlineStr"/>
       <c r="AQ137" s="65" t="inlineStr"/>
       <c r="AR137" s="23" t="inlineStr"/>
       <c r="AS137" s="23" t="n"/>
       <c r="AT137" s="67" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="68" t="inlineStr">
+      <c r="A138" s="53" t="inlineStr">
         <is>
           <t>PS5-60-17 - Power Gen Package F (UCP)</t>
         </is>
@@ -17103,18 +16663,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP138" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP138" s="65" t="inlineStr"/>
       <c r="AQ138" s="65" t="inlineStr"/>
       <c r="AR138" s="23" t="inlineStr"/>
       <c r="AS138" s="23" t="n"/>
       <c r="AT138" s="67" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="68" t="inlineStr">
+      <c r="A139" s="53" t="inlineStr">
         <is>
           <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -17225,18 +16781,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP139" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP139" s="65" t="inlineStr"/>
       <c r="AQ139" s="65" t="inlineStr"/>
       <c r="AR139" s="23" t="inlineStr"/>
       <c r="AS139" s="23" t="n"/>
       <c r="AT139" s="67" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="53" t="inlineStr">
+      <c r="A140" s="68" t="inlineStr">
         <is>
           <t>PS5-60-19 - Power Generation Package G</t>
         </is>
@@ -17347,18 +16899,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP140" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP140" s="65" t="inlineStr"/>
       <c r="AQ140" s="65" t="inlineStr"/>
       <c r="AR140" s="23" t="inlineStr"/>
       <c r="AS140" s="23" t="n"/>
       <c r="AT140" s="67" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="68" t="inlineStr">
+      <c r="A141" s="53" t="inlineStr">
         <is>
           <t>PS5-60-20 - Power Gen Package G (UCP)</t>
         </is>
@@ -17469,18 +17017,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP141" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP141" s="65" t="inlineStr"/>
       <c r="AQ141" s="65" t="inlineStr"/>
       <c r="AR141" s="23" t="inlineStr"/>
       <c r="AS141" s="23" t="n"/>
       <c r="AT141" s="67" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="68" t="inlineStr">
+      <c r="A142" s="53" t="inlineStr">
         <is>
           <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -17591,18 +17135,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP142" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP142" s="65" t="inlineStr"/>
       <c r="AQ142" s="65" t="inlineStr"/>
       <c r="AR142" s="23" t="inlineStr"/>
       <c r="AS142" s="23" t="n"/>
       <c r="AT142" s="67" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="53" t="inlineStr">
+      <c r="A143" s="68" t="inlineStr">
         <is>
           <t>PS5-60-22 - Power Gen Master UCP</t>
         </is>
@@ -17732,7 +17272,7 @@
       <c r="AT143" s="67" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="68" t="inlineStr">
+      <c r="A144" s="53" t="inlineStr">
         <is>
           <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
@@ -17839,18 +17379,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP144" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP144" s="65" t="inlineStr"/>
       <c r="AQ144" s="65" t="inlineStr"/>
       <c r="AR144" s="23" t="inlineStr"/>
       <c r="AS144" s="23" t="n"/>
       <c r="AT144" s="67" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="53" t="inlineStr">
+      <c r="A145" s="68" t="inlineStr">
         <is>
           <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
         </is>
@@ -17961,18 +17497,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP145" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="AP145" s="65" t="inlineStr"/>
       <c r="AQ145" s="65" t="inlineStr"/>
       <c r="AR145" s="23" t="inlineStr"/>
       <c r="AS145" s="23" t="n"/>
       <c r="AT145" s="67" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="53" t="inlineStr">
+      <c r="A146" s="68" t="inlineStr">
         <is>
           <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
         </is>
@@ -18083,18 +17615,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP146" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="AP146" s="65" t="inlineStr"/>
       <c r="AQ146" s="65" t="inlineStr"/>
       <c r="AR146" s="23" t="inlineStr"/>
       <c r="AS146" s="23" t="n"/>
       <c r="AT146" s="67" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="68" t="inlineStr">
+      <c r="A147" s="53" t="inlineStr">
         <is>
           <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
@@ -18205,18 +17733,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP147" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP147" s="65" t="inlineStr"/>
       <c r="AQ147" s="65" t="inlineStr"/>
       <c r="AR147" s="23" t="inlineStr"/>
       <c r="AS147" s="23" t="n"/>
       <c r="AT147" s="67" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="68" t="inlineStr">
+      <c r="A148" s="53" t="inlineStr">
         <is>
           <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
@@ -18327,11 +17851,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP148" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP148" s="65" t="inlineStr"/>
       <c r="AQ148" s="65" t="inlineStr"/>
       <c r="AR148" s="23" t="inlineStr"/>
       <c r="AS148" s="23" t="n"/>
@@ -18449,18 +17969,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP149" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP149" s="65" t="inlineStr"/>
       <c r="AQ149" s="65" t="inlineStr"/>
       <c r="AR149" s="23" t="inlineStr"/>
       <c r="AS149" s="23" t="n"/>
       <c r="AT149" s="67" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="68" t="inlineStr">
+      <c r="A150" s="53" t="inlineStr">
         <is>
           <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
@@ -18571,18 +18087,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP150" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP150" s="65" t="inlineStr"/>
       <c r="AQ150" s="65" t="inlineStr"/>
       <c r="AR150" s="23" t="inlineStr"/>
       <c r="AS150" s="23" t="n"/>
       <c r="AT150" s="67" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="68" t="inlineStr">
+      <c r="A151" s="53" t="inlineStr">
         <is>
           <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
@@ -18693,18 +18205,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP151" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP151" s="65" t="inlineStr"/>
       <c r="AQ151" s="65" t="inlineStr"/>
       <c r="AR151" s="23" t="inlineStr"/>
       <c r="AS151" s="23" t="n"/>
       <c r="AT151" s="67" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="68" t="inlineStr">
+      <c r="A152" s="53" t="inlineStr">
         <is>
           <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
@@ -18815,18 +18323,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP152" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP152" s="65" t="inlineStr"/>
       <c r="AQ152" s="65" t="inlineStr"/>
       <c r="AR152" s="23" t="inlineStr"/>
       <c r="AS152" s="23" t="n"/>
       <c r="AT152" s="67" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="68" t="inlineStr">
+      <c r="A153" s="53" t="inlineStr">
         <is>
           <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
@@ -18937,18 +18441,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP153" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP153" s="65" t="inlineStr"/>
       <c r="AQ153" s="65" t="inlineStr"/>
       <c r="AR153" s="23" t="inlineStr"/>
       <c r="AS153" s="23" t="n"/>
       <c r="AT153" s="67" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="68" t="inlineStr">
+      <c r="A154" s="53" t="inlineStr">
         <is>
           <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
@@ -19059,18 +18559,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP154" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP154" s="65" t="inlineStr"/>
       <c r="AQ154" s="65" t="inlineStr"/>
       <c r="AR154" s="23" t="inlineStr"/>
       <c r="AS154" s="23" t="n"/>
       <c r="AT154" s="67" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="68" t="inlineStr">
+      <c r="A155" s="53" t="inlineStr">
         <is>
           <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
@@ -19181,11 +18677,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP155" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP155" s="65" t="inlineStr"/>
       <c r="AQ155" s="65" t="inlineStr"/>
       <c r="AR155" s="23" t="inlineStr"/>
       <c r="AS155" s="23" t="n"/>
@@ -19299,18 +18791,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP156" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP156" s="65" t="inlineStr"/>
       <c r="AQ156" s="65" t="inlineStr"/>
       <c r="AR156" s="23" t="inlineStr"/>
       <c r="AS156" s="23" t="n"/>
       <c r="AT156" s="67" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="68" t="inlineStr">
+      <c r="A157" s="53" t="inlineStr">
         <is>
           <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
@@ -19417,18 +18905,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP157" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP157" s="65" t="inlineStr"/>
       <c r="AQ157" s="65" t="inlineStr"/>
       <c r="AR157" s="23" t="inlineStr"/>
       <c r="AS157" s="23" t="n"/>
       <c r="AT157" s="67" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="68" t="inlineStr">
+      <c r="A158" s="53" t="inlineStr">
         <is>
           <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
@@ -19539,18 +19023,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP158" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP158" s="65" t="inlineStr"/>
       <c r="AQ158" s="65" t="inlineStr"/>
       <c r="AR158" s="23" t="inlineStr"/>
       <c r="AS158" s="23" t="n"/>
       <c r="AT158" s="67" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="68" t="inlineStr">
+      <c r="A159" s="53" t="inlineStr">
         <is>
           <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
@@ -19661,18 +19141,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP159" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP159" s="65" t="inlineStr"/>
       <c r="AQ159" s="65" t="inlineStr"/>
       <c r="AR159" s="23" t="inlineStr"/>
       <c r="AS159" s="23" t="n"/>
       <c r="AT159" s="67" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="68" t="inlineStr">
+      <c r="A160" s="53" t="inlineStr">
         <is>
           <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
@@ -19783,18 +19259,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP160" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP160" s="65" t="inlineStr"/>
       <c r="AQ160" s="65" t="inlineStr"/>
       <c r="AR160" s="23" t="inlineStr"/>
       <c r="AS160" s="23" t="n"/>
       <c r="AT160" s="67" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="68" t="inlineStr">
+      <c r="A161" s="53" t="inlineStr">
         <is>
           <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
@@ -19905,18 +19377,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP161" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP161" s="65" t="inlineStr"/>
       <c r="AQ161" s="65" t="inlineStr"/>
       <c r="AR161" s="23" t="inlineStr"/>
       <c r="AS161" s="23" t="n"/>
       <c r="AT161" s="67" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="68" t="inlineStr">
+      <c r="A162" s="53" t="inlineStr">
         <is>
           <t>PS5-60-41 - Injector Tip Cooling Module G</t>
         </is>
@@ -20027,11 +19495,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP162" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP162" s="65" t="inlineStr"/>
       <c r="AQ162" s="65" t="inlineStr"/>
       <c r="AR162" s="23" t="inlineStr"/>
       <c r="AS162" s="23" t="n"/>
@@ -20145,18 +19609,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP163" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP163" s="65" t="inlineStr"/>
       <c r="AQ163" s="65" t="inlineStr"/>
       <c r="AR163" s="23" t="inlineStr"/>
       <c r="AS163" s="23" t="n"/>
       <c r="AT163" s="67" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="68" t="inlineStr">
+      <c r="A164" s="53" t="inlineStr">
         <is>
           <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
@@ -20263,18 +19723,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP164" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP164" s="65" t="inlineStr"/>
       <c r="AQ164" s="65" t="inlineStr"/>
       <c r="AR164" s="23" t="inlineStr"/>
       <c r="AS164" s="23" t="n"/>
       <c r="AT164" s="67" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="68" t="inlineStr">
+      <c r="A165" s="53" t="inlineStr">
         <is>
           <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
@@ -20385,18 +19841,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP165" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP165" s="65" t="inlineStr"/>
       <c r="AQ165" s="65" t="inlineStr"/>
       <c r="AR165" s="23" t="inlineStr"/>
       <c r="AS165" s="23" t="n"/>
       <c r="AT165" s="67" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="68" t="inlineStr">
+      <c r="A166" s="53" t="inlineStr">
         <is>
           <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
@@ -20507,18 +19959,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP166" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP166" s="65" t="inlineStr"/>
       <c r="AQ166" s="65" t="inlineStr"/>
       <c r="AR166" s="23" t="inlineStr"/>
       <c r="AS166" s="23" t="n"/>
       <c r="AT166" s="67" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="68" t="inlineStr">
+      <c r="A167" s="53" t="inlineStr">
         <is>
           <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
@@ -20629,18 +20077,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP167" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP167" s="65" t="inlineStr"/>
       <c r="AQ167" s="65" t="inlineStr"/>
       <c r="AR167" s="23" t="inlineStr"/>
       <c r="AS167" s="23" t="n"/>
       <c r="AT167" s="67" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="68" t="inlineStr">
+      <c r="A168" s="53" t="inlineStr">
         <is>
           <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
@@ -20751,11 +20195,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP168" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP168" s="65" t="inlineStr"/>
       <c r="AQ168" s="65" t="inlineStr"/>
       <c r="AR168" s="23" t="inlineStr"/>
       <c r="AS168" s="23" t="n"/>
@@ -20873,18 +20313,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP169" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP169" s="65" t="inlineStr"/>
       <c r="AQ169" s="65" t="inlineStr"/>
       <c r="AR169" s="23" t="inlineStr"/>
       <c r="AS169" s="23" t="n"/>
       <c r="AT169" s="67" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="68" t="inlineStr">
+      <c r="A170" s="53" t="inlineStr">
         <is>
           <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
         </is>
@@ -20995,11 +20431,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP170" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP170" s="65" t="inlineStr"/>
       <c r="AQ170" s="65" t="inlineStr"/>
       <c r="AR170" s="23" t="inlineStr">
         <is>
@@ -21010,7 +20442,7 @@
       <c r="AT170" s="67" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="68" t="inlineStr">
+      <c r="A171" s="53" t="inlineStr">
         <is>
           <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
         </is>
@@ -21121,18 +20553,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP171" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP171" s="65" t="inlineStr"/>
       <c r="AQ171" s="65" t="inlineStr"/>
       <c r="AR171" s="23" t="inlineStr"/>
       <c r="AS171" s="23" t="n"/>
       <c r="AT171" s="67" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="68" t="inlineStr">
+      <c r="A172" s="53" t="inlineStr">
         <is>
           <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
         </is>
@@ -21243,18 +20671,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP172" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP172" s="65" t="inlineStr"/>
       <c r="AQ172" s="65" t="inlineStr"/>
       <c r="AR172" s="23" t="inlineStr"/>
       <c r="AS172" s="23" t="n"/>
       <c r="AT172" s="67" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="68" t="inlineStr">
+      <c r="A173" s="53" t="inlineStr">
         <is>
           <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
         </is>
@@ -21365,18 +20789,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP173" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP173" s="65" t="inlineStr"/>
       <c r="AQ173" s="65" t="inlineStr"/>
       <c r="AR173" s="23" t="inlineStr"/>
       <c r="AS173" s="23" t="n"/>
       <c r="AT173" s="67" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="68" t="inlineStr">
+      <c r="A174" s="53" t="inlineStr">
         <is>
           <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
         </is>
@@ -21487,18 +20907,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP174" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP174" s="65" t="inlineStr"/>
       <c r="AQ174" s="65" t="inlineStr"/>
       <c r="AR174" s="23" t="inlineStr"/>
       <c r="AS174" s="23" t="n"/>
       <c r="AT174" s="67" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="68" t="inlineStr">
+      <c r="A175" s="53" t="inlineStr">
         <is>
           <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
         </is>
@@ -21609,18 +21025,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP175" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP175" s="65" t="inlineStr"/>
       <c r="AQ175" s="65" t="inlineStr"/>
       <c r="AR175" s="23" t="inlineStr"/>
       <c r="AS175" s="23" t="n"/>
       <c r="AT175" s="67" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="68" t="inlineStr">
+      <c r="A176" s="53" t="inlineStr">
         <is>
           <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
         </is>
@@ -21731,18 +21143,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP176" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP176" s="65" t="inlineStr"/>
       <c r="AQ176" s="65" t="inlineStr"/>
       <c r="AR176" s="23" t="inlineStr"/>
       <c r="AS176" s="23" t="n"/>
       <c r="AT176" s="67" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="68" t="inlineStr">
+      <c r="A177" s="53" t="inlineStr">
         <is>
           <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
@@ -21853,18 +21261,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP177" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP177" s="65" t="inlineStr"/>
       <c r="AQ177" s="65" t="inlineStr"/>
       <c r="AR177" s="23" t="inlineStr"/>
       <c r="AS177" s="23" t="n"/>
       <c r="AT177" s="67" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="68" t="inlineStr">
+      <c r="A178" s="53" t="inlineStr">
         <is>
           <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
         </is>
@@ -21975,18 +21379,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP178" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP178" s="65" t="inlineStr"/>
       <c r="AQ178" s="65" t="inlineStr"/>
       <c r="AR178" s="23" t="inlineStr"/>
       <c r="AS178" s="23" t="n"/>
       <c r="AT178" s="67" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="68" t="inlineStr">
+      <c r="A179" s="53" t="inlineStr">
         <is>
           <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
@@ -22097,18 +21497,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP179" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP179" s="65" t="inlineStr"/>
       <c r="AQ179" s="65" t="inlineStr"/>
       <c r="AR179" s="23" t="inlineStr"/>
       <c r="AS179" s="23" t="n"/>
       <c r="AT179" s="67" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="68" t="inlineStr">
+      <c r="A180" s="53" t="inlineStr">
         <is>
           <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
         </is>
@@ -22219,18 +21615,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP180" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP180" s="65" t="inlineStr"/>
       <c r="AQ180" s="65" t="inlineStr"/>
       <c r="AR180" s="23" t="inlineStr"/>
       <c r="AS180" s="23" t="n"/>
       <c r="AT180" s="67" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="68" t="inlineStr">
+      <c r="A181" s="53" t="inlineStr">
         <is>
           <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
@@ -22341,18 +21733,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP181" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP181" s="65" t="inlineStr"/>
       <c r="AQ181" s="65" t="inlineStr"/>
       <c r="AR181" s="23" t="inlineStr"/>
       <c r="AS181" s="23" t="n"/>
       <c r="AT181" s="67" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="68" t="inlineStr">
+      <c r="A182" s="53" t="inlineStr">
         <is>
           <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
         </is>
@@ -22463,18 +21851,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP182" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP182" s="65" t="inlineStr"/>
       <c r="AQ182" s="65" t="inlineStr"/>
       <c r="AR182" s="23" t="inlineStr"/>
       <c r="AS182" s="23" t="n"/>
       <c r="AT182" s="67" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="68" t="inlineStr">
+      <c r="A183" s="53" t="inlineStr">
         <is>
           <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
@@ -22585,18 +21969,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP183" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP183" s="65" t="inlineStr"/>
       <c r="AQ183" s="65" t="inlineStr"/>
       <c r="AR183" s="23" t="inlineStr"/>
       <c r="AS183" s="23" t="n"/>
       <c r="AT183" s="67" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="68" t="inlineStr">
+      <c r="A184" s="53" t="inlineStr">
         <is>
           <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
         </is>
@@ -22707,18 +22087,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP184" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP184" s="65" t="inlineStr"/>
       <c r="AQ184" s="65" t="inlineStr"/>
       <c r="AR184" s="23" t="inlineStr"/>
       <c r="AS184" s="23" t="n"/>
       <c r="AT184" s="67" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="53" t="inlineStr">
+      <c r="A185" s="68" t="inlineStr">
         <is>
           <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
         </is>
@@ -22829,18 +22205,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP185" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP185" s="65" t="inlineStr"/>
       <c r="AQ185" s="65" t="inlineStr"/>
       <c r="AR185" s="23" t="inlineStr"/>
       <c r="AS185" s="23" t="n"/>
       <c r="AT185" s="67" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="68" t="inlineStr">
+      <c r="A186" s="53" t="inlineStr">
         <is>
           <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
         </is>
@@ -22951,18 +22323,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP186" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP186" s="65" t="inlineStr"/>
       <c r="AQ186" s="65" t="inlineStr"/>
       <c r="AR186" s="23" t="inlineStr"/>
       <c r="AS186" s="23" t="n"/>
       <c r="AT186" s="67" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="53" t="inlineStr">
+      <c r="A187" s="68" t="inlineStr">
         <is>
           <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
         </is>
@@ -23073,18 +22441,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP187" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP187" s="65" t="inlineStr"/>
       <c r="AQ187" s="65" t="inlineStr"/>
       <c r="AR187" s="23" t="inlineStr"/>
       <c r="AS187" s="23" t="n"/>
       <c r="AT187" s="67" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="68" t="inlineStr">
+      <c r="A188" s="53" t="inlineStr">
         <is>
           <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
         </is>
@@ -23195,11 +22559,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP188" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP188" s="65" t="inlineStr"/>
       <c r="AQ188" s="65" t="inlineStr"/>
       <c r="AR188" s="23" t="inlineStr"/>
       <c r="AS188" s="23" t="n"/>
@@ -23317,18 +22677,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP189" s="65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="AP189" s="65" t="inlineStr"/>
       <c r="AQ189" s="65" t="inlineStr"/>
       <c r="AR189" s="23" t="inlineStr"/>
       <c r="AS189" s="23" t="n"/>
       <c r="AT189" s="67" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="68" t="inlineStr">
+      <c r="A190" s="53" t="inlineStr">
         <is>
           <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
         </is>
@@ -23439,18 +22795,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP190" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP190" s="65" t="inlineStr"/>
       <c r="AQ190" s="65" t="inlineStr"/>
       <c r="AR190" s="23" t="inlineStr"/>
       <c r="AS190" s="23" t="n"/>
       <c r="AT190" s="67" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="68" t="inlineStr">
+      <c r="A191" s="53" t="inlineStr">
         <is>
           <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
@@ -23561,18 +22913,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP191" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP191" s="65" t="inlineStr"/>
       <c r="AQ191" s="65" t="inlineStr"/>
       <c r="AR191" s="23" t="inlineStr"/>
       <c r="AS191" s="23" t="n"/>
       <c r="AT191" s="67" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="68" t="inlineStr">
+      <c r="A192" s="53" t="inlineStr">
         <is>
           <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
@@ -23683,18 +23031,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP192" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP192" s="65" t="inlineStr"/>
       <c r="AQ192" s="65" t="inlineStr"/>
       <c r="AR192" s="23" t="inlineStr"/>
       <c r="AS192" s="23" t="n"/>
       <c r="AT192" s="67" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="68" t="inlineStr">
+      <c r="A193" s="53" t="inlineStr">
         <is>
           <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
@@ -23805,18 +23149,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP193" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP193" s="65" t="inlineStr"/>
       <c r="AQ193" s="65" t="inlineStr"/>
       <c r="AR193" s="23" t="inlineStr"/>
       <c r="AS193" s="23" t="n"/>
       <c r="AT193" s="67" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="68" t="inlineStr">
+      <c r="A194" s="53" t="inlineStr">
         <is>
           <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
@@ -23927,18 +23267,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP194" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP194" s="65" t="inlineStr"/>
       <c r="AQ194" s="65" t="inlineStr"/>
       <c r="AR194" s="23" t="inlineStr"/>
       <c r="AS194" s="23" t="n"/>
       <c r="AT194" s="67" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="68" t="inlineStr">
+      <c r="A195" s="53" t="inlineStr">
         <is>
           <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
@@ -24049,18 +23385,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP195" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP195" s="65" t="inlineStr"/>
       <c r="AQ195" s="65" t="inlineStr"/>
       <c r="AR195" s="23" t="inlineStr"/>
       <c r="AS195" s="23" t="n"/>
       <c r="AT195" s="67" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="68" t="inlineStr">
+      <c r="A196" s="53" t="inlineStr">
         <is>
           <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
@@ -24171,18 +23503,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP196" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP196" s="65" t="inlineStr"/>
       <c r="AQ196" s="65" t="inlineStr"/>
       <c r="AR196" s="23" t="inlineStr"/>
       <c r="AS196" s="23" t="n"/>
       <c r="AT196" s="67" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="68" t="inlineStr">
+      <c r="A197" s="53" t="inlineStr">
         <is>
           <t>PS5-60-76 - Engine G Cooling system</t>
         </is>
@@ -24289,18 +23617,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP197" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP197" s="65" t="inlineStr"/>
       <c r="AQ197" s="65" t="inlineStr"/>
       <c r="AR197" s="23" t="inlineStr"/>
       <c r="AS197" s="23" t="n"/>
       <c r="AT197" s="67" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="53" t="inlineStr">
+      <c r="A198" s="68" t="inlineStr">
         <is>
           <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
         </is>
@@ -24411,18 +23735,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP198" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="AP198" s="65" t="inlineStr"/>
       <c r="AQ198" s="65" t="inlineStr"/>
       <c r="AR198" s="23" t="inlineStr"/>
       <c r="AS198" s="23" t="n"/>
       <c r="AT198" s="67" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="68" t="inlineStr">
+      <c r="A199" s="53" t="inlineStr">
         <is>
           <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
         </is>
@@ -24533,18 +23853,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP199" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP199" s="65" t="inlineStr"/>
       <c r="AQ199" s="65" t="inlineStr"/>
       <c r="AR199" s="23" t="inlineStr"/>
       <c r="AS199" s="23" t="n"/>
       <c r="AT199" s="67" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="68" t="inlineStr">
+      <c r="A200" s="53" t="inlineStr">
         <is>
           <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
         </is>
@@ -24655,18 +23971,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP200" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP200" s="65" t="inlineStr"/>
       <c r="AQ200" s="65" t="inlineStr"/>
       <c r="AR200" s="23" t="inlineStr"/>
       <c r="AS200" s="23" t="n"/>
       <c r="AT200" s="67" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="53" t="inlineStr">
+      <c r="A201" s="68" t="inlineStr">
         <is>
           <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
         </is>
@@ -24773,11 +24085,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP201" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP201" s="65" t="inlineStr"/>
       <c r="AQ201" s="65" t="inlineStr">
         <is>
           <t>23</t>
@@ -24792,7 +24100,7 @@
       <c r="AT201" s="67" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="68" t="inlineStr">
+      <c r="A202" s="53" t="inlineStr">
         <is>
           <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
@@ -24903,18 +24211,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP202" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP202" s="65" t="inlineStr"/>
       <c r="AQ202" s="65" t="inlineStr"/>
       <c r="AR202" s="23" t="inlineStr"/>
       <c r="AS202" s="23" t="n"/>
       <c r="AT202" s="67" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="53" t="inlineStr">
+      <c r="A203" s="68" t="inlineStr">
         <is>
           <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
         </is>
@@ -25025,18 +24329,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP203" s="65" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="AP203" s="65" t="inlineStr"/>
       <c r="AQ203" s="65" t="inlineStr"/>
       <c r="AR203" s="23" t="inlineStr"/>
       <c r="AS203" s="23" t="n"/>
       <c r="AT203" s="67" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="68" t="inlineStr">
+      <c r="A204" s="53" t="inlineStr">
         <is>
           <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
@@ -25147,18 +24447,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP204" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP204" s="65" t="inlineStr"/>
       <c r="AQ204" s="65" t="inlineStr"/>
       <c r="AR204" s="23" t="inlineStr"/>
       <c r="AS204" s="23" t="n"/>
       <c r="AT204" s="67" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="53" t="inlineStr">
+      <c r="A205" s="68" t="inlineStr">
         <is>
           <t>PS5-61-08 - Electrical Control System</t>
         </is>
@@ -25265,11 +24561,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP205" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP205" s="65" t="inlineStr"/>
       <c r="AQ205" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -25284,7 +24576,7 @@
       <c r="AT205" s="67" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="53" t="inlineStr">
+      <c r="A206" s="68" t="inlineStr">
         <is>
           <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
         </is>
@@ -25391,11 +24683,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP206" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP206" s="65" t="inlineStr"/>
       <c r="AQ206" s="65" t="inlineStr">
         <is>
           <t>17</t>
@@ -25410,7 +24698,7 @@
       <c r="AT206" s="67" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="68" t="inlineStr">
+      <c r="A207" s="53" t="inlineStr">
         <is>
           <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
@@ -25521,18 +24809,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP207" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP207" s="65" t="inlineStr"/>
       <c r="AQ207" s="65" t="inlineStr"/>
       <c r="AR207" s="23" t="inlineStr"/>
       <c r="AS207" s="23" t="n"/>
       <c r="AT207" s="67" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="68" t="inlineStr">
+      <c r="A208" s="53" t="inlineStr">
         <is>
           <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
@@ -25643,18 +24927,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP208" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP208" s="65" t="inlineStr"/>
       <c r="AQ208" s="65" t="inlineStr"/>
       <c r="AR208" s="23" t="inlineStr"/>
       <c r="AS208" s="23" t="n"/>
       <c r="AT208" s="67" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="53" t="inlineStr">
+      <c r="A209" s="68" t="inlineStr">
         <is>
           <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
         </is>
@@ -25738,7 +25018,7 @@
       <c r="AT209" s="67" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="53" t="inlineStr">
+      <c r="A210" s="68" t="inlineStr">
         <is>
           <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
         </is>
@@ -25841,18 +25121,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP210" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP210" s="65" t="inlineStr"/>
       <c r="AQ210" s="65" t="inlineStr"/>
       <c r="AR210" s="23" t="inlineStr"/>
       <c r="AS210" s="23" t="n"/>
       <c r="AT210" s="67" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="53" t="inlineStr">
+      <c r="A211" s="68" t="inlineStr">
         <is>
           <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
         </is>
@@ -25955,18 +25231,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP211" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP211" s="65" t="inlineStr"/>
       <c r="AQ211" s="65" t="inlineStr"/>
       <c r="AR211" s="23" t="inlineStr"/>
       <c r="AS211" s="23" t="n"/>
       <c r="AT211" s="67" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="53" t="inlineStr">
+      <c r="A212" s="68" t="inlineStr">
         <is>
           <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
         </is>
@@ -26073,11 +25345,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP212" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP212" s="65" t="inlineStr"/>
       <c r="AQ212" s="65" t="inlineStr">
         <is>
           <t>34</t>
@@ -26092,7 +25360,7 @@
       <c r="AT212" s="67" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="53" t="inlineStr">
+      <c r="A213" s="68" t="inlineStr">
         <is>
           <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
         </is>
@@ -26199,11 +25467,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP213" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP213" s="65" t="inlineStr"/>
       <c r="AQ213" s="65" t="inlineStr">
         <is>
           <t>32</t>
@@ -26218,7 +25482,7 @@
       <c r="AT213" s="67" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="68" t="inlineStr">
+      <c r="A214" s="53" t="inlineStr">
         <is>
           <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
         </is>
@@ -26329,18 +25593,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP214" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP214" s="65" t="inlineStr"/>
       <c r="AQ214" s="65" t="inlineStr"/>
       <c r="AR214" s="23" t="inlineStr"/>
       <c r="AS214" s="23" t="n"/>
       <c r="AT214" s="67" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="68" t="inlineStr">
+      <c r="A215" s="53" t="inlineStr">
         <is>
           <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
@@ -26451,18 +25711,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP215" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP215" s="65" t="inlineStr"/>
       <c r="AQ215" s="65" t="inlineStr"/>
       <c r="AR215" s="23" t="inlineStr"/>
       <c r="AS215" s="23" t="n"/>
       <c r="AT215" s="67" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="53" t="inlineStr">
+      <c r="A216" s="68" t="inlineStr">
         <is>
           <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
         </is>
@@ -26565,11 +25821,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP216" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP216" s="65" t="inlineStr"/>
       <c r="AQ216" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -26584,7 +25836,7 @@
       <c r="AT216" s="67" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="53" t="inlineStr">
+      <c r="A217" s="68" t="inlineStr">
         <is>
           <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
         </is>
@@ -26695,11 +25947,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP217" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP217" s="65" t="inlineStr"/>
       <c r="AQ217" s="65" t="inlineStr">
         <is>
           <t>14</t>
@@ -26714,7 +25962,7 @@
       <c r="AT217" s="67" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="53" t="inlineStr">
+      <c r="A218" s="68" t="inlineStr">
         <is>
           <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
         </is>
@@ -26821,11 +26069,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP218" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP218" s="65" t="inlineStr"/>
       <c r="AQ218" s="65" t="inlineStr">
         <is>
           <t>11</t>
@@ -26840,7 +26084,7 @@
       <c r="AT218" s="67" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="53" t="inlineStr">
+      <c r="A219" s="68" t="inlineStr">
         <is>
           <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
         </is>
@@ -26878,7 +26122,7 @@
       <c r="H219" s="24" t="inlineStr"/>
       <c r="I219" s="70" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="J219" s="55" t="n">
@@ -26917,14 +26161,14 @@
         <v>22</v>
       </c>
       <c r="AI219" s="23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AJ219" s="23" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AK219" s="25" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="AL219" s="23" t="inlineStr">
@@ -26947,26 +26191,22 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP219" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP219" s="65" t="inlineStr"/>
       <c r="AQ219" s="65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR219" s="23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AS219" s="23" t="n"/>
       <c r="AT219" s="67" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="53" t="inlineStr">
+      <c r="A220" s="68" t="inlineStr">
         <is>
           <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
         </is>
@@ -27073,11 +26313,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP220" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP220" s="65" t="inlineStr"/>
       <c r="AQ220" s="65" t="inlineStr">
         <is>
           <t>12</t>
@@ -27092,7 +26328,7 @@
       <c r="AT220" s="67" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="53" t="inlineStr">
+      <c r="A221" s="68" t="inlineStr">
         <is>
           <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
         </is>
@@ -27203,18 +26439,22 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP221" s="65" t="inlineStr">
+      <c r="AP221" s="65" t="inlineStr"/>
+      <c r="AQ221" s="65" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="AQ221" s="65" t="inlineStr"/>
-      <c r="AR221" s="23" t="inlineStr"/>
+      <c r="AR221" s="23" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="AS221" s="23" t="n"/>
       <c r="AT221" s="67" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="53" t="inlineStr">
+      <c r="A222" s="68" t="inlineStr">
         <is>
           <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
         </is>
@@ -27321,18 +26561,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP222" s="65" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="AP222" s="65" t="inlineStr"/>
       <c r="AQ222" s="65" t="inlineStr"/>
       <c r="AR222" s="23" t="inlineStr"/>
       <c r="AS222" s="23" t="n"/>
       <c r="AT222" s="67" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="53" t="inlineStr">
+      <c r="A223" s="68" t="inlineStr">
         <is>
           <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
         </is>
@@ -27416,7 +26652,7 @@
       <c r="AT223" s="67" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="53" t="inlineStr">
+      <c r="A224" s="68" t="inlineStr">
         <is>
           <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
         </is>
@@ -27500,7 +26736,7 @@
       <c r="AT224" s="67" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="53" t="inlineStr">
+      <c r="A225" s="68" t="inlineStr">
         <is>
           <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
         </is>
@@ -27603,18 +26839,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP225" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP225" s="65" t="inlineStr"/>
       <c r="AQ225" s="65" t="inlineStr"/>
       <c r="AR225" s="23" t="inlineStr"/>
       <c r="AS225" s="23" t="n"/>
       <c r="AT225" s="67" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="53" t="inlineStr">
+      <c r="A226" s="68" t="inlineStr">
         <is>
           <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
         </is>
@@ -27717,18 +26949,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP226" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP226" s="65" t="inlineStr"/>
       <c r="AQ226" s="65" t="inlineStr"/>
       <c r="AR226" s="23" t="inlineStr"/>
       <c r="AS226" s="23" t="n"/>
       <c r="AT226" s="67" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="53" t="inlineStr">
+      <c r="A227" s="68" t="inlineStr">
         <is>
           <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
         </is>
@@ -27831,18 +27059,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP227" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP227" s="65" t="inlineStr"/>
       <c r="AQ227" s="65" t="inlineStr"/>
       <c r="AR227" s="23" t="inlineStr"/>
       <c r="AS227" s="23" t="n"/>
       <c r="AT227" s="67" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="53" t="inlineStr">
+      <c r="A228" s="68" t="inlineStr">
         <is>
           <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
         </is>
@@ -27945,18 +27169,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP228" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP228" s="65" t="inlineStr"/>
       <c r="AQ228" s="65" t="inlineStr"/>
       <c r="AR228" s="23" t="inlineStr"/>
       <c r="AS228" s="23" t="n"/>
       <c r="AT228" s="67" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="53" t="inlineStr">
+      <c r="A229" s="68" t="inlineStr">
         <is>
           <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
         </is>
@@ -28059,18 +27279,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP229" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP229" s="65" t="inlineStr"/>
       <c r="AQ229" s="65" t="inlineStr"/>
       <c r="AR229" s="23" t="inlineStr"/>
       <c r="AS229" s="23" t="n"/>
       <c r="AT229" s="67" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="53" t="inlineStr">
+      <c r="A230" s="68" t="inlineStr">
         <is>
           <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
         </is>
@@ -28173,18 +27389,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP230" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP230" s="65" t="inlineStr"/>
       <c r="AQ230" s="65" t="inlineStr"/>
       <c r="AR230" s="23" t="inlineStr"/>
       <c r="AS230" s="23" t="n"/>
       <c r="AT230" s="67" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="53" t="inlineStr">
+      <c r="A231" s="68" t="inlineStr">
         <is>
           <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
         </is>
@@ -28287,18 +27499,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP231" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP231" s="65" t="inlineStr"/>
       <c r="AQ231" s="65" t="inlineStr"/>
       <c r="AR231" s="23" t="inlineStr"/>
       <c r="AS231" s="23" t="n"/>
       <c r="AT231" s="67" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="53" t="inlineStr">
+      <c r="A232" s="68" t="inlineStr">
         <is>
           <t>PS5-63-01 - Electrical Earthing</t>
         </is>
@@ -28409,11 +27617,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP232" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP232" s="65" t="inlineStr"/>
       <c r="AQ232" s="65" t="inlineStr">
         <is>
           <t>18 ITRs for lightning, 22 ITRs for grounding cannot be closed due to material issues.</t>
@@ -28428,7 +27632,7 @@
       <c r="AT232" s="67" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="53" t="inlineStr">
+      <c r="A233" s="68" t="inlineStr">
         <is>
           <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
         </is>
@@ -28531,11 +27735,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP233" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP233" s="65" t="inlineStr"/>
       <c r="AQ233" s="65" t="inlineStr">
         <is>
           <t>4</t>
@@ -28550,7 +27750,7 @@
       <c r="AT233" s="67" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="53" t="inlineStr">
+      <c r="A234" s="68" t="inlineStr">
         <is>
           <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
         </is>
@@ -28661,11 +27861,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP234" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP234" s="65" t="inlineStr"/>
       <c r="AQ234" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -28680,7 +27876,7 @@
       <c r="AT234" s="67" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="68" t="inlineStr">
+      <c r="A235" s="53" t="inlineStr">
         <is>
           <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
@@ -28764,7 +27960,7 @@
       <c r="AT235" s="67" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="53" t="inlineStr">
+      <c r="A236" s="68" t="inlineStr">
         <is>
           <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
         </is>
@@ -28867,11 +28063,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP236" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP236" s="65" t="inlineStr"/>
       <c r="AQ236" s="65" t="inlineStr">
         <is>
           <t>8</t>
@@ -28886,7 +28078,7 @@
       <c r="AT236" s="67" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="53" t="inlineStr">
+      <c r="A237" s="68" t="inlineStr">
         <is>
           <t>PS5-63-06 - Electrical Earthing - Guard House</t>
         </is>
@@ -28989,11 +28181,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP237" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP237" s="65" t="inlineStr"/>
       <c r="AQ237" s="65" t="inlineStr">
         <is>
           <t>4</t>
@@ -29008,7 +28196,7 @@
       <c r="AT237" s="67" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="53" t="inlineStr">
+      <c r="A238" s="68" t="inlineStr">
         <is>
           <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
         </is>
@@ -29111,11 +28299,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP238" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP238" s="65" t="inlineStr"/>
       <c r="AQ238" s="65" t="inlineStr">
         <is>
           <t>4</t>
@@ -29130,7 +28314,7 @@
       <c r="AT238" s="67" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="53" t="inlineStr">
+      <c r="A239" s="68" t="inlineStr">
         <is>
           <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
         </is>
@@ -29256,7 +28440,7 @@
       <c r="AT239" s="67" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="68" t="inlineStr">
+      <c r="A240" s="53" t="inlineStr">
         <is>
           <t>PS5-71-02 - CFO Allocation Metering Package</t>
         </is>
@@ -29367,18 +28551,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP240" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP240" s="65" t="inlineStr"/>
       <c r="AQ240" s="65" t="inlineStr"/>
       <c r="AR240" s="23" t="inlineStr"/>
       <c r="AS240" s="23" t="n"/>
       <c r="AT240" s="67" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="53" t="inlineStr">
+      <c r="A241" s="68" t="inlineStr">
         <is>
           <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
         </is>
@@ -29462,7 +28642,7 @@
       <c r="AT241" s="67" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="53" t="inlineStr">
+      <c r="A242" s="68" t="inlineStr">
         <is>
           <t>PS5-71-04 - CFO Storage Tank</t>
         </is>
@@ -29569,11 +28749,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP242" s="65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="AP242" s="65" t="inlineStr"/>
       <c r="AQ242" s="65" t="inlineStr">
         <is>
           <t>14</t>
@@ -29588,7 +28764,7 @@
       <c r="AT242" s="67" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="53" t="inlineStr">
+      <c r="A243" s="68" t="inlineStr">
         <is>
           <t>PS5-71-05 - CFO Transfer Pump A/B</t>
         </is>
@@ -29695,11 +28871,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP243" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP243" s="65" t="inlineStr"/>
       <c r="AQ243" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -29714,7 +28886,7 @@
       <c r="AT243" s="67" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="53" t="inlineStr">
+      <c r="A244" s="68" t="inlineStr">
         <is>
           <t>PS5-71-06 - Crude Fuel Separation Module</t>
         </is>
@@ -29821,18 +28993,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP244" s="65" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+      <c r="AP244" s="65" t="inlineStr"/>
       <c r="AQ244" s="65" t="inlineStr"/>
       <c r="AR244" s="23" t="inlineStr"/>
       <c r="AS244" s="23" t="n"/>
       <c r="AT244" s="67" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="53" t="inlineStr">
+      <c r="A245" s="68" t="inlineStr">
         <is>
           <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
         </is>
@@ -29939,18 +29107,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP245" s="65" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
+      <c r="AP245" s="65" t="inlineStr"/>
       <c r="AQ245" s="65" t="inlineStr"/>
       <c r="AR245" s="23" t="inlineStr"/>
       <c r="AS245" s="23" t="n"/>
       <c r="AT245" s="67" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="53" t="inlineStr">
+      <c r="A246" s="68" t="inlineStr">
         <is>
           <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
         </is>
@@ -30061,18 +29225,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP246" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="AP246" s="65" t="inlineStr"/>
       <c r="AQ246" s="65" t="inlineStr"/>
       <c r="AR246" s="23" t="inlineStr"/>
       <c r="AS246" s="23" t="n"/>
       <c r="AT246" s="67" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="68" t="inlineStr">
+      <c r="A247" s="53" t="inlineStr">
         <is>
           <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
         </is>
@@ -30183,18 +29343,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP247" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP247" s="65" t="inlineStr"/>
       <c r="AQ247" s="65" t="inlineStr"/>
       <c r="AR247" s="23" t="inlineStr"/>
       <c r="AS247" s="23" t="n"/>
       <c r="AT247" s="67" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="53" t="inlineStr">
+      <c r="A248" s="68" t="inlineStr">
         <is>
           <t>PS5-71-12 - CFO Service Tank</t>
         </is>
@@ -30301,11 +29457,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP248" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="AP248" s="65" t="inlineStr"/>
       <c r="AQ248" s="65" t="inlineStr">
         <is>
           <t>13</t>
@@ -30320,7 +29472,7 @@
       <c r="AT248" s="67" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="53" t="inlineStr">
+      <c r="A249" s="68" t="inlineStr">
         <is>
           <t>PS5-71-13 - CFO Service Pump A/B</t>
         </is>
@@ -30427,18 +29579,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP249" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="AP249" s="65" t="inlineStr"/>
       <c r="AQ249" s="65" t="inlineStr"/>
       <c r="AR249" s="23" t="inlineStr"/>
       <c r="AS249" s="23" t="n"/>
       <c r="AT249" s="67" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="68" t="inlineStr">
+      <c r="A250" s="53" t="inlineStr">
         <is>
           <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
@@ -30549,18 +29697,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP250" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP250" s="65" t="inlineStr"/>
       <c r="AQ250" s="65" t="inlineStr"/>
       <c r="AR250" s="23" t="inlineStr"/>
       <c r="AS250" s="23" t="n"/>
       <c r="AT250" s="67" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="53" t="inlineStr">
+      <c r="A251" s="68" t="inlineStr">
         <is>
           <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
         </is>
@@ -30686,7 +29830,7 @@
       <c r="AT251" s="67" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="68" t="inlineStr">
+      <c r="A252" s="53" t="inlineStr">
         <is>
           <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
@@ -30797,18 +29941,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP252" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP252" s="65" t="inlineStr"/>
       <c r="AQ252" s="65" t="inlineStr"/>
       <c r="AR252" s="23" t="inlineStr"/>
       <c r="AS252" s="23" t="n"/>
       <c r="AT252" s="67" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="53" t="inlineStr">
+      <c r="A253" s="68" t="inlineStr">
         <is>
           <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
         </is>
@@ -30919,18 +30059,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP253" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP253" s="65" t="inlineStr"/>
       <c r="AQ253" s="65" t="inlineStr"/>
       <c r="AR253" s="23" t="inlineStr"/>
       <c r="AS253" s="23" t="n"/>
       <c r="AT253" s="67" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="53" t="inlineStr">
+      <c r="A254" s="68" t="inlineStr">
         <is>
           <t>PS5-71-18 - Diesel Separator Module</t>
         </is>
@@ -31041,18 +30177,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP254" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="AP254" s="65" t="inlineStr"/>
       <c r="AQ254" s="65" t="inlineStr"/>
       <c r="AR254" s="23" t="inlineStr"/>
       <c r="AS254" s="23" t="n"/>
       <c r="AT254" s="67" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="53" t="inlineStr">
+      <c r="A255" s="68" t="inlineStr">
         <is>
           <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
         </is>
@@ -31159,18 +30291,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP255" s="65" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="AP255" s="65" t="inlineStr"/>
       <c r="AQ255" s="65" t="inlineStr"/>
       <c r="AR255" s="23" t="inlineStr"/>
       <c r="AS255" s="23" t="n"/>
       <c r="AT255" s="67" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="53" t="inlineStr">
+      <c r="A256" s="68" t="inlineStr">
         <is>
           <t>PS5-71-20 - Diesel Fuel Day Tank</t>
         </is>
@@ -31281,18 +30409,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP256" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="AP256" s="65" t="inlineStr"/>
       <c r="AQ256" s="65" t="inlineStr"/>
       <c r="AR256" s="23" t="inlineStr"/>
       <c r="AS256" s="23" t="n"/>
       <c r="AT256" s="67" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="53" t="inlineStr">
+      <c r="A257" s="68" t="inlineStr">
         <is>
           <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
         </is>
@@ -31403,18 +30527,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP257" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="AP257" s="65" t="inlineStr"/>
       <c r="AQ257" s="65" t="inlineStr"/>
       <c r="AR257" s="23" t="inlineStr"/>
       <c r="AS257" s="23" t="n"/>
       <c r="AT257" s="67" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="68" t="inlineStr">
+      <c r="A258" s="53" t="inlineStr">
         <is>
           <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
@@ -31525,18 +30645,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP258" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP258" s="65" t="inlineStr"/>
       <c r="AQ258" s="65" t="inlineStr"/>
       <c r="AR258" s="23" t="inlineStr"/>
       <c r="AS258" s="23" t="n"/>
       <c r="AT258" s="67" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="53" t="inlineStr">
+      <c r="A259" s="68" t="inlineStr">
         <is>
           <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
         </is>
@@ -31647,18 +30763,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP259" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP259" s="65" t="inlineStr"/>
       <c r="AQ259" s="65" t="inlineStr"/>
       <c r="AR259" s="23" t="inlineStr"/>
       <c r="AS259" s="23" t="n"/>
       <c r="AT259" s="67" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="68" t="inlineStr">
+      <c r="A260" s="53" t="inlineStr">
         <is>
           <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
@@ -31780,7 +30892,7 @@
       <c r="AT260" s="67" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="53" t="inlineStr">
+      <c r="A261" s="68" t="inlineStr">
         <is>
           <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
         </is>
@@ -31891,11 +31003,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP261" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP261" s="65" t="inlineStr"/>
       <c r="AQ261" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -31910,7 +31018,7 @@
       <c r="AT261" s="67" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="68" t="inlineStr">
+      <c r="A262" s="53" t="inlineStr">
         <is>
           <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
@@ -32021,18 +31129,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP262" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP262" s="65" t="inlineStr"/>
       <c r="AQ262" s="65" t="inlineStr"/>
       <c r="AR262" s="23" t="inlineStr"/>
       <c r="AS262" s="23" t="n"/>
       <c r="AT262" s="67" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="68" t="inlineStr">
+      <c r="A263" s="53" t="inlineStr">
         <is>
           <t>PS5-74-04 - Nitrogen Distribution Header</t>
         </is>
@@ -32143,26 +31247,22 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP263" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP263" s="65" t="inlineStr"/>
       <c r="AQ263" s="65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR263" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS263" s="23" t="n"/>
       <c r="AT263" s="67" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="53" t="inlineStr">
+      <c r="A264" s="68" t="inlineStr">
         <is>
           <t>PS5-75-01 - DRA Injection Package</t>
         </is>
@@ -32265,11 +31365,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP264" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP264" s="65" t="inlineStr"/>
       <c r="AQ264" s="65" t="inlineStr">
         <is>
           <t>11</t>
@@ -32284,7 +31380,7 @@
       <c r="AT264" s="67" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" s="68" t="inlineStr">
+      <c r="A265" s="53" t="inlineStr">
         <is>
           <t>PS5-75-02 - Biocide Injection Package</t>
         </is>
@@ -32395,18 +31491,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP265" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP265" s="65" t="inlineStr"/>
       <c r="AQ265" s="65" t="inlineStr"/>
       <c r="AR265" s="23" t="inlineStr"/>
       <c r="AS265" s="23" t="n"/>
       <c r="AT265" s="67" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" s="68" t="inlineStr">
+      <c r="A266" s="53" t="inlineStr">
         <is>
           <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
         </is>
@@ -32517,11 +31609,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP266" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP266" s="65" t="inlineStr"/>
       <c r="AQ266" s="65" t="inlineStr"/>
       <c r="AR266" s="23" t="inlineStr"/>
       <c r="AS266" s="23" t="n"/>
@@ -32635,11 +31723,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP267" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP267" s="65" t="inlineStr"/>
       <c r="AQ267" s="65" t="inlineStr">
         <is>
           <t>5</t>
@@ -32654,7 +31738,7 @@
       <c r="AT267" s="67" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="53" t="inlineStr">
+      <c r="A268" s="68" t="inlineStr">
         <is>
           <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
         </is>
@@ -32757,11 +31841,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP268" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP268" s="65" t="inlineStr"/>
       <c r="AQ268" s="65" t="inlineStr">
         <is>
           <t>15</t>
@@ -32776,7 +31856,7 @@
       <c r="AT268" s="67" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="53" t="inlineStr">
+      <c r="A269" s="68" t="inlineStr">
         <is>
           <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
         </is>
@@ -32879,11 +31959,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP269" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP269" s="65" t="inlineStr"/>
       <c r="AQ269" s="65" t="inlineStr">
         <is>
           <t>19</t>
@@ -32898,7 +31974,7 @@
       <c r="AT269" s="67" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="53" t="inlineStr">
+      <c r="A270" s="68" t="inlineStr">
         <is>
           <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
         </is>
@@ -33001,11 +32077,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP270" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP270" s="65" t="inlineStr"/>
       <c r="AQ270" s="65" t="inlineStr">
         <is>
           <t>37</t>
@@ -33020,7 +32092,7 @@
       <c r="AT270" s="67" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="53" t="inlineStr">
+      <c r="A271" s="68" t="inlineStr">
         <is>
           <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
         </is>
@@ -33123,11 +32195,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP271" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP271" s="65" t="inlineStr"/>
       <c r="AQ271" s="65" t="inlineStr">
         <is>
           <t>36</t>
@@ -33142,7 +32210,7 @@
       <c r="AT271" s="67" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" s="53" t="inlineStr">
+      <c r="A272" s="68" t="inlineStr">
         <is>
           <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
         </is>
@@ -33245,11 +32313,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP272" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP272" s="65" t="inlineStr"/>
       <c r="AQ272" s="65" t="inlineStr">
         <is>
           <t>43</t>
@@ -33264,7 +32328,7 @@
       <c r="AT272" s="67" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="53" t="inlineStr">
+      <c r="A273" s="68" t="inlineStr">
         <is>
           <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
         </is>
@@ -33367,11 +32431,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP273" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP273" s="65" t="inlineStr"/>
       <c r="AQ273" s="65" t="inlineStr">
         <is>
           <t>60</t>
@@ -33386,7 +32446,7 @@
       <c r="AT273" s="67" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="53" t="inlineStr">
+      <c r="A274" s="68" t="inlineStr">
         <is>
           <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
         </is>
@@ -33489,11 +32549,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP274" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP274" s="65" t="inlineStr"/>
       <c r="AQ274" s="65" t="inlineStr">
         <is>
           <t>23</t>
@@ -33508,7 +32564,7 @@
       <c r="AT274" s="67" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" s="53" t="inlineStr">
+      <c r="A275" s="68" t="inlineStr">
         <is>
           <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
         </is>
@@ -33611,11 +32667,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP275" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP275" s="65" t="inlineStr"/>
       <c r="AQ275" s="65" t="inlineStr">
         <is>
           <t>28</t>
@@ -33630,7 +32682,7 @@
       <c r="AT275" s="67" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="53" t="inlineStr">
+      <c r="A276" s="68" t="inlineStr">
         <is>
           <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
         </is>
@@ -33733,11 +32785,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP276" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP276" s="65" t="inlineStr"/>
       <c r="AQ276" s="65" t="inlineStr">
         <is>
           <t>43</t>
@@ -33752,7 +32800,7 @@
       <c r="AT276" s="67" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" s="53" t="inlineStr">
+      <c r="A277" s="68" t="inlineStr">
         <is>
           <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
         </is>
@@ -33855,11 +32903,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP277" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP277" s="65" t="inlineStr"/>
       <c r="AQ277" s="65" t="inlineStr">
         <is>
           <t>32</t>
@@ -33874,7 +32918,7 @@
       <c r="AT277" s="67" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="53" t="inlineStr">
+      <c r="A278" s="68" t="inlineStr">
         <is>
           <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
         </is>
@@ -33977,11 +33021,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP278" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP278" s="65" t="inlineStr"/>
       <c r="AQ278" s="65" t="inlineStr">
         <is>
           <t>44</t>
@@ -33996,7 +33036,7 @@
       <c r="AT278" s="67" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="53" t="inlineStr">
+      <c r="A279" s="68" t="inlineStr">
         <is>
           <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
         </is>
@@ -34099,11 +33139,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP279" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP279" s="65" t="inlineStr"/>
       <c r="AQ279" s="65" t="inlineStr">
         <is>
           <t>46</t>
@@ -34118,7 +33154,7 @@
       <c r="AT279" s="67" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="68" t="inlineStr">
+      <c r="A280" s="53" t="inlineStr">
         <is>
           <t>PS5-82-01 - Sanitary Sewage Collection</t>
         </is>
@@ -34225,18 +33261,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP280" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP280" s="65" t="inlineStr"/>
       <c r="AQ280" s="65" t="inlineStr"/>
       <c r="AR280" s="23" t="inlineStr"/>
       <c r="AS280" s="23" t="n"/>
       <c r="AT280" s="67" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="53" t="inlineStr">
+      <c r="A281" s="68" t="inlineStr">
         <is>
           <t>PS5-82-02 - Sewage Treatment Plant Package</t>
         </is>
@@ -34339,11 +33371,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP281" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP281" s="65" t="inlineStr"/>
       <c r="AQ281" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -34358,7 +33386,7 @@
       <c r="AT281" s="67" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="53" t="inlineStr">
+      <c r="A282" s="68" t="inlineStr">
         <is>
           <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
         </is>
@@ -34461,11 +33489,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP282" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP282" s="65" t="inlineStr"/>
       <c r="AQ282" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -34480,7 +33504,7 @@
       <c r="AT282" s="67" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" s="53" t="inlineStr">
+      <c r="A283" s="68" t="inlineStr">
         <is>
           <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
         </is>
@@ -34583,11 +33607,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP283" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP283" s="65" t="inlineStr"/>
       <c r="AQ283" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -34602,7 +33622,7 @@
       <c r="AT283" s="67" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" s="53" t="inlineStr">
+      <c r="A284" s="68" t="inlineStr">
         <is>
           <t>PS5-82-05 - Office and Facilities building</t>
         </is>
@@ -34705,18 +33725,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP284" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP284" s="65" t="inlineStr"/>
       <c r="AQ284" s="65" t="inlineStr"/>
       <c r="AR284" s="23" t="inlineStr"/>
       <c r="AS284" s="23" t="n"/>
       <c r="AT284" s="67" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="53" t="inlineStr">
+      <c r="A285" s="68" t="inlineStr">
         <is>
           <t>PS5-82-06 - Guard House Building</t>
         </is>
@@ -34819,18 +33835,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP285" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP285" s="65" t="inlineStr"/>
       <c r="AQ285" s="65" t="inlineStr"/>
       <c r="AR285" s="23" t="inlineStr"/>
       <c r="AS285" s="23" t="n"/>
       <c r="AT285" s="67" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="53" t="inlineStr">
+      <c r="A286" s="68" t="inlineStr">
         <is>
           <t>PS5-82-07 - Guard Huts</t>
         </is>
@@ -34933,11 +33945,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP286" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP286" s="65" t="inlineStr"/>
       <c r="AQ286" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -34952,7 +33960,7 @@
       <c r="AT286" s="67" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="68" t="inlineStr">
+      <c r="A287" s="53" t="inlineStr">
         <is>
           <t>PS5-83-01 - EITS Building</t>
         </is>
@@ -35063,18 +34071,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP287" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP287" s="65" t="inlineStr"/>
       <c r="AQ287" s="65" t="inlineStr"/>
       <c r="AR287" s="23" t="inlineStr"/>
       <c r="AS287" s="23" t="n"/>
       <c r="AT287" s="67" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="53" t="inlineStr">
+      <c r="A288" s="68" t="inlineStr">
         <is>
           <t>PS5-84-01 - Generator Building</t>
         </is>
@@ -35181,11 +34185,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP288" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP288" s="65" t="inlineStr"/>
       <c r="AQ288" s="65" t="inlineStr">
         <is>
           <t>3</t>
@@ -35200,7 +34200,7 @@
       <c r="AT288" s="67" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="53" t="inlineStr">
+      <c r="A289" s="68" t="inlineStr">
         <is>
           <t>PS5-84-02 - Workshop &amp; Warehouse</t>
         </is>
@@ -35303,11 +34303,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP289" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP289" s="65" t="inlineStr"/>
       <c r="AQ289" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -35322,7 +34318,7 @@
       <c r="AT289" s="67" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="68" t="inlineStr">
+      <c r="A290" s="53" t="inlineStr">
         <is>
           <t>PS5-84-03 - Shelters</t>
         </is>
@@ -35429,18 +34425,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP290" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP290" s="65" t="inlineStr"/>
       <c r="AQ290" s="65" t="inlineStr"/>
       <c r="AR290" s="23" t="inlineStr"/>
       <c r="AS290" s="23" t="n"/>
       <c r="AT290" s="67" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" s="68" t="inlineStr">
+      <c r="A291" s="53" t="inlineStr">
         <is>
           <t>PS5-86-01 - Shelters</t>
         </is>
@@ -35547,18 +34539,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP291" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP291" s="65" t="inlineStr"/>
       <c r="AQ291" s="65" t="inlineStr"/>
       <c r="AR291" s="23" t="inlineStr"/>
       <c r="AS291" s="23" t="n"/>
       <c r="AT291" s="67" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" s="68" t="inlineStr">
+      <c r="A292" s="53" t="inlineStr">
         <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
@@ -35669,18 +34657,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP292" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP292" s="65" t="inlineStr"/>
       <c r="AQ292" s="65" t="inlineStr"/>
       <c r="AR292" s="23" t="inlineStr"/>
       <c r="AS292" s="23" t="n"/>
       <c r="AT292" s="67" t="inlineStr"/>
     </row>
     <row r="293">
-      <c r="A293" s="53" t="inlineStr">
+      <c r="A293" s="68" t="inlineStr">
         <is>
           <t>PS5-99-01 - Area Completion for Building area</t>
         </is>
@@ -35783,11 +34767,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP293" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP293" s="65" t="inlineStr"/>
       <c r="AQ293" s="65" t="inlineStr">
         <is>
           <t>6</t>
@@ -35802,7 +34782,7 @@
       <c r="AT293" s="67" t="inlineStr"/>
     </row>
     <row r="294">
-      <c r="A294" s="53" t="inlineStr">
+      <c r="A294" s="68" t="inlineStr">
         <is>
           <t>PS5-99-02 - Area Completion for Utility area</t>
         </is>
@@ -35905,11 +34885,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP294" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP294" s="65" t="inlineStr"/>
       <c r="AQ294" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -35924,7 +34900,7 @@
       <c r="AT294" s="67" t="inlineStr"/>
     </row>
     <row r="295">
-      <c r="A295" s="53" t="inlineStr">
+      <c r="A295" s="68" t="inlineStr">
         <is>
           <t>PS5-99-03 - Area Completion for Power Distribution area</t>
         </is>
@@ -36031,11 +35007,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP295" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP295" s="65" t="inlineStr"/>
       <c r="AQ295" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -36050,7 +35022,7 @@
       <c r="AT295" s="67" t="inlineStr"/>
     </row>
     <row r="296">
-      <c r="A296" s="53" t="inlineStr">
+      <c r="A296" s="68" t="inlineStr">
         <is>
           <t>PS5-99-04 - Area Completion for Process area</t>
         </is>
@@ -36157,11 +35129,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP296" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP296" s="65" t="inlineStr"/>
       <c r="AQ296" s="65" t="inlineStr">
         <is>
           <t>9</t>
@@ -36176,7 +35144,7 @@
       <c r="AT296" s="67" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" s="53" t="inlineStr">
+      <c r="A297" s="68" t="inlineStr">
         <is>
           <t>PS5-99-05 - Area Completion for CFO area</t>
         </is>
@@ -36283,11 +35251,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP297" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP297" s="65" t="inlineStr"/>
       <c r="AQ297" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -36302,7 +35266,7 @@
       <c r="AT297" s="67" t="inlineStr"/>
     </row>
     <row r="298">
-      <c r="A298" s="53" t="inlineStr">
+      <c r="A298" s="68" t="inlineStr">
         <is>
           <t>PS5-99-06 - Area Completion for Power Generation area</t>
         </is>
@@ -36413,11 +35377,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP298" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP298" s="65" t="inlineStr"/>
       <c r="AQ298" s="65" t="inlineStr">
         <is>
           <t>1</t>

--- a/EXCEL/2 - RFC PROGRESS.xlsx
+++ b/EXCEL/2 - RFC PROGRESS.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -101,6 +101,12 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF8a97a5"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FFc00000"/>
       <sz val="10"/>
     </font>
@@ -116,6 +122,11 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="FF8a97a5"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FFb35900"/>
       <sz val="10"/>
     </font>
@@ -124,12 +135,6 @@
       <color rgb="FF0a58ca"/>
       <sz val="10"/>
       <u val="single"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FF8a97a5"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -172,7 +177,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -237,12 +242,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1b4f72"/>
         <bgColor rgb="FF1b4f72"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFffeb9c"/>
-        <bgColor rgb="FFffeb9c"/>
       </patternFill>
     </fill>
     <fill>
@@ -319,6 +318,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFffeb9c"/>
+        <bgColor rgb="FFffeb9c"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFed7d31"/>
         <bgColor rgb="FFed7d31"/>
       </patternFill>
@@ -339,6 +344,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFc6efce"/>
         <bgColor rgb="FFc6efce"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8a97a5"/>
+        <bgColor rgb="FF8a97a5"/>
       </patternFill>
     </fill>
     <fill>
@@ -504,36 +515,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -545,16 +553,19 @@
     <xf numFmtId="0" fontId="2" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -570,7 +581,7 @@
     <xf numFmtId="0" fontId="9" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -579,13 +590,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -593,7 +604,7 @@
     <xf numFmtId="0" fontId="3" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="38" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -644,10 +655,13 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -671,25 +685,22 @@
     <xf numFmtId="0" fontId="6" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -698,10 +709,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -710,10 +721,13 @@
     <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -722,25 +736,31 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -749,40 +769,37 @@
     <xf numFmtId="0" fontId="9" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1209,51 +1226,51 @@
           <t>PS5 COMPLETION PLATFORM  |  2 · RFC PROGRESS</t>
         </is>
       </c>
-      <c r="B1" s="100" t="n"/>
-      <c r="C1" s="100" t="n"/>
-      <c r="D1" s="100" t="n"/>
-      <c r="E1" s="100" t="n"/>
-      <c r="F1" s="100" t="n"/>
-      <c r="G1" s="100" t="n"/>
-      <c r="H1" s="100" t="n"/>
-      <c r="I1" s="100" t="n"/>
-      <c r="J1" s="100" t="n"/>
-      <c r="K1" s="100" t="n"/>
-      <c r="L1" s="100" t="n"/>
-      <c r="M1" s="100" t="n"/>
-      <c r="N1" s="100" t="n"/>
-      <c r="O1" s="100" t="n"/>
-      <c r="P1" s="100" t="n"/>
-      <c r="Q1" s="100" t="n"/>
-      <c r="R1" s="100" t="n"/>
-      <c r="S1" s="100" t="n"/>
-      <c r="T1" s="100" t="n"/>
-      <c r="U1" s="100" t="n"/>
-      <c r="V1" s="100" t="n"/>
-      <c r="W1" s="100" t="n"/>
-      <c r="X1" s="100" t="n"/>
-      <c r="Y1" s="100" t="n"/>
-      <c r="Z1" s="100" t="n"/>
-      <c r="AA1" s="100" t="n"/>
-      <c r="AB1" s="100" t="n"/>
-      <c r="AC1" s="100" t="n"/>
-      <c r="AD1" s="100" t="n"/>
-      <c r="AE1" s="100" t="n"/>
-      <c r="AF1" s="100" t="n"/>
-      <c r="AG1" s="100" t="n"/>
-      <c r="AH1" s="100" t="n"/>
-      <c r="AI1" s="100" t="n"/>
-      <c r="AJ1" s="100" t="n"/>
-      <c r="AK1" s="100" t="n"/>
-      <c r="AL1" s="100" t="n"/>
-      <c r="AM1" s="100" t="n"/>
-      <c r="AN1" s="100" t="n"/>
-      <c r="AO1" s="100" t="n"/>
-      <c r="AP1" s="100" t="n"/>
-      <c r="AQ1" s="100" t="n"/>
-      <c r="AR1" s="100" t="n"/>
-      <c r="AS1" s="100" t="n"/>
-      <c r="AT1" s="101" t="n"/>
+      <c r="B1" s="102" t="n"/>
+      <c r="C1" s="102" t="n"/>
+      <c r="D1" s="102" t="n"/>
+      <c r="E1" s="102" t="n"/>
+      <c r="F1" s="102" t="n"/>
+      <c r="G1" s="102" t="n"/>
+      <c r="H1" s="102" t="n"/>
+      <c r="I1" s="102" t="n"/>
+      <c r="J1" s="102" t="n"/>
+      <c r="K1" s="102" t="n"/>
+      <c r="L1" s="102" t="n"/>
+      <c r="M1" s="102" t="n"/>
+      <c r="N1" s="102" t="n"/>
+      <c r="O1" s="102" t="n"/>
+      <c r="P1" s="102" t="n"/>
+      <c r="Q1" s="102" t="n"/>
+      <c r="R1" s="102" t="n"/>
+      <c r="S1" s="102" t="n"/>
+      <c r="T1" s="102" t="n"/>
+      <c r="U1" s="102" t="n"/>
+      <c r="V1" s="102" t="n"/>
+      <c r="W1" s="102" t="n"/>
+      <c r="X1" s="102" t="n"/>
+      <c r="Y1" s="102" t="n"/>
+      <c r="Z1" s="102" t="n"/>
+      <c r="AA1" s="102" t="n"/>
+      <c r="AB1" s="102" t="n"/>
+      <c r="AC1" s="102" t="n"/>
+      <c r="AD1" s="102" t="n"/>
+      <c r="AE1" s="102" t="n"/>
+      <c r="AF1" s="102" t="n"/>
+      <c r="AG1" s="102" t="n"/>
+      <c r="AH1" s="102" t="n"/>
+      <c r="AI1" s="102" t="n"/>
+      <c r="AJ1" s="102" t="n"/>
+      <c r="AK1" s="102" t="n"/>
+      <c r="AL1" s="102" t="n"/>
+      <c r="AM1" s="102" t="n"/>
+      <c r="AN1" s="102" t="n"/>
+      <c r="AO1" s="102" t="n"/>
+      <c r="AP1" s="102" t="n"/>
+      <c r="AQ1" s="102" t="n"/>
+      <c r="AR1" s="102" t="n"/>
+      <c r="AS1" s="102" t="n"/>
+      <c r="AT1" s="103" t="n"/>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
@@ -1593,7 +1610,11 @@
           <t>2026-09-08 00:00:00</t>
         </is>
       </c>
-      <c r="F4" s="23" t="inlineStr"/>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="G4" s="28" t="inlineStr">
         <is>
           <t>Full</t>
@@ -1606,7 +1627,7 @@
       </c>
       <c r="I4" s="54" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="J4" s="55" t="n">
@@ -1647,14 +1668,14 @@
         <v>86</v>
       </c>
       <c r="AI4" s="23" t="n">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="AJ4" s="23" t="n">
-        <v>-18</v>
+        <v>2</v>
       </c>
       <c r="AK4" s="27" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="AL4" s="23" t="inlineStr">
@@ -1667,7 +1688,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AN4" s="64" t="inlineStr">
+      <c r="AN4" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1677,14 +1698,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP4" s="65" t="inlineStr"/>
-      <c r="AQ4" s="65" t="inlineStr"/>
-      <c r="AR4" s="23" t="inlineStr"/>
+      <c r="AP4" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ4" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR4" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS4" s="66" t="n"/>
       <c r="AT4" s="67" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="68" t="inlineStr">
+      <c r="A5" s="53" t="inlineStr">
         <is>
           <t>PS5-01-02 - Fire Water Pump A</t>
         </is>
@@ -1726,7 +1759,7 @@
       </c>
       <c r="I5" s="54" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="J5" s="55" t="n">
@@ -1765,14 +1798,14 @@
         <v>85</v>
       </c>
       <c r="AI5" s="23" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ5" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK5" s="27" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="AL5" s="23" t="inlineStr">
@@ -1785,7 +1818,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AN5" s="64" t="inlineStr">
+      <c r="AN5" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1795,7 +1828,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP5" s="65" t="inlineStr"/>
+      <c r="AP5" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ5" s="65" t="inlineStr">
         <is>
           <t>EACOP(MR.BENHER TBC)-EXPECTED 19-08-2026</t>
@@ -1810,7 +1847,7 @@
       <c r="AT5" s="67" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="68" t="inlineStr">
+      <c r="A6" s="53" t="inlineStr">
         <is>
           <t>PS5-01-03 - Fire Water Pump B</t>
         </is>
@@ -1835,7 +1872,11 @@
           <t>2026-09-08 00:00:00</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr"/>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="G6" s="28" t="inlineStr">
         <is>
           <t>Full</t>
@@ -1848,7 +1889,7 @@
       </c>
       <c r="I6" s="54" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="J6" s="55" t="n">
@@ -1887,14 +1928,14 @@
         <v>76</v>
       </c>
       <c r="AI6" s="23" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AJ6" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK6" s="27" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="AL6" s="23" t="inlineStr">
@@ -1907,7 +1948,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AN6" s="64" t="inlineStr">
+      <c r="AN6" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1917,7 +1958,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP6" s="65" t="inlineStr"/>
+      <c r="AP6" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ6" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -1932,7 +1977,7 @@
       <c r="AT6" s="67" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="53" t="inlineStr">
+      <c r="A7" s="68" t="inlineStr">
         <is>
           <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
         </is>
@@ -2039,14 +2084,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP7" s="65" t="inlineStr"/>
-      <c r="AQ7" s="65" t="inlineStr"/>
-      <c r="AR7" s="23" t="inlineStr"/>
+      <c r="AP7" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ7" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR7" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS7" s="23" t="n"/>
       <c r="AT7" s="67" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="53" t="inlineStr">
+      <c r="A8" s="68" t="inlineStr">
         <is>
           <t>PS5-01-05 - Foam Skid</t>
         </is>
@@ -2157,14 +2214,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP8" s="65" t="inlineStr"/>
-      <c r="AQ8" s="65" t="inlineStr"/>
-      <c r="AR8" s="23" t="inlineStr"/>
+      <c r="AP8" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ8" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR8" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS8" s="23" t="n"/>
       <c r="AT8" s="67" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="53" t="inlineStr">
+      <c r="A9" s="68" t="inlineStr">
         <is>
           <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
@@ -2271,14 +2340,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP9" s="65" t="inlineStr"/>
-      <c r="AQ9" s="65" t="inlineStr"/>
-      <c r="AR9" s="23" t="inlineStr"/>
+      <c r="AP9" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ9" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR9" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS9" s="23" t="n"/>
       <c r="AT9" s="67" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="68" t="inlineStr">
+      <c r="A10" s="53" t="inlineStr">
         <is>
           <t>PS5-01-07 - Fire Water Ring Main &amp; Distribution</t>
         </is>
@@ -2305,7 +2386,7 @@
       </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t>Material Hold</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="G10" s="28" t="inlineStr">
@@ -2387,7 +2468,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP10" s="65" t="inlineStr"/>
+      <c r="AP10" s="65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AQ10" s="65" t="inlineStr">
         <is>
           <t>4</t>
@@ -2402,7 +2487,7 @@
       <c r="AT10" s="67" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="68" t="inlineStr">
+      <c r="A11" s="53" t="inlineStr">
         <is>
           <t>PS5-01-08 - PS5 Deluge Valve Skid (PS5-01-UK-6100)</t>
         </is>
@@ -2513,14 +2598,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP11" s="65" t="inlineStr"/>
-      <c r="AQ11" s="65" t="inlineStr"/>
-      <c r="AR11" s="23" t="inlineStr"/>
+      <c r="AP11" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ11" s="65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AR11" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AS11" s="23" t="n"/>
       <c r="AT11" s="67" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="53" t="inlineStr">
+      <c r="A12" s="68" t="inlineStr">
         <is>
           <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
@@ -2623,14 +2720,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP12" s="65" t="inlineStr"/>
-      <c r="AQ12" s="65" t="inlineStr"/>
-      <c r="AR12" s="23" t="inlineStr"/>
+      <c r="AP12" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ12" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR12" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS12" s="23" t="n"/>
       <c r="AT12" s="67" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="53" t="inlineStr">
+      <c r="A13" s="68" t="inlineStr">
         <is>
           <t>PS5-01-10 - Water Mist Package</t>
         </is>
@@ -2741,14 +2850,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP13" s="65" t="inlineStr"/>
-      <c r="AQ13" s="65" t="inlineStr"/>
-      <c r="AR13" s="23" t="inlineStr"/>
+      <c r="AP13" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ13" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR13" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS13" s="23" t="n"/>
       <c r="AT13" s="67" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="53" t="inlineStr">
+      <c r="A14" s="68" t="inlineStr">
         <is>
           <t>PS5-01-11 - Inergen for Power Gen Building</t>
         </is>
@@ -2859,14 +2980,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP14" s="65" t="inlineStr"/>
-      <c r="AQ14" s="65" t="inlineStr"/>
-      <c r="AR14" s="23" t="inlineStr"/>
+      <c r="AP14" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ14" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR14" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS14" s="23" t="n"/>
       <c r="AT14" s="67" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="68" t="inlineStr">
+      <c r="A15" s="53" t="inlineStr">
         <is>
           <t>PS5-02-01 - Miscellaneous Safety equipment</t>
         </is>
@@ -2876,7 +3009,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr"/>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
           <t>E,M,S</t>
@@ -2900,7 +3037,7 @@
       <c r="H15" s="24" t="inlineStr"/>
       <c r="I15" s="69" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="J15" s="55" t="n">
@@ -2939,14 +3076,14 @@
         <v>66</v>
       </c>
       <c r="AI15" s="23" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AJ15" s="23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK15" s="26" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="AL15" s="64" t="inlineStr">
@@ -2969,22 +3106,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP15" s="65" t="inlineStr"/>
+      <c r="AP15" s="65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AQ15" s="65" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AR15" s="23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AS15" s="23" t="n"/>
       <c r="AT15" s="67" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="68" t="inlineStr">
+      <c r="A16" s="53" t="inlineStr">
         <is>
           <t>PS5-02-02 - Portable Fire Fighting Equipments</t>
         </is>
@@ -3091,7 +3232,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP16" s="65" t="inlineStr"/>
+      <c r="AP16" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ16" s="65" t="inlineStr">
         <is>
           <t>48</t>
@@ -3106,7 +3251,7 @@
       <c r="AT16" s="67" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="53" t="inlineStr">
+      <c r="A17" s="68" t="inlineStr">
         <is>
           <t>PS5-03-01 - FZ-01 - Process Area</t>
         </is>
@@ -3217,14 +3362,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP17" s="65" t="inlineStr"/>
-      <c r="AQ17" s="65" t="inlineStr"/>
-      <c r="AR17" s="23" t="inlineStr"/>
+      <c r="AP17" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ17" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR17" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS17" s="23" t="n"/>
       <c r="AT17" s="67" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="68" t="inlineStr">
+      <c r="A18" s="53" t="inlineStr">
         <is>
           <t>PS5-03-03 - FZ-03 - Buildings Area</t>
         </is>
@@ -3317,7 +3474,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AN18" s="64" t="inlineStr">
+      <c r="AN18" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3327,14 +3484,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP18" s="65" t="inlineStr"/>
-      <c r="AQ18" s="65" t="inlineStr"/>
-      <c r="AR18" s="23" t="inlineStr"/>
+      <c r="AP18" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ18" s="65" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AR18" s="23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="AS18" s="23" t="n"/>
       <c r="AT18" s="67" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="68" t="inlineStr">
+      <c r="A19" s="53" t="inlineStr">
         <is>
           <t>PS5-03-04 - FZ-04 - Utilities - Diesel and Firewater Pumps Areas</t>
         </is>
@@ -3369,7 +3538,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H19" s="24" t="inlineStr"/>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
       <c r="I19" s="54" t="inlineStr">
         <is>
           <t>94%</t>
@@ -3441,7 +3614,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP19" s="65" t="inlineStr"/>
+      <c r="AP19" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ19" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -3456,7 +3633,7 @@
       <c r="AT19" s="67" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="53" t="inlineStr">
+      <c r="A20" s="68" t="inlineStr">
         <is>
           <t>PS5-03-06 - FZ-06 - Transformer Area</t>
         </is>
@@ -3567,14 +3744,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP20" s="65" t="inlineStr"/>
-      <c r="AQ20" s="65" t="inlineStr"/>
-      <c r="AR20" s="23" t="inlineStr"/>
+      <c r="AP20" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ20" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR20" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS20" s="23" t="n"/>
       <c r="AT20" s="67" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="53" t="inlineStr">
+      <c r="A21" s="68" t="inlineStr">
         <is>
           <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
         </is>
@@ -3685,14 +3874,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP21" s="65" t="inlineStr"/>
-      <c r="AQ21" s="65" t="inlineStr"/>
-      <c r="AR21" s="23" t="inlineStr"/>
+      <c r="AP21" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ21" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR21" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS21" s="23" t="n"/>
       <c r="AT21" s="67" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="68" t="inlineStr">
+      <c r="A22" s="53" t="inlineStr">
         <is>
           <t>PS5-03-08 - FZ-08 - Utilities - Power Generation Area - External</t>
         </is>
@@ -3803,7 +4004,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP22" s="65" t="inlineStr"/>
+      <c r="AP22" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ22" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -3818,7 +4023,7 @@
       <c r="AT22" s="67" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="53" t="inlineStr">
+      <c r="A23" s="68" t="inlineStr">
         <is>
           <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
         </is>
@@ -3929,14 +4134,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP23" s="65" t="inlineStr"/>
-      <c r="AQ23" s="65" t="inlineStr"/>
-      <c r="AR23" s="23" t="inlineStr"/>
+      <c r="AP23" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ23" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR23" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS23" s="23" t="n"/>
       <c r="AT23" s="67" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="53" t="inlineStr">
+      <c r="A24" s="68" t="inlineStr">
         <is>
           <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
         </is>
@@ -4047,14 +4264,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP24" s="65" t="inlineStr"/>
-      <c r="AQ24" s="65" t="inlineStr"/>
-      <c r="AR24" s="23" t="inlineStr"/>
+      <c r="AP24" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ24" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR24" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS24" s="23" t="n"/>
       <c r="AT24" s="67" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="53" t="inlineStr">
+      <c r="A25" s="68" t="inlineStr">
         <is>
           <t>PS5-03-11 - FZ-11 - Power Generation Building - Engine Bay 3</t>
         </is>
@@ -4165,14 +4394,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP25" s="65" t="inlineStr"/>
-      <c r="AQ25" s="65" t="inlineStr"/>
-      <c r="AR25" s="23" t="inlineStr"/>
+      <c r="AP25" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ25" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR25" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS25" s="23" t="n"/>
       <c r="AT25" s="67" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="53" t="inlineStr">
+      <c r="A26" s="68" t="inlineStr">
         <is>
           <t>PS5-03-12 - FZ-12 - Power Generation Building - Engine Bay 4</t>
         </is>
@@ -4283,14 +4524,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP26" s="65" t="inlineStr"/>
-      <c r="AQ26" s="65" t="inlineStr"/>
-      <c r="AR26" s="23" t="inlineStr"/>
+      <c r="AP26" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ26" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR26" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS26" s="23" t="n"/>
       <c r="AT26" s="67" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="53" t="inlineStr">
+      <c r="A27" s="68" t="inlineStr">
         <is>
           <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
         </is>
@@ -4401,14 +4654,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP27" s="65" t="inlineStr"/>
-      <c r="AQ27" s="65" t="inlineStr"/>
-      <c r="AR27" s="23" t="inlineStr"/>
+      <c r="AP27" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ27" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR27" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS27" s="23" t="n"/>
       <c r="AT27" s="67" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="68" t="inlineStr">
+      <c r="A28" s="53" t="inlineStr">
         <is>
           <t>PS5-03-14 - FZ-14 - Power Generation Building - Switchgear Room</t>
         </is>
@@ -4515,14 +4780,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP28" s="65" t="inlineStr"/>
-      <c r="AQ28" s="65" t="inlineStr"/>
-      <c r="AR28" s="23" t="inlineStr"/>
+      <c r="AP28" s="65" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AQ28" s="65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AR28" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AS28" s="23" t="n"/>
       <c r="AT28" s="67" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="68" t="inlineStr">
+      <c r="A29" s="53" t="inlineStr">
         <is>
           <t>PS5-03-15 - FZ-15 - Power Generation Building - Generator Room 1</t>
         </is>
@@ -4629,14 +4906,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP29" s="65" t="inlineStr"/>
-      <c r="AQ29" s="65" t="inlineStr"/>
-      <c r="AR29" s="23" t="inlineStr"/>
+      <c r="AP29" s="65" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AQ29" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR29" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS29" s="23" t="n"/>
       <c r="AT29" s="67" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="68" t="inlineStr">
+      <c r="A30" s="53" t="inlineStr">
         <is>
           <t>PS5-03-16 - FZ-16 - Power Generation Building - Generator Room 2</t>
         </is>
@@ -4743,14 +5032,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP30" s="65" t="inlineStr"/>
-      <c r="AQ30" s="65" t="inlineStr"/>
-      <c r="AR30" s="23" t="inlineStr"/>
+      <c r="AP30" s="65" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AQ30" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR30" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS30" s="23" t="n"/>
       <c r="AT30" s="67" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="68" t="inlineStr">
+      <c r="A31" s="53" t="inlineStr">
         <is>
           <t>PS5-03-17 - FZ-17 - Power Generation Building - Generator Room 3</t>
         </is>
@@ -4857,14 +5158,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP31" s="65" t="inlineStr"/>
-      <c r="AQ31" s="65" t="inlineStr"/>
-      <c r="AR31" s="23" t="inlineStr"/>
+      <c r="AP31" s="65" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AQ31" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR31" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS31" s="23" t="n"/>
       <c r="AT31" s="67" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="68" t="inlineStr">
+      <c r="A32" s="53" t="inlineStr">
         <is>
           <t>PS5-03-18 - FZ-18 - Power Generation Building - Generator Room 4</t>
         </is>
@@ -4971,14 +5284,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP32" s="65" t="inlineStr"/>
-      <c r="AQ32" s="65" t="inlineStr"/>
-      <c r="AR32" s="23" t="inlineStr"/>
+      <c r="AP32" s="65" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AQ32" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR32" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS32" s="23" t="n"/>
       <c r="AT32" s="67" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="68" t="inlineStr">
+      <c r="A33" s="53" t="inlineStr">
         <is>
           <t>PS5-03-19 - FZ-19 - Power Generation Building - Battery Room</t>
         </is>
@@ -5085,14 +5410,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP33" s="65" t="inlineStr"/>
-      <c r="AQ33" s="65" t="inlineStr"/>
-      <c r="AR33" s="23" t="inlineStr"/>
+      <c r="AP33" s="65" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AQ33" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR33" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS33" s="23" t="n"/>
       <c r="AT33" s="67" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="53" t="inlineStr">
+      <c r="A34" s="68" t="inlineStr">
         <is>
           <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
         </is>
@@ -5199,14 +5536,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP34" s="65" t="inlineStr"/>
-      <c r="AQ34" s="65" t="inlineStr"/>
-      <c r="AR34" s="23" t="inlineStr"/>
+      <c r="AP34" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ34" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR34" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS34" s="23" t="n"/>
       <c r="AT34" s="67" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="68" t="inlineStr">
+      <c r="A35" s="53" t="inlineStr">
         <is>
           <t>PS5-03-21 - FZ-21 - Power Generation Building - Air Handling Unit</t>
         </is>
@@ -5309,14 +5658,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP35" s="65" t="inlineStr"/>
-      <c r="AQ35" s="65" t="inlineStr"/>
-      <c r="AR35" s="23" t="inlineStr"/>
+      <c r="AP35" s="65" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AQ35" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR35" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS35" s="23" t="n"/>
       <c r="AT35" s="67" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="68" t="inlineStr">
+      <c r="A36" s="53" t="inlineStr">
         <is>
           <t>PS5-03-22 - FZ-G1 - Guard House</t>
         </is>
@@ -5419,14 +5780,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP36" s="65" t="inlineStr"/>
-      <c r="AQ36" s="65" t="inlineStr"/>
-      <c r="AR36" s="23" t="inlineStr"/>
+      <c r="AP36" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ36" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR36" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS36" s="23" t="n"/>
       <c r="AT36" s="67" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="68" t="inlineStr">
+      <c r="A37" s="53" t="inlineStr">
         <is>
           <t>PS5-03-23 - FZ-E1 to E3 - EITS Building</t>
         </is>
@@ -5510,7 +5883,7 @@
       <c r="AT37" s="67" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="68" t="inlineStr">
+      <c r="A38" s="53" t="inlineStr">
         <is>
           <t>PS5-03-24 - FZ - Office and Facilities Building</t>
         </is>
@@ -5613,14 +5986,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP38" s="65" t="inlineStr"/>
-      <c r="AQ38" s="65" t="inlineStr"/>
-      <c r="AR38" s="23" t="inlineStr"/>
+      <c r="AP38" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ38" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR38" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS38" s="23" t="n"/>
       <c r="AT38" s="67" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="68" t="inlineStr">
+      <c r="A39" s="53" t="inlineStr">
         <is>
           <t>PS5-03-25 - FZ - Workshop &amp; Warehouse</t>
         </is>
@@ -5723,14 +6108,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP39" s="65" t="inlineStr"/>
-      <c r="AQ39" s="65" t="inlineStr"/>
-      <c r="AR39" s="23" t="inlineStr"/>
+      <c r="AP39" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ39" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR39" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS39" s="23" t="n"/>
       <c r="AT39" s="67" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="68" t="inlineStr">
+      <c r="A40" s="53" t="inlineStr">
         <is>
           <t>PS5-04-01 - Office Building PCS System</t>
         </is>
@@ -5814,7 +6211,7 @@
       <c r="AT40" s="67" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="68" t="inlineStr">
+      <c r="A41" s="53" t="inlineStr">
         <is>
           <t>PS5-04-02 - Office Building SIS/FGS System</t>
         </is>
@@ -5917,7 +6314,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP41" s="65" t="inlineStr"/>
+      <c r="AP41" s="65" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="AQ41" s="65" t="inlineStr">
         <is>
           <t>3</t>
@@ -5932,7 +6333,7 @@
       <c r="AT41" s="67" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="68" t="inlineStr">
+      <c r="A42" s="53" t="inlineStr">
         <is>
           <t>PS5-04-03 - 33kV ICSS System</t>
         </is>
@@ -6016,7 +6417,7 @@
       <c r="AT42" s="67" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="68" t="inlineStr">
+      <c r="A43" s="53" t="inlineStr">
         <is>
           <t>PS5-04-04 - 33kV PCS System</t>
         </is>
@@ -6100,7 +6501,7 @@
       <c r="AT43" s="67" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="68" t="inlineStr">
+      <c r="A44" s="53" t="inlineStr">
         <is>
           <t>PS5-04-05 - 33kV SIS/FGS System</t>
         </is>
@@ -6293,9 +6694,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP45" s="65" t="inlineStr"/>
-      <c r="AQ45" s="65" t="inlineStr"/>
-      <c r="AR45" s="23" t="inlineStr"/>
+      <c r="AP45" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ45" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR45" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS45" s="23" t="n"/>
       <c r="AT45" s="67" t="inlineStr"/>
     </row>
@@ -6407,14 +6820,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP46" s="65" t="inlineStr"/>
-      <c r="AQ46" s="65" t="inlineStr"/>
-      <c r="AR46" s="23" t="inlineStr"/>
+      <c r="AP46" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ46" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR46" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS46" s="23" t="n"/>
       <c r="AT46" s="67" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="68" t="inlineStr">
+      <c r="A47" s="53" t="inlineStr">
         <is>
           <t>PS5-06-01 - AC UPS - EITS Building</t>
         </is>
@@ -6498,7 +6923,7 @@
       <c r="AT47" s="67" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="53" t="inlineStr">
+      <c r="A48" s="68" t="inlineStr">
         <is>
           <t>PS5-06-02 - AC UPS - Power Generator Building</t>
         </is>
@@ -6609,14 +7034,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP48" s="65" t="inlineStr"/>
-      <c r="AQ48" s="65" t="inlineStr"/>
-      <c r="AR48" s="23" t="inlineStr"/>
+      <c r="AP48" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ48" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR48" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS48" s="23" t="n"/>
       <c r="AT48" s="67" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="68" t="inlineStr">
+      <c r="A49" s="53" t="inlineStr">
         <is>
           <t>PS5-06-03 - AC UPS - Office &amp; Facilities Building</t>
         </is>
@@ -6719,14 +7156,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP49" s="65" t="inlineStr"/>
-      <c r="AQ49" s="65" t="inlineStr"/>
-      <c r="AR49" s="23" t="inlineStr"/>
+      <c r="AP49" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ49" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR49" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS49" s="23" t="n"/>
       <c r="AT49" s="67" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="68" t="inlineStr">
+      <c r="A50" s="53" t="inlineStr">
         <is>
           <t>PS5-06-04 - AC UPS - Guard House</t>
         </is>
@@ -6829,14 +7278,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP50" s="65" t="inlineStr"/>
-      <c r="AQ50" s="65" t="inlineStr"/>
-      <c r="AR50" s="23" t="inlineStr"/>
+      <c r="AP50" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ50" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR50" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS50" s="23" t="n"/>
       <c r="AT50" s="67" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="68" t="inlineStr">
+      <c r="A51" s="53" t="inlineStr">
         <is>
           <t>PS5-06-05 - AC UPS - Workshop &amp; Warehouse</t>
         </is>
@@ -6939,14 +7400,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP51" s="65" t="inlineStr"/>
-      <c r="AQ51" s="65" t="inlineStr"/>
-      <c r="AR51" s="23" t="inlineStr"/>
+      <c r="AP51" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ51" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR51" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS51" s="23" t="n"/>
       <c r="AT51" s="67" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="68" t="inlineStr">
+      <c r="A52" s="53" t="inlineStr">
         <is>
           <t>PS5-08-01</t>
         </is>
@@ -6978,9 +7451,9 @@
         </is>
       </c>
       <c r="H52" s="24" t="inlineStr"/>
-      <c r="I52" s="70" t="inlineStr">
-        <is>
-          <t>36%</t>
+      <c r="I52" s="75" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="J52" s="55" t="n">
@@ -7005,28 +7478,28 @@
         <v>0</v>
       </c>
       <c r="Q52" s="62" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="R52" s="62" t="n">
-        <v>82</v>
-      </c>
-      <c r="S52" s="72" t="inlineStr">
-        <is>
-          <t>36%</t>
+        <v>0</v>
+      </c>
+      <c r="S52" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="AH52" s="28" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="AI52" s="23" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="AJ52" s="23" t="n">
-        <v>148</v>
-      </c>
-      <c r="AK52" s="25" t="inlineStr">
-        <is>
-          <t>36%</t>
+        <v>0</v>
+      </c>
+      <c r="AK52" s="76" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="AL52" s="23" t="inlineStr">
@@ -7049,22 +7522,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP52" s="65" t="inlineStr"/>
+      <c r="AP52" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ52" s="65" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR52" s="23" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS52" s="23" t="n"/>
       <c r="AT52" s="67" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="68" t="inlineStr">
+      <c r="A53" s="53" t="inlineStr">
         <is>
           <t>PS5-08-01a - PAGA (Required for SU)</t>
         </is>
@@ -7080,22 +7557,22 @@
         </is>
       </c>
       <c r="H53" s="24" t="inlineStr"/>
-      <c r="I53" s="70" t="inlineStr">
-        <is>
-          <t>20%</t>
+      <c r="I53" s="69" t="inlineStr">
+        <is>
+          <t>74%</t>
         </is>
       </c>
       <c r="J53" s="55" t="n">
         <v>0</v>
       </c>
       <c r="K53" s="56" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="L53" s="57" t="n">
         <v>0</v>
       </c>
       <c r="M53" s="58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N53" s="59" t="n">
         <v>0</v>
@@ -7107,28 +7584,28 @@
         <v>0</v>
       </c>
       <c r="Q53" s="62" t="n">
-        <v>313</v>
+        <v>96</v>
       </c>
       <c r="R53" s="62" t="n">
         <v>71</v>
       </c>
-      <c r="S53" s="72" t="inlineStr">
-        <is>
-          <t>23%</t>
+      <c r="S53" s="77" t="inlineStr">
+        <is>
+          <t>74%</t>
         </is>
       </c>
       <c r="AH53" s="28" t="n">
-        <v>388</v>
+        <v>96</v>
       </c>
       <c r="AI53" s="23" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="AJ53" s="23" t="n">
-        <v>310</v>
-      </c>
-      <c r="AK53" s="25" t="inlineStr">
-        <is>
-          <t>20%</t>
+        <v>25</v>
+      </c>
+      <c r="AK53" s="26" t="inlineStr">
+        <is>
+          <t>74%</t>
         </is>
       </c>
       <c r="AL53" s="23" t="n">
@@ -7148,7 +7625,7 @@
       <c r="AT53" s="67" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="68" t="inlineStr">
+      <c r="A54" s="53" t="inlineStr">
         <is>
           <t>PS5-08-01b - PAGA (Not required for SU)</t>
         </is>
@@ -7166,7 +7643,7 @@
       <c r="H54" s="24" t="inlineStr"/>
       <c r="I54" s="70" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="J54" s="55" t="n">
@@ -7191,28 +7668,28 @@
         <v>0</v>
       </c>
       <c r="Q54" s="62" t="n">
-        <v>414</v>
+        <v>134</v>
       </c>
       <c r="R54" s="62" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="S54" s="72" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="AH54" s="28" t="n">
-        <v>414</v>
+        <v>134</v>
       </c>
       <c r="AI54" s="23" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="AJ54" s="23" t="n">
-        <v>358</v>
+        <v>123</v>
       </c>
       <c r="AK54" s="25" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="AL54" s="23" t="n">
@@ -7232,7 +7709,7 @@
       <c r="AT54" s="67" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="68" t="inlineStr">
+      <c r="A55" s="53" t="inlineStr">
         <is>
           <t>PS5-08-03 - Telephone</t>
         </is>
@@ -7335,7 +7812,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP55" s="65" t="inlineStr"/>
+      <c r="AP55" s="65" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="AQ55" s="65" t="inlineStr">
         <is>
           <t>7</t>
@@ -7350,7 +7831,7 @@
       <c r="AT55" s="67" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="68" t="inlineStr">
+      <c r="A56" s="53" t="inlineStr">
         <is>
           <t>PS5-08-04 - Hotline</t>
         </is>
@@ -7434,7 +7915,7 @@
       <c r="AT56" s="67" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="68" t="inlineStr">
+      <c r="A57" s="53" t="inlineStr">
         <is>
           <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
         </is>
@@ -7518,7 +7999,7 @@
       <c r="AT57" s="67" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="68" t="inlineStr">
+      <c r="A58" s="53" t="inlineStr">
         <is>
           <t>PS5-08-11 - Corporate LAN  (SIE)</t>
         </is>
@@ -7621,7 +8102,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP58" s="65" t="inlineStr"/>
+      <c r="AP58" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ58" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -7636,7 +8121,7 @@
       <c r="AT58" s="67" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="68" t="inlineStr">
+      <c r="A59" s="53" t="inlineStr">
         <is>
           <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
         </is>
@@ -7739,7 +8224,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP59" s="65" t="inlineStr"/>
+      <c r="AP59" s="65" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="AQ59" s="65" t="inlineStr">
         <is>
           <t>9</t>
@@ -7754,7 +8243,7 @@
       <c r="AT59" s="67" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="68" t="inlineStr">
+      <c r="A60" s="53" t="inlineStr">
         <is>
           <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
         </is>
@@ -7857,7 +8346,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP60" s="65" t="inlineStr"/>
+      <c r="AP60" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ60" s="65" t="inlineStr">
         <is>
           <t>13</t>
@@ -7872,7 +8365,7 @@
       <c r="AT60" s="67" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="68" t="inlineStr">
+      <c r="A61" s="53" t="inlineStr">
         <is>
           <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
         </is>
@@ -7975,7 +8468,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP61" s="65" t="inlineStr"/>
+      <c r="AP61" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ61" s="65" t="inlineStr">
         <is>
           <t>12</t>
@@ -7990,7 +8487,7 @@
       <c r="AT61" s="67" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="68" t="inlineStr">
+      <c r="A62" s="53" t="inlineStr">
         <is>
           <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
         </is>
@@ -8093,7 +8590,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP62" s="65" t="inlineStr"/>
+      <c r="AP62" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ62" s="65" t="inlineStr">
         <is>
           <t>9</t>
@@ -8108,7 +8609,7 @@
       <c r="AT62" s="67" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="68" t="inlineStr">
+      <c r="A63" s="53" t="inlineStr">
         <is>
           <t>PS5-08-23 - VHF Trunk Radio System</t>
         </is>
@@ -8211,7 +8712,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP63" s="65" t="inlineStr"/>
+      <c r="AP63" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ63" s="65" t="inlineStr">
         <is>
           <t>11</t>
@@ -8226,7 +8731,7 @@
       <c r="AT63" s="67" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="68" t="inlineStr">
+      <c r="A64" s="53" t="inlineStr">
         <is>
           <t>PS5-08-34 - Satphone</t>
         </is>
@@ -8329,7 +8834,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP64" s="65" t="inlineStr"/>
+      <c r="AP64" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ64" s="65" t="inlineStr">
         <is>
           <t>4</t>
@@ -8344,7 +8853,7 @@
       <c r="AT64" s="67" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="68" t="inlineStr">
+      <c r="A65" s="53" t="inlineStr">
         <is>
           <t>PS5-08-35 - Optical Transport Network</t>
         </is>
@@ -8392,7 +8901,7 @@
       <c r="R65" s="62" t="n">
         <v>40</v>
       </c>
-      <c r="S65" s="75" t="inlineStr">
+      <c r="S65" s="77" t="inlineStr">
         <is>
           <t>87%</t>
         </is>
@@ -8428,7 +8937,7 @@
       <c r="AT65" s="67" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="68" t="inlineStr">
+      <c r="A66" s="53" t="inlineStr">
         <is>
           <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
         </is>
@@ -8521,7 +9030,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AN66" s="64" t="inlineStr">
+      <c r="AN66" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8531,14 +9040,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP66" s="65" t="inlineStr"/>
-      <c r="AQ66" s="65" t="inlineStr"/>
-      <c r="AR66" s="23" t="inlineStr"/>
+      <c r="AP66" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ66" s="65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AR66" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AS66" s="23" t="n"/>
       <c r="AT66" s="67" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="68" t="inlineStr">
+      <c r="A67" s="53" t="inlineStr">
         <is>
           <t>PS5-08-51 - Entertainment</t>
         </is>
@@ -8641,7 +9162,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP67" s="65" t="inlineStr"/>
+      <c r="AP67" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ67" s="65" t="inlineStr">
         <is>
           <t>18</t>
@@ -8656,7 +9181,7 @@
       <c r="AT67" s="67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="68" t="inlineStr">
+      <c r="A68" s="53" t="inlineStr">
         <is>
           <t>PS5-08-52a - Process &amp; Security CCTV (Required for SU)</t>
         </is>
@@ -8674,14 +9199,14 @@
       <c r="H68" s="24" t="inlineStr"/>
       <c r="I68" s="70" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="J68" s="55" t="n">
         <v>0</v>
       </c>
       <c r="K68" s="56" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="L68" s="57" t="n">
         <v>0</v>
@@ -8699,28 +9224,28 @@
         <v>0</v>
       </c>
       <c r="Q68" s="62" t="n">
-        <v>157</v>
+        <v>50</v>
       </c>
       <c r="R68" s="62" t="n">
+        <v>12</v>
+      </c>
+      <c r="S68" s="72" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="AH68" s="28" t="n">
+        <v>51</v>
+      </c>
+      <c r="AI68" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ68" s="23" t="n">
         <v>39</v>
       </c>
-      <c r="S68" s="72" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="AH68" s="28" t="n">
-        <v>232</v>
-      </c>
-      <c r="AI68" s="23" t="n">
-        <v>39</v>
-      </c>
-      <c r="AJ68" s="23" t="n">
-        <v>193</v>
-      </c>
       <c r="AK68" s="25" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="AL68" s="23" t="n">
@@ -8740,7 +9265,7 @@
       <c r="AT68" s="67" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="68" t="inlineStr">
+      <c r="A69" s="53" t="inlineStr">
         <is>
           <t>PS5-08-52b - Process &amp; Security CCTV (Not required for SU)</t>
         </is>
@@ -8758,14 +9283,14 @@
       <c r="H69" s="24" t="inlineStr"/>
       <c r="I69" s="70" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="J69" s="55" t="n">
         <v>0</v>
       </c>
       <c r="K69" s="56" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L69" s="57" t="n">
         <v>0</v>
@@ -8783,28 +9308,28 @@
         <v>0</v>
       </c>
       <c r="Q69" s="62" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="R69" s="62" t="n">
         <v>10</v>
       </c>
       <c r="S69" s="72" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="AH69" s="28" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="AI69" s="23" t="n">
         <v>10</v>
       </c>
       <c r="AJ69" s="23" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="AK69" s="25" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="AL69" s="23" t="n">
@@ -8824,7 +9349,7 @@
       <c r="AT69" s="67" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="68" t="inlineStr">
+      <c r="A70" s="53" t="inlineStr">
         <is>
           <t>PS5-08-55 - Videoconference</t>
         </is>
@@ -8908,7 +9433,7 @@
       <c r="AT70" s="67" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="68" t="inlineStr">
+      <c r="A71" s="53" t="inlineStr">
         <is>
           <t>PS5-08-61 - Meteocean</t>
         </is>
@@ -9011,7 +9536,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP71" s="65" t="inlineStr"/>
+      <c r="AP71" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ71" s="65" t="inlineStr">
         <is>
           <t>10</t>
@@ -9026,7 +9555,7 @@
       <c r="AT71" s="67" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="68" t="inlineStr">
+      <c r="A72" s="53" t="inlineStr">
         <is>
           <t>PS5-08-71 - Structured Cabling (CAT6)</t>
         </is>
@@ -9129,7 +9658,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP72" s="65" t="inlineStr"/>
+      <c r="AP72" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ72" s="65" t="inlineStr">
         <is>
           <t>240</t>
@@ -9144,7 +9677,7 @@
       <c r="AT72" s="67" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="68" t="inlineStr">
+      <c r="A73" s="53" t="inlineStr">
         <is>
           <t>PS5-08-72 - Structured Cabling (FO)</t>
         </is>
@@ -9247,7 +9780,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP73" s="65" t="inlineStr"/>
+      <c r="AP73" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ73" s="65" t="inlineStr">
         <is>
           <t>6</t>
@@ -9262,7 +9799,7 @@
       <c r="AT73" s="67" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="68" t="inlineStr">
+      <c r="A74" s="53" t="inlineStr">
         <is>
           <t>PS5-08-81 - Guard tour</t>
         </is>
@@ -9346,7 +9883,7 @@
       <c r="AT74" s="67" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="68" t="inlineStr">
+      <c r="A75" s="53" t="inlineStr">
         <is>
           <t>PS5-08-82 - Key Management</t>
         </is>
@@ -9430,7 +9967,7 @@
       <c r="AT75" s="67" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="68" t="inlineStr">
+      <c r="A76" s="53" t="inlineStr">
         <is>
           <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
         </is>
@@ -9533,14 +10070,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP76" s="65" t="inlineStr"/>
-      <c r="AQ76" s="65" t="inlineStr"/>
-      <c r="AR76" s="23" t="inlineStr"/>
+      <c r="AP76" s="65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ76" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR76" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS76" s="23" t="n"/>
       <c r="AT76" s="67" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="68" t="inlineStr">
+      <c r="A77" s="53" t="inlineStr">
         <is>
           <t>PS5-08-85</t>
         </is>
@@ -9572,16 +10121,16 @@
         </is>
       </c>
       <c r="H77" s="24" t="inlineStr"/>
-      <c r="I77" s="70" t="inlineStr">
-        <is>
-          <t>16%</t>
+      <c r="I77" s="69" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="J77" s="55" t="n">
         <v>0</v>
       </c>
       <c r="K77" s="56" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L77" s="57" t="n">
         <v>0</v>
@@ -9599,28 +10148,28 @@
         <v>0</v>
       </c>
       <c r="Q77" s="62" t="n">
-        <v>245</v>
+        <v>2</v>
       </c>
       <c r="R77" s="62" t="n">
-        <v>41</v>
-      </c>
-      <c r="S77" s="72" t="inlineStr">
-        <is>
-          <t>17%</t>
+        <v>1</v>
+      </c>
+      <c r="S77" s="77" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="AH77" s="28" t="n">
-        <v>251</v>
+        <v>2</v>
       </c>
       <c r="AI77" s="23" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="AJ77" s="23" t="n">
-        <v>210</v>
-      </c>
-      <c r="AK77" s="25" t="inlineStr">
-        <is>
-          <t>16%</t>
+        <v>1</v>
+      </c>
+      <c r="AK77" s="26" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="AL77" s="23" t="inlineStr">
@@ -9628,7 +10177,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM77" s="23" t="inlineStr">
+      <c r="AM77" s="64" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9643,14 +10192,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP77" s="65" t="inlineStr"/>
-      <c r="AQ77" s="65" t="inlineStr"/>
-      <c r="AR77" s="23" t="inlineStr"/>
+      <c r="AP77" s="65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AQ77" s="65" t="inlineStr">
+        <is>
+          <t>-208</t>
+        </is>
+      </c>
+      <c r="AR77" s="23" t="inlineStr">
+        <is>
+          <t>-208</t>
+        </is>
+      </c>
       <c r="AS77" s="23" t="n"/>
       <c r="AT77" s="67" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="68" t="inlineStr">
+      <c r="A78" s="53" t="inlineStr">
         <is>
           <t>PS5-08-85a - Access Control, POB &amp; e-Mustering (Required for SU)</t>
         </is>
@@ -9668,20 +10229,20 @@
       <c r="H78" s="24" t="inlineStr"/>
       <c r="I78" s="70" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="J78" s="55" t="n">
         <v>0</v>
       </c>
       <c r="K78" s="56" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L78" s="57" t="n">
         <v>0</v>
       </c>
       <c r="M78" s="58" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="N78" s="59" t="n">
         <v>0</v>
@@ -9693,28 +10254,28 @@
         <v>0</v>
       </c>
       <c r="Q78" s="62" t="n">
-        <v>294</v>
+        <v>92</v>
       </c>
       <c r="R78" s="62" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="S78" s="72" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="AH78" s="28" t="n">
-        <v>345</v>
+        <v>92</v>
       </c>
       <c r="AI78" s="23" t="n">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="AJ78" s="23" t="n">
-        <v>255</v>
+        <v>74</v>
       </c>
       <c r="AK78" s="25" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="AL78" s="23" t="n">
@@ -9734,7 +10295,7 @@
       <c r="AT78" s="67" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="68" t="inlineStr">
+      <c r="A79" s="53" t="inlineStr">
         <is>
           <t>PS5-08-85b - Access Control, POB &amp; e-Mustering (Not required for SU)</t>
         </is>
@@ -9752,14 +10313,14 @@
       <c r="H79" s="24" t="inlineStr"/>
       <c r="I79" s="70" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="J79" s="55" t="n">
         <v>0</v>
       </c>
       <c r="K79" s="56" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="L79" s="57" t="n">
         <v>0</v>
@@ -9777,28 +10338,28 @@
         <v>0</v>
       </c>
       <c r="Q79" s="62" t="n">
-        <v>427</v>
+        <v>151</v>
       </c>
       <c r="R79" s="62" t="n">
         <v>22</v>
       </c>
       <c r="S79" s="72" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="AH79" s="28" t="n">
-        <v>451</v>
+        <v>157</v>
       </c>
       <c r="AI79" s="23" t="n">
         <v>22</v>
       </c>
       <c r="AJ79" s="23" t="n">
-        <v>429</v>
+        <v>135</v>
       </c>
       <c r="AK79" s="25" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="AL79" s="23" t="n">
@@ -9818,7 +10379,7 @@
       <c r="AT79" s="67" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="68" t="inlineStr">
+      <c r="A80" s="53" t="inlineStr">
         <is>
           <t>PS5-08-86 - Integrated Security Management System</t>
         </is>
@@ -9902,7 +10463,7 @@
       <c r="AT80" s="67" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="68" t="inlineStr">
+      <c r="A81" s="53" t="inlineStr">
         <is>
           <t>PS5-08-92 - Telecom Mast</t>
         </is>
@@ -9986,7 +10547,7 @@
       <c r="AT81" s="67" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="68" t="inlineStr">
+      <c r="A82" s="53" t="inlineStr">
         <is>
           <t>PS5-08-93 - Telecom Monitoring System</t>
         </is>
@@ -10089,7 +10650,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP82" s="65" t="inlineStr"/>
+      <c r="AP82" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ82" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -10104,7 +10669,7 @@
       <c r="AT82" s="67" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="68" t="inlineStr">
+      <c r="A83" s="53" t="inlineStr">
         <is>
           <t>PS5-09-01 - HVAC for Office and Facilities building</t>
         </is>
@@ -10207,14 +10772,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP83" s="65" t="inlineStr"/>
-      <c r="AQ83" s="65" t="inlineStr"/>
-      <c r="AR83" s="23" t="inlineStr"/>
+      <c r="AP83" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ83" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR83" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS83" s="23" t="n"/>
       <c r="AT83" s="67" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="68" t="inlineStr">
+      <c r="A84" s="53" t="inlineStr">
         <is>
           <t>PS5-09-02 - HVAC for Guard House</t>
         </is>
@@ -10317,14 +10894,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP84" s="65" t="inlineStr"/>
-      <c r="AQ84" s="65" t="inlineStr"/>
-      <c r="AR84" s="23" t="inlineStr"/>
+      <c r="AP84" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ84" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR84" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS84" s="23" t="n"/>
       <c r="AT84" s="67" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="68" t="inlineStr">
+      <c r="A85" s="53" t="inlineStr">
         <is>
           <t>PS5-09-03 - HVAC for Generator Building</t>
         </is>
@@ -10362,7 +10951,7 @@
       <c r="H85" s="24" t="inlineStr"/>
       <c r="I85" s="70" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="J85" s="55" t="n">
@@ -10401,14 +10990,14 @@
         <v>1106</v>
       </c>
       <c r="AI85" s="23" t="n">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="AJ85" s="23" t="n">
-        <v>944</v>
+        <v>912</v>
       </c>
       <c r="AK85" s="25" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="AL85" s="64" t="inlineStr">
@@ -10431,22 +11020,26 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AP85" s="65" t="inlineStr"/>
+      <c r="AP85" s="65" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="AQ85" s="65" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>666</t>
         </is>
       </c>
       <c r="AR85" s="23" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>666</t>
         </is>
       </c>
       <c r="AS85" s="23" t="n"/>
       <c r="AT85" s="67" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="68" t="inlineStr">
+      <c r="A86" s="53" t="inlineStr">
         <is>
           <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
         </is>
@@ -10549,14 +11142,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP86" s="65" t="inlineStr"/>
-      <c r="AQ86" s="65" t="inlineStr"/>
-      <c r="AR86" s="23" t="inlineStr"/>
+      <c r="AP86" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ86" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR86" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS86" s="23" t="n"/>
       <c r="AT86" s="67" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="53" t="inlineStr">
+      <c r="A87" s="68" t="inlineStr">
         <is>
           <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
@@ -10659,14 +11264,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP87" s="65" t="inlineStr"/>
-      <c r="AQ87" s="65" t="inlineStr"/>
-      <c r="AR87" s="23" t="inlineStr"/>
+      <c r="AP87" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ87" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR87" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS87" s="23" t="n"/>
       <c r="AT87" s="67" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="68" t="inlineStr">
+      <c r="A88" s="53" t="inlineStr">
         <is>
           <t>PS5-0H-01 - HIPPS</t>
         </is>
@@ -10750,7 +11367,7 @@
       <c r="AT88" s="67" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="68" t="inlineStr">
+      <c r="A89" s="53" t="inlineStr">
         <is>
           <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
         </is>
@@ -10843,7 +11460,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AN89" s="64" t="inlineStr">
+      <c r="AN89" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10853,22 +11470,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AP89" s="65" t="inlineStr"/>
+      <c r="AP89" s="65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AQ89" s="65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR89" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AS89" s="23" t="n"/>
       <c r="AT89" s="67" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="68" t="inlineStr">
+      <c r="A90" s="53" t="inlineStr">
         <is>
           <t>PS5-25-02 - Crude Oil Export Pump A</t>
         </is>
@@ -10971,7 +11592,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP90" s="65" t="inlineStr"/>
+      <c r="AP90" s="65" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="AQ90" s="65" t="inlineStr">
         <is>
           <t>3</t>
@@ -10986,7 +11611,7 @@
       <c r="AT90" s="67" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="68" t="inlineStr">
+      <c r="A91" s="53" t="inlineStr">
         <is>
           <t>PS5-25-03 - Crude Oil Export Pump B</t>
         </is>
@@ -11020,7 +11645,7 @@
       <c r="H91" s="24" t="inlineStr"/>
       <c r="I91" s="54" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="J91" s="55" t="n">
@@ -11059,14 +11684,14 @@
         <v>220</v>
       </c>
       <c r="AI91" s="23" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AJ91" s="23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK91" s="27" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="AL91" s="23" t="inlineStr">
@@ -11089,22 +11714,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP91" s="65" t="inlineStr"/>
+      <c r="AP91" s="65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AQ91" s="65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR91" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AS91" s="23" t="n"/>
       <c r="AT91" s="67" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="68" t="inlineStr">
+      <c r="A92" s="53" t="inlineStr">
         <is>
           <t>PS5-25-04 - Crude Oil Export Pump C</t>
         </is>
@@ -11138,7 +11767,7 @@
       <c r="H92" s="24" t="inlineStr"/>
       <c r="I92" s="54" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="J92" s="55" t="n">
@@ -11177,14 +11806,14 @@
         <v>220</v>
       </c>
       <c r="AI92" s="23" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AJ92" s="23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK92" s="27" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="AL92" s="23" t="inlineStr">
@@ -11207,22 +11836,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP92" s="65" t="inlineStr"/>
+      <c r="AP92" s="65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AQ92" s="65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR92" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AS92" s="23" t="n"/>
       <c r="AT92" s="67" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="53" t="inlineStr">
+      <c r="A93" s="68" t="inlineStr">
         <is>
           <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
         </is>
@@ -11329,14 +11962,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP93" s="65" t="inlineStr"/>
-      <c r="AQ93" s="65" t="inlineStr"/>
-      <c r="AR93" s="23" t="inlineStr"/>
+      <c r="AP93" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ93" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR93" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS93" s="23" t="n"/>
       <c r="AT93" s="67" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="68" t="inlineStr">
+      <c r="A94" s="53" t="inlineStr">
         <is>
           <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
         </is>
@@ -11439,7 +12084,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP94" s="65" t="inlineStr"/>
+      <c r="AP94" s="65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AQ94" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -11454,7 +12103,7 @@
       <c r="AT94" s="67" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="68" t="inlineStr">
+      <c r="A95" s="53" t="inlineStr">
         <is>
           <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
         </is>
@@ -11557,14 +12206,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP95" s="65" t="inlineStr"/>
-      <c r="AQ95" s="65" t="inlineStr"/>
-      <c r="AR95" s="23" t="inlineStr"/>
+      <c r="AP95" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ95" s="65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AR95" s="23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AS95" s="23" t="n"/>
       <c r="AT95" s="67" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="68" t="inlineStr">
+      <c r="A96" s="53" t="inlineStr">
         <is>
           <t>PS5-28-01 - Closed Drain Header 1</t>
         </is>
@@ -11671,22 +12332,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP96" s="65" t="inlineStr"/>
+      <c r="AP96" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ96" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR96" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AS96" s="23" t="n"/>
       <c r="AT96" s="67" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="53" t="inlineStr">
+      <c r="A97" s="68" t="inlineStr">
         <is>
           <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
@@ -11793,14 +12458,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP97" s="65" t="inlineStr"/>
-      <c r="AQ97" s="65" t="inlineStr"/>
-      <c r="AR97" s="23" t="inlineStr"/>
+      <c r="AP97" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ97" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR97" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS97" s="23" t="n"/>
       <c r="AT97" s="67" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="68" t="inlineStr">
+      <c r="A98" s="53" t="inlineStr">
         <is>
           <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
         </is>
@@ -11827,7 +12504,7 @@
       </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="G98" s="28" t="inlineStr">
@@ -11911,14 +12588,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP98" s="65" t="inlineStr"/>
-      <c r="AQ98" s="65" t="inlineStr"/>
-      <c r="AR98" s="23" t="inlineStr"/>
+      <c r="AP98" s="65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AQ98" s="65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AR98" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AS98" s="23" t="n"/>
       <c r="AT98" s="67" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="68" t="inlineStr">
+      <c r="A99" s="53" t="inlineStr">
         <is>
           <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
         </is>
@@ -12029,7 +12718,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP99" s="65" t="inlineStr"/>
+      <c r="AP99" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ99" s="65" t="inlineStr">
         <is>
           <t>4</t>
@@ -12044,7 +12737,7 @@
       <c r="AT99" s="67" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="53" t="inlineStr">
+      <c r="A100" s="68" t="inlineStr">
         <is>
           <t>PS5-28-05 - HP Relief Header</t>
         </is>
@@ -12155,14 +12848,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP100" s="65" t="inlineStr"/>
-      <c r="AQ100" s="65" t="inlineStr"/>
-      <c r="AR100" s="23" t="inlineStr"/>
+      <c r="AP100" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ100" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR100" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS100" s="23" t="n"/>
       <c r="AT100" s="67" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="53" t="inlineStr">
+      <c r="A101" s="68" t="inlineStr">
         <is>
           <t>PS5-28-06 - Relief Drum and Pump</t>
         </is>
@@ -12273,14 +12978,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP101" s="65" t="inlineStr"/>
-      <c r="AQ101" s="65" t="inlineStr"/>
-      <c r="AR101" s="23" t="inlineStr"/>
+      <c r="AP101" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ101" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR101" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS101" s="23" t="n"/>
       <c r="AT101" s="67" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="53" t="inlineStr">
+      <c r="A102" s="68" t="inlineStr">
         <is>
           <t>PS5-28-07 - Open Drains (OD2)</t>
         </is>
@@ -12307,7 +13024,7 @@
       </c>
       <c r="F102" s="23" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="G102" s="28" t="inlineStr">
@@ -12357,10 +13074,10 @@
         <v>278</v>
       </c>
       <c r="AI102" s="23" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AJ102" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK102" s="27" t="inlineStr">
         <is>
@@ -12387,15 +13104,19 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP102" s="65" t="inlineStr"/>
+      <c r="AP102" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ102" s="65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR102" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS102" s="23" t="n"/>
@@ -12513,7 +13234,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP103" s="65" t="inlineStr"/>
+      <c r="AP103" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ103" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -12528,7 +13253,7 @@
       <c r="AT103" s="67" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="68" t="inlineStr">
+      <c r="A104" s="53" t="inlineStr">
         <is>
           <t>PS5-28-09 - Observation Basin</t>
         </is>
@@ -12631,7 +13356,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP104" s="65" t="inlineStr"/>
+      <c r="AP104" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ104" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -12646,7 +13375,7 @@
       <c r="AT104" s="67" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="68" t="inlineStr">
+      <c r="A105" s="53" t="inlineStr">
         <is>
           <t>PS5-28-10 - Oil Skimmer Package</t>
         </is>
@@ -12680,7 +13409,7 @@
       <c r="H105" s="24" t="inlineStr"/>
       <c r="I105" s="70" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J105" s="55" t="n">
@@ -12719,14 +13448,14 @@
         <v>11</v>
       </c>
       <c r="AI105" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ105" s="23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK105" s="25" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="AL105" s="23" t="inlineStr">
@@ -12749,22 +13478,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP105" s="65" t="inlineStr"/>
+      <c r="AP105" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ105" s="65" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR105" s="23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AS105" s="23" t="n"/>
       <c r="AT105" s="67" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="53" t="inlineStr">
+      <c r="A106" s="68" t="inlineStr">
         <is>
           <t>PS5-28-11 - Open Drain Interceptor</t>
         </is>
@@ -12875,14 +13608,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP106" s="65" t="inlineStr"/>
-      <c r="AQ106" s="65" t="inlineStr"/>
-      <c r="AR106" s="23" t="inlineStr"/>
+      <c r="AP106" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ106" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR106" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS106" s="23" t="n"/>
       <c r="AT106" s="67" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="53" t="inlineStr">
+      <c r="A107" s="68" t="inlineStr">
         <is>
           <t>PS5-28-12 - Open Drains (OD3)</t>
         </is>
@@ -12909,7 +13654,7 @@
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="G107" s="28" t="inlineStr">
@@ -12989,9 +13734,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP107" s="65" t="inlineStr"/>
-      <c r="AQ107" s="65" t="inlineStr"/>
-      <c r="AR107" s="23" t="inlineStr"/>
+      <c r="AP107" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ107" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR107" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS107" s="23" t="n"/>
       <c r="AT107" s="67" t="inlineStr"/>
     </row>
@@ -13021,7 +13778,11 @@
           <t>2026-10-15 00:00:00</t>
         </is>
       </c>
-      <c r="F108" s="23" t="inlineStr"/>
+      <c r="F108" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
       <c r="G108" s="28" t="inlineStr">
         <is>
           <t>FULL</t>
@@ -13034,7 +13795,7 @@
       </c>
       <c r="I108" s="54" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J108" s="55" t="n">
@@ -13073,14 +13834,14 @@
         <v>68</v>
       </c>
       <c r="AI108" s="23" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AJ108" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK108" s="27" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="AL108" s="23" t="inlineStr">
@@ -13103,9 +13864,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP108" s="65" t="inlineStr"/>
-      <c r="AQ108" s="65" t="inlineStr"/>
-      <c r="AR108" s="23" t="inlineStr"/>
+      <c r="AP108" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ108" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR108" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS108" s="23" t="n"/>
       <c r="AT108" s="67" t="inlineStr"/>
     </row>
@@ -13152,7 +13925,7 @@
       </c>
       <c r="I109" s="54" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J109" s="55" t="n">
@@ -13191,14 +13964,14 @@
         <v>68</v>
       </c>
       <c r="AI109" s="23" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AJ109" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK109" s="27" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="AL109" s="23" t="inlineStr">
@@ -13221,9 +13994,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP109" s="65" t="inlineStr"/>
-      <c r="AQ109" s="65" t="inlineStr"/>
-      <c r="AR109" s="23" t="inlineStr"/>
+      <c r="AP109" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ109" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR109" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS109" s="23" t="n"/>
       <c r="AT109" s="67" t="inlineStr"/>
     </row>
@@ -13263,10 +14048,14 @@
           <t>FULL</t>
         </is>
       </c>
-      <c r="H110" s="24" t="inlineStr"/>
+      <c r="H110" s="24" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
       <c r="I110" s="54" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J110" s="55" t="n">
@@ -13305,14 +14094,14 @@
         <v>68</v>
       </c>
       <c r="AI110" s="23" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AJ110" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK110" s="27" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="AL110" s="23" t="inlineStr">
@@ -13335,14 +14124,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP110" s="65" t="inlineStr"/>
-      <c r="AQ110" s="65" t="inlineStr"/>
-      <c r="AR110" s="23" t="inlineStr"/>
+      <c r="AP110" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ110" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR110" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS110" s="23" t="n"/>
       <c r="AT110" s="67" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="53" t="inlineStr">
+      <c r="A111" s="68" t="inlineStr">
         <is>
           <t>PS5-28-16 - LP Relief Header</t>
         </is>
@@ -13449,14 +14250,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP111" s="65" t="inlineStr"/>
-      <c r="AQ111" s="65" t="inlineStr"/>
-      <c r="AR111" s="23" t="inlineStr"/>
+      <c r="AP111" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ111" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR111" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS111" s="23" t="n"/>
       <c r="AT111" s="67" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="68" t="inlineStr">
+      <c r="A112" s="53" t="inlineStr">
         <is>
           <t>PS5-28-17 - Reinjection Pump</t>
         </is>
@@ -13483,7 +14296,7 @@
       </c>
       <c r="F112" s="23" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G112" s="28" t="inlineStr">
@@ -13494,7 +14307,7 @@
       <c r="H112" s="24" t="inlineStr"/>
       <c r="I112" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="J112" s="55" t="n">
@@ -13533,14 +14346,14 @@
         <v>83</v>
       </c>
       <c r="AI112" s="23" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AJ112" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK112" s="27" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="AL112" s="23" t="inlineStr">
@@ -13563,22 +14376,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP112" s="65" t="inlineStr"/>
+      <c r="AP112" s="65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AQ112" s="65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR112" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS112" s="23" t="n"/>
       <c r="AT112" s="67" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="68" t="inlineStr">
+      <c r="A113" s="53" t="inlineStr">
         <is>
           <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
         </is>
@@ -13681,7 +14498,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP113" s="65" t="inlineStr"/>
+      <c r="AP113" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ113" s="65" t="inlineStr">
         <is>
           <t>11</t>
@@ -13696,7 +14517,7 @@
       <c r="AT113" s="67" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="68" t="inlineStr">
+      <c r="A114" s="53" t="inlineStr">
         <is>
           <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
         </is>
@@ -13799,7 +14620,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP114" s="65" t="inlineStr"/>
+      <c r="AP114" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ114" s="65" t="inlineStr">
         <is>
           <t>11</t>
@@ -13814,7 +14639,7 @@
       <c r="AT114" s="67" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="68" t="inlineStr">
+      <c r="A115" s="53" t="inlineStr">
         <is>
           <t>PS5-50-03 - Water Pre-Treatment Package</t>
         </is>
@@ -13841,7 +14666,7 @@
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="G115" s="28" t="inlineStr">
@@ -13852,7 +14677,7 @@
       <c r="H115" s="24" t="inlineStr"/>
       <c r="I115" s="69" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="J115" s="55" t="n">
@@ -13891,14 +14716,14 @@
         <v>25</v>
       </c>
       <c r="AI115" s="23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AJ115" s="23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AK115" s="26" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="AL115" s="23" t="inlineStr">
@@ -13921,15 +14746,19 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP115" s="65" t="inlineStr"/>
+      <c r="AP115" s="65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AQ115" s="65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR115" s="23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS115" s="23" t="n"/>
@@ -14047,7 +14876,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP116" s="65" t="inlineStr"/>
+      <c r="AP116" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ116" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -14062,7 +14895,7 @@
       <c r="AT116" s="67" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="53" t="inlineStr">
+      <c r="A117" s="68" t="inlineStr">
         <is>
           <t>PS5-53-02 - Water Distribution Pump A/B</t>
         </is>
@@ -14089,12 +14922,12 @@
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G117" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H117" s="24" t="inlineStr">
@@ -14173,14 +15006,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP117" s="65" t="inlineStr"/>
-      <c r="AQ117" s="65" t="inlineStr"/>
-      <c r="AR117" s="23" t="inlineStr"/>
+      <c r="AP117" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ117" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR117" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS117" s="23" t="n"/>
       <c r="AT117" s="67" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="68" t="inlineStr">
+      <c r="A118" s="53" t="inlineStr">
         <is>
           <t>PS5-53-03 - Water Softener Package</t>
         </is>
@@ -14207,7 +15052,7 @@
       </c>
       <c r="F118" s="23" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="G118" s="28" t="inlineStr">
@@ -14291,7 +15136,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP118" s="65" t="inlineStr"/>
+      <c r="AP118" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ118" s="65" t="inlineStr">
         <is>
           <t>3</t>
@@ -14306,7 +15155,7 @@
       <c r="AT118" s="67" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="68" t="inlineStr">
+      <c r="A119" s="53" t="inlineStr">
         <is>
           <t>PS5-53-04 - Water Treatment Purification Package</t>
         </is>
@@ -14344,7 +15193,7 @@
       <c r="H119" s="24" t="inlineStr"/>
       <c r="I119" s="70" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="J119" s="55" t="n">
@@ -14383,14 +15232,14 @@
         <v>11</v>
       </c>
       <c r="AI119" s="23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AJ119" s="23" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AK119" s="25" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="AL119" s="23" t="inlineStr">
@@ -14413,22 +15262,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP119" s="65" t="inlineStr"/>
+      <c r="AP119" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ119" s="65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR119" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AS119" s="23" t="n"/>
       <c r="AT119" s="67" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="53" t="inlineStr">
+      <c r="A120" s="68" t="inlineStr">
         <is>
           <t>PS5-53-05 - Water Distribution Header</t>
         </is>
@@ -14539,14 +15392,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP120" s="65" t="inlineStr"/>
-      <c r="AQ120" s="65" t="inlineStr"/>
-      <c r="AR120" s="23" t="inlineStr"/>
+      <c r="AP120" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ120" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR120" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS120" s="23" t="n"/>
       <c r="AT120" s="67" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="68" t="inlineStr">
+      <c r="A121" s="53" t="inlineStr">
         <is>
           <t>PS5-53-06 - Water Distribution Consumers</t>
         </is>
@@ -14653,14 +15518,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP121" s="65" t="inlineStr"/>
-      <c r="AQ121" s="65" t="inlineStr"/>
-      <c r="AR121" s="23" t="inlineStr"/>
+      <c r="AP121" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ121" s="65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AR121" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AS121" s="23" t="n"/>
       <c r="AT121" s="67" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="53" t="inlineStr">
+      <c r="A122" s="68" t="inlineStr">
         <is>
           <t>PS5-60-01 - Power Generation Package A</t>
         </is>
@@ -14771,14 +15648,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP122" s="65" t="inlineStr"/>
-      <c r="AQ122" s="65" t="inlineStr"/>
-      <c r="AR122" s="23" t="inlineStr"/>
+      <c r="AP122" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ122" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR122" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS122" s="23" t="n"/>
       <c r="AT122" s="67" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="53" t="inlineStr">
+      <c r="A123" s="68" t="inlineStr">
         <is>
           <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
@@ -14889,8 +15778,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP123" s="65" t="inlineStr"/>
-      <c r="AQ123" s="65" t="inlineStr"/>
+      <c r="AP123" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ123" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AR123" s="23" t="inlineStr">
         <is>
           <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
@@ -14900,7 +15797,7 @@
       <c r="AT123" s="67" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="53" t="inlineStr">
+      <c r="A124" s="68" t="inlineStr">
         <is>
           <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -15011,14 +15908,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP124" s="65" t="inlineStr"/>
-      <c r="AQ124" s="65" t="inlineStr"/>
-      <c r="AR124" s="23" t="inlineStr"/>
+      <c r="AP124" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ124" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR124" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS124" s="23" t="n"/>
       <c r="AT124" s="67" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="53" t="inlineStr">
+      <c r="A125" s="68" t="inlineStr">
         <is>
           <t>PS5-60-04 - Power Generation Package B</t>
         </is>
@@ -15129,14 +16038,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP125" s="65" t="inlineStr"/>
-      <c r="AQ125" s="65" t="inlineStr"/>
-      <c r="AR125" s="23" t="inlineStr"/>
+      <c r="AP125" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ125" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR125" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS125" s="23" t="n"/>
       <c r="AT125" s="67" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="53" t="inlineStr">
+      <c r="A126" s="68" t="inlineStr">
         <is>
           <t>PS5-60-05 - Power Gen Package B (UCP)</t>
         </is>
@@ -15247,14 +16168,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP126" s="65" t="inlineStr"/>
-      <c r="AQ126" s="65" t="inlineStr"/>
-      <c r="AR126" s="23" t="inlineStr"/>
+      <c r="AP126" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ126" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR126" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS126" s="23" t="n"/>
       <c r="AT126" s="67" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="53" t="inlineStr">
+      <c r="A127" s="68" t="inlineStr">
         <is>
           <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -15365,14 +16298,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP127" s="65" t="inlineStr"/>
-      <c r="AQ127" s="65" t="inlineStr"/>
-      <c r="AR127" s="23" t="inlineStr"/>
+      <c r="AP127" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ127" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR127" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS127" s="23" t="n"/>
       <c r="AT127" s="67" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="68" t="inlineStr">
+      <c r="A128" s="53" t="inlineStr">
         <is>
           <t>PS5-60-07 - Power Generation Package C</t>
         </is>
@@ -15483,14 +16428,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP128" s="65" t="inlineStr"/>
-      <c r="AQ128" s="65" t="inlineStr"/>
-      <c r="AR128" s="23" t="inlineStr"/>
+      <c r="AP128" s="65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ128" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR128" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS128" s="23" t="n"/>
       <c r="AT128" s="67" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="53" t="inlineStr">
+      <c r="A129" s="68" t="inlineStr">
         <is>
           <t>PS5-60-08 - Power Gen Package C (UCP)</t>
         </is>
@@ -15601,14 +16558,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP129" s="65" t="inlineStr"/>
-      <c r="AQ129" s="65" t="inlineStr"/>
-      <c r="AR129" s="23" t="inlineStr"/>
+      <c r="AP129" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ129" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR129" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS129" s="23" t="n"/>
       <c r="AT129" s="67" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="53" t="inlineStr">
+      <c r="A130" s="68" t="inlineStr">
         <is>
           <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -15719,14 +16688,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP130" s="65" t="inlineStr"/>
-      <c r="AQ130" s="65" t="inlineStr"/>
-      <c r="AR130" s="23" t="inlineStr"/>
+      <c r="AP130" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ130" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR130" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS130" s="23" t="n"/>
       <c r="AT130" s="67" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="68" t="inlineStr">
+      <c r="A131" s="53" t="inlineStr">
         <is>
           <t>PS5-60-10 - Power Generation Package D</t>
         </is>
@@ -15837,14 +16818,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP131" s="65" t="inlineStr"/>
-      <c r="AQ131" s="65" t="inlineStr"/>
-      <c r="AR131" s="23" t="inlineStr"/>
+      <c r="AP131" s="65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ131" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR131" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS131" s="23" t="n"/>
       <c r="AT131" s="67" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="53" t="inlineStr">
+      <c r="A132" s="68" t="inlineStr">
         <is>
           <t>PS5-60-11 - Power Gen Package D (UCP)</t>
         </is>
@@ -15955,14 +16948,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP132" s="65" t="inlineStr"/>
-      <c r="AQ132" s="65" t="inlineStr"/>
-      <c r="AR132" s="23" t="inlineStr"/>
+      <c r="AP132" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ132" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR132" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS132" s="23" t="n"/>
       <c r="AT132" s="67" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="53" t="inlineStr">
+      <c r="A133" s="68" t="inlineStr">
         <is>
           <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -16073,14 +17078,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP133" s="65" t="inlineStr"/>
-      <c r="AQ133" s="65" t="inlineStr"/>
-      <c r="AR133" s="23" t="inlineStr"/>
+      <c r="AP133" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ133" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR133" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS133" s="23" t="n"/>
       <c r="AT133" s="67" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="53" t="inlineStr">
+      <c r="A134" s="68" t="inlineStr">
         <is>
           <t>PS5-60-13 - Power Generation Package E</t>
         </is>
@@ -16191,14 +17208,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP134" s="65" t="inlineStr"/>
-      <c r="AQ134" s="65" t="inlineStr"/>
-      <c r="AR134" s="23" t="inlineStr"/>
+      <c r="AP134" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ134" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR134" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS134" s="23" t="n"/>
       <c r="AT134" s="67" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="53" t="inlineStr">
+      <c r="A135" s="68" t="inlineStr">
         <is>
           <t>PS5-60-14 - Power Gen Package E (UCP)</t>
         </is>
@@ -16309,14 +17338,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP135" s="65" t="inlineStr"/>
-      <c r="AQ135" s="65" t="inlineStr"/>
-      <c r="AR135" s="23" t="inlineStr"/>
+      <c r="AP135" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ135" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR135" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS135" s="23" t="n"/>
       <c r="AT135" s="67" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="53" t="inlineStr">
+      <c r="A136" s="68" t="inlineStr">
         <is>
           <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -16427,14 +17468,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP136" s="65" t="inlineStr"/>
-      <c r="AQ136" s="65" t="inlineStr"/>
-      <c r="AR136" s="23" t="inlineStr"/>
+      <c r="AP136" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ136" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR136" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS136" s="23" t="n"/>
       <c r="AT136" s="67" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="68" t="inlineStr">
+      <c r="A137" s="53" t="inlineStr">
         <is>
           <t>PS5-60-16 - Power Generation Package F</t>
         </is>
@@ -16545,14 +17598,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP137" s="65" t="inlineStr"/>
-      <c r="AQ137" s="65" t="inlineStr"/>
-      <c r="AR137" s="23" t="inlineStr"/>
+      <c r="AP137" s="65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ137" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR137" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS137" s="23" t="n"/>
       <c r="AT137" s="67" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="53" t="inlineStr">
+      <c r="A138" s="68" t="inlineStr">
         <is>
           <t>PS5-60-17 - Power Gen Package F (UCP)</t>
         </is>
@@ -16663,14 +17728,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP138" s="65" t="inlineStr"/>
-      <c r="AQ138" s="65" t="inlineStr"/>
-      <c r="AR138" s="23" t="inlineStr"/>
+      <c r="AP138" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ138" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR138" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS138" s="23" t="n"/>
       <c r="AT138" s="67" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="53" t="inlineStr">
+      <c r="A139" s="68" t="inlineStr">
         <is>
           <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -16781,14 +17858,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP139" s="65" t="inlineStr"/>
-      <c r="AQ139" s="65" t="inlineStr"/>
-      <c r="AR139" s="23" t="inlineStr"/>
+      <c r="AP139" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ139" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR139" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS139" s="23" t="n"/>
       <c r="AT139" s="67" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="68" t="inlineStr">
+      <c r="A140" s="53" t="inlineStr">
         <is>
           <t>PS5-60-19 - Power Generation Package G</t>
         </is>
@@ -16899,14 +17988,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP140" s="65" t="inlineStr"/>
-      <c r="AQ140" s="65" t="inlineStr"/>
-      <c r="AR140" s="23" t="inlineStr"/>
+      <c r="AP140" s="65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ140" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR140" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS140" s="23" t="n"/>
       <c r="AT140" s="67" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="53" t="inlineStr">
+      <c r="A141" s="68" t="inlineStr">
         <is>
           <t>PS5-60-20 - Power Gen Package G (UCP)</t>
         </is>
@@ -17017,14 +18118,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP141" s="65" t="inlineStr"/>
-      <c r="AQ141" s="65" t="inlineStr"/>
-      <c r="AR141" s="23" t="inlineStr"/>
+      <c r="AP141" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ141" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR141" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS141" s="23" t="n"/>
       <c r="AT141" s="67" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="53" t="inlineStr">
+      <c r="A142" s="68" t="inlineStr">
         <is>
           <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -17135,14 +18248,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP142" s="65" t="inlineStr"/>
-      <c r="AQ142" s="65" t="inlineStr"/>
-      <c r="AR142" s="23" t="inlineStr"/>
+      <c r="AP142" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ142" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR142" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS142" s="23" t="n"/>
       <c r="AT142" s="67" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="68" t="inlineStr">
+      <c r="A143" s="53" t="inlineStr">
         <is>
           <t>PS5-60-22 - Power Gen Master UCP</t>
         </is>
@@ -17272,7 +18397,7 @@
       <c r="AT143" s="67" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="53" t="inlineStr">
+      <c r="A144" s="68" t="inlineStr">
         <is>
           <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
@@ -17379,14 +18504,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP144" s="65" t="inlineStr"/>
-      <c r="AQ144" s="65" t="inlineStr"/>
-      <c r="AR144" s="23" t="inlineStr"/>
+      <c r="AP144" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ144" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR144" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS144" s="23" t="n"/>
       <c r="AT144" s="67" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="68" t="inlineStr">
+      <c r="A145" s="53" t="inlineStr">
         <is>
           <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
         </is>
@@ -17497,14 +18634,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP145" s="65" t="inlineStr"/>
-      <c r="AQ145" s="65" t="inlineStr"/>
-      <c r="AR145" s="23" t="inlineStr"/>
+      <c r="AP145" s="65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ145" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR145" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS145" s="23" t="n"/>
       <c r="AT145" s="67" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="68" t="inlineStr">
+      <c r="A146" s="53" t="inlineStr">
         <is>
           <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
         </is>
@@ -17615,14 +18764,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP146" s="65" t="inlineStr"/>
-      <c r="AQ146" s="65" t="inlineStr"/>
-      <c r="AR146" s="23" t="inlineStr"/>
+      <c r="AP146" s="65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ146" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR146" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS146" s="23" t="n"/>
       <c r="AT146" s="67" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="53" t="inlineStr">
+      <c r="A147" s="68" t="inlineStr">
         <is>
           <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
@@ -17733,14 +18894,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP147" s="65" t="inlineStr"/>
-      <c r="AQ147" s="65" t="inlineStr"/>
-      <c r="AR147" s="23" t="inlineStr"/>
+      <c r="AP147" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ147" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR147" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS147" s="23" t="n"/>
       <c r="AT147" s="67" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="53" t="inlineStr">
+      <c r="A148" s="68" t="inlineStr">
         <is>
           <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
@@ -17851,9 +19024,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP148" s="65" t="inlineStr"/>
-      <c r="AQ148" s="65" t="inlineStr"/>
-      <c r="AR148" s="23" t="inlineStr"/>
+      <c r="AP148" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ148" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR148" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS148" s="23" t="n"/>
       <c r="AT148" s="67" t="inlineStr"/>
     </row>
@@ -17969,14 +19154,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP149" s="65" t="inlineStr"/>
-      <c r="AQ149" s="65" t="inlineStr"/>
-      <c r="AR149" s="23" t="inlineStr"/>
+      <c r="AP149" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ149" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR149" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS149" s="23" t="n"/>
       <c r="AT149" s="67" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="53" t="inlineStr">
+      <c r="A150" s="68" t="inlineStr">
         <is>
           <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
@@ -18087,14 +19284,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP150" s="65" t="inlineStr"/>
-      <c r="AQ150" s="65" t="inlineStr"/>
-      <c r="AR150" s="23" t="inlineStr"/>
+      <c r="AP150" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ150" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR150" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS150" s="23" t="n"/>
       <c r="AT150" s="67" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="53" t="inlineStr">
+      <c r="A151" s="68" t="inlineStr">
         <is>
           <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
@@ -18205,14 +19414,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP151" s="65" t="inlineStr"/>
-      <c r="AQ151" s="65" t="inlineStr"/>
-      <c r="AR151" s="23" t="inlineStr"/>
+      <c r="AP151" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ151" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR151" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS151" s="23" t="n"/>
       <c r="AT151" s="67" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="53" t="inlineStr">
+      <c r="A152" s="68" t="inlineStr">
         <is>
           <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
@@ -18323,14 +19544,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP152" s="65" t="inlineStr"/>
-      <c r="AQ152" s="65" t="inlineStr"/>
-      <c r="AR152" s="23" t="inlineStr"/>
+      <c r="AP152" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ152" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR152" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS152" s="23" t="n"/>
       <c r="AT152" s="67" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="53" t="inlineStr">
+      <c r="A153" s="68" t="inlineStr">
         <is>
           <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
@@ -18441,14 +19674,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP153" s="65" t="inlineStr"/>
-      <c r="AQ153" s="65" t="inlineStr"/>
-      <c r="AR153" s="23" t="inlineStr"/>
+      <c r="AP153" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ153" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR153" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS153" s="23" t="n"/>
       <c r="AT153" s="67" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="53" t="inlineStr">
+      <c r="A154" s="68" t="inlineStr">
         <is>
           <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
@@ -18559,14 +19804,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP154" s="65" t="inlineStr"/>
-      <c r="AQ154" s="65" t="inlineStr"/>
-      <c r="AR154" s="23" t="inlineStr"/>
+      <c r="AP154" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ154" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR154" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS154" s="23" t="n"/>
       <c r="AT154" s="67" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="53" t="inlineStr">
+      <c r="A155" s="68" t="inlineStr">
         <is>
           <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
@@ -18677,9 +19934,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP155" s="65" t="inlineStr"/>
-      <c r="AQ155" s="65" t="inlineStr"/>
-      <c r="AR155" s="23" t="inlineStr"/>
+      <c r="AP155" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ155" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR155" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS155" s="23" t="n"/>
       <c r="AT155" s="67" t="inlineStr"/>
     </row>
@@ -18791,14 +20060,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP156" s="65" t="inlineStr"/>
-      <c r="AQ156" s="65" t="inlineStr"/>
-      <c r="AR156" s="23" t="inlineStr"/>
+      <c r="AP156" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ156" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR156" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS156" s="23" t="n"/>
       <c r="AT156" s="67" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="53" t="inlineStr">
+      <c r="A157" s="68" t="inlineStr">
         <is>
           <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
@@ -18905,14 +20186,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP157" s="65" t="inlineStr"/>
-      <c r="AQ157" s="65" t="inlineStr"/>
-      <c r="AR157" s="23" t="inlineStr"/>
+      <c r="AP157" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ157" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR157" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS157" s="23" t="n"/>
       <c r="AT157" s="67" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="53" t="inlineStr">
+      <c r="A158" s="68" t="inlineStr">
         <is>
           <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
@@ -19023,14 +20316,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP158" s="65" t="inlineStr"/>
-      <c r="AQ158" s="65" t="inlineStr"/>
-      <c r="AR158" s="23" t="inlineStr"/>
+      <c r="AP158" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ158" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR158" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS158" s="23" t="n"/>
       <c r="AT158" s="67" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="53" t="inlineStr">
+      <c r="A159" s="68" t="inlineStr">
         <is>
           <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
@@ -19141,14 +20446,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP159" s="65" t="inlineStr"/>
-      <c r="AQ159" s="65" t="inlineStr"/>
-      <c r="AR159" s="23" t="inlineStr"/>
+      <c r="AP159" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ159" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR159" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS159" s="23" t="n"/>
       <c r="AT159" s="67" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="53" t="inlineStr">
+      <c r="A160" s="68" t="inlineStr">
         <is>
           <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
@@ -19259,14 +20576,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP160" s="65" t="inlineStr"/>
-      <c r="AQ160" s="65" t="inlineStr"/>
-      <c r="AR160" s="23" t="inlineStr"/>
+      <c r="AP160" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ160" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR160" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS160" s="23" t="n"/>
       <c r="AT160" s="67" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="53" t="inlineStr">
+      <c r="A161" s="68" t="inlineStr">
         <is>
           <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
@@ -19377,14 +20706,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP161" s="65" t="inlineStr"/>
-      <c r="AQ161" s="65" t="inlineStr"/>
-      <c r="AR161" s="23" t="inlineStr"/>
+      <c r="AP161" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ161" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR161" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS161" s="23" t="n"/>
       <c r="AT161" s="67" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="53" t="inlineStr">
+      <c r="A162" s="68" t="inlineStr">
         <is>
           <t>PS5-60-41 - Injector Tip Cooling Module G</t>
         </is>
@@ -19495,9 +20836,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP162" s="65" t="inlineStr"/>
-      <c r="AQ162" s="65" t="inlineStr"/>
-      <c r="AR162" s="23" t="inlineStr"/>
+      <c r="AP162" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ162" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR162" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS162" s="23" t="n"/>
       <c r="AT162" s="67" t="inlineStr"/>
     </row>
@@ -19609,14 +20962,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP163" s="65" t="inlineStr"/>
-      <c r="AQ163" s="65" t="inlineStr"/>
-      <c r="AR163" s="23" t="inlineStr"/>
+      <c r="AP163" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ163" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR163" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS163" s="23" t="n"/>
       <c r="AT163" s="67" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="53" t="inlineStr">
+      <c r="A164" s="68" t="inlineStr">
         <is>
           <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
@@ -19723,14 +21088,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP164" s="65" t="inlineStr"/>
-      <c r="AQ164" s="65" t="inlineStr"/>
-      <c r="AR164" s="23" t="inlineStr"/>
+      <c r="AP164" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ164" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR164" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS164" s="23" t="n"/>
       <c r="AT164" s="67" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="53" t="inlineStr">
+      <c r="A165" s="68" t="inlineStr">
         <is>
           <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
@@ -19841,14 +21218,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP165" s="65" t="inlineStr"/>
-      <c r="AQ165" s="65" t="inlineStr"/>
-      <c r="AR165" s="23" t="inlineStr"/>
+      <c r="AP165" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ165" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR165" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS165" s="23" t="n"/>
       <c r="AT165" s="67" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="53" t="inlineStr">
+      <c r="A166" s="68" t="inlineStr">
         <is>
           <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
@@ -19959,14 +21348,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP166" s="65" t="inlineStr"/>
-      <c r="AQ166" s="65" t="inlineStr"/>
-      <c r="AR166" s="23" t="inlineStr"/>
+      <c r="AP166" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ166" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR166" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS166" s="23" t="n"/>
       <c r="AT166" s="67" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="53" t="inlineStr">
+      <c r="A167" s="68" t="inlineStr">
         <is>
           <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
@@ -20077,14 +21478,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP167" s="65" t="inlineStr"/>
-      <c r="AQ167" s="65" t="inlineStr"/>
-      <c r="AR167" s="23" t="inlineStr"/>
+      <c r="AP167" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ167" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR167" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS167" s="23" t="n"/>
       <c r="AT167" s="67" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="53" t="inlineStr">
+      <c r="A168" s="68" t="inlineStr">
         <is>
           <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
@@ -20195,14 +21608,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP168" s="65" t="inlineStr"/>
-      <c r="AQ168" s="65" t="inlineStr"/>
-      <c r="AR168" s="23" t="inlineStr"/>
+      <c r="AP168" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ168" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR168" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS168" s="23" t="n"/>
       <c r="AT168" s="67" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="73" t="inlineStr">
+      <c r="A169" s="68" t="inlineStr">
         <is>
           <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
         </is>
@@ -20232,9 +21657,9 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G169" s="69" t="inlineStr">
-        <is>
-          <t>partial</t>
+      <c r="G169" s="28" t="inlineStr">
+        <is>
+          <t>full</t>
         </is>
       </c>
       <c r="H169" s="24" t="inlineStr">
@@ -20313,14 +21738,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP169" s="65" t="inlineStr"/>
-      <c r="AQ169" s="65" t="inlineStr"/>
-      <c r="AR169" s="23" t="inlineStr"/>
+      <c r="AP169" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ169" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR169" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS169" s="23" t="n"/>
       <c r="AT169" s="67" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="53" t="inlineStr">
+      <c r="A170" s="68" t="inlineStr">
         <is>
           <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
         </is>
@@ -20431,8 +21868,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP170" s="65" t="inlineStr"/>
-      <c r="AQ170" s="65" t="inlineStr"/>
+      <c r="AP170" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ170" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AR170" s="23" t="inlineStr">
         <is>
           <t>OBSERVATION -CLEANING ON PROGRESS</t>
@@ -20442,7 +21887,7 @@
       <c r="AT170" s="67" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="53" t="inlineStr">
+      <c r="A171" s="68" t="inlineStr">
         <is>
           <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
         </is>
@@ -20553,14 +21998,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP171" s="65" t="inlineStr"/>
-      <c r="AQ171" s="65" t="inlineStr"/>
-      <c r="AR171" s="23" t="inlineStr"/>
+      <c r="AP171" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ171" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR171" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS171" s="23" t="n"/>
       <c r="AT171" s="67" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="53" t="inlineStr">
+      <c r="A172" s="68" t="inlineStr">
         <is>
           <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
         </is>
@@ -20671,14 +22128,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP172" s="65" t="inlineStr"/>
-      <c r="AQ172" s="65" t="inlineStr"/>
-      <c r="AR172" s="23" t="inlineStr"/>
+      <c r="AP172" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ172" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR172" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS172" s="23" t="n"/>
       <c r="AT172" s="67" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="53" t="inlineStr">
+      <c r="A173" s="68" t="inlineStr">
         <is>
           <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
         </is>
@@ -20789,14 +22258,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP173" s="65" t="inlineStr"/>
-      <c r="AQ173" s="65" t="inlineStr"/>
-      <c r="AR173" s="23" t="inlineStr"/>
+      <c r="AP173" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ173" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR173" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS173" s="23" t="n"/>
       <c r="AT173" s="67" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="53" t="inlineStr">
+      <c r="A174" s="68" t="inlineStr">
         <is>
           <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
         </is>
@@ -20907,14 +22388,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP174" s="65" t="inlineStr"/>
-      <c r="AQ174" s="65" t="inlineStr"/>
-      <c r="AR174" s="23" t="inlineStr"/>
+      <c r="AP174" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ174" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR174" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS174" s="23" t="n"/>
       <c r="AT174" s="67" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="53" t="inlineStr">
+      <c r="A175" s="68" t="inlineStr">
         <is>
           <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
         </is>
@@ -21025,14 +22518,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP175" s="65" t="inlineStr"/>
-      <c r="AQ175" s="65" t="inlineStr"/>
-      <c r="AR175" s="23" t="inlineStr"/>
+      <c r="AP175" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ175" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR175" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS175" s="23" t="n"/>
       <c r="AT175" s="67" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="53" t="inlineStr">
+      <c r="A176" s="68" t="inlineStr">
         <is>
           <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
         </is>
@@ -21143,14 +22648,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP176" s="65" t="inlineStr"/>
-      <c r="AQ176" s="65" t="inlineStr"/>
-      <c r="AR176" s="23" t="inlineStr"/>
+      <c r="AP176" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ176" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR176" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS176" s="23" t="n"/>
       <c r="AT176" s="67" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="53" t="inlineStr">
+      <c r="A177" s="68" t="inlineStr">
         <is>
           <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
@@ -21261,14 +22778,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP177" s="65" t="inlineStr"/>
-      <c r="AQ177" s="65" t="inlineStr"/>
-      <c r="AR177" s="23" t="inlineStr"/>
+      <c r="AP177" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ177" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR177" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS177" s="23" t="n"/>
       <c r="AT177" s="67" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="53" t="inlineStr">
+      <c r="A178" s="68" t="inlineStr">
         <is>
           <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
         </is>
@@ -21379,14 +22908,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP178" s="65" t="inlineStr"/>
-      <c r="AQ178" s="65" t="inlineStr"/>
-      <c r="AR178" s="23" t="inlineStr"/>
+      <c r="AP178" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ178" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR178" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS178" s="23" t="n"/>
       <c r="AT178" s="67" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="53" t="inlineStr">
+      <c r="A179" s="68" t="inlineStr">
         <is>
           <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
@@ -21497,14 +23038,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP179" s="65" t="inlineStr"/>
-      <c r="AQ179" s="65" t="inlineStr"/>
-      <c r="AR179" s="23" t="inlineStr"/>
+      <c r="AP179" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ179" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR179" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS179" s="23" t="n"/>
       <c r="AT179" s="67" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="53" t="inlineStr">
+      <c r="A180" s="68" t="inlineStr">
         <is>
           <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
         </is>
@@ -21615,14 +23168,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP180" s="65" t="inlineStr"/>
-      <c r="AQ180" s="65" t="inlineStr"/>
-      <c r="AR180" s="23" t="inlineStr"/>
+      <c r="AP180" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ180" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR180" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS180" s="23" t="n"/>
       <c r="AT180" s="67" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="53" t="inlineStr">
+      <c r="A181" s="68" t="inlineStr">
         <is>
           <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
@@ -21733,14 +23298,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP181" s="65" t="inlineStr"/>
-      <c r="AQ181" s="65" t="inlineStr"/>
-      <c r="AR181" s="23" t="inlineStr"/>
+      <c r="AP181" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ181" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR181" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS181" s="23" t="n"/>
       <c r="AT181" s="67" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="53" t="inlineStr">
+      <c r="A182" s="68" t="inlineStr">
         <is>
           <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
         </is>
@@ -21851,14 +23428,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP182" s="65" t="inlineStr"/>
-      <c r="AQ182" s="65" t="inlineStr"/>
-      <c r="AR182" s="23" t="inlineStr"/>
+      <c r="AP182" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ182" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR182" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS182" s="23" t="n"/>
       <c r="AT182" s="67" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="53" t="inlineStr">
+      <c r="A183" s="68" t="inlineStr">
         <is>
           <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
@@ -21969,14 +23558,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP183" s="65" t="inlineStr"/>
-      <c r="AQ183" s="65" t="inlineStr"/>
-      <c r="AR183" s="23" t="inlineStr"/>
+      <c r="AP183" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ183" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR183" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS183" s="23" t="n"/>
       <c r="AT183" s="67" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="53" t="inlineStr">
+      <c r="A184" s="68" t="inlineStr">
         <is>
           <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
         </is>
@@ -22087,14 +23688,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP184" s="65" t="inlineStr"/>
-      <c r="AQ184" s="65" t="inlineStr"/>
-      <c r="AR184" s="23" t="inlineStr"/>
+      <c r="AP184" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ184" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR184" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS184" s="23" t="n"/>
       <c r="AT184" s="67" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="68" t="inlineStr">
+      <c r="A185" s="53" t="inlineStr">
         <is>
           <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
         </is>
@@ -22202,17 +23815,29 @@
       </c>
       <c r="AO185" s="65" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP185" s="65" t="inlineStr"/>
-      <c r="AQ185" s="65" t="inlineStr"/>
-      <c r="AR185" s="23" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AP185" s="65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ185" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR185" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS185" s="23" t="n"/>
       <c r="AT185" s="67" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="53" t="inlineStr">
+      <c r="A186" s="68" t="inlineStr">
         <is>
           <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
         </is>
@@ -22323,14 +23948,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP186" s="65" t="inlineStr"/>
-      <c r="AQ186" s="65" t="inlineStr"/>
-      <c r="AR186" s="23" t="inlineStr"/>
+      <c r="AP186" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ186" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR186" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS186" s="23" t="n"/>
       <c r="AT186" s="67" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="68" t="inlineStr">
+      <c r="A187" s="53" t="inlineStr">
         <is>
           <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
         </is>
@@ -22438,17 +24075,29 @@
       </c>
       <c r="AO187" s="65" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP187" s="65" t="inlineStr"/>
-      <c r="AQ187" s="65" t="inlineStr"/>
-      <c r="AR187" s="23" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AP187" s="65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ187" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR187" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS187" s="23" t="n"/>
       <c r="AT187" s="67" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="53" t="inlineStr">
+      <c r="A188" s="68" t="inlineStr">
         <is>
           <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
         </is>
@@ -22559,9 +24208,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP188" s="65" t="inlineStr"/>
-      <c r="AQ188" s="65" t="inlineStr"/>
-      <c r="AR188" s="23" t="inlineStr"/>
+      <c r="AP188" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ188" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR188" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS188" s="23" t="n"/>
       <c r="AT188" s="67" t="inlineStr"/>
     </row>
@@ -22674,17 +24335,29 @@
       </c>
       <c r="AO189" s="65" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP189" s="65" t="inlineStr"/>
-      <c r="AQ189" s="65" t="inlineStr"/>
-      <c r="AR189" s="23" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AP189" s="65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ189" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR189" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS189" s="23" t="n"/>
       <c r="AT189" s="67" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="53" t="inlineStr">
+      <c r="A190" s="68" t="inlineStr">
         <is>
           <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
         </is>
@@ -22795,14 +24468,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP190" s="65" t="inlineStr"/>
-      <c r="AQ190" s="65" t="inlineStr"/>
-      <c r="AR190" s="23" t="inlineStr"/>
+      <c r="AP190" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ190" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR190" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS190" s="23" t="n"/>
       <c r="AT190" s="67" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="53" t="inlineStr">
+      <c r="A191" s="68" t="inlineStr">
         <is>
           <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
@@ -22913,14 +24598,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP191" s="65" t="inlineStr"/>
-      <c r="AQ191" s="65" t="inlineStr"/>
-      <c r="AR191" s="23" t="inlineStr"/>
+      <c r="AP191" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ191" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR191" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS191" s="23" t="n"/>
       <c r="AT191" s="67" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="53" t="inlineStr">
+      <c r="A192" s="68" t="inlineStr">
         <is>
           <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
@@ -23031,14 +24728,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP192" s="65" t="inlineStr"/>
-      <c r="AQ192" s="65" t="inlineStr"/>
-      <c r="AR192" s="23" t="inlineStr"/>
+      <c r="AP192" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ192" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR192" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS192" s="23" t="n"/>
       <c r="AT192" s="67" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="53" t="inlineStr">
+      <c r="A193" s="68" t="inlineStr">
         <is>
           <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
@@ -23149,14 +24858,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP193" s="65" t="inlineStr"/>
-      <c r="AQ193" s="65" t="inlineStr"/>
-      <c r="AR193" s="23" t="inlineStr"/>
+      <c r="AP193" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ193" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR193" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS193" s="23" t="n"/>
       <c r="AT193" s="67" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="53" t="inlineStr">
+      <c r="A194" s="68" t="inlineStr">
         <is>
           <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
@@ -23267,14 +24988,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP194" s="65" t="inlineStr"/>
-      <c r="AQ194" s="65" t="inlineStr"/>
-      <c r="AR194" s="23" t="inlineStr"/>
+      <c r="AP194" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ194" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR194" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS194" s="23" t="n"/>
       <c r="AT194" s="67" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="53" t="inlineStr">
+      <c r="A195" s="68" t="inlineStr">
         <is>
           <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
@@ -23385,14 +25118,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP195" s="65" t="inlineStr"/>
-      <c r="AQ195" s="65" t="inlineStr"/>
-      <c r="AR195" s="23" t="inlineStr"/>
+      <c r="AP195" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ195" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR195" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS195" s="23" t="n"/>
       <c r="AT195" s="67" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="53" t="inlineStr">
+      <c r="A196" s="68" t="inlineStr">
         <is>
           <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
@@ -23503,14 +25248,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP196" s="65" t="inlineStr"/>
-      <c r="AQ196" s="65" t="inlineStr"/>
-      <c r="AR196" s="23" t="inlineStr"/>
+      <c r="AP196" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ196" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR196" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS196" s="23" t="n"/>
       <c r="AT196" s="67" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="53" t="inlineStr">
+      <c r="A197" s="68" t="inlineStr">
         <is>
           <t>PS5-60-76 - Engine G Cooling system</t>
         </is>
@@ -23617,14 +25374,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP197" s="65" t="inlineStr"/>
-      <c r="AQ197" s="65" t="inlineStr"/>
-      <c r="AR197" s="23" t="inlineStr"/>
+      <c r="AP197" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ197" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR197" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS197" s="23" t="n"/>
       <c r="AT197" s="67" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="68" t="inlineStr">
+      <c r="A198" s="53" t="inlineStr">
         <is>
           <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
         </is>
@@ -23735,14 +25504,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP198" s="65" t="inlineStr"/>
-      <c r="AQ198" s="65" t="inlineStr"/>
-      <c r="AR198" s="23" t="inlineStr"/>
+      <c r="AP198" s="65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AQ198" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR198" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS198" s="23" t="n"/>
       <c r="AT198" s="67" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="53" t="inlineStr">
+      <c r="A199" s="68" t="inlineStr">
         <is>
           <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
         </is>
@@ -23853,14 +25634,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP199" s="65" t="inlineStr"/>
-      <c r="AQ199" s="65" t="inlineStr"/>
-      <c r="AR199" s="23" t="inlineStr"/>
+      <c r="AP199" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ199" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR199" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS199" s="23" t="n"/>
       <c r="AT199" s="67" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="53" t="inlineStr">
+      <c r="A200" s="68" t="inlineStr">
         <is>
           <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
         </is>
@@ -23971,14 +25764,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP200" s="65" t="inlineStr"/>
-      <c r="AQ200" s="65" t="inlineStr"/>
-      <c r="AR200" s="23" t="inlineStr"/>
+      <c r="AP200" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ200" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR200" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS200" s="23" t="n"/>
       <c r="AT200" s="67" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="68" t="inlineStr">
+      <c r="A201" s="53" t="inlineStr">
         <is>
           <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
         </is>
@@ -24085,7 +25890,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP201" s="65" t="inlineStr"/>
+      <c r="AP201" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ201" s="65" t="inlineStr">
         <is>
           <t>23</t>
@@ -24100,7 +25909,7 @@
       <c r="AT201" s="67" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="53" t="inlineStr">
+      <c r="A202" s="68" t="inlineStr">
         <is>
           <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
@@ -24211,14 +26020,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP202" s="65" t="inlineStr"/>
-      <c r="AQ202" s="65" t="inlineStr"/>
-      <c r="AR202" s="23" t="inlineStr"/>
+      <c r="AP202" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ202" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR202" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS202" s="23" t="n"/>
       <c r="AT202" s="67" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="68" t="inlineStr">
+      <c r="A203" s="53" t="inlineStr">
         <is>
           <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
         </is>
@@ -24329,14 +26150,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP203" s="65" t="inlineStr"/>
-      <c r="AQ203" s="65" t="inlineStr"/>
-      <c r="AR203" s="23" t="inlineStr"/>
+      <c r="AP203" s="65" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AQ203" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR203" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS203" s="23" t="n"/>
       <c r="AT203" s="67" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="53" t="inlineStr">
+      <c r="A204" s="68" t="inlineStr">
         <is>
           <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
@@ -24447,14 +26280,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP204" s="65" t="inlineStr"/>
-      <c r="AQ204" s="65" t="inlineStr"/>
-      <c r="AR204" s="23" t="inlineStr"/>
+      <c r="AP204" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ204" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR204" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS204" s="23" t="n"/>
       <c r="AT204" s="67" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="68" t="inlineStr">
+      <c r="A205" s="53" t="inlineStr">
         <is>
           <t>PS5-61-08 - Electrical Control System</t>
         </is>
@@ -24481,7 +26326,7 @@
       </c>
       <c r="F205" s="23" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="G205" s="28" t="inlineStr">
@@ -24561,7 +26406,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP205" s="65" t="inlineStr"/>
+      <c r="AP205" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ205" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -24576,7 +26425,7 @@
       <c r="AT205" s="67" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="68" t="inlineStr">
+      <c r="A206" s="53" t="inlineStr">
         <is>
           <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
         </is>
@@ -24603,7 +26452,7 @@
       </c>
       <c r="F206" s="23" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="G206" s="28" t="inlineStr">
@@ -24683,7 +26532,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP206" s="65" t="inlineStr"/>
+      <c r="AP206" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ206" s="65" t="inlineStr">
         <is>
           <t>17</t>
@@ -24698,7 +26551,7 @@
       <c r="AT206" s="67" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="53" t="inlineStr">
+      <c r="A207" s="68" t="inlineStr">
         <is>
           <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
@@ -24809,14 +26662,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP207" s="65" t="inlineStr"/>
-      <c r="AQ207" s="65" t="inlineStr"/>
-      <c r="AR207" s="23" t="inlineStr"/>
+      <c r="AP207" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ207" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR207" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS207" s="23" t="n"/>
       <c r="AT207" s="67" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="53" t="inlineStr">
+      <c r="A208" s="68" t="inlineStr">
         <is>
           <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
@@ -24927,14 +26792,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP208" s="65" t="inlineStr"/>
-      <c r="AQ208" s="65" t="inlineStr"/>
-      <c r="AR208" s="23" t="inlineStr"/>
+      <c r="AP208" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ208" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR208" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS208" s="23" t="n"/>
       <c r="AT208" s="67" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="68" t="inlineStr">
+      <c r="A209" s="53" t="inlineStr">
         <is>
           <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
         </is>
@@ -25018,7 +26895,7 @@
       <c r="AT209" s="67" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="68" t="inlineStr">
+      <c r="A210" s="53" t="inlineStr">
         <is>
           <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
         </is>
@@ -25121,14 +26998,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP210" s="65" t="inlineStr"/>
-      <c r="AQ210" s="65" t="inlineStr"/>
-      <c r="AR210" s="23" t="inlineStr"/>
+      <c r="AP210" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ210" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR210" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS210" s="23" t="n"/>
       <c r="AT210" s="67" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="68" t="inlineStr">
+      <c r="A211" s="53" t="inlineStr">
         <is>
           <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
         </is>
@@ -25231,14 +27120,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP211" s="65" t="inlineStr"/>
-      <c r="AQ211" s="65" t="inlineStr"/>
-      <c r="AR211" s="23" t="inlineStr"/>
+      <c r="AP211" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ211" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR211" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS211" s="23" t="n"/>
       <c r="AT211" s="67" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="68" t="inlineStr">
+      <c r="A212" s="53" t="inlineStr">
         <is>
           <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
         </is>
@@ -25345,7 +27246,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP212" s="65" t="inlineStr"/>
+      <c r="AP212" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ212" s="65" t="inlineStr">
         <is>
           <t>34</t>
@@ -25360,7 +27265,7 @@
       <c r="AT212" s="67" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="68" t="inlineStr">
+      <c r="A213" s="53" t="inlineStr">
         <is>
           <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
         </is>
@@ -25467,7 +27372,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP213" s="65" t="inlineStr"/>
+      <c r="AP213" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ213" s="65" t="inlineStr">
         <is>
           <t>32</t>
@@ -25482,7 +27391,7 @@
       <c r="AT213" s="67" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="53" t="inlineStr">
+      <c r="A214" s="68" t="inlineStr">
         <is>
           <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
         </is>
@@ -25593,14 +27502,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP214" s="65" t="inlineStr"/>
-      <c r="AQ214" s="65" t="inlineStr"/>
-      <c r="AR214" s="23" t="inlineStr"/>
+      <c r="AP214" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ214" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR214" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS214" s="23" t="n"/>
       <c r="AT214" s="67" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="53" t="inlineStr">
+      <c r="A215" s="68" t="inlineStr">
         <is>
           <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
@@ -25711,14 +27632,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP215" s="65" t="inlineStr"/>
-      <c r="AQ215" s="65" t="inlineStr"/>
-      <c r="AR215" s="23" t="inlineStr"/>
+      <c r="AP215" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ215" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR215" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS215" s="23" t="n"/>
       <c r="AT215" s="67" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="68" t="inlineStr">
+      <c r="A216" s="53" t="inlineStr">
         <is>
           <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
         </is>
@@ -25821,7 +27754,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP216" s="65" t="inlineStr"/>
+      <c r="AP216" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ216" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -25836,7 +27773,7 @@
       <c r="AT216" s="67" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="68" t="inlineStr">
+      <c r="A217" s="53" t="inlineStr">
         <is>
           <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
         </is>
@@ -25947,7 +27884,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP217" s="65" t="inlineStr"/>
+      <c r="AP217" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ217" s="65" t="inlineStr">
         <is>
           <t>14</t>
@@ -25962,7 +27903,7 @@
       <c r="AT217" s="67" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="68" t="inlineStr">
+      <c r="A218" s="53" t="inlineStr">
         <is>
           <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
         </is>
@@ -26069,7 +28010,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP218" s="65" t="inlineStr"/>
+      <c r="AP218" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ218" s="65" t="inlineStr">
         <is>
           <t>11</t>
@@ -26084,7 +28029,7 @@
       <c r="AT218" s="67" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="68" t="inlineStr">
+      <c r="A219" s="53" t="inlineStr">
         <is>
           <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
         </is>
@@ -26191,7 +28136,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP219" s="65" t="inlineStr"/>
+      <c r="AP219" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ219" s="65" t="inlineStr">
         <is>
           <t>18</t>
@@ -26206,7 +28155,7 @@
       <c r="AT219" s="67" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="68" t="inlineStr">
+      <c r="A220" s="53" t="inlineStr">
         <is>
           <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
         </is>
@@ -26313,7 +28262,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP220" s="65" t="inlineStr"/>
+      <c r="AP220" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ220" s="65" t="inlineStr">
         <is>
           <t>12</t>
@@ -26328,7 +28281,7 @@
       <c r="AT220" s="67" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="68" t="inlineStr">
+      <c r="A221" s="53" t="inlineStr">
         <is>
           <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
         </is>
@@ -26370,7 +28323,7 @@
       </c>
       <c r="I221" s="70" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="J221" s="55" t="n">
@@ -26409,14 +28362,14 @@
         <v>39</v>
       </c>
       <c r="AI221" s="23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ221" s="23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK221" s="25" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="AL221" s="23" t="inlineStr">
@@ -26439,22 +28392,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP221" s="65" t="inlineStr"/>
+      <c r="AP221" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ221" s="65" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR221" s="23" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AS221" s="23" t="n"/>
       <c r="AT221" s="67" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="68" t="inlineStr">
+      <c r="A222" s="53" t="inlineStr">
         <is>
           <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
         </is>
@@ -26551,7 +28508,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AN222" s="64" t="inlineStr">
+      <c r="AN222" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -26561,14 +28518,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP222" s="65" t="inlineStr"/>
-      <c r="AQ222" s="65" t="inlineStr"/>
-      <c r="AR222" s="23" t="inlineStr"/>
+      <c r="AP222" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ222" s="65" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AR222" s="23" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="AS222" s="23" t="n"/>
       <c r="AT222" s="67" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="68" t="inlineStr">
+      <c r="A223" s="53" t="inlineStr">
         <is>
           <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
         </is>
@@ -26652,7 +28621,7 @@
       <c r="AT223" s="67" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="68" t="inlineStr">
+      <c r="A224" s="53" t="inlineStr">
         <is>
           <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
         </is>
@@ -26736,7 +28705,7 @@
       <c r="AT224" s="67" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="68" t="inlineStr">
+      <c r="A225" s="53" t="inlineStr">
         <is>
           <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
         </is>
@@ -26839,14 +28808,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP225" s="65" t="inlineStr"/>
-      <c r="AQ225" s="65" t="inlineStr"/>
-      <c r="AR225" s="23" t="inlineStr"/>
+      <c r="AP225" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ225" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR225" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS225" s="23" t="n"/>
       <c r="AT225" s="67" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="68" t="inlineStr">
+      <c r="A226" s="53" t="inlineStr">
         <is>
           <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
         </is>
@@ -26949,14 +28930,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP226" s="65" t="inlineStr"/>
-      <c r="AQ226" s="65" t="inlineStr"/>
-      <c r="AR226" s="23" t="inlineStr"/>
+      <c r="AP226" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ226" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR226" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS226" s="23" t="n"/>
       <c r="AT226" s="67" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="68" t="inlineStr">
+      <c r="A227" s="53" t="inlineStr">
         <is>
           <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
         </is>
@@ -27059,14 +29052,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP227" s="65" t="inlineStr"/>
-      <c r="AQ227" s="65" t="inlineStr"/>
-      <c r="AR227" s="23" t="inlineStr"/>
+      <c r="AP227" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ227" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR227" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS227" s="23" t="n"/>
       <c r="AT227" s="67" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="68" t="inlineStr">
+      <c r="A228" s="53" t="inlineStr">
         <is>
           <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
         </is>
@@ -27169,14 +29174,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP228" s="65" t="inlineStr"/>
-      <c r="AQ228" s="65" t="inlineStr"/>
-      <c r="AR228" s="23" t="inlineStr"/>
+      <c r="AP228" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ228" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR228" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS228" s="23" t="n"/>
       <c r="AT228" s="67" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="68" t="inlineStr">
+      <c r="A229" s="53" t="inlineStr">
         <is>
           <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
         </is>
@@ -27279,14 +29296,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP229" s="65" t="inlineStr"/>
-      <c r="AQ229" s="65" t="inlineStr"/>
-      <c r="AR229" s="23" t="inlineStr"/>
+      <c r="AP229" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ229" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR229" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS229" s="23" t="n"/>
       <c r="AT229" s="67" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="68" t="inlineStr">
+      <c r="A230" s="53" t="inlineStr">
         <is>
           <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
         </is>
@@ -27389,14 +29418,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP230" s="65" t="inlineStr"/>
-      <c r="AQ230" s="65" t="inlineStr"/>
-      <c r="AR230" s="23" t="inlineStr"/>
+      <c r="AP230" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ230" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR230" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS230" s="23" t="n"/>
       <c r="AT230" s="67" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="68" t="inlineStr">
+      <c r="A231" s="53" t="inlineStr">
         <is>
           <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
         </is>
@@ -27499,14 +29540,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP231" s="65" t="inlineStr"/>
-      <c r="AQ231" s="65" t="inlineStr"/>
-      <c r="AR231" s="23" t="inlineStr"/>
+      <c r="AP231" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ231" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR231" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS231" s="23" t="n"/>
       <c r="AT231" s="67" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="68" t="inlineStr">
+      <c r="A232" s="53" t="inlineStr">
         <is>
           <t>PS5-63-01 - Electrical Earthing</t>
         </is>
@@ -27548,7 +29601,7 @@
       </c>
       <c r="I232" s="69" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="J232" s="55" t="n">
@@ -27587,14 +29640,14 @@
         <v>68</v>
       </c>
       <c r="AI232" s="23" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="AJ232" s="23" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="AK232" s="26" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="AL232" s="23" t="inlineStr">
@@ -27617,7 +29670,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP232" s="65" t="inlineStr"/>
+      <c r="AP232" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ232" s="65" t="inlineStr">
         <is>
           <t>18 ITRs for lightning, 22 ITRs for grounding cannot be closed due to material issues.</t>
@@ -27625,14 +29682,14 @@
       </c>
       <c r="AR232" s="23" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AS232" s="23" t="n"/>
       <c r="AT232" s="67" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="68" t="inlineStr">
+      <c r="A233" s="53" t="inlineStr">
         <is>
           <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
         </is>
@@ -27735,7 +29792,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP233" s="65" t="inlineStr"/>
+      <c r="AP233" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ233" s="65" t="inlineStr">
         <is>
           <t>4</t>
@@ -27750,7 +29811,7 @@
       <c r="AT233" s="67" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="68" t="inlineStr">
+      <c r="A234" s="53" t="inlineStr">
         <is>
           <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
         </is>
@@ -27861,7 +29922,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP234" s="65" t="inlineStr"/>
+      <c r="AP234" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ234" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -27876,7 +29941,7 @@
       <c r="AT234" s="67" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="53" t="inlineStr">
+      <c r="A235" s="68" t="inlineStr">
         <is>
           <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
@@ -27960,7 +30025,7 @@
       <c r="AT235" s="67" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="68" t="inlineStr">
+      <c r="A236" s="53" t="inlineStr">
         <is>
           <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
         </is>
@@ -28063,7 +30128,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP236" s="65" t="inlineStr"/>
+      <c r="AP236" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ236" s="65" t="inlineStr">
         <is>
           <t>8</t>
@@ -28078,7 +30147,7 @@
       <c r="AT236" s="67" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="68" t="inlineStr">
+      <c r="A237" s="53" t="inlineStr">
         <is>
           <t>PS5-63-06 - Electrical Earthing - Guard House</t>
         </is>
@@ -28181,7 +30250,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP237" s="65" t="inlineStr"/>
+      <c r="AP237" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ237" s="65" t="inlineStr">
         <is>
           <t>4</t>
@@ -28196,7 +30269,7 @@
       <c r="AT237" s="67" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="68" t="inlineStr">
+      <c r="A238" s="53" t="inlineStr">
         <is>
           <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
         </is>
@@ -28299,7 +30372,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP238" s="65" t="inlineStr"/>
+      <c r="AP238" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ238" s="65" t="inlineStr">
         <is>
           <t>4</t>
@@ -28314,7 +30391,7 @@
       <c r="AT238" s="67" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="68" t="inlineStr">
+      <c r="A239" s="53" t="inlineStr">
         <is>
           <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
         </is>
@@ -28428,19 +30505,19 @@
       </c>
       <c r="AQ239" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR239" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AS239" s="23" t="n"/>
       <c r="AT239" s="67" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="53" t="inlineStr">
+      <c r="A240" s="68" t="inlineStr">
         <is>
           <t>PS5-71-02 - CFO Allocation Metering Package</t>
         </is>
@@ -28551,14 +30628,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP240" s="65" t="inlineStr"/>
-      <c r="AQ240" s="65" t="inlineStr"/>
-      <c r="AR240" s="23" t="inlineStr"/>
+      <c r="AP240" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ240" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR240" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS240" s="23" t="n"/>
       <c r="AT240" s="67" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="68" t="inlineStr">
+      <c r="A241" s="53" t="inlineStr">
         <is>
           <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
         </is>
@@ -28642,7 +30731,7 @@
       <c r="AT241" s="67" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="68" t="inlineStr">
+      <c r="A242" s="53" t="inlineStr">
         <is>
           <t>PS5-71-04 - CFO Storage Tank</t>
         </is>
@@ -28749,7 +30838,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP242" s="65" t="inlineStr"/>
+      <c r="AP242" s="65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AQ242" s="65" t="inlineStr">
         <is>
           <t>14</t>
@@ -28764,7 +30857,7 @@
       <c r="AT242" s="67" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="68" t="inlineStr">
+      <c r="A243" s="53" t="inlineStr">
         <is>
           <t>PS5-71-05 - CFO Transfer Pump A/B</t>
         </is>
@@ -28871,7 +30964,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP243" s="65" t="inlineStr"/>
+      <c r="AP243" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ243" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -28886,7 +30983,7 @@
       <c r="AT243" s="67" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="68" t="inlineStr">
+      <c r="A244" s="53" t="inlineStr">
         <is>
           <t>PS5-71-06 - Crude Fuel Separation Module</t>
         </is>
@@ -28993,14 +31090,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP244" s="65" t="inlineStr"/>
-      <c r="AQ244" s="65" t="inlineStr"/>
-      <c r="AR244" s="23" t="inlineStr"/>
+      <c r="AP244" s="65" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AQ244" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR244" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS244" s="23" t="n"/>
       <c r="AT244" s="67" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="68" t="inlineStr">
+      <c r="A245" s="53" t="inlineStr">
         <is>
           <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
         </is>
@@ -29107,14 +31216,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP245" s="65" t="inlineStr"/>
-      <c r="AQ245" s="65" t="inlineStr"/>
-      <c r="AR245" s="23" t="inlineStr"/>
+      <c r="AP245" s="65" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ245" s="65" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AR245" s="23" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="AS245" s="23" t="n"/>
       <c r="AT245" s="67" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="68" t="inlineStr">
+      <c r="A246" s="53" t="inlineStr">
         <is>
           <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
         </is>
@@ -29225,14 +31346,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP246" s="65" t="inlineStr"/>
-      <c r="AQ246" s="65" t="inlineStr"/>
-      <c r="AR246" s="23" t="inlineStr"/>
+      <c r="AP246" s="65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AQ246" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR246" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS246" s="23" t="n"/>
       <c r="AT246" s="67" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="53" t="inlineStr">
+      <c r="A247" s="68" t="inlineStr">
         <is>
           <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
         </is>
@@ -29343,14 +31476,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP247" s="65" t="inlineStr"/>
-      <c r="AQ247" s="65" t="inlineStr"/>
-      <c r="AR247" s="23" t="inlineStr"/>
+      <c r="AP247" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ247" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR247" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS247" s="23" t="n"/>
       <c r="AT247" s="67" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="68" t="inlineStr">
+      <c r="A248" s="53" t="inlineStr">
         <is>
           <t>PS5-71-12 - CFO Service Tank</t>
         </is>
@@ -29388,7 +31533,7 @@
       <c r="H248" s="24" t="inlineStr"/>
       <c r="I248" s="69" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="J248" s="55" t="n">
@@ -29427,14 +31572,14 @@
         <v>125</v>
       </c>
       <c r="AI248" s="23" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AJ248" s="23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK248" s="26" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="AL248" s="23" t="inlineStr">
@@ -29457,7 +31602,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP248" s="65" t="inlineStr"/>
+      <c r="AP248" s="65" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="AQ248" s="65" t="inlineStr">
         <is>
           <t>13</t>
@@ -29472,7 +31621,7 @@
       <c r="AT248" s="67" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="68" t="inlineStr">
+      <c r="A249" s="53" t="inlineStr">
         <is>
           <t>PS5-71-13 - CFO Service Pump A/B</t>
         </is>
@@ -29510,7 +31659,7 @@
       <c r="H249" s="24" t="inlineStr"/>
       <c r="I249" s="69" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="J249" s="55" t="n">
@@ -29549,14 +31698,14 @@
         <v>56</v>
       </c>
       <c r="AI249" s="23" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AJ249" s="23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK249" s="26" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="AL249" s="23" t="inlineStr">
@@ -29579,14 +31728,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP249" s="65" t="inlineStr"/>
-      <c r="AQ249" s="65" t="inlineStr"/>
-      <c r="AR249" s="23" t="inlineStr"/>
+      <c r="AP249" s="65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AQ249" s="65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AR249" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AS249" s="23" t="n"/>
       <c r="AT249" s="67" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="53" t="inlineStr">
+      <c r="A250" s="68" t="inlineStr">
         <is>
           <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
@@ -29697,14 +31858,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP250" s="65" t="inlineStr"/>
-      <c r="AQ250" s="65" t="inlineStr"/>
-      <c r="AR250" s="23" t="inlineStr"/>
+      <c r="AP250" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ250" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR250" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS250" s="23" t="n"/>
       <c r="AT250" s="67" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="68" t="inlineStr">
+      <c r="A251" s="53" t="inlineStr">
         <is>
           <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
         </is>
@@ -29731,7 +31904,7 @@
       </c>
       <c r="F251" s="23" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="G251" s="28" t="inlineStr">
@@ -29796,12 +31969,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM251" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN251" s="64" t="inlineStr">
+      <c r="AM251" s="64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN251" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -29818,19 +31991,19 @@
       </c>
       <c r="AQ251" s="65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR251" s="23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AS251" s="23" t="n"/>
       <c r="AT251" s="67" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="53" t="inlineStr">
+      <c r="A252" s="68" t="inlineStr">
         <is>
           <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
@@ -29941,14 +32114,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP252" s="65" t="inlineStr"/>
-      <c r="AQ252" s="65" t="inlineStr"/>
-      <c r="AR252" s="23" t="inlineStr"/>
+      <c r="AP252" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ252" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR252" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS252" s="23" t="n"/>
       <c r="AT252" s="67" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="68" t="inlineStr">
+      <c r="A253" s="53" t="inlineStr">
         <is>
           <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
         </is>
@@ -30059,14 +32244,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP253" s="65" t="inlineStr"/>
-      <c r="AQ253" s="65" t="inlineStr"/>
-      <c r="AR253" s="23" t="inlineStr"/>
+      <c r="AP253" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ253" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR253" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS253" s="23" t="n"/>
       <c r="AT253" s="67" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="68" t="inlineStr">
+      <c r="A254" s="53" t="inlineStr">
         <is>
           <t>PS5-71-18 - Diesel Separator Module</t>
         </is>
@@ -30177,14 +32374,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP254" s="65" t="inlineStr"/>
-      <c r="AQ254" s="65" t="inlineStr"/>
-      <c r="AR254" s="23" t="inlineStr"/>
+      <c r="AP254" s="65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AQ254" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR254" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS254" s="23" t="n"/>
       <c r="AT254" s="67" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="68" t="inlineStr">
+      <c r="A255" s="53" t="inlineStr">
         <is>
           <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
         </is>
@@ -30211,7 +32420,7 @@
       </c>
       <c r="F255" s="23" t="inlineStr">
         <is>
-          <t>HOLD/meterial issue</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="G255" s="28" t="inlineStr">
@@ -30291,14 +32500,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP255" s="65" t="inlineStr"/>
-      <c r="AQ255" s="65" t="inlineStr"/>
-      <c r="AR255" s="23" t="inlineStr"/>
+      <c r="AP255" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ255" s="65" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AR255" s="23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="AS255" s="23" t="n"/>
       <c r="AT255" s="67" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="68" t="inlineStr">
+      <c r="A256" s="53" t="inlineStr">
         <is>
           <t>PS5-71-20 - Diesel Fuel Day Tank</t>
         </is>
@@ -30409,14 +32630,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP256" s="65" t="inlineStr"/>
-      <c r="AQ256" s="65" t="inlineStr"/>
-      <c r="AR256" s="23" t="inlineStr"/>
+      <c r="AP256" s="65" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ256" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR256" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS256" s="23" t="n"/>
       <c r="AT256" s="67" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="68" t="inlineStr">
+      <c r="A257" s="53" t="inlineStr">
         <is>
           <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
         </is>
@@ -30458,7 +32691,7 @@
       </c>
       <c r="I257" s="54" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="J257" s="55" t="n">
@@ -30497,14 +32730,14 @@
         <v>55</v>
       </c>
       <c r="AI257" s="23" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AJ257" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK257" s="27" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="AL257" s="23" t="inlineStr">
@@ -30527,14 +32760,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP257" s="65" t="inlineStr"/>
-      <c r="AQ257" s="65" t="inlineStr"/>
-      <c r="AR257" s="23" t="inlineStr"/>
+      <c r="AP257" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ257" s="65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AR257" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="AS257" s="23" t="n"/>
       <c r="AT257" s="67" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="53" t="inlineStr">
+      <c r="A258" s="68" t="inlineStr">
         <is>
           <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
@@ -30645,14 +32890,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP258" s="65" t="inlineStr"/>
-      <c r="AQ258" s="65" t="inlineStr"/>
-      <c r="AR258" s="23" t="inlineStr"/>
+      <c r="AP258" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ258" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR258" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS258" s="23" t="n"/>
       <c r="AT258" s="67" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="68" t="inlineStr">
+      <c r="A259" s="53" t="inlineStr">
         <is>
           <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
         </is>
@@ -30763,14 +33020,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP259" s="65" t="inlineStr"/>
-      <c r="AQ259" s="65" t="inlineStr"/>
-      <c r="AR259" s="23" t="inlineStr"/>
+      <c r="AP259" s="65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ259" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR259" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS259" s="23" t="n"/>
       <c r="AT259" s="67" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="53" t="inlineStr">
+      <c r="A260" s="68" t="inlineStr">
         <is>
           <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
@@ -30807,7 +33076,7 @@
       </c>
       <c r="H260" s="24" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="I260" s="54" t="inlineStr">
@@ -30886,13 +33155,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AQ260" s="65" t="inlineStr"/>
-      <c r="AR260" s="23" t="inlineStr"/>
+      <c r="AQ260" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR260" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS260" s="23" t="n"/>
       <c r="AT260" s="67" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="68" t="inlineStr">
+      <c r="A261" s="53" t="inlineStr">
         <is>
           <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
         </is>
@@ -31003,7 +33280,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP261" s="65" t="inlineStr"/>
+      <c r="AP261" s="65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AQ261" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -31018,7 +33299,7 @@
       <c r="AT261" s="67" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="53" t="inlineStr">
+      <c r="A262" s="68" t="inlineStr">
         <is>
           <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
@@ -31129,14 +33410,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP262" s="65" t="inlineStr"/>
-      <c r="AQ262" s="65" t="inlineStr"/>
-      <c r="AR262" s="23" t="inlineStr"/>
+      <c r="AP262" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ262" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR262" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS262" s="23" t="n"/>
       <c r="AT262" s="67" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="53" t="inlineStr">
+      <c r="A263" s="68" t="inlineStr">
         <is>
           <t>PS5-74-04 - Nitrogen Distribution Header</t>
         </is>
@@ -31247,7 +33540,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP263" s="65" t="inlineStr"/>
+      <c r="AP263" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ263" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -31262,7 +33559,7 @@
       <c r="AT263" s="67" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="68" t="inlineStr">
+      <c r="A264" s="53" t="inlineStr">
         <is>
           <t>PS5-75-01 - DRA Injection Package</t>
         </is>
@@ -31296,7 +33593,7 @@
       <c r="H264" s="24" t="inlineStr"/>
       <c r="I264" s="69" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="J264" s="55" t="n">
@@ -31335,14 +33632,14 @@
         <v>30</v>
       </c>
       <c r="AI264" s="23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AJ264" s="23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AK264" s="26" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="AL264" s="64" t="inlineStr">
@@ -31365,22 +33662,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP264" s="65" t="inlineStr"/>
+      <c r="AP264" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ264" s="65" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR264" s="23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AS264" s="23" t="n"/>
       <c r="AT264" s="67" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" s="53" t="inlineStr">
+      <c r="A265" s="68" t="inlineStr">
         <is>
           <t>PS5-75-02 - Biocide Injection Package</t>
         </is>
@@ -31491,14 +33792,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP265" s="65" t="inlineStr"/>
-      <c r="AQ265" s="65" t="inlineStr"/>
-      <c r="AR265" s="23" t="inlineStr"/>
+      <c r="AP265" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ265" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR265" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS265" s="23" t="n"/>
       <c r="AT265" s="67" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" s="53" t="inlineStr">
+      <c r="A266" s="68" t="inlineStr">
         <is>
           <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
         </is>
@@ -31609,9 +33922,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP266" s="65" t="inlineStr"/>
-      <c r="AQ266" s="65" t="inlineStr"/>
-      <c r="AR266" s="23" t="inlineStr"/>
+      <c r="AP266" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ266" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR266" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS266" s="23" t="n"/>
       <c r="AT266" s="67" t="inlineStr"/>
     </row>
@@ -31723,7 +34048,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP267" s="65" t="inlineStr"/>
+      <c r="AP267" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ267" s="65" t="inlineStr">
         <is>
           <t>5</t>
@@ -31738,7 +34067,7 @@
       <c r="AT267" s="67" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="68" t="inlineStr">
+      <c r="A268" s="53" t="inlineStr">
         <is>
           <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
         </is>
@@ -31763,7 +34092,11 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="F268" s="23" t="inlineStr"/>
+      <c r="F268" s="23" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
       <c r="G268" s="28" t="inlineStr">
         <is>
           <t>-</t>
@@ -31841,7 +34174,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP268" s="65" t="inlineStr"/>
+      <c r="AP268" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ268" s="65" t="inlineStr">
         <is>
           <t>15</t>
@@ -31856,7 +34193,7 @@
       <c r="AT268" s="67" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="68" t="inlineStr">
+      <c r="A269" s="53" t="inlineStr">
         <is>
           <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
         </is>
@@ -31881,7 +34218,11 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="F269" s="23" t="inlineStr"/>
+      <c r="F269" s="23" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
       <c r="G269" s="28" t="inlineStr">
         <is>
           <t>-</t>
@@ -31890,7 +34231,7 @@
       <c r="H269" s="24" t="inlineStr"/>
       <c r="I269" s="69" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="J269" s="55" t="n">
@@ -31929,14 +34270,14 @@
         <v>71</v>
       </c>
       <c r="AI269" s="23" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AJ269" s="23" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AK269" s="26" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="AL269" s="23" t="inlineStr">
@@ -31959,22 +34300,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP269" s="65" t="inlineStr"/>
+      <c r="AP269" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ269" s="65" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR269" s="23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AS269" s="23" t="n"/>
       <c r="AT269" s="67" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="68" t="inlineStr">
+      <c r="A270" s="53" t="inlineStr">
         <is>
           <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
         </is>
@@ -31999,7 +34344,11 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="F270" s="23" t="inlineStr"/>
+      <c r="F270" s="23" t="inlineStr">
+        <is>
+          <t>2026-11-14</t>
+        </is>
+      </c>
       <c r="G270" s="28" t="inlineStr">
         <is>
           <t>-</t>
@@ -32077,7 +34426,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP270" s="65" t="inlineStr"/>
+      <c r="AP270" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ270" s="65" t="inlineStr">
         <is>
           <t>37</t>
@@ -32092,7 +34445,7 @@
       <c r="AT270" s="67" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="68" t="inlineStr">
+      <c r="A271" s="53" t="inlineStr">
         <is>
           <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
         </is>
@@ -32117,7 +34470,11 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="F271" s="23" t="inlineStr"/>
+      <c r="F271" s="23" t="inlineStr">
+        <is>
+          <t>2026-11-14</t>
+        </is>
+      </c>
       <c r="G271" s="28" t="inlineStr">
         <is>
           <t>-</t>
@@ -32195,7 +34552,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP271" s="65" t="inlineStr"/>
+      <c r="AP271" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ271" s="65" t="inlineStr">
         <is>
           <t>36</t>
@@ -32210,7 +34571,7 @@
       <c r="AT271" s="67" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" s="68" t="inlineStr">
+      <c r="A272" s="53" t="inlineStr">
         <is>
           <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
         </is>
@@ -32235,7 +34596,11 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="F272" s="23" t="inlineStr"/>
+      <c r="F272" s="23" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
       <c r="G272" s="28" t="inlineStr">
         <is>
           <t>-</t>
@@ -32313,7 +34678,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP272" s="65" t="inlineStr"/>
+      <c r="AP272" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ272" s="65" t="inlineStr">
         <is>
           <t>43</t>
@@ -32328,7 +34697,7 @@
       <c r="AT272" s="67" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="68" t="inlineStr">
+      <c r="A273" s="53" t="inlineStr">
         <is>
           <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
         </is>
@@ -32353,7 +34722,11 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="F273" s="23" t="inlineStr"/>
+      <c r="F273" s="23" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
       <c r="G273" s="28" t="inlineStr">
         <is>
           <t>-</t>
@@ -32362,7 +34735,7 @@
       <c r="H273" s="24" t="inlineStr"/>
       <c r="I273" s="70" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="J273" s="55" t="n">
@@ -32401,14 +34774,14 @@
         <v>75</v>
       </c>
       <c r="AI273" s="23" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="AJ273" s="23" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="AK273" s="25" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="AL273" s="23" t="inlineStr">
@@ -32431,22 +34804,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP273" s="65" t="inlineStr"/>
+      <c r="AP273" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ273" s="65" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AR273" s="23" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AS273" s="23" t="n"/>
       <c r="AT273" s="67" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="68" t="inlineStr">
+      <c r="A274" s="53" t="inlineStr">
         <is>
           <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
         </is>
@@ -32471,7 +34848,11 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="F274" s="23" t="inlineStr"/>
+      <c r="F274" s="23" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
       <c r="G274" s="28" t="inlineStr">
         <is>
           <t>-</t>
@@ -32480,7 +34861,7 @@
       <c r="H274" s="24" t="inlineStr"/>
       <c r="I274" s="69" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="J274" s="55" t="n">
@@ -32519,14 +34900,14 @@
         <v>75</v>
       </c>
       <c r="AI274" s="23" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ274" s="23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AK274" s="26" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="AL274" s="23" t="inlineStr">
@@ -32549,22 +34930,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP274" s="65" t="inlineStr"/>
+      <c r="AP274" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ274" s="65" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR274" s="23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AS274" s="23" t="n"/>
       <c r="AT274" s="67" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" s="68" t="inlineStr">
+      <c r="A275" s="53" t="inlineStr">
         <is>
           <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
         </is>
@@ -32589,7 +34974,11 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="F275" s="23" t="inlineStr"/>
+      <c r="F275" s="23" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
       <c r="G275" s="28" t="inlineStr">
         <is>
           <t>-</t>
@@ -32598,7 +34987,7 @@
       <c r="H275" s="24" t="inlineStr"/>
       <c r="I275" s="69" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="J275" s="55" t="n">
@@ -32637,14 +35026,14 @@
         <v>75</v>
       </c>
       <c r="AI275" s="23" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ275" s="23" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AK275" s="26" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="AL275" s="23" t="inlineStr">
@@ -32667,22 +35056,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP275" s="65" t="inlineStr"/>
+      <c r="AP275" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ275" s="65" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AR275" s="23" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AS275" s="23" t="n"/>
       <c r="AT275" s="67" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="68" t="inlineStr">
+      <c r="A276" s="53" t="inlineStr">
         <is>
           <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
         </is>
@@ -32707,7 +35100,11 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="F276" s="23" t="inlineStr"/>
+      <c r="F276" s="23" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
       <c r="G276" s="28" t="inlineStr">
         <is>
           <t>-</t>
@@ -32716,7 +35113,7 @@
       <c r="H276" s="24" t="inlineStr"/>
       <c r="I276" s="70" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="J276" s="55" t="n">
@@ -32755,14 +35152,14 @@
         <v>75</v>
       </c>
       <c r="AI276" s="23" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="AJ276" s="23" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="AK276" s="25" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="AL276" s="23" t="inlineStr">
@@ -32785,22 +35182,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP276" s="65" t="inlineStr"/>
+      <c r="AP276" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ276" s="65" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AR276" s="23" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AS276" s="23" t="n"/>
       <c r="AT276" s="67" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" s="68" t="inlineStr">
+      <c r="A277" s="53" t="inlineStr">
         <is>
           <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
         </is>
@@ -32825,7 +35226,11 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="F277" s="23" t="inlineStr"/>
+      <c r="F277" s="23" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
       <c r="G277" s="28" t="inlineStr">
         <is>
           <t>-</t>
@@ -32834,7 +35239,7 @@
       <c r="H277" s="24" t="inlineStr"/>
       <c r="I277" s="69" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="J277" s="55" t="n">
@@ -32873,14 +35278,14 @@
         <v>71</v>
       </c>
       <c r="AI277" s="23" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AJ277" s="23" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AK277" s="26" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="AL277" s="23" t="inlineStr">
@@ -32903,22 +35308,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP277" s="65" t="inlineStr"/>
+      <c r="AP277" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ277" s="65" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AR277" s="23" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AS277" s="23" t="n"/>
       <c r="AT277" s="67" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="68" t="inlineStr">
+      <c r="A278" s="53" t="inlineStr">
         <is>
           <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
         </is>
@@ -32943,7 +35352,11 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="F278" s="23" t="inlineStr"/>
+      <c r="F278" s="23" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
       <c r="G278" s="28" t="inlineStr">
         <is>
           <t>-</t>
@@ -33021,7 +35434,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP278" s="65" t="inlineStr"/>
+      <c r="AP278" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ278" s="65" t="inlineStr">
         <is>
           <t>44</t>
@@ -33036,7 +35453,7 @@
       <c r="AT278" s="67" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="68" t="inlineStr">
+      <c r="A279" s="53" t="inlineStr">
         <is>
           <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
         </is>
@@ -33061,7 +35478,11 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="F279" s="23" t="inlineStr"/>
+      <c r="F279" s="23" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
       <c r="G279" s="28" t="inlineStr">
         <is>
           <t>-</t>
@@ -33070,7 +35491,7 @@
       <c r="H279" s="24" t="inlineStr"/>
       <c r="I279" s="70" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="J279" s="55" t="n">
@@ -33109,14 +35530,14 @@
         <v>81</v>
       </c>
       <c r="AI279" s="23" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="AJ279" s="23" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="AK279" s="25" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="AL279" s="23" t="inlineStr">
@@ -33139,22 +35560,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP279" s="65" t="inlineStr"/>
+      <c r="AP279" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ279" s="65" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AR279" s="23" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AS279" s="23" t="n"/>
       <c r="AT279" s="67" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="53" t="inlineStr">
+      <c r="A280" s="68" t="inlineStr">
         <is>
           <t>PS5-82-01 - Sanitary Sewage Collection</t>
         </is>
@@ -33261,14 +35686,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP280" s="65" t="inlineStr"/>
-      <c r="AQ280" s="65" t="inlineStr"/>
-      <c r="AR280" s="23" t="inlineStr"/>
+      <c r="AP280" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ280" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR280" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS280" s="23" t="n"/>
       <c r="AT280" s="67" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="68" t="inlineStr">
+      <c r="A281" s="53" t="inlineStr">
         <is>
           <t>PS5-82-02 - Sewage Treatment Plant Package</t>
         </is>
@@ -33371,22 +35808,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP281" s="65" t="inlineStr"/>
+      <c r="AP281" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ281" s="65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR281" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS281" s="23" t="n"/>
       <c r="AT281" s="67" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="68" t="inlineStr">
+      <c r="A282" s="53" t="inlineStr">
         <is>
           <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
         </is>
@@ -33489,7 +35930,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP282" s="65" t="inlineStr"/>
+      <c r="AP282" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ282" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -33504,7 +35949,7 @@
       <c r="AT282" s="67" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" s="68" t="inlineStr">
+      <c r="A283" s="53" t="inlineStr">
         <is>
           <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
         </is>
@@ -33607,7 +36052,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP283" s="65" t="inlineStr"/>
+      <c r="AP283" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ283" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -33622,7 +36071,7 @@
       <c r="AT283" s="67" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" s="68" t="inlineStr">
+      <c r="A284" s="53" t="inlineStr">
         <is>
           <t>PS5-82-05 - Office and Facilities building</t>
         </is>
@@ -33725,14 +36174,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP284" s="65" t="inlineStr"/>
-      <c r="AQ284" s="65" t="inlineStr"/>
-      <c r="AR284" s="23" t="inlineStr"/>
+      <c r="AP284" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ284" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR284" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS284" s="23" t="n"/>
       <c r="AT284" s="67" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="68" t="inlineStr">
+      <c r="A285" s="53" t="inlineStr">
         <is>
           <t>PS5-82-06 - Guard House Building</t>
         </is>
@@ -33835,14 +36296,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP285" s="65" t="inlineStr"/>
-      <c r="AQ285" s="65" t="inlineStr"/>
-      <c r="AR285" s="23" t="inlineStr"/>
+      <c r="AP285" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ285" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR285" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS285" s="23" t="n"/>
       <c r="AT285" s="67" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="68" t="inlineStr">
+      <c r="A286" s="53" t="inlineStr">
         <is>
           <t>PS5-82-07 - Guard Huts</t>
         </is>
@@ -33945,7 +36418,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP286" s="65" t="inlineStr"/>
+      <c r="AP286" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ286" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -33960,7 +36437,7 @@
       <c r="AT286" s="67" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="53" t="inlineStr">
+      <c r="A287" s="68" t="inlineStr">
         <is>
           <t>PS5-83-01 - EITS Building</t>
         </is>
@@ -34071,14 +36548,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP287" s="65" t="inlineStr"/>
-      <c r="AQ287" s="65" t="inlineStr"/>
-      <c r="AR287" s="23" t="inlineStr"/>
+      <c r="AP287" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ287" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR287" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS287" s="23" t="n"/>
       <c r="AT287" s="67" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="68" t="inlineStr">
+      <c r="A288" s="53" t="inlineStr">
         <is>
           <t>PS5-84-01 - Generator Building</t>
         </is>
@@ -34185,7 +36674,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP288" s="65" t="inlineStr"/>
+      <c r="AP288" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ288" s="65" t="inlineStr">
         <is>
           <t>3</t>
@@ -34200,7 +36693,7 @@
       <c r="AT288" s="67" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="68" t="inlineStr">
+      <c r="A289" s="53" t="inlineStr">
         <is>
           <t>PS5-84-02 - Workshop &amp; Warehouse</t>
         </is>
@@ -34303,7 +36796,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP289" s="65" t="inlineStr"/>
+      <c r="AP289" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ289" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -34318,7 +36815,7 @@
       <c r="AT289" s="67" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="53" t="inlineStr">
+      <c r="A290" s="68" t="inlineStr">
         <is>
           <t>PS5-84-03 - Shelters</t>
         </is>
@@ -34425,14 +36922,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP290" s="65" t="inlineStr"/>
-      <c r="AQ290" s="65" t="inlineStr"/>
-      <c r="AR290" s="23" t="inlineStr"/>
+      <c r="AP290" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ290" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR290" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS290" s="23" t="n"/>
       <c r="AT290" s="67" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" s="53" t="inlineStr">
+      <c r="A291" s="68" t="inlineStr">
         <is>
           <t>PS5-86-01 - Shelters</t>
         </is>
@@ -34539,14 +37048,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP291" s="65" t="inlineStr"/>
-      <c r="AQ291" s="65" t="inlineStr"/>
-      <c r="AR291" s="23" t="inlineStr"/>
+      <c r="AP291" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ291" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR291" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS291" s="23" t="n"/>
       <c r="AT291" s="67" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" s="53" t="inlineStr">
+      <c r="A292" s="68" t="inlineStr">
         <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
@@ -34657,14 +37178,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP292" s="65" t="inlineStr"/>
-      <c r="AQ292" s="65" t="inlineStr"/>
-      <c r="AR292" s="23" t="inlineStr"/>
+      <c r="AP292" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ292" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR292" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AS292" s="23" t="n"/>
       <c r="AT292" s="67" t="inlineStr"/>
     </row>
     <row r="293">
-      <c r="A293" s="68" t="inlineStr">
+      <c r="A293" s="53" t="inlineStr">
         <is>
           <t>PS5-99-01 - Area Completion for Building area</t>
         </is>
@@ -34767,7 +37300,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP293" s="65" t="inlineStr"/>
+      <c r="AP293" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ293" s="65" t="inlineStr">
         <is>
           <t>6</t>
@@ -34782,7 +37319,7 @@
       <c r="AT293" s="67" t="inlineStr"/>
     </row>
     <row r="294">
-      <c r="A294" s="68" t="inlineStr">
+      <c r="A294" s="53" t="inlineStr">
         <is>
           <t>PS5-99-02 - Area Completion for Utility area</t>
         </is>
@@ -34885,7 +37422,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP294" s="65" t="inlineStr"/>
+      <c r="AP294" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ294" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -34900,7 +37441,7 @@
       <c r="AT294" s="67" t="inlineStr"/>
     </row>
     <row r="295">
-      <c r="A295" s="68" t="inlineStr">
+      <c r="A295" s="53" t="inlineStr">
         <is>
           <t>PS5-99-03 - Area Completion for Power Distribution area</t>
         </is>
@@ -35007,7 +37548,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP295" s="65" t="inlineStr"/>
+      <c r="AP295" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ295" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -35022,7 +37567,7 @@
       <c r="AT295" s="67" t="inlineStr"/>
     </row>
     <row r="296">
-      <c r="A296" s="68" t="inlineStr">
+      <c r="A296" s="53" t="inlineStr">
         <is>
           <t>PS5-99-04 - Area Completion for Process area</t>
         </is>
@@ -35129,7 +37674,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP296" s="65" t="inlineStr"/>
+      <c r="AP296" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ296" s="65" t="inlineStr">
         <is>
           <t>9</t>
@@ -35144,7 +37693,7 @@
       <c r="AT296" s="67" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" s="68" t="inlineStr">
+      <c r="A297" s="53" t="inlineStr">
         <is>
           <t>PS5-99-05 - Area Completion for CFO area</t>
         </is>
@@ -35251,7 +37800,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP297" s="65" t="inlineStr"/>
+      <c r="AP297" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ297" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -35266,7 +37819,7 @@
       <c r="AT297" s="67" t="inlineStr"/>
     </row>
     <row r="298">
-      <c r="A298" s="68" t="inlineStr">
+      <c r="A298" s="53" t="inlineStr">
         <is>
           <t>PS5-99-06 - Area Completion for Power Generation area</t>
         </is>
@@ -35377,7 +37930,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP298" s="65" t="inlineStr"/>
+      <c r="AP298" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AQ298" s="65" t="inlineStr">
         <is>
           <t>1</t>

--- a/EXCEL/2 - RFC PROGRESS.xlsx
+++ b/EXCEL/2 - RFC PROGRESS.xlsx
@@ -1698,21 +1698,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP4" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ4" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR4" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP4" s="65" t="inlineStr"/>
+      <c r="AQ4" s="65" t="inlineStr"/>
+      <c r="AR4" s="23" t="inlineStr"/>
       <c r="AS4" s="66" t="n"/>
       <c r="AT4" s="67" t="inlineStr"/>
     </row>
@@ -1828,21 +1816,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP5" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP5" s="65" t="inlineStr"/>
       <c r="AQ5" s="65" t="inlineStr">
         <is>
           <t>EACOP(MR.BENHER TBC)-EXPECTED 19-08-2026</t>
         </is>
       </c>
-      <c r="AR5" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AR5" s="23" t="inlineStr"/>
       <c r="AS5" s="23" t="n"/>
       <c r="AT5" s="67" t="inlineStr"/>
     </row>
@@ -1958,21 +1938,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP6" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ6" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AR6" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP6" s="65" t="inlineStr"/>
+      <c r="AQ6" s="65" t="inlineStr"/>
+      <c r="AR6" s="23" t="inlineStr"/>
       <c r="AS6" s="23" t="n"/>
       <c r="AT6" s="67" t="inlineStr"/>
     </row>
@@ -2084,21 +2052,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP7" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ7" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR7" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP7" s="65" t="inlineStr"/>
+      <c r="AQ7" s="65" t="inlineStr"/>
+      <c r="AR7" s="23" t="inlineStr"/>
       <c r="AS7" s="23" t="n"/>
       <c r="AT7" s="67" t="inlineStr"/>
     </row>
@@ -2214,21 +2170,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP8" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ8" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR8" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP8" s="65" t="inlineStr"/>
+      <c r="AQ8" s="65" t="inlineStr"/>
+      <c r="AR8" s="23" t="inlineStr"/>
       <c r="AS8" s="23" t="n"/>
       <c r="AT8" s="67" t="inlineStr"/>
     </row>
@@ -2340,21 +2284,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP9" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ9" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR9" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP9" s="65" t="inlineStr"/>
+      <c r="AQ9" s="65" t="inlineStr"/>
+      <c r="AR9" s="23" t="inlineStr"/>
       <c r="AS9" s="23" t="n"/>
       <c r="AT9" s="67" t="inlineStr"/>
     </row>
@@ -2468,21 +2400,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP10" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ10" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AR10" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="AP10" s="65" t="inlineStr"/>
+      <c r="AQ10" s="65" t="inlineStr"/>
+      <c r="AR10" s="23" t="inlineStr"/>
       <c r="AS10" s="23" t="n"/>
       <c r="AT10" s="67" t="inlineStr"/>
     </row>
@@ -2598,21 +2518,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP11" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ11" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AR11" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP11" s="65" t="inlineStr"/>
+      <c r="AQ11" s="65" t="inlineStr"/>
+      <c r="AR11" s="23" t="inlineStr"/>
       <c r="AS11" s="23" t="n"/>
       <c r="AT11" s="67" t="inlineStr"/>
     </row>
@@ -2720,21 +2628,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP12" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ12" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR12" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP12" s="65" t="inlineStr"/>
+      <c r="AQ12" s="65" t="inlineStr"/>
+      <c r="AR12" s="23" t="inlineStr"/>
       <c r="AS12" s="23" t="n"/>
       <c r="AT12" s="67" t="inlineStr"/>
     </row>
@@ -2850,21 +2746,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP13" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ13" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR13" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP13" s="65" t="inlineStr"/>
+      <c r="AQ13" s="65" t="inlineStr"/>
+      <c r="AR13" s="23" t="inlineStr"/>
       <c r="AS13" s="23" t="n"/>
       <c r="AT13" s="67" t="inlineStr"/>
     </row>
@@ -2980,21 +2864,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP14" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ14" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR14" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP14" s="65" t="inlineStr"/>
+      <c r="AQ14" s="65" t="inlineStr"/>
+      <c r="AR14" s="23" t="inlineStr"/>
       <c r="AS14" s="23" t="n"/>
       <c r="AT14" s="67" t="inlineStr"/>
     </row>
@@ -3106,21 +2978,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP15" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AQ15" s="65" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AR15" s="23" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+      <c r="AP15" s="65" t="inlineStr"/>
+      <c r="AQ15" s="65" t="inlineStr"/>
+      <c r="AR15" s="23" t="inlineStr"/>
       <c r="AS15" s="23" t="n"/>
       <c r="AT15" s="67" t="inlineStr"/>
     </row>
@@ -3232,21 +3092,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP16" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ16" s="65" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="AR16" s="23" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+      <c r="AP16" s="65" t="inlineStr"/>
+      <c r="AQ16" s="65" t="inlineStr"/>
+      <c r="AR16" s="23" t="inlineStr"/>
       <c r="AS16" s="23" t="n"/>
       <c r="AT16" s="67" t="inlineStr"/>
     </row>
@@ -3362,21 +3210,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP17" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ17" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR17" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP17" s="65" t="inlineStr"/>
+      <c r="AQ17" s="65" t="inlineStr"/>
+      <c r="AR17" s="23" t="inlineStr"/>
       <c r="AS17" s="23" t="n"/>
       <c r="AT17" s="67" t="inlineStr"/>
     </row>
@@ -3484,21 +3320,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP18" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ18" s="65" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AR18" s="23" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="AP18" s="65" t="inlineStr"/>
+      <c r="AQ18" s="65" t="inlineStr"/>
+      <c r="AR18" s="23" t="inlineStr"/>
       <c r="AS18" s="23" t="n"/>
       <c r="AT18" s="67" t="inlineStr"/>
     </row>
@@ -3614,21 +3438,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP19" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ19" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AR19" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP19" s="65" t="inlineStr"/>
+      <c r="AQ19" s="65" t="inlineStr"/>
+      <c r="AR19" s="23" t="inlineStr"/>
       <c r="AS19" s="23" t="n"/>
       <c r="AT19" s="67" t="inlineStr"/>
     </row>
@@ -3744,21 +3556,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP20" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ20" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR20" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP20" s="65" t="inlineStr"/>
+      <c r="AQ20" s="65" t="inlineStr"/>
+      <c r="AR20" s="23" t="inlineStr"/>
       <c r="AS20" s="23" t="n"/>
       <c r="AT20" s="67" t="inlineStr"/>
     </row>
@@ -3874,21 +3674,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP21" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ21" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR21" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP21" s="65" t="inlineStr"/>
+      <c r="AQ21" s="65" t="inlineStr"/>
+      <c r="AR21" s="23" t="inlineStr"/>
       <c r="AS21" s="23" t="n"/>
       <c r="AT21" s="67" t="inlineStr"/>
     </row>
@@ -4004,21 +3792,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP22" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ22" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AR22" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP22" s="65" t="inlineStr"/>
+      <c r="AQ22" s="65" t="inlineStr"/>
+      <c r="AR22" s="23" t="inlineStr"/>
       <c r="AS22" s="23" t="n"/>
       <c r="AT22" s="67" t="inlineStr"/>
     </row>
@@ -4134,21 +3910,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP23" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ23" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR23" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP23" s="65" t="inlineStr"/>
+      <c r="AQ23" s="65" t="inlineStr"/>
+      <c r="AR23" s="23" t="inlineStr"/>
       <c r="AS23" s="23" t="n"/>
       <c r="AT23" s="67" t="inlineStr"/>
     </row>
@@ -4264,21 +4028,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP24" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ24" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR24" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP24" s="65" t="inlineStr"/>
+      <c r="AQ24" s="65" t="inlineStr"/>
+      <c r="AR24" s="23" t="inlineStr"/>
       <c r="AS24" s="23" t="n"/>
       <c r="AT24" s="67" t="inlineStr"/>
     </row>
@@ -4394,21 +4146,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP25" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ25" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR25" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP25" s="65" t="inlineStr"/>
+      <c r="AQ25" s="65" t="inlineStr"/>
+      <c r="AR25" s="23" t="inlineStr"/>
       <c r="AS25" s="23" t="n"/>
       <c r="AT25" s="67" t="inlineStr"/>
     </row>
@@ -4524,21 +4264,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP26" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ26" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR26" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP26" s="65" t="inlineStr"/>
+      <c r="AQ26" s="65" t="inlineStr"/>
+      <c r="AR26" s="23" t="inlineStr"/>
       <c r="AS26" s="23" t="n"/>
       <c r="AT26" s="67" t="inlineStr"/>
     </row>
@@ -4654,21 +4382,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP27" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ27" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR27" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP27" s="65" t="inlineStr"/>
+      <c r="AQ27" s="65" t="inlineStr"/>
+      <c r="AR27" s="23" t="inlineStr"/>
       <c r="AS27" s="23" t="n"/>
       <c r="AT27" s="67" t="inlineStr"/>
     </row>
@@ -4780,21 +4496,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP28" s="65" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="AQ28" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AR28" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP28" s="65" t="inlineStr"/>
+      <c r="AQ28" s="65" t="inlineStr"/>
+      <c r="AR28" s="23" t="inlineStr"/>
       <c r="AS28" s="23" t="n"/>
       <c r="AT28" s="67" t="inlineStr"/>
     </row>
@@ -4906,21 +4610,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP29" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AQ29" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR29" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP29" s="65" t="inlineStr"/>
+      <c r="AQ29" s="65" t="inlineStr"/>
+      <c r="AR29" s="23" t="inlineStr"/>
       <c r="AS29" s="23" t="n"/>
       <c r="AT29" s="67" t="inlineStr"/>
     </row>
@@ -5032,21 +4724,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP30" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AQ30" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR30" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP30" s="65" t="inlineStr"/>
+      <c r="AQ30" s="65" t="inlineStr"/>
+      <c r="AR30" s="23" t="inlineStr"/>
       <c r="AS30" s="23" t="n"/>
       <c r="AT30" s="67" t="inlineStr"/>
     </row>
@@ -5158,21 +4838,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP31" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AQ31" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR31" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP31" s="65" t="inlineStr"/>
+      <c r="AQ31" s="65" t="inlineStr"/>
+      <c r="AR31" s="23" t="inlineStr"/>
       <c r="AS31" s="23" t="n"/>
       <c r="AT31" s="67" t="inlineStr"/>
     </row>
@@ -5284,21 +4952,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP32" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AQ32" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR32" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP32" s="65" t="inlineStr"/>
+      <c r="AQ32" s="65" t="inlineStr"/>
+      <c r="AR32" s="23" t="inlineStr"/>
       <c r="AS32" s="23" t="n"/>
       <c r="AT32" s="67" t="inlineStr"/>
     </row>
@@ -5410,21 +5066,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP33" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AQ33" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR33" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP33" s="65" t="inlineStr"/>
+      <c r="AQ33" s="65" t="inlineStr"/>
+      <c r="AR33" s="23" t="inlineStr"/>
       <c r="AS33" s="23" t="n"/>
       <c r="AT33" s="67" t="inlineStr"/>
     </row>
@@ -5536,21 +5180,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP34" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ34" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR34" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP34" s="65" t="inlineStr"/>
+      <c r="AQ34" s="65" t="inlineStr"/>
+      <c r="AR34" s="23" t="inlineStr"/>
       <c r="AS34" s="23" t="n"/>
       <c r="AT34" s="67" t="inlineStr"/>
     </row>
@@ -5658,21 +5290,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP35" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AQ35" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR35" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP35" s="65" t="inlineStr"/>
+      <c r="AQ35" s="65" t="inlineStr"/>
+      <c r="AR35" s="23" t="inlineStr"/>
       <c r="AS35" s="23" t="n"/>
       <c r="AT35" s="67" t="inlineStr"/>
     </row>
@@ -5780,21 +5400,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP36" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ36" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR36" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP36" s="65" t="inlineStr"/>
+      <c r="AQ36" s="65" t="inlineStr"/>
+      <c r="AR36" s="23" t="inlineStr"/>
       <c r="AS36" s="23" t="n"/>
       <c r="AT36" s="67" t="inlineStr"/>
     </row>
@@ -5986,21 +5594,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP38" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ38" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR38" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP38" s="65" t="inlineStr"/>
+      <c r="AQ38" s="65" t="inlineStr"/>
+      <c r="AR38" s="23" t="inlineStr"/>
       <c r="AS38" s="23" t="n"/>
       <c r="AT38" s="67" t="inlineStr"/>
     </row>
@@ -6108,21 +5704,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP39" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ39" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR39" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP39" s="65" t="inlineStr"/>
+      <c r="AQ39" s="65" t="inlineStr"/>
+      <c r="AR39" s="23" t="inlineStr"/>
       <c r="AS39" s="23" t="n"/>
       <c r="AT39" s="67" t="inlineStr"/>
     </row>
@@ -6314,21 +5898,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP41" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ41" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AR41" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="AP41" s="65" t="inlineStr"/>
+      <c r="AQ41" s="65" t="inlineStr"/>
+      <c r="AR41" s="23" t="inlineStr"/>
       <c r="AS41" s="23" t="n"/>
       <c r="AT41" s="67" t="inlineStr"/>
     </row>
@@ -6694,21 +6266,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP45" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ45" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR45" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP45" s="65" t="inlineStr"/>
+      <c r="AQ45" s="65" t="inlineStr"/>
+      <c r="AR45" s="23" t="inlineStr"/>
       <c r="AS45" s="23" t="n"/>
       <c r="AT45" s="67" t="inlineStr"/>
     </row>
@@ -6820,21 +6380,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP46" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ46" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR46" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP46" s="65" t="inlineStr"/>
+      <c r="AQ46" s="65" t="inlineStr"/>
+      <c r="AR46" s="23" t="inlineStr"/>
       <c r="AS46" s="23" t="n"/>
       <c r="AT46" s="67" t="inlineStr"/>
     </row>
@@ -7034,21 +6582,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP48" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ48" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR48" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP48" s="65" t="inlineStr"/>
+      <c r="AQ48" s="65" t="inlineStr"/>
+      <c r="AR48" s="23" t="inlineStr"/>
       <c r="AS48" s="23" t="n"/>
       <c r="AT48" s="67" t="inlineStr"/>
     </row>
@@ -7156,21 +6692,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP49" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ49" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR49" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP49" s="65" t="inlineStr"/>
+      <c r="AQ49" s="65" t="inlineStr"/>
+      <c r="AR49" s="23" t="inlineStr"/>
       <c r="AS49" s="23" t="n"/>
       <c r="AT49" s="67" t="inlineStr"/>
     </row>
@@ -7278,21 +6802,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP50" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ50" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR50" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP50" s="65" t="inlineStr"/>
+      <c r="AQ50" s="65" t="inlineStr"/>
+      <c r="AR50" s="23" t="inlineStr"/>
       <c r="AS50" s="23" t="n"/>
       <c r="AT50" s="67" t="inlineStr"/>
     </row>
@@ -7400,21 +6912,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP51" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ51" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR51" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP51" s="65" t="inlineStr"/>
+      <c r="AQ51" s="65" t="inlineStr"/>
+      <c r="AR51" s="23" t="inlineStr"/>
       <c r="AS51" s="23" t="n"/>
       <c r="AT51" s="67" t="inlineStr"/>
     </row>
@@ -7522,21 +7022,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP52" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ52" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR52" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP52" s="65" t="inlineStr"/>
+      <c r="AQ52" s="65" t="inlineStr"/>
+      <c r="AR52" s="23" t="inlineStr"/>
       <c r="AS52" s="23" t="n"/>
       <c r="AT52" s="67" t="inlineStr"/>
     </row>
@@ -7557,9 +7045,9 @@
         </is>
       </c>
       <c r="H53" s="24" t="inlineStr"/>
-      <c r="I53" s="69" t="inlineStr">
-        <is>
-          <t>74%</t>
+      <c r="I53" s="70" t="inlineStr">
+        <is>
+          <t>9%</t>
         </is>
       </c>
       <c r="J53" s="55" t="n">
@@ -7587,25 +7075,25 @@
         <v>96</v>
       </c>
       <c r="R53" s="62" t="n">
-        <v>71</v>
-      </c>
-      <c r="S53" s="77" t="inlineStr">
-        <is>
-          <t>74%</t>
+        <v>9</v>
+      </c>
+      <c r="S53" s="72" t="inlineStr">
+        <is>
+          <t>9%</t>
         </is>
       </c>
       <c r="AH53" s="28" t="n">
         <v>96</v>
       </c>
       <c r="AI53" s="23" t="n">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="AJ53" s="23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK53" s="26" t="inlineStr">
-        <is>
-          <t>74%</t>
+        <v>87</v>
+      </c>
+      <c r="AK53" s="25" t="inlineStr">
+        <is>
+          <t>9%</t>
         </is>
       </c>
       <c r="AL53" s="23" t="n">
@@ -7643,7 +7131,7 @@
       <c r="H54" s="24" t="inlineStr"/>
       <c r="I54" s="70" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="J54" s="55" t="n">
@@ -7671,25 +7159,25 @@
         <v>134</v>
       </c>
       <c r="R54" s="62" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="S54" s="72" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="AH54" s="28" t="n">
         <v>134</v>
       </c>
       <c r="AI54" s="23" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AJ54" s="23" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="AK54" s="25" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="AL54" s="23" t="n">
@@ -7812,21 +7300,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP55" s="65" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ55" s="65" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AR55" s="23" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="AP55" s="65" t="inlineStr"/>
+      <c r="AQ55" s="65" t="inlineStr"/>
+      <c r="AR55" s="23" t="inlineStr"/>
       <c r="AS55" s="23" t="n"/>
       <c r="AT55" s="67" t="inlineStr"/>
     </row>
@@ -8102,21 +7578,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP58" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ58" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AR58" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP58" s="65" t="inlineStr"/>
+      <c r="AQ58" s="65" t="inlineStr"/>
+      <c r="AR58" s="23" t="inlineStr"/>
       <c r="AS58" s="23" t="n"/>
       <c r="AT58" s="67" t="inlineStr"/>
     </row>
@@ -8224,21 +7688,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP59" s="65" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AQ59" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AR59" s="23" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="AP59" s="65" t="inlineStr"/>
+      <c r="AQ59" s="65" t="inlineStr"/>
+      <c r="AR59" s="23" t="inlineStr"/>
       <c r="AS59" s="23" t="n"/>
       <c r="AT59" s="67" t="inlineStr"/>
     </row>
@@ -8346,21 +7798,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP60" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ60" s="65" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AR60" s="23" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="AP60" s="65" t="inlineStr"/>
+      <c r="AQ60" s="65" t="inlineStr"/>
+      <c r="AR60" s="23" t="inlineStr"/>
       <c r="AS60" s="23" t="n"/>
       <c r="AT60" s="67" t="inlineStr"/>
     </row>
@@ -8468,21 +7908,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP61" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ61" s="65" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AR61" s="23" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="AP61" s="65" t="inlineStr"/>
+      <c r="AQ61" s="65" t="inlineStr"/>
+      <c r="AR61" s="23" t="inlineStr"/>
       <c r="AS61" s="23" t="n"/>
       <c r="AT61" s="67" t="inlineStr"/>
     </row>
@@ -8590,21 +8018,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP62" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ62" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AR62" s="23" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="AP62" s="65" t="inlineStr"/>
+      <c r="AQ62" s="65" t="inlineStr"/>
+      <c r="AR62" s="23" t="inlineStr"/>
       <c r="AS62" s="23" t="n"/>
       <c r="AT62" s="67" t="inlineStr"/>
     </row>
@@ -8712,21 +8128,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP63" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ63" s="65" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AR63" s="23" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="AP63" s="65" t="inlineStr"/>
+      <c r="AQ63" s="65" t="inlineStr"/>
+      <c r="AR63" s="23" t="inlineStr"/>
       <c r="AS63" s="23" t="n"/>
       <c r="AT63" s="67" t="inlineStr"/>
     </row>
@@ -8834,21 +8238,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP64" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ64" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AR64" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="AP64" s="65" t="inlineStr"/>
+      <c r="AQ64" s="65" t="inlineStr"/>
+      <c r="AR64" s="23" t="inlineStr"/>
       <c r="AS64" s="23" t="n"/>
       <c r="AT64" s="67" t="inlineStr"/>
     </row>
@@ -9040,21 +8432,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP66" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ66" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AR66" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP66" s="65" t="inlineStr"/>
+      <c r="AQ66" s="65" t="inlineStr"/>
+      <c r="AR66" s="23" t="inlineStr"/>
       <c r="AS66" s="23" t="n"/>
       <c r="AT66" s="67" t="inlineStr"/>
     </row>
@@ -9162,21 +8542,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP67" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ67" s="65" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AR67" s="23" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="AP67" s="65" t="inlineStr"/>
+      <c r="AQ67" s="65" t="inlineStr"/>
+      <c r="AR67" s="23" t="inlineStr"/>
       <c r="AS67" s="23" t="n"/>
       <c r="AT67" s="67" t="inlineStr"/>
     </row>
@@ -9199,7 +8567,7 @@
       <c r="H68" s="24" t="inlineStr"/>
       <c r="I68" s="70" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J68" s="55" t="n">
@@ -9227,25 +8595,25 @@
         <v>50</v>
       </c>
       <c r="R68" s="62" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S68" s="72" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AH68" s="28" t="n">
         <v>51</v>
       </c>
       <c r="AI68" s="23" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ68" s="23" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="AK68" s="25" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AL68" s="23" t="n">
@@ -9283,7 +8651,7 @@
       <c r="H69" s="24" t="inlineStr"/>
       <c r="I69" s="70" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J69" s="55" t="n">
@@ -9311,25 +8679,25 @@
         <v>23</v>
       </c>
       <c r="R69" s="62" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S69" s="72" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AH69" s="28" t="n">
         <v>23</v>
       </c>
       <c r="AI69" s="23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ69" s="23" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AK69" s="25" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AL69" s="23" t="n">
@@ -9536,21 +8904,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP71" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ71" s="65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AR71" s="23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="AP71" s="65" t="inlineStr"/>
+      <c r="AQ71" s="65" t="inlineStr"/>
+      <c r="AR71" s="23" t="inlineStr"/>
       <c r="AS71" s="23" t="n"/>
       <c r="AT71" s="67" t="inlineStr"/>
     </row>
@@ -9658,21 +9014,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP72" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ72" s="65" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="AR72" s="23" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
+      <c r="AP72" s="65" t="inlineStr"/>
+      <c r="AQ72" s="65" t="inlineStr"/>
+      <c r="AR72" s="23" t="inlineStr"/>
       <c r="AS72" s="23" t="n"/>
       <c r="AT72" s="67" t="inlineStr"/>
     </row>
@@ -9780,21 +9124,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP73" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ73" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AR73" s="23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="AP73" s="65" t="inlineStr"/>
+      <c r="AQ73" s="65" t="inlineStr"/>
+      <c r="AR73" s="23" t="inlineStr"/>
       <c r="AS73" s="23" t="n"/>
       <c r="AT73" s="67" t="inlineStr"/>
     </row>
@@ -10070,21 +9402,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP76" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AQ76" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR76" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP76" s="65" t="inlineStr"/>
+      <c r="AQ76" s="65" t="inlineStr"/>
+      <c r="AR76" s="23" t="inlineStr"/>
       <c r="AS76" s="23" t="n"/>
       <c r="AT76" s="67" t="inlineStr"/>
     </row>
@@ -10177,7 +9497,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM77" s="64" t="inlineStr">
+      <c r="AM77" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10192,21 +9512,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP77" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AQ77" s="65" t="inlineStr">
-        <is>
-          <t>-208</t>
-        </is>
-      </c>
-      <c r="AR77" s="23" t="inlineStr">
-        <is>
-          <t>-208</t>
-        </is>
-      </c>
+      <c r="AP77" s="65" t="inlineStr"/>
+      <c r="AQ77" s="65" t="inlineStr"/>
+      <c r="AR77" s="23" t="inlineStr"/>
       <c r="AS77" s="23" t="n"/>
       <c r="AT77" s="67" t="inlineStr"/>
     </row>
@@ -10229,7 +9537,7 @@
       <c r="H78" s="24" t="inlineStr"/>
       <c r="I78" s="70" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="J78" s="55" t="n">
@@ -10257,25 +9565,25 @@
         <v>92</v>
       </c>
       <c r="R78" s="62" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="S78" s="72" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="AH78" s="28" t="n">
         <v>92</v>
       </c>
       <c r="AI78" s="23" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AJ78" s="23" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="AK78" s="25" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="AL78" s="23" t="n">
@@ -10313,7 +9621,7 @@
       <c r="H79" s="24" t="inlineStr"/>
       <c r="I79" s="70" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="J79" s="55" t="n">
@@ -10341,25 +9649,25 @@
         <v>151</v>
       </c>
       <c r="R79" s="62" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="S79" s="72" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="AH79" s="28" t="n">
         <v>157</v>
       </c>
       <c r="AI79" s="23" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AJ79" s="23" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AK79" s="25" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="AL79" s="23" t="n">
@@ -10650,21 +9958,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP82" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ82" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AR82" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP82" s="65" t="inlineStr"/>
+      <c r="AQ82" s="65" t="inlineStr"/>
+      <c r="AR82" s="23" t="inlineStr"/>
       <c r="AS82" s="23" t="n"/>
       <c r="AT82" s="67" t="inlineStr"/>
     </row>
@@ -10772,21 +10068,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP83" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ83" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR83" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP83" s="65" t="inlineStr"/>
+      <c r="AQ83" s="65" t="inlineStr"/>
+      <c r="AR83" s="23" t="inlineStr"/>
       <c r="AS83" s="23" t="n"/>
       <c r="AT83" s="67" t="inlineStr"/>
     </row>
@@ -10894,21 +10178,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP84" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ84" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR84" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP84" s="65" t="inlineStr"/>
+      <c r="AQ84" s="65" t="inlineStr"/>
+      <c r="AR84" s="23" t="inlineStr"/>
       <c r="AS84" s="23" t="n"/>
       <c r="AT84" s="67" t="inlineStr"/>
     </row>
@@ -11020,21 +10292,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AP85" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AQ85" s="65" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="AR85" s="23" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
+      <c r="AP85" s="65" t="inlineStr"/>
+      <c r="AQ85" s="65" t="inlineStr"/>
+      <c r="AR85" s="23" t="inlineStr"/>
       <c r="AS85" s="23" t="n"/>
       <c r="AT85" s="67" t="inlineStr"/>
     </row>
@@ -11142,21 +10402,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP86" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ86" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR86" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP86" s="65" t="inlineStr"/>
+      <c r="AQ86" s="65" t="inlineStr"/>
+      <c r="AR86" s="23" t="inlineStr"/>
       <c r="AS86" s="23" t="n"/>
       <c r="AT86" s="67" t="inlineStr"/>
     </row>
@@ -11264,21 +10512,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP87" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ87" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR87" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP87" s="65" t="inlineStr"/>
+      <c r="AQ87" s="65" t="inlineStr"/>
+      <c r="AR87" s="23" t="inlineStr"/>
       <c r="AS87" s="23" t="n"/>
       <c r="AT87" s="67" t="inlineStr"/>
     </row>
@@ -11470,21 +10706,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AP89" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ89" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AR89" s="23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="AP89" s="65" t="inlineStr"/>
+      <c r="AQ89" s="65" t="inlineStr"/>
+      <c r="AR89" s="23" t="inlineStr"/>
       <c r="AS89" s="23" t="n"/>
       <c r="AT89" s="67" t="inlineStr"/>
     </row>
@@ -11592,21 +10816,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP90" s="65" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AQ90" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AR90" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="AP90" s="65" t="inlineStr"/>
+      <c r="AQ90" s="65" t="inlineStr"/>
+      <c r="AR90" s="23" t="inlineStr"/>
       <c r="AS90" s="23" t="n"/>
       <c r="AT90" s="67" t="inlineStr"/>
     </row>
@@ -11714,21 +10926,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP91" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AQ91" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AR91" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP91" s="65" t="inlineStr"/>
+      <c r="AQ91" s="65" t="inlineStr"/>
+      <c r="AR91" s="23" t="inlineStr"/>
       <c r="AS91" s="23" t="n"/>
       <c r="AT91" s="67" t="inlineStr"/>
     </row>
@@ -11836,21 +11036,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP92" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AQ92" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AR92" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP92" s="65" t="inlineStr"/>
+      <c r="AQ92" s="65" t="inlineStr"/>
+      <c r="AR92" s="23" t="inlineStr"/>
       <c r="AS92" s="23" t="n"/>
       <c r="AT92" s="67" t="inlineStr"/>
     </row>
@@ -11962,21 +11150,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP93" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ93" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR93" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP93" s="65" t="inlineStr"/>
+      <c r="AQ93" s="65" t="inlineStr"/>
+      <c r="AR93" s="23" t="inlineStr"/>
       <c r="AS93" s="23" t="n"/>
       <c r="AT93" s="67" t="inlineStr"/>
     </row>
@@ -12084,21 +11260,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP94" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ94" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AR94" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP94" s="65" t="inlineStr"/>
+      <c r="AQ94" s="65" t="inlineStr"/>
+      <c r="AR94" s="23" t="inlineStr"/>
       <c r="AS94" s="23" t="n"/>
       <c r="AT94" s="67" t="inlineStr"/>
     </row>
@@ -12206,21 +11370,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP95" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ95" s="65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AR95" s="23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="AP95" s="65" t="inlineStr"/>
+      <c r="AQ95" s="65" t="inlineStr"/>
+      <c r="AR95" s="23" t="inlineStr"/>
       <c r="AS95" s="23" t="n"/>
       <c r="AT95" s="67" t="inlineStr"/>
     </row>
@@ -12332,21 +11484,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP96" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ96" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AR96" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP96" s="65" t="inlineStr"/>
+      <c r="AQ96" s="65" t="inlineStr"/>
+      <c r="AR96" s="23" t="inlineStr"/>
       <c r="AS96" s="23" t="n"/>
       <c r="AT96" s="67" t="inlineStr"/>
     </row>
@@ -12458,21 +11598,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP97" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ97" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR97" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP97" s="65" t="inlineStr"/>
+      <c r="AQ97" s="65" t="inlineStr"/>
+      <c r="AR97" s="23" t="inlineStr"/>
       <c r="AS97" s="23" t="n"/>
       <c r="AT97" s="67" t="inlineStr"/>
     </row>
@@ -12588,21 +11716,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP98" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ98" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AR98" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP98" s="65" t="inlineStr"/>
+      <c r="AQ98" s="65" t="inlineStr"/>
+      <c r="AR98" s="23" t="inlineStr"/>
       <c r="AS98" s="23" t="n"/>
       <c r="AT98" s="67" t="inlineStr"/>
     </row>
@@ -12718,21 +11834,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP99" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ99" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AR99" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="AP99" s="65" t="inlineStr"/>
+      <c r="AQ99" s="65" t="inlineStr"/>
+      <c r="AR99" s="23" t="inlineStr"/>
       <c r="AS99" s="23" t="n"/>
       <c r="AT99" s="67" t="inlineStr"/>
     </row>
@@ -12848,21 +11952,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP100" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ100" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR100" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP100" s="65" t="inlineStr"/>
+      <c r="AQ100" s="65" t="inlineStr"/>
+      <c r="AR100" s="23" t="inlineStr"/>
       <c r="AS100" s="23" t="n"/>
       <c r="AT100" s="67" t="inlineStr"/>
     </row>
@@ -12978,21 +12070,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP101" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ101" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR101" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP101" s="65" t="inlineStr"/>
+      <c r="AQ101" s="65" t="inlineStr"/>
+      <c r="AR101" s="23" t="inlineStr"/>
       <c r="AS101" s="23" t="n"/>
       <c r="AT101" s="67" t="inlineStr"/>
     </row>
@@ -13104,21 +12184,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP102" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ102" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR102" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP102" s="65" t="inlineStr"/>
+      <c r="AQ102" s="65" t="inlineStr"/>
+      <c r="AR102" s="23" t="inlineStr"/>
       <c r="AS102" s="23" t="n"/>
       <c r="AT102" s="67" t="inlineStr"/>
     </row>
@@ -13234,21 +12302,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP103" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ103" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AR103" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP103" s="65" t="inlineStr"/>
+      <c r="AQ103" s="65" t="inlineStr"/>
+      <c r="AR103" s="23" t="inlineStr"/>
       <c r="AS103" s="23" t="n"/>
       <c r="AT103" s="67" t="inlineStr"/>
     </row>
@@ -13356,21 +12412,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP104" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ104" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AR104" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP104" s="65" t="inlineStr"/>
+      <c r="AQ104" s="65" t="inlineStr"/>
+      <c r="AR104" s="23" t="inlineStr"/>
       <c r="AS104" s="23" t="n"/>
       <c r="AT104" s="67" t="inlineStr"/>
     </row>
@@ -13478,21 +12522,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP105" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ105" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AR105" s="23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="AP105" s="65" t="inlineStr"/>
+      <c r="AQ105" s="65" t="inlineStr"/>
+      <c r="AR105" s="23" t="inlineStr"/>
       <c r="AS105" s="23" t="n"/>
       <c r="AT105" s="67" t="inlineStr"/>
     </row>
@@ -13608,21 +12640,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP106" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ106" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR106" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP106" s="65" t="inlineStr"/>
+      <c r="AQ106" s="65" t="inlineStr"/>
+      <c r="AR106" s="23" t="inlineStr"/>
       <c r="AS106" s="23" t="n"/>
       <c r="AT106" s="67" t="inlineStr"/>
     </row>
@@ -13734,21 +12754,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP107" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ107" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR107" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP107" s="65" t="inlineStr"/>
+      <c r="AQ107" s="65" t="inlineStr"/>
+      <c r="AR107" s="23" t="inlineStr"/>
       <c r="AS107" s="23" t="n"/>
       <c r="AT107" s="67" t="inlineStr"/>
     </row>
@@ -13864,21 +12872,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP108" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ108" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR108" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP108" s="65" t="inlineStr"/>
+      <c r="AQ108" s="65" t="inlineStr"/>
+      <c r="AR108" s="23" t="inlineStr"/>
       <c r="AS108" s="23" t="n"/>
       <c r="AT108" s="67" t="inlineStr"/>
     </row>
@@ -13994,21 +12990,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP109" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ109" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR109" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP109" s="65" t="inlineStr"/>
+      <c r="AQ109" s="65" t="inlineStr"/>
+      <c r="AR109" s="23" t="inlineStr"/>
       <c r="AS109" s="23" t="n"/>
       <c r="AT109" s="67" t="inlineStr"/>
     </row>
@@ -14124,21 +13108,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP110" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ110" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR110" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP110" s="65" t="inlineStr"/>
+      <c r="AQ110" s="65" t="inlineStr"/>
+      <c r="AR110" s="23" t="inlineStr"/>
       <c r="AS110" s="23" t="n"/>
       <c r="AT110" s="67" t="inlineStr"/>
     </row>
@@ -14250,21 +13222,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP111" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ111" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR111" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP111" s="65" t="inlineStr"/>
+      <c r="AQ111" s="65" t="inlineStr"/>
+      <c r="AR111" s="23" t="inlineStr"/>
       <c r="AS111" s="23" t="n"/>
       <c r="AT111" s="67" t="inlineStr"/>
     </row>
@@ -14376,21 +13336,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP112" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ112" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AR112" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="AP112" s="65" t="inlineStr"/>
+      <c r="AQ112" s="65" t="inlineStr"/>
+      <c r="AR112" s="23" t="inlineStr"/>
       <c r="AS112" s="23" t="n"/>
       <c r="AT112" s="67" t="inlineStr"/>
     </row>
@@ -14498,21 +13446,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP113" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ113" s="65" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AR113" s="23" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="AP113" s="65" t="inlineStr"/>
+      <c r="AQ113" s="65" t="inlineStr"/>
+      <c r="AR113" s="23" t="inlineStr"/>
       <c r="AS113" s="23" t="n"/>
       <c r="AT113" s="67" t="inlineStr"/>
     </row>
@@ -14620,21 +13556,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP114" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ114" s="65" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AR114" s="23" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="AP114" s="65" t="inlineStr"/>
+      <c r="AQ114" s="65" t="inlineStr"/>
+      <c r="AR114" s="23" t="inlineStr"/>
       <c r="AS114" s="23" t="n"/>
       <c r="AT114" s="67" t="inlineStr"/>
     </row>
@@ -14746,21 +13670,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP115" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AQ115" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AR115" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="AP115" s="65" t="inlineStr"/>
+      <c r="AQ115" s="65" t="inlineStr"/>
+      <c r="AR115" s="23" t="inlineStr"/>
       <c r="AS115" s="23" t="n"/>
       <c r="AT115" s="67" t="inlineStr"/>
     </row>
@@ -14876,21 +13788,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP116" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ116" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AR116" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP116" s="65" t="inlineStr"/>
+      <c r="AQ116" s="65" t="inlineStr"/>
+      <c r="AR116" s="23" t="inlineStr"/>
       <c r="AS116" s="23" t="n"/>
       <c r="AT116" s="67" t="inlineStr"/>
     </row>
@@ -15006,21 +13906,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP117" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ117" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR117" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP117" s="65" t="inlineStr"/>
+      <c r="AQ117" s="65" t="inlineStr"/>
+      <c r="AR117" s="23" t="inlineStr"/>
       <c r="AS117" s="23" t="n"/>
       <c r="AT117" s="67" t="inlineStr"/>
     </row>
@@ -15136,21 +14024,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP118" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ118" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AR118" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="AP118" s="65" t="inlineStr"/>
+      <c r="AQ118" s="65" t="inlineStr"/>
+      <c r="AR118" s="23" t="inlineStr"/>
       <c r="AS118" s="23" t="n"/>
       <c r="AT118" s="67" t="inlineStr"/>
     </row>
@@ -15262,21 +14138,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP119" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ119" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AR119" s="23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="AP119" s="65" t="inlineStr"/>
+      <c r="AQ119" s="65" t="inlineStr"/>
+      <c r="AR119" s="23" t="inlineStr"/>
       <c r="AS119" s="23" t="n"/>
       <c r="AT119" s="67" t="inlineStr"/>
     </row>
@@ -15392,21 +14256,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP120" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ120" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR120" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP120" s="65" t="inlineStr"/>
+      <c r="AQ120" s="65" t="inlineStr"/>
+      <c r="AR120" s="23" t="inlineStr"/>
       <c r="AS120" s="23" t="n"/>
       <c r="AT120" s="67" t="inlineStr"/>
     </row>
@@ -15518,21 +14370,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP121" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ121" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AR121" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP121" s="65" t="inlineStr"/>
+      <c r="AQ121" s="65" t="inlineStr"/>
+      <c r="AR121" s="23" t="inlineStr"/>
       <c r="AS121" s="23" t="n"/>
       <c r="AT121" s="67" t="inlineStr"/>
     </row>
@@ -15648,21 +14488,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP122" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ122" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR122" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP122" s="65" t="inlineStr"/>
+      <c r="AQ122" s="65" t="inlineStr"/>
+      <c r="AR122" s="23" t="inlineStr"/>
       <c r="AS122" s="23" t="n"/>
       <c r="AT122" s="67" t="inlineStr"/>
     </row>
@@ -15778,16 +14606,8 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP123" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ123" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP123" s="65" t="inlineStr"/>
+      <c r="AQ123" s="65" t="inlineStr"/>
       <c r="AR123" s="23" t="inlineStr">
         <is>
           <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
@@ -15908,21 +14728,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP124" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ124" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR124" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP124" s="65" t="inlineStr"/>
+      <c r="AQ124" s="65" t="inlineStr"/>
+      <c r="AR124" s="23" t="inlineStr"/>
       <c r="AS124" s="23" t="n"/>
       <c r="AT124" s="67" t="inlineStr"/>
     </row>
@@ -16038,21 +14846,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP125" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ125" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR125" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP125" s="65" t="inlineStr"/>
+      <c r="AQ125" s="65" t="inlineStr"/>
+      <c r="AR125" s="23" t="inlineStr"/>
       <c r="AS125" s="23" t="n"/>
       <c r="AT125" s="67" t="inlineStr"/>
     </row>
@@ -16168,21 +14964,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP126" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ126" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR126" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP126" s="65" t="inlineStr"/>
+      <c r="AQ126" s="65" t="inlineStr"/>
+      <c r="AR126" s="23" t="inlineStr"/>
       <c r="AS126" s="23" t="n"/>
       <c r="AT126" s="67" t="inlineStr"/>
     </row>
@@ -16298,21 +15082,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP127" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ127" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR127" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP127" s="65" t="inlineStr"/>
+      <c r="AQ127" s="65" t="inlineStr"/>
+      <c r="AR127" s="23" t="inlineStr"/>
       <c r="AS127" s="23" t="n"/>
       <c r="AT127" s="67" t="inlineStr"/>
     </row>
@@ -16428,21 +15200,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP128" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AQ128" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR128" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP128" s="65" t="inlineStr"/>
+      <c r="AQ128" s="65" t="inlineStr"/>
+      <c r="AR128" s="23" t="inlineStr"/>
       <c r="AS128" s="23" t="n"/>
       <c r="AT128" s="67" t="inlineStr"/>
     </row>
@@ -16558,21 +15318,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP129" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ129" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR129" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP129" s="65" t="inlineStr"/>
+      <c r="AQ129" s="65" t="inlineStr"/>
+      <c r="AR129" s="23" t="inlineStr"/>
       <c r="AS129" s="23" t="n"/>
       <c r="AT129" s="67" t="inlineStr"/>
     </row>
@@ -16688,21 +15436,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP130" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ130" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR130" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP130" s="65" t="inlineStr"/>
+      <c r="AQ130" s="65" t="inlineStr"/>
+      <c r="AR130" s="23" t="inlineStr"/>
       <c r="AS130" s="23" t="n"/>
       <c r="AT130" s="67" t="inlineStr"/>
     </row>
@@ -16818,21 +15554,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP131" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AQ131" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR131" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP131" s="65" t="inlineStr"/>
+      <c r="AQ131" s="65" t="inlineStr"/>
+      <c r="AR131" s="23" t="inlineStr"/>
       <c r="AS131" s="23" t="n"/>
       <c r="AT131" s="67" t="inlineStr"/>
     </row>
@@ -16948,21 +15672,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP132" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ132" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR132" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP132" s="65" t="inlineStr"/>
+      <c r="AQ132" s="65" t="inlineStr"/>
+      <c r="AR132" s="23" t="inlineStr"/>
       <c r="AS132" s="23" t="n"/>
       <c r="AT132" s="67" t="inlineStr"/>
     </row>
@@ -17078,21 +15790,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP133" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ133" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR133" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP133" s="65" t="inlineStr"/>
+      <c r="AQ133" s="65" t="inlineStr"/>
+      <c r="AR133" s="23" t="inlineStr"/>
       <c r="AS133" s="23" t="n"/>
       <c r="AT133" s="67" t="inlineStr"/>
     </row>
@@ -17208,21 +15908,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP134" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ134" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR134" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP134" s="65" t="inlineStr"/>
+      <c r="AQ134" s="65" t="inlineStr"/>
+      <c r="AR134" s="23" t="inlineStr"/>
       <c r="AS134" s="23" t="n"/>
       <c r="AT134" s="67" t="inlineStr"/>
     </row>
@@ -17338,21 +16026,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP135" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ135" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR135" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP135" s="65" t="inlineStr"/>
+      <c r="AQ135" s="65" t="inlineStr"/>
+      <c r="AR135" s="23" t="inlineStr"/>
       <c r="AS135" s="23" t="n"/>
       <c r="AT135" s="67" t="inlineStr"/>
     </row>
@@ -17468,21 +16144,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP136" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ136" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR136" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP136" s="65" t="inlineStr"/>
+      <c r="AQ136" s="65" t="inlineStr"/>
+      <c r="AR136" s="23" t="inlineStr"/>
       <c r="AS136" s="23" t="n"/>
       <c r="AT136" s="67" t="inlineStr"/>
     </row>
@@ -17598,21 +16262,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP137" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AQ137" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR137" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP137" s="65" t="inlineStr"/>
+      <c r="AQ137" s="65" t="inlineStr"/>
+      <c r="AR137" s="23" t="inlineStr"/>
       <c r="AS137" s="23" t="n"/>
       <c r="AT137" s="67" t="inlineStr"/>
     </row>
@@ -17728,21 +16380,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP138" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ138" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR138" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP138" s="65" t="inlineStr"/>
+      <c r="AQ138" s="65" t="inlineStr"/>
+      <c r="AR138" s="23" t="inlineStr"/>
       <c r="AS138" s="23" t="n"/>
       <c r="AT138" s="67" t="inlineStr"/>
     </row>
@@ -17858,21 +16498,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP139" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ139" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR139" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP139" s="65" t="inlineStr"/>
+      <c r="AQ139" s="65" t="inlineStr"/>
+      <c r="AR139" s="23" t="inlineStr"/>
       <c r="AS139" s="23" t="n"/>
       <c r="AT139" s="67" t="inlineStr"/>
     </row>
@@ -17988,21 +16616,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP140" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AQ140" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR140" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP140" s="65" t="inlineStr"/>
+      <c r="AQ140" s="65" t="inlineStr"/>
+      <c r="AR140" s="23" t="inlineStr"/>
       <c r="AS140" s="23" t="n"/>
       <c r="AT140" s="67" t="inlineStr"/>
     </row>
@@ -18118,21 +16734,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP141" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ141" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR141" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP141" s="65" t="inlineStr"/>
+      <c r="AQ141" s="65" t="inlineStr"/>
+      <c r="AR141" s="23" t="inlineStr"/>
       <c r="AS141" s="23" t="n"/>
       <c r="AT141" s="67" t="inlineStr"/>
     </row>
@@ -18248,21 +16852,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP142" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ142" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR142" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP142" s="65" t="inlineStr"/>
+      <c r="AQ142" s="65" t="inlineStr"/>
+      <c r="AR142" s="23" t="inlineStr"/>
       <c r="AS142" s="23" t="n"/>
       <c r="AT142" s="67" t="inlineStr"/>
     </row>
@@ -18383,16 +16975,8 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AQ143" s="65" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AR143" s="23" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="AQ143" s="65" t="inlineStr"/>
+      <c r="AR143" s="23" t="inlineStr"/>
       <c r="AS143" s="23" t="n"/>
       <c r="AT143" s="67" t="inlineStr"/>
     </row>
@@ -18504,21 +17088,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP144" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ144" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR144" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP144" s="65" t="inlineStr"/>
+      <c r="AQ144" s="65" t="inlineStr"/>
+      <c r="AR144" s="23" t="inlineStr"/>
       <c r="AS144" s="23" t="n"/>
       <c r="AT144" s="67" t="inlineStr"/>
     </row>
@@ -18634,21 +17206,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP145" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AQ145" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR145" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP145" s="65" t="inlineStr"/>
+      <c r="AQ145" s="65" t="inlineStr"/>
+      <c r="AR145" s="23" t="inlineStr"/>
       <c r="AS145" s="23" t="n"/>
       <c r="AT145" s="67" t="inlineStr"/>
     </row>
@@ -18764,21 +17324,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP146" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AQ146" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR146" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP146" s="65" t="inlineStr"/>
+      <c r="AQ146" s="65" t="inlineStr"/>
+      <c r="AR146" s="23" t="inlineStr"/>
       <c r="AS146" s="23" t="n"/>
       <c r="AT146" s="67" t="inlineStr"/>
     </row>
@@ -18894,21 +17442,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP147" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ147" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR147" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP147" s="65" t="inlineStr"/>
+      <c r="AQ147" s="65" t="inlineStr"/>
+      <c r="AR147" s="23" t="inlineStr"/>
       <c r="AS147" s="23" t="n"/>
       <c r="AT147" s="67" t="inlineStr"/>
     </row>
@@ -19024,21 +17560,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP148" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ148" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR148" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP148" s="65" t="inlineStr"/>
+      <c r="AQ148" s="65" t="inlineStr"/>
+      <c r="AR148" s="23" t="inlineStr"/>
       <c r="AS148" s="23" t="n"/>
       <c r="AT148" s="67" t="inlineStr"/>
     </row>
@@ -19154,21 +17678,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP149" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ149" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR149" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP149" s="65" t="inlineStr"/>
+      <c r="AQ149" s="65" t="inlineStr"/>
+      <c r="AR149" s="23" t="inlineStr"/>
       <c r="AS149" s="23" t="n"/>
       <c r="AT149" s="67" t="inlineStr"/>
     </row>
@@ -19284,21 +17796,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP150" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ150" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR150" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP150" s="65" t="inlineStr"/>
+      <c r="AQ150" s="65" t="inlineStr"/>
+      <c r="AR150" s="23" t="inlineStr"/>
       <c r="AS150" s="23" t="n"/>
       <c r="AT150" s="67" t="inlineStr"/>
     </row>
@@ -19414,21 +17914,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP151" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ151" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR151" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP151" s="65" t="inlineStr"/>
+      <c r="AQ151" s="65" t="inlineStr"/>
+      <c r="AR151" s="23" t="inlineStr"/>
       <c r="AS151" s="23" t="n"/>
       <c r="AT151" s="67" t="inlineStr"/>
     </row>
@@ -19544,21 +18032,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP152" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ152" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR152" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP152" s="65" t="inlineStr"/>
+      <c r="AQ152" s="65" t="inlineStr"/>
+      <c r="AR152" s="23" t="inlineStr"/>
       <c r="AS152" s="23" t="n"/>
       <c r="AT152" s="67" t="inlineStr"/>
     </row>
@@ -19674,21 +18150,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP153" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ153" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR153" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP153" s="65" t="inlineStr"/>
+      <c r="AQ153" s="65" t="inlineStr"/>
+      <c r="AR153" s="23" t="inlineStr"/>
       <c r="AS153" s="23" t="n"/>
       <c r="AT153" s="67" t="inlineStr"/>
     </row>
@@ -19804,21 +18268,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP154" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ154" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR154" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP154" s="65" t="inlineStr"/>
+      <c r="AQ154" s="65" t="inlineStr"/>
+      <c r="AR154" s="23" t="inlineStr"/>
       <c r="AS154" s="23" t="n"/>
       <c r="AT154" s="67" t="inlineStr"/>
     </row>
@@ -19934,21 +18386,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP155" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ155" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR155" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP155" s="65" t="inlineStr"/>
+      <c r="AQ155" s="65" t="inlineStr"/>
+      <c r="AR155" s="23" t="inlineStr"/>
       <c r="AS155" s="23" t="n"/>
       <c r="AT155" s="67" t="inlineStr"/>
     </row>
@@ -20060,21 +18500,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP156" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ156" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR156" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP156" s="65" t="inlineStr"/>
+      <c r="AQ156" s="65" t="inlineStr"/>
+      <c r="AR156" s="23" t="inlineStr"/>
       <c r="AS156" s="23" t="n"/>
       <c r="AT156" s="67" t="inlineStr"/>
     </row>
@@ -20186,21 +18614,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP157" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ157" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR157" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP157" s="65" t="inlineStr"/>
+      <c r="AQ157" s="65" t="inlineStr"/>
+      <c r="AR157" s="23" t="inlineStr"/>
       <c r="AS157" s="23" t="n"/>
       <c r="AT157" s="67" t="inlineStr"/>
     </row>
@@ -20316,21 +18732,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP158" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ158" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR158" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP158" s="65" t="inlineStr"/>
+      <c r="AQ158" s="65" t="inlineStr"/>
+      <c r="AR158" s="23" t="inlineStr"/>
       <c r="AS158" s="23" t="n"/>
       <c r="AT158" s="67" t="inlineStr"/>
     </row>
@@ -20446,21 +18850,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP159" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ159" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR159" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP159" s="65" t="inlineStr"/>
+      <c r="AQ159" s="65" t="inlineStr"/>
+      <c r="AR159" s="23" t="inlineStr"/>
       <c r="AS159" s="23" t="n"/>
       <c r="AT159" s="67" t="inlineStr"/>
     </row>
@@ -20576,21 +18968,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP160" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ160" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR160" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP160" s="65" t="inlineStr"/>
+      <c r="AQ160" s="65" t="inlineStr"/>
+      <c r="AR160" s="23" t="inlineStr"/>
       <c r="AS160" s="23" t="n"/>
       <c r="AT160" s="67" t="inlineStr"/>
     </row>
@@ -20706,21 +19086,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP161" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ161" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR161" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP161" s="65" t="inlineStr"/>
+      <c r="AQ161" s="65" t="inlineStr"/>
+      <c r="AR161" s="23" t="inlineStr"/>
       <c r="AS161" s="23" t="n"/>
       <c r="AT161" s="67" t="inlineStr"/>
     </row>
@@ -20836,21 +19204,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP162" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ162" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR162" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP162" s="65" t="inlineStr"/>
+      <c r="AQ162" s="65" t="inlineStr"/>
+      <c r="AR162" s="23" t="inlineStr"/>
       <c r="AS162" s="23" t="n"/>
       <c r="AT162" s="67" t="inlineStr"/>
     </row>
@@ -20962,21 +19318,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP163" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ163" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR163" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP163" s="65" t="inlineStr"/>
+      <c r="AQ163" s="65" t="inlineStr"/>
+      <c r="AR163" s="23" t="inlineStr"/>
       <c r="AS163" s="23" t="n"/>
       <c r="AT163" s="67" t="inlineStr"/>
     </row>
@@ -21088,21 +19432,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP164" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ164" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR164" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP164" s="65" t="inlineStr"/>
+      <c r="AQ164" s="65" t="inlineStr"/>
+      <c r="AR164" s="23" t="inlineStr"/>
       <c r="AS164" s="23" t="n"/>
       <c r="AT164" s="67" t="inlineStr"/>
     </row>
@@ -21218,21 +19550,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP165" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ165" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR165" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP165" s="65" t="inlineStr"/>
+      <c r="AQ165" s="65" t="inlineStr"/>
+      <c r="AR165" s="23" t="inlineStr"/>
       <c r="AS165" s="23" t="n"/>
       <c r="AT165" s="67" t="inlineStr"/>
     </row>
@@ -21348,21 +19668,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP166" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ166" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR166" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP166" s="65" t="inlineStr"/>
+      <c r="AQ166" s="65" t="inlineStr"/>
+      <c r="AR166" s="23" t="inlineStr"/>
       <c r="AS166" s="23" t="n"/>
       <c r="AT166" s="67" t="inlineStr"/>
     </row>
@@ -21478,21 +19786,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP167" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ167" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR167" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP167" s="65" t="inlineStr"/>
+      <c r="AQ167" s="65" t="inlineStr"/>
+      <c r="AR167" s="23" t="inlineStr"/>
       <c r="AS167" s="23" t="n"/>
       <c r="AT167" s="67" t="inlineStr"/>
     </row>
@@ -21608,21 +19904,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP168" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ168" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR168" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP168" s="65" t="inlineStr"/>
+      <c r="AQ168" s="65" t="inlineStr"/>
+      <c r="AR168" s="23" t="inlineStr"/>
       <c r="AS168" s="23" t="n"/>
       <c r="AT168" s="67" t="inlineStr"/>
     </row>
@@ -21738,21 +20022,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP169" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ169" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR169" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP169" s="65" t="inlineStr"/>
+      <c r="AQ169" s="65" t="inlineStr"/>
+      <c r="AR169" s="23" t="inlineStr"/>
       <c r="AS169" s="23" t="n"/>
       <c r="AT169" s="67" t="inlineStr"/>
     </row>
@@ -21868,16 +20140,8 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP170" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ170" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP170" s="65" t="inlineStr"/>
+      <c r="AQ170" s="65" t="inlineStr"/>
       <c r="AR170" s="23" t="inlineStr">
         <is>
           <t>OBSERVATION -CLEANING ON PROGRESS</t>
@@ -21998,21 +20262,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP171" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ171" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR171" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP171" s="65" t="inlineStr"/>
+      <c r="AQ171" s="65" t="inlineStr"/>
+      <c r="AR171" s="23" t="inlineStr"/>
       <c r="AS171" s="23" t="n"/>
       <c r="AT171" s="67" t="inlineStr"/>
     </row>
@@ -22128,21 +20380,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP172" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ172" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR172" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP172" s="65" t="inlineStr"/>
+      <c r="AQ172" s="65" t="inlineStr"/>
+      <c r="AR172" s="23" t="inlineStr"/>
       <c r="AS172" s="23" t="n"/>
       <c r="AT172" s="67" t="inlineStr"/>
     </row>
@@ -22258,21 +20498,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP173" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ173" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR173" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP173" s="65" t="inlineStr"/>
+      <c r="AQ173" s="65" t="inlineStr"/>
+      <c r="AR173" s="23" t="inlineStr"/>
       <c r="AS173" s="23" t="n"/>
       <c r="AT173" s="67" t="inlineStr"/>
     </row>
@@ -22388,21 +20616,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP174" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ174" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR174" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP174" s="65" t="inlineStr"/>
+      <c r="AQ174" s="65" t="inlineStr"/>
+      <c r="AR174" s="23" t="inlineStr"/>
       <c r="AS174" s="23" t="n"/>
       <c r="AT174" s="67" t="inlineStr"/>
     </row>
@@ -22518,21 +20734,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP175" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ175" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR175" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP175" s="65" t="inlineStr"/>
+      <c r="AQ175" s="65" t="inlineStr"/>
+      <c r="AR175" s="23" t="inlineStr"/>
       <c r="AS175" s="23" t="n"/>
       <c r="AT175" s="67" t="inlineStr"/>
     </row>
@@ -22648,21 +20852,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP176" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ176" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR176" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP176" s="65" t="inlineStr"/>
+      <c r="AQ176" s="65" t="inlineStr"/>
+      <c r="AR176" s="23" t="inlineStr"/>
       <c r="AS176" s="23" t="n"/>
       <c r="AT176" s="67" t="inlineStr"/>
     </row>
@@ -22778,21 +20970,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP177" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ177" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR177" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP177" s="65" t="inlineStr"/>
+      <c r="AQ177" s="65" t="inlineStr"/>
+      <c r="AR177" s="23" t="inlineStr"/>
       <c r="AS177" s="23" t="n"/>
       <c r="AT177" s="67" t="inlineStr"/>
     </row>
@@ -22908,21 +21088,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP178" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ178" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR178" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP178" s="65" t="inlineStr"/>
+      <c r="AQ178" s="65" t="inlineStr"/>
+      <c r="AR178" s="23" t="inlineStr"/>
       <c r="AS178" s="23" t="n"/>
       <c r="AT178" s="67" t="inlineStr"/>
     </row>
@@ -23038,21 +21206,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP179" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ179" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR179" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP179" s="65" t="inlineStr"/>
+      <c r="AQ179" s="65" t="inlineStr"/>
+      <c r="AR179" s="23" t="inlineStr"/>
       <c r="AS179" s="23" t="n"/>
       <c r="AT179" s="67" t="inlineStr"/>
     </row>
@@ -23168,21 +21324,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP180" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ180" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR180" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP180" s="65" t="inlineStr"/>
+      <c r="AQ180" s="65" t="inlineStr"/>
+      <c r="AR180" s="23" t="inlineStr"/>
       <c r="AS180" s="23" t="n"/>
       <c r="AT180" s="67" t="inlineStr"/>
     </row>
@@ -23298,21 +21442,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP181" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ181" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR181" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP181" s="65" t="inlineStr"/>
+      <c r="AQ181" s="65" t="inlineStr"/>
+      <c r="AR181" s="23" t="inlineStr"/>
       <c r="AS181" s="23" t="n"/>
       <c r="AT181" s="67" t="inlineStr"/>
     </row>
@@ -23428,21 +21560,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP182" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ182" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR182" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP182" s="65" t="inlineStr"/>
+      <c r="AQ182" s="65" t="inlineStr"/>
+      <c r="AR182" s="23" t="inlineStr"/>
       <c r="AS182" s="23" t="n"/>
       <c r="AT182" s="67" t="inlineStr"/>
     </row>
@@ -23558,21 +21678,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP183" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ183" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR183" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP183" s="65" t="inlineStr"/>
+      <c r="AQ183" s="65" t="inlineStr"/>
+      <c r="AR183" s="23" t="inlineStr"/>
       <c r="AS183" s="23" t="n"/>
       <c r="AT183" s="67" t="inlineStr"/>
     </row>
@@ -23688,21 +21796,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP184" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ184" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR184" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP184" s="65" t="inlineStr"/>
+      <c r="AQ184" s="65" t="inlineStr"/>
+      <c r="AR184" s="23" t="inlineStr"/>
       <c r="AS184" s="23" t="n"/>
       <c r="AT184" s="67" t="inlineStr"/>
     </row>
@@ -23818,21 +21914,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AP185" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AQ185" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR185" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP185" s="65" t="inlineStr"/>
+      <c r="AQ185" s="65" t="inlineStr"/>
+      <c r="AR185" s="23" t="inlineStr"/>
       <c r="AS185" s="23" t="n"/>
       <c r="AT185" s="67" t="inlineStr"/>
     </row>
@@ -23948,21 +22032,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP186" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ186" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR186" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP186" s="65" t="inlineStr"/>
+      <c r="AQ186" s="65" t="inlineStr"/>
+      <c r="AR186" s="23" t="inlineStr"/>
       <c r="AS186" s="23" t="n"/>
       <c r="AT186" s="67" t="inlineStr"/>
     </row>
@@ -24078,21 +22150,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AP187" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AQ187" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR187" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP187" s="65" t="inlineStr"/>
+      <c r="AQ187" s="65" t="inlineStr"/>
+      <c r="AR187" s="23" t="inlineStr"/>
       <c r="AS187" s="23" t="n"/>
       <c r="AT187" s="67" t="inlineStr"/>
     </row>
@@ -24208,21 +22268,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP188" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ188" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR188" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP188" s="65" t="inlineStr"/>
+      <c r="AQ188" s="65" t="inlineStr"/>
+      <c r="AR188" s="23" t="inlineStr"/>
       <c r="AS188" s="23" t="n"/>
       <c r="AT188" s="67" t="inlineStr"/>
     </row>
@@ -24338,21 +22386,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AP189" s="65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ189" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR189" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP189" s="65" t="inlineStr"/>
+      <c r="AQ189" s="65" t="inlineStr"/>
+      <c r="AR189" s="23" t="inlineStr"/>
       <c r="AS189" s="23" t="n"/>
       <c r="AT189" s="67" t="inlineStr"/>
     </row>
@@ -24468,21 +22504,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP190" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ190" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR190" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP190" s="65" t="inlineStr"/>
+      <c r="AQ190" s="65" t="inlineStr"/>
+      <c r="AR190" s="23" t="inlineStr"/>
       <c r="AS190" s="23" t="n"/>
       <c r="AT190" s="67" t="inlineStr"/>
     </row>
@@ -24598,21 +22622,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP191" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ191" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR191" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP191" s="65" t="inlineStr"/>
+      <c r="AQ191" s="65" t="inlineStr"/>
+      <c r="AR191" s="23" t="inlineStr"/>
       <c r="AS191" s="23" t="n"/>
       <c r="AT191" s="67" t="inlineStr"/>
     </row>
@@ -24728,21 +22740,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP192" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ192" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR192" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP192" s="65" t="inlineStr"/>
+      <c r="AQ192" s="65" t="inlineStr"/>
+      <c r="AR192" s="23" t="inlineStr"/>
       <c r="AS192" s="23" t="n"/>
       <c r="AT192" s="67" t="inlineStr"/>
     </row>
@@ -24858,21 +22858,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP193" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ193" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR193" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP193" s="65" t="inlineStr"/>
+      <c r="AQ193" s="65" t="inlineStr"/>
+      <c r="AR193" s="23" t="inlineStr"/>
       <c r="AS193" s="23" t="n"/>
       <c r="AT193" s="67" t="inlineStr"/>
     </row>
@@ -24988,21 +22976,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP194" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ194" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR194" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP194" s="65" t="inlineStr"/>
+      <c r="AQ194" s="65" t="inlineStr"/>
+      <c r="AR194" s="23" t="inlineStr"/>
       <c r="AS194" s="23" t="n"/>
       <c r="AT194" s="67" t="inlineStr"/>
     </row>
@@ -25118,21 +23094,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP195" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ195" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR195" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP195" s="65" t="inlineStr"/>
+      <c r="AQ195" s="65" t="inlineStr"/>
+      <c r="AR195" s="23" t="inlineStr"/>
       <c r="AS195" s="23" t="n"/>
       <c r="AT195" s="67" t="inlineStr"/>
     </row>
@@ -25248,21 +23212,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP196" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ196" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR196" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP196" s="65" t="inlineStr"/>
+      <c r="AQ196" s="65" t="inlineStr"/>
+      <c r="AR196" s="23" t="inlineStr"/>
       <c r="AS196" s="23" t="n"/>
       <c r="AT196" s="67" t="inlineStr"/>
     </row>
@@ -25374,21 +23326,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP197" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ197" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR197" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP197" s="65" t="inlineStr"/>
+      <c r="AQ197" s="65" t="inlineStr"/>
+      <c r="AR197" s="23" t="inlineStr"/>
       <c r="AS197" s="23" t="n"/>
       <c r="AT197" s="67" t="inlineStr"/>
     </row>
@@ -25504,21 +23444,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP198" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AQ198" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR198" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP198" s="65" t="inlineStr"/>
+      <c r="AQ198" s="65" t="inlineStr"/>
+      <c r="AR198" s="23" t="inlineStr"/>
       <c r="AS198" s="23" t="n"/>
       <c r="AT198" s="67" t="inlineStr"/>
     </row>
@@ -25634,21 +23562,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP199" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ199" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR199" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP199" s="65" t="inlineStr"/>
+      <c r="AQ199" s="65" t="inlineStr"/>
+      <c r="AR199" s="23" t="inlineStr"/>
       <c r="AS199" s="23" t="n"/>
       <c r="AT199" s="67" t="inlineStr"/>
     </row>
@@ -25764,21 +23680,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP200" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ200" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR200" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP200" s="65" t="inlineStr"/>
+      <c r="AQ200" s="65" t="inlineStr"/>
+      <c r="AR200" s="23" t="inlineStr"/>
       <c r="AS200" s="23" t="n"/>
       <c r="AT200" s="67" t="inlineStr"/>
     </row>
@@ -25890,21 +23794,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP201" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ201" s="65" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AR201" s="23" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+      <c r="AP201" s="65" t="inlineStr"/>
+      <c r="AQ201" s="65" t="inlineStr"/>
+      <c r="AR201" s="23" t="inlineStr"/>
       <c r="AS201" s="23" t="n"/>
       <c r="AT201" s="67" t="inlineStr"/>
     </row>
@@ -26020,21 +23912,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP202" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ202" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR202" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP202" s="65" t="inlineStr"/>
+      <c r="AQ202" s="65" t="inlineStr"/>
+      <c r="AR202" s="23" t="inlineStr"/>
       <c r="AS202" s="23" t="n"/>
       <c r="AT202" s="67" t="inlineStr"/>
     </row>
@@ -26150,21 +24030,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP203" s="65" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AQ203" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR203" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP203" s="65" t="inlineStr"/>
+      <c r="AQ203" s="65" t="inlineStr"/>
+      <c r="AR203" s="23" t="inlineStr"/>
       <c r="AS203" s="23" t="n"/>
       <c r="AT203" s="67" t="inlineStr"/>
     </row>
@@ -26280,21 +24148,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP204" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ204" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR204" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP204" s="65" t="inlineStr"/>
+      <c r="AQ204" s="65" t="inlineStr"/>
+      <c r="AR204" s="23" t="inlineStr"/>
       <c r="AS204" s="23" t="n"/>
       <c r="AT204" s="67" t="inlineStr"/>
     </row>
@@ -26406,21 +24262,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP205" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ205" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AR205" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP205" s="65" t="inlineStr"/>
+      <c r="AQ205" s="65" t="inlineStr"/>
+      <c r="AR205" s="23" t="inlineStr"/>
       <c r="AS205" s="23" t="n"/>
       <c r="AT205" s="67" t="inlineStr"/>
     </row>
@@ -26532,21 +24376,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP206" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ206" s="65" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AR206" s="23" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+      <c r="AP206" s="65" t="inlineStr"/>
+      <c r="AQ206" s="65" t="inlineStr"/>
+      <c r="AR206" s="23" t="inlineStr"/>
       <c r="AS206" s="23" t="n"/>
       <c r="AT206" s="67" t="inlineStr"/>
     </row>
@@ -26662,21 +24494,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP207" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ207" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR207" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP207" s="65" t="inlineStr"/>
+      <c r="AQ207" s="65" t="inlineStr"/>
+      <c r="AR207" s="23" t="inlineStr"/>
       <c r="AS207" s="23" t="n"/>
       <c r="AT207" s="67" t="inlineStr"/>
     </row>
@@ -26792,21 +24612,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP208" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ208" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR208" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP208" s="65" t="inlineStr"/>
+      <c r="AQ208" s="65" t="inlineStr"/>
+      <c r="AR208" s="23" t="inlineStr"/>
       <c r="AS208" s="23" t="n"/>
       <c r="AT208" s="67" t="inlineStr"/>
     </row>
@@ -26998,21 +24806,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP210" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ210" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR210" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP210" s="65" t="inlineStr"/>
+      <c r="AQ210" s="65" t="inlineStr"/>
+      <c r="AR210" s="23" t="inlineStr"/>
       <c r="AS210" s="23" t="n"/>
       <c r="AT210" s="67" t="inlineStr"/>
     </row>
@@ -27120,21 +24916,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP211" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ211" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR211" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP211" s="65" t="inlineStr"/>
+      <c r="AQ211" s="65" t="inlineStr"/>
+      <c r="AR211" s="23" t="inlineStr"/>
       <c r="AS211" s="23" t="n"/>
       <c r="AT211" s="67" t="inlineStr"/>
     </row>
@@ -27246,21 +25030,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP212" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ212" s="65" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AR212" s="23" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+      <c r="AP212" s="65" t="inlineStr"/>
+      <c r="AQ212" s="65" t="inlineStr"/>
+      <c r="AR212" s="23" t="inlineStr"/>
       <c r="AS212" s="23" t="n"/>
       <c r="AT212" s="67" t="inlineStr"/>
     </row>
@@ -27372,21 +25144,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP213" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ213" s="65" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AR213" s="23" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="AP213" s="65" t="inlineStr"/>
+      <c r="AQ213" s="65" t="inlineStr"/>
+      <c r="AR213" s="23" t="inlineStr"/>
       <c r="AS213" s="23" t="n"/>
       <c r="AT213" s="67" t="inlineStr"/>
     </row>
@@ -27502,21 +25262,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP214" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ214" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR214" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP214" s="65" t="inlineStr"/>
+      <c r="AQ214" s="65" t="inlineStr"/>
+      <c r="AR214" s="23" t="inlineStr"/>
       <c r="AS214" s="23" t="n"/>
       <c r="AT214" s="67" t="inlineStr"/>
     </row>
@@ -27632,21 +25380,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP215" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ215" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR215" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP215" s="65" t="inlineStr"/>
+      <c r="AQ215" s="65" t="inlineStr"/>
+      <c r="AR215" s="23" t="inlineStr"/>
       <c r="AS215" s="23" t="n"/>
       <c r="AT215" s="67" t="inlineStr"/>
     </row>
@@ -27754,21 +25490,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP216" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ216" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR216" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP216" s="65" t="inlineStr"/>
+      <c r="AQ216" s="65" t="inlineStr"/>
+      <c r="AR216" s="23" t="inlineStr"/>
       <c r="AS216" s="23" t="n"/>
       <c r="AT216" s="67" t="inlineStr"/>
     </row>
@@ -27884,21 +25608,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP217" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ217" s="65" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AR217" s="23" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="AP217" s="65" t="inlineStr"/>
+      <c r="AQ217" s="65" t="inlineStr"/>
+      <c r="AR217" s="23" t="inlineStr"/>
       <c r="AS217" s="23" t="n"/>
       <c r="AT217" s="67" t="inlineStr"/>
     </row>
@@ -28010,21 +25722,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP218" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ218" s="65" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AR218" s="23" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="AP218" s="65" t="inlineStr"/>
+      <c r="AQ218" s="65" t="inlineStr"/>
+      <c r="AR218" s="23" t="inlineStr"/>
       <c r="AS218" s="23" t="n"/>
       <c r="AT218" s="67" t="inlineStr"/>
     </row>
@@ -28136,21 +25836,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP219" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ219" s="65" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AR219" s="23" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="AP219" s="65" t="inlineStr"/>
+      <c r="AQ219" s="65" t="inlineStr"/>
+      <c r="AR219" s="23" t="inlineStr"/>
       <c r="AS219" s="23" t="n"/>
       <c r="AT219" s="67" t="inlineStr"/>
     </row>
@@ -28262,21 +25950,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP220" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ220" s="65" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AR220" s="23" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="AP220" s="65" t="inlineStr"/>
+      <c r="AQ220" s="65" t="inlineStr"/>
+      <c r="AR220" s="23" t="inlineStr"/>
       <c r="AS220" s="23" t="n"/>
       <c r="AT220" s="67" t="inlineStr"/>
     </row>
@@ -28392,21 +26068,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP221" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ221" s="65" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AR221" s="23" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+      <c r="AP221" s="65" t="inlineStr"/>
+      <c r="AQ221" s="65" t="inlineStr"/>
+      <c r="AR221" s="23" t="inlineStr"/>
       <c r="AS221" s="23" t="n"/>
       <c r="AT221" s="67" t="inlineStr"/>
     </row>
@@ -28518,21 +26182,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP222" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ222" s="65" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AR222" s="23" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="AP222" s="65" t="inlineStr"/>
+      <c r="AQ222" s="65" t="inlineStr"/>
+      <c r="AR222" s="23" t="inlineStr"/>
       <c r="AS222" s="23" t="n"/>
       <c r="AT222" s="67" t="inlineStr"/>
     </row>
@@ -28808,21 +26460,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP225" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ225" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR225" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP225" s="65" t="inlineStr"/>
+      <c r="AQ225" s="65" t="inlineStr"/>
+      <c r="AR225" s="23" t="inlineStr"/>
       <c r="AS225" s="23" t="n"/>
       <c r="AT225" s="67" t="inlineStr"/>
     </row>
@@ -28930,21 +26570,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP226" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ226" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR226" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP226" s="65" t="inlineStr"/>
+      <c r="AQ226" s="65" t="inlineStr"/>
+      <c r="AR226" s="23" t="inlineStr"/>
       <c r="AS226" s="23" t="n"/>
       <c r="AT226" s="67" t="inlineStr"/>
     </row>
@@ -29052,21 +26680,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP227" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ227" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR227" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP227" s="65" t="inlineStr"/>
+      <c r="AQ227" s="65" t="inlineStr"/>
+      <c r="AR227" s="23" t="inlineStr"/>
       <c r="AS227" s="23" t="n"/>
       <c r="AT227" s="67" t="inlineStr"/>
     </row>
@@ -29174,21 +26790,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP228" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ228" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR228" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP228" s="65" t="inlineStr"/>
+      <c r="AQ228" s="65" t="inlineStr"/>
+      <c r="AR228" s="23" t="inlineStr"/>
       <c r="AS228" s="23" t="n"/>
       <c r="AT228" s="67" t="inlineStr"/>
     </row>
@@ -29296,21 +26900,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP229" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ229" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR229" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP229" s="65" t="inlineStr"/>
+      <c r="AQ229" s="65" t="inlineStr"/>
+      <c r="AR229" s="23" t="inlineStr"/>
       <c r="AS229" s="23" t="n"/>
       <c r="AT229" s="67" t="inlineStr"/>
     </row>
@@ -29418,21 +27010,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP230" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ230" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR230" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP230" s="65" t="inlineStr"/>
+      <c r="AQ230" s="65" t="inlineStr"/>
+      <c r="AR230" s="23" t="inlineStr"/>
       <c r="AS230" s="23" t="n"/>
       <c r="AT230" s="67" t="inlineStr"/>
     </row>
@@ -29540,21 +27120,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP231" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ231" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR231" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP231" s="65" t="inlineStr"/>
+      <c r="AQ231" s="65" t="inlineStr"/>
+      <c r="AR231" s="23" t="inlineStr"/>
       <c r="AS231" s="23" t="n"/>
       <c r="AT231" s="67" t="inlineStr"/>
     </row>
@@ -29670,21 +27238,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP232" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP232" s="65" t="inlineStr"/>
       <c r="AQ232" s="65" t="inlineStr">
         <is>
           <t>18 ITRs for lightning, 22 ITRs for grounding cannot be closed due to material issues.</t>
         </is>
       </c>
-      <c r="AR232" s="23" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
+      <c r="AR232" s="23" t="inlineStr"/>
       <c r="AS232" s="23" t="n"/>
       <c r="AT232" s="67" t="inlineStr"/>
     </row>
@@ -29792,21 +27352,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP233" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ233" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AR233" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="AP233" s="65" t="inlineStr"/>
+      <c r="AQ233" s="65" t="inlineStr"/>
+      <c r="AR233" s="23" t="inlineStr"/>
       <c r="AS233" s="23" t="n"/>
       <c r="AT233" s="67" t="inlineStr"/>
     </row>
@@ -29922,21 +27470,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP234" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ234" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AR234" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP234" s="65" t="inlineStr"/>
+      <c r="AQ234" s="65" t="inlineStr"/>
+      <c r="AR234" s="23" t="inlineStr"/>
       <c r="AS234" s="23" t="n"/>
       <c r="AT234" s="67" t="inlineStr"/>
     </row>
@@ -30128,21 +27664,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP236" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ236" s="65" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AR236" s="23" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="AP236" s="65" t="inlineStr"/>
+      <c r="AQ236" s="65" t="inlineStr"/>
+      <c r="AR236" s="23" t="inlineStr"/>
       <c r="AS236" s="23" t="n"/>
       <c r="AT236" s="67" t="inlineStr"/>
     </row>
@@ -30250,21 +27774,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP237" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ237" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AR237" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="AP237" s="65" t="inlineStr"/>
+      <c r="AQ237" s="65" t="inlineStr"/>
+      <c r="AR237" s="23" t="inlineStr"/>
       <c r="AS237" s="23" t="n"/>
       <c r="AT237" s="67" t="inlineStr"/>
     </row>
@@ -30372,21 +27884,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP238" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ238" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AR238" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="AP238" s="65" t="inlineStr"/>
+      <c r="AQ238" s="65" t="inlineStr"/>
+      <c r="AR238" s="23" t="inlineStr"/>
       <c r="AS238" s="23" t="n"/>
       <c r="AT238" s="67" t="inlineStr"/>
     </row>
@@ -30503,16 +28003,8 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AQ239" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AR239" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AQ239" s="65" t="inlineStr"/>
+      <c r="AR239" s="23" t="inlineStr"/>
       <c r="AS239" s="23" t="n"/>
       <c r="AT239" s="67" t="inlineStr"/>
     </row>
@@ -30628,21 +28120,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP240" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ240" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR240" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP240" s="65" t="inlineStr"/>
+      <c r="AQ240" s="65" t="inlineStr"/>
+      <c r="AR240" s="23" t="inlineStr"/>
       <c r="AS240" s="23" t="n"/>
       <c r="AT240" s="67" t="inlineStr"/>
     </row>
@@ -30838,21 +28318,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP242" s="65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ242" s="65" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AR242" s="23" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="AP242" s="65" t="inlineStr"/>
+      <c r="AQ242" s="65" t="inlineStr"/>
+      <c r="AR242" s="23" t="inlineStr"/>
       <c r="AS242" s="23" t="n"/>
       <c r="AT242" s="67" t="inlineStr"/>
     </row>
@@ -30964,21 +28432,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP243" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ243" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AR243" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP243" s="65" t="inlineStr"/>
+      <c r="AQ243" s="65" t="inlineStr"/>
+      <c r="AR243" s="23" t="inlineStr"/>
       <c r="AS243" s="23" t="n"/>
       <c r="AT243" s="67" t="inlineStr"/>
     </row>
@@ -31090,21 +28546,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP244" s="65" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AQ244" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR244" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP244" s="65" t="inlineStr"/>
+      <c r="AQ244" s="65" t="inlineStr"/>
+      <c r="AR244" s="23" t="inlineStr"/>
       <c r="AS244" s="23" t="n"/>
       <c r="AT244" s="67" t="inlineStr"/>
     </row>
@@ -31216,21 +28660,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP245" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ245" s="65" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="AR245" s="23" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+      <c r="AP245" s="65" t="inlineStr"/>
+      <c r="AQ245" s="65" t="inlineStr"/>
+      <c r="AR245" s="23" t="inlineStr"/>
       <c r="AS245" s="23" t="n"/>
       <c r="AT245" s="67" t="inlineStr"/>
     </row>
@@ -31346,21 +28778,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP246" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AQ246" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR246" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP246" s="65" t="inlineStr"/>
+      <c r="AQ246" s="65" t="inlineStr"/>
+      <c r="AR246" s="23" t="inlineStr"/>
       <c r="AS246" s="23" t="n"/>
       <c r="AT246" s="67" t="inlineStr"/>
     </row>
@@ -31476,21 +28896,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP247" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ247" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR247" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP247" s="65" t="inlineStr"/>
+      <c r="AQ247" s="65" t="inlineStr"/>
+      <c r="AR247" s="23" t="inlineStr"/>
       <c r="AS247" s="23" t="n"/>
       <c r="AT247" s="67" t="inlineStr"/>
     </row>
@@ -31602,21 +29010,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP248" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ248" s="65" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AR248" s="23" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="AP248" s="65" t="inlineStr"/>
+      <c r="AQ248" s="65" t="inlineStr"/>
+      <c r="AR248" s="23" t="inlineStr"/>
       <c r="AS248" s="23" t="n"/>
       <c r="AT248" s="67" t="inlineStr"/>
     </row>
@@ -31728,21 +29124,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP249" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AQ249" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AR249" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP249" s="65" t="inlineStr"/>
+      <c r="AQ249" s="65" t="inlineStr"/>
+      <c r="AR249" s="23" t="inlineStr"/>
       <c r="AS249" s="23" t="n"/>
       <c r="AT249" s="67" t="inlineStr"/>
     </row>
@@ -31858,21 +29242,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP250" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ250" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR250" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP250" s="65" t="inlineStr"/>
+      <c r="AQ250" s="65" t="inlineStr"/>
+      <c r="AR250" s="23" t="inlineStr"/>
       <c r="AS250" s="23" t="n"/>
       <c r="AT250" s="67" t="inlineStr"/>
     </row>
@@ -31989,16 +29361,8 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AQ251" s="65" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AR251" s="23" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="AQ251" s="65" t="inlineStr"/>
+      <c r="AR251" s="23" t="inlineStr"/>
       <c r="AS251" s="23" t="n"/>
       <c r="AT251" s="67" t="inlineStr"/>
     </row>
@@ -32114,21 +29478,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP252" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ252" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR252" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP252" s="65" t="inlineStr"/>
+      <c r="AQ252" s="65" t="inlineStr"/>
+      <c r="AR252" s="23" t="inlineStr"/>
       <c r="AS252" s="23" t="n"/>
       <c r="AT252" s="67" t="inlineStr"/>
     </row>
@@ -32244,21 +29596,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP253" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ253" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR253" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP253" s="65" t="inlineStr"/>
+      <c r="AQ253" s="65" t="inlineStr"/>
+      <c r="AR253" s="23" t="inlineStr"/>
       <c r="AS253" s="23" t="n"/>
       <c r="AT253" s="67" t="inlineStr"/>
     </row>
@@ -32374,21 +29714,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP254" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AQ254" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR254" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP254" s="65" t="inlineStr"/>
+      <c r="AQ254" s="65" t="inlineStr"/>
+      <c r="AR254" s="23" t="inlineStr"/>
       <c r="AS254" s="23" t="n"/>
       <c r="AT254" s="67" t="inlineStr"/>
     </row>
@@ -32500,21 +29828,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP255" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ255" s="65" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AR255" s="23" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="AP255" s="65" t="inlineStr"/>
+      <c r="AQ255" s="65" t="inlineStr"/>
+      <c r="AR255" s="23" t="inlineStr"/>
       <c r="AS255" s="23" t="n"/>
       <c r="AT255" s="67" t="inlineStr"/>
     </row>
@@ -32630,21 +29946,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP256" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ256" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR256" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP256" s="65" t="inlineStr"/>
+      <c r="AQ256" s="65" t="inlineStr"/>
+      <c r="AR256" s="23" t="inlineStr"/>
       <c r="AS256" s="23" t="n"/>
       <c r="AT256" s="67" t="inlineStr"/>
     </row>
@@ -32760,21 +30064,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP257" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ257" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AR257" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="AP257" s="65" t="inlineStr"/>
+      <c r="AQ257" s="65" t="inlineStr"/>
+      <c r="AR257" s="23" t="inlineStr"/>
       <c r="AS257" s="23" t="n"/>
       <c r="AT257" s="67" t="inlineStr"/>
     </row>
@@ -32890,21 +30182,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP258" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ258" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR258" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP258" s="65" t="inlineStr"/>
+      <c r="AQ258" s="65" t="inlineStr"/>
+      <c r="AR258" s="23" t="inlineStr"/>
       <c r="AS258" s="23" t="n"/>
       <c r="AT258" s="67" t="inlineStr"/>
     </row>
@@ -33020,21 +30300,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP259" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AQ259" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR259" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP259" s="65" t="inlineStr"/>
+      <c r="AQ259" s="65" t="inlineStr"/>
+      <c r="AR259" s="23" t="inlineStr"/>
       <c r="AS259" s="23" t="n"/>
       <c r="AT259" s="67" t="inlineStr"/>
     </row>
@@ -33155,16 +30423,8 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AQ260" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR260" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AQ260" s="65" t="inlineStr"/>
+      <c r="AR260" s="23" t="inlineStr"/>
       <c r="AS260" s="23" t="n"/>
       <c r="AT260" s="67" t="inlineStr"/>
     </row>
@@ -33280,21 +30540,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP261" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ261" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AR261" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP261" s="65" t="inlineStr"/>
+      <c r="AQ261" s="65" t="inlineStr"/>
+      <c r="AR261" s="23" t="inlineStr"/>
       <c r="AS261" s="23" t="n"/>
       <c r="AT261" s="67" t="inlineStr"/>
     </row>
@@ -33410,21 +30658,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP262" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ262" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR262" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP262" s="65" t="inlineStr"/>
+      <c r="AQ262" s="65" t="inlineStr"/>
+      <c r="AR262" s="23" t="inlineStr"/>
       <c r="AS262" s="23" t="n"/>
       <c r="AT262" s="67" t="inlineStr"/>
     </row>
@@ -33540,21 +30776,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP263" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ263" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR263" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP263" s="65" t="inlineStr"/>
+      <c r="AQ263" s="65" t="inlineStr"/>
+      <c r="AR263" s="23" t="inlineStr"/>
       <c r="AS263" s="23" t="n"/>
       <c r="AT263" s="67" t="inlineStr"/>
     </row>
@@ -33662,21 +30886,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP264" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ264" s="65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AR264" s="23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="AP264" s="65" t="inlineStr"/>
+      <c r="AQ264" s="65" t="inlineStr"/>
+      <c r="AR264" s="23" t="inlineStr"/>
       <c r="AS264" s="23" t="n"/>
       <c r="AT264" s="67" t="inlineStr"/>
     </row>
@@ -33792,21 +31004,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP265" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ265" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR265" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP265" s="65" t="inlineStr"/>
+      <c r="AQ265" s="65" t="inlineStr"/>
+      <c r="AR265" s="23" t="inlineStr"/>
       <c r="AS265" s="23" t="n"/>
       <c r="AT265" s="67" t="inlineStr"/>
     </row>
@@ -33922,21 +31122,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP266" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ266" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR266" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP266" s="65" t="inlineStr"/>
+      <c r="AQ266" s="65" t="inlineStr"/>
+      <c r="AR266" s="23" t="inlineStr"/>
       <c r="AS266" s="23" t="n"/>
       <c r="AT266" s="67" t="inlineStr"/>
     </row>
@@ -34048,21 +31236,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP267" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ267" s="65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AR267" s="23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="AP267" s="65" t="inlineStr"/>
+      <c r="AQ267" s="65" t="inlineStr"/>
+      <c r="AR267" s="23" t="inlineStr"/>
       <c r="AS267" s="23" t="n"/>
       <c r="AT267" s="67" t="inlineStr"/>
     </row>
@@ -34174,21 +31350,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP268" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ268" s="65" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AR268" s="23" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="AP268" s="65" t="inlineStr"/>
+      <c r="AQ268" s="65" t="inlineStr"/>
+      <c r="AR268" s="23" t="inlineStr"/>
       <c r="AS268" s="23" t="n"/>
       <c r="AT268" s="67" t="inlineStr"/>
     </row>
@@ -34300,21 +31464,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP269" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ269" s="65" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AR269" s="23" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="AP269" s="65" t="inlineStr"/>
+      <c r="AQ269" s="65" t="inlineStr"/>
+      <c r="AR269" s="23" t="inlineStr"/>
       <c r="AS269" s="23" t="n"/>
       <c r="AT269" s="67" t="inlineStr"/>
     </row>
@@ -34426,21 +31578,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP270" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ270" s="65" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="AR270" s="23" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+      <c r="AP270" s="65" t="inlineStr"/>
+      <c r="AQ270" s="65" t="inlineStr"/>
+      <c r="AR270" s="23" t="inlineStr"/>
       <c r="AS270" s="23" t="n"/>
       <c r="AT270" s="67" t="inlineStr"/>
     </row>
@@ -34552,21 +31692,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP271" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ271" s="65" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="AR271" s="23" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
+      <c r="AP271" s="65" t="inlineStr"/>
+      <c r="AQ271" s="65" t="inlineStr"/>
+      <c r="AR271" s="23" t="inlineStr"/>
       <c r="AS271" s="23" t="n"/>
       <c r="AT271" s="67" t="inlineStr"/>
     </row>
@@ -34678,21 +31806,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP272" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ272" s="65" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="AR272" s="23" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
+      <c r="AP272" s="65" t="inlineStr"/>
+      <c r="AQ272" s="65" t="inlineStr"/>
+      <c r="AR272" s="23" t="inlineStr"/>
       <c r="AS272" s="23" t="n"/>
       <c r="AT272" s="67" t="inlineStr"/>
     </row>
@@ -34804,21 +31920,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP273" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ273" s="65" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="AR273" s="23" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+      <c r="AP273" s="65" t="inlineStr"/>
+      <c r="AQ273" s="65" t="inlineStr"/>
+      <c r="AR273" s="23" t="inlineStr"/>
       <c r="AS273" s="23" t="n"/>
       <c r="AT273" s="67" t="inlineStr"/>
     </row>
@@ -34930,21 +32034,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP274" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ274" s="65" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AR274" s="23" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="AP274" s="65" t="inlineStr"/>
+      <c r="AQ274" s="65" t="inlineStr"/>
+      <c r="AR274" s="23" t="inlineStr"/>
       <c r="AS274" s="23" t="n"/>
       <c r="AT274" s="67" t="inlineStr"/>
     </row>
@@ -35056,21 +32148,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP275" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ275" s="65" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AR275" s="23" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+      <c r="AP275" s="65" t="inlineStr"/>
+      <c r="AQ275" s="65" t="inlineStr"/>
+      <c r="AR275" s="23" t="inlineStr"/>
       <c r="AS275" s="23" t="n"/>
       <c r="AT275" s="67" t="inlineStr"/>
     </row>
@@ -35182,21 +32262,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP276" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ276" s="65" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="AR276" s="23" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="AP276" s="65" t="inlineStr"/>
+      <c r="AQ276" s="65" t="inlineStr"/>
+      <c r="AR276" s="23" t="inlineStr"/>
       <c r="AS276" s="23" t="n"/>
       <c r="AT276" s="67" t="inlineStr"/>
     </row>
@@ -35308,21 +32376,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP277" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ277" s="65" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AR277" s="23" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+      <c r="AP277" s="65" t="inlineStr"/>
+      <c r="AQ277" s="65" t="inlineStr"/>
+      <c r="AR277" s="23" t="inlineStr"/>
       <c r="AS277" s="23" t="n"/>
       <c r="AT277" s="67" t="inlineStr"/>
     </row>
@@ -35434,21 +32490,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP278" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ278" s="65" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="AR278" s="23" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
+      <c r="AP278" s="65" t="inlineStr"/>
+      <c r="AQ278" s="65" t="inlineStr"/>
+      <c r="AR278" s="23" t="inlineStr"/>
       <c r="AS278" s="23" t="n"/>
       <c r="AT278" s="67" t="inlineStr"/>
     </row>
@@ -35560,21 +32604,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP279" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ279" s="65" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="AR279" s="23" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
+      <c r="AP279" s="65" t="inlineStr"/>
+      <c r="AQ279" s="65" t="inlineStr"/>
+      <c r="AR279" s="23" t="inlineStr"/>
       <c r="AS279" s="23" t="n"/>
       <c r="AT279" s="67" t="inlineStr"/>
     </row>
@@ -35686,21 +32718,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP280" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ280" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR280" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP280" s="65" t="inlineStr"/>
+      <c r="AQ280" s="65" t="inlineStr"/>
+      <c r="AR280" s="23" t="inlineStr"/>
       <c r="AS280" s="23" t="n"/>
       <c r="AT280" s="67" t="inlineStr"/>
     </row>
@@ -35808,21 +32828,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP281" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ281" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AR281" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="AP281" s="65" t="inlineStr"/>
+      <c r="AQ281" s="65" t="inlineStr"/>
+      <c r="AR281" s="23" t="inlineStr"/>
       <c r="AS281" s="23" t="n"/>
       <c r="AT281" s="67" t="inlineStr"/>
     </row>
@@ -35930,21 +32938,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP282" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ282" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AR282" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP282" s="65" t="inlineStr"/>
+      <c r="AQ282" s="65" t="inlineStr"/>
+      <c r="AR282" s="23" t="inlineStr"/>
       <c r="AS282" s="23" t="n"/>
       <c r="AT282" s="67" t="inlineStr"/>
     </row>
@@ -36052,21 +33048,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP283" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ283" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR283" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP283" s="65" t="inlineStr"/>
+      <c r="AQ283" s="65" t="inlineStr"/>
+      <c r="AR283" s="23" t="inlineStr"/>
       <c r="AS283" s="23" t="n"/>
       <c r="AT283" s="67" t="inlineStr"/>
     </row>
@@ -36174,21 +33158,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP284" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ284" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR284" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP284" s="65" t="inlineStr"/>
+      <c r="AQ284" s="65" t="inlineStr"/>
+      <c r="AR284" s="23" t="inlineStr"/>
       <c r="AS284" s="23" t="n"/>
       <c r="AT284" s="67" t="inlineStr"/>
     </row>
@@ -36296,21 +33268,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP285" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ285" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR285" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP285" s="65" t="inlineStr"/>
+      <c r="AQ285" s="65" t="inlineStr"/>
+      <c r="AR285" s="23" t="inlineStr"/>
       <c r="AS285" s="23" t="n"/>
       <c r="AT285" s="67" t="inlineStr"/>
     </row>
@@ -36418,21 +33378,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP286" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ286" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AR286" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP286" s="65" t="inlineStr"/>
+      <c r="AQ286" s="65" t="inlineStr"/>
+      <c r="AR286" s="23" t="inlineStr"/>
       <c r="AS286" s="23" t="n"/>
       <c r="AT286" s="67" t="inlineStr"/>
     </row>
@@ -36548,21 +33496,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP287" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ287" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR287" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP287" s="65" t="inlineStr"/>
+      <c r="AQ287" s="65" t="inlineStr"/>
+      <c r="AR287" s="23" t="inlineStr"/>
       <c r="AS287" s="23" t="n"/>
       <c r="AT287" s="67" t="inlineStr"/>
     </row>
@@ -36674,21 +33610,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP288" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ288" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AR288" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="AP288" s="65" t="inlineStr"/>
+      <c r="AQ288" s="65" t="inlineStr"/>
+      <c r="AR288" s="23" t="inlineStr"/>
       <c r="AS288" s="23" t="n"/>
       <c r="AT288" s="67" t="inlineStr"/>
     </row>
@@ -36796,21 +33720,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP289" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ289" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR289" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP289" s="65" t="inlineStr"/>
+      <c r="AQ289" s="65" t="inlineStr"/>
+      <c r="AR289" s="23" t="inlineStr"/>
       <c r="AS289" s="23" t="n"/>
       <c r="AT289" s="67" t="inlineStr"/>
     </row>
@@ -36922,21 +33834,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP290" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ290" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR290" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP290" s="65" t="inlineStr"/>
+      <c r="AQ290" s="65" t="inlineStr"/>
+      <c r="AR290" s="23" t="inlineStr"/>
       <c r="AS290" s="23" t="n"/>
       <c r="AT290" s="67" t="inlineStr"/>
     </row>
@@ -37048,21 +33948,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP291" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ291" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR291" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP291" s="65" t="inlineStr"/>
+      <c r="AQ291" s="65" t="inlineStr"/>
+      <c r="AR291" s="23" t="inlineStr"/>
       <c r="AS291" s="23" t="n"/>
       <c r="AT291" s="67" t="inlineStr"/>
     </row>
@@ -37178,21 +34066,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP292" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ292" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR292" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP292" s="65" t="inlineStr"/>
+      <c r="AQ292" s="65" t="inlineStr"/>
+      <c r="AR292" s="23" t="inlineStr"/>
       <c r="AS292" s="23" t="n"/>
       <c r="AT292" s="67" t="inlineStr"/>
     </row>
@@ -37300,21 +34176,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP293" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ293" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AR293" s="23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="AP293" s="65" t="inlineStr"/>
+      <c r="AQ293" s="65" t="inlineStr"/>
+      <c r="AR293" s="23" t="inlineStr"/>
       <c r="AS293" s="23" t="n"/>
       <c r="AT293" s="67" t="inlineStr"/>
     </row>
@@ -37422,21 +34286,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP294" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ294" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AR294" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP294" s="65" t="inlineStr"/>
+      <c r="AQ294" s="65" t="inlineStr"/>
+      <c r="AR294" s="23" t="inlineStr"/>
       <c r="AS294" s="23" t="n"/>
       <c r="AT294" s="67" t="inlineStr"/>
     </row>
@@ -37548,21 +34400,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP295" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ295" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AR295" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP295" s="65" t="inlineStr"/>
+      <c r="AQ295" s="65" t="inlineStr"/>
+      <c r="AR295" s="23" t="inlineStr"/>
       <c r="AS295" s="23" t="n"/>
       <c r="AT295" s="67" t="inlineStr"/>
     </row>
@@ -37674,21 +34514,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP296" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ296" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AR296" s="23" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="AP296" s="65" t="inlineStr"/>
+      <c r="AQ296" s="65" t="inlineStr"/>
+      <c r="AR296" s="23" t="inlineStr"/>
       <c r="AS296" s="23" t="n"/>
       <c r="AT296" s="67" t="inlineStr"/>
     </row>
@@ -37800,21 +34628,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP297" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ297" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AR297" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP297" s="65" t="inlineStr"/>
+      <c r="AQ297" s="65" t="inlineStr"/>
+      <c r="AR297" s="23" t="inlineStr"/>
       <c r="AS297" s="23" t="n"/>
       <c r="AT297" s="67" t="inlineStr"/>
     </row>
@@ -37930,21 +34746,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AP298" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ298" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AR298" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AP298" s="65" t="inlineStr"/>
+      <c r="AQ298" s="65" t="inlineStr"/>
+      <c r="AR298" s="23" t="inlineStr"/>
       <c r="AS298" s="23" t="n"/>
       <c r="AT298" s="67" t="inlineStr"/>
     </row>
